--- a/vignettes/vignette-2/tail_exceedance_plot_data.xlsx
+++ b/vignettes/vignette-2/tail_exceedance_plot_data.xlsx
@@ -5341,7 +5341,7 @@
         </is>
       </c>
       <c r="B379" t="n">
-        <v>9.3e-05</v>
+        <v>9.399999999999999e-05</v>
       </c>
       <c r="C379" t="n">
         <v>0.99734</v>
@@ -5393,7 +5393,7 @@
         </is>
       </c>
       <c r="B383" t="n">
-        <v>0.001491</v>
+        <v>0.001496</v>
       </c>
       <c r="C383" t="n">
         <v>0.986702</v>
@@ -5406,7 +5406,7 @@
         </is>
       </c>
       <c r="B384" t="n">
-        <v>0.001691</v>
+        <v>0.001695</v>
       </c>
       <c r="C384" t="n">
         <v>0.984043</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="B385" t="n">
-        <v>0.001724</v>
+        <v>0.001731</v>
       </c>
       <c r="C385" t="n">
         <v>0.981383</v>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="B386" t="n">
-        <v>0.001899</v>
+        <v>0.001921</v>
       </c>
       <c r="C386" t="n">
         <v>0.978723</v>
@@ -5445,7 +5445,7 @@
         </is>
       </c>
       <c r="B387" t="n">
-        <v>0.002427</v>
+        <v>0.002439</v>
       </c>
       <c r="C387" t="n">
         <v>0.976064</v>
@@ -5458,7 +5458,7 @@
         </is>
       </c>
       <c r="B388" t="n">
-        <v>0.002559</v>
+        <v>0.00258</v>
       </c>
       <c r="C388" t="n">
         <v>0.973404</v>
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="B389" t="n">
-        <v>0.002861</v>
+        <v>0.002862</v>
       </c>
       <c r="C389" t="n">
         <v>0.970745</v>
@@ -5484,7 +5484,7 @@
         </is>
       </c>
       <c r="B390" t="n">
-        <v>0.003128</v>
+        <v>0.003149</v>
       </c>
       <c r="C390" t="n">
         <v>0.968085</v>
@@ -5497,7 +5497,7 @@
         </is>
       </c>
       <c r="B391" t="n">
-        <v>0.003671</v>
+        <v>0.003708</v>
       </c>
       <c r="C391" t="n">
         <v>0.965426</v>
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="B392" t="n">
-        <v>0.003702</v>
+        <v>0.003786</v>
       </c>
       <c r="C392" t="n">
         <v>0.962766</v>
@@ -5523,7 +5523,7 @@
         </is>
       </c>
       <c r="B393" t="n">
-        <v>0.003806</v>
+        <v>0.003832</v>
       </c>
       <c r="C393" t="n">
         <v>0.960106</v>
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c r="B394" t="n">
-        <v>0.004001</v>
+        <v>0.003993</v>
       </c>
       <c r="C394" t="n">
         <v>0.957447</v>
@@ -5549,7 +5549,7 @@
         </is>
       </c>
       <c r="B395" t="n">
-        <v>0.004296</v>
+        <v>0.004311</v>
       </c>
       <c r="C395" t="n">
         <v>0.9547870000000001</v>
@@ -5562,7 +5562,7 @@
         </is>
       </c>
       <c r="B396" t="n">
-        <v>0.004312</v>
+        <v>0.004337</v>
       </c>
       <c r="C396" t="n">
         <v>0.952128</v>
@@ -5575,7 +5575,7 @@
         </is>
       </c>
       <c r="B397" t="n">
-        <v>0.004313</v>
+        <v>0.004344</v>
       </c>
       <c r="C397" t="n">
         <v>0.949468</v>
@@ -5588,7 +5588,7 @@
         </is>
       </c>
       <c r="B398" t="n">
-        <v>0.004382</v>
+        <v>0.004472</v>
       </c>
       <c r="C398" t="n">
         <v>0.946809</v>
@@ -5601,7 +5601,7 @@
         </is>
       </c>
       <c r="B399" t="n">
-        <v>0.004505</v>
+        <v>0.004566</v>
       </c>
       <c r="C399" t="n">
         <v>0.944149</v>
@@ -5614,7 +5614,7 @@
         </is>
       </c>
       <c r="B400" t="n">
-        <v>0.004789</v>
+        <v>0.004792</v>
       </c>
       <c r="C400" t="n">
         <v>0.941489</v>
@@ -5627,7 +5627,7 @@
         </is>
       </c>
       <c r="B401" t="n">
-        <v>0.004928</v>
+        <v>0.004943</v>
       </c>
       <c r="C401" t="n">
         <v>0.9388300000000001</v>
@@ -5640,7 +5640,7 @@
         </is>
       </c>
       <c r="B402" t="n">
-        <v>0.004939</v>
+        <v>0.004963</v>
       </c>
       <c r="C402" t="n">
         <v>0.9361699999999999</v>
@@ -5653,7 +5653,7 @@
         </is>
       </c>
       <c r="B403" t="n">
-        <v>0.005352</v>
+        <v>0.005363</v>
       </c>
       <c r="C403" t="n">
         <v>0.933511</v>
@@ -5666,7 +5666,7 @@
         </is>
       </c>
       <c r="B404" t="n">
-        <v>0.005354</v>
+        <v>0.005371</v>
       </c>
       <c r="C404" t="n">
         <v>0.930851</v>
@@ -5679,7 +5679,7 @@
         </is>
       </c>
       <c r="B405" t="n">
-        <v>0.005821</v>
+        <v>0.005975</v>
       </c>
       <c r="C405" t="n">
         <v>0.928191</v>
@@ -5705,7 +5705,7 @@
         </is>
       </c>
       <c r="B407" t="n">
-        <v>0.00691</v>
+        <v>0.006911</v>
       </c>
       <c r="C407" t="n">
         <v>0.922872</v>
@@ -5718,7 +5718,7 @@
         </is>
       </c>
       <c r="B408" t="n">
-        <v>0.007213</v>
+        <v>0.00727</v>
       </c>
       <c r="C408" t="n">
         <v>0.9202129999999999</v>
@@ -5731,7 +5731,7 @@
         </is>
       </c>
       <c r="B409" t="n">
-        <v>0.007399</v>
+        <v>0.007387</v>
       </c>
       <c r="C409" t="n">
         <v>0.917553</v>
@@ -5744,7 +5744,7 @@
         </is>
       </c>
       <c r="B410" t="n">
-        <v>0.007497</v>
+        <v>0.007495</v>
       </c>
       <c r="C410" t="n">
         <v>0.914894</v>
@@ -5757,7 +5757,7 @@
         </is>
       </c>
       <c r="B411" t="n">
-        <v>0.00751</v>
+        <v>0.007554</v>
       </c>
       <c r="C411" t="n">
         <v>0.912234</v>
@@ -5770,7 +5770,7 @@
         </is>
       </c>
       <c r="B412" t="n">
-        <v>0.007613</v>
+        <v>0.007626</v>
       </c>
       <c r="C412" t="n">
         <v>0.909574</v>
@@ -5783,7 +5783,7 @@
         </is>
       </c>
       <c r="B413" t="n">
-        <v>0.007849</v>
+        <v>0.007839</v>
       </c>
       <c r="C413" t="n">
         <v>0.906915</v>
@@ -5796,7 +5796,7 @@
         </is>
       </c>
       <c r="B414" t="n">
-        <v>0.007927999999999999</v>
+        <v>0.007932</v>
       </c>
       <c r="C414" t="n">
         <v>0.904255</v>
@@ -5809,7 +5809,7 @@
         </is>
       </c>
       <c r="B415" t="n">
-        <v>0.007952000000000001</v>
+        <v>0.008023000000000001</v>
       </c>
       <c r="C415" t="n">
         <v>0.901596</v>
@@ -5822,7 +5822,7 @@
         </is>
       </c>
       <c r="B416" t="n">
-        <v>0.008082000000000001</v>
+        <v>0.008159</v>
       </c>
       <c r="C416" t="n">
         <v>0.898936</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="B417" t="n">
-        <v>0.008734</v>
+        <v>0.008749</v>
       </c>
       <c r="C417" t="n">
         <v>0.896277</v>
@@ -5848,7 +5848,7 @@
         </is>
       </c>
       <c r="B418" t="n">
-        <v>0.008758999999999999</v>
+        <v>0.008789</v>
       </c>
       <c r="C418" t="n">
         <v>0.893617</v>
@@ -5861,7 +5861,7 @@
         </is>
       </c>
       <c r="B419" t="n">
-        <v>0.008763</v>
+        <v>0.008874999999999999</v>
       </c>
       <c r="C419" t="n">
         <v>0.890957</v>
@@ -5874,7 +5874,7 @@
         </is>
       </c>
       <c r="B420" t="n">
-        <v>0.008879</v>
+        <v>0.008895999999999999</v>
       </c>
       <c r="C420" t="n">
         <v>0.888298</v>
@@ -5887,7 +5887,7 @@
         </is>
       </c>
       <c r="B421" t="n">
-        <v>0.009001</v>
+        <v>0.009122999999999999</v>
       </c>
       <c r="C421" t="n">
         <v>0.885638</v>
@@ -5900,7 +5900,7 @@
         </is>
       </c>
       <c r="B422" t="n">
-        <v>0.009002</v>
+        <v>0.009129</v>
       </c>
       <c r="C422" t="n">
         <v>0.882979</v>
@@ -5913,7 +5913,7 @@
         </is>
       </c>
       <c r="B423" t="n">
-        <v>0.009046999999999999</v>
+        <v>0.009169999999999999</v>
       </c>
       <c r="C423" t="n">
         <v>0.880319</v>
@@ -5926,7 +5926,7 @@
         </is>
       </c>
       <c r="B424" t="n">
-        <v>0.009304</v>
+        <v>0.009309</v>
       </c>
       <c r="C424" t="n">
         <v>0.87766</v>
@@ -5939,7 +5939,7 @@
         </is>
       </c>
       <c r="B425" t="n">
-        <v>0.009421000000000001</v>
+        <v>0.009433</v>
       </c>
       <c r="C425" t="n">
         <v>0.875</v>
@@ -5952,7 +5952,7 @@
         </is>
       </c>
       <c r="B426" t="n">
-        <v>0.009601999999999999</v>
+        <v>0.009632999999999999</v>
       </c>
       <c r="C426" t="n">
         <v>0.87234</v>
@@ -5965,7 +5965,7 @@
         </is>
       </c>
       <c r="B427" t="n">
-        <v>0.010054</v>
+        <v>0.010085</v>
       </c>
       <c r="C427" t="n">
         <v>0.869681</v>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="B428" t="n">
-        <v>0.010588</v>
+        <v>0.010592</v>
       </c>
       <c r="C428" t="n">
         <v>0.867021</v>
@@ -5991,7 +5991,7 @@
         </is>
       </c>
       <c r="B429" t="n">
-        <v>0.010737</v>
+        <v>0.010778</v>
       </c>
       <c r="C429" t="n">
         <v>0.864362</v>
@@ -6004,7 +6004,7 @@
         </is>
       </c>
       <c r="B430" t="n">
-        <v>0.01088</v>
+        <v>0.01087</v>
       </c>
       <c r="C430" t="n">
         <v>0.861702</v>
@@ -6017,7 +6017,7 @@
         </is>
       </c>
       <c r="B431" t="n">
-        <v>0.01092</v>
+        <v>0.011144</v>
       </c>
       <c r="C431" t="n">
         <v>0.859043</v>
@@ -6030,7 +6030,7 @@
         </is>
       </c>
       <c r="B432" t="n">
-        <v>0.011191</v>
+        <v>0.011177</v>
       </c>
       <c r="C432" t="n">
         <v>0.856383</v>
@@ -6043,7 +6043,7 @@
         </is>
       </c>
       <c r="B433" t="n">
-        <v>0.011236</v>
+        <v>0.011241</v>
       </c>
       <c r="C433" t="n">
         <v>0.853723</v>
@@ -6056,7 +6056,7 @@
         </is>
       </c>
       <c r="B434" t="n">
-        <v>0.011556</v>
+        <v>0.011778</v>
       </c>
       <c r="C434" t="n">
         <v>0.851064</v>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="B435" t="n">
-        <v>0.011806</v>
+        <v>0.011825</v>
       </c>
       <c r="C435" t="n">
         <v>0.848404</v>
@@ -6082,7 +6082,7 @@
         </is>
       </c>
       <c r="B436" t="n">
-        <v>0.011988</v>
+        <v>0.011981</v>
       </c>
       <c r="C436" t="n">
         <v>0.845745</v>
@@ -6095,7 +6095,7 @@
         </is>
       </c>
       <c r="B437" t="n">
-        <v>0.012285</v>
+        <v>0.012367</v>
       </c>
       <c r="C437" t="n">
         <v>0.843085</v>
@@ -6108,7 +6108,7 @@
         </is>
       </c>
       <c r="B438" t="n">
-        <v>0.012473</v>
+        <v>0.012512</v>
       </c>
       <c r="C438" t="n">
         <v>0.840426</v>
@@ -6121,7 +6121,7 @@
         </is>
       </c>
       <c r="B439" t="n">
-        <v>0.012484</v>
+        <v>0.012552</v>
       </c>
       <c r="C439" t="n">
         <v>0.837766</v>
@@ -6134,7 +6134,7 @@
         </is>
       </c>
       <c r="B440" t="n">
-        <v>0.012996</v>
+        <v>0.012991</v>
       </c>
       <c r="C440" t="n">
         <v>0.835106</v>
@@ -6147,7 +6147,7 @@
         </is>
       </c>
       <c r="B441" t="n">
-        <v>0.013003</v>
+        <v>0.013081</v>
       </c>
       <c r="C441" t="n">
         <v>0.832447</v>
@@ -6160,7 +6160,7 @@
         </is>
       </c>
       <c r="B442" t="n">
-        <v>0.01323</v>
+        <v>0.013275</v>
       </c>
       <c r="C442" t="n">
         <v>0.8297870000000001</v>
@@ -6173,7 +6173,7 @@
         </is>
       </c>
       <c r="B443" t="n">
-        <v>0.013273</v>
+        <v>0.013561</v>
       </c>
       <c r="C443" t="n">
         <v>0.827128</v>
@@ -6186,7 +6186,7 @@
         </is>
       </c>
       <c r="B444" t="n">
-        <v>0.013552</v>
+        <v>0.013802</v>
       </c>
       <c r="C444" t="n">
         <v>0.824468</v>
@@ -6199,7 +6199,7 @@
         </is>
       </c>
       <c r="B445" t="n">
-        <v>0.013768</v>
+        <v>0.01402</v>
       </c>
       <c r="C445" t="n">
         <v>0.821809</v>
@@ -6212,7 +6212,7 @@
         </is>
       </c>
       <c r="B446" t="n">
-        <v>0.013937</v>
+        <v>0.014163</v>
       </c>
       <c r="C446" t="n">
         <v>0.819149</v>
@@ -6225,7 +6225,7 @@
         </is>
       </c>
       <c r="B447" t="n">
-        <v>0.014221</v>
+        <v>0.014244</v>
       </c>
       <c r="C447" t="n">
         <v>0.816489</v>
@@ -6238,7 +6238,7 @@
         </is>
       </c>
       <c r="B448" t="n">
-        <v>0.01427</v>
+        <v>0.014333</v>
       </c>
       <c r="C448" t="n">
         <v>0.8138300000000001</v>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="B449" t="n">
-        <v>0.014454</v>
+        <v>0.014438</v>
       </c>
       <c r="C449" t="n">
         <v>0.8111699999999999</v>
@@ -6264,7 +6264,7 @@
         </is>
       </c>
       <c r="B450" t="n">
-        <v>0.014459</v>
+        <v>0.014452</v>
       </c>
       <c r="C450" t="n">
         <v>0.808511</v>
@@ -6277,7 +6277,7 @@
         </is>
       </c>
       <c r="B451" t="n">
-        <v>0.014876</v>
+        <v>0.014932</v>
       </c>
       <c r="C451" t="n">
         <v>0.805851</v>
@@ -6290,7 +6290,7 @@
         </is>
       </c>
       <c r="B452" t="n">
-        <v>0.015037</v>
+        <v>0.015105</v>
       </c>
       <c r="C452" t="n">
         <v>0.803191</v>
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="B453" t="n">
-        <v>0.015124</v>
+        <v>0.01517</v>
       </c>
       <c r="C453" t="n">
         <v>0.800532</v>
@@ -6316,7 +6316,7 @@
         </is>
       </c>
       <c r="B454" t="n">
-        <v>0.01565</v>
+        <v>0.015673</v>
       </c>
       <c r="C454" t="n">
         <v>0.797872</v>
@@ -6329,7 +6329,7 @@
         </is>
       </c>
       <c r="B455" t="n">
-        <v>0.015798</v>
+        <v>0.015814</v>
       </c>
       <c r="C455" t="n">
         <v>0.7952129999999999</v>
@@ -6342,7 +6342,7 @@
         </is>
       </c>
       <c r="B456" t="n">
-        <v>0.015854</v>
+        <v>0.015946</v>
       </c>
       <c r="C456" t="n">
         <v>0.792553</v>
@@ -6355,7 +6355,7 @@
         </is>
       </c>
       <c r="B457" t="n">
-        <v>0.01633</v>
+        <v>0.016375</v>
       </c>
       <c r="C457" t="n">
         <v>0.789894</v>
@@ -6368,7 +6368,7 @@
         </is>
       </c>
       <c r="B458" t="n">
-        <v>0.016429</v>
+        <v>0.016467</v>
       </c>
       <c r="C458" t="n">
         <v>0.787234</v>
@@ -6381,7 +6381,7 @@
         </is>
       </c>
       <c r="B459" t="n">
-        <v>0.016661</v>
+        <v>0.016718</v>
       </c>
       <c r="C459" t="n">
         <v>0.784574</v>
@@ -6394,7 +6394,7 @@
         </is>
       </c>
       <c r="B460" t="n">
-        <v>0.016924</v>
+        <v>0.016897</v>
       </c>
       <c r="C460" t="n">
         <v>0.781915</v>
@@ -6407,7 +6407,7 @@
         </is>
       </c>
       <c r="B461" t="n">
-        <v>0.016983</v>
+        <v>0.016959</v>
       </c>
       <c r="C461" t="n">
         <v>0.779255</v>
@@ -6420,7 +6420,7 @@
         </is>
       </c>
       <c r="B462" t="n">
-        <v>0.01714</v>
+        <v>0.01728</v>
       </c>
       <c r="C462" t="n">
         <v>0.776596</v>
@@ -6433,7 +6433,7 @@
         </is>
       </c>
       <c r="B463" t="n">
-        <v>0.01734</v>
+        <v>0.017403</v>
       </c>
       <c r="C463" t="n">
         <v>0.773936</v>
@@ -6446,7 +6446,7 @@
         </is>
       </c>
       <c r="B464" t="n">
-        <v>0.018101</v>
+        <v>0.018074</v>
       </c>
       <c r="C464" t="n">
         <v>0.771277</v>
@@ -6459,7 +6459,7 @@
         </is>
       </c>
       <c r="B465" t="n">
-        <v>0.018362</v>
+        <v>0.018371</v>
       </c>
       <c r="C465" t="n">
         <v>0.768617</v>
@@ -6472,7 +6472,7 @@
         </is>
       </c>
       <c r="B466" t="n">
-        <v>0.018649</v>
+        <v>0.018835</v>
       </c>
       <c r="C466" t="n">
         <v>0.765957</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="B467" t="n">
-        <v>0.019204</v>
+        <v>0.019189</v>
       </c>
       <c r="C467" t="n">
         <v>0.763298</v>
@@ -6498,7 +6498,7 @@
         </is>
       </c>
       <c r="B468" t="n">
-        <v>0.019287</v>
+        <v>0.019331</v>
       </c>
       <c r="C468" t="n">
         <v>0.760638</v>
@@ -6511,7 +6511,7 @@
         </is>
       </c>
       <c r="B469" t="n">
-        <v>0.019552</v>
+        <v>0.019601</v>
       </c>
       <c r="C469" t="n">
         <v>0.757979</v>
@@ -6524,7 +6524,7 @@
         </is>
       </c>
       <c r="B470" t="n">
-        <v>0.019606</v>
+        <v>0.019709</v>
       </c>
       <c r="C470" t="n">
         <v>0.755319</v>
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="B471" t="n">
-        <v>0.019623</v>
+        <v>0.019728</v>
       </c>
       <c r="C471" t="n">
         <v>0.75266</v>
@@ -6550,7 +6550,7 @@
         </is>
       </c>
       <c r="B472" t="n">
-        <v>0.019671</v>
+        <v>0.019801</v>
       </c>
       <c r="C472" t="n">
         <v>0.75</v>
@@ -6563,7 +6563,7 @@
         </is>
       </c>
       <c r="B473" t="n">
-        <v>0.020622</v>
+        <v>0.020789</v>
       </c>
       <c r="C473" t="n">
         <v>0.74734</v>
@@ -6576,7 +6576,7 @@
         </is>
       </c>
       <c r="B474" t="n">
-        <v>0.020723</v>
+        <v>0.020819</v>
       </c>
       <c r="C474" t="n">
         <v>0.744681</v>
@@ -6589,7 +6589,7 @@
         </is>
       </c>
       <c r="B475" t="n">
-        <v>0.020798</v>
+        <v>0.020923</v>
       </c>
       <c r="C475" t="n">
         <v>0.742021</v>
@@ -6602,7 +6602,7 @@
         </is>
       </c>
       <c r="B476" t="n">
-        <v>0.021172</v>
+        <v>0.021177</v>
       </c>
       <c r="C476" t="n">
         <v>0.739362</v>
@@ -6615,7 +6615,7 @@
         </is>
       </c>
       <c r="B477" t="n">
-        <v>0.021226</v>
+        <v>0.021237</v>
       </c>
       <c r="C477" t="n">
         <v>0.736702</v>
@@ -6628,7 +6628,7 @@
         </is>
       </c>
       <c r="B478" t="n">
-        <v>0.021295</v>
+        <v>0.021496</v>
       </c>
       <c r="C478" t="n">
         <v>0.734043</v>
@@ -6641,7 +6641,7 @@
         </is>
       </c>
       <c r="B479" t="n">
-        <v>0.021358</v>
+        <v>0.021694</v>
       </c>
       <c r="C479" t="n">
         <v>0.731383</v>
@@ -6654,7 +6654,7 @@
         </is>
       </c>
       <c r="B480" t="n">
-        <v>0.021692</v>
+        <v>0.02177</v>
       </c>
       <c r="C480" t="n">
         <v>0.728723</v>
@@ -6667,7 +6667,7 @@
         </is>
       </c>
       <c r="B481" t="n">
-        <v>0.021953</v>
+        <v>0.021933</v>
       </c>
       <c r="C481" t="n">
         <v>0.726064</v>
@@ -6680,7 +6680,7 @@
         </is>
       </c>
       <c r="B482" t="n">
-        <v>0.022102</v>
+        <v>0.022286</v>
       </c>
       <c r="C482" t="n">
         <v>0.723404</v>
@@ -6693,7 +6693,7 @@
         </is>
       </c>
       <c r="B483" t="n">
-        <v>0.022664</v>
+        <v>0.022777</v>
       </c>
       <c r="C483" t="n">
         <v>0.720745</v>
@@ -6706,7 +6706,7 @@
         </is>
       </c>
       <c r="B484" t="n">
-        <v>0.022702</v>
+        <v>0.022892</v>
       </c>
       <c r="C484" t="n">
         <v>0.718085</v>
@@ -6719,7 +6719,7 @@
         </is>
       </c>
       <c r="B485" t="n">
-        <v>0.022803</v>
+        <v>0.022945</v>
       </c>
       <c r="C485" t="n">
         <v>0.715426</v>
@@ -6732,7 +6732,7 @@
         </is>
       </c>
       <c r="B486" t="n">
-        <v>0.02283</v>
+        <v>0.022978</v>
       </c>
       <c r="C486" t="n">
         <v>0.712766</v>
@@ -6745,7 +6745,7 @@
         </is>
       </c>
       <c r="B487" t="n">
-        <v>0.022923</v>
+        <v>0.023137</v>
       </c>
       <c r="C487" t="n">
         <v>0.710106</v>
@@ -6758,7 +6758,7 @@
         </is>
       </c>
       <c r="B488" t="n">
-        <v>0.023302</v>
+        <v>0.023325</v>
       </c>
       <c r="C488" t="n">
         <v>0.707447</v>
@@ -6771,7 +6771,7 @@
         </is>
       </c>
       <c r="B489" t="n">
-        <v>0.023534</v>
+        <v>0.023701</v>
       </c>
       <c r="C489" t="n">
         <v>0.7047870000000001</v>
@@ -6784,7 +6784,7 @@
         </is>
       </c>
       <c r="B490" t="n">
-        <v>0.023737</v>
+        <v>0.023811</v>
       </c>
       <c r="C490" t="n">
         <v>0.702128</v>
@@ -6797,7 +6797,7 @@
         </is>
       </c>
       <c r="B491" t="n">
-        <v>0.023979</v>
+        <v>0.023975</v>
       </c>
       <c r="C491" t="n">
         <v>0.699468</v>
@@ -6810,7 +6810,7 @@
         </is>
       </c>
       <c r="B492" t="n">
-        <v>0.02439</v>
+        <v>0.024395</v>
       </c>
       <c r="C492" t="n">
         <v>0.696809</v>
@@ -6823,7 +6823,7 @@
         </is>
       </c>
       <c r="B493" t="n">
-        <v>0.024399</v>
+        <v>0.024435</v>
       </c>
       <c r="C493" t="n">
         <v>0.694149</v>
@@ -6836,7 +6836,7 @@
         </is>
       </c>
       <c r="B494" t="n">
-        <v>0.024401</v>
+        <v>0.024459</v>
       </c>
       <c r="C494" t="n">
         <v>0.691489</v>
@@ -6849,7 +6849,7 @@
         </is>
       </c>
       <c r="B495" t="n">
-        <v>0.024438</v>
+        <v>0.024529</v>
       </c>
       <c r="C495" t="n">
         <v>0.6888300000000001</v>
@@ -6862,7 +6862,7 @@
         </is>
       </c>
       <c r="B496" t="n">
-        <v>0.024517</v>
+        <v>0.024543</v>
       </c>
       <c r="C496" t="n">
         <v>0.6861699999999999</v>
@@ -6875,7 +6875,7 @@
         </is>
       </c>
       <c r="B497" t="n">
-        <v>0.024703</v>
+        <v>0.024907</v>
       </c>
       <c r="C497" t="n">
         <v>0.683511</v>
@@ -6888,7 +6888,7 @@
         </is>
       </c>
       <c r="B498" t="n">
-        <v>0.024978</v>
+        <v>0.025038</v>
       </c>
       <c r="C498" t="n">
         <v>0.680851</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="B499" t="n">
-        <v>0.025286</v>
+        <v>0.025324</v>
       </c>
       <c r="C499" t="n">
         <v>0.678191</v>
@@ -6914,7 +6914,7 @@
         </is>
       </c>
       <c r="B500" t="n">
-        <v>0.025907</v>
+        <v>0.025881</v>
       </c>
       <c r="C500" t="n">
         <v>0.675532</v>
@@ -6927,7 +6927,7 @@
         </is>
       </c>
       <c r="B501" t="n">
-        <v>0.025935</v>
+        <v>0.026098</v>
       </c>
       <c r="C501" t="n">
         <v>0.672872</v>
@@ -6940,7 +6940,7 @@
         </is>
       </c>
       <c r="B502" t="n">
-        <v>0.026445</v>
+        <v>0.026594</v>
       </c>
       <c r="C502" t="n">
         <v>0.6702129999999999</v>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="B503" t="n">
-        <v>0.026528</v>
+        <v>0.026769</v>
       </c>
       <c r="C503" t="n">
         <v>0.667553</v>
@@ -6966,7 +6966,7 @@
         </is>
       </c>
       <c r="B504" t="n">
-        <v>0.026823</v>
+        <v>0.02704</v>
       </c>
       <c r="C504" t="n">
         <v>0.664894</v>
@@ -6979,7 +6979,7 @@
         </is>
       </c>
       <c r="B505" t="n">
-        <v>0.027114</v>
+        <v>0.027065</v>
       </c>
       <c r="C505" t="n">
         <v>0.662234</v>
@@ -6992,7 +6992,7 @@
         </is>
       </c>
       <c r="B506" t="n">
-        <v>0.027828</v>
+        <v>0.027823</v>
       </c>
       <c r="C506" t="n">
         <v>0.659574</v>
@@ -7005,7 +7005,7 @@
         </is>
       </c>
       <c r="B507" t="n">
-        <v>0.027965</v>
+        <v>0.027949</v>
       </c>
       <c r="C507" t="n">
         <v>0.656915</v>
@@ -7018,7 +7018,7 @@
         </is>
       </c>
       <c r="B508" t="n">
-        <v>0.028201</v>
+        <v>0.02835</v>
       </c>
       <c r="C508" t="n">
         <v>0.654255</v>
@@ -7031,7 +7031,7 @@
         </is>
       </c>
       <c r="B509" t="n">
-        <v>0.028375</v>
+        <v>0.028395</v>
       </c>
       <c r="C509" t="n">
         <v>0.651596</v>
@@ -7044,7 +7044,7 @@
         </is>
       </c>
       <c r="B510" t="n">
-        <v>0.028664</v>
+        <v>0.028767</v>
       </c>
       <c r="C510" t="n">
         <v>0.648936</v>
@@ -7057,7 +7057,7 @@
         </is>
       </c>
       <c r="B511" t="n">
-        <v>0.028928</v>
+        <v>0.028916</v>
       </c>
       <c r="C511" t="n">
         <v>0.646277</v>
@@ -7070,7 +7070,7 @@
         </is>
       </c>
       <c r="B512" t="n">
-        <v>0.02968</v>
+        <v>0.029699</v>
       </c>
       <c r="C512" t="n">
         <v>0.643617</v>
@@ -7083,7 +7083,7 @@
         </is>
       </c>
       <c r="B513" t="n">
-        <v>0.029774</v>
+        <v>0.029782</v>
       </c>
       <c r="C513" t="n">
         <v>0.640957</v>
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="B514" t="n">
-        <v>0.029821</v>
+        <v>0.029879</v>
       </c>
       <c r="C514" t="n">
         <v>0.638298</v>
@@ -7109,7 +7109,7 @@
         </is>
       </c>
       <c r="B515" t="n">
-        <v>0.029862</v>
+        <v>0.029933</v>
       </c>
       <c r="C515" t="n">
         <v>0.635638</v>
@@ -7122,7 +7122,7 @@
         </is>
       </c>
       <c r="B516" t="n">
-        <v>0.029914</v>
+        <v>0.029986</v>
       </c>
       <c r="C516" t="n">
         <v>0.632979</v>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="B517" t="n">
-        <v>0.03014</v>
+        <v>0.030253</v>
       </c>
       <c r="C517" t="n">
         <v>0.630319</v>
@@ -7148,7 +7148,7 @@
         </is>
       </c>
       <c r="B518" t="n">
-        <v>0.030266</v>
+        <v>0.030322</v>
       </c>
       <c r="C518" t="n">
         <v>0.62766</v>
@@ -7161,7 +7161,7 @@
         </is>
       </c>
       <c r="B519" t="n">
-        <v>0.030638</v>
+        <v>0.030689</v>
       </c>
       <c r="C519" t="n">
         <v>0.625</v>
@@ -7174,7 +7174,7 @@
         </is>
       </c>
       <c r="B520" t="n">
-        <v>0.030645</v>
+        <v>0.030981</v>
       </c>
       <c r="C520" t="n">
         <v>0.62234</v>
@@ -7187,7 +7187,7 @@
         </is>
       </c>
       <c r="B521" t="n">
-        <v>0.030936</v>
+        <v>0.031026</v>
       </c>
       <c r="C521" t="n">
         <v>0.619681</v>
@@ -7200,7 +7200,7 @@
         </is>
       </c>
       <c r="B522" t="n">
-        <v>0.030952</v>
+        <v>0.031242</v>
       </c>
       <c r="C522" t="n">
         <v>0.617021</v>
@@ -7213,7 +7213,7 @@
         </is>
       </c>
       <c r="B523" t="n">
-        <v>0.031155</v>
+        <v>0.031257</v>
       </c>
       <c r="C523" t="n">
         <v>0.614362</v>
@@ -7226,7 +7226,7 @@
         </is>
       </c>
       <c r="B524" t="n">
-        <v>0.031373</v>
+        <v>0.031329</v>
       </c>
       <c r="C524" t="n">
         <v>0.611702</v>
@@ -7239,7 +7239,7 @@
         </is>
       </c>
       <c r="B525" t="n">
-        <v>0.031423</v>
+        <v>0.031495</v>
       </c>
       <c r="C525" t="n">
         <v>0.609043</v>
@@ -7252,7 +7252,7 @@
         </is>
       </c>
       <c r="B526" t="n">
-        <v>0.031629</v>
+        <v>0.031718</v>
       </c>
       <c r="C526" t="n">
         <v>0.606383</v>
@@ -7265,7 +7265,7 @@
         </is>
       </c>
       <c r="B527" t="n">
-        <v>0.031864</v>
+        <v>0.031921</v>
       </c>
       <c r="C527" t="n">
         <v>0.603723</v>
@@ -7278,7 +7278,7 @@
         </is>
       </c>
       <c r="B528" t="n">
-        <v>0.032046</v>
+        <v>0.032158</v>
       </c>
       <c r="C528" t="n">
         <v>0.601064</v>
@@ -7291,7 +7291,7 @@
         </is>
       </c>
       <c r="B529" t="n">
-        <v>0.032467</v>
+        <v>0.032463</v>
       </c>
       <c r="C529" t="n">
         <v>0.598404</v>
@@ -7304,7 +7304,7 @@
         </is>
       </c>
       <c r="B530" t="n">
-        <v>0.032696</v>
+        <v>0.032788</v>
       </c>
       <c r="C530" t="n">
         <v>0.595745</v>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="B531" t="n">
-        <v>0.032968</v>
+        <v>0.033219</v>
       </c>
       <c r="C531" t="n">
         <v>0.593085</v>
@@ -7330,7 +7330,7 @@
         </is>
       </c>
       <c r="B532" t="n">
-        <v>0.033481</v>
+        <v>0.033771</v>
       </c>
       <c r="C532" t="n">
         <v>0.590426</v>
@@ -7343,7 +7343,7 @@
         </is>
       </c>
       <c r="B533" t="n">
-        <v>0.033592</v>
+        <v>0.033811</v>
       </c>
       <c r="C533" t="n">
         <v>0.587766</v>
@@ -7356,7 +7356,7 @@
         </is>
       </c>
       <c r="B534" t="n">
-        <v>0.03378</v>
+        <v>0.03384</v>
       </c>
       <c r="C534" t="n">
         <v>0.585106</v>
@@ -7369,7 +7369,7 @@
         </is>
       </c>
       <c r="B535" t="n">
-        <v>0.034163</v>
+        <v>0.034137</v>
       </c>
       <c r="C535" t="n">
         <v>0.582447</v>
@@ -7382,7 +7382,7 @@
         </is>
       </c>
       <c r="B536" t="n">
-        <v>0.034185</v>
+        <v>0.034181</v>
       </c>
       <c r="C536" t="n">
         <v>0.5797870000000001</v>
@@ -7395,7 +7395,7 @@
         </is>
       </c>
       <c r="B537" t="n">
-        <v>0.034222</v>
+        <v>0.034423</v>
       </c>
       <c r="C537" t="n">
         <v>0.577128</v>
@@ -7408,7 +7408,7 @@
         </is>
       </c>
       <c r="B538" t="n">
-        <v>0.03427</v>
+        <v>0.03445</v>
       </c>
       <c r="C538" t="n">
         <v>0.574468</v>
@@ -7421,7 +7421,7 @@
         </is>
       </c>
       <c r="B539" t="n">
-        <v>0.034302</v>
+        <v>0.034455</v>
       </c>
       <c r="C539" t="n">
         <v>0.571809</v>
@@ -7434,7 +7434,7 @@
         </is>
       </c>
       <c r="B540" t="n">
-        <v>0.034556</v>
+        <v>0.034682</v>
       </c>
       <c r="C540" t="n">
         <v>0.569149</v>
@@ -7447,7 +7447,7 @@
         </is>
       </c>
       <c r="B541" t="n">
-        <v>0.034581</v>
+        <v>0.0347</v>
       </c>
       <c r="C541" t="n">
         <v>0.566489</v>
@@ -7460,7 +7460,7 @@
         </is>
       </c>
       <c r="B542" t="n">
-        <v>0.034615</v>
+        <v>0.034718</v>
       </c>
       <c r="C542" t="n">
         <v>0.5638300000000001</v>
@@ -7473,7 +7473,7 @@
         </is>
       </c>
       <c r="B543" t="n">
-        <v>0.035027</v>
+        <v>0.035156</v>
       </c>
       <c r="C543" t="n">
         <v>0.5611699999999999</v>
@@ -7486,7 +7486,7 @@
         </is>
       </c>
       <c r="B544" t="n">
-        <v>0.035261</v>
+        <v>0.035381</v>
       </c>
       <c r="C544" t="n">
         <v>0.558511</v>
@@ -7499,7 +7499,7 @@
         </is>
       </c>
       <c r="B545" t="n">
-        <v>0.035295</v>
+        <v>0.035385</v>
       </c>
       <c r="C545" t="n">
         <v>0.555851</v>
@@ -7512,7 +7512,7 @@
         </is>
       </c>
       <c r="B546" t="n">
-        <v>0.035397</v>
+        <v>0.03554</v>
       </c>
       <c r="C546" t="n">
         <v>0.553191</v>
@@ -7525,7 +7525,7 @@
         </is>
       </c>
       <c r="B547" t="n">
-        <v>0.035442</v>
+        <v>0.035561</v>
       </c>
       <c r="C547" t="n">
         <v>0.550532</v>
@@ -7538,7 +7538,7 @@
         </is>
       </c>
       <c r="B548" t="n">
-        <v>0.035491</v>
+        <v>0.035595</v>
       </c>
       <c r="C548" t="n">
         <v>0.547872</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="B549" t="n">
-        <v>0.035758</v>
+        <v>0.035893</v>
       </c>
       <c r="C549" t="n">
         <v>0.5452129999999999</v>
@@ -7564,7 +7564,7 @@
         </is>
       </c>
       <c r="B550" t="n">
-        <v>0.035961</v>
+        <v>0.036039</v>
       </c>
       <c r="C550" t="n">
         <v>0.542553</v>
@@ -7577,7 +7577,7 @@
         </is>
       </c>
       <c r="B551" t="n">
-        <v>0.036127</v>
+        <v>0.036239</v>
       </c>
       <c r="C551" t="n">
         <v>0.539894</v>
@@ -7590,7 +7590,7 @@
         </is>
       </c>
       <c r="B552" t="n">
-        <v>0.03687</v>
+        <v>0.036859</v>
       </c>
       <c r="C552" t="n">
         <v>0.537234</v>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="B553" t="n">
-        <v>0.037588</v>
+        <v>0.037655</v>
       </c>
       <c r="C553" t="n">
         <v>0.534574</v>
@@ -7616,7 +7616,7 @@
         </is>
       </c>
       <c r="B554" t="n">
-        <v>0.03763</v>
+        <v>0.037692</v>
       </c>
       <c r="C554" t="n">
         <v>0.531915</v>
@@ -7629,7 +7629,7 @@
         </is>
       </c>
       <c r="B555" t="n">
-        <v>0.037696</v>
+        <v>0.037853</v>
       </c>
       <c r="C555" t="n">
         <v>0.529255</v>
@@ -7642,7 +7642,7 @@
         </is>
       </c>
       <c r="B556" t="n">
-        <v>0.037756</v>
+        <v>0.037985</v>
       </c>
       <c r="C556" t="n">
         <v>0.526596</v>
@@ -7655,7 +7655,7 @@
         </is>
       </c>
       <c r="B557" t="n">
-        <v>0.037893</v>
+        <v>0.038059</v>
       </c>
       <c r="C557" t="n">
         <v>0.523936</v>
@@ -7668,7 +7668,7 @@
         </is>
       </c>
       <c r="B558" t="n">
-        <v>0.038154</v>
+        <v>0.038348</v>
       </c>
       <c r="C558" t="n">
         <v>0.521277</v>
@@ -7681,7 +7681,7 @@
         </is>
       </c>
       <c r="B559" t="n">
-        <v>0.038277</v>
+        <v>0.038592</v>
       </c>
       <c r="C559" t="n">
         <v>0.518617</v>
@@ -7694,7 +7694,7 @@
         </is>
       </c>
       <c r="B560" t="n">
-        <v>0.038608</v>
+        <v>0.0386</v>
       </c>
       <c r="C560" t="n">
         <v>0.515957</v>
@@ -7707,7 +7707,7 @@
         </is>
       </c>
       <c r="B561" t="n">
-        <v>0.038864</v>
+        <v>0.039024</v>
       </c>
       <c r="C561" t="n">
         <v>0.513298</v>
@@ -7720,7 +7720,7 @@
         </is>
       </c>
       <c r="B562" t="n">
-        <v>0.038915</v>
+        <v>0.039071</v>
       </c>
       <c r="C562" t="n">
         <v>0.510638</v>
@@ -7733,7 +7733,7 @@
         </is>
       </c>
       <c r="B563" t="n">
-        <v>0.039006</v>
+        <v>0.040028</v>
       </c>
       <c r="C563" t="n">
         <v>0.507979</v>
@@ -7746,7 +7746,7 @@
         </is>
       </c>
       <c r="B564" t="n">
-        <v>0.040002</v>
+        <v>0.040593</v>
       </c>
       <c r="C564" t="n">
         <v>0.505319</v>
@@ -7759,7 +7759,7 @@
         </is>
       </c>
       <c r="B565" t="n">
-        <v>0.040323</v>
+        <v>0.040672</v>
       </c>
       <c r="C565" t="n">
         <v>0.50266</v>
@@ -7772,7 +7772,7 @@
         </is>
       </c>
       <c r="B566" t="n">
-        <v>0.040399</v>
+        <v>0.040843</v>
       </c>
       <c r="C566" t="n">
         <v>0.5</v>
@@ -7785,7 +7785,7 @@
         </is>
       </c>
       <c r="B567" t="n">
-        <v>0.040596</v>
+        <v>0.040924</v>
       </c>
       <c r="C567" t="n">
         <v>0.49734</v>
@@ -7798,7 +7798,7 @@
         </is>
       </c>
       <c r="B568" t="n">
-        <v>0.040915</v>
+        <v>0.041201</v>
       </c>
       <c r="C568" t="n">
         <v>0.494681</v>
@@ -7811,7 +7811,7 @@
         </is>
       </c>
       <c r="B569" t="n">
-        <v>0.042122</v>
+        <v>0.042053</v>
       </c>
       <c r="C569" t="n">
         <v>0.492021</v>
@@ -7824,7 +7824,7 @@
         </is>
       </c>
       <c r="B570" t="n">
-        <v>0.042127</v>
+        <v>0.042249</v>
       </c>
       <c r="C570" t="n">
         <v>0.489362</v>
@@ -7837,7 +7837,7 @@
         </is>
       </c>
       <c r="B571" t="n">
-        <v>0.042368</v>
+        <v>0.042383</v>
       </c>
       <c r="C571" t="n">
         <v>0.486702</v>
@@ -7850,7 +7850,7 @@
         </is>
       </c>
       <c r="B572" t="n">
-        <v>0.042412</v>
+        <v>0.042461</v>
       </c>
       <c r="C572" t="n">
         <v>0.484043</v>
@@ -7863,7 +7863,7 @@
         </is>
       </c>
       <c r="B573" t="n">
-        <v>0.042511</v>
+        <v>0.042487</v>
       </c>
       <c r="C573" t="n">
         <v>0.481383</v>
@@ -7876,7 +7876,7 @@
         </is>
       </c>
       <c r="B574" t="n">
-        <v>0.0431</v>
+        <v>0.043495</v>
       </c>
       <c r="C574" t="n">
         <v>0.478723</v>
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="B575" t="n">
-        <v>0.043488</v>
+        <v>0.043501</v>
       </c>
       <c r="C575" t="n">
         <v>0.476064</v>
@@ -7902,7 +7902,7 @@
         </is>
       </c>
       <c r="B576" t="n">
-        <v>0.043587</v>
+        <v>0.043722</v>
       </c>
       <c r="C576" t="n">
         <v>0.473404</v>
@@ -7915,7 +7915,7 @@
         </is>
       </c>
       <c r="B577" t="n">
-        <v>0.043613</v>
+        <v>0.04413</v>
       </c>
       <c r="C577" t="n">
         <v>0.470745</v>
@@ -7928,7 +7928,7 @@
         </is>
       </c>
       <c r="B578" t="n">
-        <v>0.044055</v>
+        <v>0.044249</v>
       </c>
       <c r="C578" t="n">
         <v>0.468085</v>
@@ -7941,7 +7941,7 @@
         </is>
       </c>
       <c r="B579" t="n">
-        <v>0.044225</v>
+        <v>0.044304</v>
       </c>
       <c r="C579" t="n">
         <v>0.465426</v>
@@ -7954,7 +7954,7 @@
         </is>
       </c>
       <c r="B580" t="n">
-        <v>0.044569</v>
+        <v>0.044659</v>
       </c>
       <c r="C580" t="n">
         <v>0.462766</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="B581" t="n">
-        <v>0.045321</v>
+        <v>0.045529</v>
       </c>
       <c r="C581" t="n">
         <v>0.460106</v>
@@ -7980,7 +7980,7 @@
         </is>
       </c>
       <c r="B582" t="n">
-        <v>0.045557</v>
+        <v>0.045842</v>
       </c>
       <c r="C582" t="n">
         <v>0.457447</v>
@@ -7993,7 +7993,7 @@
         </is>
       </c>
       <c r="B583" t="n">
-        <v>0.045952</v>
+        <v>0.046097</v>
       </c>
       <c r="C583" t="n">
         <v>0.454787</v>
@@ -8006,7 +8006,7 @@
         </is>
       </c>
       <c r="B584" t="n">
-        <v>0.046504</v>
+        <v>0.046491</v>
       </c>
       <c r="C584" t="n">
         <v>0.452128</v>
@@ -8019,7 +8019,7 @@
         </is>
       </c>
       <c r="B585" t="n">
-        <v>0.046513</v>
+        <v>0.046595</v>
       </c>
       <c r="C585" t="n">
         <v>0.449468</v>
@@ -8032,7 +8032,7 @@
         </is>
       </c>
       <c r="B586" t="n">
-        <v>0.046906</v>
+        <v>0.046958</v>
       </c>
       <c r="C586" t="n">
         <v>0.446809</v>
@@ -8045,7 +8045,7 @@
         </is>
       </c>
       <c r="B587" t="n">
-        <v>0.047028</v>
+        <v>0.047084</v>
       </c>
       <c r="C587" t="n">
         <v>0.444149</v>
@@ -8058,7 +8058,7 @@
         </is>
       </c>
       <c r="B588" t="n">
-        <v>0.047373</v>
+        <v>0.047379</v>
       </c>
       <c r="C588" t="n">
         <v>0.441489</v>
@@ -8071,7 +8071,7 @@
         </is>
       </c>
       <c r="B589" t="n">
-        <v>0.047548</v>
+        <v>0.047551</v>
       </c>
       <c r="C589" t="n">
         <v>0.43883</v>
@@ -8084,7 +8084,7 @@
         </is>
       </c>
       <c r="B590" t="n">
-        <v>0.047601</v>
+        <v>0.047575</v>
       </c>
       <c r="C590" t="n">
         <v>0.43617</v>
@@ -8097,7 +8097,7 @@
         </is>
       </c>
       <c r="B591" t="n">
-        <v>0.047671</v>
+        <v>0.047695</v>
       </c>
       <c r="C591" t="n">
         <v>0.433511</v>
@@ -8110,7 +8110,7 @@
         </is>
       </c>
       <c r="B592" t="n">
-        <v>0.047764</v>
+        <v>0.047932</v>
       </c>
       <c r="C592" t="n">
         <v>0.430851</v>
@@ -8123,7 +8123,7 @@
         </is>
       </c>
       <c r="B593" t="n">
-        <v>0.048827</v>
+        <v>0.048712</v>
       </c>
       <c r="C593" t="n">
         <v>0.428191</v>
@@ -8136,7 +8136,7 @@
         </is>
       </c>
       <c r="B594" t="n">
-        <v>0.049117</v>
+        <v>0.049466</v>
       </c>
       <c r="C594" t="n">
         <v>0.425532</v>
@@ -8149,7 +8149,7 @@
         </is>
       </c>
       <c r="B595" t="n">
-        <v>0.049551</v>
+        <v>0.049668</v>
       </c>
       <c r="C595" t="n">
         <v>0.422872</v>
@@ -8162,7 +8162,7 @@
         </is>
       </c>
       <c r="B596" t="n">
-        <v>0.049793</v>
+        <v>0.04983</v>
       </c>
       <c r="C596" t="n">
         <v>0.420213</v>
@@ -8175,7 +8175,7 @@
         </is>
       </c>
       <c r="B597" t="n">
-        <v>0.049811</v>
+        <v>0.049972</v>
       </c>
       <c r="C597" t="n">
         <v>0.417553</v>
@@ -8188,7 +8188,7 @@
         </is>
       </c>
       <c r="B598" t="n">
-        <v>0.051384</v>
+        <v>0.051346</v>
       </c>
       <c r="C598" t="n">
         <v>0.414894</v>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="B599" t="n">
-        <v>0.051815</v>
+        <v>0.052217</v>
       </c>
       <c r="C599" t="n">
         <v>0.412234</v>
@@ -8214,7 +8214,7 @@
         </is>
       </c>
       <c r="B600" t="n">
-        <v>0.052098</v>
+        <v>0.052418</v>
       </c>
       <c r="C600" t="n">
         <v>0.409574</v>
@@ -8227,7 +8227,7 @@
         </is>
       </c>
       <c r="B601" t="n">
-        <v>0.053597</v>
+        <v>0.053895</v>
       </c>
       <c r="C601" t="n">
         <v>0.406915</v>
@@ -8240,7 +8240,7 @@
         </is>
       </c>
       <c r="B602" t="n">
-        <v>0.053634</v>
+        <v>0.053896</v>
       </c>
       <c r="C602" t="n">
         <v>0.404255</v>
@@ -8253,7 +8253,7 @@
         </is>
       </c>
       <c r="B603" t="n">
-        <v>0.054344</v>
+        <v>0.054553</v>
       </c>
       <c r="C603" t="n">
         <v>0.401596</v>
@@ -8266,7 +8266,7 @@
         </is>
       </c>
       <c r="B604" t="n">
-        <v>0.054509</v>
+        <v>0.054669</v>
       </c>
       <c r="C604" t="n">
         <v>0.398936</v>
@@ -8279,7 +8279,7 @@
         </is>
       </c>
       <c r="B605" t="n">
-        <v>0.054898</v>
+        <v>0.054847</v>
       </c>
       <c r="C605" t="n">
         <v>0.396277</v>
@@ -8292,7 +8292,7 @@
         </is>
       </c>
       <c r="B606" t="n">
-        <v>0.055086</v>
+        <v>0.055465</v>
       </c>
       <c r="C606" t="n">
         <v>0.393617</v>
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="B607" t="n">
-        <v>0.055315</v>
+        <v>0.055598</v>
       </c>
       <c r="C607" t="n">
         <v>0.390957</v>
@@ -8318,7 +8318,7 @@
         </is>
       </c>
       <c r="B608" t="n">
-        <v>0.055813</v>
+        <v>0.056072</v>
       </c>
       <c r="C608" t="n">
         <v>0.388298</v>
@@ -8331,7 +8331,7 @@
         </is>
       </c>
       <c r="B609" t="n">
-        <v>0.055956</v>
+        <v>0.056238</v>
       </c>
       <c r="C609" t="n">
         <v>0.385638</v>
@@ -8344,7 +8344,7 @@
         </is>
       </c>
       <c r="B610" t="n">
-        <v>0.056143</v>
+        <v>0.056259</v>
       </c>
       <c r="C610" t="n">
         <v>0.382979</v>
@@ -8357,7 +8357,7 @@
         </is>
       </c>
       <c r="B611" t="n">
-        <v>0.056336</v>
+        <v>0.056486</v>
       </c>
       <c r="C611" t="n">
         <v>0.380319</v>
@@ -8370,7 +8370,7 @@
         </is>
       </c>
       <c r="B612" t="n">
-        <v>0.056499</v>
+        <v>0.056676</v>
       </c>
       <c r="C612" t="n">
         <v>0.37766</v>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="B613" t="n">
-        <v>0.056673</v>
+        <v>0.057149</v>
       </c>
       <c r="C613" t="n">
         <v>0.375</v>
@@ -8396,7 +8396,7 @@
         </is>
       </c>
       <c r="B614" t="n">
-        <v>0.056839</v>
+        <v>0.05721</v>
       </c>
       <c r="C614" t="n">
         <v>0.37234</v>
@@ -8409,7 +8409,7 @@
         </is>
       </c>
       <c r="B615" t="n">
-        <v>0.056956</v>
+        <v>0.057348</v>
       </c>
       <c r="C615" t="n">
         <v>0.369681</v>
@@ -8422,7 +8422,7 @@
         </is>
       </c>
       <c r="B616" t="n">
-        <v>0.057298</v>
+        <v>0.057542</v>
       </c>
       <c r="C616" t="n">
         <v>0.367021</v>
@@ -8435,7 +8435,7 @@
         </is>
       </c>
       <c r="B617" t="n">
-        <v>0.057597</v>
+        <v>0.057585</v>
       </c>
       <c r="C617" t="n">
         <v>0.364362</v>
@@ -8448,7 +8448,7 @@
         </is>
       </c>
       <c r="B618" t="n">
-        <v>0.057654</v>
+        <v>0.057818</v>
       </c>
       <c r="C618" t="n">
         <v>0.361702</v>
@@ -8461,7 +8461,7 @@
         </is>
       </c>
       <c r="B619" t="n">
-        <v>0.057849</v>
+        <v>0.058291</v>
       </c>
       <c r="C619" t="n">
         <v>0.359043</v>
@@ -8474,7 +8474,7 @@
         </is>
       </c>
       <c r="B620" t="n">
-        <v>0.058317</v>
+        <v>0.058525</v>
       </c>
       <c r="C620" t="n">
         <v>0.356383</v>
@@ -8487,7 +8487,7 @@
         </is>
       </c>
       <c r="B621" t="n">
-        <v>0.05865</v>
+        <v>0.058925</v>
       </c>
       <c r="C621" t="n">
         <v>0.353723</v>
@@ -8500,7 +8500,7 @@
         </is>
       </c>
       <c r="B622" t="n">
-        <v>0.058965</v>
+        <v>0.059627</v>
       </c>
       <c r="C622" t="n">
         <v>0.351064</v>
@@ -8513,7 +8513,7 @@
         </is>
       </c>
       <c r="B623" t="n">
-        <v>0.059229</v>
+        <v>0.05987</v>
       </c>
       <c r="C623" t="n">
         <v>0.348404</v>
@@ -8526,7 +8526,7 @@
         </is>
       </c>
       <c r="B624" t="n">
-        <v>0.059501</v>
+        <v>0.060325</v>
       </c>
       <c r="C624" t="n">
         <v>0.345745</v>
@@ -8539,7 +8539,7 @@
         </is>
       </c>
       <c r="B625" t="n">
-        <v>0.060231</v>
+        <v>0.060432</v>
       </c>
       <c r="C625" t="n">
         <v>0.343085</v>
@@ -8552,7 +8552,7 @@
         </is>
       </c>
       <c r="B626" t="n">
-        <v>0.060398</v>
+        <v>0.060781</v>
       </c>
       <c r="C626" t="n">
         <v>0.340426</v>
@@ -8565,7 +8565,7 @@
         </is>
       </c>
       <c r="B627" t="n">
-        <v>0.06068</v>
+        <v>0.060837</v>
       </c>
       <c r="C627" t="n">
         <v>0.337766</v>
@@ -8578,7 +8578,7 @@
         </is>
       </c>
       <c r="B628" t="n">
-        <v>0.06086</v>
+        <v>0.060998</v>
       </c>
       <c r="C628" t="n">
         <v>0.335106</v>
@@ -8591,7 +8591,7 @@
         </is>
       </c>
       <c r="B629" t="n">
-        <v>0.061206</v>
+        <v>0.062062</v>
       </c>
       <c r="C629" t="n">
         <v>0.332447</v>
@@ -8604,7 +8604,7 @@
         </is>
       </c>
       <c r="B630" t="n">
-        <v>0.061813</v>
+        <v>0.062349</v>
       </c>
       <c r="C630" t="n">
         <v>0.329787</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="B631" t="n">
-        <v>0.062047</v>
+        <v>0.062471</v>
       </c>
       <c r="C631" t="n">
         <v>0.327128</v>
@@ -8630,7 +8630,7 @@
         </is>
       </c>
       <c r="B632" t="n">
-        <v>0.062152</v>
+        <v>0.062524</v>
       </c>
       <c r="C632" t="n">
         <v>0.324468</v>
@@ -8643,7 +8643,7 @@
         </is>
       </c>
       <c r="B633" t="n">
-        <v>0.062226</v>
+        <v>0.063184</v>
       </c>
       <c r="C633" t="n">
         <v>0.321809</v>
@@ -8656,7 +8656,7 @@
         </is>
       </c>
       <c r="B634" t="n">
-        <v>0.063266</v>
+        <v>0.063656</v>
       </c>
       <c r="C634" t="n">
         <v>0.319149</v>
@@ -8669,7 +8669,7 @@
         </is>
       </c>
       <c r="B635" t="n">
-        <v>0.063426</v>
+        <v>0.06374100000000001</v>
       </c>
       <c r="C635" t="n">
         <v>0.316489</v>
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="B636" t="n">
-        <v>0.064086</v>
+        <v>0.06425</v>
       </c>
       <c r="C636" t="n">
         <v>0.31383</v>
@@ -8695,7 +8695,7 @@
         </is>
       </c>
       <c r="B637" t="n">
-        <v>0.064166</v>
+        <v>0.06439499999999999</v>
       </c>
       <c r="C637" t="n">
         <v>0.31117</v>
@@ -8708,7 +8708,7 @@
         </is>
       </c>
       <c r="B638" t="n">
-        <v>0.06433999999999999</v>
+        <v>0.06447899999999999</v>
       </c>
       <c r="C638" t="n">
         <v>0.308511</v>
@@ -8721,7 +8721,7 @@
         </is>
       </c>
       <c r="B639" t="n">
-        <v>0.06450699999999999</v>
+        <v>0.06457599999999999</v>
       </c>
       <c r="C639" t="n">
         <v>0.305851</v>
@@ -8734,7 +8734,7 @@
         </is>
       </c>
       <c r="B640" t="n">
-        <v>0.065133</v>
+        <v>0.064999</v>
       </c>
       <c r="C640" t="n">
         <v>0.303191</v>
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="B641" t="n">
-        <v>0.065645</v>
+        <v>0.06608700000000001</v>
       </c>
       <c r="C641" t="n">
         <v>0.300532</v>
@@ -8760,7 +8760,7 @@
         </is>
       </c>
       <c r="B642" t="n">
-        <v>0.066372</v>
+        <v>0.066411</v>
       </c>
       <c r="C642" t="n">
         <v>0.297872</v>
@@ -8773,7 +8773,7 @@
         </is>
       </c>
       <c r="B643" t="n">
-        <v>0.06662999999999999</v>
+        <v>0.06682200000000001</v>
       </c>
       <c r="C643" t="n">
         <v>0.295213</v>
@@ -8786,7 +8786,7 @@
         </is>
       </c>
       <c r="B644" t="n">
-        <v>0.066834</v>
+        <v>0.066978</v>
       </c>
       <c r="C644" t="n">
         <v>0.292553</v>
@@ -8799,7 +8799,7 @@
         </is>
       </c>
       <c r="B645" t="n">
-        <v>0.067927</v>
+        <v>0.068303</v>
       </c>
       <c r="C645" t="n">
         <v>0.289894</v>
@@ -8812,7 +8812,7 @@
         </is>
       </c>
       <c r="B646" t="n">
-        <v>0.06805799999999999</v>
+        <v>0.068658</v>
       </c>
       <c r="C646" t="n">
         <v>0.287234</v>
@@ -8825,7 +8825,7 @@
         </is>
       </c>
       <c r="B647" t="n">
-        <v>0.068248</v>
+        <v>0.06919699999999999</v>
       </c>
       <c r="C647" t="n">
         <v>0.284574</v>
@@ -8838,7 +8838,7 @@
         </is>
       </c>
       <c r="B648" t="n">
-        <v>0.06848700000000001</v>
+        <v>0.069437</v>
       </c>
       <c r="C648" t="n">
         <v>0.281915</v>
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="B649" t="n">
-        <v>0.06970800000000001</v>
+        <v>0.06977999999999999</v>
       </c>
       <c r="C649" t="n">
         <v>0.279255</v>
@@ -8864,7 +8864,7 @@
         </is>
       </c>
       <c r="B650" t="n">
-        <v>0.070185</v>
+        <v>0.070109</v>
       </c>
       <c r="C650" t="n">
         <v>0.276596</v>
@@ -8877,7 +8877,7 @@
         </is>
       </c>
       <c r="B651" t="n">
-        <v>0.070205</v>
+        <v>0.070308</v>
       </c>
       <c r="C651" t="n">
         <v>0.273936</v>
@@ -8890,7 +8890,7 @@
         </is>
       </c>
       <c r="B652" t="n">
-        <v>0.072381</v>
+        <v>0.072837</v>
       </c>
       <c r="C652" t="n">
         <v>0.271277</v>
@@ -8903,7 +8903,7 @@
         </is>
       </c>
       <c r="B653" t="n">
-        <v>0.07247000000000001</v>
+        <v>0.072954</v>
       </c>
       <c r="C653" t="n">
         <v>0.268617</v>
@@ -8916,7 +8916,7 @@
         </is>
       </c>
       <c r="B654" t="n">
-        <v>0.07356799999999999</v>
+        <v>0.073598</v>
       </c>
       <c r="C654" t="n">
         <v>0.265957</v>
@@ -8929,7 +8929,7 @@
         </is>
       </c>
       <c r="B655" t="n">
-        <v>0.07377400000000001</v>
+        <v>0.073811</v>
       </c>
       <c r="C655" t="n">
         <v>0.263298</v>
@@ -8942,7 +8942,7 @@
         </is>
       </c>
       <c r="B656" t="n">
-        <v>0.073833</v>
+        <v>0.07420499999999999</v>
       </c>
       <c r="C656" t="n">
         <v>0.260638</v>
@@ -8955,7 +8955,7 @@
         </is>
       </c>
       <c r="B657" t="n">
-        <v>0.073931</v>
+        <v>0.07442</v>
       </c>
       <c r="C657" t="n">
         <v>0.257979</v>
@@ -8968,7 +8968,7 @@
         </is>
       </c>
       <c r="B658" t="n">
-        <v>0.07502200000000001</v>
+        <v>0.07513599999999999</v>
       </c>
       <c r="C658" t="n">
         <v>0.255319</v>
@@ -8981,7 +8981,7 @@
         </is>
       </c>
       <c r="B659" t="n">
-        <v>0.07517799999999999</v>
+        <v>0.07573199999999999</v>
       </c>
       <c r="C659" t="n">
         <v>0.25266</v>
@@ -8994,7 +8994,7 @@
         </is>
       </c>
       <c r="B660" t="n">
-        <v>0.075798</v>
+        <v>0.075866</v>
       </c>
       <c r="C660" t="n">
         <v>0.25</v>
@@ -9007,7 +9007,7 @@
         </is>
       </c>
       <c r="B661" t="n">
-        <v>0.075806</v>
+        <v>0.07648099999999999</v>
       </c>
       <c r="C661" t="n">
         <v>0.24734</v>
@@ -9020,7 +9020,7 @@
         </is>
       </c>
       <c r="B662" t="n">
-        <v>0.076117</v>
+        <v>0.07686800000000001</v>
       </c>
       <c r="C662" t="n">
         <v>0.244681</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="B663" t="n">
-        <v>0.07685699999999999</v>
+        <v>0.07698199999999999</v>
       </c>
       <c r="C663" t="n">
         <v>0.242021</v>
@@ -9046,7 +9046,7 @@
         </is>
       </c>
       <c r="B664" t="n">
-        <v>0.07689500000000001</v>
+        <v>0.077169</v>
       </c>
       <c r="C664" t="n">
         <v>0.239362</v>
@@ -9059,7 +9059,7 @@
         </is>
       </c>
       <c r="B665" t="n">
-        <v>0.077179</v>
+        <v>0.07751</v>
       </c>
       <c r="C665" t="n">
         <v>0.236702</v>
@@ -9072,7 +9072,7 @@
         </is>
       </c>
       <c r="B666" t="n">
-        <v>0.077622</v>
+        <v>0.077676</v>
       </c>
       <c r="C666" t="n">
         <v>0.234043</v>
@@ -9085,7 +9085,7 @@
         </is>
       </c>
       <c r="B667" t="n">
-        <v>0.078665</v>
+        <v>0.079245</v>
       </c>
       <c r="C667" t="n">
         <v>0.231383</v>
@@ -9098,7 +9098,7 @@
         </is>
       </c>
       <c r="B668" t="n">
-        <v>0.07942</v>
+        <v>0.079318</v>
       </c>
       <c r="C668" t="n">
         <v>0.228723</v>
@@ -9111,7 +9111,7 @@
         </is>
       </c>
       <c r="B669" t="n">
-        <v>0.07983</v>
+        <v>0.079763</v>
       </c>
       <c r="C669" t="n">
         <v>0.226064</v>
@@ -9124,7 +9124,7 @@
         </is>
       </c>
       <c r="B670" t="n">
-        <v>0.079831</v>
+        <v>0.079984</v>
       </c>
       <c r="C670" t="n">
         <v>0.223404</v>
@@ -9137,7 +9137,7 @@
         </is>
       </c>
       <c r="B671" t="n">
-        <v>0.079982</v>
+        <v>0.080261</v>
       </c>
       <c r="C671" t="n">
         <v>0.220745</v>
@@ -9150,7 +9150,7 @@
         </is>
       </c>
       <c r="B672" t="n">
-        <v>0.079987</v>
+        <v>0.08111599999999999</v>
       </c>
       <c r="C672" t="n">
         <v>0.218085</v>
@@ -9163,7 +9163,7 @@
         </is>
       </c>
       <c r="B673" t="n">
-        <v>0.08050599999999999</v>
+        <v>0.08125</v>
       </c>
       <c r="C673" t="n">
         <v>0.215426</v>
@@ -9176,7 +9176,7 @@
         </is>
       </c>
       <c r="B674" t="n">
-        <v>0.080537</v>
+        <v>0.081381</v>
       </c>
       <c r="C674" t="n">
         <v>0.212766</v>
@@ -9189,7 +9189,7 @@
         </is>
       </c>
       <c r="B675" t="n">
-        <v>0.08254499999999999</v>
+        <v>0.082645</v>
       </c>
       <c r="C675" t="n">
         <v>0.210106</v>
@@ -9202,7 +9202,7 @@
         </is>
       </c>
       <c r="B676" t="n">
-        <v>0.08271100000000001</v>
+        <v>0.082889</v>
       </c>
       <c r="C676" t="n">
         <v>0.207447</v>
@@ -9215,7 +9215,7 @@
         </is>
       </c>
       <c r="B677" t="n">
-        <v>0.083276</v>
+        <v>0.083857</v>
       </c>
       <c r="C677" t="n">
         <v>0.204787</v>
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="B678" t="n">
-        <v>0.08397499999999999</v>
+        <v>0.08432199999999999</v>
       </c>
       <c r="C678" t="n">
         <v>0.202128</v>
@@ -9241,7 +9241,7 @@
         </is>
       </c>
       <c r="B679" t="n">
-        <v>0.08402</v>
+        <v>0.08486100000000001</v>
       </c>
       <c r="C679" t="n">
         <v>0.199468</v>
@@ -9254,7 +9254,7 @@
         </is>
       </c>
       <c r="B680" t="n">
-        <v>0.08484800000000001</v>
+        <v>0.08595700000000001</v>
       </c>
       <c r="C680" t="n">
         <v>0.196809</v>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="B681" t="n">
-        <v>0.085691</v>
+        <v>0.085993</v>
       </c>
       <c r="C681" t="n">
         <v>0.194149</v>
@@ -9280,7 +9280,7 @@
         </is>
       </c>
       <c r="B682" t="n">
-        <v>0.086134</v>
+        <v>0.08605</v>
       </c>
       <c r="C682" t="n">
         <v>0.191489</v>
@@ -9293,7 +9293,7 @@
         </is>
       </c>
       <c r="B683" t="n">
-        <v>0.08651</v>
+        <v>0.086608</v>
       </c>
       <c r="C683" t="n">
         <v>0.18883</v>
@@ -9306,7 +9306,7 @@
         </is>
       </c>
       <c r="B684" t="n">
-        <v>0.087075</v>
+        <v>0.087086</v>
       </c>
       <c r="C684" t="n">
         <v>0.18617</v>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="B685" t="n">
-        <v>0.088765</v>
+        <v>0.088853</v>
       </c>
       <c r="C685" t="n">
         <v>0.183511</v>
@@ -9332,7 +9332,7 @@
         </is>
       </c>
       <c r="B686" t="n">
-        <v>0.088838</v>
+        <v>0.088974</v>
       </c>
       <c r="C686" t="n">
         <v>0.180851</v>
@@ -9345,7 +9345,7 @@
         </is>
       </c>
       <c r="B687" t="n">
-        <v>0.091709</v>
+        <v>0.091695</v>
       </c>
       <c r="C687" t="n">
         <v>0.178191</v>
@@ -9358,7 +9358,7 @@
         </is>
       </c>
       <c r="B688" t="n">
-        <v>0.09320000000000001</v>
+        <v>0.093196</v>
       </c>
       <c r="C688" t="n">
         <v>0.175532</v>
@@ -9371,7 +9371,7 @@
         </is>
       </c>
       <c r="B689" t="n">
-        <v>0.09342399999999999</v>
+        <v>0.09482500000000001</v>
       </c>
       <c r="C689" t="n">
         <v>0.172872</v>
@@ -9384,7 +9384,7 @@
         </is>
       </c>
       <c r="B690" t="n">
-        <v>0.095235</v>
+        <v>0.09531199999999999</v>
       </c>
       <c r="C690" t="n">
         <v>0.170213</v>
@@ -9397,7 +9397,7 @@
         </is>
       </c>
       <c r="B691" t="n">
-        <v>0.09550599999999999</v>
+        <v>0.09582499999999999</v>
       </c>
       <c r="C691" t="n">
         <v>0.167553</v>
@@ -9410,7 +9410,7 @@
         </is>
       </c>
       <c r="B692" t="n">
-        <v>0.09605900000000001</v>
+        <v>0.096002</v>
       </c>
       <c r="C692" t="n">
         <v>0.164894</v>
@@ -9423,7 +9423,7 @@
         </is>
       </c>
       <c r="B693" t="n">
-        <v>0.097583</v>
+        <v>0.098423</v>
       </c>
       <c r="C693" t="n">
         <v>0.162234</v>
@@ -9436,7 +9436,7 @@
         </is>
       </c>
       <c r="B694" t="n">
-        <v>0.097706</v>
+        <v>0.098874</v>
       </c>
       <c r="C694" t="n">
         <v>0.159574</v>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="B695" t="n">
-        <v>0.09902</v>
+        <v>0.09919799999999999</v>
       </c>
       <c r="C695" t="n">
         <v>0.156915</v>
@@ -9462,7 +9462,7 @@
         </is>
       </c>
       <c r="B696" t="n">
-        <v>0.100445</v>
+        <v>0.101128</v>
       </c>
       <c r="C696" t="n">
         <v>0.154255</v>
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="B697" t="n">
-        <v>0.101124</v>
+        <v>0.101738</v>
       </c>
       <c r="C697" t="n">
         <v>0.151596</v>
@@ -9488,7 +9488,7 @@
         </is>
       </c>
       <c r="B698" t="n">
-        <v>0.102025</v>
+        <v>0.102304</v>
       </c>
       <c r="C698" t="n">
         <v>0.148936</v>
@@ -9501,7 +9501,7 @@
         </is>
       </c>
       <c r="B699" t="n">
-        <v>0.103595</v>
+        <v>0.103534</v>
       </c>
       <c r="C699" t="n">
         <v>0.146277</v>
@@ -9514,7 +9514,7 @@
         </is>
       </c>
       <c r="B700" t="n">
-        <v>0.104844</v>
+        <v>0.104677</v>
       </c>
       <c r="C700" t="n">
         <v>0.143617</v>
@@ -9527,7 +9527,7 @@
         </is>
       </c>
       <c r="B701" t="n">
-        <v>0.105967</v>
+        <v>0.106291</v>
       </c>
       <c r="C701" t="n">
         <v>0.140957</v>
@@ -9540,7 +9540,7 @@
         </is>
       </c>
       <c r="B702" t="n">
-        <v>0.106126</v>
+        <v>0.106468</v>
       </c>
       <c r="C702" t="n">
         <v>0.138298</v>
@@ -9553,7 +9553,7 @@
         </is>
       </c>
       <c r="B703" t="n">
-        <v>0.106355</v>
+        <v>0.106908</v>
       </c>
       <c r="C703" t="n">
         <v>0.135638</v>
@@ -9566,7 +9566,7 @@
         </is>
       </c>
       <c r="B704" t="n">
-        <v>0.10715</v>
+        <v>0.107413</v>
       </c>
       <c r="C704" t="n">
         <v>0.132979</v>
@@ -9579,7 +9579,7 @@
         </is>
       </c>
       <c r="B705" t="n">
-        <v>0.107529</v>
+        <v>0.107634</v>
       </c>
       <c r="C705" t="n">
         <v>0.130319</v>
@@ -9592,7 +9592,7 @@
         </is>
       </c>
       <c r="B706" t="n">
-        <v>0.107602</v>
+        <v>0.108749</v>
       </c>
       <c r="C706" t="n">
         <v>0.12766</v>
@@ -9605,7 +9605,7 @@
         </is>
       </c>
       <c r="B707" t="n">
-        <v>0.108328</v>
+        <v>0.10891</v>
       </c>
       <c r="C707" t="n">
         <v>0.125</v>
@@ -9618,7 +9618,7 @@
         </is>
       </c>
       <c r="B708" t="n">
-        <v>0.108871</v>
+        <v>0.109305</v>
       </c>
       <c r="C708" t="n">
         <v>0.12234</v>
@@ -9631,7 +9631,7 @@
         </is>
       </c>
       <c r="B709" t="n">
-        <v>0.11138</v>
+        <v>0.112144</v>
       </c>
       <c r="C709" t="n">
         <v>0.119681</v>
@@ -9644,7 +9644,7 @@
         </is>
       </c>
       <c r="B710" t="n">
-        <v>0.111805</v>
+        <v>0.112558</v>
       </c>
       <c r="C710" t="n">
         <v>0.117021</v>
@@ -9657,7 +9657,7 @@
         </is>
       </c>
       <c r="B711" t="n">
-        <v>0.112512</v>
+        <v>0.113295</v>
       </c>
       <c r="C711" t="n">
         <v>0.114362</v>
@@ -9670,7 +9670,7 @@
         </is>
       </c>
       <c r="B712" t="n">
-        <v>0.114732</v>
+        <v>0.115033</v>
       </c>
       <c r="C712" t="n">
         <v>0.111702</v>
@@ -9683,7 +9683,7 @@
         </is>
       </c>
       <c r="B713" t="n">
-        <v>0.115701</v>
+        <v>0.116543</v>
       </c>
       <c r="C713" t="n">
         <v>0.109043</v>
@@ -9696,7 +9696,7 @@
         </is>
       </c>
       <c r="B714" t="n">
-        <v>0.11651</v>
+        <v>0.116552</v>
       </c>
       <c r="C714" t="n">
         <v>0.106383</v>
@@ -9709,7 +9709,7 @@
         </is>
       </c>
       <c r="B715" t="n">
-        <v>0.116775</v>
+        <v>0.117552</v>
       </c>
       <c r="C715" t="n">
         <v>0.103723</v>
@@ -9722,7 +9722,7 @@
         </is>
       </c>
       <c r="B716" t="n">
-        <v>0.118208</v>
+        <v>0.118562</v>
       </c>
       <c r="C716" t="n">
         <v>0.101064</v>
@@ -9748,7 +9748,7 @@
         </is>
       </c>
       <c r="B718" t="n">
-        <v>0.119975</v>
+        <v>0.119746</v>
       </c>
       <c r="C718" t="n">
         <v>0.095745</v>
@@ -9761,7 +9761,7 @@
         </is>
       </c>
       <c r="B719" t="n">
-        <v>0.120122</v>
+        <v>0.120081</v>
       </c>
       <c r="C719" t="n">
         <v>0.093085</v>
@@ -9774,7 +9774,7 @@
         </is>
       </c>
       <c r="B720" t="n">
-        <v>0.121056</v>
+        <v>0.121602</v>
       </c>
       <c r="C720" t="n">
         <v>0.09042600000000001</v>
@@ -9787,7 +9787,7 @@
         </is>
       </c>
       <c r="B721" t="n">
-        <v>0.121281</v>
+        <v>0.121738</v>
       </c>
       <c r="C721" t="n">
         <v>0.087766</v>
@@ -9800,7 +9800,7 @@
         </is>
       </c>
       <c r="B722" t="n">
-        <v>0.125199</v>
+        <v>0.12499</v>
       </c>
       <c r="C722" t="n">
         <v>0.085106</v>
@@ -9813,7 +9813,7 @@
         </is>
       </c>
       <c r="B723" t="n">
-        <v>0.131266</v>
+        <v>0.133281</v>
       </c>
       <c r="C723" t="n">
         <v>0.08244700000000001</v>
@@ -9826,7 +9826,7 @@
         </is>
       </c>
       <c r="B724" t="n">
-        <v>0.131909</v>
+        <v>0.134557</v>
       </c>
       <c r="C724" t="n">
         <v>0.079787</v>
@@ -9839,7 +9839,7 @@
         </is>
       </c>
       <c r="B725" t="n">
-        <v>0.136653</v>
+        <v>0.136676</v>
       </c>
       <c r="C725" t="n">
         <v>0.077128</v>
@@ -9852,7 +9852,7 @@
         </is>
       </c>
       <c r="B726" t="n">
-        <v>0.137398</v>
+        <v>0.137774</v>
       </c>
       <c r="C726" t="n">
         <v>0.07446800000000001</v>
@@ -9865,7 +9865,7 @@
         </is>
       </c>
       <c r="B727" t="n">
-        <v>0.139274</v>
+        <v>0.13941</v>
       </c>
       <c r="C727" t="n">
         <v>0.071809</v>
@@ -9878,7 +9878,7 @@
         </is>
       </c>
       <c r="B728" t="n">
-        <v>0.141499</v>
+        <v>0.144106</v>
       </c>
       <c r="C728" t="n">
         <v>0.069149</v>
@@ -9891,7 +9891,7 @@
         </is>
       </c>
       <c r="B729" t="n">
-        <v>0.143404</v>
+        <v>0.144444</v>
       </c>
       <c r="C729" t="n">
         <v>0.06648900000000001</v>
@@ -9904,7 +9904,7 @@
         </is>
       </c>
       <c r="B730" t="n">
-        <v>0.144301</v>
+        <v>0.144995</v>
       </c>
       <c r="C730" t="n">
         <v>0.06383</v>
@@ -9917,7 +9917,7 @@
         </is>
       </c>
       <c r="B731" t="n">
-        <v>0.145508</v>
+        <v>0.146908</v>
       </c>
       <c r="C731" t="n">
         <v>0.06117</v>
@@ -9930,7 +9930,7 @@
         </is>
       </c>
       <c r="B732" t="n">
-        <v>0.14902</v>
+        <v>0.149408</v>
       </c>
       <c r="C732" t="n">
         <v>0.058511</v>
@@ -9943,7 +9943,7 @@
         </is>
       </c>
       <c r="B733" t="n">
-        <v>0.150094</v>
+        <v>0.151252</v>
       </c>
       <c r="C733" t="n">
         <v>0.055851</v>
@@ -9956,7 +9956,7 @@
         </is>
       </c>
       <c r="B734" t="n">
-        <v>0.151867</v>
+        <v>0.151828</v>
       </c>
       <c r="C734" t="n">
         <v>0.053191</v>
@@ -9969,7 +9969,7 @@
         </is>
       </c>
       <c r="B735" t="n">
-        <v>0.154826</v>
+        <v>0.154691</v>
       </c>
       <c r="C735" t="n">
         <v>0.050532</v>
@@ -9982,7 +9982,7 @@
         </is>
       </c>
       <c r="B736" t="n">
-        <v>0.157688</v>
+        <v>0.159389</v>
       </c>
       <c r="C736" t="n">
         <v>0.047872</v>
@@ -9995,7 +9995,7 @@
         </is>
       </c>
       <c r="B737" t="n">
-        <v>0.159928</v>
+        <v>0.160768</v>
       </c>
       <c r="C737" t="n">
         <v>0.045213</v>
@@ -10008,7 +10008,7 @@
         </is>
       </c>
       <c r="B738" t="n">
-        <v>0.160711</v>
+        <v>0.16308</v>
       </c>
       <c r="C738" t="n">
         <v>0.042553</v>
@@ -10021,7 +10021,7 @@
         </is>
       </c>
       <c r="B739" t="n">
-        <v>0.162557</v>
+        <v>0.164557</v>
       </c>
       <c r="C739" t="n">
         <v>0.039894</v>
@@ -10034,7 +10034,7 @@
         </is>
       </c>
       <c r="B740" t="n">
-        <v>0.171993</v>
+        <v>0.172148</v>
       </c>
       <c r="C740" t="n">
         <v>0.037234</v>
@@ -10047,7 +10047,7 @@
         </is>
       </c>
       <c r="B741" t="n">
-        <v>0.175246</v>
+        <v>0.176635</v>
       </c>
       <c r="C741" t="n">
         <v>0.034574</v>
@@ -10060,7 +10060,7 @@
         </is>
       </c>
       <c r="B742" t="n">
-        <v>0.179712</v>
+        <v>0.18449</v>
       </c>
       <c r="C742" t="n">
         <v>0.031915</v>
@@ -10073,7 +10073,7 @@
         </is>
       </c>
       <c r="B743" t="n">
-        <v>0.184723</v>
+        <v>0.187885</v>
       </c>
       <c r="C743" t="n">
         <v>0.029255</v>
@@ -10086,7 +10086,7 @@
         </is>
       </c>
       <c r="B744" t="n">
-        <v>0.193835</v>
+        <v>0.1964</v>
       </c>
       <c r="C744" t="n">
         <v>0.026596</v>
@@ -10099,7 +10099,7 @@
         </is>
       </c>
       <c r="B745" t="n">
-        <v>0.203837</v>
+        <v>0.203977</v>
       </c>
       <c r="C745" t="n">
         <v>0.023936</v>
@@ -10112,7 +10112,7 @@
         </is>
       </c>
       <c r="B746" t="n">
-        <v>0.204493</v>
+        <v>0.205321</v>
       </c>
       <c r="C746" t="n">
         <v>0.021277</v>
@@ -10125,7 +10125,7 @@
         </is>
       </c>
       <c r="B747" t="n">
-        <v>0.210785</v>
+        <v>0.211738</v>
       </c>
       <c r="C747" t="n">
         <v>0.018617</v>
@@ -10138,7 +10138,7 @@
         </is>
       </c>
       <c r="B748" t="n">
-        <v>0.226129</v>
+        <v>0.226545</v>
       </c>
       <c r="C748" t="n">
         <v>0.015957</v>
@@ -10151,7 +10151,7 @@
         </is>
       </c>
       <c r="B749" t="n">
-        <v>0.252857</v>
+        <v>0.253662</v>
       </c>
       <c r="C749" t="n">
         <v>0.013298</v>
@@ -10164,7 +10164,7 @@
         </is>
       </c>
       <c r="B750" t="n">
-        <v>0.253831</v>
+        <v>0.25523</v>
       </c>
       <c r="C750" t="n">
         <v>0.010638</v>
@@ -10177,7 +10177,7 @@
         </is>
       </c>
       <c r="B751" t="n">
-        <v>0.286035</v>
+        <v>0.286214</v>
       </c>
       <c r="C751" t="n">
         <v>0.007979</v>
@@ -10190,7 +10190,7 @@
         </is>
       </c>
       <c r="B752" t="n">
-        <v>0.317429</v>
+        <v>0.320483</v>
       </c>
       <c r="C752" t="n">
         <v>0.005319</v>
@@ -10203,7 +10203,7 @@
         </is>
       </c>
       <c r="B753" t="n">
-        <v>0.368815</v>
+        <v>0.371703</v>
       </c>
       <c r="C753" t="n">
         <v>0.00266</v>
@@ -10242,7 +10242,7 @@
         </is>
       </c>
       <c r="B756" t="n">
-        <v>0.000303</v>
+        <v>0.000304</v>
       </c>
       <c r="C756" t="n">
         <v>0.994681</v>
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="B758" t="n">
-        <v>0.001007</v>
+        <v>0.001008</v>
       </c>
       <c r="C758" t="n">
         <v>0.989362</v>
@@ -10281,7 +10281,7 @@
         </is>
       </c>
       <c r="B759" t="n">
-        <v>0.001611</v>
+        <v>0.001617</v>
       </c>
       <c r="C759" t="n">
         <v>0.986702</v>
@@ -10294,7 +10294,7 @@
         </is>
       </c>
       <c r="B760" t="n">
-        <v>0.001827</v>
+        <v>0.001832</v>
       </c>
       <c r="C760" t="n">
         <v>0.984043</v>
@@ -10307,7 +10307,7 @@
         </is>
       </c>
       <c r="B761" t="n">
-        <v>0.001862</v>
+        <v>0.001871</v>
       </c>
       <c r="C761" t="n">
         <v>0.981383</v>
@@ -10320,7 +10320,7 @@
         </is>
       </c>
       <c r="B762" t="n">
-        <v>0.002052</v>
+        <v>0.002076</v>
       </c>
       <c r="C762" t="n">
         <v>0.978723</v>
@@ -10333,7 +10333,7 @@
         </is>
       </c>
       <c r="B763" t="n">
-        <v>0.002622</v>
+        <v>0.002636</v>
       </c>
       <c r="C763" t="n">
         <v>0.976064</v>
@@ -10346,7 +10346,7 @@
         </is>
       </c>
       <c r="B764" t="n">
-        <v>0.002764</v>
+        <v>0.002787</v>
       </c>
       <c r="C764" t="n">
         <v>0.973404</v>
@@ -10359,7 +10359,7 @@
         </is>
       </c>
       <c r="B765" t="n">
-        <v>0.003091</v>
+        <v>0.003093</v>
       </c>
       <c r="C765" t="n">
         <v>0.970745</v>
@@ -10372,7 +10372,7 @@
         </is>
       </c>
       <c r="B766" t="n">
-        <v>0.00338</v>
+        <v>0.003403</v>
       </c>
       <c r="C766" t="n">
         <v>0.968085</v>
@@ -10385,7 +10385,7 @@
         </is>
       </c>
       <c r="B767" t="n">
-        <v>0.003965</v>
+        <v>0.004007</v>
       </c>
       <c r="C767" t="n">
         <v>0.965426</v>
@@ -10398,7 +10398,7 @@
         </is>
       </c>
       <c r="B768" t="n">
-        <v>0.004</v>
+        <v>0.004091</v>
       </c>
       <c r="C768" t="n">
         <v>0.962766</v>
@@ -10411,7 +10411,7 @@
         </is>
       </c>
       <c r="B769" t="n">
-        <v>0.004112</v>
+        <v>0.00414</v>
       </c>
       <c r="C769" t="n">
         <v>0.960106</v>
@@ -10424,7 +10424,7 @@
         </is>
       </c>
       <c r="B770" t="n">
-        <v>0.004323</v>
+        <v>0.004314</v>
       </c>
       <c r="C770" t="n">
         <v>0.957447</v>
@@ -10437,7 +10437,7 @@
         </is>
       </c>
       <c r="B771" t="n">
-        <v>0.004641</v>
+        <v>0.004658</v>
       </c>
       <c r="C771" t="n">
         <v>0.9547870000000001</v>
@@ -10450,7 +10450,7 @@
         </is>
       </c>
       <c r="B772" t="n">
-        <v>0.004658</v>
+        <v>0.004687</v>
       </c>
       <c r="C772" t="n">
         <v>0.952128</v>
@@ -10463,7 +10463,7 @@
         </is>
       </c>
       <c r="B773" t="n">
-        <v>0.004659</v>
+        <v>0.004694</v>
       </c>
       <c r="C773" t="n">
         <v>0.949468</v>
@@ -10476,7 +10476,7 @@
         </is>
       </c>
       <c r="B774" t="n">
-        <v>0.004734</v>
+        <v>0.004832</v>
       </c>
       <c r="C774" t="n">
         <v>0.946809</v>
@@ -10489,7 +10489,7 @@
         </is>
       </c>
       <c r="B775" t="n">
-        <v>0.004867</v>
+        <v>0.004934</v>
       </c>
       <c r="C775" t="n">
         <v>0.944149</v>
@@ -10502,7 +10502,7 @@
         </is>
       </c>
       <c r="B776" t="n">
-        <v>0.005174</v>
+        <v>0.005179</v>
       </c>
       <c r="C776" t="n">
         <v>0.941489</v>
@@ -10515,7 +10515,7 @@
         </is>
       </c>
       <c r="B777" t="n">
-        <v>0.005324</v>
+        <v>0.005341</v>
       </c>
       <c r="C777" t="n">
         <v>0.9388300000000001</v>
@@ -10528,7 +10528,7 @@
         </is>
       </c>
       <c r="B778" t="n">
-        <v>0.005336</v>
+        <v>0.005363</v>
       </c>
       <c r="C778" t="n">
         <v>0.9361699999999999</v>
@@ -10541,7 +10541,7 @@
         </is>
       </c>
       <c r="B779" t="n">
-        <v>0.005782</v>
+        <v>0.005795</v>
       </c>
       <c r="C779" t="n">
         <v>0.933511</v>
@@ -10554,7 +10554,7 @@
         </is>
       </c>
       <c r="B780" t="n">
-        <v>0.005784</v>
+        <v>0.005803</v>
       </c>
       <c r="C780" t="n">
         <v>0.930851</v>
@@ -10567,7 +10567,7 @@
         </is>
       </c>
       <c r="B781" t="n">
-        <v>0.006289</v>
+        <v>0.006456</v>
       </c>
       <c r="C781" t="n">
         <v>0.928191</v>
@@ -10580,7 +10580,7 @@
         </is>
       </c>
       <c r="B782" t="n">
-        <v>0.006678</v>
+        <v>0.006679</v>
       </c>
       <c r="C782" t="n">
         <v>0.925532</v>
@@ -10593,7 +10593,7 @@
         </is>
       </c>
       <c r="B783" t="n">
-        <v>0.007465</v>
+        <v>0.007468</v>
       </c>
       <c r="C783" t="n">
         <v>0.922872</v>
@@ -10606,7 +10606,7 @@
         </is>
       </c>
       <c r="B784" t="n">
-        <v>0.007792</v>
+        <v>0.007856</v>
       </c>
       <c r="C784" t="n">
         <v>0.9202129999999999</v>
@@ -10619,7 +10619,7 @@
         </is>
       </c>
       <c r="B785" t="n">
-        <v>0.007993</v>
+        <v>0.007982</v>
       </c>
       <c r="C785" t="n">
         <v>0.917553</v>
@@ -10645,7 +10645,7 @@
         </is>
       </c>
       <c r="B787" t="n">
-        <v>0.008113</v>
+        <v>0.008163</v>
       </c>
       <c r="C787" t="n">
         <v>0.912234</v>
@@ -10658,7 +10658,7 @@
         </is>
       </c>
       <c r="B788" t="n">
-        <v>0.008224</v>
+        <v>0.008240000000000001</v>
       </c>
       <c r="C788" t="n">
         <v>0.909574</v>
@@ -10671,7 +10671,7 @@
         </is>
       </c>
       <c r="B789" t="n">
-        <v>0.00848</v>
+        <v>0.00847</v>
       </c>
       <c r="C789" t="n">
         <v>0.906915</v>
@@ -10684,7 +10684,7 @@
         </is>
       </c>
       <c r="B790" t="n">
-        <v>0.008565</v>
+        <v>0.008572</v>
       </c>
       <c r="C790" t="n">
         <v>0.904255</v>
@@ -10697,7 +10697,7 @@
         </is>
       </c>
       <c r="B791" t="n">
-        <v>0.008591</v>
+        <v>0.008669</v>
       </c>
       <c r="C791" t="n">
         <v>0.901596</v>
@@ -10710,7 +10710,7 @@
         </is>
       </c>
       <c r="B792" t="n">
-        <v>0.008730999999999999</v>
+        <v>0.008815999999999999</v>
       </c>
       <c r="C792" t="n">
         <v>0.898936</v>
@@ -10723,7 +10723,7 @@
         </is>
       </c>
       <c r="B793" t="n">
-        <v>0.009436</v>
+        <v>0.009454000000000001</v>
       </c>
       <c r="C793" t="n">
         <v>0.896277</v>
@@ -10736,7 +10736,7 @@
         </is>
       </c>
       <c r="B794" t="n">
-        <v>0.009462999999999999</v>
+        <v>0.009497</v>
       </c>
       <c r="C794" t="n">
         <v>0.893617</v>
@@ -10749,7 +10749,7 @@
         </is>
       </c>
       <c r="B795" t="n">
-        <v>0.009466</v>
+        <v>0.00959</v>
       </c>
       <c r="C795" t="n">
         <v>0.890957</v>
@@ -10762,7 +10762,7 @@
         </is>
       </c>
       <c r="B796" t="n">
-        <v>0.009592</v>
+        <v>0.009613</v>
       </c>
       <c r="C796" t="n">
         <v>0.888298</v>
@@ -10775,7 +10775,7 @@
         </is>
       </c>
       <c r="B797" t="n">
-        <v>0.009724</v>
+        <v>0.009858</v>
       </c>
       <c r="C797" t="n">
         <v>0.885638</v>
@@ -10788,7 +10788,7 @@
         </is>
       </c>
       <c r="B798" t="n">
-        <v>0.009724999999999999</v>
+        <v>0.009865000000000001</v>
       </c>
       <c r="C798" t="n">
         <v>0.882979</v>
@@ -10801,7 +10801,7 @@
         </is>
       </c>
       <c r="B799" t="n">
-        <v>0.009774</v>
+        <v>0.009908999999999999</v>
       </c>
       <c r="C799" t="n">
         <v>0.880319</v>
@@ -10814,7 +10814,7 @@
         </is>
       </c>
       <c r="B800" t="n">
-        <v>0.010052</v>
+        <v>0.010059</v>
       </c>
       <c r="C800" t="n">
         <v>0.87766</v>
@@ -10827,7 +10827,7 @@
         </is>
       </c>
       <c r="B801" t="n">
-        <v>0.010178</v>
+        <v>0.010193</v>
       </c>
       <c r="C801" t="n">
         <v>0.875</v>
@@ -10840,7 +10840,7 @@
         </is>
       </c>
       <c r="B802" t="n">
-        <v>0.010374</v>
+        <v>0.010409</v>
       </c>
       <c r="C802" t="n">
         <v>0.87234</v>
@@ -10853,7 +10853,7 @@
         </is>
       </c>
       <c r="B803" t="n">
-        <v>0.010862</v>
+        <v>0.010898</v>
       </c>
       <c r="C803" t="n">
         <v>0.869681</v>
@@ -10866,7 +10866,7 @@
         </is>
       </c>
       <c r="B804" t="n">
-        <v>0.011438</v>
+        <v>0.011445</v>
       </c>
       <c r="C804" t="n">
         <v>0.867021</v>
@@ -10879,7 +10879,7 @@
         </is>
       </c>
       <c r="B805" t="n">
-        <v>0.0116</v>
+        <v>0.011646</v>
       </c>
       <c r="C805" t="n">
         <v>0.864362</v>
@@ -10892,7 +10892,7 @@
         </is>
       </c>
       <c r="B806" t="n">
-        <v>0.011754</v>
+        <v>0.011746</v>
       </c>
       <c r="C806" t="n">
         <v>0.861702</v>
@@ -10905,7 +10905,7 @@
         </is>
       </c>
       <c r="B807" t="n">
-        <v>0.011797</v>
+        <v>0.012041</v>
       </c>
       <c r="C807" t="n">
         <v>0.859043</v>
@@ -10918,7 +10918,7 @@
         </is>
       </c>
       <c r="B808" t="n">
-        <v>0.01209</v>
+        <v>0.012077</v>
       </c>
       <c r="C808" t="n">
         <v>0.856383</v>
@@ -10931,7 +10931,7 @@
         </is>
       </c>
       <c r="B809" t="n">
-        <v>0.012139</v>
+        <v>0.012147</v>
       </c>
       <c r="C809" t="n">
         <v>0.853723</v>
@@ -10944,7 +10944,7 @@
         </is>
       </c>
       <c r="B810" t="n">
-        <v>0.012484</v>
+        <v>0.012726</v>
       </c>
       <c r="C810" t="n">
         <v>0.851064</v>
@@ -10957,7 +10957,7 @@
         </is>
       </c>
       <c r="B811" t="n">
-        <v>0.012755</v>
+        <v>0.012777</v>
       </c>
       <c r="C811" t="n">
         <v>0.848404</v>
@@ -10970,7 +10970,7 @@
         </is>
       </c>
       <c r="B812" t="n">
-        <v>0.012951</v>
+        <v>0.012946</v>
       </c>
       <c r="C812" t="n">
         <v>0.845745</v>
@@ -10983,7 +10983,7 @@
         </is>
       </c>
       <c r="B813" t="n">
-        <v>0.013272</v>
+        <v>0.013364</v>
       </c>
       <c r="C813" t="n">
         <v>0.843085</v>
@@ -10996,7 +10996,7 @@
         </is>
       </c>
       <c r="B814" t="n">
-        <v>0.013475</v>
+        <v>0.01352</v>
       </c>
       <c r="C814" t="n">
         <v>0.840426</v>
@@ -11009,7 +11009,7 @@
         </is>
       </c>
       <c r="B815" t="n">
-        <v>0.013487</v>
+        <v>0.013563</v>
       </c>
       <c r="C815" t="n">
         <v>0.837766</v>
@@ -11022,7 +11022,7 @@
         </is>
       </c>
       <c r="B816" t="n">
-        <v>0.01404</v>
+        <v>0.014037</v>
       </c>
       <c r="C816" t="n">
         <v>0.835106</v>
@@ -11035,7 +11035,7 @@
         </is>
       </c>
       <c r="B817" t="n">
-        <v>0.014047</v>
+        <v>0.014135</v>
       </c>
       <c r="C817" t="n">
         <v>0.832447</v>
@@ -11048,7 +11048,7 @@
         </is>
       </c>
       <c r="B818" t="n">
-        <v>0.014293</v>
+        <v>0.014345</v>
       </c>
       <c r="C818" t="n">
         <v>0.8297870000000001</v>
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="B819" t="n">
-        <v>0.014339</v>
+        <v>0.014654</v>
       </c>
       <c r="C819" t="n">
         <v>0.827128</v>
@@ -11074,7 +11074,7 @@
         </is>
       </c>
       <c r="B820" t="n">
-        <v>0.014641</v>
+        <v>0.014913</v>
       </c>
       <c r="C820" t="n">
         <v>0.824468</v>
@@ -11087,7 +11087,7 @@
         </is>
       </c>
       <c r="B821" t="n">
-        <v>0.014874</v>
+        <v>0.015149</v>
       </c>
       <c r="C821" t="n">
         <v>0.821809</v>
@@ -11100,7 +11100,7 @@
         </is>
       </c>
       <c r="B822" t="n">
-        <v>0.015057</v>
+        <v>0.015304</v>
       </c>
       <c r="C822" t="n">
         <v>0.819149</v>
@@ -11113,7 +11113,7 @@
         </is>
       </c>
       <c r="B823" t="n">
-        <v>0.015363</v>
+        <v>0.015392</v>
       </c>
       <c r="C823" t="n">
         <v>0.816489</v>
@@ -11126,7 +11126,7 @@
         </is>
       </c>
       <c r="B824" t="n">
-        <v>0.015416</v>
+        <v>0.015488</v>
       </c>
       <c r="C824" t="n">
         <v>0.8138300000000001</v>
@@ -11139,7 +11139,7 @@
         </is>
       </c>
       <c r="B825" t="n">
-        <v>0.015615</v>
+        <v>0.015601</v>
       </c>
       <c r="C825" t="n">
         <v>0.8111699999999999</v>
@@ -11152,7 +11152,7 @@
         </is>
       </c>
       <c r="B826" t="n">
-        <v>0.015621</v>
+        <v>0.015616</v>
       </c>
       <c r="C826" t="n">
         <v>0.808511</v>
@@ -11165,7 +11165,7 @@
         </is>
       </c>
       <c r="B827" t="n">
-        <v>0.016071</v>
+        <v>0.016134</v>
       </c>
       <c r="C827" t="n">
         <v>0.805851</v>
@@ -11178,7 +11178,7 @@
         </is>
       </c>
       <c r="B828" t="n">
-        <v>0.016245</v>
+        <v>0.016322</v>
       </c>
       <c r="C828" t="n">
         <v>0.803191</v>
@@ -11191,7 +11191,7 @@
         </is>
       </c>
       <c r="B829" t="n">
-        <v>0.016339</v>
+        <v>0.016392</v>
       </c>
       <c r="C829" t="n">
         <v>0.800532</v>
@@ -11204,7 +11204,7 @@
         </is>
       </c>
       <c r="B830" t="n">
-        <v>0.016908</v>
+        <v>0.016936</v>
       </c>
       <c r="C830" t="n">
         <v>0.797872</v>
@@ -11217,7 +11217,7 @@
         </is>
       </c>
       <c r="B831" t="n">
-        <v>0.017068</v>
+        <v>0.017087</v>
       </c>
       <c r="C831" t="n">
         <v>0.7952129999999999</v>
@@ -11230,7 +11230,7 @@
         </is>
       </c>
       <c r="B832" t="n">
-        <v>0.017128</v>
+        <v>0.01723</v>
       </c>
       <c r="C832" t="n">
         <v>0.792553</v>
@@ -11243,7 +11243,7 @@
         </is>
       </c>
       <c r="B833" t="n">
-        <v>0.017642</v>
+        <v>0.017694</v>
       </c>
       <c r="C833" t="n">
         <v>0.789894</v>
@@ -11256,7 +11256,7 @@
         </is>
       </c>
       <c r="B834" t="n">
-        <v>0.017749</v>
+        <v>0.017794</v>
       </c>
       <c r="C834" t="n">
         <v>0.787234</v>
@@ -11269,7 +11269,7 @@
         </is>
       </c>
       <c r="B835" t="n">
-        <v>0.018</v>
+        <v>0.018064</v>
       </c>
       <c r="C835" t="n">
         <v>0.784574</v>
@@ -11282,7 +11282,7 @@
         </is>
       </c>
       <c r="B836" t="n">
-        <v>0.018283</v>
+        <v>0.018258</v>
       </c>
       <c r="C836" t="n">
         <v>0.781915</v>
@@ -11295,7 +11295,7 @@
         </is>
       </c>
       <c r="B837" t="n">
-        <v>0.018348</v>
+        <v>0.018325</v>
       </c>
       <c r="C837" t="n">
         <v>0.779255</v>
@@ -11308,7 +11308,7 @@
         </is>
       </c>
       <c r="B838" t="n">
-        <v>0.018517</v>
+        <v>0.018672</v>
       </c>
       <c r="C838" t="n">
         <v>0.776596</v>
@@ -11321,7 +11321,7 @@
         </is>
       </c>
       <c r="B839" t="n">
-        <v>0.018733</v>
+        <v>0.018805</v>
       </c>
       <c r="C839" t="n">
         <v>0.773936</v>
@@ -11334,7 +11334,7 @@
         </is>
       </c>
       <c r="B840" t="n">
-        <v>0.019555</v>
+        <v>0.01953</v>
       </c>
       <c r="C840" t="n">
         <v>0.771277</v>
@@ -11347,7 +11347,7 @@
         </is>
       </c>
       <c r="B841" t="n">
-        <v>0.019838</v>
+        <v>0.019851</v>
       </c>
       <c r="C841" t="n">
         <v>0.768617</v>
@@ -11360,7 +11360,7 @@
         </is>
       </c>
       <c r="B842" t="n">
-        <v>0.020147</v>
+        <v>0.020353</v>
       </c>
       <c r="C842" t="n">
         <v>0.765957</v>
@@ -11373,7 +11373,7 @@
         </is>
       </c>
       <c r="B843" t="n">
-        <v>0.020746</v>
+        <v>0.020735</v>
       </c>
       <c r="C843" t="n">
         <v>0.763298</v>
@@ -11386,7 +11386,7 @@
         </is>
       </c>
       <c r="B844" t="n">
-        <v>0.020836</v>
+        <v>0.020888</v>
       </c>
       <c r="C844" t="n">
         <v>0.760638</v>
@@ -11399,7 +11399,7 @@
         </is>
       </c>
       <c r="B845" t="n">
-        <v>0.021122</v>
+        <v>0.02118</v>
       </c>
       <c r="C845" t="n">
         <v>0.757979</v>
@@ -11412,7 +11412,7 @@
         </is>
       </c>
       <c r="B846" t="n">
-        <v>0.021181</v>
+        <v>0.021296</v>
       </c>
       <c r="C846" t="n">
         <v>0.755319</v>
@@ -11425,7 +11425,7 @@
         </is>
       </c>
       <c r="B847" t="n">
-        <v>0.0212</v>
+        <v>0.021317</v>
       </c>
       <c r="C847" t="n">
         <v>0.75266</v>
@@ -11438,7 +11438,7 @@
         </is>
       </c>
       <c r="B848" t="n">
-        <v>0.021252</v>
+        <v>0.021397</v>
       </c>
       <c r="C848" t="n">
         <v>0.75</v>
@@ -11451,7 +11451,7 @@
         </is>
       </c>
       <c r="B849" t="n">
-        <v>0.022278</v>
+        <v>0.022464</v>
       </c>
       <c r="C849" t="n">
         <v>0.74734</v>
@@ -11464,7 +11464,7 @@
         </is>
       </c>
       <c r="B850" t="n">
-        <v>0.022388</v>
+        <v>0.022496</v>
       </c>
       <c r="C850" t="n">
         <v>0.744681</v>
@@ -11477,7 +11477,7 @@
         </is>
       </c>
       <c r="B851" t="n">
-        <v>0.022468</v>
+        <v>0.022609</v>
       </c>
       <c r="C851" t="n">
         <v>0.742021</v>
@@ -11490,7 +11490,7 @@
         </is>
       </c>
       <c r="B852" t="n">
-        <v>0.022873</v>
+        <v>0.022883</v>
       </c>
       <c r="C852" t="n">
         <v>0.739362</v>
@@ -11503,7 +11503,7 @@
         </is>
       </c>
       <c r="B853" t="n">
-        <v>0.022931</v>
+        <v>0.022948</v>
       </c>
       <c r="C853" t="n">
         <v>0.736702</v>
@@ -11516,7 +11516,7 @@
         </is>
       </c>
       <c r="B854" t="n">
-        <v>0.023006</v>
+        <v>0.023227</v>
       </c>
       <c r="C854" t="n">
         <v>0.734043</v>
@@ -11529,7 +11529,7 @@
         </is>
       </c>
       <c r="B855" t="n">
-        <v>0.023074</v>
+        <v>0.023442</v>
       </c>
       <c r="C855" t="n">
         <v>0.731383</v>
@@ -11542,7 +11542,7 @@
         </is>
       </c>
       <c r="B856" t="n">
-        <v>0.023435</v>
+        <v>0.023524</v>
       </c>
       <c r="C856" t="n">
         <v>0.728723</v>
@@ -11555,7 +11555,7 @@
         </is>
       </c>
       <c r="B857" t="n">
-        <v>0.023717</v>
+        <v>0.0237</v>
       </c>
       <c r="C857" t="n">
         <v>0.726064</v>
@@ -11568,7 +11568,7 @@
         </is>
       </c>
       <c r="B858" t="n">
-        <v>0.023878</v>
+        <v>0.024081</v>
       </c>
       <c r="C858" t="n">
         <v>0.723404</v>
@@ -11581,7 +11581,7 @@
         </is>
       </c>
       <c r="B859" t="n">
-        <v>0.024485</v>
+        <v>0.024612</v>
       </c>
       <c r="C859" t="n">
         <v>0.720745</v>
@@ -11594,7 +11594,7 @@
         </is>
       </c>
       <c r="B860" t="n">
-        <v>0.024526</v>
+        <v>0.024736</v>
       </c>
       <c r="C860" t="n">
         <v>0.718085</v>
@@ -11607,7 +11607,7 @@
         </is>
       </c>
       <c r="B861" t="n">
-        <v>0.024635</v>
+        <v>0.024794</v>
       </c>
       <c r="C861" t="n">
         <v>0.715426</v>
@@ -11620,7 +11620,7 @@
         </is>
       </c>
       <c r="B862" t="n">
-        <v>0.024664</v>
+        <v>0.024829</v>
       </c>
       <c r="C862" t="n">
         <v>0.712766</v>
@@ -11633,7 +11633,7 @@
         </is>
       </c>
       <c r="B863" t="n">
-        <v>0.024764</v>
+        <v>0.025001</v>
       </c>
       <c r="C863" t="n">
         <v>0.710106</v>
@@ -11646,7 +11646,7 @@
         </is>
       </c>
       <c r="B864" t="n">
-        <v>0.025174</v>
+        <v>0.025204</v>
       </c>
       <c r="C864" t="n">
         <v>0.707447</v>
@@ -11659,7 +11659,7 @@
         </is>
       </c>
       <c r="B865" t="n">
-        <v>0.025425</v>
+        <v>0.025611</v>
       </c>
       <c r="C865" t="n">
         <v>0.7047870000000001</v>
@@ -11672,7 +11672,7 @@
         </is>
       </c>
       <c r="B866" t="n">
-        <v>0.025644</v>
+        <v>0.025729</v>
       </c>
       <c r="C866" t="n">
         <v>0.702128</v>
@@ -11685,7 +11685,7 @@
         </is>
       </c>
       <c r="B867" t="n">
-        <v>0.025905</v>
+        <v>0.025907</v>
       </c>
       <c r="C867" t="n">
         <v>0.699468</v>
@@ -11698,7 +11698,7 @@
         </is>
       </c>
       <c r="B868" t="n">
-        <v>0.026349</v>
+        <v>0.02636</v>
       </c>
       <c r="C868" t="n">
         <v>0.696809</v>
@@ -11711,7 +11711,7 @@
         </is>
       </c>
       <c r="B869" t="n">
-        <v>0.026359</v>
+        <v>0.026404</v>
       </c>
       <c r="C869" t="n">
         <v>0.694149</v>
@@ -11724,7 +11724,7 @@
         </is>
       </c>
       <c r="B870" t="n">
-        <v>0.026362</v>
+        <v>0.026429</v>
       </c>
       <c r="C870" t="n">
         <v>0.691489</v>
@@ -11737,7 +11737,7 @@
         </is>
       </c>
       <c r="B871" t="n">
-        <v>0.026401</v>
+        <v>0.026505</v>
       </c>
       <c r="C871" t="n">
         <v>0.6888300000000001</v>
@@ -11750,7 +11750,7 @@
         </is>
       </c>
       <c r="B872" t="n">
-        <v>0.026487</v>
+        <v>0.02652</v>
       </c>
       <c r="C872" t="n">
         <v>0.6861699999999999</v>
@@ -11763,7 +11763,7 @@
         </is>
       </c>
       <c r="B873" t="n">
-        <v>0.026687</v>
+        <v>0.026914</v>
       </c>
       <c r="C873" t="n">
         <v>0.683511</v>
@@ -11776,7 +11776,7 @@
         </is>
       </c>
       <c r="B874" t="n">
-        <v>0.026984</v>
+        <v>0.027055</v>
       </c>
       <c r="C874" t="n">
         <v>0.680851</v>
@@ -11789,7 +11789,7 @@
         </is>
       </c>
       <c r="B875" t="n">
-        <v>0.027317</v>
+        <v>0.027364</v>
       </c>
       <c r="C875" t="n">
         <v>0.678191</v>
@@ -11802,7 +11802,7 @@
         </is>
       </c>
       <c r="B876" t="n">
-        <v>0.027988</v>
+        <v>0.027966</v>
       </c>
       <c r="C876" t="n">
         <v>0.675532</v>
@@ -11815,7 +11815,7 @@
         </is>
       </c>
       <c r="B877" t="n">
-        <v>0.028018</v>
+        <v>0.028201</v>
       </c>
       <c r="C877" t="n">
         <v>0.672872</v>
@@ -11828,7 +11828,7 @@
         </is>
       </c>
       <c r="B878" t="n">
-        <v>0.028569</v>
+        <v>0.028737</v>
       </c>
       <c r="C878" t="n">
         <v>0.6702129999999999</v>
@@ -11841,7 +11841,7 @@
         </is>
       </c>
       <c r="B879" t="n">
-        <v>0.028659</v>
+        <v>0.028926</v>
       </c>
       <c r="C879" t="n">
         <v>0.667553</v>
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="B880" t="n">
-        <v>0.028978</v>
+        <v>0.029218</v>
       </c>
       <c r="C880" t="n">
         <v>0.664894</v>
@@ -11867,7 +11867,7 @@
         </is>
       </c>
       <c r="B881" t="n">
-        <v>0.029292</v>
+        <v>0.029245</v>
       </c>
       <c r="C881" t="n">
         <v>0.662234</v>
@@ -11893,7 +11893,7 @@
         </is>
       </c>
       <c r="B883" t="n">
-        <v>0.030212</v>
+        <v>0.030201</v>
       </c>
       <c r="C883" t="n">
         <v>0.656915</v>
@@ -11906,7 +11906,7 @@
         </is>
       </c>
       <c r="B884" t="n">
-        <v>0.030466</v>
+        <v>0.030634</v>
       </c>
       <c r="C884" t="n">
         <v>0.654255</v>
@@ -11919,7 +11919,7 @@
         </is>
       </c>
       <c r="B885" t="n">
-        <v>0.030655</v>
+        <v>0.030683</v>
       </c>
       <c r="C885" t="n">
         <v>0.651596</v>
@@ -11932,7 +11932,7 @@
         </is>
       </c>
       <c r="B886" t="n">
-        <v>0.030967</v>
+        <v>0.031084</v>
       </c>
       <c r="C886" t="n">
         <v>0.648936</v>
@@ -11945,7 +11945,7 @@
         </is>
       </c>
       <c r="B887" t="n">
-        <v>0.031252</v>
+        <v>0.031245</v>
       </c>
       <c r="C887" t="n">
         <v>0.646277</v>
@@ -11958,7 +11958,7 @@
         </is>
       </c>
       <c r="B888" t="n">
-        <v>0.032064</v>
+        <v>0.032091</v>
       </c>
       <c r="C888" t="n">
         <v>0.643617</v>
@@ -11971,7 +11971,7 @@
         </is>
       </c>
       <c r="B889" t="n">
-        <v>0.032166</v>
+        <v>0.032181</v>
       </c>
       <c r="C889" t="n">
         <v>0.640957</v>
@@ -11984,7 +11984,7 @@
         </is>
       </c>
       <c r="B890" t="n">
-        <v>0.032217</v>
+        <v>0.032286</v>
       </c>
       <c r="C890" t="n">
         <v>0.638298</v>
@@ -11997,7 +11997,7 @@
         </is>
       </c>
       <c r="B891" t="n">
-        <v>0.032261</v>
+        <v>0.032344</v>
       </c>
       <c r="C891" t="n">
         <v>0.635638</v>
@@ -12010,7 +12010,7 @@
         </is>
       </c>
       <c r="B892" t="n">
-        <v>0.032317</v>
+        <v>0.032402</v>
       </c>
       <c r="C892" t="n">
         <v>0.632979</v>
@@ -12023,7 +12023,7 @@
         </is>
       </c>
       <c r="B893" t="n">
-        <v>0.032561</v>
+        <v>0.03269</v>
       </c>
       <c r="C893" t="n">
         <v>0.630319</v>
@@ -12036,7 +12036,7 @@
         </is>
       </c>
       <c r="B894" t="n">
-        <v>0.032697</v>
+        <v>0.032764</v>
       </c>
       <c r="C894" t="n">
         <v>0.62766</v>
@@ -12049,7 +12049,7 @@
         </is>
       </c>
       <c r="B895" t="n">
-        <v>0.0331</v>
+        <v>0.033162</v>
       </c>
       <c r="C895" t="n">
         <v>0.625</v>
@@ -12062,7 +12062,7 @@
         </is>
       </c>
       <c r="B896" t="n">
-        <v>0.033106</v>
+        <v>0.033477</v>
       </c>
       <c r="C896" t="n">
         <v>0.62234</v>
@@ -12075,7 +12075,7 @@
         </is>
       </c>
       <c r="B897" t="n">
-        <v>0.033421</v>
+        <v>0.033525</v>
       </c>
       <c r="C897" t="n">
         <v>0.619681</v>
@@ -12088,7 +12088,7 @@
         </is>
       </c>
       <c r="B898" t="n">
-        <v>0.033439</v>
+        <v>0.033759</v>
       </c>
       <c r="C898" t="n">
         <v>0.617021</v>
@@ -12101,7 +12101,7 @@
         </is>
       </c>
       <c r="B899" t="n">
-        <v>0.033658</v>
+        <v>0.033775</v>
       </c>
       <c r="C899" t="n">
         <v>0.614362</v>
@@ -12114,7 +12114,7 @@
         </is>
       </c>
       <c r="B900" t="n">
-        <v>0.033893</v>
+        <v>0.033853</v>
       </c>
       <c r="C900" t="n">
         <v>0.611702</v>
@@ -12127,7 +12127,7 @@
         </is>
       </c>
       <c r="B901" t="n">
-        <v>0.033947</v>
+        <v>0.034033</v>
       </c>
       <c r="C901" t="n">
         <v>0.609043</v>
@@ -12140,7 +12140,7 @@
         </is>
       </c>
       <c r="B902" t="n">
-        <v>0.03417</v>
+        <v>0.034274</v>
       </c>
       <c r="C902" t="n">
         <v>0.606383</v>
@@ -12153,7 +12153,7 @@
         </is>
       </c>
       <c r="B903" t="n">
-        <v>0.034424</v>
+        <v>0.034492</v>
       </c>
       <c r="C903" t="n">
         <v>0.603723</v>
@@ -12166,7 +12166,7 @@
         </is>
       </c>
       <c r="B904" t="n">
-        <v>0.03462</v>
+        <v>0.034749</v>
       </c>
       <c r="C904" t="n">
         <v>0.601064</v>
@@ -12179,7 +12179,7 @@
         </is>
       </c>
       <c r="B905" t="n">
-        <v>0.035075</v>
+        <v>0.035079</v>
       </c>
       <c r="C905" t="n">
         <v>0.598404</v>
@@ -12192,7 +12192,7 @@
         </is>
       </c>
       <c r="B906" t="n">
-        <v>0.035322</v>
+        <v>0.035429</v>
       </c>
       <c r="C906" t="n">
         <v>0.595745</v>
@@ -12205,7 +12205,7 @@
         </is>
       </c>
       <c r="B907" t="n">
-        <v>0.035616</v>
+        <v>0.035895</v>
       </c>
       <c r="C907" t="n">
         <v>0.593085</v>
@@ -12218,7 +12218,7 @@
         </is>
       </c>
       <c r="B908" t="n">
-        <v>0.03617</v>
+        <v>0.036492</v>
       </c>
       <c r="C908" t="n">
         <v>0.590426</v>
@@ -12231,7 +12231,7 @@
         </is>
       </c>
       <c r="B909" t="n">
-        <v>0.03629</v>
+        <v>0.036534</v>
       </c>
       <c r="C909" t="n">
         <v>0.587766</v>
@@ -12244,7 +12244,7 @@
         </is>
       </c>
       <c r="B910" t="n">
-        <v>0.036493</v>
+        <v>0.036566</v>
       </c>
       <c r="C910" t="n">
         <v>0.585106</v>
@@ -12257,7 +12257,7 @@
         </is>
       </c>
       <c r="B911" t="n">
-        <v>0.036907</v>
+        <v>0.036887</v>
       </c>
       <c r="C911" t="n">
         <v>0.582447</v>
@@ -12270,7 +12270,7 @@
         </is>
       </c>
       <c r="B912" t="n">
-        <v>0.036932</v>
+        <v>0.036935</v>
       </c>
       <c r="C912" t="n">
         <v>0.5797870000000001</v>
@@ -12283,7 +12283,7 @@
         </is>
       </c>
       <c r="B913" t="n">
-        <v>0.036971</v>
+        <v>0.037196</v>
       </c>
       <c r="C913" t="n">
         <v>0.577128</v>
@@ -12296,7 +12296,7 @@
         </is>
       </c>
       <c r="B914" t="n">
-        <v>0.037023</v>
+        <v>0.037225</v>
       </c>
       <c r="C914" t="n">
         <v>0.574468</v>
@@ -12309,7 +12309,7 @@
         </is>
       </c>
       <c r="B915" t="n">
-        <v>0.037058</v>
+        <v>0.03723</v>
       </c>
       <c r="C915" t="n">
         <v>0.571809</v>
@@ -12322,7 +12322,7 @@
         </is>
       </c>
       <c r="B916" t="n">
-        <v>0.037332</v>
+        <v>0.037475</v>
       </c>
       <c r="C916" t="n">
         <v>0.569149</v>
@@ -12335,7 +12335,7 @@
         </is>
       </c>
       <c r="B917" t="n">
-        <v>0.037359</v>
+        <v>0.037496</v>
       </c>
       <c r="C917" t="n">
         <v>0.566489</v>
@@ -12348,7 +12348,7 @@
         </is>
       </c>
       <c r="B918" t="n">
-        <v>0.037396</v>
+        <v>0.037514</v>
       </c>
       <c r="C918" t="n">
         <v>0.5638300000000001</v>
@@ -12361,7 +12361,7 @@
         </is>
       </c>
       <c r="B919" t="n">
-        <v>0.037841</v>
+        <v>0.037988</v>
       </c>
       <c r="C919" t="n">
         <v>0.5611699999999999</v>
@@ -12374,7 +12374,7 @@
         </is>
       </c>
       <c r="B920" t="n">
-        <v>0.038094</v>
+        <v>0.038231</v>
       </c>
       <c r="C920" t="n">
         <v>0.558511</v>
@@ -12387,7 +12387,7 @@
         </is>
       </c>
       <c r="B921" t="n">
-        <v>0.038131</v>
+        <v>0.038235</v>
       </c>
       <c r="C921" t="n">
         <v>0.555851</v>
@@ -12400,7 +12400,7 @@
         </is>
       </c>
       <c r="B922" t="n">
-        <v>0.038241</v>
+        <v>0.038403</v>
       </c>
       <c r="C922" t="n">
         <v>0.553191</v>
@@ -12413,7 +12413,7 @@
         </is>
       </c>
       <c r="B923" t="n">
-        <v>0.038289</v>
+        <v>0.038425</v>
       </c>
       <c r="C923" t="n">
         <v>0.550532</v>
@@ -12426,7 +12426,7 @@
         </is>
       </c>
       <c r="B924" t="n">
-        <v>0.038342</v>
+        <v>0.038462</v>
       </c>
       <c r="C924" t="n">
         <v>0.547872</v>
@@ -12439,7 +12439,7 @@
         </is>
       </c>
       <c r="B925" t="n">
-        <v>0.038631</v>
+        <v>0.038784</v>
       </c>
       <c r="C925" t="n">
         <v>0.5452129999999999</v>
@@ -12452,7 +12452,7 @@
         </is>
       </c>
       <c r="B926" t="n">
-        <v>0.03885</v>
+        <v>0.038942</v>
       </c>
       <c r="C926" t="n">
         <v>0.542553</v>
@@ -12465,7 +12465,7 @@
         </is>
       </c>
       <c r="B927" t="n">
-        <v>0.039029</v>
+        <v>0.039158</v>
       </c>
       <c r="C927" t="n">
         <v>0.539894</v>
@@ -12478,7 +12478,7 @@
         </is>
       </c>
       <c r="B928" t="n">
-        <v>0.039832</v>
+        <v>0.039828</v>
       </c>
       <c r="C928" t="n">
         <v>0.537234</v>
@@ -12491,7 +12491,7 @@
         </is>
       </c>
       <c r="B929" t="n">
-        <v>0.040608</v>
+        <v>0.040689</v>
       </c>
       <c r="C929" t="n">
         <v>0.534574</v>
@@ -12504,7 +12504,7 @@
         </is>
       </c>
       <c r="B930" t="n">
-        <v>0.040653</v>
+        <v>0.040728</v>
       </c>
       <c r="C930" t="n">
         <v>0.531915</v>
@@ -12517,7 +12517,7 @@
         </is>
       </c>
       <c r="B931" t="n">
-        <v>0.040724</v>
+        <v>0.040903</v>
       </c>
       <c r="C931" t="n">
         <v>0.529255</v>
@@ -12530,7 +12530,7 @@
         </is>
       </c>
       <c r="B932" t="n">
-        <v>0.040789</v>
+        <v>0.041045</v>
       </c>
       <c r="C932" t="n">
         <v>0.526596</v>
@@ -12543,7 +12543,7 @@
         </is>
       </c>
       <c r="B933" t="n">
-        <v>0.040937</v>
+        <v>0.041125</v>
       </c>
       <c r="C933" t="n">
         <v>0.523936</v>
@@ -12556,7 +12556,7 @@
         </is>
       </c>
       <c r="B934" t="n">
-        <v>0.04122</v>
+        <v>0.041437</v>
       </c>
       <c r="C934" t="n">
         <v>0.521277</v>
@@ -12569,7 +12569,7 @@
         </is>
       </c>
       <c r="B935" t="n">
-        <v>0.041352</v>
+        <v>0.041701</v>
       </c>
       <c r="C935" t="n">
         <v>0.518617</v>
@@ -12595,7 +12595,7 @@
         </is>
       </c>
       <c r="B937" t="n">
-        <v>0.041987</v>
+        <v>0.042168</v>
       </c>
       <c r="C937" t="n">
         <v>0.513298</v>
@@ -12608,7 +12608,7 @@
         </is>
       </c>
       <c r="B938" t="n">
-        <v>0.042041</v>
+        <v>0.042219</v>
       </c>
       <c r="C938" t="n">
         <v>0.510638</v>
@@ -12621,7 +12621,7 @@
         </is>
       </c>
       <c r="B939" t="n">
-        <v>0.04214</v>
+        <v>0.043252</v>
       </c>
       <c r="C939" t="n">
         <v>0.507979</v>
@@ -12634,7 +12634,7 @@
         </is>
       </c>
       <c r="B940" t="n">
-        <v>0.043216</v>
+        <v>0.043863</v>
       </c>
       <c r="C940" t="n">
         <v>0.505319</v>
@@ -12647,7 +12647,7 @@
         </is>
       </c>
       <c r="B941" t="n">
-        <v>0.043562</v>
+        <v>0.043948</v>
       </c>
       <c r="C941" t="n">
         <v>0.50266</v>
@@ -12660,7 +12660,7 @@
         </is>
       </c>
       <c r="B942" t="n">
-        <v>0.043645</v>
+        <v>0.044134</v>
       </c>
       <c r="C942" t="n">
         <v>0.5</v>
@@ -12673,7 +12673,7 @@
         </is>
       </c>
       <c r="B943" t="n">
-        <v>0.043857</v>
+        <v>0.044221</v>
       </c>
       <c r="C943" t="n">
         <v>0.49734</v>
@@ -12686,7 +12686,7 @@
         </is>
       </c>
       <c r="B944" t="n">
-        <v>0.044202</v>
+        <v>0.04452</v>
       </c>
       <c r="C944" t="n">
         <v>0.494681</v>
@@ -12699,7 +12699,7 @@
         </is>
       </c>
       <c r="B945" t="n">
-        <v>0.045506</v>
+        <v>0.045441</v>
       </c>
       <c r="C945" t="n">
         <v>0.492021</v>
@@ -12712,7 +12712,7 @@
         </is>
       </c>
       <c r="B946" t="n">
-        <v>0.045512</v>
+        <v>0.045653</v>
       </c>
       <c r="C946" t="n">
         <v>0.489362</v>
@@ -12725,7 +12725,7 @@
         </is>
       </c>
       <c r="B947" t="n">
-        <v>0.045772</v>
+        <v>0.045798</v>
       </c>
       <c r="C947" t="n">
         <v>0.486702</v>
@@ -12738,7 +12738,7 @@
         </is>
       </c>
       <c r="B948" t="n">
-        <v>0.04582</v>
+        <v>0.045882</v>
       </c>
       <c r="C948" t="n">
         <v>0.484043</v>
@@ -12751,7 +12751,7 @@
         </is>
       </c>
       <c r="B949" t="n">
-        <v>0.045926</v>
+        <v>0.04591</v>
       </c>
       <c r="C949" t="n">
         <v>0.481383</v>
@@ -12764,7 +12764,7 @@
         </is>
       </c>
       <c r="B950" t="n">
-        <v>0.046563</v>
+        <v>0.046999</v>
       </c>
       <c r="C950" t="n">
         <v>0.478723</v>
@@ -12777,7 +12777,7 @@
         </is>
       </c>
       <c r="B951" t="n">
-        <v>0.046982</v>
+        <v>0.047005</v>
       </c>
       <c r="C951" t="n">
         <v>0.476064</v>
@@ -12790,7 +12790,7 @@
         </is>
       </c>
       <c r="B952" t="n">
-        <v>0.047088</v>
+        <v>0.047244</v>
       </c>
       <c r="C952" t="n">
         <v>0.473404</v>
@@ -12803,7 +12803,7 @@
         </is>
       </c>
       <c r="B953" t="n">
-        <v>0.047116</v>
+        <v>0.047685</v>
       </c>
       <c r="C953" t="n">
         <v>0.470745</v>
@@ -12816,7 +12816,7 @@
         </is>
       </c>
       <c r="B954" t="n">
-        <v>0.047594</v>
+        <v>0.047814</v>
       </c>
       <c r="C954" t="n">
         <v>0.468085</v>
@@ -12829,7 +12829,7 @@
         </is>
       </c>
       <c r="B955" t="n">
-        <v>0.047777</v>
+        <v>0.047873</v>
       </c>
       <c r="C955" t="n">
         <v>0.465426</v>
@@ -12842,7 +12842,7 @@
         </is>
       </c>
       <c r="B956" t="n">
-        <v>0.04815</v>
+        <v>0.048256</v>
       </c>
       <c r="C956" t="n">
         <v>0.462766</v>
@@ -12855,7 +12855,7 @@
         </is>
       </c>
       <c r="B957" t="n">
-        <v>0.048962</v>
+        <v>0.049197</v>
       </c>
       <c r="C957" t="n">
         <v>0.460106</v>
@@ -12868,7 +12868,7 @@
         </is>
       </c>
       <c r="B958" t="n">
-        <v>0.049217</v>
+        <v>0.049535</v>
       </c>
       <c r="C958" t="n">
         <v>0.457447</v>
@@ -12881,7 +12881,7 @@
         </is>
       </c>
       <c r="B959" t="n">
-        <v>0.049643</v>
+        <v>0.049811</v>
       </c>
       <c r="C959" t="n">
         <v>0.454787</v>
@@ -12894,7 +12894,7 @@
         </is>
       </c>
       <c r="B960" t="n">
-        <v>0.05024</v>
+        <v>0.050237</v>
       </c>
       <c r="C960" t="n">
         <v>0.452128</v>
@@ -12907,7 +12907,7 @@
         </is>
       </c>
       <c r="B961" t="n">
-        <v>0.05025</v>
+        <v>0.050348</v>
       </c>
       <c r="C961" t="n">
         <v>0.449468</v>
@@ -12920,7 +12920,7 @@
         </is>
       </c>
       <c r="B962" t="n">
-        <v>0.050675</v>
+        <v>0.050741</v>
       </c>
       <c r="C962" t="n">
         <v>0.446809</v>
@@ -12933,7 +12933,7 @@
         </is>
       </c>
       <c r="B963" t="n">
-        <v>0.050806</v>
+        <v>0.050877</v>
       </c>
       <c r="C963" t="n">
         <v>0.444149</v>
@@ -12946,7 +12946,7 @@
         </is>
       </c>
       <c r="B964" t="n">
-        <v>0.051179</v>
+        <v>0.051196</v>
       </c>
       <c r="C964" t="n">
         <v>0.441489</v>
@@ -12959,7 +12959,7 @@
         </is>
       </c>
       <c r="B965" t="n">
-        <v>0.051368</v>
+        <v>0.051382</v>
       </c>
       <c r="C965" t="n">
         <v>0.43883</v>
@@ -12972,7 +12972,7 @@
         </is>
       </c>
       <c r="B966" t="n">
-        <v>0.051426</v>
+        <v>0.051408</v>
       </c>
       <c r="C966" t="n">
         <v>0.43617</v>
@@ -12985,7 +12985,7 @@
         </is>
       </c>
       <c r="B967" t="n">
-        <v>0.0515</v>
+        <v>0.051538</v>
       </c>
       <c r="C967" t="n">
         <v>0.433511</v>
@@ -12998,7 +12998,7 @@
         </is>
       </c>
       <c r="B968" t="n">
-        <v>0.051601</v>
+        <v>0.051793</v>
       </c>
       <c r="C968" t="n">
         <v>0.430851</v>
@@ -13011,7 +13011,7 @@
         </is>
       </c>
       <c r="B969" t="n">
-        <v>0.05275</v>
+        <v>0.052636</v>
       </c>
       <c r="C969" t="n">
         <v>0.428191</v>
@@ -13024,7 +13024,7 @@
         </is>
       </c>
       <c r="B970" t="n">
-        <v>0.053063</v>
+        <v>0.053451</v>
       </c>
       <c r="C970" t="n">
         <v>0.425532</v>
@@ -13037,7 +13037,7 @@
         </is>
       </c>
       <c r="B971" t="n">
-        <v>0.053531</v>
+        <v>0.053669</v>
       </c>
       <c r="C971" t="n">
         <v>0.422872</v>
@@ -13050,7 +13050,7 @@
         </is>
       </c>
       <c r="B972" t="n">
-        <v>0.053793</v>
+        <v>0.053844</v>
       </c>
       <c r="C972" t="n">
         <v>0.420213</v>
@@ -13063,7 +13063,7 @@
         </is>
       </c>
       <c r="B973" t="n">
-        <v>0.053812</v>
+        <v>0.053998</v>
       </c>
       <c r="C973" t="n">
         <v>0.417553</v>
@@ -13076,7 +13076,7 @@
         </is>
       </c>
       <c r="B974" t="n">
-        <v>0.055512</v>
+        <v>0.055483</v>
       </c>
       <c r="C974" t="n">
         <v>0.414894</v>
@@ -13089,7 +13089,7 @@
         </is>
       </c>
       <c r="B975" t="n">
-        <v>0.055977</v>
+        <v>0.056424</v>
       </c>
       <c r="C975" t="n">
         <v>0.412234</v>
@@ -13102,7 +13102,7 @@
         </is>
       </c>
       <c r="B976" t="n">
-        <v>0.056284</v>
+        <v>0.056641</v>
       </c>
       <c r="C976" t="n">
         <v>0.409574</v>
@@ -13115,7 +13115,7 @@
         </is>
       </c>
       <c r="B977" t="n">
-        <v>0.057903</v>
+        <v>0.058237</v>
       </c>
       <c r="C977" t="n">
         <v>0.406915</v>
@@ -13128,7 +13128,7 @@
         </is>
       </c>
       <c r="B978" t="n">
-        <v>0.057942</v>
+        <v>0.058238</v>
       </c>
       <c r="C978" t="n">
         <v>0.404255</v>
@@ -13141,7 +13141,7 @@
         </is>
       </c>
       <c r="B979" t="n">
-        <v>0.05871</v>
+        <v>0.058948</v>
       </c>
       <c r="C979" t="n">
         <v>0.401596</v>
@@ -13154,7 +13154,7 @@
         </is>
       </c>
       <c r="B980" t="n">
-        <v>0.058888</v>
+        <v>0.059073</v>
       </c>
       <c r="C980" t="n">
         <v>0.398936</v>
@@ -13167,7 +13167,7 @@
         </is>
       </c>
       <c r="B981" t="n">
-        <v>0.059308</v>
+        <v>0.059266</v>
       </c>
       <c r="C981" t="n">
         <v>0.396277</v>
@@ -13180,7 +13180,7 @@
         </is>
       </c>
       <c r="B982" t="n">
-        <v>0.059511</v>
+        <v>0.059934</v>
       </c>
       <c r="C982" t="n">
         <v>0.393617</v>
@@ -13193,7 +13193,7 @@
         </is>
       </c>
       <c r="B983" t="n">
-        <v>0.059759</v>
+        <v>0.060077</v>
       </c>
       <c r="C983" t="n">
         <v>0.390957</v>
@@ -13206,7 +13206,7 @@
         </is>
       </c>
       <c r="B984" t="n">
-        <v>0.060297</v>
+        <v>0.060589</v>
       </c>
       <c r="C984" t="n">
         <v>0.388298</v>
@@ -13219,7 +13219,7 @@
         </is>
       </c>
       <c r="B985" t="n">
-        <v>0.060451</v>
+        <v>0.060768</v>
       </c>
       <c r="C985" t="n">
         <v>0.385638</v>
@@ -13232,7 +13232,7 @@
         </is>
       </c>
       <c r="B986" t="n">
-        <v>0.060654</v>
+        <v>0.060791</v>
       </c>
       <c r="C986" t="n">
         <v>0.382979</v>
@@ -13245,7 +13245,7 @@
         </is>
       </c>
       <c r="B987" t="n">
-        <v>0.060861</v>
+        <v>0.061036</v>
       </c>
       <c r="C987" t="n">
         <v>0.380319</v>
@@ -13258,7 +13258,7 @@
         </is>
       </c>
       <c r="B988" t="n">
-        <v>0.061037</v>
+        <v>0.061242</v>
       </c>
       <c r="C988" t="n">
         <v>0.37766</v>
@@ -13271,7 +13271,7 @@
         </is>
       </c>
       <c r="B989" t="n">
-        <v>0.061226</v>
+        <v>0.061753</v>
       </c>
       <c r="C989" t="n">
         <v>0.375</v>
@@ -13284,7 +13284,7 @@
         </is>
       </c>
       <c r="B990" t="n">
-        <v>0.061406</v>
+        <v>0.061819</v>
       </c>
       <c r="C990" t="n">
         <v>0.37234</v>
@@ -13297,7 +13297,7 @@
         </is>
       </c>
       <c r="B991" t="n">
-        <v>0.061531</v>
+        <v>0.061968</v>
       </c>
       <c r="C991" t="n">
         <v>0.369681</v>
@@ -13310,7 +13310,7 @@
         </is>
       </c>
       <c r="B992" t="n">
-        <v>0.061901</v>
+        <v>0.062177</v>
       </c>
       <c r="C992" t="n">
         <v>0.367021</v>
@@ -13336,7 +13336,7 @@
         </is>
       </c>
       <c r="B994" t="n">
-        <v>0.062285</v>
+        <v>0.062476</v>
       </c>
       <c r="C994" t="n">
         <v>0.361702</v>
@@ -13349,7 +13349,7 @@
         </is>
       </c>
       <c r="B995" t="n">
-        <v>0.062496</v>
+        <v>0.062987</v>
       </c>
       <c r="C995" t="n">
         <v>0.359043</v>
@@ -13362,7 +13362,7 @@
         </is>
       </c>
       <c r="B996" t="n">
-        <v>0.063001</v>
+        <v>0.06324</v>
       </c>
       <c r="C996" t="n">
         <v>0.356383</v>
@@ -13375,7 +13375,7 @@
         </is>
       </c>
       <c r="B997" t="n">
-        <v>0.063361</v>
+        <v>0.06367200000000001</v>
       </c>
       <c r="C997" t="n">
         <v>0.353723</v>
@@ -13388,7 +13388,7 @@
         </is>
       </c>
       <c r="B998" t="n">
-        <v>0.06370199999999999</v>
+        <v>0.06443</v>
       </c>
       <c r="C998" t="n">
         <v>0.351064</v>
@@ -13401,7 +13401,7 @@
         </is>
       </c>
       <c r="B999" t="n">
-        <v>0.063987</v>
+        <v>0.064693</v>
       </c>
       <c r="C999" t="n">
         <v>0.348404</v>
@@ -13414,7 +13414,7 @@
         </is>
       </c>
       <c r="B1000" t="n">
-        <v>0.064281</v>
+        <v>0.06518500000000001</v>
       </c>
       <c r="C1000" t="n">
         <v>0.345745</v>
@@ -13427,7 +13427,7 @@
         </is>
       </c>
       <c r="B1001" t="n">
-        <v>0.065069</v>
+        <v>0.065301</v>
       </c>
       <c r="C1001" t="n">
         <v>0.343085</v>
@@ -13440,7 +13440,7 @@
         </is>
       </c>
       <c r="B1002" t="n">
-        <v>0.06525</v>
+        <v>0.065678</v>
       </c>
       <c r="C1002" t="n">
         <v>0.340426</v>
@@ -13453,7 +13453,7 @@
         </is>
       </c>
       <c r="B1003" t="n">
-        <v>0.065555</v>
+        <v>0.065738</v>
       </c>
       <c r="C1003" t="n">
         <v>0.337766</v>
@@ -13466,7 +13466,7 @@
         </is>
       </c>
       <c r="B1004" t="n">
-        <v>0.065749</v>
+        <v>0.065912</v>
       </c>
       <c r="C1004" t="n">
         <v>0.335106</v>
@@ -13479,7 +13479,7 @@
         </is>
       </c>
       <c r="B1005" t="n">
-        <v>0.066123</v>
+        <v>0.067062</v>
       </c>
       <c r="C1005" t="n">
         <v>0.332447</v>
@@ -13492,7 +13492,7 @@
         </is>
       </c>
       <c r="B1006" t="n">
-        <v>0.06677900000000001</v>
+        <v>0.067372</v>
       </c>
       <c r="C1006" t="n">
         <v>0.329787</v>
@@ -13505,7 +13505,7 @@
         </is>
       </c>
       <c r="B1007" t="n">
-        <v>0.06703199999999999</v>
+        <v>0.06750399999999999</v>
       </c>
       <c r="C1007" t="n">
         <v>0.327128</v>
@@ -13518,7 +13518,7 @@
         </is>
       </c>
       <c r="B1008" t="n">
-        <v>0.067145</v>
+        <v>0.06756</v>
       </c>
       <c r="C1008" t="n">
         <v>0.324468</v>
@@ -13531,7 +13531,7 @@
         </is>
       </c>
       <c r="B1009" t="n">
-        <v>0.06722499999999999</v>
+        <v>0.068274</v>
       </c>
       <c r="C1009" t="n">
         <v>0.321809</v>
@@ -13544,7 +13544,7 @@
         </is>
       </c>
       <c r="B1010" t="n">
-        <v>0.06834800000000001</v>
+        <v>0.068784</v>
       </c>
       <c r="C1010" t="n">
         <v>0.319149</v>
@@ -13557,7 +13557,7 @@
         </is>
       </c>
       <c r="B1011" t="n">
-        <v>0.068522</v>
+        <v>0.06887600000000001</v>
       </c>
       <c r="C1011" t="n">
         <v>0.316489</v>
@@ -13570,7 +13570,7 @@
         </is>
       </c>
       <c r="B1012" t="n">
-        <v>0.069234</v>
+        <v>0.069426</v>
       </c>
       <c r="C1012" t="n">
         <v>0.31383</v>
@@ -13583,7 +13583,7 @@
         </is>
       </c>
       <c r="B1013" t="n">
-        <v>0.06932099999999999</v>
+        <v>0.069582</v>
       </c>
       <c r="C1013" t="n">
         <v>0.31117</v>
@@ -13596,7 +13596,7 @@
         </is>
       </c>
       <c r="B1014" t="n">
-        <v>0.069509</v>
+        <v>0.069674</v>
       </c>
       <c r="C1014" t="n">
         <v>0.308511</v>
@@ -13609,7 +13609,7 @@
         </is>
       </c>
       <c r="B1015" t="n">
-        <v>0.069689</v>
+        <v>0.06977899999999999</v>
       </c>
       <c r="C1015" t="n">
         <v>0.305851</v>
@@ -13622,7 +13622,7 @@
         </is>
       </c>
       <c r="B1016" t="n">
-        <v>0.070365</v>
+        <v>0.07023500000000001</v>
       </c>
       <c r="C1016" t="n">
         <v>0.303191</v>
@@ -13635,7 +13635,7 @@
         </is>
       </c>
       <c r="B1017" t="n">
-        <v>0.07091799999999999</v>
+        <v>0.071411</v>
       </c>
       <c r="C1017" t="n">
         <v>0.300532</v>
@@ -13648,7 +13648,7 @@
         </is>
       </c>
       <c r="B1018" t="n">
-        <v>0.071704</v>
+        <v>0.07176100000000001</v>
       </c>
       <c r="C1018" t="n">
         <v>0.297872</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="B1019" t="n">
-        <v>0.07198300000000001</v>
+        <v>0.07220600000000001</v>
       </c>
       <c r="C1019" t="n">
         <v>0.295213</v>
@@ -13674,7 +13674,7 @@
         </is>
       </c>
       <c r="B1020" t="n">
-        <v>0.072204</v>
+        <v>0.07237399999999999</v>
       </c>
       <c r="C1020" t="n">
         <v>0.292553</v>
@@ -13687,7 +13687,7 @@
         </is>
       </c>
       <c r="B1021" t="n">
-        <v>0.073384</v>
+        <v>0.073805</v>
       </c>
       <c r="C1021" t="n">
         <v>0.289894</v>
@@ -13700,7 +13700,7 @@
         </is>
       </c>
       <c r="B1022" t="n">
-        <v>0.07352499999999999</v>
+        <v>0.07419000000000001</v>
       </c>
       <c r="C1022" t="n">
         <v>0.287234</v>
@@ -13713,7 +13713,7 @@
         </is>
       </c>
       <c r="B1023" t="n">
-        <v>0.073731</v>
+        <v>0.074771</v>
       </c>
       <c r="C1023" t="n">
         <v>0.284574</v>
@@ -13726,7 +13726,7 @@
         </is>
       </c>
       <c r="B1024" t="n">
-        <v>0.073989</v>
+        <v>0.075031</v>
       </c>
       <c r="C1024" t="n">
         <v>0.281915</v>
@@ -13739,7 +13739,7 @@
         </is>
       </c>
       <c r="B1025" t="n">
-        <v>0.075308</v>
+        <v>0.075402</v>
       </c>
       <c r="C1025" t="n">
         <v>0.279255</v>
@@ -13752,7 +13752,7 @@
         </is>
       </c>
       <c r="B1026" t="n">
-        <v>0.075823</v>
+        <v>0.075757</v>
       </c>
       <c r="C1026" t="n">
         <v>0.276596</v>
@@ -13765,7 +13765,7 @@
         </is>
       </c>
       <c r="B1027" t="n">
-        <v>0.075845</v>
+        <v>0.075972</v>
       </c>
       <c r="C1027" t="n">
         <v>0.273936</v>
@@ -13778,7 +13778,7 @@
         </is>
       </c>
       <c r="B1028" t="n">
-        <v>0.078196</v>
+        <v>0.078705</v>
       </c>
       <c r="C1028" t="n">
         <v>0.271277</v>
@@ -13791,7 +13791,7 @@
         </is>
       </c>
       <c r="B1029" t="n">
-        <v>0.078291</v>
+        <v>0.078831</v>
       </c>
       <c r="C1029" t="n">
         <v>0.268617</v>
@@ -13804,7 +13804,7 @@
         </is>
       </c>
       <c r="B1030" t="n">
-        <v>0.07947899999999999</v>
+        <v>0.079528</v>
       </c>
       <c r="C1030" t="n">
         <v>0.265957</v>
@@ -13817,7 +13817,7 @@
         </is>
       </c>
       <c r="B1031" t="n">
-        <v>0.07969999999999999</v>
+        <v>0.07975699999999999</v>
       </c>
       <c r="C1031" t="n">
         <v>0.263298</v>
@@ -13830,7 +13830,7 @@
         </is>
       </c>
       <c r="B1032" t="n">
-        <v>0.079765</v>
+        <v>0.080183</v>
       </c>
       <c r="C1032" t="n">
         <v>0.260638</v>
@@ -13843,7 +13843,7 @@
         </is>
       </c>
       <c r="B1033" t="n">
-        <v>0.079871</v>
+        <v>0.080415</v>
       </c>
       <c r="C1033" t="n">
         <v>0.257979</v>
@@ -13856,7 +13856,7 @@
         </is>
       </c>
       <c r="B1034" t="n">
-        <v>0.081049</v>
+        <v>0.081189</v>
       </c>
       <c r="C1034" t="n">
         <v>0.255319</v>
@@ -13869,7 +13869,7 @@
         </is>
       </c>
       <c r="B1035" t="n">
-        <v>0.081218</v>
+        <v>0.081833</v>
       </c>
       <c r="C1035" t="n">
         <v>0.25266</v>
@@ -13882,7 +13882,7 @@
         </is>
       </c>
       <c r="B1036" t="n">
-        <v>0.081888</v>
+        <v>0.081978</v>
       </c>
       <c r="C1036" t="n">
         <v>0.25</v>
@@ -13895,7 +13895,7 @@
         </is>
       </c>
       <c r="B1037" t="n">
-        <v>0.081896</v>
+        <v>0.08264199999999999</v>
       </c>
       <c r="C1037" t="n">
         <v>0.24734</v>
@@ -13908,7 +13908,7 @@
         </is>
       </c>
       <c r="B1038" t="n">
-        <v>0.082232</v>
+        <v>0.083061</v>
       </c>
       <c r="C1038" t="n">
         <v>0.244681</v>
@@ -13921,7 +13921,7 @@
         </is>
       </c>
       <c r="B1039" t="n">
-        <v>0.08303199999999999</v>
+        <v>0.08318399999999999</v>
       </c>
       <c r="C1039" t="n">
         <v>0.242021</v>
@@ -13934,7 +13934,7 @@
         </is>
       </c>
       <c r="B1040" t="n">
-        <v>0.08307199999999999</v>
+        <v>0.083386</v>
       </c>
       <c r="C1040" t="n">
         <v>0.239362</v>
@@ -13947,7 +13947,7 @@
         </is>
       </c>
       <c r="B1041" t="n">
-        <v>0.08338</v>
+        <v>0.083755</v>
       </c>
       <c r="C1041" t="n">
         <v>0.236702</v>
@@ -13960,7 +13960,7 @@
         </is>
       </c>
       <c r="B1042" t="n">
-        <v>0.083858</v>
+        <v>0.08393299999999999</v>
       </c>
       <c r="C1042" t="n">
         <v>0.234043</v>
@@ -13973,7 +13973,7 @@
         </is>
       </c>
       <c r="B1043" t="n">
-        <v>0.084985</v>
+        <v>0.085629</v>
       </c>
       <c r="C1043" t="n">
         <v>0.231383</v>
@@ -13986,7 +13986,7 @@
         </is>
       </c>
       <c r="B1044" t="n">
-        <v>0.085801</v>
+        <v>0.08570700000000001</v>
       </c>
       <c r="C1044" t="n">
         <v>0.228723</v>
@@ -13999,7 +13999,7 @@
         </is>
       </c>
       <c r="B1045" t="n">
-        <v>0.086243</v>
+        <v>0.086189</v>
       </c>
       <c r="C1045" t="n">
         <v>0.226064</v>
@@ -14012,7 +14012,7 @@
         </is>
       </c>
       <c r="B1046" t="n">
-        <v>0.086245</v>
+        <v>0.086427</v>
       </c>
       <c r="C1046" t="n">
         <v>0.223404</v>
@@ -14025,7 +14025,7 @@
         </is>
       </c>
       <c r="B1047" t="n">
-        <v>0.086407</v>
+        <v>0.086727</v>
       </c>
       <c r="C1047" t="n">
         <v>0.220745</v>
@@ -14038,7 +14038,7 @@
         </is>
       </c>
       <c r="B1048" t="n">
-        <v>0.086412</v>
+        <v>0.08765100000000001</v>
       </c>
       <c r="C1048" t="n">
         <v>0.218085</v>
@@ -14051,7 +14051,7 @@
         </is>
       </c>
       <c r="B1049" t="n">
-        <v>0.08697299999999999</v>
+        <v>0.087795</v>
       </c>
       <c r="C1049" t="n">
         <v>0.215426</v>
@@ -14064,7 +14064,7 @@
         </is>
       </c>
       <c r="B1050" t="n">
-        <v>0.087006</v>
+        <v>0.087937</v>
       </c>
       <c r="C1050" t="n">
         <v>0.212766</v>
@@ -14077,7 +14077,7 @@
         </is>
       </c>
       <c r="B1051" t="n">
-        <v>0.08917600000000001</v>
+        <v>0.08930299999999999</v>
       </c>
       <c r="C1051" t="n">
         <v>0.210106</v>
@@ -14090,7 +14090,7 @@
         </is>
       </c>
       <c r="B1052" t="n">
-        <v>0.089355</v>
+        <v>0.08956699999999999</v>
       </c>
       <c r="C1052" t="n">
         <v>0.207447</v>
@@ -14103,7 +14103,7 @@
         </is>
       </c>
       <c r="B1053" t="n">
-        <v>0.089966</v>
+        <v>0.090612</v>
       </c>
       <c r="C1053" t="n">
         <v>0.204787</v>
@@ -14116,7 +14116,7 @@
         </is>
       </c>
       <c r="B1054" t="n">
-        <v>0.090721</v>
+        <v>0.091115</v>
       </c>
       <c r="C1054" t="n">
         <v>0.202128</v>
@@ -14129,7 +14129,7 @@
         </is>
       </c>
       <c r="B1055" t="n">
-        <v>0.09077</v>
+        <v>0.091698</v>
       </c>
       <c r="C1055" t="n">
         <v>0.199468</v>
@@ -14142,7 +14142,7 @@
         </is>
       </c>
       <c r="B1056" t="n">
-        <v>0.091664</v>
+        <v>0.09288100000000001</v>
       </c>
       <c r="C1056" t="n">
         <v>0.196809</v>
@@ -14155,7 +14155,7 @@
         </is>
       </c>
       <c r="B1057" t="n">
-        <v>0.092575</v>
+        <v>0.092921</v>
       </c>
       <c r="C1057" t="n">
         <v>0.194149</v>
@@ -14168,7 +14168,7 @@
         </is>
       </c>
       <c r="B1058" t="n">
-        <v>0.093053</v>
+        <v>0.092982</v>
       </c>
       <c r="C1058" t="n">
         <v>0.191489</v>
@@ -14181,7 +14181,7 @@
         </is>
       </c>
       <c r="B1059" t="n">
-        <v>0.09346</v>
+        <v>0.093586</v>
       </c>
       <c r="C1059" t="n">
         <v>0.18883</v>
@@ -14194,7 +14194,7 @@
         </is>
       </c>
       <c r="B1060" t="n">
-        <v>0.09407</v>
+        <v>0.09410200000000001</v>
       </c>
       <c r="C1060" t="n">
         <v>0.18617</v>
@@ -14207,7 +14207,7 @@
         </is>
       </c>
       <c r="B1061" t="n">
-        <v>0.095896</v>
+        <v>0.096011</v>
       </c>
       <c r="C1061" t="n">
         <v>0.183511</v>
@@ -14220,7 +14220,7 @@
         </is>
       </c>
       <c r="B1062" t="n">
-        <v>0.095974</v>
+        <v>0.09614200000000001</v>
       </c>
       <c r="C1062" t="n">
         <v>0.180851</v>
@@ -14233,7 +14233,7 @@
         </is>
       </c>
       <c r="B1063" t="n">
-        <v>0.099077</v>
+        <v>0.099082</v>
       </c>
       <c r="C1063" t="n">
         <v>0.178191</v>
@@ -14246,7 +14246,7 @@
         </is>
       </c>
       <c r="B1064" t="n">
-        <v>0.100687</v>
+        <v>0.100704</v>
       </c>
       <c r="C1064" t="n">
         <v>0.175532</v>
@@ -14259,7 +14259,7 @@
         </is>
       </c>
       <c r="B1065" t="n">
-        <v>0.100929</v>
+        <v>0.102464</v>
       </c>
       <c r="C1065" t="n">
         <v>0.172872</v>
@@ -14272,7 +14272,7 @@
         </is>
       </c>
       <c r="B1066" t="n">
-        <v>0.102885</v>
+        <v>0.10299</v>
       </c>
       <c r="C1066" t="n">
         <v>0.170213</v>
@@ -14285,7 +14285,7 @@
         </is>
       </c>
       <c r="B1067" t="n">
-        <v>0.103178</v>
+        <v>0.103545</v>
       </c>
       <c r="C1067" t="n">
         <v>0.167553</v>
@@ -14298,7 +14298,7 @@
         </is>
       </c>
       <c r="B1068" t="n">
-        <v>0.103776</v>
+        <v>0.103736</v>
       </c>
       <c r="C1068" t="n">
         <v>0.164894</v>
@@ -14311,7 +14311,7 @@
         </is>
       </c>
       <c r="B1069" t="n">
-        <v>0.105422</v>
+        <v>0.106351</v>
       </c>
       <c r="C1069" t="n">
         <v>0.162234</v>
@@ -14324,7 +14324,7 @@
         </is>
       </c>
       <c r="B1070" t="n">
-        <v>0.105556</v>
+        <v>0.10684</v>
       </c>
       <c r="C1070" t="n">
         <v>0.159574</v>
@@ -14337,7 +14337,7 @@
         </is>
       </c>
       <c r="B1071" t="n">
-        <v>0.106974</v>
+        <v>0.10719</v>
       </c>
       <c r="C1071" t="n">
         <v>0.156915</v>
@@ -14350,7 +14350,7 @@
         </is>
       </c>
       <c r="B1072" t="n">
-        <v>0.108515</v>
+        <v>0.109275</v>
       </c>
       <c r="C1072" t="n">
         <v>0.154255</v>
@@ -14363,7 +14363,7 @@
         </is>
       </c>
       <c r="B1073" t="n">
-        <v>0.109248</v>
+        <v>0.109934</v>
       </c>
       <c r="C1073" t="n">
         <v>0.151596</v>
@@ -14376,7 +14376,7 @@
         </is>
       </c>
       <c r="B1074" t="n">
-        <v>0.110221</v>
+        <v>0.110546</v>
       </c>
       <c r="C1074" t="n">
         <v>0.148936</v>
@@ -14389,7 +14389,7 @@
         </is>
       </c>
       <c r="B1075" t="n">
-        <v>0.111917</v>
+        <v>0.111874</v>
       </c>
       <c r="C1075" t="n">
         <v>0.146277</v>
@@ -14402,7 +14402,7 @@
         </is>
       </c>
       <c r="B1076" t="n">
-        <v>0.113267</v>
+        <v>0.11311</v>
       </c>
       <c r="C1076" t="n">
         <v>0.143617</v>
@@ -14415,7 +14415,7 @@
         </is>
       </c>
       <c r="B1077" t="n">
-        <v>0.11448</v>
+        <v>0.114854</v>
       </c>
       <c r="C1077" t="n">
         <v>0.140957</v>
@@ -14428,7 +14428,7 @@
         </is>
       </c>
       <c r="B1078" t="n">
-        <v>0.114652</v>
+        <v>0.115045</v>
       </c>
       <c r="C1078" t="n">
         <v>0.138298</v>
@@ -14441,7 +14441,7 @@
         </is>
       </c>
       <c r="B1079" t="n">
-        <v>0.114899</v>
+        <v>0.11552</v>
       </c>
       <c r="C1079" t="n">
         <v>0.135638</v>
@@ -14454,7 +14454,7 @@
         </is>
       </c>
       <c r="B1080" t="n">
-        <v>0.115757</v>
+        <v>0.116066</v>
       </c>
       <c r="C1080" t="n">
         <v>0.132979</v>
@@ -14467,7 +14467,7 @@
         </is>
       </c>
       <c r="B1081" t="n">
-        <v>0.116168</v>
+        <v>0.116305</v>
       </c>
       <c r="C1081" t="n">
         <v>0.130319</v>
@@ -14480,7 +14480,7 @@
         </is>
       </c>
       <c r="B1082" t="n">
-        <v>0.116246</v>
+        <v>0.11751</v>
       </c>
       <c r="C1082" t="n">
         <v>0.12766</v>
@@ -14493,7 +14493,7 @@
         </is>
       </c>
       <c r="B1083" t="n">
-        <v>0.117031</v>
+        <v>0.117684</v>
       </c>
       <c r="C1083" t="n">
         <v>0.125</v>
@@ -14506,7 +14506,7 @@
         </is>
       </c>
       <c r="B1084" t="n">
-        <v>0.117618</v>
+        <v>0.118111</v>
       </c>
       <c r="C1084" t="n">
         <v>0.12234</v>
@@ -14519,7 +14519,7 @@
         </is>
       </c>
       <c r="B1085" t="n">
-        <v>0.120327</v>
+        <v>0.121178</v>
       </c>
       <c r="C1085" t="n">
         <v>0.119681</v>
@@ -14532,7 +14532,7 @@
         </is>
       </c>
       <c r="B1086" t="n">
-        <v>0.120787</v>
+        <v>0.121626</v>
       </c>
       <c r="C1086" t="n">
         <v>0.117021</v>
@@ -14545,7 +14545,7 @@
         </is>
       </c>
       <c r="B1087" t="n">
-        <v>0.12155</v>
+        <v>0.122422</v>
       </c>
       <c r="C1087" t="n">
         <v>0.114362</v>
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="B1088" t="n">
-        <v>0.123949</v>
+        <v>0.1243</v>
       </c>
       <c r="C1088" t="n">
         <v>0.111702</v>
@@ -14571,7 +14571,7 @@
         </is>
       </c>
       <c r="B1089" t="n">
-        <v>0.124996</v>
+        <v>0.125932</v>
       </c>
       <c r="C1089" t="n">
         <v>0.109043</v>
@@ -14584,7 +14584,7 @@
         </is>
       </c>
       <c r="B1090" t="n">
-        <v>0.12587</v>
+        <v>0.125941</v>
       </c>
       <c r="C1090" t="n">
         <v>0.106383</v>
@@ -14597,7 +14597,7 @@
         </is>
       </c>
       <c r="B1091" t="n">
-        <v>0.126157</v>
+        <v>0.127022</v>
       </c>
       <c r="C1091" t="n">
         <v>0.103723</v>
@@ -14610,7 +14610,7 @@
         </is>
       </c>
       <c r="B1092" t="n">
-        <v>0.127704</v>
+        <v>0.128113</v>
       </c>
       <c r="C1092" t="n">
         <v>0.101064</v>
@@ -14623,7 +14623,7 @@
         </is>
       </c>
       <c r="B1093" t="n">
-        <v>0.129016</v>
+        <v>0.129042</v>
       </c>
       <c r="C1093" t="n">
         <v>0.09840400000000001</v>
@@ -14636,7 +14636,7 @@
         </is>
       </c>
       <c r="B1094" t="n">
-        <v>0.129614</v>
+        <v>0.129393</v>
       </c>
       <c r="C1094" t="n">
         <v>0.095745</v>
@@ -14649,7 +14649,7 @@
         </is>
       </c>
       <c r="B1095" t="n">
-        <v>0.129772</v>
+        <v>0.129754</v>
       </c>
       <c r="C1095" t="n">
         <v>0.093085</v>
@@ -14662,7 +14662,7 @@
         </is>
       </c>
       <c r="B1096" t="n">
-        <v>0.130781</v>
+        <v>0.131398</v>
       </c>
       <c r="C1096" t="n">
         <v>0.09042600000000001</v>
@@ -14675,7 +14675,7 @@
         </is>
       </c>
       <c r="B1097" t="n">
-        <v>0.131024</v>
+        <v>0.131545</v>
       </c>
       <c r="C1097" t="n">
         <v>0.087766</v>
@@ -14688,7 +14688,7 @@
         </is>
       </c>
       <c r="B1098" t="n">
-        <v>0.135256</v>
+        <v>0.135059</v>
       </c>
       <c r="C1098" t="n">
         <v>0.085106</v>
@@ -14701,7 +14701,7 @@
         </is>
       </c>
       <c r="B1099" t="n">
-        <v>0.141811</v>
+        <v>0.144018</v>
       </c>
       <c r="C1099" t="n">
         <v>0.08244700000000001</v>
@@ -14714,7 +14714,7 @@
         </is>
       </c>
       <c r="B1100" t="n">
-        <v>0.142506</v>
+        <v>0.145397</v>
       </c>
       <c r="C1100" t="n">
         <v>0.079787</v>
@@ -14727,7 +14727,7 @@
         </is>
       </c>
       <c r="B1101" t="n">
-        <v>0.147631</v>
+        <v>0.147686</v>
       </c>
       <c r="C1101" t="n">
         <v>0.077128</v>
@@ -14740,7 +14740,7 @@
         </is>
       </c>
       <c r="B1102" t="n">
-        <v>0.148436</v>
+        <v>0.148873</v>
       </c>
       <c r="C1102" t="n">
         <v>0.07446800000000001</v>
@@ -14753,7 +14753,7 @@
         </is>
       </c>
       <c r="B1103" t="n">
-        <v>0.150463</v>
+        <v>0.15064</v>
       </c>
       <c r="C1103" t="n">
         <v>0.071809</v>
@@ -14766,7 +14766,7 @@
         </is>
       </c>
       <c r="B1104" t="n">
-        <v>0.152867</v>
+        <v>0.155715</v>
       </c>
       <c r="C1104" t="n">
         <v>0.069149</v>
@@ -14779,7 +14779,7 @@
         </is>
       </c>
       <c r="B1105" t="n">
-        <v>0.154925</v>
+        <v>0.15608</v>
       </c>
       <c r="C1105" t="n">
         <v>0.06648900000000001</v>
@@ -14792,7 +14792,7 @@
         </is>
       </c>
       <c r="B1106" t="n">
-        <v>0.155894</v>
+        <v>0.156676</v>
       </c>
       <c r="C1106" t="n">
         <v>0.06383</v>
@@ -14805,7 +14805,7 @@
         </is>
       </c>
       <c r="B1107" t="n">
-        <v>0.157197</v>
+        <v>0.158743</v>
       </c>
       <c r="C1107" t="n">
         <v>0.06117</v>
@@ -14818,7 +14818,7 @@
         </is>
       </c>
       <c r="B1108" t="n">
-        <v>0.160992</v>
+        <v>0.161444</v>
       </c>
       <c r="C1108" t="n">
         <v>0.058511</v>
@@ -14831,7 +14831,7 @@
         </is>
       </c>
       <c r="B1109" t="n">
-        <v>0.162152</v>
+        <v>0.163437</v>
       </c>
       <c r="C1109" t="n">
         <v>0.055851</v>
@@ -14844,7 +14844,7 @@
         </is>
       </c>
       <c r="B1110" t="n">
-        <v>0.164067</v>
+        <v>0.164059</v>
       </c>
       <c r="C1110" t="n">
         <v>0.053191</v>
@@ -14857,7 +14857,7 @@
         </is>
       </c>
       <c r="B1111" t="n">
-        <v>0.167264</v>
+        <v>0.167153</v>
       </c>
       <c r="C1111" t="n">
         <v>0.050532</v>
@@ -14870,7 +14870,7 @@
         </is>
       </c>
       <c r="B1112" t="n">
-        <v>0.170355</v>
+        <v>0.172229</v>
       </c>
       <c r="C1112" t="n">
         <v>0.047872</v>
@@ -14883,7 +14883,7 @@
         </is>
       </c>
       <c r="B1113" t="n">
-        <v>0.172775</v>
+        <v>0.173719</v>
       </c>
       <c r="C1113" t="n">
         <v>0.045213</v>
@@ -14896,7 +14896,7 @@
         </is>
       </c>
       <c r="B1114" t="n">
-        <v>0.173622</v>
+        <v>0.176217</v>
       </c>
       <c r="C1114" t="n">
         <v>0.042553</v>
@@ -14909,7 +14909,7 @@
         </is>
       </c>
       <c r="B1115" t="n">
-        <v>0.175616</v>
+        <v>0.177813</v>
       </c>
       <c r="C1115" t="n">
         <v>0.039894</v>
@@ -14922,7 +14922,7 @@
         </is>
       </c>
       <c r="B1116" t="n">
-        <v>0.18581</v>
+        <v>0.186016</v>
       </c>
       <c r="C1116" t="n">
         <v>0.037234</v>
@@ -14935,7 +14935,7 @@
         </is>
       </c>
       <c r="B1117" t="n">
-        <v>0.189325</v>
+        <v>0.190864</v>
       </c>
       <c r="C1117" t="n">
         <v>0.034574</v>
@@ -14948,7 +14948,7 @@
         </is>
       </c>
       <c r="B1118" t="n">
-        <v>0.194149</v>
+        <v>0.199352</v>
       </c>
       <c r="C1118" t="n">
         <v>0.031915</v>
@@ -14961,7 +14961,7 @@
         </is>
       </c>
       <c r="B1119" t="n">
-        <v>0.199563</v>
+        <v>0.203021</v>
       </c>
       <c r="C1119" t="n">
         <v>0.029255</v>
@@ -14974,7 +14974,7 @@
         </is>
       </c>
       <c r="B1120" t="n">
-        <v>0.209406</v>
+        <v>0.212222</v>
       </c>
       <c r="C1120" t="n">
         <v>0.026596</v>
@@ -14987,7 +14987,7 @@
         </is>
       </c>
       <c r="B1121" t="n">
-        <v>0.220212</v>
+        <v>0.22041</v>
       </c>
       <c r="C1121" t="n">
         <v>0.023936</v>
@@ -15000,7 +15000,7 @@
         </is>
       </c>
       <c r="B1122" t="n">
-        <v>0.220921</v>
+        <v>0.221862</v>
       </c>
       <c r="C1122" t="n">
         <v>0.021277</v>
@@ -15013,7 +15013,7 @@
         </is>
       </c>
       <c r="B1123" t="n">
-        <v>0.227718</v>
+        <v>0.228795</v>
       </c>
       <c r="C1123" t="n">
         <v>0.018617</v>
@@ -15026,7 +15026,7 @@
         </is>
       </c>
       <c r="B1124" t="n">
-        <v>0.244295</v>
+        <v>0.244795</v>
       </c>
       <c r="C1124" t="n">
         <v>0.015957</v>
@@ -15039,7 +15039,7 @@
         </is>
       </c>
       <c r="B1125" t="n">
-        <v>0.27317</v>
+        <v>0.274097</v>
       </c>
       <c r="C1125" t="n">
         <v>0.013298</v>
@@ -15052,7 +15052,7 @@
         </is>
       </c>
       <c r="B1126" t="n">
-        <v>0.274223</v>
+        <v>0.275792</v>
       </c>
       <c r="C1126" t="n">
         <v>0.010638</v>
@@ -15065,7 +15065,7 @@
         </is>
       </c>
       <c r="B1127" t="n">
-        <v>0.309013</v>
+        <v>0.309272</v>
       </c>
       <c r="C1127" t="n">
         <v>0.007979</v>
@@ -15078,7 +15078,7 @@
         </is>
       </c>
       <c r="B1128" t="n">
-        <v>0.34293</v>
+        <v>0.346301</v>
       </c>
       <c r="C1128" t="n">
         <v>0.005319</v>
@@ -15091,7 +15091,7 @@
         </is>
       </c>
       <c r="B1129" t="n">
-        <v>0.398444</v>
+        <v>0.401648</v>
       </c>
       <c r="C1129" t="n">
         <v>0.00266</v>

--- a/vignettes/vignette-2/tail_exceedance_plot_data.xlsx
+++ b/vignettes/vignette-2/tail_exceedance_plot_data.xlsx
@@ -5250,7 +5250,7 @@
         </is>
       </c>
       <c r="B372" t="n">
-        <v>0.000296</v>
+        <v>0.000299</v>
       </c>
       <c r="C372" t="n">
         <v>0.994565</v>
@@ -5263,7 +5263,7 @@
         </is>
       </c>
       <c r="B373" t="n">
-        <v>0.000475</v>
+        <v>0.000476</v>
       </c>
       <c r="C373" t="n">
         <v>0.991848</v>
@@ -5276,7 +5276,7 @@
         </is>
       </c>
       <c r="B374" t="n">
-        <v>0.000966</v>
+        <v>0.000972</v>
       </c>
       <c r="C374" t="n">
         <v>0.98913</v>
@@ -5289,7 +5289,7 @@
         </is>
       </c>
       <c r="B375" t="n">
-        <v>0.001529</v>
+        <v>0.001548</v>
       </c>
       <c r="C375" t="n">
         <v>0.986413</v>
@@ -5302,7 +5302,7 @@
         </is>
       </c>
       <c r="B376" t="n">
-        <v>0.001816</v>
+        <v>0.00181</v>
       </c>
       <c r="C376" t="n">
         <v>0.983696</v>
@@ -5315,7 +5315,7 @@
         </is>
       </c>
       <c r="B377" t="n">
-        <v>0.001873</v>
+        <v>0.001893</v>
       </c>
       <c r="C377" t="n">
         <v>0.980978</v>
@@ -5328,7 +5328,7 @@
         </is>
       </c>
       <c r="B378" t="n">
-        <v>0.00204</v>
+        <v>0.002068</v>
       </c>
       <c r="C378" t="n">
         <v>0.978261</v>
@@ -5341,7 +5341,7 @@
         </is>
       </c>
       <c r="B379" t="n">
-        <v>0.002158</v>
+        <v>0.002184</v>
       </c>
       <c r="C379" t="n">
         <v>0.975543</v>
@@ -5354,7 +5354,7 @@
         </is>
       </c>
       <c r="B380" t="n">
-        <v>0.002741</v>
+        <v>0.002764</v>
       </c>
       <c r="C380" t="n">
         <v>0.972826</v>
@@ -5367,7 +5367,7 @@
         </is>
       </c>
       <c r="B381" t="n">
-        <v>0.002744</v>
+        <v>0.00278</v>
       </c>
       <c r="C381" t="n">
         <v>0.970109</v>
@@ -5380,7 +5380,7 @@
         </is>
       </c>
       <c r="B382" t="n">
-        <v>0.002985</v>
+        <v>0.003006</v>
       </c>
       <c r="C382" t="n">
         <v>0.967391</v>
@@ -5393,7 +5393,7 @@
         </is>
       </c>
       <c r="B383" t="n">
-        <v>0.003167</v>
+        <v>0.003209</v>
       </c>
       <c r="C383" t="n">
         <v>0.964674</v>
@@ -5406,7 +5406,7 @@
         </is>
       </c>
       <c r="B384" t="n">
-        <v>0.003925</v>
+        <v>0.003947</v>
       </c>
       <c r="C384" t="n">
         <v>0.961957</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="B385" t="n">
-        <v>0.003979</v>
+        <v>0.004004</v>
       </c>
       <c r="C385" t="n">
         <v>0.959239</v>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="B386" t="n">
-        <v>0.004406</v>
+        <v>0.004434</v>
       </c>
       <c r="C386" t="n">
         <v>0.956522</v>
@@ -5445,7 +5445,7 @@
         </is>
       </c>
       <c r="B387" t="n">
-        <v>0.004408</v>
+        <v>0.004461</v>
       </c>
       <c r="C387" t="n">
         <v>0.953804</v>
@@ -5458,7 +5458,7 @@
         </is>
       </c>
       <c r="B388" t="n">
-        <v>0.004436</v>
+        <v>0.004494</v>
       </c>
       <c r="C388" t="n">
         <v>0.951087</v>
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="B389" t="n">
-        <v>0.004485</v>
+        <v>0.00452</v>
       </c>
       <c r="C389" t="n">
         <v>0.94837</v>
@@ -5484,7 +5484,7 @@
         </is>
       </c>
       <c r="B390" t="n">
-        <v>0.004639</v>
+        <v>0.004629</v>
       </c>
       <c r="C390" t="n">
         <v>0.945652</v>
@@ -5497,7 +5497,7 @@
         </is>
       </c>
       <c r="B391" t="n">
-        <v>0.004706</v>
+        <v>0.004698</v>
       </c>
       <c r="C391" t="n">
         <v>0.942935</v>
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="B392" t="n">
-        <v>0.004742</v>
+        <v>0.004803</v>
       </c>
       <c r="C392" t="n">
         <v>0.940217</v>
@@ -5523,7 +5523,7 @@
         </is>
       </c>
       <c r="B393" t="n">
-        <v>0.004908</v>
+        <v>0.004946</v>
       </c>
       <c r="C393" t="n">
         <v>0.9375</v>
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c r="B394" t="n">
-        <v>0.004953</v>
+        <v>0.004957</v>
       </c>
       <c r="C394" t="n">
         <v>0.934783</v>
@@ -5549,7 +5549,7 @@
         </is>
       </c>
       <c r="B395" t="n">
-        <v>0.005502</v>
+        <v>0.005563</v>
       </c>
       <c r="C395" t="n">
         <v>0.932065</v>
@@ -5562,7 +5562,7 @@
         </is>
       </c>
       <c r="B396" t="n">
-        <v>0.005731</v>
+        <v>0.005785</v>
       </c>
       <c r="C396" t="n">
         <v>0.929348</v>
@@ -5575,7 +5575,7 @@
         </is>
       </c>
       <c r="B397" t="n">
-        <v>0.005816</v>
+        <v>0.005871</v>
       </c>
       <c r="C397" t="n">
         <v>0.92663</v>
@@ -5588,7 +5588,7 @@
         </is>
       </c>
       <c r="B398" t="n">
-        <v>0.006386</v>
+        <v>0.006431</v>
       </c>
       <c r="C398" t="n">
         <v>0.923913</v>
@@ -5601,7 +5601,7 @@
         </is>
       </c>
       <c r="B399" t="n">
-        <v>0.007115</v>
+        <v>0.007194</v>
       </c>
       <c r="C399" t="n">
         <v>0.921196</v>
@@ -5614,7 +5614,7 @@
         </is>
       </c>
       <c r="B400" t="n">
-        <v>0.007137</v>
+        <v>0.007211</v>
       </c>
       <c r="C400" t="n">
         <v>0.918478</v>
@@ -5627,7 +5627,7 @@
         </is>
       </c>
       <c r="B401" t="n">
-        <v>0.007374</v>
+        <v>0.007473</v>
       </c>
       <c r="C401" t="n">
         <v>0.915761</v>
@@ -5640,7 +5640,7 @@
         </is>
       </c>
       <c r="B402" t="n">
-        <v>0.00758</v>
+        <v>0.007652</v>
       </c>
       <c r="C402" t="n">
         <v>0.913043</v>
@@ -5653,7 +5653,7 @@
         </is>
       </c>
       <c r="B403" t="n">
-        <v>0.007807</v>
+        <v>0.007837999999999999</v>
       </c>
       <c r="C403" t="n">
         <v>0.910326</v>
@@ -5666,7 +5666,7 @@
         </is>
       </c>
       <c r="B404" t="n">
-        <v>0.007919000000000001</v>
+        <v>0.007875</v>
       </c>
       <c r="C404" t="n">
         <v>0.907609</v>
@@ -5679,7 +5679,7 @@
         </is>
       </c>
       <c r="B405" t="n">
-        <v>0.007995</v>
+        <v>0.008102</v>
       </c>
       <c r="C405" t="n">
         <v>0.904891</v>
@@ -5692,7 +5692,7 @@
         </is>
       </c>
       <c r="B406" t="n">
-        <v>0.008107</v>
+        <v>0.008104999999999999</v>
       </c>
       <c r="C406" t="n">
         <v>0.902174</v>
@@ -5705,7 +5705,7 @@
         </is>
       </c>
       <c r="B407" t="n">
-        <v>0.008174000000000001</v>
+        <v>0.008227</v>
       </c>
       <c r="C407" t="n">
         <v>0.899457</v>
@@ -5718,7 +5718,7 @@
         </is>
       </c>
       <c r="B408" t="n">
-        <v>0.008636</v>
+        <v>0.008543</v>
       </c>
       <c r="C408" t="n">
         <v>0.896739</v>
@@ -5731,7 +5731,7 @@
         </is>
       </c>
       <c r="B409" t="n">
-        <v>0.008914999999999999</v>
+        <v>0.009031000000000001</v>
       </c>
       <c r="C409" t="n">
         <v>0.894022</v>
@@ -5744,7 +5744,7 @@
         </is>
       </c>
       <c r="B410" t="n">
-        <v>0.009109000000000001</v>
+        <v>0.009218</v>
       </c>
       <c r="C410" t="n">
         <v>0.891304</v>
@@ -5757,7 +5757,7 @@
         </is>
       </c>
       <c r="B411" t="n">
-        <v>0.009115</v>
+        <v>0.009231</v>
       </c>
       <c r="C411" t="n">
         <v>0.888587</v>
@@ -5770,7 +5770,7 @@
         </is>
       </c>
       <c r="B412" t="n">
-        <v>0.009559</v>
+        <v>0.009646999999999999</v>
       </c>
       <c r="C412" t="n">
         <v>0.88587</v>
@@ -5783,7 +5783,7 @@
         </is>
       </c>
       <c r="B413" t="n">
-        <v>0.009766</v>
+        <v>0.009812</v>
       </c>
       <c r="C413" t="n">
         <v>0.883152</v>
@@ -5796,7 +5796,7 @@
         </is>
       </c>
       <c r="B414" t="n">
-        <v>0.009868999999999999</v>
+        <v>0.009866</v>
       </c>
       <c r="C414" t="n">
         <v>0.880435</v>
@@ -5809,7 +5809,7 @@
         </is>
       </c>
       <c r="B415" t="n">
-        <v>0.010045</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="C415" t="n">
         <v>0.877717</v>
@@ -5822,7 +5822,7 @@
         </is>
       </c>
       <c r="B416" t="n">
-        <v>0.010295</v>
+        <v>0.010434</v>
       </c>
       <c r="C416" t="n">
         <v>0.875</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="B417" t="n">
-        <v>0.010567</v>
+        <v>0.010532</v>
       </c>
       <c r="C417" t="n">
         <v>0.872283</v>
@@ -5848,7 +5848,7 @@
         </is>
       </c>
       <c r="B418" t="n">
-        <v>0.010584</v>
+        <v>0.010649</v>
       </c>
       <c r="C418" t="n">
         <v>0.869565</v>
@@ -5861,7 +5861,7 @@
         </is>
       </c>
       <c r="B419" t="n">
-        <v>0.010863</v>
+        <v>0.010927</v>
       </c>
       <c r="C419" t="n">
         <v>0.866848</v>
@@ -5874,7 +5874,7 @@
         </is>
       </c>
       <c r="B420" t="n">
-        <v>0.010943</v>
+        <v>0.010961</v>
       </c>
       <c r="C420" t="n">
         <v>0.86413</v>
@@ -5887,7 +5887,7 @@
         </is>
       </c>
       <c r="B421" t="n">
-        <v>0.011005</v>
+        <v>0.011057</v>
       </c>
       <c r="C421" t="n">
         <v>0.861413</v>
@@ -5900,7 +5900,7 @@
         </is>
       </c>
       <c r="B422" t="n">
-        <v>0.011228</v>
+        <v>0.011309</v>
       </c>
       <c r="C422" t="n">
         <v>0.858696</v>
@@ -5913,7 +5913,7 @@
         </is>
       </c>
       <c r="B423" t="n">
-        <v>0.011301</v>
+        <v>0.011435</v>
       </c>
       <c r="C423" t="n">
         <v>0.855978</v>
@@ -5926,7 +5926,7 @@
         </is>
       </c>
       <c r="B424" t="n">
-        <v>0.011541</v>
+        <v>0.01163</v>
       </c>
       <c r="C424" t="n">
         <v>0.853261</v>
@@ -5939,7 +5939,7 @@
         </is>
       </c>
       <c r="B425" t="n">
-        <v>0.011615</v>
+        <v>0.011664</v>
       </c>
       <c r="C425" t="n">
         <v>0.850543</v>
@@ -5952,7 +5952,7 @@
         </is>
       </c>
       <c r="B426" t="n">
-        <v>0.011831</v>
+        <v>0.011983</v>
       </c>
       <c r="C426" t="n">
         <v>0.847826</v>
@@ -5965,7 +5965,7 @@
         </is>
       </c>
       <c r="B427" t="n">
-        <v>0.01204</v>
+        <v>0.012176</v>
       </c>
       <c r="C427" t="n">
         <v>0.845109</v>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="B428" t="n">
-        <v>0.012234</v>
+        <v>0.012311</v>
       </c>
       <c r="C428" t="n">
         <v>0.842391</v>
@@ -5991,7 +5991,7 @@
         </is>
       </c>
       <c r="B429" t="n">
-        <v>0.013121</v>
+        <v>0.013165</v>
       </c>
       <c r="C429" t="n">
         <v>0.839674</v>
@@ -6004,7 +6004,7 @@
         </is>
       </c>
       <c r="B430" t="n">
-        <v>0.013313</v>
+        <v>0.013174</v>
       </c>
       <c r="C430" t="n">
         <v>0.836957</v>
@@ -6017,7 +6017,7 @@
         </is>
       </c>
       <c r="B431" t="n">
-        <v>0.013319</v>
+        <v>0.013342</v>
       </c>
       <c r="C431" t="n">
         <v>0.834239</v>
@@ -6030,7 +6030,7 @@
         </is>
       </c>
       <c r="B432" t="n">
-        <v>0.01365</v>
+        <v>0.013694</v>
       </c>
       <c r="C432" t="n">
         <v>0.831522</v>
@@ -6043,7 +6043,7 @@
         </is>
       </c>
       <c r="B433" t="n">
-        <v>0.013786</v>
+        <v>0.01397</v>
       </c>
       <c r="C433" t="n">
         <v>0.828804</v>
@@ -6056,7 +6056,7 @@
         </is>
       </c>
       <c r="B434" t="n">
-        <v>0.013901</v>
+        <v>0.013973</v>
       </c>
       <c r="C434" t="n">
         <v>0.826087</v>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="B435" t="n">
-        <v>0.013968</v>
+        <v>0.014061</v>
       </c>
       <c r="C435" t="n">
         <v>0.82337</v>
@@ -6082,7 +6082,7 @@
         </is>
       </c>
       <c r="B436" t="n">
-        <v>0.014363</v>
+        <v>0.014423</v>
       </c>
       <c r="C436" t="n">
         <v>0.820652</v>
@@ -6095,7 +6095,7 @@
         </is>
       </c>
       <c r="B437" t="n">
-        <v>0.01487</v>
+        <v>0.014922</v>
       </c>
       <c r="C437" t="n">
         <v>0.817935</v>
@@ -6108,7 +6108,7 @@
         </is>
       </c>
       <c r="B438" t="n">
-        <v>0.014899</v>
+        <v>0.014942</v>
       </c>
       <c r="C438" t="n">
         <v>0.815217</v>
@@ -6121,7 +6121,7 @@
         </is>
       </c>
       <c r="B439" t="n">
-        <v>0.014946</v>
+        <v>0.015084</v>
       </c>
       <c r="C439" t="n">
         <v>0.8125</v>
@@ -6134,7 +6134,7 @@
         </is>
       </c>
       <c r="B440" t="n">
-        <v>0.014951</v>
+        <v>0.01509</v>
       </c>
       <c r="C440" t="n">
         <v>0.809783</v>
@@ -6147,7 +6147,7 @@
         </is>
       </c>
       <c r="B441" t="n">
-        <v>0.015235</v>
+        <v>0.015121</v>
       </c>
       <c r="C441" t="n">
         <v>0.807065</v>
@@ -6160,7 +6160,7 @@
         </is>
       </c>
       <c r="B442" t="n">
-        <v>0.015279</v>
+        <v>0.015372</v>
       </c>
       <c r="C442" t="n">
         <v>0.804348</v>
@@ -6173,7 +6173,7 @@
         </is>
       </c>
       <c r="B443" t="n">
-        <v>0.015733</v>
+        <v>0.015651</v>
       </c>
       <c r="C443" t="n">
         <v>0.80163</v>
@@ -6186,7 +6186,7 @@
         </is>
       </c>
       <c r="B444" t="n">
-        <v>0.015957</v>
+        <v>0.016128</v>
       </c>
       <c r="C444" t="n">
         <v>0.798913</v>
@@ -6199,7 +6199,7 @@
         </is>
       </c>
       <c r="B445" t="n">
-        <v>0.016068</v>
+        <v>0.016255</v>
       </c>
       <c r="C445" t="n">
         <v>0.796196</v>
@@ -6212,7 +6212,7 @@
         </is>
       </c>
       <c r="B446" t="n">
-        <v>0.016603</v>
+        <v>0.016732</v>
       </c>
       <c r="C446" t="n">
         <v>0.793478</v>
@@ -6225,7 +6225,7 @@
         </is>
       </c>
       <c r="B447" t="n">
-        <v>0.016663</v>
+        <v>0.016784</v>
       </c>
       <c r="C447" t="n">
         <v>0.790761</v>
@@ -6238,7 +6238,7 @@
         </is>
       </c>
       <c r="B448" t="n">
-        <v>0.016777</v>
+        <v>0.016814</v>
       </c>
       <c r="C448" t="n">
         <v>0.788043</v>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="B449" t="n">
-        <v>0.016873</v>
+        <v>0.016916</v>
       </c>
       <c r="C449" t="n">
         <v>0.785326</v>
@@ -6264,7 +6264,7 @@
         </is>
       </c>
       <c r="B450" t="n">
-        <v>0.016894</v>
+        <v>0.017065</v>
       </c>
       <c r="C450" t="n">
         <v>0.782609</v>
@@ -6277,7 +6277,7 @@
         </is>
       </c>
       <c r="B451" t="n">
-        <v>0.016974</v>
+        <v>0.017068</v>
       </c>
       <c r="C451" t="n">
         <v>0.779891</v>
@@ -6290,7 +6290,7 @@
         </is>
       </c>
       <c r="B452" t="n">
-        <v>0.017917</v>
+        <v>0.017833</v>
       </c>
       <c r="C452" t="n">
         <v>0.777174</v>
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="B453" t="n">
-        <v>0.018086</v>
+        <v>0.018204</v>
       </c>
       <c r="C453" t="n">
         <v>0.774457</v>
@@ -6316,7 +6316,7 @@
         </is>
       </c>
       <c r="B454" t="n">
-        <v>0.01838</v>
+        <v>0.018517</v>
       </c>
       <c r="C454" t="n">
         <v>0.771739</v>
@@ -6329,7 +6329,7 @@
         </is>
       </c>
       <c r="B455" t="n">
-        <v>0.018767</v>
+        <v>0.018769</v>
       </c>
       <c r="C455" t="n">
         <v>0.769022</v>
@@ -6342,7 +6342,7 @@
         </is>
       </c>
       <c r="B456" t="n">
-        <v>0.018927</v>
+        <v>0.019164</v>
       </c>
       <c r="C456" t="n">
         <v>0.766304</v>
@@ -6355,7 +6355,7 @@
         </is>
       </c>
       <c r="B457" t="n">
-        <v>0.019322</v>
+        <v>0.019489</v>
       </c>
       <c r="C457" t="n">
         <v>0.763587</v>
@@ -6368,7 +6368,7 @@
         </is>
       </c>
       <c r="B458" t="n">
-        <v>0.019495</v>
+        <v>0.019494</v>
       </c>
       <c r="C458" t="n">
         <v>0.76087</v>
@@ -6381,7 +6381,7 @@
         </is>
       </c>
       <c r="B459" t="n">
-        <v>0.020374</v>
+        <v>0.020047</v>
       </c>
       <c r="C459" t="n">
         <v>0.758152</v>
@@ -6394,7 +6394,7 @@
         </is>
       </c>
       <c r="B460" t="n">
-        <v>0.020394</v>
+        <v>0.0206</v>
       </c>
       <c r="C460" t="n">
         <v>0.755435</v>
@@ -6407,7 +6407,7 @@
         </is>
       </c>
       <c r="B461" t="n">
-        <v>0.020794</v>
+        <v>0.020761</v>
       </c>
       <c r="C461" t="n">
         <v>0.752717</v>
@@ -6420,7 +6420,7 @@
         </is>
       </c>
       <c r="B462" t="n">
-        <v>0.021108</v>
+        <v>0.021192</v>
       </c>
       <c r="C462" t="n">
         <v>0.75</v>
@@ -6433,7 +6433,7 @@
         </is>
       </c>
       <c r="B463" t="n">
-        <v>0.021666</v>
+        <v>0.021667</v>
       </c>
       <c r="C463" t="n">
         <v>0.747283</v>
@@ -6446,7 +6446,7 @@
         </is>
       </c>
       <c r="B464" t="n">
-        <v>0.021893</v>
+        <v>0.021899</v>
       </c>
       <c r="C464" t="n">
         <v>0.744565</v>
@@ -6459,7 +6459,7 @@
         </is>
       </c>
       <c r="B465" t="n">
-        <v>0.021895</v>
+        <v>0.021908</v>
       </c>
       <c r="C465" t="n">
         <v>0.741848</v>
@@ -6472,7 +6472,7 @@
         </is>
       </c>
       <c r="B466" t="n">
-        <v>0.021898</v>
+        <v>0.021951</v>
       </c>
       <c r="C466" t="n">
         <v>0.73913</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="B467" t="n">
-        <v>0.022062</v>
+        <v>0.022162</v>
       </c>
       <c r="C467" t="n">
         <v>0.736413</v>
@@ -6498,7 +6498,7 @@
         </is>
       </c>
       <c r="B468" t="n">
-        <v>0.022102</v>
+        <v>0.022201</v>
       </c>
       <c r="C468" t="n">
         <v>0.733696</v>
@@ -6511,7 +6511,7 @@
         </is>
       </c>
       <c r="B469" t="n">
-        <v>0.022369</v>
+        <v>0.022236</v>
       </c>
       <c r="C469" t="n">
         <v>0.730978</v>
@@ -6524,7 +6524,7 @@
         </is>
       </c>
       <c r="B470" t="n">
-        <v>0.022519</v>
+        <v>0.022384</v>
       </c>
       <c r="C470" t="n">
         <v>0.728261</v>
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="B471" t="n">
-        <v>0.022553</v>
+        <v>0.022651</v>
       </c>
       <c r="C471" t="n">
         <v>0.725543</v>
@@ -6550,7 +6550,7 @@
         </is>
       </c>
       <c r="B472" t="n">
-        <v>0.023464</v>
+        <v>0.023083</v>
       </c>
       <c r="C472" t="n">
         <v>0.722826</v>
@@ -6563,7 +6563,7 @@
         </is>
       </c>
       <c r="B473" t="n">
-        <v>0.023651</v>
+        <v>0.023319</v>
       </c>
       <c r="C473" t="n">
         <v>0.720109</v>
@@ -6576,7 +6576,7 @@
         </is>
       </c>
       <c r="B474" t="n">
-        <v>0.023967</v>
+        <v>0.023878</v>
       </c>
       <c r="C474" t="n">
         <v>0.717391</v>
@@ -6589,7 +6589,7 @@
         </is>
       </c>
       <c r="B475" t="n">
-        <v>0.024088</v>
+        <v>0.024282</v>
       </c>
       <c r="C475" t="n">
         <v>0.714674</v>
@@ -6602,7 +6602,7 @@
         </is>
       </c>
       <c r="B476" t="n">
-        <v>0.024328</v>
+        <v>0.024335</v>
       </c>
       <c r="C476" t="n">
         <v>0.711957</v>
@@ -6615,7 +6615,7 @@
         </is>
       </c>
       <c r="B477" t="n">
-        <v>0.024392</v>
+        <v>0.024601</v>
       </c>
       <c r="C477" t="n">
         <v>0.709239</v>
@@ -6628,7 +6628,7 @@
         </is>
       </c>
       <c r="B478" t="n">
-        <v>0.024617</v>
+        <v>0.024784</v>
       </c>
       <c r="C478" t="n">
         <v>0.706522</v>
@@ -6641,7 +6641,7 @@
         </is>
       </c>
       <c r="B479" t="n">
-        <v>0.024824</v>
+        <v>0.025139</v>
       </c>
       <c r="C479" t="n">
         <v>0.703804</v>
@@ -6654,7 +6654,7 @@
         </is>
       </c>
       <c r="B480" t="n">
-        <v>0.024926</v>
+        <v>0.025199</v>
       </c>
       <c r="C480" t="n">
         <v>0.701087</v>
@@ -6667,7 +6667,7 @@
         </is>
       </c>
       <c r="B481" t="n">
-        <v>0.025157</v>
+        <v>0.025312</v>
       </c>
       <c r="C481" t="n">
         <v>0.69837</v>
@@ -6680,7 +6680,7 @@
         </is>
       </c>
       <c r="B482" t="n">
-        <v>0.025176</v>
+        <v>0.025506</v>
       </c>
       <c r="C482" t="n">
         <v>0.695652</v>
@@ -6693,7 +6693,7 @@
         </is>
       </c>
       <c r="B483" t="n">
-        <v>0.025701</v>
+        <v>0.025976</v>
       </c>
       <c r="C483" t="n">
         <v>0.692935</v>
@@ -6706,7 +6706,7 @@
         </is>
       </c>
       <c r="B484" t="n">
-        <v>0.025774</v>
+        <v>0.026001</v>
       </c>
       <c r="C484" t="n">
         <v>0.690217</v>
@@ -6719,7 +6719,7 @@
         </is>
       </c>
       <c r="B485" t="n">
-        <v>0.02603</v>
+        <v>0.026124</v>
       </c>
       <c r="C485" t="n">
         <v>0.6875</v>
@@ -6732,7 +6732,7 @@
         </is>
       </c>
       <c r="B486" t="n">
-        <v>0.026093</v>
+        <v>0.026159</v>
       </c>
       <c r="C486" t="n">
         <v>0.684783</v>
@@ -6758,7 +6758,7 @@
         </is>
       </c>
       <c r="B488" t="n">
-        <v>0.026211</v>
+        <v>0.026199</v>
       </c>
       <c r="C488" t="n">
         <v>0.679348</v>
@@ -6771,7 +6771,7 @@
         </is>
       </c>
       <c r="B489" t="n">
-        <v>0.026277</v>
+        <v>0.026245</v>
       </c>
       <c r="C489" t="n">
         <v>0.67663</v>
@@ -6784,7 +6784,7 @@
         </is>
       </c>
       <c r="B490" t="n">
-        <v>0.026629</v>
+        <v>0.026986</v>
       </c>
       <c r="C490" t="n">
         <v>0.673913</v>
@@ -6797,7 +6797,7 @@
         </is>
       </c>
       <c r="B491" t="n">
-        <v>0.027215</v>
+        <v>0.027398</v>
       </c>
       <c r="C491" t="n">
         <v>0.671196</v>
@@ -6810,7 +6810,7 @@
         </is>
       </c>
       <c r="B492" t="n">
-        <v>0.027239</v>
+        <v>0.027507</v>
       </c>
       <c r="C492" t="n">
         <v>0.668478</v>
@@ -6823,7 +6823,7 @@
         </is>
       </c>
       <c r="B493" t="n">
-        <v>0.02788</v>
+        <v>0.027656</v>
       </c>
       <c r="C493" t="n">
         <v>0.665761</v>
@@ -6836,7 +6836,7 @@
         </is>
       </c>
       <c r="B494" t="n">
-        <v>0.02796</v>
+        <v>0.028214</v>
       </c>
       <c r="C494" t="n">
         <v>0.663043</v>
@@ -6849,7 +6849,7 @@
         </is>
       </c>
       <c r="B495" t="n">
-        <v>0.028001</v>
+        <v>0.028276</v>
       </c>
       <c r="C495" t="n">
         <v>0.660326</v>
@@ -6862,7 +6862,7 @@
         </is>
       </c>
       <c r="B496" t="n">
-        <v>0.028524</v>
+        <v>0.028609</v>
       </c>
       <c r="C496" t="n">
         <v>0.657609</v>
@@ -6875,7 +6875,7 @@
         </is>
       </c>
       <c r="B497" t="n">
-        <v>0.029257</v>
+        <v>0.029098</v>
       </c>
       <c r="C497" t="n">
         <v>0.654891</v>
@@ -6888,7 +6888,7 @@
         </is>
       </c>
       <c r="B498" t="n">
-        <v>0.02942</v>
+        <v>0.029255</v>
       </c>
       <c r="C498" t="n">
         <v>0.652174</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="B499" t="n">
-        <v>0.029506</v>
+        <v>0.029534</v>
       </c>
       <c r="C499" t="n">
         <v>0.649457</v>
@@ -6914,7 +6914,7 @@
         </is>
       </c>
       <c r="B500" t="n">
-        <v>0.029559</v>
+        <v>0.029632</v>
       </c>
       <c r="C500" t="n">
         <v>0.646739</v>
@@ -6927,7 +6927,7 @@
         </is>
       </c>
       <c r="B501" t="n">
-        <v>0.029597</v>
+        <v>0.029716</v>
       </c>
       <c r="C501" t="n">
         <v>0.644022</v>
@@ -6940,7 +6940,7 @@
         </is>
       </c>
       <c r="B502" t="n">
-        <v>0.029726</v>
+        <v>0.029802</v>
       </c>
       <c r="C502" t="n">
         <v>0.641304</v>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="B503" t="n">
-        <v>0.030164</v>
+        <v>0.030378</v>
       </c>
       <c r="C503" t="n">
         <v>0.638587</v>
@@ -6966,7 +6966,7 @@
         </is>
       </c>
       <c r="B504" t="n">
-        <v>0.030216</v>
+        <v>0.030423</v>
       </c>
       <c r="C504" t="n">
         <v>0.63587</v>
@@ -6979,7 +6979,7 @@
         </is>
       </c>
       <c r="B505" t="n">
-        <v>0.030237</v>
+        <v>0.030434</v>
       </c>
       <c r="C505" t="n">
         <v>0.633152</v>
@@ -6992,7 +6992,7 @@
         </is>
       </c>
       <c r="B506" t="n">
-        <v>0.030386</v>
+        <v>0.030629</v>
       </c>
       <c r="C506" t="n">
         <v>0.630435</v>
@@ -7005,7 +7005,7 @@
         </is>
       </c>
       <c r="B507" t="n">
-        <v>0.030572</v>
+        <v>0.03069</v>
       </c>
       <c r="C507" t="n">
         <v>0.627717</v>
@@ -7018,7 +7018,7 @@
         </is>
       </c>
       <c r="B508" t="n">
-        <v>0.030828</v>
+        <v>0.030935</v>
       </c>
       <c r="C508" t="n">
         <v>0.625</v>
@@ -7031,7 +7031,7 @@
         </is>
       </c>
       <c r="B509" t="n">
-        <v>0.030849</v>
+        <v>0.031068</v>
       </c>
       <c r="C509" t="n">
         <v>0.622283</v>
@@ -7044,7 +7044,7 @@
         </is>
       </c>
       <c r="B510" t="n">
-        <v>0.031371</v>
+        <v>0.03151</v>
       </c>
       <c r="C510" t="n">
         <v>0.619565</v>
@@ -7057,7 +7057,7 @@
         </is>
       </c>
       <c r="B511" t="n">
-        <v>0.031619</v>
+        <v>0.031547</v>
       </c>
       <c r="C511" t="n">
         <v>0.616848</v>
@@ -7070,7 +7070,7 @@
         </is>
       </c>
       <c r="B512" t="n">
-        <v>0.032684</v>
+        <v>0.032679</v>
       </c>
       <c r="C512" t="n">
         <v>0.61413</v>
@@ -7083,7 +7083,7 @@
         </is>
       </c>
       <c r="B513" t="n">
-        <v>0.032812</v>
+        <v>0.033105</v>
       </c>
       <c r="C513" t="n">
         <v>0.611413</v>
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="B514" t="n">
-        <v>0.032892</v>
+        <v>0.033298</v>
       </c>
       <c r="C514" t="n">
         <v>0.608696</v>
@@ -7109,7 +7109,7 @@
         </is>
       </c>
       <c r="B515" t="n">
-        <v>0.033565</v>
+        <v>0.033503</v>
       </c>
       <c r="C515" t="n">
         <v>0.605978</v>
@@ -7122,7 +7122,7 @@
         </is>
       </c>
       <c r="B516" t="n">
-        <v>0.033598</v>
+        <v>0.033738</v>
       </c>
       <c r="C516" t="n">
         <v>0.603261</v>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="B517" t="n">
-        <v>0.033598</v>
+        <v>0.033968</v>
       </c>
       <c r="C517" t="n">
         <v>0.600543</v>
@@ -7148,7 +7148,7 @@
         </is>
       </c>
       <c r="B518" t="n">
-        <v>0.034018</v>
+        <v>0.034013</v>
       </c>
       <c r="C518" t="n">
         <v>0.597826</v>
@@ -7161,7 +7161,7 @@
         </is>
       </c>
       <c r="B519" t="n">
-        <v>0.034164</v>
+        <v>0.034619</v>
       </c>
       <c r="C519" t="n">
         <v>0.595109</v>
@@ -7174,7 +7174,7 @@
         </is>
       </c>
       <c r="B520" t="n">
-        <v>0.034319</v>
+        <v>0.034697</v>
       </c>
       <c r="C520" t="n">
         <v>0.592391</v>
@@ -7187,7 +7187,7 @@
         </is>
       </c>
       <c r="B521" t="n">
-        <v>0.034547</v>
+        <v>0.034823</v>
       </c>
       <c r="C521" t="n">
         <v>0.589674</v>
@@ -7200,7 +7200,7 @@
         </is>
       </c>
       <c r="B522" t="n">
-        <v>0.034669</v>
+        <v>0.034908</v>
       </c>
       <c r="C522" t="n">
         <v>0.586957</v>
@@ -7213,7 +7213,7 @@
         </is>
       </c>
       <c r="B523" t="n">
-        <v>0.034873</v>
+        <v>0.035181</v>
       </c>
       <c r="C523" t="n">
         <v>0.584239</v>
@@ -7226,7 +7226,7 @@
         </is>
       </c>
       <c r="B524" t="n">
-        <v>0.035076</v>
+        <v>0.035194</v>
       </c>
       <c r="C524" t="n">
         <v>0.581522</v>
@@ -7239,7 +7239,7 @@
         </is>
       </c>
       <c r="B525" t="n">
-        <v>0.035318</v>
+        <v>0.035752</v>
       </c>
       <c r="C525" t="n">
         <v>0.578804</v>
@@ -7252,7 +7252,7 @@
         </is>
       </c>
       <c r="B526" t="n">
-        <v>0.036312</v>
+        <v>0.03613</v>
       </c>
       <c r="C526" t="n">
         <v>0.576087</v>
@@ -7265,7 +7265,7 @@
         </is>
       </c>
       <c r="B527" t="n">
-        <v>0.036449</v>
+        <v>0.036466</v>
       </c>
       <c r="C527" t="n">
         <v>0.57337</v>
@@ -7278,7 +7278,7 @@
         </is>
       </c>
       <c r="B528" t="n">
-        <v>0.036613</v>
+        <v>0.036895</v>
       </c>
       <c r="C528" t="n">
         <v>0.570652</v>
@@ -7291,7 +7291,7 @@
         </is>
       </c>
       <c r="B529" t="n">
-        <v>0.036763</v>
+        <v>0.036987</v>
       </c>
       <c r="C529" t="n">
         <v>0.567935</v>
@@ -7304,7 +7304,7 @@
         </is>
       </c>
       <c r="B530" t="n">
-        <v>0.037014</v>
+        <v>0.037235</v>
       </c>
       <c r="C530" t="n">
         <v>0.565217</v>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="B531" t="n">
-        <v>0.037079</v>
+        <v>0.037462</v>
       </c>
       <c r="C531" t="n">
         <v>0.5625</v>
@@ -7330,7 +7330,7 @@
         </is>
       </c>
       <c r="B532" t="n">
-        <v>0.037186</v>
+        <v>0.037564</v>
       </c>
       <c r="C532" t="n">
         <v>0.559783</v>
@@ -7343,7 +7343,7 @@
         </is>
       </c>
       <c r="B533" t="n">
-        <v>0.037443</v>
+        <v>0.037641</v>
       </c>
       <c r="C533" t="n">
         <v>0.557065</v>
@@ -7356,7 +7356,7 @@
         </is>
       </c>
       <c r="B534" t="n">
-        <v>0.037449</v>
+        <v>0.037735</v>
       </c>
       <c r="C534" t="n">
         <v>0.554348</v>
@@ -7369,7 +7369,7 @@
         </is>
       </c>
       <c r="B535" t="n">
-        <v>0.037629</v>
+        <v>0.037891</v>
       </c>
       <c r="C535" t="n">
         <v>0.55163</v>
@@ -7382,7 +7382,7 @@
         </is>
       </c>
       <c r="B536" t="n">
-        <v>0.037639</v>
+        <v>0.038055</v>
       </c>
       <c r="C536" t="n">
         <v>0.548913</v>
@@ -7395,7 +7395,7 @@
         </is>
       </c>
       <c r="B537" t="n">
-        <v>0.037813</v>
+        <v>0.038148</v>
       </c>
       <c r="C537" t="n">
         <v>0.546196</v>
@@ -7408,7 +7408,7 @@
         </is>
       </c>
       <c r="B538" t="n">
-        <v>0.037832</v>
+        <v>0.038201</v>
       </c>
       <c r="C538" t="n">
         <v>0.543478</v>
@@ -7421,7 +7421,7 @@
         </is>
       </c>
       <c r="B539" t="n">
-        <v>0.038117</v>
+        <v>0.038279</v>
       </c>
       <c r="C539" t="n">
         <v>0.540761</v>
@@ -7434,7 +7434,7 @@
         </is>
       </c>
       <c r="B540" t="n">
-        <v>0.038246</v>
+        <v>0.038664</v>
       </c>
       <c r="C540" t="n">
         <v>0.538043</v>
@@ -7447,7 +7447,7 @@
         </is>
       </c>
       <c r="B541" t="n">
-        <v>0.038791</v>
+        <v>0.039105</v>
       </c>
       <c r="C541" t="n">
         <v>0.535326</v>
@@ -7460,7 +7460,7 @@
         </is>
       </c>
       <c r="B542" t="n">
-        <v>0.038887</v>
+        <v>0.039218</v>
       </c>
       <c r="C542" t="n">
         <v>0.532609</v>
@@ -7473,7 +7473,7 @@
         </is>
       </c>
       <c r="B543" t="n">
-        <v>0.039024</v>
+        <v>0.03923</v>
       </c>
       <c r="C543" t="n">
         <v>0.529891</v>
@@ -7486,7 +7486,7 @@
         </is>
       </c>
       <c r="B544" t="n">
-        <v>0.039274</v>
+        <v>0.039296</v>
       </c>
       <c r="C544" t="n">
         <v>0.527174</v>
@@ -7499,7 +7499,7 @@
         </is>
       </c>
       <c r="B545" t="n">
-        <v>0.039412</v>
+        <v>0.039301</v>
       </c>
       <c r="C545" t="n">
         <v>0.524457</v>
@@ -7512,7 +7512,7 @@
         </is>
       </c>
       <c r="B546" t="n">
-        <v>0.039554</v>
+        <v>0.039865</v>
       </c>
       <c r="C546" t="n">
         <v>0.521739</v>
@@ -7525,7 +7525,7 @@
         </is>
       </c>
       <c r="B547" t="n">
-        <v>0.039731</v>
+        <v>0.040132</v>
       </c>
       <c r="C547" t="n">
         <v>0.519022</v>
@@ -7538,7 +7538,7 @@
         </is>
       </c>
       <c r="B548" t="n">
-        <v>0.040312</v>
+        <v>0.040497</v>
       </c>
       <c r="C548" t="n">
         <v>0.516304</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="B549" t="n">
-        <v>0.040822</v>
+        <v>0.040581</v>
       </c>
       <c r="C549" t="n">
         <v>0.513587</v>
@@ -7564,7 +7564,7 @@
         </is>
       </c>
       <c r="B550" t="n">
-        <v>0.041041</v>
+        <v>0.040699</v>
       </c>
       <c r="C550" t="n">
         <v>0.51087</v>
@@ -7577,7 +7577,7 @@
         </is>
       </c>
       <c r="B551" t="n">
-        <v>0.041476</v>
+        <v>0.041793</v>
       </c>
       <c r="C551" t="n">
         <v>0.508152</v>
@@ -7590,7 +7590,7 @@
         </is>
       </c>
       <c r="B552" t="n">
-        <v>0.041624</v>
+        <v>0.041995</v>
       </c>
       <c r="C552" t="n">
         <v>0.505435</v>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="B553" t="n">
-        <v>0.041983</v>
+        <v>0.042204</v>
       </c>
       <c r="C553" t="n">
         <v>0.502717</v>
@@ -7616,7 +7616,7 @@
         </is>
       </c>
       <c r="B554" t="n">
-        <v>0.042691</v>
+        <v>0.042256</v>
       </c>
       <c r="C554" t="n">
         <v>0.5</v>
@@ -7629,7 +7629,7 @@
         </is>
       </c>
       <c r="B555" t="n">
-        <v>0.043035</v>
+        <v>0.043162</v>
       </c>
       <c r="C555" t="n">
         <v>0.497283</v>
@@ -7642,7 +7642,7 @@
         </is>
       </c>
       <c r="B556" t="n">
-        <v>0.043062</v>
+        <v>0.043308</v>
       </c>
       <c r="C556" t="n">
         <v>0.494565</v>
@@ -7655,7 +7655,7 @@
         </is>
       </c>
       <c r="B557" t="n">
-        <v>0.043171</v>
+        <v>0.043602</v>
       </c>
       <c r="C557" t="n">
         <v>0.491848</v>
@@ -7668,7 +7668,7 @@
         </is>
       </c>
       <c r="B558" t="n">
-        <v>0.04429</v>
+        <v>0.044132</v>
       </c>
       <c r="C558" t="n">
         <v>0.48913</v>
@@ -7681,7 +7681,7 @@
         </is>
       </c>
       <c r="B559" t="n">
-        <v>0.044982</v>
+        <v>0.0445</v>
       </c>
       <c r="C559" t="n">
         <v>0.486413</v>
@@ -7694,7 +7694,7 @@
         </is>
       </c>
       <c r="B560" t="n">
-        <v>0.045264</v>
+        <v>0.045799</v>
       </c>
       <c r="C560" t="n">
         <v>0.483696</v>
@@ -7707,7 +7707,7 @@
         </is>
       </c>
       <c r="B561" t="n">
-        <v>0.045791</v>
+        <v>0.046274</v>
       </c>
       <c r="C561" t="n">
         <v>0.480978</v>
@@ -7720,7 +7720,7 @@
         </is>
       </c>
       <c r="B562" t="n">
-        <v>0.046244</v>
+        <v>0.046572</v>
       </c>
       <c r="C562" t="n">
         <v>0.478261</v>
@@ -7733,7 +7733,7 @@
         </is>
       </c>
       <c r="B563" t="n">
-        <v>0.04643</v>
+        <v>0.046735</v>
       </c>
       <c r="C563" t="n">
         <v>0.475543</v>
@@ -7746,7 +7746,7 @@
         </is>
       </c>
       <c r="B564" t="n">
-        <v>0.046764</v>
+        <v>0.046853</v>
       </c>
       <c r="C564" t="n">
         <v>0.472826</v>
@@ -7759,7 +7759,7 @@
         </is>
       </c>
       <c r="B565" t="n">
-        <v>0.046997</v>
+        <v>0.046917</v>
       </c>
       <c r="C565" t="n">
         <v>0.470109</v>
@@ -7772,7 +7772,7 @@
         </is>
       </c>
       <c r="B566" t="n">
-        <v>0.047488</v>
+        <v>0.047146</v>
       </c>
       <c r="C566" t="n">
         <v>0.467391</v>
@@ -7785,7 +7785,7 @@
         </is>
       </c>
       <c r="B567" t="n">
-        <v>0.047532</v>
+        <v>0.047443</v>
       </c>
       <c r="C567" t="n">
         <v>0.464674</v>
@@ -7798,7 +7798,7 @@
         </is>
       </c>
       <c r="B568" t="n">
-        <v>0.048101</v>
+        <v>0.047785</v>
       </c>
       <c r="C568" t="n">
         <v>0.461957</v>
@@ -7811,7 +7811,7 @@
         </is>
       </c>
       <c r="B569" t="n">
-        <v>0.04813</v>
+        <v>0.04833</v>
       </c>
       <c r="C569" t="n">
         <v>0.459239</v>
@@ -7824,7 +7824,7 @@
         </is>
       </c>
       <c r="B570" t="n">
-        <v>0.048286</v>
+        <v>0.048373</v>
       </c>
       <c r="C570" t="n">
         <v>0.456522</v>
@@ -7837,7 +7837,7 @@
         </is>
       </c>
       <c r="B571" t="n">
-        <v>0.048332</v>
+        <v>0.048403</v>
       </c>
       <c r="C571" t="n">
         <v>0.453804</v>
@@ -7850,7 +7850,7 @@
         </is>
       </c>
       <c r="B572" t="n">
-        <v>0.048437</v>
+        <v>0.048634</v>
       </c>
       <c r="C572" t="n">
         <v>0.451087</v>
@@ -7863,7 +7863,7 @@
         </is>
       </c>
       <c r="B573" t="n">
-        <v>0.048469</v>
+        <v>0.048939</v>
       </c>
       <c r="C573" t="n">
         <v>0.44837</v>
@@ -7876,7 +7876,7 @@
         </is>
       </c>
       <c r="B574" t="n">
-        <v>0.04866</v>
+        <v>0.049093</v>
       </c>
       <c r="C574" t="n">
         <v>0.445652</v>
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="B575" t="n">
-        <v>0.049755</v>
+        <v>0.049874</v>
       </c>
       <c r="C575" t="n">
         <v>0.442935</v>
@@ -7902,7 +7902,7 @@
         </is>
       </c>
       <c r="B576" t="n">
-        <v>0.050088</v>
+        <v>0.050399</v>
       </c>
       <c r="C576" t="n">
         <v>0.440217</v>
@@ -7915,7 +7915,7 @@
         </is>
       </c>
       <c r="B577" t="n">
-        <v>0.050435</v>
+        <v>0.050677</v>
       </c>
       <c r="C577" t="n">
         <v>0.4375</v>
@@ -7928,7 +7928,7 @@
         </is>
       </c>
       <c r="B578" t="n">
-        <v>0.050975</v>
+        <v>0.050837</v>
       </c>
       <c r="C578" t="n">
         <v>0.434783</v>
@@ -7941,7 +7941,7 @@
         </is>
       </c>
       <c r="B579" t="n">
-        <v>0.052133</v>
+        <v>0.051923</v>
       </c>
       <c r="C579" t="n">
         <v>0.432065</v>
@@ -7954,7 +7954,7 @@
         </is>
       </c>
       <c r="B580" t="n">
-        <v>0.052173</v>
+        <v>0.052397</v>
       </c>
       <c r="C580" t="n">
         <v>0.429348</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="B581" t="n">
-        <v>0.052185</v>
+        <v>0.052403</v>
       </c>
       <c r="C581" t="n">
         <v>0.42663</v>
@@ -7980,7 +7980,7 @@
         </is>
       </c>
       <c r="B582" t="n">
-        <v>0.052507</v>
+        <v>0.052697</v>
       </c>
       <c r="C582" t="n">
         <v>0.423913</v>
@@ -7993,7 +7993,7 @@
         </is>
       </c>
       <c r="B583" t="n">
-        <v>0.052937</v>
+        <v>0.053188</v>
       </c>
       <c r="C583" t="n">
         <v>0.421196</v>
@@ -8006,7 +8006,7 @@
         </is>
       </c>
       <c r="B584" t="n">
-        <v>0.053299</v>
+        <v>0.053681</v>
       </c>
       <c r="C584" t="n">
         <v>0.418478</v>
@@ -8019,7 +8019,7 @@
         </is>
       </c>
       <c r="B585" t="n">
-        <v>0.053594</v>
+        <v>0.053754</v>
       </c>
       <c r="C585" t="n">
         <v>0.415761</v>
@@ -8032,7 +8032,7 @@
         </is>
       </c>
       <c r="B586" t="n">
-        <v>0.053775</v>
+        <v>0.054192</v>
       </c>
       <c r="C586" t="n">
         <v>0.413043</v>
@@ -8045,7 +8045,7 @@
         </is>
       </c>
       <c r="B587" t="n">
-        <v>0.054497</v>
+        <v>0.054641</v>
       </c>
       <c r="C587" t="n">
         <v>0.410326</v>
@@ -8058,7 +8058,7 @@
         </is>
       </c>
       <c r="B588" t="n">
-        <v>0.055395</v>
+        <v>0.055365</v>
       </c>
       <c r="C588" t="n">
         <v>0.407609</v>
@@ -8071,7 +8071,7 @@
         </is>
       </c>
       <c r="B589" t="n">
-        <v>0.055654</v>
+        <v>0.056359</v>
       </c>
       <c r="C589" t="n">
         <v>0.404891</v>
@@ -8084,7 +8084,7 @@
         </is>
       </c>
       <c r="B590" t="n">
-        <v>0.057512</v>
+        <v>0.057143</v>
       </c>
       <c r="C590" t="n">
         <v>0.402174</v>
@@ -8097,7 +8097,7 @@
         </is>
       </c>
       <c r="B591" t="n">
-        <v>0.05772</v>
+        <v>0.057867</v>
       </c>
       <c r="C591" t="n">
         <v>0.399457</v>
@@ -8110,7 +8110,7 @@
         </is>
       </c>
       <c r="B592" t="n">
-        <v>0.058153</v>
+        <v>0.058375</v>
       </c>
       <c r="C592" t="n">
         <v>0.396739</v>
@@ -8123,7 +8123,7 @@
         </is>
       </c>
       <c r="B593" t="n">
-        <v>0.058249</v>
+        <v>0.058617</v>
       </c>
       <c r="C593" t="n">
         <v>0.394022</v>
@@ -8136,7 +8136,7 @@
         </is>
       </c>
       <c r="B594" t="n">
-        <v>0.058286</v>
+        <v>0.058747</v>
       </c>
       <c r="C594" t="n">
         <v>0.391304</v>
@@ -8149,7 +8149,7 @@
         </is>
       </c>
       <c r="B595" t="n">
-        <v>0.05888</v>
+        <v>0.058761</v>
       </c>
       <c r="C595" t="n">
         <v>0.388587</v>
@@ -8162,7 +8162,7 @@
         </is>
       </c>
       <c r="B596" t="n">
-        <v>0.058928</v>
+        <v>0.059319</v>
       </c>
       <c r="C596" t="n">
         <v>0.38587</v>
@@ -8175,7 +8175,7 @@
         </is>
       </c>
       <c r="B597" t="n">
-        <v>0.059004</v>
+        <v>0.059335</v>
       </c>
       <c r="C597" t="n">
         <v>0.383152</v>
@@ -8188,7 +8188,7 @@
         </is>
       </c>
       <c r="B598" t="n">
-        <v>0.05932</v>
+        <v>0.059599</v>
       </c>
       <c r="C598" t="n">
         <v>0.380435</v>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="B599" t="n">
-        <v>0.05971</v>
+        <v>0.0596</v>
       </c>
       <c r="C599" t="n">
         <v>0.377717</v>
@@ -8214,7 +8214,7 @@
         </is>
       </c>
       <c r="B600" t="n">
-        <v>0.060104</v>
+        <v>0.059922</v>
       </c>
       <c r="C600" t="n">
         <v>0.375</v>
@@ -8227,7 +8227,7 @@
         </is>
       </c>
       <c r="B601" t="n">
-        <v>0.06028</v>
+        <v>0.059976</v>
       </c>
       <c r="C601" t="n">
         <v>0.372283</v>
@@ -8240,7 +8240,7 @@
         </is>
       </c>
       <c r="B602" t="n">
-        <v>0.060282</v>
+        <v>0.060232</v>
       </c>
       <c r="C602" t="n">
         <v>0.369565</v>
@@ -8253,7 +8253,7 @@
         </is>
       </c>
       <c r="B603" t="n">
-        <v>0.060616</v>
+        <v>0.060457</v>
       </c>
       <c r="C603" t="n">
         <v>0.366848</v>
@@ -8266,7 +8266,7 @@
         </is>
       </c>
       <c r="B604" t="n">
-        <v>0.060696</v>
+        <v>0.060672</v>
       </c>
       <c r="C604" t="n">
         <v>0.36413</v>
@@ -8279,7 +8279,7 @@
         </is>
       </c>
       <c r="B605" t="n">
-        <v>0.060721</v>
+        <v>0.0608</v>
       </c>
       <c r="C605" t="n">
         <v>0.361413</v>
@@ -8292,7 +8292,7 @@
         </is>
       </c>
       <c r="B606" t="n">
-        <v>0.061796</v>
+        <v>0.062504</v>
       </c>
       <c r="C606" t="n">
         <v>0.358696</v>
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="B607" t="n">
-        <v>0.062424</v>
+        <v>0.063268</v>
       </c>
       <c r="C607" t="n">
         <v>0.355978</v>
@@ -8318,7 +8318,7 @@
         </is>
       </c>
       <c r="B608" t="n">
-        <v>0.062512</v>
+        <v>0.06335499999999999</v>
       </c>
       <c r="C608" t="n">
         <v>0.353261</v>
@@ -8331,7 +8331,7 @@
         </is>
       </c>
       <c r="B609" t="n">
-        <v>0.063374</v>
+        <v>0.063679</v>
       </c>
       <c r="C609" t="n">
         <v>0.350543</v>
@@ -8344,7 +8344,7 @@
         </is>
       </c>
       <c r="B610" t="n">
-        <v>0.06406199999999999</v>
+        <v>0.064055</v>
       </c>
       <c r="C610" t="n">
         <v>0.347826</v>
@@ -8357,7 +8357,7 @@
         </is>
       </c>
       <c r="B611" t="n">
-        <v>0.064469</v>
+        <v>0.06455</v>
       </c>
       <c r="C611" t="n">
         <v>0.345109</v>
@@ -8370,7 +8370,7 @@
         </is>
       </c>
       <c r="B612" t="n">
-        <v>0.06460299999999999</v>
+        <v>0.064835</v>
       </c>
       <c r="C612" t="n">
         <v>0.342391</v>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="B613" t="n">
-        <v>0.064749</v>
+        <v>0.06485399999999999</v>
       </c>
       <c r="C613" t="n">
         <v>0.339674</v>
@@ -8396,7 +8396,7 @@
         </is>
       </c>
       <c r="B614" t="n">
-        <v>0.06496399999999999</v>
+        <v>0.065098</v>
       </c>
       <c r="C614" t="n">
         <v>0.336957</v>
@@ -8409,7 +8409,7 @@
         </is>
       </c>
       <c r="B615" t="n">
-        <v>0.06501</v>
+        <v>0.065259</v>
       </c>
       <c r="C615" t="n">
         <v>0.334239</v>
@@ -8422,7 +8422,7 @@
         </is>
       </c>
       <c r="B616" t="n">
-        <v>0.065803</v>
+        <v>0.06578299999999999</v>
       </c>
       <c r="C616" t="n">
         <v>0.331522</v>
@@ -8435,7 +8435,7 @@
         </is>
       </c>
       <c r="B617" t="n">
-        <v>0.06596100000000001</v>
+        <v>0.066217</v>
       </c>
       <c r="C617" t="n">
         <v>0.328804</v>
@@ -8448,7 +8448,7 @@
         </is>
       </c>
       <c r="B618" t="n">
-        <v>0.066125</v>
+        <v>0.066718</v>
       </c>
       <c r="C618" t="n">
         <v>0.326087</v>
@@ -8461,7 +8461,7 @@
         </is>
       </c>
       <c r="B619" t="n">
-        <v>0.06733599999999999</v>
+        <v>0.066999</v>
       </c>
       <c r="C619" t="n">
         <v>0.32337</v>
@@ -8474,7 +8474,7 @@
         </is>
       </c>
       <c r="B620" t="n">
-        <v>0.067454</v>
+        <v>0.06733699999999999</v>
       </c>
       <c r="C620" t="n">
         <v>0.320652</v>
@@ -8487,7 +8487,7 @@
         </is>
       </c>
       <c r="B621" t="n">
-        <v>0.067659</v>
+        <v>0.068081</v>
       </c>
       <c r="C621" t="n">
         <v>0.317935</v>
@@ -8500,7 +8500,7 @@
         </is>
       </c>
       <c r="B622" t="n">
-        <v>0.06773999999999999</v>
+        <v>0.068146</v>
       </c>
       <c r="C622" t="n">
         <v>0.315217</v>
@@ -8513,7 +8513,7 @@
         </is>
       </c>
       <c r="B623" t="n">
-        <v>0.06808</v>
+        <v>0.068202</v>
       </c>
       <c r="C623" t="n">
         <v>0.3125</v>
@@ -8526,7 +8526,7 @@
         </is>
       </c>
       <c r="B624" t="n">
-        <v>0.068175</v>
+        <v>0.068441</v>
       </c>
       <c r="C624" t="n">
         <v>0.309783</v>
@@ -8539,7 +8539,7 @@
         </is>
       </c>
       <c r="B625" t="n">
-        <v>0.068458</v>
+        <v>0.068899</v>
       </c>
       <c r="C625" t="n">
         <v>0.307065</v>
@@ -8552,7 +8552,7 @@
         </is>
       </c>
       <c r="B626" t="n">
-        <v>0.06855</v>
+        <v>0.069064</v>
       </c>
       <c r="C626" t="n">
         <v>0.304348</v>
@@ -8565,7 +8565,7 @@
         </is>
       </c>
       <c r="B627" t="n">
-        <v>0.06858300000000001</v>
+        <v>0.06923899999999999</v>
       </c>
       <c r="C627" t="n">
         <v>0.30163</v>
@@ -8578,7 +8578,7 @@
         </is>
       </c>
       <c r="B628" t="n">
-        <v>0.06895</v>
+        <v>0.069296</v>
       </c>
       <c r="C628" t="n">
         <v>0.298913</v>
@@ -8591,7 +8591,7 @@
         </is>
       </c>
       <c r="B629" t="n">
-        <v>0.07001599999999999</v>
+        <v>0.070227</v>
       </c>
       <c r="C629" t="n">
         <v>0.296196</v>
@@ -8604,7 +8604,7 @@
         </is>
       </c>
       <c r="B630" t="n">
-        <v>0.072823</v>
+        <v>0.07330200000000001</v>
       </c>
       <c r="C630" t="n">
         <v>0.293478</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="B631" t="n">
-        <v>0.07301100000000001</v>
+        <v>0.073543</v>
       </c>
       <c r="C631" t="n">
         <v>0.290761</v>
@@ -8630,7 +8630,7 @@
         </is>
       </c>
       <c r="B632" t="n">
-        <v>0.073521</v>
+        <v>0.074307</v>
       </c>
       <c r="C632" t="n">
         <v>0.288043</v>
@@ -8643,7 +8643,7 @@
         </is>
       </c>
       <c r="B633" t="n">
-        <v>0.074304</v>
+        <v>0.074346</v>
       </c>
       <c r="C633" t="n">
         <v>0.285326</v>
@@ -8656,7 +8656,7 @@
         </is>
       </c>
       <c r="B634" t="n">
-        <v>0.074861</v>
+        <v>0.07491100000000001</v>
       </c>
       <c r="C634" t="n">
         <v>0.282609</v>
@@ -8669,7 +8669,7 @@
         </is>
       </c>
       <c r="B635" t="n">
-        <v>0.075047</v>
+        <v>0.07529</v>
       </c>
       <c r="C635" t="n">
         <v>0.279891</v>
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="B636" t="n">
-        <v>0.076081</v>
+        <v>0.07605199999999999</v>
       </c>
       <c r="C636" t="n">
         <v>0.277174</v>
@@ -8695,7 +8695,7 @@
         </is>
       </c>
       <c r="B637" t="n">
-        <v>0.07609</v>
+        <v>0.076196</v>
       </c>
       <c r="C637" t="n">
         <v>0.274457</v>
@@ -8708,7 +8708,7 @@
         </is>
       </c>
       <c r="B638" t="n">
-        <v>0.076113</v>
+        <v>0.076956</v>
       </c>
       <c r="C638" t="n">
         <v>0.271739</v>
@@ -8721,7 +8721,7 @@
         </is>
       </c>
       <c r="B639" t="n">
-        <v>0.076737</v>
+        <v>0.077029</v>
       </c>
       <c r="C639" t="n">
         <v>0.269022</v>
@@ -8734,7 +8734,7 @@
         </is>
       </c>
       <c r="B640" t="n">
-        <v>0.077339</v>
+        <v>0.07708</v>
       </c>
       <c r="C640" t="n">
         <v>0.266304</v>
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="B641" t="n">
-        <v>0.078004</v>
+        <v>0.077691</v>
       </c>
       <c r="C641" t="n">
         <v>0.263587</v>
@@ -8760,7 +8760,7 @@
         </is>
       </c>
       <c r="B642" t="n">
-        <v>0.078192</v>
+        <v>0.07833</v>
       </c>
       <c r="C642" t="n">
         <v>0.26087</v>
@@ -8773,7 +8773,7 @@
         </is>
       </c>
       <c r="B643" t="n">
-        <v>0.078459</v>
+        <v>0.07838100000000001</v>
       </c>
       <c r="C643" t="n">
         <v>0.258152</v>
@@ -8786,7 +8786,7 @@
         </is>
       </c>
       <c r="B644" t="n">
-        <v>0.07924200000000001</v>
+        <v>0.0788</v>
       </c>
       <c r="C644" t="n">
         <v>0.255435</v>
@@ -8799,7 +8799,7 @@
         </is>
       </c>
       <c r="B645" t="n">
-        <v>0.079361</v>
+        <v>0.079017</v>
       </c>
       <c r="C645" t="n">
         <v>0.252717</v>
@@ -8812,7 +8812,7 @@
         </is>
       </c>
       <c r="B646" t="n">
-        <v>0.08007400000000001</v>
+        <v>0.080416</v>
       </c>
       <c r="C646" t="n">
         <v>0.25</v>
@@ -8825,7 +8825,7 @@
         </is>
       </c>
       <c r="B647" t="n">
-        <v>0.080221</v>
+        <v>0.080985</v>
       </c>
       <c r="C647" t="n">
         <v>0.247283</v>
@@ -8838,7 +8838,7 @@
         </is>
       </c>
       <c r="B648" t="n">
-        <v>0.08033800000000001</v>
+        <v>0.08100400000000001</v>
       </c>
       <c r="C648" t="n">
         <v>0.244565</v>
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="B649" t="n">
-        <v>0.080691</v>
+        <v>0.081181</v>
       </c>
       <c r="C649" t="n">
         <v>0.241848</v>
@@ -8864,7 +8864,7 @@
         </is>
       </c>
       <c r="B650" t="n">
-        <v>0.081175</v>
+        <v>0.082181</v>
       </c>
       <c r="C650" t="n">
         <v>0.23913</v>
@@ -8877,7 +8877,7 @@
         </is>
       </c>
       <c r="B651" t="n">
-        <v>0.081625</v>
+        <v>0.08244</v>
       </c>
       <c r="C651" t="n">
         <v>0.236413</v>
@@ -8890,7 +8890,7 @@
         </is>
       </c>
       <c r="B652" t="n">
-        <v>0.085068</v>
+        <v>0.085978</v>
       </c>
       <c r="C652" t="n">
         <v>0.233696</v>
@@ -8903,7 +8903,7 @@
         </is>
       </c>
       <c r="B653" t="n">
-        <v>0.085547</v>
+        <v>0.08612599999999999</v>
       </c>
       <c r="C653" t="n">
         <v>0.230978</v>
@@ -8916,7 +8916,7 @@
         </is>
       </c>
       <c r="B654" t="n">
-        <v>0.086634</v>
+        <v>0.086204</v>
       </c>
       <c r="C654" t="n">
         <v>0.228261</v>
@@ -8929,7 +8929,7 @@
         </is>
       </c>
       <c r="B655" t="n">
-        <v>0.086863</v>
+        <v>0.086256</v>
       </c>
       <c r="C655" t="n">
         <v>0.225543</v>
@@ -8942,7 +8942,7 @@
         </is>
       </c>
       <c r="B656" t="n">
-        <v>0.087118</v>
+        <v>0.08687400000000001</v>
       </c>
       <c r="C656" t="n">
         <v>0.222826</v>
@@ -8955,7 +8955,7 @@
         </is>
       </c>
       <c r="B657" t="n">
-        <v>0.087196</v>
+        <v>0.087659</v>
       </c>
       <c r="C657" t="n">
         <v>0.220109</v>
@@ -8968,7 +8968,7 @@
         </is>
       </c>
       <c r="B658" t="n">
-        <v>0.087377</v>
+        <v>0.08814900000000001</v>
       </c>
       <c r="C658" t="n">
         <v>0.217391</v>
@@ -8981,7 +8981,7 @@
         </is>
       </c>
       <c r="B659" t="n">
-        <v>0.087688</v>
+        <v>0.088365</v>
       </c>
       <c r="C659" t="n">
         <v>0.214674</v>
@@ -8994,7 +8994,7 @@
         </is>
       </c>
       <c r="B660" t="n">
-        <v>0.088688</v>
+        <v>0.088528</v>
       </c>
       <c r="C660" t="n">
         <v>0.211957</v>
@@ -9007,7 +9007,7 @@
         </is>
       </c>
       <c r="B661" t="n">
-        <v>0.088773</v>
+        <v>0.08855399999999999</v>
       </c>
       <c r="C661" t="n">
         <v>0.209239</v>
@@ -9020,7 +9020,7 @@
         </is>
       </c>
       <c r="B662" t="n">
-        <v>0.088861</v>
+        <v>0.088811</v>
       </c>
       <c r="C662" t="n">
         <v>0.206522</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="B663" t="n">
-        <v>0.088933</v>
+        <v>0.088953</v>
       </c>
       <c r="C663" t="n">
         <v>0.203804</v>
@@ -9046,7 +9046,7 @@
         </is>
       </c>
       <c r="B664" t="n">
-        <v>0.090171</v>
+        <v>0.089433</v>
       </c>
       <c r="C664" t="n">
         <v>0.201087</v>
@@ -9059,7 +9059,7 @@
         </is>
       </c>
       <c r="B665" t="n">
-        <v>0.090653</v>
+        <v>0.090734</v>
       </c>
       <c r="C665" t="n">
         <v>0.19837</v>
@@ -9072,7 +9072,7 @@
         </is>
       </c>
       <c r="B666" t="n">
-        <v>0.090889</v>
+        <v>0.091629</v>
       </c>
       <c r="C666" t="n">
         <v>0.195652</v>
@@ -9085,7 +9085,7 @@
         </is>
       </c>
       <c r="B667" t="n">
-        <v>0.092099</v>
+        <v>0.09202200000000001</v>
       </c>
       <c r="C667" t="n">
         <v>0.192935</v>
@@ -9098,7 +9098,7 @@
         </is>
       </c>
       <c r="B668" t="n">
-        <v>0.093266</v>
+        <v>0.094086</v>
       </c>
       <c r="C668" t="n">
         <v>0.190217</v>
@@ -9111,7 +9111,7 @@
         </is>
       </c>
       <c r="B669" t="n">
-        <v>0.094564</v>
+        <v>0.09517100000000001</v>
       </c>
       <c r="C669" t="n">
         <v>0.1875</v>
@@ -9124,7 +9124,7 @@
         </is>
       </c>
       <c r="B670" t="n">
-        <v>0.095913</v>
+        <v>0.09618699999999999</v>
       </c>
       <c r="C670" t="n">
         <v>0.184783</v>
@@ -9137,7 +9137,7 @@
         </is>
       </c>
       <c r="B671" t="n">
-        <v>0.096245</v>
+        <v>0.0965</v>
       </c>
       <c r="C671" t="n">
         <v>0.182065</v>
@@ -9150,7 +9150,7 @@
         </is>
       </c>
       <c r="B672" t="n">
-        <v>0.09672699999999999</v>
+        <v>0.09735000000000001</v>
       </c>
       <c r="C672" t="n">
         <v>0.179348</v>
@@ -9163,7 +9163,7 @@
         </is>
       </c>
       <c r="B673" t="n">
-        <v>0.097084</v>
+        <v>0.097931</v>
       </c>
       <c r="C673" t="n">
         <v>0.17663</v>
@@ -9176,7 +9176,7 @@
         </is>
       </c>
       <c r="B674" t="n">
-        <v>0.09832</v>
+        <v>0.098305</v>
       </c>
       <c r="C674" t="n">
         <v>0.173913</v>
@@ -9189,7 +9189,7 @@
         </is>
       </c>
       <c r="B675" t="n">
-        <v>0.0997</v>
+        <v>0.101049</v>
       </c>
       <c r="C675" t="n">
         <v>0.171196</v>
@@ -9202,7 +9202,7 @@
         </is>
       </c>
       <c r="B676" t="n">
-        <v>0.103921</v>
+        <v>0.103724</v>
       </c>
       <c r="C676" t="n">
         <v>0.168478</v>
@@ -9215,7 +9215,7 @@
         </is>
       </c>
       <c r="B677" t="n">
-        <v>0.104297</v>
+        <v>0.105071</v>
       </c>
       <c r="C677" t="n">
         <v>0.165761</v>
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="B678" t="n">
-        <v>0.104958</v>
+        <v>0.105274</v>
       </c>
       <c r="C678" t="n">
         <v>0.163043</v>
@@ -9241,7 +9241,7 @@
         </is>
       </c>
       <c r="B679" t="n">
-        <v>0.105707</v>
+        <v>0.106482</v>
       </c>
       <c r="C679" t="n">
         <v>0.160326</v>
@@ -9254,7 +9254,7 @@
         </is>
       </c>
       <c r="B680" t="n">
-        <v>0.107948</v>
+        <v>0.107524</v>
       </c>
       <c r="C680" t="n">
         <v>0.157609</v>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="B681" t="n">
-        <v>0.109441</v>
+        <v>0.108954</v>
       </c>
       <c r="C681" t="n">
         <v>0.154891</v>
@@ -9280,7 +9280,7 @@
         </is>
       </c>
       <c r="B682" t="n">
-        <v>0.109632</v>
+        <v>0.109672</v>
       </c>
       <c r="C682" t="n">
         <v>0.152174</v>
@@ -9293,7 +9293,7 @@
         </is>
       </c>
       <c r="B683" t="n">
-        <v>0.111107</v>
+        <v>0.110959</v>
       </c>
       <c r="C683" t="n">
         <v>0.149457</v>
@@ -9306,7 +9306,7 @@
         </is>
       </c>
       <c r="B684" t="n">
-        <v>0.11173</v>
+        <v>0.111819</v>
       </c>
       <c r="C684" t="n">
         <v>0.146739</v>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="B685" t="n">
-        <v>0.112795</v>
+        <v>0.113502</v>
       </c>
       <c r="C685" t="n">
         <v>0.144022</v>
@@ -9332,7 +9332,7 @@
         </is>
       </c>
       <c r="B686" t="n">
-        <v>0.113266</v>
+        <v>0.114283</v>
       </c>
       <c r="C686" t="n">
         <v>0.141304</v>
@@ -9345,7 +9345,7 @@
         </is>
       </c>
       <c r="B687" t="n">
-        <v>0.113602</v>
+        <v>0.114515</v>
       </c>
       <c r="C687" t="n">
         <v>0.138587</v>
@@ -9358,7 +9358,7 @@
         </is>
       </c>
       <c r="B688" t="n">
-        <v>0.113703</v>
+        <v>0.115027</v>
       </c>
       <c r="C688" t="n">
         <v>0.13587</v>
@@ -9371,7 +9371,7 @@
         </is>
       </c>
       <c r="B689" t="n">
-        <v>0.114929</v>
+        <v>0.116099</v>
       </c>
       <c r="C689" t="n">
         <v>0.133152</v>
@@ -9384,7 +9384,7 @@
         </is>
       </c>
       <c r="B690" t="n">
-        <v>0.114973</v>
+        <v>0.116118</v>
       </c>
       <c r="C690" t="n">
         <v>0.130435</v>
@@ -9397,7 +9397,7 @@
         </is>
       </c>
       <c r="B691" t="n">
-        <v>0.115994</v>
+        <v>0.116387</v>
       </c>
       <c r="C691" t="n">
         <v>0.127717</v>
@@ -9410,7 +9410,7 @@
         </is>
       </c>
       <c r="B692" t="n">
-        <v>0.118482</v>
+        <v>0.117837</v>
       </c>
       <c r="C692" t="n">
         <v>0.125</v>
@@ -9423,7 +9423,7 @@
         </is>
       </c>
       <c r="B693" t="n">
-        <v>0.11971</v>
+        <v>0.118044</v>
       </c>
       <c r="C693" t="n">
         <v>0.122283</v>
@@ -9436,7 +9436,7 @@
         </is>
       </c>
       <c r="B694" t="n">
-        <v>0.1204</v>
+        <v>0.119071</v>
       </c>
       <c r="C694" t="n">
         <v>0.119565</v>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="B695" t="n">
-        <v>0.120556</v>
+        <v>0.12081</v>
       </c>
       <c r="C695" t="n">
         <v>0.116848</v>
@@ -9462,7 +9462,7 @@
         </is>
       </c>
       <c r="B696" t="n">
-        <v>0.120623</v>
+        <v>0.122077</v>
       </c>
       <c r="C696" t="n">
         <v>0.11413</v>
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="B697" t="n">
-        <v>0.120841</v>
+        <v>0.122477</v>
       </c>
       <c r="C697" t="n">
         <v>0.111413</v>
@@ -9488,7 +9488,7 @@
         </is>
       </c>
       <c r="B698" t="n">
-        <v>0.123011</v>
+        <v>0.123732</v>
       </c>
       <c r="C698" t="n">
         <v>0.108696</v>
@@ -9501,7 +9501,7 @@
         </is>
       </c>
       <c r="B699" t="n">
-        <v>0.12322</v>
+        <v>0.123957</v>
       </c>
       <c r="C699" t="n">
         <v>0.105978</v>
@@ -9514,7 +9514,7 @@
         </is>
       </c>
       <c r="B700" t="n">
-        <v>0.124144</v>
+        <v>0.124101</v>
       </c>
       <c r="C700" t="n">
         <v>0.103261</v>
@@ -9527,7 +9527,7 @@
         </is>
       </c>
       <c r="B701" t="n">
-        <v>0.124683</v>
+        <v>0.124759</v>
       </c>
       <c r="C701" t="n">
         <v>0.100543</v>
@@ -9540,7 +9540,7 @@
         </is>
       </c>
       <c r="B702" t="n">
-        <v>0.126152</v>
+        <v>0.125713</v>
       </c>
       <c r="C702" t="n">
         <v>0.097826</v>
@@ -9553,7 +9553,7 @@
         </is>
       </c>
       <c r="B703" t="n">
-        <v>0.127171</v>
+        <v>0.126254</v>
       </c>
       <c r="C703" t="n">
         <v>0.095109</v>
@@ -9566,7 +9566,7 @@
         </is>
       </c>
       <c r="B704" t="n">
-        <v>0.133663</v>
+        <v>0.134325</v>
       </c>
       <c r="C704" t="n">
         <v>0.092391</v>
@@ -9579,7 +9579,7 @@
         </is>
       </c>
       <c r="B705" t="n">
-        <v>0.13491</v>
+        <v>0.135263</v>
       </c>
       <c r="C705" t="n">
         <v>0.089674</v>
@@ -9592,7 +9592,7 @@
         </is>
       </c>
       <c r="B706" t="n">
-        <v>0.134976</v>
+        <v>0.136398</v>
       </c>
       <c r="C706" t="n">
         <v>0.08695700000000001</v>
@@ -9605,7 +9605,7 @@
         </is>
       </c>
       <c r="B707" t="n">
-        <v>0.138604</v>
+        <v>0.138663</v>
       </c>
       <c r="C707" t="n">
         <v>0.08423899999999999</v>
@@ -9618,7 +9618,7 @@
         </is>
       </c>
       <c r="B708" t="n">
-        <v>0.141291</v>
+        <v>0.141753</v>
       </c>
       <c r="C708" t="n">
         <v>0.081522</v>
@@ -9631,7 +9631,7 @@
         </is>
       </c>
       <c r="B709" t="n">
-        <v>0.141961</v>
+        <v>0.143679</v>
       </c>
       <c r="C709" t="n">
         <v>0.078804</v>
@@ -9644,7 +9644,7 @@
         </is>
       </c>
       <c r="B710" t="n">
-        <v>0.144517</v>
+        <v>0.143914</v>
       </c>
       <c r="C710" t="n">
         <v>0.076087</v>
@@ -9657,7 +9657,7 @@
         </is>
       </c>
       <c r="B711" t="n">
-        <v>0.147325</v>
+        <v>0.148269</v>
       </c>
       <c r="C711" t="n">
         <v>0.07337</v>
@@ -9670,7 +9670,7 @@
         </is>
       </c>
       <c r="B712" t="n">
-        <v>0.148241</v>
+        <v>0.149759</v>
       </c>
       <c r="C712" t="n">
         <v>0.07065200000000001</v>
@@ -9683,7 +9683,7 @@
         </is>
       </c>
       <c r="B713" t="n">
-        <v>0.155056</v>
+        <v>0.156339</v>
       </c>
       <c r="C713" t="n">
         <v>0.067935</v>
@@ -9696,7 +9696,7 @@
         </is>
       </c>
       <c r="B714" t="n">
-        <v>0.155279</v>
+        <v>0.157112</v>
       </c>
       <c r="C714" t="n">
         <v>0.065217</v>
@@ -9709,7 +9709,7 @@
         </is>
       </c>
       <c r="B715" t="n">
-        <v>0.155999</v>
+        <v>0.157287</v>
       </c>
       <c r="C715" t="n">
         <v>0.0625</v>
@@ -9722,7 +9722,7 @@
         </is>
       </c>
       <c r="B716" t="n">
-        <v>0.157722</v>
+        <v>0.159812</v>
       </c>
       <c r="C716" t="n">
         <v>0.059783</v>
@@ -9735,7 +9735,7 @@
         </is>
       </c>
       <c r="B717" t="n">
-        <v>0.160246</v>
+        <v>0.161449</v>
       </c>
       <c r="C717" t="n">
         <v>0.057065</v>
@@ -9748,7 +9748,7 @@
         </is>
       </c>
       <c r="B718" t="n">
-        <v>0.161692</v>
+        <v>0.162335</v>
       </c>
       <c r="C718" t="n">
         <v>0.054348</v>
@@ -9761,7 +9761,7 @@
         </is>
       </c>
       <c r="B719" t="n">
-        <v>0.162093</v>
+        <v>0.164206</v>
       </c>
       <c r="C719" t="n">
         <v>0.05163</v>
@@ -9774,7 +9774,7 @@
         </is>
       </c>
       <c r="B720" t="n">
-        <v>0.170274</v>
+        <v>0.170176</v>
       </c>
       <c r="C720" t="n">
         <v>0.048913</v>
@@ -9787,7 +9787,7 @@
         </is>
       </c>
       <c r="B721" t="n">
-        <v>0.171073</v>
+        <v>0.172562</v>
       </c>
       <c r="C721" t="n">
         <v>0.046196</v>
@@ -9800,7 +9800,7 @@
         </is>
       </c>
       <c r="B722" t="n">
-        <v>0.174315</v>
+        <v>0.172807</v>
       </c>
       <c r="C722" t="n">
         <v>0.043478</v>
@@ -9813,7 +9813,7 @@
         </is>
       </c>
       <c r="B723" t="n">
-        <v>0.182019</v>
+        <v>0.182656</v>
       </c>
       <c r="C723" t="n">
         <v>0.040761</v>
@@ -9826,7 +9826,7 @@
         </is>
       </c>
       <c r="B724" t="n">
-        <v>0.182107</v>
+        <v>0.184453</v>
       </c>
       <c r="C724" t="n">
         <v>0.038043</v>
@@ -9839,7 +9839,7 @@
         </is>
       </c>
       <c r="B725" t="n">
-        <v>0.187047</v>
+        <v>0.184498</v>
       </c>
       <c r="C725" t="n">
         <v>0.035326</v>
@@ -9852,7 +9852,7 @@
         </is>
       </c>
       <c r="B726" t="n">
-        <v>0.198953</v>
+        <v>0.200409</v>
       </c>
       <c r="C726" t="n">
         <v>0.032609</v>
@@ -9865,7 +9865,7 @@
         </is>
       </c>
       <c r="B727" t="n">
-        <v>0.202884</v>
+        <v>0.205404</v>
       </c>
       <c r="C727" t="n">
         <v>0.029891</v>
@@ -9878,7 +9878,7 @@
         </is>
       </c>
       <c r="B728" t="n">
-        <v>0.210375</v>
+        <v>0.213223</v>
       </c>
       <c r="C728" t="n">
         <v>0.027174</v>
@@ -9891,7 +9891,7 @@
         </is>
       </c>
       <c r="B729" t="n">
-        <v>0.210856</v>
+        <v>0.213544</v>
       </c>
       <c r="C729" t="n">
         <v>0.024457</v>
@@ -9904,7 +9904,7 @@
         </is>
       </c>
       <c r="B730" t="n">
-        <v>0.212936</v>
+        <v>0.215819</v>
       </c>
       <c r="C730" t="n">
         <v>0.021739</v>
@@ -9917,7 +9917,7 @@
         </is>
       </c>
       <c r="B731" t="n">
-        <v>0.227431</v>
+        <v>0.225764</v>
       </c>
       <c r="C731" t="n">
         <v>0.019022</v>
@@ -9930,7 +9930,7 @@
         </is>
       </c>
       <c r="B732" t="n">
-        <v>0.229027</v>
+        <v>0.231673</v>
       </c>
       <c r="C732" t="n">
         <v>0.016304</v>
@@ -9943,7 +9943,7 @@
         </is>
       </c>
       <c r="B733" t="n">
-        <v>0.23626</v>
+        <v>0.238669</v>
       </c>
       <c r="C733" t="n">
         <v>0.013587</v>
@@ -9956,7 +9956,7 @@
         </is>
       </c>
       <c r="B734" t="n">
-        <v>0.257426</v>
+        <v>0.258349</v>
       </c>
       <c r="C734" t="n">
         <v>0.01087</v>
@@ -9969,7 +9969,7 @@
         </is>
       </c>
       <c r="B735" t="n">
-        <v>0.269307</v>
+        <v>0.272908</v>
       </c>
       <c r="C735" t="n">
         <v>0.008152</v>
@@ -9982,7 +9982,7 @@
         </is>
       </c>
       <c r="B736" t="n">
-        <v>0.295963</v>
+        <v>0.298613</v>
       </c>
       <c r="C736" t="n">
         <v>0.005435</v>
@@ -9995,7 +9995,7 @@
         </is>
       </c>
       <c r="B737" t="n">
-        <v>0.421771</v>
+        <v>0.426501</v>
       </c>
       <c r="C737" t="n">
         <v>0.002717</v>
@@ -10034,7 +10034,7 @@
         </is>
       </c>
       <c r="B740" t="n">
-        <v>0.000314</v>
+        <v>0.000316</v>
       </c>
       <c r="C740" t="n">
         <v>0.994565</v>
@@ -10047,7 +10047,7 @@
         </is>
       </c>
       <c r="B741" t="n">
-        <v>0.000503</v>
+        <v>0.000504</v>
       </c>
       <c r="C741" t="n">
         <v>0.991848</v>
@@ -10060,7 +10060,7 @@
         </is>
       </c>
       <c r="B742" t="n">
-        <v>0.001025</v>
+        <v>0.001029</v>
       </c>
       <c r="C742" t="n">
         <v>0.98913</v>
@@ -10073,7 +10073,7 @@
         </is>
       </c>
       <c r="B743" t="n">
-        <v>0.001622</v>
+        <v>0.001639</v>
       </c>
       <c r="C743" t="n">
         <v>0.986413</v>
@@ -10086,7 +10086,7 @@
         </is>
       </c>
       <c r="B744" t="n">
-        <v>0.001926</v>
+        <v>0.001916</v>
       </c>
       <c r="C744" t="n">
         <v>0.983696</v>
@@ -10099,7 +10099,7 @@
         </is>
       </c>
       <c r="B745" t="n">
-        <v>0.001987</v>
+        <v>0.002004</v>
       </c>
       <c r="C745" t="n">
         <v>0.980978</v>
@@ -10112,7 +10112,7 @@
         </is>
       </c>
       <c r="B746" t="n">
-        <v>0.002164</v>
+        <v>0.002189</v>
       </c>
       <c r="C746" t="n">
         <v>0.978261</v>
@@ -10125,7 +10125,7 @@
         </is>
       </c>
       <c r="B747" t="n">
-        <v>0.002289</v>
+        <v>0.002312</v>
       </c>
       <c r="C747" t="n">
         <v>0.975543</v>
@@ -10138,7 +10138,7 @@
         </is>
       </c>
       <c r="B748" t="n">
-        <v>0.002907</v>
+        <v>0.002925</v>
       </c>
       <c r="C748" t="n">
         <v>0.972826</v>
@@ -10151,7 +10151,7 @@
         </is>
       </c>
       <c r="B749" t="n">
-        <v>0.002911</v>
+        <v>0.002943</v>
       </c>
       <c r="C749" t="n">
         <v>0.970109</v>
@@ -10164,7 +10164,7 @@
         </is>
       </c>
       <c r="B750" t="n">
-        <v>0.003166</v>
+        <v>0.003181</v>
       </c>
       <c r="C750" t="n">
         <v>0.967391</v>
@@ -10177,7 +10177,7 @@
         </is>
       </c>
       <c r="B751" t="n">
-        <v>0.003359</v>
+        <v>0.003397</v>
       </c>
       <c r="C751" t="n">
         <v>0.964674</v>
@@ -10190,7 +10190,7 @@
         </is>
       </c>
       <c r="B752" t="n">
-        <v>0.004163</v>
+        <v>0.004178</v>
       </c>
       <c r="C752" t="n">
         <v>0.961957</v>
@@ -10203,7 +10203,7 @@
         </is>
       </c>
       <c r="B753" t="n">
-        <v>0.00422</v>
+        <v>0.004238</v>
       </c>
       <c r="C753" t="n">
         <v>0.959239</v>
@@ -10216,7 +10216,7 @@
         </is>
       </c>
       <c r="B754" t="n">
-        <v>0.004674</v>
+        <v>0.004693</v>
       </c>
       <c r="C754" t="n">
         <v>0.956522</v>
@@ -10229,7 +10229,7 @@
         </is>
       </c>
       <c r="B755" t="n">
-        <v>0.004675</v>
+        <v>0.004722</v>
       </c>
       <c r="C755" t="n">
         <v>0.953804</v>
@@ -10242,7 +10242,7 @@
         </is>
       </c>
       <c r="B756" t="n">
-        <v>0.004705</v>
+        <v>0.004757</v>
       </c>
       <c r="C756" t="n">
         <v>0.951087</v>
@@ -10255,7 +10255,7 @@
         </is>
       </c>
       <c r="B757" t="n">
-        <v>0.004757</v>
+        <v>0.004784</v>
       </c>
       <c r="C757" t="n">
         <v>0.94837</v>
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="B758" t="n">
-        <v>0.00492</v>
+        <v>0.0049</v>
       </c>
       <c r="C758" t="n">
         <v>0.945652</v>
@@ -10281,7 +10281,7 @@
         </is>
       </c>
       <c r="B759" t="n">
-        <v>0.004992</v>
+        <v>0.004973</v>
       </c>
       <c r="C759" t="n">
         <v>0.942935</v>
@@ -10294,7 +10294,7 @@
         </is>
       </c>
       <c r="B760" t="n">
-        <v>0.00503</v>
+        <v>0.005084</v>
       </c>
       <c r="C760" t="n">
         <v>0.940217</v>
@@ -10307,7 +10307,7 @@
         </is>
       </c>
       <c r="B761" t="n">
-        <v>0.005206</v>
+        <v>0.005235</v>
       </c>
       <c r="C761" t="n">
         <v>0.9375</v>
@@ -10320,7 +10320,7 @@
         </is>
       </c>
       <c r="B762" t="n">
-        <v>0.005253</v>
+        <v>0.005247</v>
       </c>
       <c r="C762" t="n">
         <v>0.934783</v>
@@ -10333,7 +10333,7 @@
         </is>
       </c>
       <c r="B763" t="n">
-        <v>0.005836</v>
+        <v>0.005889</v>
       </c>
       <c r="C763" t="n">
         <v>0.932065</v>
@@ -10346,7 +10346,7 @@
         </is>
       </c>
       <c r="B764" t="n">
-        <v>0.006079</v>
+        <v>0.006123</v>
       </c>
       <c r="C764" t="n">
         <v>0.929348</v>
@@ -10359,7 +10359,7 @@
         </is>
       </c>
       <c r="B765" t="n">
-        <v>0.006168</v>
+        <v>0.006215</v>
       </c>
       <c r="C765" t="n">
         <v>0.92663</v>
@@ -10372,7 +10372,7 @@
         </is>
       </c>
       <c r="B766" t="n">
-        <v>0.006774</v>
+        <v>0.006807</v>
       </c>
       <c r="C766" t="n">
         <v>0.923913</v>
@@ -10385,7 +10385,7 @@
         </is>
       </c>
       <c r="B767" t="n">
-        <v>0.007546</v>
+        <v>0.007615</v>
       </c>
       <c r="C767" t="n">
         <v>0.921196</v>
@@ -10398,7 +10398,7 @@
         </is>
       </c>
       <c r="B768" t="n">
-        <v>0.00757</v>
+        <v>0.007632</v>
       </c>
       <c r="C768" t="n">
         <v>0.918478</v>
@@ -10411,7 +10411,7 @@
         </is>
       </c>
       <c r="B769" t="n">
-        <v>0.007822000000000001</v>
+        <v>0.00791</v>
       </c>
       <c r="C769" t="n">
         <v>0.915761</v>
@@ -10424,7 +10424,7 @@
         </is>
       </c>
       <c r="B770" t="n">
-        <v>0.008038999999999999</v>
+        <v>0.008099</v>
       </c>
       <c r="C770" t="n">
         <v>0.913043</v>
@@ -10437,7 +10437,7 @@
         </is>
       </c>
       <c r="B771" t="n">
-        <v>0.008279999999999999</v>
+        <v>0.008297000000000001</v>
       </c>
       <c r="C771" t="n">
         <v>0.910326</v>
@@ -10450,7 +10450,7 @@
         </is>
       </c>
       <c r="B772" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.008336</v>
       </c>
       <c r="C772" t="n">
         <v>0.907609</v>
@@ -10463,7 +10463,7 @@
         </is>
       </c>
       <c r="B773" t="n">
-        <v>0.00848</v>
+        <v>0.008576</v>
       </c>
       <c r="C773" t="n">
         <v>0.904891</v>
@@ -10476,7 +10476,7 @@
         </is>
       </c>
       <c r="B774" t="n">
-        <v>0.008598</v>
+        <v>0.008579</v>
       </c>
       <c r="C774" t="n">
         <v>0.902174</v>
@@ -10489,7 +10489,7 @@
         </is>
       </c>
       <c r="B775" t="n">
-        <v>0.008669</v>
+        <v>0.008708</v>
       </c>
       <c r="C775" t="n">
         <v>0.899457</v>
@@ -10502,7 +10502,7 @@
         </is>
       </c>
       <c r="B776" t="n">
-        <v>0.009159</v>
+        <v>0.009043000000000001</v>
       </c>
       <c r="C776" t="n">
         <v>0.896739</v>
@@ -10515,7 +10515,7 @@
         </is>
       </c>
       <c r="B777" t="n">
-        <v>0.009456000000000001</v>
+        <v>0.009559</v>
       </c>
       <c r="C777" t="n">
         <v>0.894022</v>
@@ -10528,7 +10528,7 @@
         </is>
       </c>
       <c r="B778" t="n">
-        <v>0.009660999999999999</v>
+        <v>0.009757</v>
       </c>
       <c r="C778" t="n">
         <v>0.891304</v>
@@ -10541,7 +10541,7 @@
         </is>
       </c>
       <c r="B779" t="n">
-        <v>0.009668</v>
+        <v>0.009771</v>
       </c>
       <c r="C779" t="n">
         <v>0.888587</v>
@@ -10554,7 +10554,7 @@
         </is>
       </c>
       <c r="B780" t="n">
-        <v>0.010139</v>
+        <v>0.010211</v>
       </c>
       <c r="C780" t="n">
         <v>0.88587</v>
@@ -10567,7 +10567,7 @@
         </is>
       </c>
       <c r="B781" t="n">
-        <v>0.010358</v>
+        <v>0.010386</v>
       </c>
       <c r="C781" t="n">
         <v>0.883152</v>
@@ -10580,7 +10580,7 @@
         </is>
       </c>
       <c r="B782" t="n">
-        <v>0.010468</v>
+        <v>0.010443</v>
       </c>
       <c r="C782" t="n">
         <v>0.880435</v>
@@ -10593,7 +10593,7 @@
         </is>
       </c>
       <c r="B783" t="n">
-        <v>0.010655</v>
+        <v>0.010479</v>
       </c>
       <c r="C783" t="n">
         <v>0.877717</v>
@@ -10606,7 +10606,7 @@
         </is>
       </c>
       <c r="B784" t="n">
-        <v>0.01092</v>
+        <v>0.011044</v>
       </c>
       <c r="C784" t="n">
         <v>0.875</v>
@@ -10619,7 +10619,7 @@
         </is>
       </c>
       <c r="B785" t="n">
-        <v>0.011208</v>
+        <v>0.011147</v>
       </c>
       <c r="C785" t="n">
         <v>0.872283</v>
@@ -10632,7 +10632,7 @@
         </is>
       </c>
       <c r="B786" t="n">
-        <v>0.011226</v>
+        <v>0.011271</v>
       </c>
       <c r="C786" t="n">
         <v>0.869565</v>
@@ -10645,7 +10645,7 @@
         </is>
       </c>
       <c r="B787" t="n">
-        <v>0.011522</v>
+        <v>0.011566</v>
       </c>
       <c r="C787" t="n">
         <v>0.866848</v>
@@ -10658,7 +10658,7 @@
         </is>
       </c>
       <c r="B788" t="n">
-        <v>0.011607</v>
+        <v>0.011602</v>
       </c>
       <c r="C788" t="n">
         <v>0.86413</v>
@@ -10671,7 +10671,7 @@
         </is>
       </c>
       <c r="B789" t="n">
-        <v>0.011673</v>
+        <v>0.011703</v>
       </c>
       <c r="C789" t="n">
         <v>0.861413</v>
@@ -10684,7 +10684,7 @@
         </is>
       </c>
       <c r="B790" t="n">
-        <v>0.011909</v>
+        <v>0.01197</v>
       </c>
       <c r="C790" t="n">
         <v>0.858696</v>
@@ -10697,7 +10697,7 @@
         </is>
       </c>
       <c r="B791" t="n">
-        <v>0.011987</v>
+        <v>0.012103</v>
       </c>
       <c r="C791" t="n">
         <v>0.855978</v>
@@ -10710,7 +10710,7 @@
         </is>
       </c>
       <c r="B792" t="n">
-        <v>0.012241</v>
+        <v>0.012309</v>
       </c>
       <c r="C792" t="n">
         <v>0.853261</v>
@@ -10723,7 +10723,7 @@
         </is>
       </c>
       <c r="B793" t="n">
-        <v>0.012319</v>
+        <v>0.012346</v>
       </c>
       <c r="C793" t="n">
         <v>0.850543</v>
@@ -10736,7 +10736,7 @@
         </is>
       </c>
       <c r="B794" t="n">
-        <v>0.012548</v>
+        <v>0.012684</v>
       </c>
       <c r="C794" t="n">
         <v>0.847826</v>
@@ -10749,7 +10749,7 @@
         </is>
       </c>
       <c r="B795" t="n">
-        <v>0.012771</v>
+        <v>0.012888</v>
       </c>
       <c r="C795" t="n">
         <v>0.845109</v>
@@ -10762,7 +10762,7 @@
         </is>
       </c>
       <c r="B796" t="n">
-        <v>0.012976</v>
+        <v>0.01303</v>
       </c>
       <c r="C796" t="n">
         <v>0.842391</v>
@@ -10775,7 +10775,7 @@
         </is>
       </c>
       <c r="B797" t="n">
-        <v>0.013917</v>
+        <v>0.013934</v>
       </c>
       <c r="C797" t="n">
         <v>0.839674</v>
@@ -10788,7 +10788,7 @@
         </is>
       </c>
       <c r="B798" t="n">
-        <v>0.01412</v>
+        <v>0.013945</v>
       </c>
       <c r="C798" t="n">
         <v>0.836957</v>
@@ -10801,7 +10801,7 @@
         </is>
       </c>
       <c r="B799" t="n">
-        <v>0.014126</v>
+        <v>0.014122</v>
       </c>
       <c r="C799" t="n">
         <v>0.834239</v>
@@ -10814,7 +10814,7 @@
         </is>
       </c>
       <c r="B800" t="n">
-        <v>0.014477</v>
+        <v>0.014495</v>
       </c>
       <c r="C800" t="n">
         <v>0.831522</v>
@@ -10827,7 +10827,7 @@
         </is>
       </c>
       <c r="B801" t="n">
-        <v>0.014622</v>
+        <v>0.014787</v>
       </c>
       <c r="C801" t="n">
         <v>0.828804</v>
@@ -10840,7 +10840,7 @@
         </is>
       </c>
       <c r="B802" t="n">
-        <v>0.014745</v>
+        <v>0.01479</v>
       </c>
       <c r="C802" t="n">
         <v>0.826087</v>
@@ -10853,7 +10853,7 @@
         </is>
       </c>
       <c r="B803" t="n">
-        <v>0.014815</v>
+        <v>0.014883</v>
       </c>
       <c r="C803" t="n">
         <v>0.82337</v>
@@ -10866,7 +10866,7 @@
         </is>
       </c>
       <c r="B804" t="n">
-        <v>0.015234</v>
+        <v>0.015267</v>
       </c>
       <c r="C804" t="n">
         <v>0.820652</v>
@@ -10879,7 +10879,7 @@
         </is>
       </c>
       <c r="B805" t="n">
-        <v>0.015771</v>
+        <v>0.015795</v>
       </c>
       <c r="C805" t="n">
         <v>0.817935</v>
@@ -10892,7 +10892,7 @@
         </is>
       </c>
       <c r="B806" t="n">
-        <v>0.015803</v>
+        <v>0.015816</v>
       </c>
       <c r="C806" t="n">
         <v>0.815217</v>
@@ -10905,7 +10905,7 @@
         </is>
       </c>
       <c r="B807" t="n">
-        <v>0.015853</v>
+        <v>0.015966</v>
       </c>
       <c r="C807" t="n">
         <v>0.8125</v>
@@ -10918,7 +10918,7 @@
         </is>
       </c>
       <c r="B808" t="n">
-        <v>0.015857</v>
+        <v>0.015972</v>
       </c>
       <c r="C808" t="n">
         <v>0.809783</v>
@@ -10931,7 +10931,7 @@
         </is>
       </c>
       <c r="B809" t="n">
-        <v>0.016159</v>
+        <v>0.016005</v>
       </c>
       <c r="C809" t="n">
         <v>0.807065</v>
@@ -10944,7 +10944,7 @@
         </is>
       </c>
       <c r="B810" t="n">
-        <v>0.016205</v>
+        <v>0.016271</v>
       </c>
       <c r="C810" t="n">
         <v>0.804348</v>
@@ -10957,7 +10957,7 @@
         </is>
       </c>
       <c r="B811" t="n">
-        <v>0.016687</v>
+        <v>0.016566</v>
       </c>
       <c r="C811" t="n">
         <v>0.80163</v>
@@ -10970,7 +10970,7 @@
         </is>
       </c>
       <c r="B812" t="n">
-        <v>0.016925</v>
+        <v>0.017071</v>
       </c>
       <c r="C812" t="n">
         <v>0.798913</v>
@@ -10983,7 +10983,7 @@
         </is>
       </c>
       <c r="B813" t="n">
-        <v>0.017042</v>
+        <v>0.017205</v>
       </c>
       <c r="C813" t="n">
         <v>0.796196</v>
@@ -10996,7 +10996,7 @@
         </is>
       </c>
       <c r="B814" t="n">
-        <v>0.01761</v>
+        <v>0.01771</v>
       </c>
       <c r="C814" t="n">
         <v>0.793478</v>
@@ -11009,7 +11009,7 @@
         </is>
       </c>
       <c r="B815" t="n">
-        <v>0.017674</v>
+        <v>0.017766</v>
       </c>
       <c r="C815" t="n">
         <v>0.790761</v>
@@ -11022,7 +11022,7 @@
         </is>
       </c>
       <c r="B816" t="n">
-        <v>0.017794</v>
+        <v>0.017797</v>
       </c>
       <c r="C816" t="n">
         <v>0.788043</v>
@@ -11035,7 +11035,7 @@
         </is>
       </c>
       <c r="B817" t="n">
-        <v>0.017896</v>
+        <v>0.017905</v>
       </c>
       <c r="C817" t="n">
         <v>0.785326</v>
@@ -11048,7 +11048,7 @@
         </is>
       </c>
       <c r="B818" t="n">
-        <v>0.017919</v>
+        <v>0.018062</v>
       </c>
       <c r="C818" t="n">
         <v>0.782609</v>
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="B819" t="n">
-        <v>0.018003</v>
+        <v>0.018066</v>
       </c>
       <c r="C819" t="n">
         <v>0.779891</v>
@@ -11074,7 +11074,7 @@
         </is>
       </c>
       <c r="B820" t="n">
-        <v>0.019004</v>
+        <v>0.018875</v>
       </c>
       <c r="C820" t="n">
         <v>0.777174</v>
@@ -11087,7 +11087,7 @@
         </is>
       </c>
       <c r="B821" t="n">
-        <v>0.019184</v>
+        <v>0.019268</v>
       </c>
       <c r="C821" t="n">
         <v>0.774457</v>
@@ -11100,7 +11100,7 @@
         </is>
       </c>
       <c r="B822" t="n">
-        <v>0.019495</v>
+        <v>0.0196</v>
       </c>
       <c r="C822" t="n">
         <v>0.771739</v>
@@ -11113,7 +11113,7 @@
         </is>
       </c>
       <c r="B823" t="n">
-        <v>0.019906</v>
+        <v>0.019866</v>
       </c>
       <c r="C823" t="n">
         <v>0.769022</v>
@@ -11126,7 +11126,7 @@
         </is>
       </c>
       <c r="B824" t="n">
-        <v>0.020075</v>
+        <v>0.020285</v>
       </c>
       <c r="C824" t="n">
         <v>0.766304</v>
@@ -11139,7 +11139,7 @@
         </is>
       </c>
       <c r="B825" t="n">
-        <v>0.020494</v>
+        <v>0.020629</v>
       </c>
       <c r="C825" t="n">
         <v>0.763587</v>
@@ -11152,7 +11152,7 @@
         </is>
       </c>
       <c r="B826" t="n">
-        <v>0.020677</v>
+        <v>0.020633</v>
       </c>
       <c r="C826" t="n">
         <v>0.76087</v>
@@ -11165,7 +11165,7 @@
         </is>
       </c>
       <c r="B827" t="n">
-        <v>0.021609</v>
+        <v>0.02122</v>
       </c>
       <c r="C827" t="n">
         <v>0.758152</v>
@@ -11178,7 +11178,7 @@
         </is>
       </c>
       <c r="B828" t="n">
-        <v>0.021631</v>
+        <v>0.021805</v>
       </c>
       <c r="C828" t="n">
         <v>0.755435</v>
@@ -11191,7 +11191,7 @@
         </is>
       </c>
       <c r="B829" t="n">
-        <v>0.022056</v>
+        <v>0.021974</v>
       </c>
       <c r="C829" t="n">
         <v>0.752717</v>
@@ -11204,7 +11204,7 @@
         </is>
       </c>
       <c r="B830" t="n">
-        <v>0.022388</v>
+        <v>0.022431</v>
       </c>
       <c r="C830" t="n">
         <v>0.75</v>
@@ -11217,7 +11217,7 @@
         </is>
       </c>
       <c r="B831" t="n">
-        <v>0.02298</v>
+        <v>0.022934</v>
       </c>
       <c r="C831" t="n">
         <v>0.747283</v>
@@ -11230,7 +11230,7 @@
         </is>
       </c>
       <c r="B832" t="n">
-        <v>0.023221</v>
+        <v>0.023179</v>
       </c>
       <c r="C832" t="n">
         <v>0.744565</v>
@@ -11243,7 +11243,7 @@
         </is>
       </c>
       <c r="B833" t="n">
-        <v>0.023223</v>
+        <v>0.023189</v>
       </c>
       <c r="C833" t="n">
         <v>0.741848</v>
@@ -11256,7 +11256,7 @@
         </is>
       </c>
       <c r="B834" t="n">
-        <v>0.023226</v>
+        <v>0.023234</v>
       </c>
       <c r="C834" t="n">
         <v>0.73913</v>
@@ -11269,7 +11269,7 @@
         </is>
       </c>
       <c r="B835" t="n">
-        <v>0.023401</v>
+        <v>0.023458</v>
       </c>
       <c r="C835" t="n">
         <v>0.736413</v>
@@ -11282,7 +11282,7 @@
         </is>
       </c>
       <c r="B836" t="n">
-        <v>0.023443</v>
+        <v>0.023499</v>
       </c>
       <c r="C836" t="n">
         <v>0.733696</v>
@@ -11295,7 +11295,7 @@
         </is>
       </c>
       <c r="B837" t="n">
-        <v>0.023726</v>
+        <v>0.023536</v>
       </c>
       <c r="C837" t="n">
         <v>0.730978</v>
@@ -11308,7 +11308,7 @@
         </is>
       </c>
       <c r="B838" t="n">
-        <v>0.023885</v>
+        <v>0.023693</v>
       </c>
       <c r="C838" t="n">
         <v>0.728261</v>
@@ -11321,7 +11321,7 @@
         </is>
       </c>
       <c r="B839" t="n">
-        <v>0.023921</v>
+        <v>0.023976</v>
       </c>
       <c r="C839" t="n">
         <v>0.725543</v>
@@ -11334,7 +11334,7 @@
         </is>
       </c>
       <c r="B840" t="n">
-        <v>0.024887</v>
+        <v>0.024432</v>
       </c>
       <c r="C840" t="n">
         <v>0.722826</v>
@@ -11347,7 +11347,7 @@
         </is>
       </c>
       <c r="B841" t="n">
-        <v>0.025086</v>
+        <v>0.024683</v>
       </c>
       <c r="C841" t="n">
         <v>0.720109</v>
@@ -11360,7 +11360,7 @@
         </is>
       </c>
       <c r="B842" t="n">
-        <v>0.02542</v>
+        <v>0.025274</v>
       </c>
       <c r="C842" t="n">
         <v>0.717391</v>
@@ -11373,7 +11373,7 @@
         </is>
       </c>
       <c r="B843" t="n">
-        <v>0.025549</v>
+        <v>0.025702</v>
       </c>
       <c r="C843" t="n">
         <v>0.714674</v>
@@ -11386,7 +11386,7 @@
         </is>
       </c>
       <c r="B844" t="n">
-        <v>0.025803</v>
+        <v>0.025758</v>
       </c>
       <c r="C844" t="n">
         <v>0.711957</v>
@@ -11399,7 +11399,7 @@
         </is>
       </c>
       <c r="B845" t="n">
-        <v>0.025872</v>
+        <v>0.026039</v>
       </c>
       <c r="C845" t="n">
         <v>0.709239</v>
@@ -11412,7 +11412,7 @@
         </is>
       </c>
       <c r="B846" t="n">
-        <v>0.02611</v>
+        <v>0.026233</v>
       </c>
       <c r="C846" t="n">
         <v>0.706522</v>
@@ -11425,7 +11425,7 @@
         </is>
       </c>
       <c r="B847" t="n">
-        <v>0.026329</v>
+        <v>0.026609</v>
       </c>
       <c r="C847" t="n">
         <v>0.703804</v>
@@ -11438,7 +11438,7 @@
         </is>
       </c>
       <c r="B848" t="n">
-        <v>0.026437</v>
+        <v>0.026673</v>
       </c>
       <c r="C848" t="n">
         <v>0.701087</v>
@@ -11451,7 +11451,7 @@
         </is>
       </c>
       <c r="B849" t="n">
-        <v>0.026683</v>
+        <v>0.026792</v>
       </c>
       <c r="C849" t="n">
         <v>0.69837</v>
@@ -11464,7 +11464,7 @@
         </is>
       </c>
       <c r="B850" t="n">
-        <v>0.026704</v>
+        <v>0.026997</v>
       </c>
       <c r="C850" t="n">
         <v>0.695652</v>
@@ -11477,7 +11477,7 @@
         </is>
       </c>
       <c r="B851" t="n">
-        <v>0.02726</v>
+        <v>0.027495</v>
       </c>
       <c r="C851" t="n">
         <v>0.692935</v>
@@ -11490,7 +11490,7 @@
         </is>
       </c>
       <c r="B852" t="n">
-        <v>0.027337</v>
+        <v>0.027521</v>
       </c>
       <c r="C852" t="n">
         <v>0.690217</v>
@@ -11503,7 +11503,7 @@
         </is>
       </c>
       <c r="B853" t="n">
-        <v>0.027609</v>
+        <v>0.027652</v>
       </c>
       <c r="C853" t="n">
         <v>0.6875</v>
@@ -11516,7 +11516,7 @@
         </is>
       </c>
       <c r="B854" t="n">
-        <v>0.027675</v>
+        <v>0.027689</v>
       </c>
       <c r="C854" t="n">
         <v>0.684783</v>
@@ -11529,7 +11529,7 @@
         </is>
       </c>
       <c r="B855" t="n">
-        <v>0.027764</v>
+        <v>0.027706</v>
       </c>
       <c r="C855" t="n">
         <v>0.682065</v>
@@ -11542,7 +11542,7 @@
         </is>
       </c>
       <c r="B856" t="n">
-        <v>0.027801</v>
+        <v>0.02773</v>
       </c>
       <c r="C856" t="n">
         <v>0.679348</v>
@@ -11555,7 +11555,7 @@
         </is>
       </c>
       <c r="B857" t="n">
-        <v>0.027871</v>
+        <v>0.027779</v>
       </c>
       <c r="C857" t="n">
         <v>0.67663</v>
@@ -11568,7 +11568,7 @@
         </is>
       </c>
       <c r="B858" t="n">
-        <v>0.028244</v>
+        <v>0.028564</v>
       </c>
       <c r="C858" t="n">
         <v>0.673913</v>
@@ -11581,7 +11581,7 @@
         </is>
       </c>
       <c r="B859" t="n">
-        <v>0.028866</v>
+        <v>0.029</v>
       </c>
       <c r="C859" t="n">
         <v>0.671196</v>
@@ -11594,7 +11594,7 @@
         </is>
       </c>
       <c r="B860" t="n">
-        <v>0.028891</v>
+        <v>0.029115</v>
       </c>
       <c r="C860" t="n">
         <v>0.668478</v>
@@ -11607,7 +11607,7 @@
         </is>
       </c>
       <c r="B861" t="n">
-        <v>0.029571</v>
+        <v>0.029273</v>
       </c>
       <c r="C861" t="n">
         <v>0.665761</v>
@@ -11620,7 +11620,7 @@
         </is>
       </c>
       <c r="B862" t="n">
-        <v>0.029656</v>
+        <v>0.029864</v>
       </c>
       <c r="C862" t="n">
         <v>0.663043</v>
@@ -11633,7 +11633,7 @@
         </is>
       </c>
       <c r="B863" t="n">
-        <v>0.0297</v>
+        <v>0.029929</v>
       </c>
       <c r="C863" t="n">
         <v>0.660326</v>
@@ -11646,7 +11646,7 @@
         </is>
       </c>
       <c r="B864" t="n">
-        <v>0.030254</v>
+        <v>0.030282</v>
       </c>
       <c r="C864" t="n">
         <v>0.657609</v>
@@ -11659,7 +11659,7 @@
         </is>
       </c>
       <c r="B865" t="n">
-        <v>0.031032</v>
+        <v>0.030799</v>
       </c>
       <c r="C865" t="n">
         <v>0.654891</v>
@@ -11672,7 +11672,7 @@
         </is>
       </c>
       <c r="B866" t="n">
-        <v>0.031204</v>
+        <v>0.030965</v>
       </c>
       <c r="C866" t="n">
         <v>0.652174</v>
@@ -11685,7 +11685,7 @@
         </is>
       </c>
       <c r="B867" t="n">
-        <v>0.031296</v>
+        <v>0.031261</v>
       </c>
       <c r="C867" t="n">
         <v>0.649457</v>
@@ -11698,7 +11698,7 @@
         </is>
       </c>
       <c r="B868" t="n">
-        <v>0.031352</v>
+        <v>0.031365</v>
       </c>
       <c r="C868" t="n">
         <v>0.646739</v>
@@ -11711,7 +11711,7 @@
         </is>
       </c>
       <c r="B869" t="n">
-        <v>0.031392</v>
+        <v>0.031453</v>
       </c>
       <c r="C869" t="n">
         <v>0.644022</v>
@@ -11724,7 +11724,7 @@
         </is>
       </c>
       <c r="B870" t="n">
-        <v>0.031529</v>
+        <v>0.031545</v>
       </c>
       <c r="C870" t="n">
         <v>0.641304</v>
@@ -11737,7 +11737,7 @@
         </is>
       </c>
       <c r="B871" t="n">
-        <v>0.031993</v>
+        <v>0.032154</v>
       </c>
       <c r="C871" t="n">
         <v>0.638587</v>
@@ -11750,7 +11750,7 @@
         </is>
       </c>
       <c r="B872" t="n">
-        <v>0.032049</v>
+        <v>0.032202</v>
       </c>
       <c r="C872" t="n">
         <v>0.63587</v>
@@ -11763,7 +11763,7 @@
         </is>
       </c>
       <c r="B873" t="n">
-        <v>0.032071</v>
+        <v>0.032213</v>
       </c>
       <c r="C873" t="n">
         <v>0.633152</v>
@@ -11776,7 +11776,7 @@
         </is>
       </c>
       <c r="B874" t="n">
-        <v>0.032229</v>
+        <v>0.03242</v>
       </c>
       <c r="C874" t="n">
         <v>0.630435</v>
@@ -11789,7 +11789,7 @@
         </is>
       </c>
       <c r="B875" t="n">
-        <v>0.032427</v>
+        <v>0.032484</v>
       </c>
       <c r="C875" t="n">
         <v>0.627717</v>
@@ -11802,7 +11802,7 @@
         </is>
       </c>
       <c r="B876" t="n">
-        <v>0.032698</v>
+        <v>0.032744</v>
       </c>
       <c r="C876" t="n">
         <v>0.625</v>
@@ -11815,7 +11815,7 @@
         </is>
       </c>
       <c r="B877" t="n">
-        <v>0.03272</v>
+        <v>0.032885</v>
       </c>
       <c r="C877" t="n">
         <v>0.622283</v>
@@ -11828,7 +11828,7 @@
         </is>
       </c>
       <c r="B878" t="n">
-        <v>0.033274</v>
+        <v>0.033353</v>
       </c>
       <c r="C878" t="n">
         <v>0.619565</v>
@@ -11841,7 +11841,7 @@
         </is>
       </c>
       <c r="B879" t="n">
-        <v>0.033537</v>
+        <v>0.033391</v>
       </c>
       <c r="C879" t="n">
         <v>0.616848</v>
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="B880" t="n">
-        <v>0.034667</v>
+        <v>0.03459</v>
       </c>
       <c r="C880" t="n">
         <v>0.61413</v>
@@ -11867,7 +11867,7 @@
         </is>
       </c>
       <c r="B881" t="n">
-        <v>0.034802</v>
+        <v>0.035041</v>
       </c>
       <c r="C881" t="n">
         <v>0.611413</v>
@@ -11880,7 +11880,7 @@
         </is>
       </c>
       <c r="B882" t="n">
-        <v>0.034887</v>
+        <v>0.035245</v>
       </c>
       <c r="C882" t="n">
         <v>0.608696</v>
@@ -11893,7 +11893,7 @@
         </is>
       </c>
       <c r="B883" t="n">
-        <v>0.035601</v>
+        <v>0.035462</v>
       </c>
       <c r="C883" t="n">
         <v>0.605978</v>
@@ -11906,7 +11906,7 @@
         </is>
       </c>
       <c r="B884" t="n">
-        <v>0.035636</v>
+        <v>0.035711</v>
       </c>
       <c r="C884" t="n">
         <v>0.603261</v>
@@ -11919,7 +11919,7 @@
         </is>
       </c>
       <c r="B885" t="n">
-        <v>0.035636</v>
+        <v>0.035954</v>
       </c>
       <c r="C885" t="n">
         <v>0.600543</v>
@@ -11932,7 +11932,7 @@
         </is>
       </c>
       <c r="B886" t="n">
-        <v>0.036082</v>
+        <v>0.036002</v>
       </c>
       <c r="C886" t="n">
         <v>0.597826</v>
@@ -11945,7 +11945,7 @@
         </is>
       </c>
       <c r="B887" t="n">
-        <v>0.036237</v>
+        <v>0.036643</v>
       </c>
       <c r="C887" t="n">
         <v>0.595109</v>
@@ -11958,7 +11958,7 @@
         </is>
       </c>
       <c r="B888" t="n">
-        <v>0.036401</v>
+        <v>0.036726</v>
       </c>
       <c r="C888" t="n">
         <v>0.592391</v>
@@ -11971,7 +11971,7 @@
         </is>
       </c>
       <c r="B889" t="n">
-        <v>0.036643</v>
+        <v>0.036859</v>
       </c>
       <c r="C889" t="n">
         <v>0.589674</v>
@@ -11984,7 +11984,7 @@
         </is>
       </c>
       <c r="B890" t="n">
-        <v>0.036772</v>
+        <v>0.036949</v>
       </c>
       <c r="C890" t="n">
         <v>0.586957</v>
@@ -11997,7 +11997,7 @@
         </is>
       </c>
       <c r="B891" t="n">
-        <v>0.036988</v>
+        <v>0.037238</v>
       </c>
       <c r="C891" t="n">
         <v>0.584239</v>
@@ -12010,7 +12010,7 @@
         </is>
       </c>
       <c r="B892" t="n">
-        <v>0.037204</v>
+        <v>0.037252</v>
       </c>
       <c r="C892" t="n">
         <v>0.581522</v>
@@ -12023,7 +12023,7 @@
         </is>
       </c>
       <c r="B893" t="n">
-        <v>0.037461</v>
+        <v>0.037842</v>
       </c>
       <c r="C893" t="n">
         <v>0.578804</v>
@@ -12036,7 +12036,7 @@
         </is>
       </c>
       <c r="B894" t="n">
-        <v>0.038515</v>
+        <v>0.038243</v>
       </c>
       <c r="C894" t="n">
         <v>0.576087</v>
@@ -12049,7 +12049,7 @@
         </is>
       </c>
       <c r="B895" t="n">
-        <v>0.03866</v>
+        <v>0.038598</v>
       </c>
       <c r="C895" t="n">
         <v>0.57337</v>
@@ -12062,7 +12062,7 @@
         </is>
       </c>
       <c r="B896" t="n">
-        <v>0.038834</v>
+        <v>0.039052</v>
       </c>
       <c r="C896" t="n">
         <v>0.570652</v>
@@ -12075,7 +12075,7 @@
         </is>
       </c>
       <c r="B897" t="n">
-        <v>0.038993</v>
+        <v>0.039149</v>
       </c>
       <c r="C897" t="n">
         <v>0.567935</v>
@@ -12088,7 +12088,7 @@
         </is>
       </c>
       <c r="B898" t="n">
-        <v>0.039259</v>
+        <v>0.039412</v>
       </c>
       <c r="C898" t="n">
         <v>0.565217</v>
@@ -12101,7 +12101,7 @@
         </is>
       </c>
       <c r="B899" t="n">
-        <v>0.039328</v>
+        <v>0.039652</v>
       </c>
       <c r="C899" t="n">
         <v>0.5625</v>
@@ -12114,7 +12114,7 @@
         </is>
       </c>
       <c r="B900" t="n">
-        <v>0.039442</v>
+        <v>0.039761</v>
       </c>
       <c r="C900" t="n">
         <v>0.559783</v>
@@ -12127,7 +12127,7 @@
         </is>
       </c>
       <c r="B901" t="n">
-        <v>0.039714</v>
+        <v>0.039842</v>
       </c>
       <c r="C901" t="n">
         <v>0.557065</v>
@@ -12140,7 +12140,7 @@
         </is>
       </c>
       <c r="B902" t="n">
-        <v>0.03972</v>
+        <v>0.039942</v>
       </c>
       <c r="C902" t="n">
         <v>0.554348</v>
@@ -12153,7 +12153,7 @@
         </is>
       </c>
       <c r="B903" t="n">
-        <v>0.039912</v>
+        <v>0.040107</v>
       </c>
       <c r="C903" t="n">
         <v>0.55163</v>
@@ -12166,7 +12166,7 @@
         </is>
       </c>
       <c r="B904" t="n">
-        <v>0.039922</v>
+        <v>0.04028</v>
       </c>
       <c r="C904" t="n">
         <v>0.548913</v>
@@ -12179,7 +12179,7 @@
         </is>
       </c>
       <c r="B905" t="n">
-        <v>0.040106</v>
+        <v>0.040378</v>
       </c>
       <c r="C905" t="n">
         <v>0.546196</v>
@@ -12192,7 +12192,7 @@
         </is>
       </c>
       <c r="B906" t="n">
-        <v>0.040127</v>
+        <v>0.040434</v>
       </c>
       <c r="C906" t="n">
         <v>0.543478</v>
@@ -12205,7 +12205,7 @@
         </is>
       </c>
       <c r="B907" t="n">
-        <v>0.040429</v>
+        <v>0.040517</v>
       </c>
       <c r="C907" t="n">
         <v>0.540761</v>
@@ -12218,7 +12218,7 @@
         </is>
       </c>
       <c r="B908" t="n">
-        <v>0.040565</v>
+        <v>0.040925</v>
       </c>
       <c r="C908" t="n">
         <v>0.538043</v>
@@ -12231,7 +12231,7 @@
         </is>
       </c>
       <c r="B909" t="n">
-        <v>0.041143</v>
+        <v>0.041392</v>
       </c>
       <c r="C909" t="n">
         <v>0.535326</v>
@@ -12244,7 +12244,7 @@
         </is>
       </c>
       <c r="B910" t="n">
-        <v>0.041246</v>
+        <v>0.041511</v>
       </c>
       <c r="C910" t="n">
         <v>0.532609</v>
@@ -12257,7 +12257,7 @@
         </is>
       </c>
       <c r="B911" t="n">
-        <v>0.041391</v>
+        <v>0.041523</v>
       </c>
       <c r="C911" t="n">
         <v>0.529891</v>
@@ -12270,7 +12270,7 @@
         </is>
       </c>
       <c r="B912" t="n">
-        <v>0.041656</v>
+        <v>0.041594</v>
       </c>
       <c r="C912" t="n">
         <v>0.527174</v>
@@ -12283,7 +12283,7 @@
         </is>
       </c>
       <c r="B913" t="n">
-        <v>0.041803</v>
+        <v>0.041599</v>
       </c>
       <c r="C913" t="n">
         <v>0.524457</v>
@@ -12296,7 +12296,7 @@
         </is>
       </c>
       <c r="B914" t="n">
-        <v>0.041953</v>
+        <v>0.042196</v>
       </c>
       <c r="C914" t="n">
         <v>0.521739</v>
@@ -12309,7 +12309,7 @@
         </is>
       </c>
       <c r="B915" t="n">
-        <v>0.042141</v>
+        <v>0.042479</v>
       </c>
       <c r="C915" t="n">
         <v>0.519022</v>
@@ -12322,7 +12322,7 @@
         </is>
       </c>
       <c r="B916" t="n">
-        <v>0.042757</v>
+        <v>0.042865</v>
       </c>
       <c r="C916" t="n">
         <v>0.516304</v>
@@ -12335,7 +12335,7 @@
         </is>
       </c>
       <c r="B917" t="n">
-        <v>0.043298</v>
+        <v>0.042954</v>
       </c>
       <c r="C917" t="n">
         <v>0.513587</v>
@@ -12348,7 +12348,7 @@
         </is>
       </c>
       <c r="B918" t="n">
-        <v>0.043531</v>
+        <v>0.043078</v>
       </c>
       <c r="C918" t="n">
         <v>0.51087</v>
@@ -12361,7 +12361,7 @@
         </is>
       </c>
       <c r="B919" t="n">
-        <v>0.043992</v>
+        <v>0.044236</v>
       </c>
       <c r="C919" t="n">
         <v>0.508152</v>
@@ -12374,7 +12374,7 @@
         </is>
       </c>
       <c r="B920" t="n">
-        <v>0.044148</v>
+        <v>0.044451</v>
       </c>
       <c r="C920" t="n">
         <v>0.505435</v>
@@ -12387,7 +12387,7 @@
         </is>
       </c>
       <c r="B921" t="n">
-        <v>0.044529</v>
+        <v>0.044671</v>
       </c>
       <c r="C921" t="n">
         <v>0.502717</v>
@@ -12400,7 +12400,7 @@
         </is>
       </c>
       <c r="B922" t="n">
-        <v>0.045281</v>
+        <v>0.044727</v>
       </c>
       <c r="C922" t="n">
         <v>0.5</v>
@@ -12413,7 +12413,7 @@
         </is>
       </c>
       <c r="B923" t="n">
-        <v>0.045646</v>
+        <v>0.045685</v>
       </c>
       <c r="C923" t="n">
         <v>0.497283</v>
@@ -12426,7 +12426,7 @@
         </is>
       </c>
       <c r="B924" t="n">
-        <v>0.045674</v>
+        <v>0.04584</v>
       </c>
       <c r="C924" t="n">
         <v>0.494565</v>
@@ -12439,7 +12439,7 @@
         </is>
       </c>
       <c r="B925" t="n">
-        <v>0.04579</v>
+        <v>0.046152</v>
       </c>
       <c r="C925" t="n">
         <v>0.491848</v>
@@ -12452,7 +12452,7 @@
         </is>
       </c>
       <c r="B926" t="n">
-        <v>0.046976</v>
+        <v>0.046712</v>
       </c>
       <c r="C926" t="n">
         <v>0.48913</v>
@@ -12465,7 +12465,7 @@
         </is>
       </c>
       <c r="B927" t="n">
-        <v>0.04771</v>
+        <v>0.047102</v>
       </c>
       <c r="C927" t="n">
         <v>0.486413</v>
@@ -12478,7 +12478,7 @@
         </is>
       </c>
       <c r="B928" t="n">
-        <v>0.04801</v>
+        <v>0.048477</v>
       </c>
       <c r="C928" t="n">
         <v>0.483696</v>
@@ -12491,7 +12491,7 @@
         </is>
       </c>
       <c r="B929" t="n">
-        <v>0.048568</v>
+        <v>0.04898</v>
       </c>
       <c r="C929" t="n">
         <v>0.480978</v>
@@ -12504,7 +12504,7 @@
         </is>
       </c>
       <c r="B930" t="n">
-        <v>0.049048</v>
+        <v>0.049295</v>
       </c>
       <c r="C930" t="n">
         <v>0.478261</v>
@@ -12517,7 +12517,7 @@
         </is>
       </c>
       <c r="B931" t="n">
-        <v>0.049246</v>
+        <v>0.049467</v>
       </c>
       <c r="C931" t="n">
         <v>0.475543</v>
@@ -12530,7 +12530,7 @@
         </is>
       </c>
       <c r="B932" t="n">
-        <v>0.0496</v>
+        <v>0.049592</v>
       </c>
       <c r="C932" t="n">
         <v>0.472826</v>
@@ -12543,7 +12543,7 @@
         </is>
       </c>
       <c r="B933" t="n">
-        <v>0.049848</v>
+        <v>0.04966</v>
       </c>
       <c r="C933" t="n">
         <v>0.470109</v>
@@ -12556,7 +12556,7 @@
         </is>
       </c>
       <c r="B934" t="n">
-        <v>0.050368</v>
+        <v>0.049903</v>
       </c>
       <c r="C934" t="n">
         <v>0.467391</v>
@@ -12569,7 +12569,7 @@
         </is>
       </c>
       <c r="B935" t="n">
-        <v>0.050415</v>
+        <v>0.050217</v>
       </c>
       <c r="C935" t="n">
         <v>0.464674</v>
@@ -12582,7 +12582,7 @@
         </is>
       </c>
       <c r="B936" t="n">
-        <v>0.051019</v>
+        <v>0.050579</v>
       </c>
       <c r="C936" t="n">
         <v>0.461957</v>
@@ -12595,7 +12595,7 @@
         </is>
       </c>
       <c r="B937" t="n">
-        <v>0.051049</v>
+        <v>0.051156</v>
       </c>
       <c r="C937" t="n">
         <v>0.459239</v>
@@ -12608,7 +12608,7 @@
         </is>
       </c>
       <c r="B938" t="n">
-        <v>0.051215</v>
+        <v>0.051202</v>
       </c>
       <c r="C938" t="n">
         <v>0.456522</v>
@@ -12621,7 +12621,7 @@
         </is>
       </c>
       <c r="B939" t="n">
-        <v>0.051264</v>
+        <v>0.051233</v>
       </c>
       <c r="C939" t="n">
         <v>0.453804</v>
@@ -12634,7 +12634,7 @@
         </is>
       </c>
       <c r="B940" t="n">
-        <v>0.051375</v>
+        <v>0.051477</v>
       </c>
       <c r="C940" t="n">
         <v>0.451087</v>
@@ -12647,7 +12647,7 @@
         </is>
       </c>
       <c r="B941" t="n">
-        <v>0.051409</v>
+        <v>0.0518</v>
       </c>
       <c r="C941" t="n">
         <v>0.44837</v>
@@ -12660,7 +12660,7 @@
         </is>
       </c>
       <c r="B942" t="n">
-        <v>0.051611</v>
+        <v>0.051963</v>
       </c>
       <c r="C942" t="n">
         <v>0.445652</v>
@@ -12673,7 +12673,7 @@
         </is>
       </c>
       <c r="B943" t="n">
-        <v>0.052773</v>
+        <v>0.05279</v>
       </c>
       <c r="C943" t="n">
         <v>0.442935</v>
@@ -12686,7 +12686,7 @@
         </is>
       </c>
       <c r="B944" t="n">
-        <v>0.053126</v>
+        <v>0.053346</v>
       </c>
       <c r="C944" t="n">
         <v>0.440217</v>
@@ -12699,7 +12699,7 @@
         </is>
       </c>
       <c r="B945" t="n">
-        <v>0.053494</v>
+        <v>0.05364</v>
       </c>
       <c r="C945" t="n">
         <v>0.4375</v>
@@ -12712,7 +12712,7 @@
         </is>
       </c>
       <c r="B946" t="n">
-        <v>0.054067</v>
+        <v>0.05381</v>
       </c>
       <c r="C946" t="n">
         <v>0.434783</v>
@@ -12725,7 +12725,7 @@
         </is>
       </c>
       <c r="B947" t="n">
-        <v>0.055295</v>
+        <v>0.054958</v>
       </c>
       <c r="C947" t="n">
         <v>0.432065</v>
@@ -12738,7 +12738,7 @@
         </is>
       </c>
       <c r="B948" t="n">
-        <v>0.055338</v>
+        <v>0.055461</v>
       </c>
       <c r="C948" t="n">
         <v>0.429348</v>
@@ -12751,7 +12751,7 @@
         </is>
       </c>
       <c r="B949" t="n">
-        <v>0.05535</v>
+        <v>0.055467</v>
       </c>
       <c r="C949" t="n">
         <v>0.42663</v>
@@ -12764,7 +12764,7 @@
         </is>
       </c>
       <c r="B950" t="n">
-        <v>0.055692</v>
+        <v>0.055778</v>
       </c>
       <c r="C950" t="n">
         <v>0.423913</v>
@@ -12777,7 +12777,7 @@
         </is>
       </c>
       <c r="B951" t="n">
-        <v>0.056148</v>
+        <v>0.056298</v>
       </c>
       <c r="C951" t="n">
         <v>0.421196</v>
@@ -12790,7 +12790,7 @@
         </is>
       </c>
       <c r="B952" t="n">
-        <v>0.056532</v>
+        <v>0.056819</v>
       </c>
       <c r="C952" t="n">
         <v>0.418478</v>
@@ -12803,7 +12803,7 @@
         </is>
       </c>
       <c r="B953" t="n">
-        <v>0.056845</v>
+        <v>0.056897</v>
       </c>
       <c r="C953" t="n">
         <v>0.415761</v>
@@ -12816,7 +12816,7 @@
         </is>
       </c>
       <c r="B954" t="n">
-        <v>0.057037</v>
+        <v>0.057361</v>
       </c>
       <c r="C954" t="n">
         <v>0.413043</v>
@@ -12829,7 +12829,7 @@
         </is>
       </c>
       <c r="B955" t="n">
-        <v>0.057802</v>
+        <v>0.057835</v>
       </c>
       <c r="C955" t="n">
         <v>0.410326</v>
@@ -12842,7 +12842,7 @@
         </is>
       </c>
       <c r="B956" t="n">
-        <v>0.058755</v>
+        <v>0.058602</v>
       </c>
       <c r="C956" t="n">
         <v>0.407609</v>
@@ -12855,7 +12855,7 @@
         </is>
       </c>
       <c r="B957" t="n">
-        <v>0.059029</v>
+        <v>0.059654</v>
       </c>
       <c r="C957" t="n">
         <v>0.404891</v>
@@ -12868,7 +12868,7 @@
         </is>
       </c>
       <c r="B958" t="n">
-        <v>0.061</v>
+        <v>0.060484</v>
       </c>
       <c r="C958" t="n">
         <v>0.402174</v>
@@ -12881,7 +12881,7 @@
         </is>
       </c>
       <c r="B959" t="n">
-        <v>0.061221</v>
+        <v>0.06125</v>
       </c>
       <c r="C959" t="n">
         <v>0.399457</v>
@@ -12894,7 +12894,7 @@
         </is>
       </c>
       <c r="B960" t="n">
-        <v>0.061681</v>
+        <v>0.061788</v>
       </c>
       <c r="C960" t="n">
         <v>0.396739</v>
@@ -12907,7 +12907,7 @@
         </is>
       </c>
       <c r="B961" t="n">
-        <v>0.061782</v>
+        <v>0.062044</v>
       </c>
       <c r="C961" t="n">
         <v>0.394022</v>
@@ -12920,7 +12920,7 @@
         </is>
       </c>
       <c r="B962" t="n">
-        <v>0.061821</v>
+        <v>0.062182</v>
       </c>
       <c r="C962" t="n">
         <v>0.391304</v>
@@ -12933,7 +12933,7 @@
         </is>
       </c>
       <c r="B963" t="n">
-        <v>0.062452</v>
+        <v>0.062197</v>
       </c>
       <c r="C963" t="n">
         <v>0.388587</v>
@@ -12946,7 +12946,7 @@
         </is>
       </c>
       <c r="B964" t="n">
-        <v>0.062502</v>
+        <v>0.062787</v>
       </c>
       <c r="C964" t="n">
         <v>0.38587</v>
@@ -12959,7 +12959,7 @@
         </is>
       </c>
       <c r="B965" t="n">
-        <v>0.062583</v>
+        <v>0.062804</v>
       </c>
       <c r="C965" t="n">
         <v>0.383152</v>
@@ -12972,7 +12972,7 @@
         </is>
       </c>
       <c r="B966" t="n">
-        <v>0.062918</v>
+        <v>0.063084</v>
       </c>
       <c r="C966" t="n">
         <v>0.380435</v>
@@ -12985,7 +12985,7 @@
         </is>
       </c>
       <c r="B967" t="n">
-        <v>0.063332</v>
+        <v>0.063085</v>
       </c>
       <c r="C967" t="n">
         <v>0.377717</v>
@@ -12998,7 +12998,7 @@
         </is>
       </c>
       <c r="B968" t="n">
-        <v>0.06375</v>
+        <v>0.063426</v>
       </c>
       <c r="C968" t="n">
         <v>0.375</v>
@@ -13011,7 +13011,7 @@
         </is>
       </c>
       <c r="B969" t="n">
-        <v>0.06393600000000001</v>
+        <v>0.063483</v>
       </c>
       <c r="C969" t="n">
         <v>0.372283</v>
@@ -13024,7 +13024,7 @@
         </is>
       </c>
       <c r="B970" t="n">
-        <v>0.06393799999999999</v>
+        <v>0.06375400000000001</v>
       </c>
       <c r="C970" t="n">
         <v>0.369565</v>
@@ -13037,7 +13037,7 @@
         </is>
       </c>
       <c r="B971" t="n">
-        <v>0.064293</v>
+        <v>0.06399199999999999</v>
       </c>
       <c r="C971" t="n">
         <v>0.366848</v>
@@ -13050,7 +13050,7 @@
         </is>
       </c>
       <c r="B972" t="n">
-        <v>0.064378</v>
+        <v>0.06422</v>
       </c>
       <c r="C972" t="n">
         <v>0.36413</v>
@@ -13063,7 +13063,7 @@
         </is>
       </c>
       <c r="B973" t="n">
-        <v>0.064405</v>
+        <v>0.064355</v>
       </c>
       <c r="C973" t="n">
         <v>0.361413</v>
@@ -13076,7 +13076,7 @@
         </is>
       </c>
       <c r="B974" t="n">
-        <v>0.06554400000000001</v>
+        <v>0.06615799999999999</v>
       </c>
       <c r="C974" t="n">
         <v>0.358696</v>
@@ -13089,7 +13089,7 @@
         </is>
       </c>
       <c r="B975" t="n">
-        <v>0.06621</v>
+        <v>0.066967</v>
       </c>
       <c r="C975" t="n">
         <v>0.355978</v>
@@ -13102,7 +13102,7 @@
         </is>
       </c>
       <c r="B976" t="n">
-        <v>0.066304</v>
+        <v>0.06705999999999999</v>
       </c>
       <c r="C976" t="n">
         <v>0.353261</v>
@@ -13115,7 +13115,7 @@
         </is>
       </c>
       <c r="B977" t="n">
-        <v>0.067218</v>
+        <v>0.067403</v>
       </c>
       <c r="C977" t="n">
         <v>0.350543</v>
@@ -13128,7 +13128,7 @@
         </is>
       </c>
       <c r="B978" t="n">
-        <v>0.06794799999999999</v>
+        <v>0.0678</v>
       </c>
       <c r="C978" t="n">
         <v>0.347826</v>
@@ -13141,7 +13141,7 @@
         </is>
       </c>
       <c r="B979" t="n">
-        <v>0.068379</v>
+        <v>0.068324</v>
       </c>
       <c r="C979" t="n">
         <v>0.345109</v>
@@ -13154,7 +13154,7 @@
         </is>
       </c>
       <c r="B980" t="n">
-        <v>0.068522</v>
+        <v>0.06862600000000001</v>
       </c>
       <c r="C980" t="n">
         <v>0.342391</v>
@@ -13167,7 +13167,7 @@
         </is>
       </c>
       <c r="B981" t="n">
-        <v>0.068676</v>
+        <v>0.068646</v>
       </c>
       <c r="C981" t="n">
         <v>0.339674</v>
@@ -13193,7 +13193,7 @@
         </is>
       </c>
       <c r="B983" t="n">
-        <v>0.068954</v>
+        <v>0.069075</v>
       </c>
       <c r="C983" t="n">
         <v>0.334239</v>
@@ -13206,7 +13206,7 @@
         </is>
       </c>
       <c r="B984" t="n">
-        <v>0.06979399999999999</v>
+        <v>0.069629</v>
       </c>
       <c r="C984" t="n">
         <v>0.331522</v>
@@ -13219,7 +13219,7 @@
         </is>
       </c>
       <c r="B985" t="n">
-        <v>0.069962</v>
+        <v>0.070089</v>
       </c>
       <c r="C985" t="n">
         <v>0.328804</v>
@@ -13232,7 +13232,7 @@
         </is>
       </c>
       <c r="B986" t="n">
-        <v>0.070136</v>
+        <v>0.070618</v>
       </c>
       <c r="C986" t="n">
         <v>0.326087</v>
@@ -13245,7 +13245,7 @@
         </is>
       </c>
       <c r="B987" t="n">
-        <v>0.071421</v>
+        <v>0.07091600000000001</v>
       </c>
       <c r="C987" t="n">
         <v>0.32337</v>
@@ -13258,7 +13258,7 @@
         </is>
       </c>
       <c r="B988" t="n">
-        <v>0.071546</v>
+        <v>0.07127500000000001</v>
       </c>
       <c r="C988" t="n">
         <v>0.320652</v>
@@ -13271,7 +13271,7 @@
         </is>
       </c>
       <c r="B989" t="n">
-        <v>0.07176299999999999</v>
+        <v>0.072062</v>
       </c>
       <c r="C989" t="n">
         <v>0.317935</v>
@@ -13284,7 +13284,7 @@
         </is>
       </c>
       <c r="B990" t="n">
-        <v>0.071849</v>
+        <v>0.072131</v>
       </c>
       <c r="C990" t="n">
         <v>0.315217</v>
@@ -13297,7 +13297,7 @@
         </is>
       </c>
       <c r="B991" t="n">
-        <v>0.07221</v>
+        <v>0.072189</v>
       </c>
       <c r="C991" t="n">
         <v>0.3125</v>
@@ -13310,7 +13310,7 @@
         </is>
       </c>
       <c r="B992" t="n">
-        <v>0.07231</v>
+        <v>0.07244299999999999</v>
       </c>
       <c r="C992" t="n">
         <v>0.309783</v>
@@ -13323,7 +13323,7 @@
         </is>
       </c>
       <c r="B993" t="n">
-        <v>0.07260999999999999</v>
+        <v>0.07292700000000001</v>
       </c>
       <c r="C993" t="n">
         <v>0.307065</v>
@@ -13336,7 +13336,7 @@
         </is>
       </c>
       <c r="B994" t="n">
-        <v>0.07270799999999999</v>
+        <v>0.073102</v>
       </c>
       <c r="C994" t="n">
         <v>0.304348</v>
@@ -13349,7 +13349,7 @@
         </is>
       </c>
       <c r="B995" t="n">
-        <v>0.072743</v>
+        <v>0.07328800000000001</v>
       </c>
       <c r="C995" t="n">
         <v>0.30163</v>
@@ -13362,7 +13362,7 @@
         </is>
       </c>
       <c r="B996" t="n">
-        <v>0.073132</v>
+        <v>0.073348</v>
       </c>
       <c r="C996" t="n">
         <v>0.298913</v>
@@ -13375,7 +13375,7 @@
         </is>
       </c>
       <c r="B997" t="n">
-        <v>0.07426199999999999</v>
+        <v>0.074334</v>
       </c>
       <c r="C997" t="n">
         <v>0.296196</v>
@@ -13388,7 +13388,7 @@
         </is>
       </c>
       <c r="B998" t="n">
-        <v>0.07724</v>
+        <v>0.077588</v>
       </c>
       <c r="C998" t="n">
         <v>0.293478</v>
@@ -13401,7 +13401,7 @@
         </is>
       </c>
       <c r="B999" t="n">
-        <v>0.07743999999999999</v>
+        <v>0.077843</v>
       </c>
       <c r="C999" t="n">
         <v>0.290761</v>
@@ -13414,7 +13414,7 @@
         </is>
       </c>
       <c r="B1000" t="n">
-        <v>0.07797999999999999</v>
+        <v>0.078652</v>
       </c>
       <c r="C1000" t="n">
         <v>0.288043</v>
@@ -13427,7 +13427,7 @@
         </is>
       </c>
       <c r="B1001" t="n">
-        <v>0.07881100000000001</v>
+        <v>0.078693</v>
       </c>
       <c r="C1001" t="n">
         <v>0.285326</v>
@@ -13440,7 +13440,7 @@
         </is>
       </c>
       <c r="B1002" t="n">
-        <v>0.079402</v>
+        <v>0.079291</v>
       </c>
       <c r="C1002" t="n">
         <v>0.282609</v>
@@ -13453,7 +13453,7 @@
         </is>
       </c>
       <c r="B1003" t="n">
-        <v>0.079599</v>
+        <v>0.079693</v>
       </c>
       <c r="C1003" t="n">
         <v>0.279891</v>
@@ -13466,7 +13466,7 @@
         </is>
       </c>
       <c r="B1004" t="n">
-        <v>0.080696</v>
+        <v>0.080499</v>
       </c>
       <c r="C1004" t="n">
         <v>0.277174</v>
@@ -13479,7 +13479,7 @@
         </is>
       </c>
       <c r="B1005" t="n">
-        <v>0.080706</v>
+        <v>0.080651</v>
       </c>
       <c r="C1005" t="n">
         <v>0.274457</v>
@@ -13492,7 +13492,7 @@
         </is>
       </c>
       <c r="B1006" t="n">
-        <v>0.080729</v>
+        <v>0.081456</v>
       </c>
       <c r="C1006" t="n">
         <v>0.271739</v>
@@ -13505,7 +13505,7 @@
         </is>
       </c>
       <c r="B1007" t="n">
-        <v>0.08139100000000001</v>
+        <v>0.08153199999999999</v>
       </c>
       <c r="C1007" t="n">
         <v>0.269022</v>
@@ -13518,7 +13518,7 @@
         </is>
       </c>
       <c r="B1008" t="n">
-        <v>0.08203000000000001</v>
+        <v>0.08158700000000001</v>
       </c>
       <c r="C1008" t="n">
         <v>0.266304</v>
@@ -13531,7 +13531,7 @@
         </is>
       </c>
       <c r="B1009" t="n">
-        <v>0.082735</v>
+        <v>0.082234</v>
       </c>
       <c r="C1009" t="n">
         <v>0.263587</v>
@@ -13544,7 +13544,7 @@
         </is>
       </c>
       <c r="B1010" t="n">
-        <v>0.08293399999999999</v>
+        <v>0.08291</v>
       </c>
       <c r="C1010" t="n">
         <v>0.26087</v>
@@ -13557,7 +13557,7 @@
         </is>
       </c>
       <c r="B1011" t="n">
-        <v>0.083218</v>
+        <v>0.082964</v>
       </c>
       <c r="C1011" t="n">
         <v>0.258152</v>
@@ -13570,7 +13570,7 @@
         </is>
       </c>
       <c r="B1012" t="n">
-        <v>0.084048</v>
+        <v>0.083407</v>
       </c>
       <c r="C1012" t="n">
         <v>0.255435</v>
@@ -13583,7 +13583,7 @@
         </is>
       </c>
       <c r="B1013" t="n">
-        <v>0.084175</v>
+        <v>0.083637</v>
       </c>
       <c r="C1013" t="n">
         <v>0.252717</v>
@@ -13596,7 +13596,7 @@
         </is>
       </c>
       <c r="B1014" t="n">
-        <v>0.08493100000000001</v>
+        <v>0.085118</v>
       </c>
       <c r="C1014" t="n">
         <v>0.25</v>
@@ -13609,7 +13609,7 @@
         </is>
       </c>
       <c r="B1015" t="n">
-        <v>0.085087</v>
+        <v>0.08572</v>
       </c>
       <c r="C1015" t="n">
         <v>0.247283</v>
@@ -13622,7 +13622,7 @@
         </is>
       </c>
       <c r="B1016" t="n">
-        <v>0.085211</v>
+        <v>0.085741</v>
       </c>
       <c r="C1016" t="n">
         <v>0.244565</v>
@@ -13635,7 +13635,7 @@
         </is>
       </c>
       <c r="B1017" t="n">
-        <v>0.08558499999999999</v>
+        <v>0.085928</v>
       </c>
       <c r="C1017" t="n">
         <v>0.241848</v>
@@ -13648,7 +13648,7 @@
         </is>
       </c>
       <c r="B1018" t="n">
-        <v>0.08609899999999999</v>
+        <v>0.08698599999999999</v>
       </c>
       <c r="C1018" t="n">
         <v>0.23913</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="B1019" t="n">
-        <v>0.086576</v>
+        <v>0.08726</v>
       </c>
       <c r="C1019" t="n">
         <v>0.236413</v>
@@ -13674,7 +13674,7 @@
         </is>
       </c>
       <c r="B1020" t="n">
-        <v>0.090228</v>
+        <v>0.091005</v>
       </c>
       <c r="C1020" t="n">
         <v>0.233696</v>
@@ -13687,7 +13687,7 @@
         </is>
       </c>
       <c r="B1021" t="n">
-        <v>0.090736</v>
+        <v>0.09116200000000001</v>
       </c>
       <c r="C1021" t="n">
         <v>0.230978</v>
@@ -13700,7 +13700,7 @@
         </is>
       </c>
       <c r="B1022" t="n">
-        <v>0.091889</v>
+        <v>0.09124400000000001</v>
       </c>
       <c r="C1022" t="n">
         <v>0.228261</v>
@@ -13713,7 +13713,7 @@
         </is>
       </c>
       <c r="B1023" t="n">
-        <v>0.092131</v>
+        <v>0.09129900000000001</v>
       </c>
       <c r="C1023" t="n">
         <v>0.225543</v>
@@ -13726,7 +13726,7 @@
         </is>
       </c>
       <c r="B1024" t="n">
-        <v>0.092402</v>
+        <v>0.09195299999999999</v>
       </c>
       <c r="C1024" t="n">
         <v>0.222826</v>
@@ -13739,7 +13739,7 @@
         </is>
       </c>
       <c r="B1025" t="n">
-        <v>0.092485</v>
+        <v>0.09278400000000001</v>
       </c>
       <c r="C1025" t="n">
         <v>0.220109</v>
@@ -13752,7 +13752,7 @@
         </is>
       </c>
       <c r="B1026" t="n">
-        <v>0.09267599999999999</v>
+        <v>0.093303</v>
       </c>
       <c r="C1026" t="n">
         <v>0.217391</v>
@@ -13765,7 +13765,7 @@
         </is>
       </c>
       <c r="B1027" t="n">
-        <v>0.09300600000000001</v>
+        <v>0.093531</v>
       </c>
       <c r="C1027" t="n">
         <v>0.214674</v>
@@ -13778,7 +13778,7 @@
         </is>
       </c>
       <c r="B1028" t="n">
-        <v>0.094068</v>
+        <v>0.093704</v>
       </c>
       <c r="C1028" t="n">
         <v>0.211957</v>
@@ -13791,7 +13791,7 @@
         </is>
       </c>
       <c r="B1029" t="n">
-        <v>0.09415800000000001</v>
+        <v>0.093732</v>
       </c>
       <c r="C1029" t="n">
         <v>0.209239</v>
@@ -13804,7 +13804,7 @@
         </is>
       </c>
       <c r="B1030" t="n">
-        <v>0.094251</v>
+        <v>0.094004</v>
       </c>
       <c r="C1030" t="n">
         <v>0.206522</v>
@@ -13817,7 +13817,7 @@
         </is>
       </c>
       <c r="B1031" t="n">
-        <v>0.09432699999999999</v>
+        <v>0.094154</v>
       </c>
       <c r="C1031" t="n">
         <v>0.203804</v>
@@ -13830,7 +13830,7 @@
         </is>
       </c>
       <c r="B1032" t="n">
-        <v>0.095641</v>
+        <v>0.094662</v>
       </c>
       <c r="C1032" t="n">
         <v>0.201087</v>
@@ -13843,7 +13843,7 @@
         </is>
       </c>
       <c r="B1033" t="n">
-        <v>0.096151</v>
+        <v>0.096039</v>
       </c>
       <c r="C1033" t="n">
         <v>0.19837</v>
@@ -13856,7 +13856,7 @@
         </is>
       </c>
       <c r="B1034" t="n">
-        <v>0.096402</v>
+        <v>0.096987</v>
       </c>
       <c r="C1034" t="n">
         <v>0.195652</v>
@@ -13869,7 +13869,7 @@
         </is>
       </c>
       <c r="B1035" t="n">
-        <v>0.09768499999999999</v>
+        <v>0.097403</v>
       </c>
       <c r="C1035" t="n">
         <v>0.192935</v>
@@ -13882,7 +13882,7 @@
         </is>
       </c>
       <c r="B1036" t="n">
-        <v>0.098923</v>
+        <v>0.09958699999999999</v>
       </c>
       <c r="C1036" t="n">
         <v>0.190217</v>
@@ -13895,7 +13895,7 @@
         </is>
       </c>
       <c r="B1037" t="n">
-        <v>0.1003</v>
+        <v>0.100735</v>
       </c>
       <c r="C1037" t="n">
         <v>0.1875</v>
@@ -13908,7 +13908,7 @@
         </is>
       </c>
       <c r="B1038" t="n">
-        <v>0.101731</v>
+        <v>0.101811</v>
       </c>
       <c r="C1038" t="n">
         <v>0.184783</v>
@@ -13921,7 +13921,7 @@
         </is>
       </c>
       <c r="B1039" t="n">
-        <v>0.102083</v>
+        <v>0.102142</v>
       </c>
       <c r="C1039" t="n">
         <v>0.182065</v>
@@ -13934,7 +13934,7 @@
         </is>
       </c>
       <c r="B1040" t="n">
-        <v>0.102594</v>
+        <v>0.103043</v>
       </c>
       <c r="C1040" t="n">
         <v>0.179348</v>
@@ -13947,7 +13947,7 @@
         </is>
       </c>
       <c r="B1041" t="n">
-        <v>0.102973</v>
+        <v>0.103657</v>
       </c>
       <c r="C1041" t="n">
         <v>0.17663</v>
@@ -13960,7 +13960,7 @@
         </is>
       </c>
       <c r="B1042" t="n">
-        <v>0.104284</v>
+        <v>0.104053</v>
       </c>
       <c r="C1042" t="n">
         <v>0.173913</v>
@@ -13973,7 +13973,7 @@
         </is>
       </c>
       <c r="B1043" t="n">
-        <v>0.105748</v>
+        <v>0.106958</v>
       </c>
       <c r="C1043" t="n">
         <v>0.171196</v>
@@ -13986,7 +13986,7 @@
         </is>
       </c>
       <c r="B1044" t="n">
-        <v>0.110224</v>
+        <v>0.109789</v>
       </c>
       <c r="C1044" t="n">
         <v>0.168478</v>
@@ -13999,7 +13999,7 @@
         </is>
       </c>
       <c r="B1045" t="n">
-        <v>0.110624</v>
+        <v>0.111214</v>
       </c>
       <c r="C1045" t="n">
         <v>0.165761</v>
@@ -14012,7 +14012,7 @@
         </is>
       </c>
       <c r="B1046" t="n">
-        <v>0.111325</v>
+        <v>0.111429</v>
       </c>
       <c r="C1046" t="n">
         <v>0.163043</v>
@@ -14025,7 +14025,7 @@
         </is>
       </c>
       <c r="B1047" t="n">
-        <v>0.112119</v>
+        <v>0.112707</v>
       </c>
       <c r="C1047" t="n">
         <v>0.160326</v>
@@ -14038,7 +14038,7 @@
         </is>
       </c>
       <c r="B1048" t="n">
-        <v>0.114495</v>
+        <v>0.113811</v>
       </c>
       <c r="C1048" t="n">
         <v>0.157609</v>
@@ -14051,7 +14051,7 @@
         </is>
       </c>
       <c r="B1049" t="n">
-        <v>0.116079</v>
+        <v>0.115324</v>
       </c>
       <c r="C1049" t="n">
         <v>0.154891</v>
@@ -14064,7 +14064,7 @@
         </is>
       </c>
       <c r="B1050" t="n">
-        <v>0.116282</v>
+        <v>0.116084</v>
       </c>
       <c r="C1050" t="n">
         <v>0.152174</v>
@@ -14077,7 +14077,7 @@
         </is>
       </c>
       <c r="B1051" t="n">
-        <v>0.117847</v>
+        <v>0.117447</v>
       </c>
       <c r="C1051" t="n">
         <v>0.149457</v>
@@ -14090,7 +14090,7 @@
         </is>
       </c>
       <c r="B1052" t="n">
-        <v>0.118508</v>
+        <v>0.118357</v>
       </c>
       <c r="C1052" t="n">
         <v>0.146739</v>
@@ -14103,7 +14103,7 @@
         </is>
       </c>
       <c r="B1053" t="n">
-        <v>0.119636</v>
+        <v>0.120138</v>
       </c>
       <c r="C1053" t="n">
         <v>0.144022</v>
@@ -14116,7 +14116,7 @@
         </is>
       </c>
       <c r="B1054" t="n">
-        <v>0.120136</v>
+        <v>0.120965</v>
       </c>
       <c r="C1054" t="n">
         <v>0.141304</v>
@@ -14129,7 +14129,7 @@
         </is>
       </c>
       <c r="B1055" t="n">
-        <v>0.120493</v>
+        <v>0.121211</v>
       </c>
       <c r="C1055" t="n">
         <v>0.138587</v>
@@ -14142,7 +14142,7 @@
         </is>
       </c>
       <c r="B1056" t="n">
-        <v>0.1206</v>
+        <v>0.121753</v>
       </c>
       <c r="C1056" t="n">
         <v>0.13587</v>
@@ -14155,7 +14155,7 @@
         </is>
       </c>
       <c r="B1057" t="n">
-        <v>0.1219</v>
+        <v>0.122888</v>
       </c>
       <c r="C1057" t="n">
         <v>0.133152</v>
@@ -14168,7 +14168,7 @@
         </is>
       </c>
       <c r="B1058" t="n">
-        <v>0.121947</v>
+        <v>0.122907</v>
       </c>
       <c r="C1058" t="n">
         <v>0.130435</v>
@@ -14181,7 +14181,7 @@
         </is>
       </c>
       <c r="B1059" t="n">
-        <v>0.123029</v>
+        <v>0.123192</v>
       </c>
       <c r="C1059" t="n">
         <v>0.127717</v>
@@ -14194,7 +14194,7 @@
         </is>
       </c>
       <c r="B1060" t="n">
-        <v>0.125669</v>
+        <v>0.124727</v>
       </c>
       <c r="C1060" t="n">
         <v>0.125</v>
@@ -14207,7 +14207,7 @@
         </is>
       </c>
       <c r="B1061" t="n">
-        <v>0.126971</v>
+        <v>0.124946</v>
       </c>
       <c r="C1061" t="n">
         <v>0.122283</v>
@@ -14220,7 +14220,7 @@
         </is>
       </c>
       <c r="B1062" t="n">
-        <v>0.127703</v>
+        <v>0.126033</v>
       </c>
       <c r="C1062" t="n">
         <v>0.119565</v>
@@ -14233,7 +14233,7 @@
         </is>
       </c>
       <c r="B1063" t="n">
-        <v>0.127869</v>
+        <v>0.127874</v>
       </c>
       <c r="C1063" t="n">
         <v>0.116848</v>
@@ -14246,7 +14246,7 @@
         </is>
       </c>
       <c r="B1064" t="n">
-        <v>0.127939</v>
+        <v>0.129215</v>
       </c>
       <c r="C1064" t="n">
         <v>0.11413</v>
@@ -14259,7 +14259,7 @@
         </is>
       </c>
       <c r="B1065" t="n">
-        <v>0.128171</v>
+        <v>0.129638</v>
       </c>
       <c r="C1065" t="n">
         <v>0.111413</v>
@@ -14272,7 +14272,7 @@
         </is>
       </c>
       <c r="B1066" t="n">
-        <v>0.130472</v>
+        <v>0.130967</v>
       </c>
       <c r="C1066" t="n">
         <v>0.108696</v>
@@ -14285,7 +14285,7 @@
         </is>
       </c>
       <c r="B1067" t="n">
-        <v>0.130694</v>
+        <v>0.131204</v>
       </c>
       <c r="C1067" t="n">
         <v>0.105978</v>
@@ -14298,7 +14298,7 @@
         </is>
       </c>
       <c r="B1068" t="n">
-        <v>0.131674</v>
+        <v>0.131358</v>
       </c>
       <c r="C1068" t="n">
         <v>0.103261</v>
@@ -14311,7 +14311,7 @@
         </is>
       </c>
       <c r="B1069" t="n">
-        <v>0.132246</v>
+        <v>0.132054</v>
       </c>
       <c r="C1069" t="n">
         <v>0.100543</v>
@@ -14324,7 +14324,7 @@
         </is>
       </c>
       <c r="B1070" t="n">
-        <v>0.133804</v>
+        <v>0.133063</v>
       </c>
       <c r="C1070" t="n">
         <v>0.097826</v>
@@ -14337,7 +14337,7 @@
         </is>
       </c>
       <c r="B1071" t="n">
-        <v>0.134885</v>
+        <v>0.133636</v>
       </c>
       <c r="C1071" t="n">
         <v>0.095109</v>
@@ -14350,7 +14350,7 @@
         </is>
       </c>
       <c r="B1072" t="n">
-        <v>0.141771</v>
+        <v>0.142179</v>
       </c>
       <c r="C1072" t="n">
         <v>0.092391</v>
@@ -14363,7 +14363,7 @@
         </is>
       </c>
       <c r="B1073" t="n">
-        <v>0.143094</v>
+        <v>0.143172</v>
       </c>
       <c r="C1073" t="n">
         <v>0.089674</v>
@@ -14376,7 +14376,7 @@
         </is>
       </c>
       <c r="B1074" t="n">
-        <v>0.143163</v>
+        <v>0.144373</v>
       </c>
       <c r="C1074" t="n">
         <v>0.08695700000000001</v>
@@ -14389,7 +14389,7 @@
         </is>
       </c>
       <c r="B1075" t="n">
-        <v>0.147011</v>
+        <v>0.146771</v>
       </c>
       <c r="C1075" t="n">
         <v>0.08423899999999999</v>
@@ -14402,7 +14402,7 @@
         </is>
       </c>
       <c r="B1076" t="n">
-        <v>0.149861</v>
+        <v>0.150042</v>
       </c>
       <c r="C1076" t="n">
         <v>0.081522</v>
@@ -14415,7 +14415,7 @@
         </is>
       </c>
       <c r="B1077" t="n">
-        <v>0.150572</v>
+        <v>0.15208</v>
       </c>
       <c r="C1077" t="n">
         <v>0.078804</v>
@@ -14428,7 +14428,7 @@
         </is>
       </c>
       <c r="B1078" t="n">
-        <v>0.153283</v>
+        <v>0.152329</v>
       </c>
       <c r="C1078" t="n">
         <v>0.076087</v>
@@ -14441,7 +14441,7 @@
         </is>
       </c>
       <c r="B1079" t="n">
-        <v>0.156261</v>
+        <v>0.156939</v>
       </c>
       <c r="C1079" t="n">
         <v>0.07337</v>
@@ -14454,7 +14454,7 @@
         </is>
       </c>
       <c r="B1080" t="n">
-        <v>0.157233</v>
+        <v>0.158515</v>
       </c>
       <c r="C1080" t="n">
         <v>0.07065200000000001</v>
@@ -14467,7 +14467,7 @@
         </is>
       </c>
       <c r="B1081" t="n">
-        <v>0.164461</v>
+        <v>0.16548</v>
       </c>
       <c r="C1081" t="n">
         <v>0.067935</v>
@@ -14480,7 +14480,7 @@
         </is>
       </c>
       <c r="B1082" t="n">
-        <v>0.164697</v>
+        <v>0.166298</v>
       </c>
       <c r="C1082" t="n">
         <v>0.065217</v>
@@ -14493,7 +14493,7 @@
         </is>
       </c>
       <c r="B1083" t="n">
-        <v>0.165461</v>
+        <v>0.166483</v>
       </c>
       <c r="C1083" t="n">
         <v>0.0625</v>
@@ -14506,7 +14506,7 @@
         </is>
       </c>
       <c r="B1084" t="n">
-        <v>0.167289</v>
+        <v>0.169156</v>
       </c>
       <c r="C1084" t="n">
         <v>0.059783</v>
@@ -14519,7 +14519,7 @@
         </is>
       </c>
       <c r="B1085" t="n">
-        <v>0.169966</v>
+        <v>0.170889</v>
       </c>
       <c r="C1085" t="n">
         <v>0.057065</v>
@@ -14532,7 +14532,7 @@
         </is>
       </c>
       <c r="B1086" t="n">
-        <v>0.1715</v>
+        <v>0.171827</v>
       </c>
       <c r="C1086" t="n">
         <v>0.054348</v>
@@ -14545,7 +14545,7 @@
         </is>
       </c>
       <c r="B1087" t="n">
-        <v>0.171925</v>
+        <v>0.173807</v>
       </c>
       <c r="C1087" t="n">
         <v>0.05163</v>
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="B1088" t="n">
-        <v>0.180602</v>
+        <v>0.180126</v>
       </c>
       <c r="C1088" t="n">
         <v>0.048913</v>
@@ -14571,7 +14571,7 @@
         </is>
       </c>
       <c r="B1089" t="n">
-        <v>0.18145</v>
+        <v>0.182651</v>
       </c>
       <c r="C1089" t="n">
         <v>0.046196</v>
@@ -14584,7 +14584,7 @@
         </is>
       </c>
       <c r="B1090" t="n">
-        <v>0.184889</v>
+        <v>0.182911</v>
       </c>
       <c r="C1090" t="n">
         <v>0.043478</v>
@@ -14597,7 +14597,7 @@
         </is>
       </c>
       <c r="B1091" t="n">
-        <v>0.19306</v>
+        <v>0.193335</v>
       </c>
       <c r="C1091" t="n">
         <v>0.040761</v>
@@ -14610,7 +14610,7 @@
         </is>
       </c>
       <c r="B1092" t="n">
-        <v>0.193153</v>
+        <v>0.195238</v>
       </c>
       <c r="C1092" t="n">
         <v>0.038043</v>
@@ -14623,7 +14623,7 @@
         </is>
       </c>
       <c r="B1093" t="n">
-        <v>0.198393</v>
+        <v>0.195286</v>
       </c>
       <c r="C1093" t="n">
         <v>0.035326</v>
@@ -14636,7 +14636,7 @@
         </is>
       </c>
       <c r="B1094" t="n">
-        <v>0.211021</v>
+        <v>0.212126</v>
       </c>
       <c r="C1094" t="n">
         <v>0.032609</v>
@@ -14649,7 +14649,7 @@
         </is>
       </c>
       <c r="B1095" t="n">
-        <v>0.215191</v>
+        <v>0.217414</v>
       </c>
       <c r="C1095" t="n">
         <v>0.029891</v>
@@ -14662,7 +14662,7 @@
         </is>
       </c>
       <c r="B1096" t="n">
-        <v>0.223136</v>
+        <v>0.22569</v>
       </c>
       <c r="C1096" t="n">
         <v>0.027174</v>
@@ -14675,7 +14675,7 @@
         </is>
       </c>
       <c r="B1097" t="n">
-        <v>0.223645</v>
+        <v>0.22603</v>
       </c>
       <c r="C1097" t="n">
         <v>0.024457</v>
@@ -14688,7 +14688,7 @@
         </is>
       </c>
       <c r="B1098" t="n">
-        <v>0.225852</v>
+        <v>0.228438</v>
       </c>
       <c r="C1098" t="n">
         <v>0.021739</v>
@@ -14701,7 +14701,7 @@
         </is>
       </c>
       <c r="B1099" t="n">
-        <v>0.241226</v>
+        <v>0.238965</v>
       </c>
       <c r="C1099" t="n">
         <v>0.019022</v>
@@ -14714,7 +14714,7 @@
         </is>
       </c>
       <c r="B1100" t="n">
-        <v>0.242919</v>
+        <v>0.245219</v>
       </c>
       <c r="C1100" t="n">
         <v>0.016304</v>
@@ -14727,7 +14727,7 @@
         </is>
       </c>
       <c r="B1101" t="n">
-        <v>0.25059</v>
+        <v>0.252624</v>
       </c>
       <c r="C1101" t="n">
         <v>0.013587</v>
@@ -14740,7 +14740,7 @@
         </is>
       </c>
       <c r="B1102" t="n">
-        <v>0.273041</v>
+        <v>0.273454</v>
       </c>
       <c r="C1102" t="n">
         <v>0.01087</v>
@@ -14753,7 +14753,7 @@
         </is>
       </c>
       <c r="B1103" t="n">
-        <v>0.285642</v>
+        <v>0.288865</v>
       </c>
       <c r="C1103" t="n">
         <v>0.008152</v>
@@ -14766,7 +14766,7 @@
         </is>
       </c>
       <c r="B1104" t="n">
-        <v>0.313915</v>
+        <v>0.316073</v>
       </c>
       <c r="C1104" t="n">
         <v>0.005435</v>
@@ -14779,7 +14779,7 @@
         </is>
       </c>
       <c r="B1105" t="n">
-        <v>0.447354</v>
+        <v>0.451438</v>
       </c>
       <c r="C1105" t="n">
         <v>0.002717</v>

--- a/vignettes/vignette-2/tail_exceedance_plot_data.xlsx
+++ b/vignettes/vignette-2/tail_exceedance_plot_data.xlsx
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.008377000000000001</v>
+        <v>0.008333999999999999</v>
       </c>
       <c r="C28" t="n">
         <v>0.929348</v>
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.008593999999999999</v>
+        <v>0.008377000000000001</v>
       </c>
       <c r="C29" t="n">
         <v>0.92663</v>
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.009165</v>
+        <v>0.008593999999999999</v>
       </c>
       <c r="C30" t="n">
         <v>0.923913</v>
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.009428000000000001</v>
+        <v>0.009165</v>
       </c>
       <c r="C31" t="n">
         <v>0.921196</v>
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.009578</v>
+        <v>0.009428000000000001</v>
       </c>
       <c r="C32" t="n">
         <v>0.918478</v>
@@ -843,7 +843,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.009774</v>
+        <v>0.009578</v>
       </c>
       <c r="C33" t="n">
         <v>0.915761</v>
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.009811</v>
+        <v>0.009774</v>
       </c>
       <c r="C34" t="n">
         <v>0.913043</v>
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.010226</v>
+        <v>0.009811</v>
       </c>
       <c r="C35" t="n">
         <v>0.910326</v>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.010518</v>
+        <v>0.010226</v>
       </c>
       <c r="C36" t="n">
         <v>0.907609</v>
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.010943</v>
+        <v>0.010518</v>
       </c>
       <c r="C37" t="n">
         <v>0.904891</v>
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.011156</v>
+        <v>0.010943</v>
       </c>
       <c r="C38" t="n">
         <v>0.902174</v>
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.011326</v>
+        <v>0.011156</v>
       </c>
       <c r="C39" t="n">
         <v>0.899457</v>
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.01145</v>
+        <v>0.011326</v>
       </c>
       <c r="C40" t="n">
         <v>0.896739</v>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.012035</v>
+        <v>0.01145</v>
       </c>
       <c r="C41" t="n">
         <v>0.894022</v>
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.012747</v>
+        <v>0.012035</v>
       </c>
       <c r="C42" t="n">
         <v>0.891304</v>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.012918</v>
+        <v>0.012747</v>
       </c>
       <c r="C43" t="n">
         <v>0.888587</v>
@@ -986,7 +986,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.013202</v>
+        <v>0.012918</v>
       </c>
       <c r="C44" t="n">
         <v>0.88587</v>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.013714</v>
+        <v>0.013202</v>
       </c>
       <c r="C45" t="n">
         <v>0.883152</v>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.01393</v>
+        <v>0.013714</v>
       </c>
       <c r="C46" t="n">
         <v>0.880435</v>
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.013971</v>
+        <v>0.01393</v>
       </c>
       <c r="C47" t="n">
         <v>0.877717</v>
@@ -1038,7 +1038,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.014018</v>
+        <v>0.013971</v>
       </c>
       <c r="C48" t="n">
         <v>0.875</v>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.01417</v>
+        <v>0.014018</v>
       </c>
       <c r="C49" t="n">
         <v>0.872283</v>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.014481</v>
+        <v>0.01417</v>
       </c>
       <c r="C50" t="n">
         <v>0.869565</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.014731</v>
+        <v>0.014481</v>
       </c>
       <c r="C51" t="n">
         <v>0.866848</v>
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.014841</v>
+        <v>0.014731</v>
       </c>
       <c r="C52" t="n">
         <v>0.86413</v>
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.01486</v>
+        <v>0.014841</v>
       </c>
       <c r="C53" t="n">
         <v>0.861413</v>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.015041</v>
+        <v>0.01486</v>
       </c>
       <c r="C54" t="n">
         <v>0.858696</v>
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.015107</v>
+        <v>0.015041</v>
       </c>
       <c r="C55" t="n">
         <v>0.855978</v>
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.015553</v>
+        <v>0.015107</v>
       </c>
       <c r="C57" t="n">
         <v>0.850543</v>
@@ -1168,7 +1168,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.016031</v>
+        <v>0.015553</v>
       </c>
       <c r="C58" t="n">
         <v>0.847826</v>
@@ -1181,7 +1181,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.016343</v>
+        <v>0.016031</v>
       </c>
       <c r="C59" t="n">
         <v>0.845109</v>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.016545</v>
+        <v>0.016343</v>
       </c>
       <c r="C60" t="n">
         <v>0.842391</v>
@@ -1207,7 +1207,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.017135</v>
+        <v>0.016545</v>
       </c>
       <c r="C61" t="n">
         <v>0.839674</v>
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.017276</v>
+        <v>0.017135</v>
       </c>
       <c r="C62" t="n">
         <v>0.836957</v>
@@ -1233,7 +1233,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.017621</v>
+        <v>0.017276</v>
       </c>
       <c r="C63" t="n">
         <v>0.834239</v>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.017975</v>
+        <v>0.017621</v>
       </c>
       <c r="C64" t="n">
         <v>0.831522</v>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.018505</v>
+        <v>0.017975</v>
       </c>
       <c r="C65" t="n">
         <v>0.828804</v>
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.018757</v>
+        <v>0.018505</v>
       </c>
       <c r="C66" t="n">
         <v>0.826087</v>
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.018801</v>
+        <v>0.018757</v>
       </c>
       <c r="C67" t="n">
         <v>0.82337</v>
@@ -1298,7 +1298,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.018847</v>
+        <v>0.018801</v>
       </c>
       <c r="C68" t="n">
         <v>0.820652</v>
@@ -1311,7 +1311,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.018931</v>
+        <v>0.018847</v>
       </c>
       <c r="C69" t="n">
         <v>0.817935</v>
@@ -1324,7 +1324,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.019288</v>
+        <v>0.018931</v>
       </c>
       <c r="C70" t="n">
         <v>0.815217</v>
@@ -1337,7 +1337,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.019352</v>
+        <v>0.019288</v>
       </c>
       <c r="C71" t="n">
         <v>0.8125</v>
@@ -1350,7 +1350,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.01962</v>
+        <v>0.019352</v>
       </c>
       <c r="C72" t="n">
         <v>0.809783</v>
@@ -1363,7 +1363,7 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.019953</v>
+        <v>0.01962</v>
       </c>
       <c r="C73" t="n">
         <v>0.807065</v>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.020186</v>
+        <v>0.019953</v>
       </c>
       <c r="C74" t="n">
         <v>0.804348</v>
@@ -1389,7 +1389,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.020393</v>
+        <v>0.020186</v>
       </c>
       <c r="C75" t="n">
         <v>0.80163</v>
@@ -1402,7 +1402,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.02048</v>
+        <v>0.020393</v>
       </c>
       <c r="C76" t="n">
         <v>0.798913</v>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.021572</v>
+        <v>0.02048</v>
       </c>
       <c r="C77" t="n">
         <v>0.796196</v>
@@ -1428,7 +1428,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.021604</v>
+        <v>0.021572</v>
       </c>
       <c r="C78" t="n">
         <v>0.793478</v>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.021912</v>
+        <v>0.021604</v>
       </c>
       <c r="C79" t="n">
         <v>0.790761</v>
@@ -1454,7 +1454,7 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.021918</v>
+        <v>0.021912</v>
       </c>
       <c r="C80" t="n">
         <v>0.788043</v>
@@ -1467,7 +1467,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.021962</v>
+        <v>0.021918</v>
       </c>
       <c r="C81" t="n">
         <v>0.785326</v>
@@ -1480,7 +1480,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.022008</v>
+        <v>0.021962</v>
       </c>
       <c r="C82" t="n">
         <v>0.782609</v>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.022011</v>
+        <v>0.022008</v>
       </c>
       <c r="C83" t="n">
         <v>0.779891</v>
@@ -1506,7 +1506,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.022121</v>
+        <v>0.022011</v>
       </c>
       <c r="C84" t="n">
         <v>0.777174</v>
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.022299</v>
+        <v>0.022121</v>
       </c>
       <c r="C85" t="n">
         <v>0.774457</v>
@@ -1532,7 +1532,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.022324</v>
+        <v>0.022299</v>
       </c>
       <c r="C86" t="n">
         <v>0.771739</v>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.022543</v>
+        <v>0.022324</v>
       </c>
       <c r="C87" t="n">
         <v>0.769022</v>
@@ -1558,7 +1558,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.022891</v>
+        <v>0.022543</v>
       </c>
       <c r="C88" t="n">
         <v>0.766304</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.023483</v>
+        <v>0.022891</v>
       </c>
       <c r="C89" t="n">
         <v>0.763587</v>
@@ -1584,7 +1584,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.023843</v>
+        <v>0.023483</v>
       </c>
       <c r="C90" t="n">
         <v>0.76087</v>
@@ -1597,7 +1597,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.023991</v>
+        <v>0.023843</v>
       </c>
       <c r="C91" t="n">
         <v>0.758152</v>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.02408</v>
+        <v>0.023991</v>
       </c>
       <c r="C92" t="n">
         <v>0.755435</v>
@@ -1623,7 +1623,7 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.024413</v>
+        <v>0.02408</v>
       </c>
       <c r="C93" t="n">
         <v>0.752717</v>
@@ -1636,7 +1636,7 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.024896</v>
+        <v>0.024413</v>
       </c>
       <c r="C94" t="n">
         <v>0.75</v>
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.025327</v>
+        <v>0.024896</v>
       </c>
       <c r="C95" t="n">
         <v>0.747283</v>
@@ -1662,7 +1662,7 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.025416</v>
+        <v>0.025327</v>
       </c>
       <c r="C96" t="n">
         <v>0.744565</v>
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.025544</v>
+        <v>0.025416</v>
       </c>
       <c r="C97" t="n">
         <v>0.741848</v>
@@ -1688,7 +1688,7 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.025755</v>
+        <v>0.025544</v>
       </c>
       <c r="C98" t="n">
         <v>0.73913</v>
@@ -1701,7 +1701,7 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.026545</v>
+        <v>0.025755</v>
       </c>
       <c r="C99" t="n">
         <v>0.736413</v>
@@ -1714,7 +1714,7 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.027214</v>
+        <v>0.026545</v>
       </c>
       <c r="C100" t="n">
         <v>0.733696</v>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.027321</v>
+        <v>0.027214</v>
       </c>
       <c r="C101" t="n">
         <v>0.730978</v>
@@ -1740,7 +1740,7 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.027355</v>
+        <v>0.027321</v>
       </c>
       <c r="C102" t="n">
         <v>0.728261</v>
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.028098</v>
+        <v>0.027355</v>
       </c>
       <c r="C103" t="n">
         <v>0.725543</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.028186</v>
+        <v>0.028098</v>
       </c>
       <c r="C104" t="n">
         <v>0.722826</v>
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.028375</v>
+        <v>0.028186</v>
       </c>
       <c r="C105" t="n">
         <v>0.720109</v>
@@ -1792,7 +1792,7 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.029046</v>
+        <v>0.028375</v>
       </c>
       <c r="C106" t="n">
         <v>0.717391</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.029071</v>
+        <v>0.029046</v>
       </c>
       <c r="C107" t="n">
         <v>0.714674</v>
@@ -1818,7 +1818,7 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.029588</v>
+        <v>0.029071</v>
       </c>
       <c r="C108" t="n">
         <v>0.711957</v>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.029854</v>
+        <v>0.029588</v>
       </c>
       <c r="C109" t="n">
         <v>0.709239</v>
@@ -1844,7 +1844,7 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.030158</v>
+        <v>0.029854</v>
       </c>
       <c r="C110" t="n">
         <v>0.706522</v>
@@ -1857,7 +1857,7 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.030201</v>
+        <v>0.030158</v>
       </c>
       <c r="C111" t="n">
         <v>0.703804</v>
@@ -1870,7 +1870,7 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.03027</v>
+        <v>0.030201</v>
       </c>
       <c r="C112" t="n">
         <v>0.701087</v>
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.030697</v>
+        <v>0.03027</v>
       </c>
       <c r="C113" t="n">
         <v>0.69837</v>
@@ -1896,7 +1896,7 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.030903</v>
+        <v>0.030697</v>
       </c>
       <c r="C114" t="n">
         <v>0.695652</v>
@@ -1909,7 +1909,7 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.031116</v>
+        <v>0.030903</v>
       </c>
       <c r="C115" t="n">
         <v>0.692935</v>
@@ -1922,7 +1922,7 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.031127</v>
+        <v>0.031116</v>
       </c>
       <c r="C116" t="n">
         <v>0.690217</v>
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.031327</v>
+        <v>0.031127</v>
       </c>
       <c r="C117" t="n">
         <v>0.6875</v>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.031556</v>
+        <v>0.031327</v>
       </c>
       <c r="C118" t="n">
         <v>0.684783</v>
@@ -1961,7 +1961,7 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.031969</v>
+        <v>0.031556</v>
       </c>
       <c r="C119" t="n">
         <v>0.682065</v>
@@ -1974,7 +1974,7 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.032545</v>
+        <v>0.031969</v>
       </c>
       <c r="C120" t="n">
         <v>0.679348</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.032827</v>
+        <v>0.032545</v>
       </c>
       <c r="C121" t="n">
         <v>0.67663</v>
@@ -2000,7 +2000,7 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.033481</v>
+        <v>0.032827</v>
       </c>
       <c r="C122" t="n">
         <v>0.673913</v>
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.033774</v>
+        <v>0.033481</v>
       </c>
       <c r="C123" t="n">
         <v>0.671196</v>
@@ -2026,7 +2026,7 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.033884</v>
+        <v>0.033774</v>
       </c>
       <c r="C124" t="n">
         <v>0.668478</v>
@@ -2039,7 +2039,7 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.034047</v>
+        <v>0.033884</v>
       </c>
       <c r="C125" t="n">
         <v>0.665761</v>
@@ -2052,7 +2052,7 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.034274</v>
+        <v>0.034047</v>
       </c>
       <c r="C126" t="n">
         <v>0.663043</v>
@@ -2065,7 +2065,7 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.034573</v>
+        <v>0.034274</v>
       </c>
       <c r="C127" t="n">
         <v>0.660326</v>
@@ -2078,7 +2078,7 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.035039</v>
+        <v>0.034573</v>
       </c>
       <c r="C128" t="n">
         <v>0.657609</v>
@@ -2091,7 +2091,7 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.035117</v>
+        <v>0.035039</v>
       </c>
       <c r="C129" t="n">
         <v>0.654891</v>
@@ -2104,7 +2104,7 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.035159</v>
+        <v>0.035117</v>
       </c>
       <c r="C130" t="n">
         <v>0.652174</v>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.035374</v>
+        <v>0.035159</v>
       </c>
       <c r="C131" t="n">
         <v>0.649457</v>
@@ -2130,7 +2130,7 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.035654</v>
+        <v>0.035374</v>
       </c>
       <c r="C132" t="n">
         <v>0.646739</v>
@@ -2143,7 +2143,7 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.036</v>
+        <v>0.035654</v>
       </c>
       <c r="C133" t="n">
         <v>0.644022</v>
@@ -2156,7 +2156,7 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.036242</v>
+        <v>0.036</v>
       </c>
       <c r="C134" t="n">
         <v>0.641304</v>
@@ -2169,7 +2169,7 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.037307</v>
+        <v>0.036242</v>
       </c>
       <c r="C135" t="n">
         <v>0.638587</v>
@@ -2182,7 +2182,7 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.037805</v>
+        <v>0.037156</v>
       </c>
       <c r="C136" t="n">
         <v>0.63587</v>
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.03815</v>
+        <v>0.037307</v>
       </c>
       <c r="C137" t="n">
         <v>0.633152</v>
@@ -2208,7 +2208,7 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.038316</v>
+        <v>0.037805</v>
       </c>
       <c r="C138" t="n">
         <v>0.630435</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.03876</v>
+        <v>0.038316</v>
       </c>
       <c r="C139" t="n">
         <v>0.627717</v>
@@ -2234,7 +2234,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.039595</v>
+        <v>0.03876</v>
       </c>
       <c r="C140" t="n">
         <v>0.625</v>
@@ -2247,7 +2247,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.03982</v>
+        <v>0.039595</v>
       </c>
       <c r="C141" t="n">
         <v>0.622283</v>
@@ -2260,7 +2260,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.040867</v>
+        <v>0.03982</v>
       </c>
       <c r="C142" t="n">
         <v>0.619565</v>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.040915</v>
+        <v>0.040867</v>
       </c>
       <c r="C143" t="n">
         <v>0.616848</v>
@@ -2286,7 +2286,7 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.040931</v>
+        <v>0.040915</v>
       </c>
       <c r="C144" t="n">
         <v>0.61413</v>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.040948</v>
+        <v>0.040931</v>
       </c>
       <c r="C145" t="n">
         <v>0.611413</v>
@@ -2312,7 +2312,7 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.041019</v>
+        <v>0.040948</v>
       </c>
       <c r="C146" t="n">
         <v>0.608696</v>
@@ -2325,7 +2325,7 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.041132</v>
+        <v>0.041019</v>
       </c>
       <c r="C147" t="n">
         <v>0.605978</v>
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.041331</v>
+        <v>0.041132</v>
       </c>
       <c r="C148" t="n">
         <v>0.603261</v>
@@ -2351,7 +2351,7 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.041359</v>
+        <v>0.041331</v>
       </c>
       <c r="C149" t="n">
         <v>0.600543</v>
@@ -2793,7 +2793,7 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>0.054595</v>
+        <v>0.05496</v>
       </c>
       <c r="C183" t="n">
         <v>0.508152</v>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>0.05496</v>
+        <v>0.0555</v>
       </c>
       <c r="C184" t="n">
         <v>0.505435</v>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>0.0555</v>
+        <v>0.055621</v>
       </c>
       <c r="C185" t="n">
         <v>0.502717</v>
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>0.055621</v>
+        <v>0.055736</v>
       </c>
       <c r="C186" t="n">
         <v>0.5</v>
@@ -2845,7 +2845,7 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>0.055736</v>
+        <v>0.056242</v>
       </c>
       <c r="C187" t="n">
         <v>0.497283</v>
@@ -2858,7 +2858,7 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>0.056242</v>
+        <v>0.056433</v>
       </c>
       <c r="C188" t="n">
         <v>0.494565</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>0.056433</v>
+        <v>0.056487</v>
       </c>
       <c r="C189" t="n">
         <v>0.491848</v>
@@ -2884,7 +2884,7 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>0.056487</v>
+        <v>0.056702</v>
       </c>
       <c r="C190" t="n">
         <v>0.48913</v>
@@ -2897,7 +2897,7 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>0.056702</v>
+        <v>0.056785</v>
       </c>
       <c r="C191" t="n">
         <v>0.486413</v>
@@ -2910,7 +2910,7 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>0.056785</v>
+        <v>0.05854</v>
       </c>
       <c r="C192" t="n">
         <v>0.483696</v>
@@ -2923,7 +2923,7 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>0.05854</v>
+        <v>0.058745</v>
       </c>
       <c r="C193" t="n">
         <v>0.480978</v>
@@ -2936,7 +2936,7 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>0.058745</v>
+        <v>0.058836</v>
       </c>
       <c r="C194" t="n">
         <v>0.478261</v>
@@ -2949,7 +2949,7 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>0.058836</v>
+        <v>0.059279</v>
       </c>
       <c r="C195" t="n">
         <v>0.475543</v>
@@ -2962,7 +2962,7 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>0.059279</v>
+        <v>0.059367</v>
       </c>
       <c r="C196" t="n">
         <v>0.472826</v>
@@ -2975,7 +2975,7 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>0.059367</v>
+        <v>0.059553</v>
       </c>
       <c r="C197" t="n">
         <v>0.470109</v>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>0.059553</v>
+        <v>0.059579</v>
       </c>
       <c r="C198" t="n">
         <v>0.467391</v>
@@ -3001,7 +3001,7 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>0.059579</v>
+        <v>0.060111</v>
       </c>
       <c r="C199" t="n">
         <v>0.464674</v>
@@ -3014,7 +3014,7 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>0.060111</v>
+        <v>0.060827</v>
       </c>
       <c r="C200" t="n">
         <v>0.461957</v>
@@ -3027,7 +3027,7 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>0.060827</v>
+        <v>0.060882</v>
       </c>
       <c r="C201" t="n">
         <v>0.459239</v>
@@ -3040,7 +3040,7 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>0.060882</v>
+        <v>0.061437</v>
       </c>
       <c r="C202" t="n">
         <v>0.456522</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>0.061437</v>
+        <v>0.061712</v>
       </c>
       <c r="C203" t="n">
         <v>0.453804</v>
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>0.061712</v>
+        <v>0.061784</v>
       </c>
       <c r="C204" t="n">
         <v>0.451087</v>
@@ -3079,7 +3079,7 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>0.061784</v>
+        <v>0.06179</v>
       </c>
       <c r="C205" t="n">
         <v>0.44837</v>
@@ -3092,7 +3092,7 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>0.06179</v>
+        <v>0.061969</v>
       </c>
       <c r="C206" t="n">
         <v>0.445652</v>
@@ -3105,7 +3105,7 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>0.061969</v>
+        <v>0.062129</v>
       </c>
       <c r="C207" t="n">
         <v>0.442935</v>
@@ -3118,7 +3118,7 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>0.062129</v>
+        <v>0.062168</v>
       </c>
       <c r="C208" t="n">
         <v>0.440217</v>
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>0.062168</v>
+        <v>0.062246</v>
       </c>
       <c r="C209" t="n">
         <v>0.4375</v>
@@ -3144,7 +3144,7 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>0.062246</v>
+        <v>0.06263299999999999</v>
       </c>
       <c r="C210" t="n">
         <v>0.434783</v>
@@ -3157,7 +3157,7 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>0.06263299999999999</v>
+        <v>0.062844</v>
       </c>
       <c r="C211" t="n">
         <v>0.432065</v>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>0.062844</v>
+        <v>0.063808</v>
       </c>
       <c r="C212" t="n">
         <v>0.429348</v>
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>0.063808</v>
+        <v>0.064842</v>
       </c>
       <c r="C213" t="n">
         <v>0.42663</v>
@@ -3196,7 +3196,7 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>0.06464300000000001</v>
+        <v>0.06555900000000001</v>
       </c>
       <c r="C214" t="n">
         <v>0.423913</v>
@@ -3209,7 +3209,7 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>0.064842</v>
+        <v>0.067176</v>
       </c>
       <c r="C215" t="n">
         <v>0.421196</v>
@@ -3222,7 +3222,7 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>0.06555900000000001</v>
+        <v>0.06736399999999999</v>
       </c>
       <c r="C216" t="n">
         <v>0.418478</v>
@@ -3235,7 +3235,7 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>0.067176</v>
+        <v>0.067375</v>
       </c>
       <c r="C217" t="n">
         <v>0.415761</v>
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>0.06736399999999999</v>
+        <v>0.067555</v>
       </c>
       <c r="C218" t="n">
         <v>0.413043</v>
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>0.067375</v>
+        <v>0.067604</v>
       </c>
       <c r="C219" t="n">
         <v>0.410326</v>
@@ -3274,7 +3274,7 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>0.067555</v>
+        <v>0.067644</v>
       </c>
       <c r="C220" t="n">
         <v>0.407609</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="B221" t="n">
-        <v>0.067604</v>
+        <v>0.068111</v>
       </c>
       <c r="C221" t="n">
         <v>0.404891</v>
@@ -3300,7 +3300,7 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>0.067644</v>
+        <v>0.068538</v>
       </c>
       <c r="C222" t="n">
         <v>0.402174</v>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>0.068111</v>
+        <v>0.068601</v>
       </c>
       <c r="C223" t="n">
         <v>0.399457</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>0.068538</v>
+        <v>0.068939</v>
       </c>
       <c r="C224" t="n">
         <v>0.396739</v>
@@ -3339,7 +3339,7 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>0.068601</v>
+        <v>0.06909</v>
       </c>
       <c r="C225" t="n">
         <v>0.394022</v>
@@ -3352,7 +3352,7 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>0.068939</v>
+        <v>0.069253</v>
       </c>
       <c r="C226" t="n">
         <v>0.391304</v>
@@ -3365,7 +3365,7 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>0.06909</v>
+        <v>0.070214</v>
       </c>
       <c r="C227" t="n">
         <v>0.388587</v>
@@ -3378,7 +3378,7 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>0.069253</v>
+        <v>0.070659</v>
       </c>
       <c r="C228" t="n">
         <v>0.38587</v>
@@ -3391,7 +3391,7 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>0.070214</v>
+        <v>0.072684</v>
       </c>
       <c r="C229" t="n">
         <v>0.383152</v>
@@ -3404,7 +3404,7 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>0.070659</v>
+        <v>0.072744</v>
       </c>
       <c r="C230" t="n">
         <v>0.380435</v>
@@ -3417,7 +3417,7 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>0.072684</v>
+        <v>0.07295599999999999</v>
       </c>
       <c r="C231" t="n">
         <v>0.377717</v>
@@ -3430,7 +3430,7 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>0.072744</v>
+        <v>0.07331</v>
       </c>
       <c r="C232" t="n">
         <v>0.375</v>
@@ -3443,7 +3443,7 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>0.07295599999999999</v>
+        <v>0.07380299999999999</v>
       </c>
       <c r="C233" t="n">
         <v>0.372283</v>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>0.07331</v>
+        <v>0.07424799999999999</v>
       </c>
       <c r="C234" t="n">
         <v>0.369565</v>
@@ -3469,7 +3469,7 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>0.07380299999999999</v>
+        <v>0.07437100000000001</v>
       </c>
       <c r="C235" t="n">
         <v>0.366848</v>
@@ -3482,7 +3482,7 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>0.07424799999999999</v>
+        <v>0.075854</v>
       </c>
       <c r="C236" t="n">
         <v>0.36413</v>
@@ -3495,7 +3495,7 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>0.07437100000000001</v>
+        <v>0.075876</v>
       </c>
       <c r="C237" t="n">
         <v>0.361413</v>
@@ -3508,7 +3508,7 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>0.075854</v>
+        <v>0.076543</v>
       </c>
       <c r="C238" t="n">
         <v>0.358696</v>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>0.075876</v>
+        <v>0.07708</v>
       </c>
       <c r="C239" t="n">
         <v>0.355978</v>
@@ -3534,7 +3534,7 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>0.076543</v>
+        <v>0.077863</v>
       </c>
       <c r="C240" t="n">
         <v>0.353261</v>
@@ -3547,7 +3547,7 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>0.07708</v>
+        <v>0.077912</v>
       </c>
       <c r="C241" t="n">
         <v>0.350543</v>
@@ -3560,7 +3560,7 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>0.077863</v>
+        <v>0.078084</v>
       </c>
       <c r="C242" t="n">
         <v>0.347826</v>
@@ -3573,7 +3573,7 @@
         </is>
       </c>
       <c r="B243" t="n">
-        <v>0.077912</v>
+        <v>0.07843899999999999</v>
       </c>
       <c r="C243" t="n">
         <v>0.345109</v>
@@ -3586,7 +3586,7 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>0.078084</v>
+        <v>0.07921499999999999</v>
       </c>
       <c r="C244" t="n">
         <v>0.342391</v>
@@ -3599,7 +3599,7 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>0.07843899999999999</v>
+        <v>0.080791</v>
       </c>
       <c r="C245" t="n">
         <v>0.339674</v>
@@ -3612,7 +3612,7 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>0.07921499999999999</v>
+        <v>0.08092199999999999</v>
       </c>
       <c r="C246" t="n">
         <v>0.336957</v>
@@ -3625,7 +3625,7 @@
         </is>
       </c>
       <c r="B247" t="n">
-        <v>0.08092199999999999</v>
+        <v>0.080995</v>
       </c>
       <c r="C247" t="n">
         <v>0.334239</v>
@@ -5250,7 +5250,7 @@
         </is>
       </c>
       <c r="B372" t="n">
-        <v>0.000299</v>
+        <v>0.0003</v>
       </c>
       <c r="C372" t="n">
         <v>0.994565</v>
@@ -5263,7 +5263,7 @@
         </is>
       </c>
       <c r="B373" t="n">
-        <v>0.000476</v>
+        <v>0.000477</v>
       </c>
       <c r="C373" t="n">
         <v>0.991848</v>
@@ -5276,7 +5276,7 @@
         </is>
       </c>
       <c r="B374" t="n">
-        <v>0.000972</v>
+        <v>0.000974</v>
       </c>
       <c r="C374" t="n">
         <v>0.98913</v>
@@ -5289,7 +5289,7 @@
         </is>
       </c>
       <c r="B375" t="n">
-        <v>0.001548</v>
+        <v>0.001557</v>
       </c>
       <c r="C375" t="n">
         <v>0.986413</v>
@@ -5302,7 +5302,7 @@
         </is>
       </c>
       <c r="B376" t="n">
-        <v>0.00181</v>
+        <v>0.001808</v>
       </c>
       <c r="C376" t="n">
         <v>0.983696</v>
@@ -5315,7 +5315,7 @@
         </is>
       </c>
       <c r="B377" t="n">
-        <v>0.001893</v>
+        <v>0.001902</v>
       </c>
       <c r="C377" t="n">
         <v>0.980978</v>
@@ -5328,7 +5328,7 @@
         </is>
       </c>
       <c r="B378" t="n">
-        <v>0.002068</v>
+        <v>0.002082</v>
       </c>
       <c r="C378" t="n">
         <v>0.978261</v>
@@ -5341,7 +5341,7 @@
         </is>
       </c>
       <c r="B379" t="n">
-        <v>0.002184</v>
+        <v>0.002196</v>
       </c>
       <c r="C379" t="n">
         <v>0.975543</v>
@@ -5354,7 +5354,7 @@
         </is>
       </c>
       <c r="B380" t="n">
-        <v>0.002764</v>
+        <v>0.002774</v>
       </c>
       <c r="C380" t="n">
         <v>0.972826</v>
@@ -5367,7 +5367,7 @@
         </is>
       </c>
       <c r="B381" t="n">
-        <v>0.00278</v>
+        <v>0.002797</v>
       </c>
       <c r="C381" t="n">
         <v>0.970109</v>
@@ -5380,7 +5380,7 @@
         </is>
       </c>
       <c r="B382" t="n">
-        <v>0.003006</v>
+        <v>0.003014</v>
       </c>
       <c r="C382" t="n">
         <v>0.967391</v>
@@ -5393,7 +5393,7 @@
         </is>
       </c>
       <c r="B383" t="n">
-        <v>0.003209</v>
+        <v>0.00323</v>
       </c>
       <c r="C383" t="n">
         <v>0.964674</v>
@@ -5406,7 +5406,7 @@
         </is>
       </c>
       <c r="B384" t="n">
-        <v>0.003947</v>
+        <v>0.003956</v>
       </c>
       <c r="C384" t="n">
         <v>0.961957</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="B385" t="n">
-        <v>0.004004</v>
+        <v>0.004015</v>
       </c>
       <c r="C385" t="n">
         <v>0.959239</v>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="B386" t="n">
-        <v>0.004434</v>
+        <v>0.004445</v>
       </c>
       <c r="C386" t="n">
         <v>0.956522</v>
@@ -5445,7 +5445,7 @@
         </is>
       </c>
       <c r="B387" t="n">
-        <v>0.004461</v>
+        <v>0.004493</v>
       </c>
       <c r="C387" t="n">
         <v>0.953804</v>
@@ -5458,7 +5458,7 @@
         </is>
       </c>
       <c r="B388" t="n">
-        <v>0.004494</v>
+        <v>0.004526</v>
       </c>
       <c r="C388" t="n">
         <v>0.951087</v>
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="B389" t="n">
-        <v>0.00452</v>
+        <v>0.004534</v>
       </c>
       <c r="C389" t="n">
         <v>0.94837</v>
@@ -5484,7 +5484,7 @@
         </is>
       </c>
       <c r="B390" t="n">
-        <v>0.004629</v>
+        <v>0.0046</v>
       </c>
       <c r="C390" t="n">
         <v>0.945652</v>
@@ -5497,7 +5497,7 @@
         </is>
       </c>
       <c r="B391" t="n">
-        <v>0.004698</v>
+        <v>0.004726</v>
       </c>
       <c r="C391" t="n">
         <v>0.942935</v>
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="B392" t="n">
-        <v>0.004803</v>
+        <v>0.004837</v>
       </c>
       <c r="C392" t="n">
         <v>0.940217</v>
@@ -5523,7 +5523,7 @@
         </is>
       </c>
       <c r="B393" t="n">
-        <v>0.004946</v>
+        <v>0.004943</v>
       </c>
       <c r="C393" t="n">
         <v>0.9375</v>
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c r="B394" t="n">
-        <v>0.004957</v>
+        <v>0.004978</v>
       </c>
       <c r="C394" t="n">
         <v>0.934783</v>
@@ -5549,7 +5549,7 @@
         </is>
       </c>
       <c r="B395" t="n">
-        <v>0.005563</v>
+        <v>0.005591</v>
       </c>
       <c r="C395" t="n">
         <v>0.932065</v>
@@ -5562,7 +5562,7 @@
         </is>
       </c>
       <c r="B396" t="n">
-        <v>0.005785</v>
+        <v>0.005809</v>
       </c>
       <c r="C396" t="n">
         <v>0.929348</v>
@@ -5575,7 +5575,7 @@
         </is>
       </c>
       <c r="B397" t="n">
-        <v>0.005871</v>
+        <v>0.005896</v>
       </c>
       <c r="C397" t="n">
         <v>0.92663</v>
@@ -5588,7 +5588,7 @@
         </is>
       </c>
       <c r="B398" t="n">
-        <v>0.006431</v>
+        <v>0.00645</v>
       </c>
       <c r="C398" t="n">
         <v>0.923913</v>
@@ -5601,7 +5601,7 @@
         </is>
       </c>
       <c r="B399" t="n">
-        <v>0.007194</v>
+        <v>0.007219</v>
       </c>
       <c r="C399" t="n">
         <v>0.921196</v>
@@ -5614,7 +5614,7 @@
         </is>
       </c>
       <c r="B400" t="n">
-        <v>0.007211</v>
+        <v>0.007257</v>
       </c>
       <c r="C400" t="n">
         <v>0.918478</v>
@@ -5627,7 +5627,7 @@
         </is>
       </c>
       <c r="B401" t="n">
-        <v>0.007473</v>
+        <v>0.007525</v>
       </c>
       <c r="C401" t="n">
         <v>0.915761</v>
@@ -5640,7 +5640,7 @@
         </is>
       </c>
       <c r="B402" t="n">
-        <v>0.007652</v>
+        <v>0.007683</v>
       </c>
       <c r="C402" t="n">
         <v>0.913043</v>
@@ -5653,7 +5653,7 @@
         </is>
       </c>
       <c r="B403" t="n">
-        <v>0.007837999999999999</v>
+        <v>0.007808</v>
       </c>
       <c r="C403" t="n">
         <v>0.910326</v>
@@ -5666,7 +5666,7 @@
         </is>
       </c>
       <c r="B404" t="n">
-        <v>0.007875</v>
+        <v>0.007905000000000001</v>
       </c>
       <c r="C404" t="n">
         <v>0.907609</v>
@@ -5679,7 +5679,7 @@
         </is>
       </c>
       <c r="B405" t="n">
-        <v>0.008102</v>
+        <v>0.008104999999999999</v>
       </c>
       <c r="C405" t="n">
         <v>0.904891</v>
@@ -5692,7 +5692,7 @@
         </is>
       </c>
       <c r="B406" t="n">
-        <v>0.008104999999999999</v>
+        <v>0.008158</v>
       </c>
       <c r="C406" t="n">
         <v>0.902174</v>
@@ -5705,7 +5705,7 @@
         </is>
       </c>
       <c r="B407" t="n">
-        <v>0.008227</v>
+        <v>0.00825</v>
       </c>
       <c r="C407" t="n">
         <v>0.899457</v>
@@ -5718,7 +5718,7 @@
         </is>
       </c>
       <c r="B408" t="n">
-        <v>0.008543</v>
+        <v>0.008508</v>
       </c>
       <c r="C408" t="n">
         <v>0.896739</v>
@@ -5731,7 +5731,7 @@
         </is>
       </c>
       <c r="B409" t="n">
-        <v>0.009031000000000001</v>
+        <v>0.008567</v>
       </c>
       <c r="C409" t="n">
         <v>0.894022</v>
@@ -5744,7 +5744,7 @@
         </is>
       </c>
       <c r="B410" t="n">
-        <v>0.009218</v>
+        <v>0.009086</v>
       </c>
       <c r="C410" t="n">
         <v>0.891304</v>
@@ -5757,7 +5757,7 @@
         </is>
       </c>
       <c r="B411" t="n">
-        <v>0.009231</v>
+        <v>0.009264</v>
       </c>
       <c r="C411" t="n">
         <v>0.888587</v>
@@ -5770,7 +5770,7 @@
         </is>
       </c>
       <c r="B412" t="n">
-        <v>0.009646999999999999</v>
+        <v>0.009294</v>
       </c>
       <c r="C412" t="n">
         <v>0.88587</v>
@@ -5783,7 +5783,7 @@
         </is>
       </c>
       <c r="B413" t="n">
-        <v>0.009812</v>
+        <v>0.009684999999999999</v>
       </c>
       <c r="C413" t="n">
         <v>0.883152</v>
@@ -5796,7 +5796,7 @@
         </is>
       </c>
       <c r="B414" t="n">
-        <v>0.009866</v>
+        <v>0.009830999999999999</v>
       </c>
       <c r="C414" t="n">
         <v>0.880435</v>
@@ -5809,7 +5809,7 @@
         </is>
       </c>
       <c r="B415" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.009845</v>
       </c>
       <c r="C415" t="n">
         <v>0.877717</v>
@@ -5822,7 +5822,7 @@
         </is>
       </c>
       <c r="B416" t="n">
-        <v>0.010434</v>
+        <v>0.009864</v>
       </c>
       <c r="C416" t="n">
         <v>0.875</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="B417" t="n">
-        <v>0.010532</v>
+        <v>0.010505</v>
       </c>
       <c r="C417" t="n">
         <v>0.872283</v>
@@ -5848,7 +5848,7 @@
         </is>
       </c>
       <c r="B418" t="n">
-        <v>0.010649</v>
+        <v>0.010511</v>
       </c>
       <c r="C418" t="n">
         <v>0.869565</v>
@@ -5861,7 +5861,7 @@
         </is>
       </c>
       <c r="B419" t="n">
-        <v>0.010927</v>
+        <v>0.010683</v>
       </c>
       <c r="C419" t="n">
         <v>0.866848</v>
@@ -5874,7 +5874,7 @@
         </is>
       </c>
       <c r="B420" t="n">
-        <v>0.010961</v>
+        <v>0.010954</v>
       </c>
       <c r="C420" t="n">
         <v>0.86413</v>
@@ -5887,7 +5887,7 @@
         </is>
       </c>
       <c r="B421" t="n">
-        <v>0.011057</v>
+        <v>0.010968</v>
       </c>
       <c r="C421" t="n">
         <v>0.861413</v>
@@ -5900,7 +5900,7 @@
         </is>
       </c>
       <c r="B422" t="n">
-        <v>0.011309</v>
+        <v>0.011078</v>
       </c>
       <c r="C422" t="n">
         <v>0.858696</v>
@@ -5913,7 +5913,7 @@
         </is>
       </c>
       <c r="B423" t="n">
-        <v>0.011435</v>
+        <v>0.011343</v>
       </c>
       <c r="C423" t="n">
         <v>0.855978</v>
@@ -5926,7 +5926,7 @@
         </is>
       </c>
       <c r="B424" t="n">
-        <v>0.01163</v>
+        <v>0.011495</v>
       </c>
       <c r="C424" t="n">
         <v>0.853261</v>
@@ -5939,7 +5939,7 @@
         </is>
       </c>
       <c r="B425" t="n">
-        <v>0.011664</v>
+        <v>0.011636</v>
       </c>
       <c r="C425" t="n">
         <v>0.850543</v>
@@ -5952,7 +5952,7 @@
         </is>
       </c>
       <c r="B426" t="n">
-        <v>0.011983</v>
+        <v>0.011718</v>
       </c>
       <c r="C426" t="n">
         <v>0.847826</v>
@@ -5965,7 +5965,7 @@
         </is>
       </c>
       <c r="B427" t="n">
-        <v>0.012176</v>
+        <v>0.012067</v>
       </c>
       <c r="C427" t="n">
         <v>0.845109</v>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="B428" t="n">
-        <v>0.012311</v>
+        <v>0.012237</v>
       </c>
       <c r="C428" t="n">
         <v>0.842391</v>
@@ -5991,7 +5991,7 @@
         </is>
       </c>
       <c r="B429" t="n">
-        <v>0.013165</v>
+        <v>0.012343</v>
       </c>
       <c r="C429" t="n">
         <v>0.839674</v>
@@ -6004,7 +6004,7 @@
         </is>
       </c>
       <c r="B430" t="n">
-        <v>0.013174</v>
+        <v>0.013106</v>
       </c>
       <c r="C430" t="n">
         <v>0.836957</v>
@@ -6017,7 +6017,7 @@
         </is>
       </c>
       <c r="B431" t="n">
-        <v>0.013342</v>
+        <v>0.013196</v>
       </c>
       <c r="C431" t="n">
         <v>0.834239</v>
@@ -6030,7 +6030,7 @@
         </is>
       </c>
       <c r="B432" t="n">
-        <v>0.013694</v>
+        <v>0.013354</v>
       </c>
       <c r="C432" t="n">
         <v>0.831522</v>
@@ -6043,7 +6043,7 @@
         </is>
       </c>
       <c r="B433" t="n">
-        <v>0.01397</v>
+        <v>0.013712</v>
       </c>
       <c r="C433" t="n">
         <v>0.828804</v>
@@ -6056,7 +6056,7 @@
         </is>
       </c>
       <c r="B434" t="n">
-        <v>0.013973</v>
+        <v>0.013971</v>
       </c>
       <c r="C434" t="n">
         <v>0.826087</v>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="B435" t="n">
-        <v>0.014061</v>
+        <v>0.014066</v>
       </c>
       <c r="C435" t="n">
         <v>0.82337</v>
@@ -6082,7 +6082,7 @@
         </is>
       </c>
       <c r="B436" t="n">
-        <v>0.014423</v>
+        <v>0.014132</v>
       </c>
       <c r="C436" t="n">
         <v>0.820652</v>
@@ -6095,7 +6095,7 @@
         </is>
       </c>
       <c r="B437" t="n">
-        <v>0.014922</v>
+        <v>0.014448</v>
       </c>
       <c r="C437" t="n">
         <v>0.817935</v>
@@ -6108,7 +6108,7 @@
         </is>
       </c>
       <c r="B438" t="n">
-        <v>0.014942</v>
+        <v>0.014939</v>
       </c>
       <c r="C438" t="n">
         <v>0.815217</v>
@@ -6121,7 +6121,7 @@
         </is>
       </c>
       <c r="B439" t="n">
-        <v>0.015084</v>
+        <v>0.014944</v>
       </c>
       <c r="C439" t="n">
         <v>0.8125</v>
@@ -6134,7 +6134,7 @@
         </is>
       </c>
       <c r="B440" t="n">
-        <v>0.01509</v>
+        <v>0.015077</v>
       </c>
       <c r="C440" t="n">
         <v>0.809783</v>
@@ -6147,7 +6147,7 @@
         </is>
       </c>
       <c r="B441" t="n">
-        <v>0.015121</v>
+        <v>0.015152</v>
       </c>
       <c r="C441" t="n">
         <v>0.807065</v>
@@ -6160,7 +6160,7 @@
         </is>
       </c>
       <c r="B442" t="n">
-        <v>0.015372</v>
+        <v>0.015168</v>
       </c>
       <c r="C442" t="n">
         <v>0.804348</v>
@@ -6173,7 +6173,7 @@
         </is>
       </c>
       <c r="B443" t="n">
-        <v>0.015651</v>
+        <v>0.015412</v>
       </c>
       <c r="C443" t="n">
         <v>0.80163</v>
@@ -6186,7 +6186,7 @@
         </is>
       </c>
       <c r="B444" t="n">
-        <v>0.016128</v>
+        <v>0.015618</v>
       </c>
       <c r="C444" t="n">
         <v>0.798913</v>
@@ -6199,7 +6199,7 @@
         </is>
       </c>
       <c r="B445" t="n">
-        <v>0.016255</v>
+        <v>0.016204</v>
       </c>
       <c r="C445" t="n">
         <v>0.796196</v>
@@ -6212,7 +6212,7 @@
         </is>
       </c>
       <c r="B446" t="n">
-        <v>0.016732</v>
+        <v>0.016339</v>
       </c>
       <c r="C446" t="n">
         <v>0.793478</v>
@@ -6225,7 +6225,7 @@
         </is>
       </c>
       <c r="B447" t="n">
-        <v>0.016784</v>
+        <v>0.016783</v>
       </c>
       <c r="C447" t="n">
         <v>0.790761</v>
@@ -6238,7 +6238,7 @@
         </is>
       </c>
       <c r="B448" t="n">
-        <v>0.016814</v>
+        <v>0.016787</v>
       </c>
       <c r="C448" t="n">
         <v>0.788043</v>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="B449" t="n">
-        <v>0.016916</v>
+        <v>0.016836</v>
       </c>
       <c r="C449" t="n">
         <v>0.785326</v>
@@ -6264,7 +6264,7 @@
         </is>
       </c>
       <c r="B450" t="n">
-        <v>0.017065</v>
+        <v>0.016976</v>
       </c>
       <c r="C450" t="n">
         <v>0.782609</v>
@@ -6277,7 +6277,7 @@
         </is>
       </c>
       <c r="B451" t="n">
-        <v>0.017068</v>
+        <v>0.017103</v>
       </c>
       <c r="C451" t="n">
         <v>0.779891</v>
@@ -6290,7 +6290,7 @@
         </is>
       </c>
       <c r="B452" t="n">
-        <v>0.017833</v>
+        <v>0.017156</v>
       </c>
       <c r="C452" t="n">
         <v>0.777174</v>
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="B453" t="n">
-        <v>0.018204</v>
+        <v>0.017799</v>
       </c>
       <c r="C453" t="n">
         <v>0.774457</v>
@@ -6316,7 +6316,7 @@
         </is>
       </c>
       <c r="B454" t="n">
-        <v>0.018517</v>
+        <v>0.018253</v>
       </c>
       <c r="C454" t="n">
         <v>0.771739</v>
@@ -6329,7 +6329,7 @@
         </is>
       </c>
       <c r="B455" t="n">
-        <v>0.018769</v>
+        <v>0.018576</v>
       </c>
       <c r="C455" t="n">
         <v>0.769022</v>
@@ -6342,7 +6342,7 @@
         </is>
       </c>
       <c r="B456" t="n">
-        <v>0.019164</v>
+        <v>0.018769</v>
       </c>
       <c r="C456" t="n">
         <v>0.766304</v>
@@ -6355,7 +6355,7 @@
         </is>
       </c>
       <c r="B457" t="n">
-        <v>0.019489</v>
+        <v>0.019274</v>
       </c>
       <c r="C457" t="n">
         <v>0.763587</v>
@@ -6368,7 +6368,7 @@
         </is>
       </c>
       <c r="B458" t="n">
-        <v>0.019494</v>
+        <v>0.019487</v>
       </c>
       <c r="C458" t="n">
         <v>0.76087</v>
@@ -6381,7 +6381,7 @@
         </is>
       </c>
       <c r="B459" t="n">
-        <v>0.020047</v>
+        <v>0.019567</v>
       </c>
       <c r="C459" t="n">
         <v>0.758152</v>
@@ -6394,7 +6394,7 @@
         </is>
       </c>
       <c r="B460" t="n">
-        <v>0.0206</v>
+        <v>0.019918</v>
       </c>
       <c r="C460" t="n">
         <v>0.755435</v>
@@ -6407,7 +6407,7 @@
         </is>
       </c>
       <c r="B461" t="n">
-        <v>0.020761</v>
+        <v>0.020701</v>
       </c>
       <c r="C461" t="n">
         <v>0.752717</v>
@@ -6420,7 +6420,7 @@
         </is>
       </c>
       <c r="B462" t="n">
-        <v>0.021192</v>
+        <v>0.020747</v>
       </c>
       <c r="C462" t="n">
         <v>0.75</v>
@@ -6433,7 +6433,7 @@
         </is>
       </c>
       <c r="B463" t="n">
-        <v>0.021667</v>
+        <v>0.021227</v>
       </c>
       <c r="C463" t="n">
         <v>0.747283</v>
@@ -6446,7 +6446,7 @@
         </is>
       </c>
       <c r="B464" t="n">
-        <v>0.021899</v>
+        <v>0.02158</v>
       </c>
       <c r="C464" t="n">
         <v>0.744565</v>
@@ -6459,7 +6459,7 @@
         </is>
       </c>
       <c r="B465" t="n">
-        <v>0.021908</v>
+        <v>0.021914</v>
       </c>
       <c r="C465" t="n">
         <v>0.741848</v>
@@ -6472,7 +6472,7 @@
         </is>
       </c>
       <c r="B466" t="n">
-        <v>0.021951</v>
+        <v>0.021972</v>
       </c>
       <c r="C466" t="n">
         <v>0.73913</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="B467" t="n">
-        <v>0.022162</v>
+        <v>0.022002</v>
       </c>
       <c r="C467" t="n">
         <v>0.736413</v>
@@ -6498,7 +6498,7 @@
         </is>
       </c>
       <c r="B468" t="n">
-        <v>0.022201</v>
+        <v>0.022116</v>
       </c>
       <c r="C468" t="n">
         <v>0.733696</v>
@@ -6511,7 +6511,7 @@
         </is>
       </c>
       <c r="B469" t="n">
-        <v>0.022236</v>
+        <v>0.022135</v>
       </c>
       <c r="C469" t="n">
         <v>0.730978</v>
@@ -6524,7 +6524,7 @@
         </is>
       </c>
       <c r="B470" t="n">
-        <v>0.022384</v>
+        <v>0.022204</v>
       </c>
       <c r="C470" t="n">
         <v>0.728261</v>
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="B471" t="n">
-        <v>0.022651</v>
+        <v>0.022515</v>
       </c>
       <c r="C471" t="n">
         <v>0.725543</v>
@@ -6550,7 +6550,7 @@
         </is>
       </c>
       <c r="B472" t="n">
-        <v>0.023083</v>
+        <v>0.022706</v>
       </c>
       <c r="C472" t="n">
         <v>0.722826</v>
@@ -6563,7 +6563,7 @@
         </is>
       </c>
       <c r="B473" t="n">
-        <v>0.023319</v>
+        <v>0.022941</v>
       </c>
       <c r="C473" t="n">
         <v>0.720109</v>
@@ -6576,7 +6576,7 @@
         </is>
       </c>
       <c r="B474" t="n">
-        <v>0.023878</v>
+        <v>0.023194</v>
       </c>
       <c r="C474" t="n">
         <v>0.717391</v>
@@ -6589,7 +6589,7 @@
         </is>
       </c>
       <c r="B475" t="n">
-        <v>0.024282</v>
+        <v>0.023843</v>
       </c>
       <c r="C475" t="n">
         <v>0.714674</v>
@@ -6602,7 +6602,7 @@
         </is>
       </c>
       <c r="B476" t="n">
-        <v>0.024335</v>
+        <v>0.024239</v>
       </c>
       <c r="C476" t="n">
         <v>0.711957</v>
@@ -6615,7 +6615,7 @@
         </is>
       </c>
       <c r="B477" t="n">
-        <v>0.024601</v>
+        <v>0.024443</v>
       </c>
       <c r="C477" t="n">
         <v>0.709239</v>
@@ -6628,7 +6628,7 @@
         </is>
       </c>
       <c r="B478" t="n">
-        <v>0.024784</v>
+        <v>0.024722</v>
       </c>
       <c r="C478" t="n">
         <v>0.706522</v>
@@ -6641,7 +6641,7 @@
         </is>
       </c>
       <c r="B479" t="n">
-        <v>0.025139</v>
+        <v>0.024855</v>
       </c>
       <c r="C479" t="n">
         <v>0.703804</v>
@@ -6654,7 +6654,7 @@
         </is>
       </c>
       <c r="B480" t="n">
-        <v>0.025199</v>
+        <v>0.025285</v>
       </c>
       <c r="C480" t="n">
         <v>0.701087</v>
@@ -6667,7 +6667,7 @@
         </is>
       </c>
       <c r="B481" t="n">
-        <v>0.025312</v>
+        <v>0.025321</v>
       </c>
       <c r="C481" t="n">
         <v>0.69837</v>
@@ -6680,7 +6680,7 @@
         </is>
       </c>
       <c r="B482" t="n">
-        <v>0.025506</v>
+        <v>0.025376</v>
       </c>
       <c r="C482" t="n">
         <v>0.695652</v>
@@ -6693,7 +6693,7 @@
         </is>
       </c>
       <c r="B483" t="n">
-        <v>0.025976</v>
+        <v>0.025684</v>
       </c>
       <c r="C483" t="n">
         <v>0.692935</v>
@@ -6706,7 +6706,7 @@
         </is>
       </c>
       <c r="B484" t="n">
-        <v>0.026001</v>
+        <v>0.026098</v>
       </c>
       <c r="C484" t="n">
         <v>0.690217</v>
@@ -6719,7 +6719,7 @@
         </is>
       </c>
       <c r="B485" t="n">
-        <v>0.026124</v>
+        <v>0.026099</v>
       </c>
       <c r="C485" t="n">
         <v>0.6875</v>
@@ -6732,7 +6732,7 @@
         </is>
       </c>
       <c r="B486" t="n">
-        <v>0.026159</v>
+        <v>0.026104</v>
       </c>
       <c r="C486" t="n">
         <v>0.684783</v>
@@ -6745,7 +6745,7 @@
         </is>
       </c>
       <c r="B487" t="n">
-        <v>0.026176</v>
+        <v>0.026162</v>
       </c>
       <c r="C487" t="n">
         <v>0.682065</v>
@@ -6758,7 +6758,7 @@
         </is>
       </c>
       <c r="B488" t="n">
-        <v>0.026199</v>
+        <v>0.026167</v>
       </c>
       <c r="C488" t="n">
         <v>0.679348</v>
@@ -6771,7 +6771,7 @@
         </is>
       </c>
       <c r="B489" t="n">
-        <v>0.026245</v>
+        <v>0.026187</v>
       </c>
       <c r="C489" t="n">
         <v>0.67663</v>
@@ -6784,7 +6784,7 @@
         </is>
       </c>
       <c r="B490" t="n">
-        <v>0.026986</v>
+        <v>0.026336</v>
       </c>
       <c r="C490" t="n">
         <v>0.673913</v>
@@ -6797,7 +6797,7 @@
         </is>
       </c>
       <c r="B491" t="n">
-        <v>0.027398</v>
+        <v>0.027158</v>
       </c>
       <c r="C491" t="n">
         <v>0.671196</v>
@@ -6810,7 +6810,7 @@
         </is>
       </c>
       <c r="B492" t="n">
-        <v>0.027507</v>
+        <v>0.027475</v>
       </c>
       <c r="C492" t="n">
         <v>0.668478</v>
@@ -6823,7 +6823,7 @@
         </is>
       </c>
       <c r="B493" t="n">
-        <v>0.027656</v>
+        <v>0.02754</v>
       </c>
       <c r="C493" t="n">
         <v>0.665761</v>
@@ -6836,7 +6836,7 @@
         </is>
       </c>
       <c r="B494" t="n">
-        <v>0.028214</v>
+        <v>0.027624</v>
       </c>
       <c r="C494" t="n">
         <v>0.663043</v>
@@ -6849,7 +6849,7 @@
         </is>
       </c>
       <c r="B495" t="n">
-        <v>0.028276</v>
+        <v>0.028366</v>
       </c>
       <c r="C495" t="n">
         <v>0.660326</v>
@@ -6862,7 +6862,7 @@
         </is>
       </c>
       <c r="B496" t="n">
-        <v>0.028609</v>
+        <v>0.028396</v>
       </c>
       <c r="C496" t="n">
         <v>0.657609</v>
@@ -6875,7 +6875,7 @@
         </is>
       </c>
       <c r="B497" t="n">
-        <v>0.029098</v>
+        <v>0.028644</v>
       </c>
       <c r="C497" t="n">
         <v>0.654891</v>
@@ -6888,7 +6888,7 @@
         </is>
       </c>
       <c r="B498" t="n">
-        <v>0.029255</v>
+        <v>0.028926</v>
       </c>
       <c r="C498" t="n">
         <v>0.652174</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="B499" t="n">
-        <v>0.029534</v>
+        <v>0.029079</v>
       </c>
       <c r="C499" t="n">
         <v>0.649457</v>
@@ -6914,7 +6914,7 @@
         </is>
       </c>
       <c r="B500" t="n">
-        <v>0.029632</v>
+        <v>0.029545</v>
       </c>
       <c r="C500" t="n">
         <v>0.646739</v>
@@ -6927,7 +6927,7 @@
         </is>
       </c>
       <c r="B501" t="n">
-        <v>0.029716</v>
+        <v>0.029765</v>
       </c>
       <c r="C501" t="n">
         <v>0.644022</v>
@@ -6940,7 +6940,7 @@
         </is>
       </c>
       <c r="B502" t="n">
-        <v>0.029802</v>
+        <v>0.029807</v>
       </c>
       <c r="C502" t="n">
         <v>0.641304</v>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="B503" t="n">
-        <v>0.030378</v>
+        <v>0.029982</v>
       </c>
       <c r="C503" t="n">
         <v>0.638587</v>
@@ -6966,7 +6966,7 @@
         </is>
       </c>
       <c r="B504" t="n">
-        <v>0.030423</v>
+        <v>0.030374</v>
       </c>
       <c r="C504" t="n">
         <v>0.63587</v>
@@ -6979,7 +6979,7 @@
         </is>
       </c>
       <c r="B505" t="n">
-        <v>0.030434</v>
+        <v>0.030511</v>
       </c>
       <c r="C505" t="n">
         <v>0.633152</v>
@@ -6992,7 +6992,7 @@
         </is>
       </c>
       <c r="B506" t="n">
-        <v>0.030629</v>
+        <v>0.03055</v>
       </c>
       <c r="C506" t="n">
         <v>0.630435</v>
@@ -7005,7 +7005,7 @@
         </is>
       </c>
       <c r="B507" t="n">
-        <v>0.03069</v>
+        <v>0.030628</v>
       </c>
       <c r="C507" t="n">
         <v>0.627717</v>
@@ -7018,7 +7018,7 @@
         </is>
       </c>
       <c r="B508" t="n">
-        <v>0.030935</v>
+        <v>0.030812</v>
       </c>
       <c r="C508" t="n">
         <v>0.625</v>
@@ -7031,7 +7031,7 @@
         </is>
       </c>
       <c r="B509" t="n">
-        <v>0.031068</v>
+        <v>0.0311</v>
       </c>
       <c r="C509" t="n">
         <v>0.622283</v>
@@ -7044,7 +7044,7 @@
         </is>
       </c>
       <c r="B510" t="n">
-        <v>0.03151</v>
+        <v>0.031171</v>
       </c>
       <c r="C510" t="n">
         <v>0.619565</v>
@@ -7057,7 +7057,7 @@
         </is>
       </c>
       <c r="B511" t="n">
-        <v>0.031547</v>
+        <v>0.031518</v>
       </c>
       <c r="C511" t="n">
         <v>0.616848</v>
@@ -7070,7 +7070,7 @@
         </is>
       </c>
       <c r="B512" t="n">
-        <v>0.032679</v>
+        <v>0.031568</v>
       </c>
       <c r="C512" t="n">
         <v>0.61413</v>
@@ -7083,7 +7083,7 @@
         </is>
       </c>
       <c r="B513" t="n">
-        <v>0.033105</v>
+        <v>0.032677</v>
       </c>
       <c r="C513" t="n">
         <v>0.611413</v>
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="B514" t="n">
-        <v>0.033298</v>
+        <v>0.033232</v>
       </c>
       <c r="C514" t="n">
         <v>0.608696</v>
@@ -7109,7 +7109,7 @@
         </is>
       </c>
       <c r="B515" t="n">
-        <v>0.033503</v>
+        <v>0.033465</v>
       </c>
       <c r="C515" t="n">
         <v>0.605978</v>
@@ -7122,7 +7122,7 @@
         </is>
       </c>
       <c r="B516" t="n">
-        <v>0.033738</v>
+        <v>0.033484</v>
       </c>
       <c r="C516" t="n">
         <v>0.603261</v>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="B517" t="n">
-        <v>0.033968</v>
+        <v>0.03381</v>
       </c>
       <c r="C517" t="n">
         <v>0.600543</v>
@@ -7148,7 +7148,7 @@
         </is>
       </c>
       <c r="B518" t="n">
-        <v>0.034013</v>
+        <v>0.034011</v>
       </c>
       <c r="C518" t="n">
         <v>0.597826</v>
@@ -7161,7 +7161,7 @@
         </is>
       </c>
       <c r="B519" t="n">
-        <v>0.034619</v>
+        <v>0.034132</v>
       </c>
       <c r="C519" t="n">
         <v>0.595109</v>
@@ -7174,7 +7174,7 @@
         </is>
       </c>
       <c r="B520" t="n">
-        <v>0.034697</v>
+        <v>0.034836</v>
       </c>
       <c r="C520" t="n">
         <v>0.592391</v>
@@ -7187,7 +7187,7 @@
         </is>
       </c>
       <c r="B521" t="n">
-        <v>0.034823</v>
+        <v>0.034865</v>
       </c>
       <c r="C521" t="n">
         <v>0.589674</v>
@@ -7200,7 +7200,7 @@
         </is>
       </c>
       <c r="B522" t="n">
-        <v>0.034908</v>
+        <v>0.034887</v>
       </c>
       <c r="C522" t="n">
         <v>0.586957</v>
@@ -7213,7 +7213,7 @@
         </is>
       </c>
       <c r="B523" t="n">
-        <v>0.035181</v>
+        <v>0.035067</v>
       </c>
       <c r="C523" t="n">
         <v>0.584239</v>
@@ -7226,7 +7226,7 @@
         </is>
       </c>
       <c r="B524" t="n">
-        <v>0.035194</v>
+        <v>0.035242</v>
       </c>
       <c r="C524" t="n">
         <v>0.581522</v>
@@ -7239,7 +7239,7 @@
         </is>
       </c>
       <c r="B525" t="n">
-        <v>0.035752</v>
+        <v>0.035314</v>
       </c>
       <c r="C525" t="n">
         <v>0.578804</v>
@@ -7252,7 +7252,7 @@
         </is>
       </c>
       <c r="B526" t="n">
-        <v>0.03613</v>
+        <v>0.035948</v>
       </c>
       <c r="C526" t="n">
         <v>0.576087</v>
@@ -7265,7 +7265,7 @@
         </is>
       </c>
       <c r="B527" t="n">
-        <v>0.036466</v>
+        <v>0.03595</v>
       </c>
       <c r="C527" t="n">
         <v>0.57337</v>
@@ -7278,7 +7278,7 @@
         </is>
       </c>
       <c r="B528" t="n">
-        <v>0.036895</v>
+        <v>0.036908</v>
       </c>
       <c r="C528" t="n">
         <v>0.570652</v>
@@ -7291,7 +7291,7 @@
         </is>
       </c>
       <c r="B529" t="n">
-        <v>0.036987</v>
+        <v>0.037098</v>
       </c>
       <c r="C529" t="n">
         <v>0.567935</v>
@@ -7304,7 +7304,7 @@
         </is>
       </c>
       <c r="B530" t="n">
-        <v>0.037235</v>
+        <v>0.037455</v>
       </c>
       <c r="C530" t="n">
         <v>0.565217</v>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="B531" t="n">
-        <v>0.037462</v>
+        <v>0.037665</v>
       </c>
       <c r="C531" t="n">
         <v>0.5625</v>
@@ -7330,7 +7330,7 @@
         </is>
       </c>
       <c r="B532" t="n">
-        <v>0.037564</v>
+        <v>0.037723</v>
       </c>
       <c r="C532" t="n">
         <v>0.559783</v>
@@ -7343,7 +7343,7 @@
         </is>
       </c>
       <c r="B533" t="n">
-        <v>0.037641</v>
+        <v>0.037779</v>
       </c>
       <c r="C533" t="n">
         <v>0.557065</v>
@@ -7356,7 +7356,7 @@
         </is>
       </c>
       <c r="B534" t="n">
-        <v>0.037735</v>
+        <v>0.037793</v>
       </c>
       <c r="C534" t="n">
         <v>0.554348</v>
@@ -7369,7 +7369,7 @@
         </is>
       </c>
       <c r="B535" t="n">
-        <v>0.037891</v>
+        <v>0.03809</v>
       </c>
       <c r="C535" t="n">
         <v>0.55163</v>
@@ -7382,7 +7382,7 @@
         </is>
       </c>
       <c r="B536" t="n">
-        <v>0.038055</v>
+        <v>0.038156</v>
       </c>
       <c r="C536" t="n">
         <v>0.548913</v>
@@ -7395,7 +7395,7 @@
         </is>
       </c>
       <c r="B537" t="n">
-        <v>0.038148</v>
+        <v>0.038346</v>
       </c>
       <c r="C537" t="n">
         <v>0.546196</v>
@@ -7408,7 +7408,7 @@
         </is>
       </c>
       <c r="B538" t="n">
-        <v>0.038201</v>
+        <v>0.038361</v>
       </c>
       <c r="C538" t="n">
         <v>0.543478</v>
@@ -7421,7 +7421,7 @@
         </is>
       </c>
       <c r="B539" t="n">
-        <v>0.038279</v>
+        <v>0.038399</v>
       </c>
       <c r="C539" t="n">
         <v>0.540761</v>
@@ -7434,7 +7434,7 @@
         </is>
       </c>
       <c r="B540" t="n">
-        <v>0.038664</v>
+        <v>0.03885</v>
       </c>
       <c r="C540" t="n">
         <v>0.538043</v>
@@ -7447,7 +7447,7 @@
         </is>
       </c>
       <c r="B541" t="n">
-        <v>0.039105</v>
+        <v>0.039142</v>
       </c>
       <c r="C541" t="n">
         <v>0.535326</v>
@@ -7460,7 +7460,7 @@
         </is>
       </c>
       <c r="B542" t="n">
-        <v>0.039218</v>
+        <v>0.03924</v>
       </c>
       <c r="C542" t="n">
         <v>0.532609</v>
@@ -7473,7 +7473,7 @@
         </is>
       </c>
       <c r="B543" t="n">
-        <v>0.03923</v>
+        <v>0.039411</v>
       </c>
       <c r="C543" t="n">
         <v>0.529891</v>
@@ -7486,7 +7486,7 @@
         </is>
       </c>
       <c r="B544" t="n">
-        <v>0.039296</v>
+        <v>0.039484</v>
       </c>
       <c r="C544" t="n">
         <v>0.527174</v>
@@ -7499,7 +7499,7 @@
         </is>
       </c>
       <c r="B545" t="n">
-        <v>0.039301</v>
+        <v>0.039997</v>
       </c>
       <c r="C545" t="n">
         <v>0.524457</v>
@@ -7512,7 +7512,7 @@
         </is>
       </c>
       <c r="B546" t="n">
-        <v>0.039865</v>
+        <v>0.040291</v>
       </c>
       <c r="C546" t="n">
         <v>0.521739</v>
@@ -7525,7 +7525,7 @@
         </is>
       </c>
       <c r="B547" t="n">
-        <v>0.040132</v>
+        <v>0.040308</v>
       </c>
       <c r="C547" t="n">
         <v>0.519022</v>
@@ -7538,7 +7538,7 @@
         </is>
       </c>
       <c r="B548" t="n">
-        <v>0.040497</v>
+        <v>0.040487</v>
       </c>
       <c r="C548" t="n">
         <v>0.516304</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="B549" t="n">
-        <v>0.040581</v>
+        <v>0.040867</v>
       </c>
       <c r="C549" t="n">
         <v>0.513587</v>
@@ -7564,7 +7564,7 @@
         </is>
       </c>
       <c r="B550" t="n">
-        <v>0.040699</v>
+        <v>0.041863</v>
       </c>
       <c r="C550" t="n">
         <v>0.51087</v>
@@ -7577,7 +7577,7 @@
         </is>
       </c>
       <c r="B551" t="n">
-        <v>0.041793</v>
+        <v>0.041888</v>
       </c>
       <c r="C551" t="n">
         <v>0.508152</v>
@@ -7590,7 +7590,7 @@
         </is>
       </c>
       <c r="B552" t="n">
-        <v>0.041995</v>
+        <v>0.042234</v>
       </c>
       <c r="C552" t="n">
         <v>0.505435</v>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="B553" t="n">
-        <v>0.042204</v>
+        <v>0.042371</v>
       </c>
       <c r="C553" t="n">
         <v>0.502717</v>
@@ -7616,7 +7616,7 @@
         </is>
       </c>
       <c r="B554" t="n">
-        <v>0.042256</v>
+        <v>0.043364</v>
       </c>
       <c r="C554" t="n">
         <v>0.5</v>
@@ -7629,7 +7629,7 @@
         </is>
       </c>
       <c r="B555" t="n">
-        <v>0.043162</v>
+        <v>0.04337</v>
       </c>
       <c r="C555" t="n">
         <v>0.497283</v>
@@ -7642,7 +7642,7 @@
         </is>
       </c>
       <c r="B556" t="n">
-        <v>0.043308</v>
+        <v>0.043819</v>
       </c>
       <c r="C556" t="n">
         <v>0.494565</v>
@@ -7655,7 +7655,7 @@
         </is>
       </c>
       <c r="B557" t="n">
-        <v>0.043602</v>
+        <v>0.043871</v>
       </c>
       <c r="C557" t="n">
         <v>0.491848</v>
@@ -7668,7 +7668,7 @@
         </is>
       </c>
       <c r="B558" t="n">
-        <v>0.044132</v>
+        <v>0.044588</v>
       </c>
       <c r="C558" t="n">
         <v>0.48913</v>
@@ -7681,7 +7681,7 @@
         </is>
       </c>
       <c r="B559" t="n">
-        <v>0.0445</v>
+        <v>0.046041</v>
       </c>
       <c r="C559" t="n">
         <v>0.486413</v>
@@ -7694,7 +7694,7 @@
         </is>
       </c>
       <c r="B560" t="n">
-        <v>0.045799</v>
+        <v>0.046454</v>
       </c>
       <c r="C560" t="n">
         <v>0.483696</v>
@@ -7707,7 +7707,7 @@
         </is>
       </c>
       <c r="B561" t="n">
-        <v>0.046274</v>
+        <v>0.046487</v>
       </c>
       <c r="C561" t="n">
         <v>0.480978</v>
@@ -7720,7 +7720,7 @@
         </is>
       </c>
       <c r="B562" t="n">
-        <v>0.046572</v>
+        <v>0.04671</v>
       </c>
       <c r="C562" t="n">
         <v>0.478261</v>
@@ -7733,7 +7733,7 @@
         </is>
       </c>
       <c r="B563" t="n">
-        <v>0.046735</v>
+        <v>0.046796</v>
       </c>
       <c r="C563" t="n">
         <v>0.475543</v>
@@ -7746,7 +7746,7 @@
         </is>
       </c>
       <c r="B564" t="n">
-        <v>0.046853</v>
+        <v>0.046889</v>
       </c>
       <c r="C564" t="n">
         <v>0.472826</v>
@@ -7759,7 +7759,7 @@
         </is>
       </c>
       <c r="B565" t="n">
-        <v>0.046917</v>
+        <v>0.047131</v>
       </c>
       <c r="C565" t="n">
         <v>0.470109</v>
@@ -7772,7 +7772,7 @@
         </is>
       </c>
       <c r="B566" t="n">
-        <v>0.047146</v>
+        <v>0.047637</v>
       </c>
       <c r="C566" t="n">
         <v>0.467391</v>
@@ -7785,7 +7785,7 @@
         </is>
       </c>
       <c r="B567" t="n">
-        <v>0.047443</v>
+        <v>0.047891</v>
       </c>
       <c r="C567" t="n">
         <v>0.464674</v>
@@ -7798,7 +7798,7 @@
         </is>
       </c>
       <c r="B568" t="n">
-        <v>0.047785</v>
+        <v>0.048348</v>
       </c>
       <c r="C568" t="n">
         <v>0.461957</v>
@@ -7811,7 +7811,7 @@
         </is>
       </c>
       <c r="B569" t="n">
-        <v>0.04833</v>
+        <v>0.048376</v>
       </c>
       <c r="C569" t="n">
         <v>0.459239</v>
@@ -7824,7 +7824,7 @@
         </is>
       </c>
       <c r="B570" t="n">
-        <v>0.048373</v>
+        <v>0.04839</v>
       </c>
       <c r="C570" t="n">
         <v>0.456522</v>
@@ -7837,7 +7837,7 @@
         </is>
       </c>
       <c r="B571" t="n">
-        <v>0.048403</v>
+        <v>0.048855</v>
       </c>
       <c r="C571" t="n">
         <v>0.453804</v>
@@ -7850,7 +7850,7 @@
         </is>
       </c>
       <c r="B572" t="n">
-        <v>0.048634</v>
+        <v>0.049056</v>
       </c>
       <c r="C572" t="n">
         <v>0.451087</v>
@@ -7863,7 +7863,7 @@
         </is>
       </c>
       <c r="B573" t="n">
-        <v>0.048939</v>
+        <v>0.049418</v>
       </c>
       <c r="C573" t="n">
         <v>0.44837</v>
@@ -7876,7 +7876,7 @@
         </is>
       </c>
       <c r="B574" t="n">
-        <v>0.049093</v>
+        <v>0.049456</v>
       </c>
       <c r="C574" t="n">
         <v>0.445652</v>
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="B575" t="n">
-        <v>0.049874</v>
+        <v>0.049923</v>
       </c>
       <c r="C575" t="n">
         <v>0.442935</v>
@@ -7902,7 +7902,7 @@
         </is>
       </c>
       <c r="B576" t="n">
-        <v>0.050399</v>
+        <v>0.05053</v>
       </c>
       <c r="C576" t="n">
         <v>0.440217</v>
@@ -7915,7 +7915,7 @@
         </is>
       </c>
       <c r="B577" t="n">
-        <v>0.050677</v>
+        <v>0.05056</v>
       </c>
       <c r="C577" t="n">
         <v>0.4375</v>
@@ -7928,7 +7928,7 @@
         </is>
       </c>
       <c r="B578" t="n">
-        <v>0.050837</v>
+        <v>0.051009</v>
       </c>
       <c r="C578" t="n">
         <v>0.434783</v>
@@ -7941,7 +7941,7 @@
         </is>
       </c>
       <c r="B579" t="n">
-        <v>0.051923</v>
+        <v>0.05184</v>
       </c>
       <c r="C579" t="n">
         <v>0.432065</v>
@@ -7954,7 +7954,7 @@
         </is>
       </c>
       <c r="B580" t="n">
-        <v>0.052397</v>
+        <v>0.05249</v>
       </c>
       <c r="C580" t="n">
         <v>0.429348</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="B581" t="n">
-        <v>0.052403</v>
+        <v>0.052494</v>
       </c>
       <c r="C581" t="n">
         <v>0.42663</v>
@@ -7980,7 +7980,7 @@
         </is>
       </c>
       <c r="B582" t="n">
-        <v>0.052697</v>
+        <v>0.052775</v>
       </c>
       <c r="C582" t="n">
         <v>0.423913</v>
@@ -7993,7 +7993,7 @@
         </is>
       </c>
       <c r="B583" t="n">
-        <v>0.053188</v>
+        <v>0.053292</v>
       </c>
       <c r="C583" t="n">
         <v>0.421196</v>
@@ -8006,7 +8006,7 @@
         </is>
       </c>
       <c r="B584" t="n">
-        <v>0.053681</v>
+        <v>0.053746</v>
       </c>
       <c r="C584" t="n">
         <v>0.418478</v>
@@ -8019,7 +8019,7 @@
         </is>
       </c>
       <c r="B585" t="n">
-        <v>0.053754</v>
+        <v>0.053842</v>
       </c>
       <c r="C585" t="n">
         <v>0.415761</v>
@@ -8032,7 +8032,7 @@
         </is>
       </c>
       <c r="B586" t="n">
-        <v>0.054192</v>
+        <v>0.054575</v>
       </c>
       <c r="C586" t="n">
         <v>0.413043</v>
@@ -8045,7 +8045,7 @@
         </is>
       </c>
       <c r="B587" t="n">
-        <v>0.054641</v>
+        <v>0.054699</v>
       </c>
       <c r="C587" t="n">
         <v>0.410326</v>
@@ -8058,7 +8058,7 @@
         </is>
       </c>
       <c r="B588" t="n">
-        <v>0.055365</v>
+        <v>0.056685</v>
       </c>
       <c r="C588" t="n">
         <v>0.407609</v>
@@ -8071,7 +8071,7 @@
         </is>
       </c>
       <c r="B589" t="n">
-        <v>0.056359</v>
+        <v>0.056999</v>
       </c>
       <c r="C589" t="n">
         <v>0.404891</v>
@@ -8084,7 +8084,7 @@
         </is>
       </c>
       <c r="B590" t="n">
-        <v>0.057143</v>
+        <v>0.057927</v>
       </c>
       <c r="C590" t="n">
         <v>0.402174</v>
@@ -8097,7 +8097,7 @@
         </is>
       </c>
       <c r="B591" t="n">
-        <v>0.057867</v>
+        <v>0.058426</v>
       </c>
       <c r="C591" t="n">
         <v>0.399457</v>
@@ -8110,7 +8110,7 @@
         </is>
       </c>
       <c r="B592" t="n">
-        <v>0.058375</v>
+        <v>0.058547</v>
       </c>
       <c r="C592" t="n">
         <v>0.396739</v>
@@ -8123,7 +8123,7 @@
         </is>
       </c>
       <c r="B593" t="n">
-        <v>0.058617</v>
+        <v>0.058755</v>
       </c>
       <c r="C593" t="n">
         <v>0.394022</v>
@@ -8136,7 +8136,7 @@
         </is>
       </c>
       <c r="B594" t="n">
-        <v>0.058747</v>
+        <v>0.05896</v>
       </c>
       <c r="C594" t="n">
         <v>0.391304</v>
@@ -8149,7 +8149,7 @@
         </is>
       </c>
       <c r="B595" t="n">
-        <v>0.058761</v>
+        <v>0.059007</v>
       </c>
       <c r="C595" t="n">
         <v>0.388587</v>
@@ -8162,7 +8162,7 @@
         </is>
       </c>
       <c r="B596" t="n">
-        <v>0.059319</v>
+        <v>0.059528</v>
       </c>
       <c r="C596" t="n">
         <v>0.38587</v>
@@ -8175,7 +8175,7 @@
         </is>
       </c>
       <c r="B597" t="n">
-        <v>0.059335</v>
+        <v>0.059621</v>
       </c>
       <c r="C597" t="n">
         <v>0.383152</v>
@@ -8188,7 +8188,7 @@
         </is>
       </c>
       <c r="B598" t="n">
-        <v>0.059599</v>
+        <v>0.059859</v>
       </c>
       <c r="C598" t="n">
         <v>0.380435</v>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="B599" t="n">
-        <v>0.0596</v>
+        <v>0.0599</v>
       </c>
       <c r="C599" t="n">
         <v>0.377717</v>
@@ -8214,7 +8214,7 @@
         </is>
       </c>
       <c r="B600" t="n">
-        <v>0.059922</v>
+        <v>0.060052</v>
       </c>
       <c r="C600" t="n">
         <v>0.375</v>
@@ -8227,7 +8227,7 @@
         </is>
       </c>
       <c r="B601" t="n">
-        <v>0.059976</v>
+        <v>0.060086</v>
       </c>
       <c r="C601" t="n">
         <v>0.372283</v>
@@ -8240,7 +8240,7 @@
         </is>
       </c>
       <c r="B602" t="n">
-        <v>0.060232</v>
+        <v>0.060605</v>
       </c>
       <c r="C602" t="n">
         <v>0.369565</v>
@@ -8253,7 +8253,7 @@
         </is>
       </c>
       <c r="B603" t="n">
-        <v>0.060457</v>
+        <v>0.060695</v>
       </c>
       <c r="C603" t="n">
         <v>0.366848</v>
@@ -8266,7 +8266,7 @@
         </is>
       </c>
       <c r="B604" t="n">
-        <v>0.060672</v>
+        <v>0.061023</v>
       </c>
       <c r="C604" t="n">
         <v>0.36413</v>
@@ -8279,7 +8279,7 @@
         </is>
       </c>
       <c r="B605" t="n">
-        <v>0.0608</v>
+        <v>0.062821</v>
       </c>
       <c r="C605" t="n">
         <v>0.361413</v>
@@ -8292,7 +8292,7 @@
         </is>
       </c>
       <c r="B606" t="n">
-        <v>0.062504</v>
+        <v>0.063694</v>
       </c>
       <c r="C606" t="n">
         <v>0.358696</v>
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="B607" t="n">
-        <v>0.063268</v>
+        <v>0.063786</v>
       </c>
       <c r="C607" t="n">
         <v>0.355978</v>
@@ -8318,7 +8318,7 @@
         </is>
       </c>
       <c r="B608" t="n">
-        <v>0.06335499999999999</v>
+        <v>0.063806</v>
       </c>
       <c r="C608" t="n">
         <v>0.353261</v>
@@ -8331,7 +8331,7 @@
         </is>
       </c>
       <c r="B609" t="n">
-        <v>0.063679</v>
+        <v>0.06389400000000001</v>
       </c>
       <c r="C609" t="n">
         <v>0.350543</v>
@@ -8344,7 +8344,7 @@
         </is>
       </c>
       <c r="B610" t="n">
-        <v>0.064055</v>
+        <v>0.064757</v>
       </c>
       <c r="C610" t="n">
         <v>0.347826</v>
@@ -8357,7 +8357,7 @@
         </is>
       </c>
       <c r="B611" t="n">
-        <v>0.06455</v>
+        <v>0.06478399999999999</v>
       </c>
       <c r="C611" t="n">
         <v>0.345109</v>
@@ -8370,7 +8370,7 @@
         </is>
       </c>
       <c r="B612" t="n">
-        <v>0.064835</v>
+        <v>0.064957</v>
       </c>
       <c r="C612" t="n">
         <v>0.342391</v>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="B613" t="n">
-        <v>0.06485399999999999</v>
+        <v>0.06505</v>
       </c>
       <c r="C613" t="n">
         <v>0.339674</v>
@@ -8396,7 +8396,7 @@
         </is>
       </c>
       <c r="B614" t="n">
-        <v>0.065098</v>
+        <v>0.065243</v>
       </c>
       <c r="C614" t="n">
         <v>0.336957</v>
@@ -8409,7 +8409,7 @@
         </is>
       </c>
       <c r="B615" t="n">
-        <v>0.065259</v>
+        <v>0.066248</v>
       </c>
       <c r="C615" t="n">
         <v>0.334239</v>
@@ -8422,7 +8422,7 @@
         </is>
       </c>
       <c r="B616" t="n">
-        <v>0.06578299999999999</v>
+        <v>0.06632299999999999</v>
       </c>
       <c r="C616" t="n">
         <v>0.331522</v>
@@ -8435,7 +8435,7 @@
         </is>
       </c>
       <c r="B617" t="n">
-        <v>0.066217</v>
+        <v>0.066437</v>
       </c>
       <c r="C617" t="n">
         <v>0.328804</v>
@@ -8448,7 +8448,7 @@
         </is>
       </c>
       <c r="B618" t="n">
-        <v>0.066718</v>
+        <v>0.067338</v>
       </c>
       <c r="C618" t="n">
         <v>0.326087</v>
@@ -8461,7 +8461,7 @@
         </is>
       </c>
       <c r="B619" t="n">
-        <v>0.066999</v>
+        <v>0.067414</v>
       </c>
       <c r="C619" t="n">
         <v>0.32337</v>
@@ -8474,7 +8474,7 @@
         </is>
       </c>
       <c r="B620" t="n">
-        <v>0.06733699999999999</v>
+        <v>0.068066</v>
       </c>
       <c r="C620" t="n">
         <v>0.320652</v>
@@ -8487,7 +8487,7 @@
         </is>
       </c>
       <c r="B621" t="n">
-        <v>0.068081</v>
+        <v>0.068082</v>
       </c>
       <c r="C621" t="n">
         <v>0.317935</v>
@@ -8500,7 +8500,7 @@
         </is>
       </c>
       <c r="B622" t="n">
-        <v>0.068146</v>
+        <v>0.068352</v>
       </c>
       <c r="C622" t="n">
         <v>0.315217</v>
@@ -8513,7 +8513,7 @@
         </is>
       </c>
       <c r="B623" t="n">
-        <v>0.068202</v>
+        <v>0.068749</v>
       </c>
       <c r="C623" t="n">
         <v>0.3125</v>
@@ -8526,7 +8526,7 @@
         </is>
       </c>
       <c r="B624" t="n">
-        <v>0.068441</v>
+        <v>0.06902999999999999</v>
       </c>
       <c r="C624" t="n">
         <v>0.309783</v>
@@ -8539,7 +8539,7 @@
         </is>
       </c>
       <c r="B625" t="n">
-        <v>0.068899</v>
+        <v>0.06944</v>
       </c>
       <c r="C625" t="n">
         <v>0.307065</v>
@@ -8552,7 +8552,7 @@
         </is>
       </c>
       <c r="B626" t="n">
-        <v>0.069064</v>
+        <v>0.069482</v>
       </c>
       <c r="C626" t="n">
         <v>0.304348</v>
@@ -8565,7 +8565,7 @@
         </is>
       </c>
       <c r="B627" t="n">
-        <v>0.06923899999999999</v>
+        <v>0.069589</v>
       </c>
       <c r="C627" t="n">
         <v>0.30163</v>
@@ -8578,7 +8578,7 @@
         </is>
       </c>
       <c r="B628" t="n">
-        <v>0.069296</v>
+        <v>0.070314</v>
       </c>
       <c r="C628" t="n">
         <v>0.298913</v>
@@ -8591,7 +8591,7 @@
         </is>
       </c>
       <c r="B629" t="n">
-        <v>0.070227</v>
+        <v>0.073423</v>
       </c>
       <c r="C629" t="n">
         <v>0.296196</v>
@@ -8604,7 +8604,7 @@
         </is>
       </c>
       <c r="B630" t="n">
-        <v>0.07330200000000001</v>
+        <v>0.074058</v>
       </c>
       <c r="C630" t="n">
         <v>0.293478</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="B631" t="n">
-        <v>0.073543</v>
+        <v>0.074308</v>
       </c>
       <c r="C631" t="n">
         <v>0.290761</v>
@@ -8630,7 +8630,7 @@
         </is>
       </c>
       <c r="B632" t="n">
-        <v>0.074307</v>
+        <v>0.074473</v>
       </c>
       <c r="C632" t="n">
         <v>0.288043</v>
@@ -8643,7 +8643,7 @@
         </is>
       </c>
       <c r="B633" t="n">
-        <v>0.074346</v>
+        <v>0.074714</v>
       </c>
       <c r="C633" t="n">
         <v>0.285326</v>
@@ -8656,7 +8656,7 @@
         </is>
       </c>
       <c r="B634" t="n">
-        <v>0.07491100000000001</v>
+        <v>0.07547</v>
       </c>
       <c r="C634" t="n">
         <v>0.282609</v>
@@ -8669,7 +8669,7 @@
         </is>
       </c>
       <c r="B635" t="n">
-        <v>0.07529</v>
+        <v>0.07622900000000001</v>
       </c>
       <c r="C635" t="n">
         <v>0.279891</v>
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="B636" t="n">
-        <v>0.07605199999999999</v>
+        <v>0.0765</v>
       </c>
       <c r="C636" t="n">
         <v>0.277174</v>
@@ -8695,7 +8695,7 @@
         </is>
       </c>
       <c r="B637" t="n">
-        <v>0.076196</v>
+        <v>0.07653699999999999</v>
       </c>
       <c r="C637" t="n">
         <v>0.274457</v>
@@ -8708,7 +8708,7 @@
         </is>
       </c>
       <c r="B638" t="n">
-        <v>0.076956</v>
+        <v>0.077222</v>
       </c>
       <c r="C638" t="n">
         <v>0.271739</v>
@@ -8721,7 +8721,7 @@
         </is>
       </c>
       <c r="B639" t="n">
-        <v>0.077029</v>
+        <v>0.077343</v>
       </c>
       <c r="C639" t="n">
         <v>0.269022</v>
@@ -8734,7 +8734,7 @@
         </is>
       </c>
       <c r="B640" t="n">
-        <v>0.07708</v>
+        <v>0.077837</v>
       </c>
       <c r="C640" t="n">
         <v>0.266304</v>
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="B641" t="n">
-        <v>0.077691</v>
+        <v>0.077984</v>
       </c>
       <c r="C641" t="n">
         <v>0.263587</v>
@@ -8760,7 +8760,7 @@
         </is>
       </c>
       <c r="B642" t="n">
-        <v>0.07833</v>
+        <v>0.078458</v>
       </c>
       <c r="C642" t="n">
         <v>0.26087</v>
@@ -8773,7 +8773,7 @@
         </is>
       </c>
       <c r="B643" t="n">
-        <v>0.07838100000000001</v>
+        <v>0.078566</v>
       </c>
       <c r="C643" t="n">
         <v>0.258152</v>
@@ -8786,7 +8786,7 @@
         </is>
       </c>
       <c r="B644" t="n">
-        <v>0.0788</v>
+        <v>0.079149</v>
       </c>
       <c r="C644" t="n">
         <v>0.255435</v>
@@ -8799,7 +8799,7 @@
         </is>
       </c>
       <c r="B645" t="n">
-        <v>0.079017</v>
+        <v>0.080973</v>
       </c>
       <c r="C645" t="n">
         <v>0.252717</v>
@@ -8812,7 +8812,7 @@
         </is>
       </c>
       <c r="B646" t="n">
-        <v>0.080416</v>
+        <v>0.081134</v>
       </c>
       <c r="C646" t="n">
         <v>0.25</v>
@@ -8825,7 +8825,7 @@
         </is>
       </c>
       <c r="B647" t="n">
-        <v>0.080985</v>
+        <v>0.08139200000000001</v>
       </c>
       <c r="C647" t="n">
         <v>0.247283</v>
@@ -8838,7 +8838,7 @@
         </is>
       </c>
       <c r="B648" t="n">
-        <v>0.08100400000000001</v>
+        <v>0.081552</v>
       </c>
       <c r="C648" t="n">
         <v>0.244565</v>
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="B649" t="n">
-        <v>0.081181</v>
+        <v>0.082118</v>
       </c>
       <c r="C649" t="n">
         <v>0.241848</v>
@@ -8864,7 +8864,7 @@
         </is>
       </c>
       <c r="B650" t="n">
-        <v>0.082181</v>
+        <v>0.08264299999999999</v>
       </c>
       <c r="C650" t="n">
         <v>0.23913</v>
@@ -8877,7 +8877,7 @@
         </is>
       </c>
       <c r="B651" t="n">
-        <v>0.08244</v>
+        <v>0.08279599999999999</v>
       </c>
       <c r="C651" t="n">
         <v>0.236413</v>
@@ -8890,7 +8890,7 @@
         </is>
       </c>
       <c r="B652" t="n">
-        <v>0.085978</v>
+        <v>0.085548</v>
       </c>
       <c r="C652" t="n">
         <v>0.233696</v>
@@ -8903,7 +8903,7 @@
         </is>
       </c>
       <c r="B653" t="n">
-        <v>0.08612599999999999</v>
+        <v>0.086107</v>
       </c>
       <c r="C653" t="n">
         <v>0.230978</v>
@@ -8916,7 +8916,7 @@
         </is>
       </c>
       <c r="B654" t="n">
-        <v>0.086204</v>
+        <v>0.086483</v>
       </c>
       <c r="C654" t="n">
         <v>0.228261</v>
@@ -8929,7 +8929,7 @@
         </is>
       </c>
       <c r="B655" t="n">
-        <v>0.086256</v>
+        <v>0.08661199999999999</v>
       </c>
       <c r="C655" t="n">
         <v>0.225543</v>
@@ -8942,7 +8942,7 @@
         </is>
       </c>
       <c r="B656" t="n">
-        <v>0.08687400000000001</v>
+        <v>0.086878</v>
       </c>
       <c r="C656" t="n">
         <v>0.222826</v>
@@ -8955,7 +8955,7 @@
         </is>
       </c>
       <c r="B657" t="n">
-        <v>0.087659</v>
+        <v>0.087851</v>
       </c>
       <c r="C657" t="n">
         <v>0.220109</v>
@@ -8968,7 +8968,7 @@
         </is>
       </c>
       <c r="B658" t="n">
-        <v>0.08814900000000001</v>
+        <v>0.087907</v>
       </c>
       <c r="C658" t="n">
         <v>0.217391</v>
@@ -8981,7 +8981,7 @@
         </is>
       </c>
       <c r="B659" t="n">
-        <v>0.088365</v>
+        <v>0.088653</v>
       </c>
       <c r="C659" t="n">
         <v>0.214674</v>
@@ -8994,7 +8994,7 @@
         </is>
       </c>
       <c r="B660" t="n">
-        <v>0.088528</v>
+        <v>0.08876299999999999</v>
       </c>
       <c r="C660" t="n">
         <v>0.211957</v>
@@ -9007,7 +9007,7 @@
         </is>
       </c>
       <c r="B661" t="n">
-        <v>0.08855399999999999</v>
+        <v>0.088991</v>
       </c>
       <c r="C661" t="n">
         <v>0.209239</v>
@@ -9020,7 +9020,7 @@
         </is>
       </c>
       <c r="B662" t="n">
-        <v>0.088811</v>
+        <v>0.089158</v>
       </c>
       <c r="C662" t="n">
         <v>0.206522</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="B663" t="n">
-        <v>0.088953</v>
+        <v>0.089752</v>
       </c>
       <c r="C663" t="n">
         <v>0.203804</v>
@@ -9046,7 +9046,7 @@
         </is>
       </c>
       <c r="B664" t="n">
-        <v>0.089433</v>
+        <v>0.090766</v>
       </c>
       <c r="C664" t="n">
         <v>0.201087</v>
@@ -9059,7 +9059,7 @@
         </is>
       </c>
       <c r="B665" t="n">
-        <v>0.090734</v>
+        <v>0.091445</v>
       </c>
       <c r="C665" t="n">
         <v>0.19837</v>
@@ -9072,7 +9072,7 @@
         </is>
       </c>
       <c r="B666" t="n">
-        <v>0.091629</v>
+        <v>0.092543</v>
       </c>
       <c r="C666" t="n">
         <v>0.195652</v>
@@ -9085,7 +9085,7 @@
         </is>
       </c>
       <c r="B667" t="n">
-        <v>0.09202200000000001</v>
+        <v>0.094439</v>
       </c>
       <c r="C667" t="n">
         <v>0.192935</v>
@@ -9098,7 +9098,7 @@
         </is>
       </c>
       <c r="B668" t="n">
-        <v>0.094086</v>
+        <v>0.095425</v>
       </c>
       <c r="C668" t="n">
         <v>0.190217</v>
@@ -9111,7 +9111,7 @@
         </is>
       </c>
       <c r="B669" t="n">
-        <v>0.09517100000000001</v>
+        <v>0.096299</v>
       </c>
       <c r="C669" t="n">
         <v>0.1875</v>
@@ -9124,7 +9124,7 @@
         </is>
       </c>
       <c r="B670" t="n">
-        <v>0.09618699999999999</v>
+        <v>0.096604</v>
       </c>
       <c r="C670" t="n">
         <v>0.184783</v>
@@ -9137,7 +9137,7 @@
         </is>
       </c>
       <c r="B671" t="n">
-        <v>0.0965</v>
+        <v>0.09761300000000001</v>
       </c>
       <c r="C671" t="n">
         <v>0.182065</v>
@@ -9150,7 +9150,7 @@
         </is>
       </c>
       <c r="B672" t="n">
-        <v>0.09735000000000001</v>
+        <v>0.09829499999999999</v>
       </c>
       <c r="C672" t="n">
         <v>0.179348</v>
@@ -9163,7 +9163,7 @@
         </is>
       </c>
       <c r="B673" t="n">
-        <v>0.097931</v>
+        <v>0.098299</v>
       </c>
       <c r="C673" t="n">
         <v>0.17663</v>
@@ -9176,7 +9176,7 @@
         </is>
       </c>
       <c r="B674" t="n">
-        <v>0.098305</v>
+        <v>0.101718</v>
       </c>
       <c r="C674" t="n">
         <v>0.173913</v>
@@ -9189,7 +9189,7 @@
         </is>
       </c>
       <c r="B675" t="n">
-        <v>0.101049</v>
+        <v>0.103646</v>
       </c>
       <c r="C675" t="n">
         <v>0.171196</v>
@@ -9202,7 +9202,7 @@
         </is>
       </c>
       <c r="B676" t="n">
-        <v>0.103724</v>
+        <v>0.105399</v>
       </c>
       <c r="C676" t="n">
         <v>0.168478</v>
@@ -9215,7 +9215,7 @@
         </is>
       </c>
       <c r="B677" t="n">
-        <v>0.105071</v>
+        <v>0.105403</v>
       </c>
       <c r="C677" t="n">
         <v>0.165761</v>
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="B678" t="n">
-        <v>0.105274</v>
+        <v>0.10681</v>
       </c>
       <c r="C678" t="n">
         <v>0.163043</v>
@@ -9241,7 +9241,7 @@
         </is>
       </c>
       <c r="B679" t="n">
-        <v>0.106482</v>
+        <v>0.107357</v>
       </c>
       <c r="C679" t="n">
         <v>0.160326</v>
@@ -9254,7 +9254,7 @@
         </is>
       </c>
       <c r="B680" t="n">
-        <v>0.107524</v>
+        <v>0.108762</v>
       </c>
       <c r="C680" t="n">
         <v>0.157609</v>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="B681" t="n">
-        <v>0.108954</v>
+        <v>0.109688</v>
       </c>
       <c r="C681" t="n">
         <v>0.154891</v>
@@ -9280,7 +9280,7 @@
         </is>
       </c>
       <c r="B682" t="n">
-        <v>0.109672</v>
+        <v>0.109882</v>
       </c>
       <c r="C682" t="n">
         <v>0.152174</v>
@@ -9293,7 +9293,7 @@
         </is>
       </c>
       <c r="B683" t="n">
-        <v>0.110959</v>
+        <v>0.1109</v>
       </c>
       <c r="C683" t="n">
         <v>0.149457</v>
@@ -9306,7 +9306,7 @@
         </is>
       </c>
       <c r="B684" t="n">
-        <v>0.111819</v>
+        <v>0.111855</v>
       </c>
       <c r="C684" t="n">
         <v>0.146739</v>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="B685" t="n">
-        <v>0.113502</v>
+        <v>0.113799</v>
       </c>
       <c r="C685" t="n">
         <v>0.144022</v>
@@ -9332,7 +9332,7 @@
         </is>
       </c>
       <c r="B686" t="n">
-        <v>0.114283</v>
+        <v>0.114568</v>
       </c>
       <c r="C686" t="n">
         <v>0.141304</v>
@@ -9345,7 +9345,7 @@
         </is>
       </c>
       <c r="B687" t="n">
-        <v>0.114515</v>
+        <v>0.11507</v>
       </c>
       <c r="C687" t="n">
         <v>0.138587</v>
@@ -9358,7 +9358,7 @@
         </is>
       </c>
       <c r="B688" t="n">
-        <v>0.115027</v>
+        <v>0.115622</v>
       </c>
       <c r="C688" t="n">
         <v>0.13587</v>
@@ -9371,7 +9371,7 @@
         </is>
       </c>
       <c r="B689" t="n">
-        <v>0.116099</v>
+        <v>0.116168</v>
       </c>
       <c r="C689" t="n">
         <v>0.133152</v>
@@ -9384,7 +9384,7 @@
         </is>
       </c>
       <c r="B690" t="n">
-        <v>0.116118</v>
+        <v>0.11659</v>
       </c>
       <c r="C690" t="n">
         <v>0.130435</v>
@@ -9397,7 +9397,7 @@
         </is>
       </c>
       <c r="B691" t="n">
-        <v>0.116387</v>
+        <v>0.117061</v>
       </c>
       <c r="C691" t="n">
         <v>0.127717</v>
@@ -9410,7 +9410,7 @@
         </is>
       </c>
       <c r="B692" t="n">
-        <v>0.117837</v>
+        <v>0.117137</v>
       </c>
       <c r="C692" t="n">
         <v>0.125</v>
@@ -9423,7 +9423,7 @@
         </is>
       </c>
       <c r="B693" t="n">
-        <v>0.118044</v>
+        <v>0.117178</v>
       </c>
       <c r="C693" t="n">
         <v>0.122283</v>
@@ -9436,7 +9436,7 @@
         </is>
       </c>
       <c r="B694" t="n">
-        <v>0.119071</v>
+        <v>0.119316</v>
       </c>
       <c r="C694" t="n">
         <v>0.119565</v>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="B695" t="n">
-        <v>0.12081</v>
+        <v>0.120913</v>
       </c>
       <c r="C695" t="n">
         <v>0.116848</v>
@@ -9462,7 +9462,7 @@
         </is>
       </c>
       <c r="B696" t="n">
-        <v>0.122077</v>
+        <v>0.122737</v>
       </c>
       <c r="C696" t="n">
         <v>0.11413</v>
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="B697" t="n">
-        <v>0.122477</v>
+        <v>0.123296</v>
       </c>
       <c r="C697" t="n">
         <v>0.111413</v>
@@ -9488,7 +9488,7 @@
         </is>
       </c>
       <c r="B698" t="n">
-        <v>0.123732</v>
+        <v>0.123873</v>
       </c>
       <c r="C698" t="n">
         <v>0.108696</v>
@@ -9501,7 +9501,7 @@
         </is>
       </c>
       <c r="B699" t="n">
-        <v>0.123957</v>
+        <v>0.123944</v>
       </c>
       <c r="C699" t="n">
         <v>0.105978</v>
@@ -9514,7 +9514,7 @@
         </is>
       </c>
       <c r="B700" t="n">
-        <v>0.124101</v>
+        <v>0.124359</v>
       </c>
       <c r="C700" t="n">
         <v>0.103261</v>
@@ -9527,7 +9527,7 @@
         </is>
       </c>
       <c r="B701" t="n">
-        <v>0.124759</v>
+        <v>0.125015</v>
       </c>
       <c r="C701" t="n">
         <v>0.100543</v>
@@ -9540,7 +9540,7 @@
         </is>
       </c>
       <c r="B702" t="n">
-        <v>0.125713</v>
+        <v>0.125158</v>
       </c>
       <c r="C702" t="n">
         <v>0.097826</v>
@@ -9553,7 +9553,7 @@
         </is>
       </c>
       <c r="B703" t="n">
-        <v>0.126254</v>
+        <v>0.126295</v>
       </c>
       <c r="C703" t="n">
         <v>0.095109</v>
@@ -9566,7 +9566,7 @@
         </is>
       </c>
       <c r="B704" t="n">
-        <v>0.134325</v>
+        <v>0.134601</v>
       </c>
       <c r="C704" t="n">
         <v>0.092391</v>
@@ -9579,7 +9579,7 @@
         </is>
       </c>
       <c r="B705" t="n">
-        <v>0.135263</v>
+        <v>0.135407</v>
       </c>
       <c r="C705" t="n">
         <v>0.089674</v>
@@ -9592,7 +9592,7 @@
         </is>
       </c>
       <c r="B706" t="n">
-        <v>0.136398</v>
+        <v>0.137024</v>
       </c>
       <c r="C706" t="n">
         <v>0.08695700000000001</v>
@@ -9605,7 +9605,7 @@
         </is>
       </c>
       <c r="B707" t="n">
-        <v>0.138663</v>
+        <v>0.138687</v>
       </c>
       <c r="C707" t="n">
         <v>0.08423899999999999</v>
@@ -9618,7 +9618,7 @@
         </is>
       </c>
       <c r="B708" t="n">
-        <v>0.141753</v>
+        <v>0.141943</v>
       </c>
       <c r="C708" t="n">
         <v>0.081522</v>
@@ -9631,7 +9631,7 @@
         </is>
       </c>
       <c r="B709" t="n">
-        <v>0.143679</v>
+        <v>0.143678</v>
       </c>
       <c r="C709" t="n">
         <v>0.078804</v>
@@ -9644,7 +9644,7 @@
         </is>
       </c>
       <c r="B710" t="n">
-        <v>0.143914</v>
+        <v>0.144696</v>
       </c>
       <c r="C710" t="n">
         <v>0.076087</v>
@@ -9657,7 +9657,7 @@
         </is>
       </c>
       <c r="B711" t="n">
-        <v>0.148269</v>
+        <v>0.148666</v>
       </c>
       <c r="C711" t="n">
         <v>0.07337</v>
@@ -9670,7 +9670,7 @@
         </is>
       </c>
       <c r="B712" t="n">
-        <v>0.149759</v>
+        <v>0.150424</v>
       </c>
       <c r="C712" t="n">
         <v>0.07065200000000001</v>
@@ -9683,7 +9683,7 @@
         </is>
       </c>
       <c r="B713" t="n">
-        <v>0.156339</v>
+        <v>0.156889</v>
       </c>
       <c r="C713" t="n">
         <v>0.067935</v>
@@ -9696,7 +9696,7 @@
         </is>
       </c>
       <c r="B714" t="n">
-        <v>0.157112</v>
+        <v>0.157838</v>
       </c>
       <c r="C714" t="n">
         <v>0.065217</v>
@@ -9709,7 +9709,7 @@
         </is>
       </c>
       <c r="B715" t="n">
-        <v>0.157287</v>
+        <v>0.157939</v>
       </c>
       <c r="C715" t="n">
         <v>0.0625</v>
@@ -9722,7 +9722,7 @@
         </is>
       </c>
       <c r="B716" t="n">
-        <v>0.159812</v>
+        <v>0.160807</v>
       </c>
       <c r="C716" t="n">
         <v>0.059783</v>
@@ -9735,7 +9735,7 @@
         </is>
       </c>
       <c r="B717" t="n">
-        <v>0.161449</v>
+        <v>0.161352</v>
       </c>
       <c r="C717" t="n">
         <v>0.057065</v>
@@ -9748,7 +9748,7 @@
         </is>
       </c>
       <c r="B718" t="n">
-        <v>0.162335</v>
+        <v>0.163317</v>
       </c>
       <c r="C718" t="n">
         <v>0.054348</v>
@@ -9761,7 +9761,7 @@
         </is>
       </c>
       <c r="B719" t="n">
-        <v>0.164206</v>
+        <v>0.165198</v>
       </c>
       <c r="C719" t="n">
         <v>0.05163</v>
@@ -9774,7 +9774,7 @@
         </is>
       </c>
       <c r="B720" t="n">
-        <v>0.170176</v>
+        <v>0.169826</v>
       </c>
       <c r="C720" t="n">
         <v>0.048913</v>
@@ -9787,7 +9787,7 @@
         </is>
       </c>
       <c r="B721" t="n">
-        <v>0.172562</v>
+        <v>0.172227</v>
       </c>
       <c r="C721" t="n">
         <v>0.046196</v>
@@ -9800,7 +9800,7 @@
         </is>
       </c>
       <c r="B722" t="n">
-        <v>0.172807</v>
+        <v>0.173671</v>
       </c>
       <c r="C722" t="n">
         <v>0.043478</v>
@@ -9813,7 +9813,7 @@
         </is>
       </c>
       <c r="B723" t="n">
-        <v>0.182656</v>
+        <v>0.182917</v>
       </c>
       <c r="C723" t="n">
         <v>0.040761</v>
@@ -9826,7 +9826,7 @@
         </is>
       </c>
       <c r="B724" t="n">
-        <v>0.184453</v>
+        <v>0.183538</v>
       </c>
       <c r="C724" t="n">
         <v>0.038043</v>
@@ -9839,7 +9839,7 @@
         </is>
       </c>
       <c r="B725" t="n">
-        <v>0.184498</v>
+        <v>0.185547</v>
       </c>
       <c r="C725" t="n">
         <v>0.035326</v>
@@ -9852,7 +9852,7 @@
         </is>
       </c>
       <c r="B726" t="n">
-        <v>0.200409</v>
+        <v>0.201026</v>
       </c>
       <c r="C726" t="n">
         <v>0.032609</v>
@@ -9865,7 +9865,7 @@
         </is>
       </c>
       <c r="B727" t="n">
-        <v>0.205404</v>
+        <v>0.20656</v>
       </c>
       <c r="C727" t="n">
         <v>0.029891</v>
@@ -9878,7 +9878,7 @@
         </is>
       </c>
       <c r="B728" t="n">
-        <v>0.213223</v>
+        <v>0.214642</v>
       </c>
       <c r="C728" t="n">
         <v>0.027174</v>
@@ -9891,7 +9891,7 @@
         </is>
       </c>
       <c r="B729" t="n">
-        <v>0.213544</v>
+        <v>0.215048</v>
       </c>
       <c r="C729" t="n">
         <v>0.024457</v>
@@ -9904,7 +9904,7 @@
         </is>
       </c>
       <c r="B730" t="n">
-        <v>0.215819</v>
+        <v>0.217258</v>
       </c>
       <c r="C730" t="n">
         <v>0.021739</v>
@@ -9917,7 +9917,7 @@
         </is>
       </c>
       <c r="B731" t="n">
-        <v>0.225764</v>
+        <v>0.225119</v>
       </c>
       <c r="C731" t="n">
         <v>0.019022</v>
@@ -9930,7 +9930,7 @@
         </is>
       </c>
       <c r="B732" t="n">
-        <v>0.231673</v>
+        <v>0.23286</v>
       </c>
       <c r="C732" t="n">
         <v>0.016304</v>
@@ -9943,7 +9943,7 @@
         </is>
       </c>
       <c r="B733" t="n">
-        <v>0.238669</v>
+        <v>0.239725</v>
       </c>
       <c r="C733" t="n">
         <v>0.013587</v>
@@ -9956,7 +9956,7 @@
         </is>
       </c>
       <c r="B734" t="n">
-        <v>0.258349</v>
+        <v>0.258728</v>
       </c>
       <c r="C734" t="n">
         <v>0.01087</v>
@@ -9969,7 +9969,7 @@
         </is>
       </c>
       <c r="B735" t="n">
-        <v>0.272908</v>
+        <v>0.274641</v>
       </c>
       <c r="C735" t="n">
         <v>0.008152</v>
@@ -9982,7 +9982,7 @@
         </is>
       </c>
       <c r="B736" t="n">
-        <v>0.298613</v>
+        <v>0.299755</v>
       </c>
       <c r="C736" t="n">
         <v>0.005435</v>
@@ -9995,7 +9995,7 @@
         </is>
       </c>
       <c r="B737" t="n">
-        <v>0.426501</v>
+        <v>0.428609</v>
       </c>
       <c r="C737" t="n">
         <v>0.002717</v>
@@ -10021,7 +10021,7 @@
         </is>
       </c>
       <c r="B739" t="n">
-        <v>0.000106</v>
+        <v>0.000105</v>
       </c>
       <c r="C739" t="n">
         <v>0.997283</v>
@@ -10034,7 +10034,7 @@
         </is>
       </c>
       <c r="B740" t="n">
-        <v>0.000316</v>
+        <v>0.000317</v>
       </c>
       <c r="C740" t="n">
         <v>0.994565</v>
@@ -10060,7 +10060,7 @@
         </is>
       </c>
       <c r="B742" t="n">
-        <v>0.001029</v>
+        <v>0.00103</v>
       </c>
       <c r="C742" t="n">
         <v>0.98913</v>
@@ -10073,7 +10073,7 @@
         </is>
       </c>
       <c r="B743" t="n">
-        <v>0.001639</v>
+        <v>0.001646</v>
       </c>
       <c r="C743" t="n">
         <v>0.986413</v>
@@ -10086,7 +10086,7 @@
         </is>
       </c>
       <c r="B744" t="n">
-        <v>0.001916</v>
+        <v>0.001912</v>
       </c>
       <c r="C744" t="n">
         <v>0.983696</v>
@@ -10099,7 +10099,7 @@
         </is>
       </c>
       <c r="B745" t="n">
-        <v>0.002004</v>
+        <v>0.002011</v>
       </c>
       <c r="C745" t="n">
         <v>0.980978</v>
@@ -10112,7 +10112,7 @@
         </is>
       </c>
       <c r="B746" t="n">
-        <v>0.002189</v>
+        <v>0.002201</v>
       </c>
       <c r="C746" t="n">
         <v>0.978261</v>
@@ -10125,7 +10125,7 @@
         </is>
       </c>
       <c r="B747" t="n">
-        <v>0.002312</v>
+        <v>0.002323</v>
       </c>
       <c r="C747" t="n">
         <v>0.975543</v>
@@ -10138,7 +10138,7 @@
         </is>
       </c>
       <c r="B748" t="n">
-        <v>0.002925</v>
+        <v>0.002933</v>
       </c>
       <c r="C748" t="n">
         <v>0.972826</v>
@@ -10151,7 +10151,7 @@
         </is>
       </c>
       <c r="B749" t="n">
-        <v>0.002943</v>
+        <v>0.002958</v>
       </c>
       <c r="C749" t="n">
         <v>0.970109</v>
@@ -10164,7 +10164,7 @@
         </is>
       </c>
       <c r="B750" t="n">
-        <v>0.003181</v>
+        <v>0.003188</v>
       </c>
       <c r="C750" t="n">
         <v>0.967391</v>
@@ -10177,7 +10177,7 @@
         </is>
       </c>
       <c r="B751" t="n">
-        <v>0.003397</v>
+        <v>0.003416</v>
       </c>
       <c r="C751" t="n">
         <v>0.964674</v>
@@ -10190,7 +10190,7 @@
         </is>
       </c>
       <c r="B752" t="n">
-        <v>0.004178</v>
+        <v>0.004184</v>
       </c>
       <c r="C752" t="n">
         <v>0.961957</v>
@@ -10203,7 +10203,7 @@
         </is>
       </c>
       <c r="B753" t="n">
-        <v>0.004238</v>
+        <v>0.004246</v>
       </c>
       <c r="C753" t="n">
         <v>0.959239</v>
@@ -10216,7 +10216,7 @@
         </is>
       </c>
       <c r="B754" t="n">
-        <v>0.004693</v>
+        <v>0.004701</v>
       </c>
       <c r="C754" t="n">
         <v>0.956522</v>
@@ -10229,7 +10229,7 @@
         </is>
       </c>
       <c r="B755" t="n">
-        <v>0.004722</v>
+        <v>0.004752</v>
       </c>
       <c r="C755" t="n">
         <v>0.953804</v>
@@ -10242,7 +10242,7 @@
         </is>
       </c>
       <c r="B756" t="n">
-        <v>0.004757</v>
+        <v>0.004786</v>
       </c>
       <c r="C756" t="n">
         <v>0.951087</v>
@@ -10255,7 +10255,7 @@
         </is>
       </c>
       <c r="B757" t="n">
-        <v>0.004784</v>
+        <v>0.004796</v>
       </c>
       <c r="C757" t="n">
         <v>0.94837</v>
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="B758" t="n">
-        <v>0.0049</v>
+        <v>0.004865</v>
       </c>
       <c r="C758" t="n">
         <v>0.945652</v>
@@ -10281,7 +10281,7 @@
         </is>
       </c>
       <c r="B759" t="n">
-        <v>0.004973</v>
+        <v>0.004998</v>
       </c>
       <c r="C759" t="n">
         <v>0.942935</v>
@@ -10294,7 +10294,7 @@
         </is>
       </c>
       <c r="B760" t="n">
-        <v>0.005084</v>
+        <v>0.005115</v>
       </c>
       <c r="C760" t="n">
         <v>0.940217</v>
@@ -10307,7 +10307,7 @@
         </is>
       </c>
       <c r="B761" t="n">
-        <v>0.005235</v>
+        <v>0.005228</v>
       </c>
       <c r="C761" t="n">
         <v>0.9375</v>
@@ -10320,7 +10320,7 @@
         </is>
       </c>
       <c r="B762" t="n">
-        <v>0.005247</v>
+        <v>0.005265</v>
       </c>
       <c r="C762" t="n">
         <v>0.934783</v>
@@ -10333,7 +10333,7 @@
         </is>
       </c>
       <c r="B763" t="n">
-        <v>0.005889</v>
+        <v>0.005912</v>
       </c>
       <c r="C763" t="n">
         <v>0.932065</v>
@@ -10346,7 +10346,7 @@
         </is>
       </c>
       <c r="B764" t="n">
-        <v>0.006123</v>
+        <v>0.006143</v>
       </c>
       <c r="C764" t="n">
         <v>0.929348</v>
@@ -10359,7 +10359,7 @@
         </is>
       </c>
       <c r="B765" t="n">
-        <v>0.006215</v>
+        <v>0.006235</v>
       </c>
       <c r="C765" t="n">
         <v>0.92663</v>
@@ -10372,7 +10372,7 @@
         </is>
       </c>
       <c r="B766" t="n">
-        <v>0.006807</v>
+        <v>0.006822</v>
       </c>
       <c r="C766" t="n">
         <v>0.923913</v>
@@ -10385,7 +10385,7 @@
         </is>
       </c>
       <c r="B767" t="n">
-        <v>0.007615</v>
+        <v>0.007634</v>
       </c>
       <c r="C767" t="n">
         <v>0.921196</v>
@@ -10398,7 +10398,7 @@
         </is>
       </c>
       <c r="B768" t="n">
-        <v>0.007632</v>
+        <v>0.007675</v>
       </c>
       <c r="C768" t="n">
         <v>0.918478</v>
@@ -10411,7 +10411,7 @@
         </is>
       </c>
       <c r="B769" t="n">
-        <v>0.00791</v>
+        <v>0.007958</v>
       </c>
       <c r="C769" t="n">
         <v>0.915761</v>
@@ -10424,7 +10424,7 @@
         </is>
       </c>
       <c r="B770" t="n">
-        <v>0.008099</v>
+        <v>0.008126</v>
       </c>
       <c r="C770" t="n">
         <v>0.913043</v>
@@ -10437,7 +10437,7 @@
         </is>
       </c>
       <c r="B771" t="n">
-        <v>0.008297000000000001</v>
+        <v>0.008257</v>
       </c>
       <c r="C771" t="n">
         <v>0.910326</v>
@@ -10450,7 +10450,7 @@
         </is>
       </c>
       <c r="B772" t="n">
-        <v>0.008336</v>
+        <v>0.008359999999999999</v>
       </c>
       <c r="C772" t="n">
         <v>0.907609</v>
@@ -10463,7 +10463,7 @@
         </is>
       </c>
       <c r="B773" t="n">
-        <v>0.008576</v>
+        <v>0.008571</v>
       </c>
       <c r="C773" t="n">
         <v>0.904891</v>
@@ -10476,7 +10476,7 @@
         </is>
       </c>
       <c r="B774" t="n">
-        <v>0.008579</v>
+        <v>0.008628</v>
       </c>
       <c r="C774" t="n">
         <v>0.902174</v>
@@ -10489,7 +10489,7 @@
         </is>
       </c>
       <c r="B775" t="n">
-        <v>0.008708</v>
+        <v>0.008725</v>
       </c>
       <c r="C775" t="n">
         <v>0.899457</v>
@@ -10502,7 +10502,7 @@
         </is>
       </c>
       <c r="B776" t="n">
-        <v>0.009043000000000001</v>
+        <v>0.008998000000000001</v>
       </c>
       <c r="C776" t="n">
         <v>0.896739</v>
@@ -10515,7 +10515,7 @@
         </is>
       </c>
       <c r="B777" t="n">
-        <v>0.009559</v>
+        <v>0.00906</v>
       </c>
       <c r="C777" t="n">
         <v>0.894022</v>
@@ -10528,7 +10528,7 @@
         </is>
       </c>
       <c r="B778" t="n">
-        <v>0.009757</v>
+        <v>0.009608999999999999</v>
       </c>
       <c r="C778" t="n">
         <v>0.891304</v>
@@ -10541,7 +10541,7 @@
         </is>
       </c>
       <c r="B779" t="n">
-        <v>0.009771</v>
+        <v>0.009797999999999999</v>
       </c>
       <c r="C779" t="n">
         <v>0.888587</v>
@@ -10554,7 +10554,7 @@
         </is>
       </c>
       <c r="B780" t="n">
-        <v>0.010211</v>
+        <v>0.00983</v>
       </c>
       <c r="C780" t="n">
         <v>0.88587</v>
@@ -10567,7 +10567,7 @@
         </is>
       </c>
       <c r="B781" t="n">
-        <v>0.010386</v>
+        <v>0.010242</v>
       </c>
       <c r="C781" t="n">
         <v>0.883152</v>
@@ -10580,7 +10580,7 @@
         </is>
       </c>
       <c r="B782" t="n">
-        <v>0.010443</v>
+        <v>0.010397</v>
       </c>
       <c r="C782" t="n">
         <v>0.880435</v>
@@ -10593,7 +10593,7 @@
         </is>
       </c>
       <c r="B783" t="n">
-        <v>0.010479</v>
+        <v>0.010412</v>
       </c>
       <c r="C783" t="n">
         <v>0.877717</v>
@@ -10606,7 +10606,7 @@
         </is>
       </c>
       <c r="B784" t="n">
-        <v>0.011044</v>
+        <v>0.010432</v>
       </c>
       <c r="C784" t="n">
         <v>0.875</v>
@@ -10619,7 +10619,7 @@
         </is>
       </c>
       <c r="B785" t="n">
-        <v>0.011147</v>
+        <v>0.01111</v>
       </c>
       <c r="C785" t="n">
         <v>0.872283</v>
@@ -10632,7 +10632,7 @@
         </is>
       </c>
       <c r="B786" t="n">
-        <v>0.011271</v>
+        <v>0.011116</v>
       </c>
       <c r="C786" t="n">
         <v>0.869565</v>
@@ -10645,7 +10645,7 @@
         </is>
       </c>
       <c r="B787" t="n">
-        <v>0.011566</v>
+        <v>0.011299</v>
       </c>
       <c r="C787" t="n">
         <v>0.866848</v>
@@ -10658,7 +10658,7 @@
         </is>
       </c>
       <c r="B788" t="n">
-        <v>0.011602</v>
+        <v>0.011585</v>
       </c>
       <c r="C788" t="n">
         <v>0.86413</v>
@@ -10671,7 +10671,7 @@
         </is>
       </c>
       <c r="B789" t="n">
-        <v>0.011703</v>
+        <v>0.011599</v>
       </c>
       <c r="C789" t="n">
         <v>0.861413</v>
@@ -10684,7 +10684,7 @@
         </is>
       </c>
       <c r="B790" t="n">
-        <v>0.01197</v>
+        <v>0.011716</v>
       </c>
       <c r="C790" t="n">
         <v>0.858696</v>
@@ -10697,7 +10697,7 @@
         </is>
       </c>
       <c r="B791" t="n">
-        <v>0.012103</v>
+        <v>0.011996</v>
       </c>
       <c r="C791" t="n">
         <v>0.855978</v>
@@ -10710,7 +10710,7 @@
         </is>
       </c>
       <c r="B792" t="n">
-        <v>0.012309</v>
+        <v>0.012157</v>
       </c>
       <c r="C792" t="n">
         <v>0.853261</v>
@@ -10723,7 +10723,7 @@
         </is>
       </c>
       <c r="B793" t="n">
-        <v>0.012346</v>
+        <v>0.012306</v>
       </c>
       <c r="C793" t="n">
         <v>0.850543</v>
@@ -10736,7 +10736,7 @@
         </is>
       </c>
       <c r="B794" t="n">
-        <v>0.012684</v>
+        <v>0.012393</v>
       </c>
       <c r="C794" t="n">
         <v>0.847826</v>
@@ -10749,7 +10749,7 @@
         </is>
       </c>
       <c r="B795" t="n">
-        <v>0.012888</v>
+        <v>0.012762</v>
       </c>
       <c r="C795" t="n">
         <v>0.845109</v>
@@ -10762,7 +10762,7 @@
         </is>
       </c>
       <c r="B796" t="n">
-        <v>0.01303</v>
+        <v>0.012942</v>
       </c>
       <c r="C796" t="n">
         <v>0.842391</v>
@@ -10775,7 +10775,7 @@
         </is>
       </c>
       <c r="B797" t="n">
-        <v>0.013934</v>
+        <v>0.013054</v>
       </c>
       <c r="C797" t="n">
         <v>0.839674</v>
@@ -10788,7 +10788,7 @@
         </is>
       </c>
       <c r="B798" t="n">
-        <v>0.013945</v>
+        <v>0.013861</v>
       </c>
       <c r="C798" t="n">
         <v>0.836957</v>
@@ -10801,7 +10801,7 @@
         </is>
       </c>
       <c r="B799" t="n">
-        <v>0.014122</v>
+        <v>0.013956</v>
       </c>
       <c r="C799" t="n">
         <v>0.834239</v>
@@ -10814,7 +10814,7 @@
         </is>
       </c>
       <c r="B800" t="n">
-        <v>0.014495</v>
+        <v>0.014123</v>
       </c>
       <c r="C800" t="n">
         <v>0.831522</v>
@@ -10827,7 +10827,7 @@
         </is>
       </c>
       <c r="B801" t="n">
-        <v>0.014787</v>
+        <v>0.014502</v>
       </c>
       <c r="C801" t="n">
         <v>0.828804</v>
@@ -10840,7 +10840,7 @@
         </is>
       </c>
       <c r="B802" t="n">
-        <v>0.01479</v>
+        <v>0.014775</v>
       </c>
       <c r="C802" t="n">
         <v>0.826087</v>
@@ -10853,7 +10853,7 @@
         </is>
       </c>
       <c r="B803" t="n">
-        <v>0.014883</v>
+        <v>0.014876</v>
       </c>
       <c r="C803" t="n">
         <v>0.82337</v>
@@ -10866,7 +10866,7 @@
         </is>
       </c>
       <c r="B804" t="n">
-        <v>0.015267</v>
+        <v>0.014946</v>
       </c>
       <c r="C804" t="n">
         <v>0.820652</v>
@@ -10879,7 +10879,7 @@
         </is>
       </c>
       <c r="B805" t="n">
-        <v>0.015795</v>
+        <v>0.01528</v>
       </c>
       <c r="C805" t="n">
         <v>0.817935</v>
@@ -10892,7 +10892,7 @@
         </is>
       </c>
       <c r="B806" t="n">
-        <v>0.015816</v>
+        <v>0.015799</v>
       </c>
       <c r="C806" t="n">
         <v>0.815217</v>
@@ -10905,7 +10905,7 @@
         </is>
       </c>
       <c r="B807" t="n">
-        <v>0.015966</v>
+        <v>0.015805</v>
       </c>
       <c r="C807" t="n">
         <v>0.8125</v>
@@ -10918,7 +10918,7 @@
         </is>
       </c>
       <c r="B808" t="n">
-        <v>0.015972</v>
+        <v>0.015946</v>
       </c>
       <c r="C808" t="n">
         <v>0.809783</v>
@@ -10931,7 +10931,7 @@
         </is>
       </c>
       <c r="B809" t="n">
-        <v>0.016005</v>
+        <v>0.016025</v>
       </c>
       <c r="C809" t="n">
         <v>0.807065</v>
@@ -10944,7 +10944,7 @@
         </is>
       </c>
       <c r="B810" t="n">
-        <v>0.016271</v>
+        <v>0.016042</v>
       </c>
       <c r="C810" t="n">
         <v>0.804348</v>
@@ -10957,7 +10957,7 @@
         </is>
       </c>
       <c r="B811" t="n">
-        <v>0.016566</v>
+        <v>0.016299</v>
       </c>
       <c r="C811" t="n">
         <v>0.80163</v>
@@ -10970,7 +10970,7 @@
         </is>
       </c>
       <c r="B812" t="n">
-        <v>0.017071</v>
+        <v>0.016518</v>
       </c>
       <c r="C812" t="n">
         <v>0.798913</v>
@@ -10983,7 +10983,7 @@
         </is>
       </c>
       <c r="B813" t="n">
-        <v>0.017205</v>
+        <v>0.017137</v>
       </c>
       <c r="C813" t="n">
         <v>0.796196</v>
@@ -10996,7 +10996,7 @@
         </is>
       </c>
       <c r="B814" t="n">
-        <v>0.01771</v>
+        <v>0.01728</v>
       </c>
       <c r="C814" t="n">
         <v>0.793478</v>
@@ -11009,7 +11009,7 @@
         </is>
       </c>
       <c r="B815" t="n">
-        <v>0.017766</v>
+        <v>0.017749</v>
       </c>
       <c r="C815" t="n">
         <v>0.790761</v>
@@ -11022,7 +11022,7 @@
         </is>
       </c>
       <c r="B816" t="n">
-        <v>0.017797</v>
+        <v>0.017754</v>
       </c>
       <c r="C816" t="n">
         <v>0.788043</v>
@@ -11035,7 +11035,7 @@
         </is>
       </c>
       <c r="B817" t="n">
-        <v>0.017905</v>
+        <v>0.017805</v>
       </c>
       <c r="C817" t="n">
         <v>0.785326</v>
@@ -11048,7 +11048,7 @@
         </is>
       </c>
       <c r="B818" t="n">
-        <v>0.018062</v>
+        <v>0.017953</v>
       </c>
       <c r="C818" t="n">
         <v>0.782609</v>
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="B819" t="n">
-        <v>0.018066</v>
+        <v>0.018087</v>
       </c>
       <c r="C819" t="n">
         <v>0.779891</v>
@@ -11074,7 +11074,7 @@
         </is>
       </c>
       <c r="B820" t="n">
-        <v>0.018875</v>
+        <v>0.018144</v>
       </c>
       <c r="C820" t="n">
         <v>0.777174</v>
@@ -11087,7 +11087,7 @@
         </is>
       </c>
       <c r="B821" t="n">
-        <v>0.019268</v>
+        <v>0.018824</v>
       </c>
       <c r="C821" t="n">
         <v>0.774457</v>
@@ -11100,7 +11100,7 @@
         </is>
       </c>
       <c r="B822" t="n">
-        <v>0.0196</v>
+        <v>0.019304</v>
       </c>
       <c r="C822" t="n">
         <v>0.771739</v>
@@ -11113,7 +11113,7 @@
         </is>
       </c>
       <c r="B823" t="n">
-        <v>0.019866</v>
+        <v>0.019645</v>
       </c>
       <c r="C823" t="n">
         <v>0.769022</v>
@@ -11126,7 +11126,7 @@
         </is>
       </c>
       <c r="B824" t="n">
-        <v>0.020285</v>
+        <v>0.01985</v>
       </c>
       <c r="C824" t="n">
         <v>0.766304</v>
@@ -11139,7 +11139,7 @@
         </is>
       </c>
       <c r="B825" t="n">
-        <v>0.020629</v>
+        <v>0.020383</v>
       </c>
       <c r="C825" t="n">
         <v>0.763587</v>
@@ -11152,7 +11152,7 @@
         </is>
       </c>
       <c r="B826" t="n">
-        <v>0.020633</v>
+        <v>0.020609</v>
       </c>
       <c r="C826" t="n">
         <v>0.76087</v>
@@ -11165,7 +11165,7 @@
         </is>
       </c>
       <c r="B827" t="n">
-        <v>0.02122</v>
+        <v>0.020694</v>
       </c>
       <c r="C827" t="n">
         <v>0.758152</v>
@@ -11178,7 +11178,7 @@
         </is>
       </c>
       <c r="B828" t="n">
-        <v>0.021805</v>
+        <v>0.021065</v>
       </c>
       <c r="C828" t="n">
         <v>0.755435</v>
@@ -11191,7 +11191,7 @@
         </is>
       </c>
       <c r="B829" t="n">
-        <v>0.021974</v>
+        <v>0.021893</v>
       </c>
       <c r="C829" t="n">
         <v>0.752717</v>
@@ -11204,7 +11204,7 @@
         </is>
       </c>
       <c r="B830" t="n">
-        <v>0.022431</v>
+        <v>0.021942</v>
       </c>
       <c r="C830" t="n">
         <v>0.75</v>
@@ -11217,7 +11217,7 @@
         </is>
       </c>
       <c r="B831" t="n">
-        <v>0.022934</v>
+        <v>0.022449</v>
       </c>
       <c r="C831" t="n">
         <v>0.747283</v>
@@ -11230,7 +11230,7 @@
         </is>
       </c>
       <c r="B832" t="n">
-        <v>0.023179</v>
+        <v>0.022823</v>
       </c>
       <c r="C832" t="n">
         <v>0.744565</v>
@@ -11243,7 +11243,7 @@
         </is>
       </c>
       <c r="B833" t="n">
-        <v>0.023189</v>
+        <v>0.023176</v>
       </c>
       <c r="C833" t="n">
         <v>0.741848</v>
@@ -11256,7 +11256,7 @@
         </is>
       </c>
       <c r="B834" t="n">
-        <v>0.023234</v>
+        <v>0.023237</v>
       </c>
       <c r="C834" t="n">
         <v>0.73913</v>
@@ -11269,7 +11269,7 @@
         </is>
       </c>
       <c r="B835" t="n">
-        <v>0.023458</v>
+        <v>0.023269</v>
       </c>
       <c r="C835" t="n">
         <v>0.736413</v>
@@ -11282,7 +11282,7 @@
         </is>
       </c>
       <c r="B836" t="n">
-        <v>0.023499</v>
+        <v>0.02339</v>
       </c>
       <c r="C836" t="n">
         <v>0.733696</v>
@@ -11295,7 +11295,7 @@
         </is>
       </c>
       <c r="B837" t="n">
-        <v>0.023536</v>
+        <v>0.02341</v>
       </c>
       <c r="C837" t="n">
         <v>0.730978</v>
@@ -11308,7 +11308,7 @@
         </is>
       </c>
       <c r="B838" t="n">
-        <v>0.023693</v>
+        <v>0.023482</v>
       </c>
       <c r="C838" t="n">
         <v>0.728261</v>
@@ -11321,7 +11321,7 @@
         </is>
       </c>
       <c r="B839" t="n">
-        <v>0.023976</v>
+        <v>0.023812</v>
       </c>
       <c r="C839" t="n">
         <v>0.725543</v>
@@ -11334,7 +11334,7 @@
         </is>
       </c>
       <c r="B840" t="n">
-        <v>0.024432</v>
+        <v>0.024014</v>
       </c>
       <c r="C840" t="n">
         <v>0.722826</v>
@@ -11347,7 +11347,7 @@
         </is>
       </c>
       <c r="B841" t="n">
-        <v>0.024683</v>
+        <v>0.024262</v>
       </c>
       <c r="C841" t="n">
         <v>0.720109</v>
@@ -11360,7 +11360,7 @@
         </is>
       </c>
       <c r="B842" t="n">
-        <v>0.025274</v>
+        <v>0.02453</v>
       </c>
       <c r="C842" t="n">
         <v>0.717391</v>
@@ -11373,7 +11373,7 @@
         </is>
       </c>
       <c r="B843" t="n">
-        <v>0.025702</v>
+        <v>0.025216</v>
       </c>
       <c r="C843" t="n">
         <v>0.714674</v>
@@ -11386,7 +11386,7 @@
         </is>
       </c>
       <c r="B844" t="n">
-        <v>0.025758</v>
+        <v>0.025634</v>
       </c>
       <c r="C844" t="n">
         <v>0.711957</v>
@@ -11399,7 +11399,7 @@
         </is>
       </c>
       <c r="B845" t="n">
-        <v>0.026039</v>
+        <v>0.02585</v>
       </c>
       <c r="C845" t="n">
         <v>0.709239</v>
@@ -11412,7 +11412,7 @@
         </is>
       </c>
       <c r="B846" t="n">
-        <v>0.026233</v>
+        <v>0.026146</v>
       </c>
       <c r="C846" t="n">
         <v>0.706522</v>
@@ -11425,7 +11425,7 @@
         </is>
       </c>
       <c r="B847" t="n">
-        <v>0.026609</v>
+        <v>0.026286</v>
       </c>
       <c r="C847" t="n">
         <v>0.703804</v>
@@ -11438,7 +11438,7 @@
         </is>
       </c>
       <c r="B848" t="n">
-        <v>0.026673</v>
+        <v>0.026741</v>
       </c>
       <c r="C848" t="n">
         <v>0.701087</v>
@@ -11451,7 +11451,7 @@
         </is>
       </c>
       <c r="B849" t="n">
-        <v>0.026792</v>
+        <v>0.026779</v>
       </c>
       <c r="C849" t="n">
         <v>0.69837</v>
@@ -11464,7 +11464,7 @@
         </is>
       </c>
       <c r="B850" t="n">
-        <v>0.026997</v>
+        <v>0.026838</v>
       </c>
       <c r="C850" t="n">
         <v>0.695652</v>
@@ -11477,7 +11477,7 @@
         </is>
       </c>
       <c r="B851" t="n">
-        <v>0.027495</v>
+        <v>0.027163</v>
       </c>
       <c r="C851" t="n">
         <v>0.692935</v>
@@ -11490,7 +11490,7 @@
         </is>
       </c>
       <c r="B852" t="n">
-        <v>0.027521</v>
+        <v>0.0276</v>
       </c>
       <c r="C852" t="n">
         <v>0.690217</v>
@@ -11503,7 +11503,7 @@
         </is>
       </c>
       <c r="B853" t="n">
-        <v>0.027652</v>
+        <v>0.027602</v>
       </c>
       <c r="C853" t="n">
         <v>0.6875</v>
@@ -11516,7 +11516,7 @@
         </is>
       </c>
       <c r="B854" t="n">
-        <v>0.027689</v>
+        <v>0.027607</v>
       </c>
       <c r="C854" t="n">
         <v>0.684783</v>
@@ -11529,7 +11529,7 @@
         </is>
       </c>
       <c r="B855" t="n">
-        <v>0.027706</v>
+        <v>0.027668</v>
       </c>
       <c r="C855" t="n">
         <v>0.682065</v>
@@ -11542,7 +11542,7 @@
         </is>
       </c>
       <c r="B856" t="n">
-        <v>0.02773</v>
+        <v>0.027674</v>
       </c>
       <c r="C856" t="n">
         <v>0.679348</v>
@@ -11555,7 +11555,7 @@
         </is>
       </c>
       <c r="B857" t="n">
-        <v>0.027779</v>
+        <v>0.027695</v>
       </c>
       <c r="C857" t="n">
         <v>0.67663</v>
@@ -11568,7 +11568,7 @@
         </is>
       </c>
       <c r="B858" t="n">
-        <v>0.028564</v>
+        <v>0.027853</v>
       </c>
       <c r="C858" t="n">
         <v>0.673913</v>
@@ -11581,7 +11581,7 @@
         </is>
       </c>
       <c r="B859" t="n">
-        <v>0.029</v>
+        <v>0.028722</v>
       </c>
       <c r="C859" t="n">
         <v>0.671196</v>
@@ -11594,7 +11594,7 @@
         </is>
       </c>
       <c r="B860" t="n">
-        <v>0.029115</v>
+        <v>0.029057</v>
       </c>
       <c r="C860" t="n">
         <v>0.668478</v>
@@ -11607,7 +11607,7 @@
         </is>
       </c>
       <c r="B861" t="n">
-        <v>0.029273</v>
+        <v>0.029125</v>
       </c>
       <c r="C861" t="n">
         <v>0.665761</v>
@@ -11620,7 +11620,7 @@
         </is>
       </c>
       <c r="B862" t="n">
-        <v>0.029864</v>
+        <v>0.029215</v>
       </c>
       <c r="C862" t="n">
         <v>0.663043</v>
@@ -11633,7 +11633,7 @@
         </is>
       </c>
       <c r="B863" t="n">
-        <v>0.029929</v>
+        <v>0.029999</v>
       </c>
       <c r="C863" t="n">
         <v>0.660326</v>
@@ -11646,7 +11646,7 @@
         </is>
       </c>
       <c r="B864" t="n">
-        <v>0.030282</v>
+        <v>0.030031</v>
       </c>
       <c r="C864" t="n">
         <v>0.657609</v>
@@ -11659,7 +11659,7 @@
         </is>
       </c>
       <c r="B865" t="n">
-        <v>0.030799</v>
+        <v>0.030293</v>
       </c>
       <c r="C865" t="n">
         <v>0.654891</v>
@@ -11672,7 +11672,7 @@
         </is>
       </c>
       <c r="B866" t="n">
-        <v>0.030965</v>
+        <v>0.030591</v>
       </c>
       <c r="C866" t="n">
         <v>0.652174</v>
@@ -11685,7 +11685,7 @@
         </is>
       </c>
       <c r="B867" t="n">
-        <v>0.031261</v>
+        <v>0.030753</v>
       </c>
       <c r="C867" t="n">
         <v>0.649457</v>
@@ -11698,7 +11698,7 @@
         </is>
       </c>
       <c r="B868" t="n">
-        <v>0.031365</v>
+        <v>0.031246</v>
       </c>
       <c r="C868" t="n">
         <v>0.646739</v>
@@ -11711,7 +11711,7 @@
         </is>
       </c>
       <c r="B869" t="n">
-        <v>0.031453</v>
+        <v>0.031479</v>
       </c>
       <c r="C869" t="n">
         <v>0.644022</v>
@@ -11724,7 +11724,7 @@
         </is>
       </c>
       <c r="B870" t="n">
-        <v>0.031545</v>
+        <v>0.031523</v>
       </c>
       <c r="C870" t="n">
         <v>0.641304</v>
@@ -11737,7 +11737,7 @@
         </is>
       </c>
       <c r="B871" t="n">
-        <v>0.032154</v>
+        <v>0.031708</v>
       </c>
       <c r="C871" t="n">
         <v>0.638587</v>
@@ -11750,7 +11750,7 @@
         </is>
       </c>
       <c r="B872" t="n">
-        <v>0.032202</v>
+        <v>0.032123</v>
       </c>
       <c r="C872" t="n">
         <v>0.63587</v>
@@ -11763,7 +11763,7 @@
         </is>
       </c>
       <c r="B873" t="n">
-        <v>0.032213</v>
+        <v>0.032268</v>
       </c>
       <c r="C873" t="n">
         <v>0.633152</v>
@@ -11776,7 +11776,7 @@
         </is>
       </c>
       <c r="B874" t="n">
-        <v>0.03242</v>
+        <v>0.032309</v>
       </c>
       <c r="C874" t="n">
         <v>0.630435</v>
@@ -11789,7 +11789,7 @@
         </is>
       </c>
       <c r="B875" t="n">
-        <v>0.032484</v>
+        <v>0.032391</v>
       </c>
       <c r="C875" t="n">
         <v>0.627717</v>
@@ -11802,7 +11802,7 @@
         </is>
       </c>
       <c r="B876" t="n">
-        <v>0.032744</v>
+        <v>0.032586</v>
       </c>
       <c r="C876" t="n">
         <v>0.625</v>
@@ -11815,7 +11815,7 @@
         </is>
       </c>
       <c r="B877" t="n">
-        <v>0.032885</v>
+        <v>0.03289</v>
       </c>
       <c r="C877" t="n">
         <v>0.622283</v>
@@ -11828,7 +11828,7 @@
         </is>
       </c>
       <c r="B878" t="n">
-        <v>0.033353</v>
+        <v>0.032965</v>
       </c>
       <c r="C878" t="n">
         <v>0.619565</v>
@@ -11841,7 +11841,7 @@
         </is>
       </c>
       <c r="B879" t="n">
-        <v>0.033391</v>
+        <v>0.033333</v>
       </c>
       <c r="C879" t="n">
         <v>0.616848</v>
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="B880" t="n">
-        <v>0.03459</v>
+        <v>0.033386</v>
       </c>
       <c r="C880" t="n">
         <v>0.61413</v>
@@ -11867,7 +11867,7 @@
         </is>
       </c>
       <c r="B881" t="n">
-        <v>0.035041</v>
+        <v>0.034559</v>
       </c>
       <c r="C881" t="n">
         <v>0.611413</v>
@@ -11880,7 +11880,7 @@
         </is>
       </c>
       <c r="B882" t="n">
-        <v>0.035245</v>
+        <v>0.035145</v>
       </c>
       <c r="C882" t="n">
         <v>0.608696</v>
@@ -11893,7 +11893,7 @@
         </is>
       </c>
       <c r="B883" t="n">
-        <v>0.035462</v>
+        <v>0.035392</v>
       </c>
       <c r="C883" t="n">
         <v>0.605978</v>
@@ -11906,7 +11906,7 @@
         </is>
       </c>
       <c r="B884" t="n">
-        <v>0.035711</v>
+        <v>0.035413</v>
       </c>
       <c r="C884" t="n">
         <v>0.603261</v>
@@ -11919,7 +11919,7 @@
         </is>
       </c>
       <c r="B885" t="n">
-        <v>0.035954</v>
+        <v>0.035757</v>
       </c>
       <c r="C885" t="n">
         <v>0.600543</v>
@@ -11932,7 +11932,7 @@
         </is>
       </c>
       <c r="B886" t="n">
-        <v>0.036002</v>
+        <v>0.03597</v>
       </c>
       <c r="C886" t="n">
         <v>0.597826</v>
@@ -11945,7 +11945,7 @@
         </is>
       </c>
       <c r="B887" t="n">
-        <v>0.036643</v>
+        <v>0.036098</v>
       </c>
       <c r="C887" t="n">
         <v>0.595109</v>
@@ -11958,7 +11958,7 @@
         </is>
       </c>
       <c r="B888" t="n">
-        <v>0.036726</v>
+        <v>0.036842</v>
       </c>
       <c r="C888" t="n">
         <v>0.592391</v>
@@ -11971,7 +11971,7 @@
         </is>
       </c>
       <c r="B889" t="n">
-        <v>0.036859</v>
+        <v>0.036873</v>
       </c>
       <c r="C889" t="n">
         <v>0.589674</v>
@@ -11984,7 +11984,7 @@
         </is>
       </c>
       <c r="B890" t="n">
-        <v>0.036949</v>
+        <v>0.036896</v>
       </c>
       <c r="C890" t="n">
         <v>0.586957</v>
@@ -11997,7 +11997,7 @@
         </is>
       </c>
       <c r="B891" t="n">
-        <v>0.037238</v>
+        <v>0.037086</v>
       </c>
       <c r="C891" t="n">
         <v>0.584239</v>
@@ -12010,7 +12010,7 @@
         </is>
       </c>
       <c r="B892" t="n">
-        <v>0.037252</v>
+        <v>0.037271</v>
       </c>
       <c r="C892" t="n">
         <v>0.581522</v>
@@ -12023,7 +12023,7 @@
         </is>
       </c>
       <c r="B893" t="n">
-        <v>0.037842</v>
+        <v>0.037347</v>
       </c>
       <c r="C893" t="n">
         <v>0.578804</v>
@@ -12036,7 +12036,7 @@
         </is>
       </c>
       <c r="B894" t="n">
-        <v>0.038243</v>
+        <v>0.038018</v>
       </c>
       <c r="C894" t="n">
         <v>0.576087</v>
@@ -12049,7 +12049,7 @@
         </is>
       </c>
       <c r="B895" t="n">
-        <v>0.038598</v>
+        <v>0.03802</v>
       </c>
       <c r="C895" t="n">
         <v>0.57337</v>
@@ -12062,7 +12062,7 @@
         </is>
       </c>
       <c r="B896" t="n">
-        <v>0.039052</v>
+        <v>0.039034</v>
       </c>
       <c r="C896" t="n">
         <v>0.570652</v>
@@ -12075,7 +12075,7 @@
         </is>
       </c>
       <c r="B897" t="n">
-        <v>0.039149</v>
+        <v>0.039234</v>
       </c>
       <c r="C897" t="n">
         <v>0.567935</v>
@@ -12088,7 +12088,7 @@
         </is>
       </c>
       <c r="B898" t="n">
-        <v>0.039412</v>
+        <v>0.039611</v>
       </c>
       <c r="C898" t="n">
         <v>0.565217</v>
@@ -12101,7 +12101,7 @@
         </is>
       </c>
       <c r="B899" t="n">
-        <v>0.039652</v>
+        <v>0.039834</v>
       </c>
       <c r="C899" t="n">
         <v>0.5625</v>
@@ -12114,7 +12114,7 @@
         </is>
       </c>
       <c r="B900" t="n">
-        <v>0.039761</v>
+        <v>0.039896</v>
       </c>
       <c r="C900" t="n">
         <v>0.559783</v>
@@ -12127,7 +12127,7 @@
         </is>
       </c>
       <c r="B901" t="n">
-        <v>0.039842</v>
+        <v>0.039954</v>
       </c>
       <c r="C901" t="n">
         <v>0.557065</v>
@@ -12140,7 +12140,7 @@
         </is>
       </c>
       <c r="B902" t="n">
-        <v>0.039942</v>
+        <v>0.039969</v>
       </c>
       <c r="C902" t="n">
         <v>0.554348</v>
@@ -12153,7 +12153,7 @@
         </is>
       </c>
       <c r="B903" t="n">
-        <v>0.040107</v>
+        <v>0.040284</v>
       </c>
       <c r="C903" t="n">
         <v>0.55163</v>
@@ -12166,7 +12166,7 @@
         </is>
       </c>
       <c r="B904" t="n">
-        <v>0.04028</v>
+        <v>0.040353</v>
       </c>
       <c r="C904" t="n">
         <v>0.548913</v>
@@ -12179,7 +12179,7 @@
         </is>
       </c>
       <c r="B905" t="n">
-        <v>0.040378</v>
+        <v>0.040554</v>
       </c>
       <c r="C905" t="n">
         <v>0.546196</v>
@@ -12192,7 +12192,7 @@
         </is>
       </c>
       <c r="B906" t="n">
-        <v>0.040434</v>
+        <v>0.04057</v>
       </c>
       <c r="C906" t="n">
         <v>0.543478</v>
@@ -12205,7 +12205,7 @@
         </is>
       </c>
       <c r="B907" t="n">
-        <v>0.040517</v>
+        <v>0.04061</v>
       </c>
       <c r="C907" t="n">
         <v>0.540761</v>
@@ -12218,7 +12218,7 @@
         </is>
       </c>
       <c r="B908" t="n">
-        <v>0.040925</v>
+        <v>0.041087</v>
       </c>
       <c r="C908" t="n">
         <v>0.538043</v>
@@ -12231,7 +12231,7 @@
         </is>
       </c>
       <c r="B909" t="n">
-        <v>0.041392</v>
+        <v>0.041396</v>
       </c>
       <c r="C909" t="n">
         <v>0.535326</v>
@@ -12244,7 +12244,7 @@
         </is>
       </c>
       <c r="B910" t="n">
-        <v>0.041511</v>
+        <v>0.041499</v>
       </c>
       <c r="C910" t="n">
         <v>0.532609</v>
@@ -12257,7 +12257,7 @@
         </is>
       </c>
       <c r="B911" t="n">
-        <v>0.041523</v>
+        <v>0.04168</v>
       </c>
       <c r="C911" t="n">
         <v>0.529891</v>
@@ -12270,7 +12270,7 @@
         </is>
       </c>
       <c r="B912" t="n">
-        <v>0.041594</v>
+        <v>0.041757</v>
       </c>
       <c r="C912" t="n">
         <v>0.527174</v>
@@ -12283,7 +12283,7 @@
         </is>
       </c>
       <c r="B913" t="n">
-        <v>0.041599</v>
+        <v>0.042301</v>
       </c>
       <c r="C913" t="n">
         <v>0.524457</v>
@@ -12296,7 +12296,7 @@
         </is>
       </c>
       <c r="B914" t="n">
-        <v>0.042196</v>
+        <v>0.042611</v>
       </c>
       <c r="C914" t="n">
         <v>0.521739</v>
@@ -12309,7 +12309,7 @@
         </is>
       </c>
       <c r="B915" t="n">
-        <v>0.042479</v>
+        <v>0.042629</v>
       </c>
       <c r="C915" t="n">
         <v>0.519022</v>
@@ -12322,7 +12322,7 @@
         </is>
       </c>
       <c r="B916" t="n">
-        <v>0.042865</v>
+        <v>0.042819</v>
       </c>
       <c r="C916" t="n">
         <v>0.516304</v>
@@ -12335,7 +12335,7 @@
         </is>
       </c>
       <c r="B917" t="n">
-        <v>0.042954</v>
+        <v>0.04322</v>
       </c>
       <c r="C917" t="n">
         <v>0.513587</v>
@@ -12348,7 +12348,7 @@
         </is>
       </c>
       <c r="B918" t="n">
-        <v>0.043078</v>
+        <v>0.044273</v>
       </c>
       <c r="C918" t="n">
         <v>0.51087</v>
@@ -12361,7 +12361,7 @@
         </is>
       </c>
       <c r="B919" t="n">
-        <v>0.044236</v>
+        <v>0.0443</v>
       </c>
       <c r="C919" t="n">
         <v>0.508152</v>
@@ -12374,7 +12374,7 @@
         </is>
       </c>
       <c r="B920" t="n">
-        <v>0.044451</v>
+        <v>0.044666</v>
       </c>
       <c r="C920" t="n">
         <v>0.505435</v>
@@ -12387,7 +12387,7 @@
         </is>
       </c>
       <c r="B921" t="n">
-        <v>0.044671</v>
+        <v>0.044811</v>
       </c>
       <c r="C921" t="n">
         <v>0.502717</v>
@@ -12400,7 +12400,7 @@
         </is>
       </c>
       <c r="B922" t="n">
-        <v>0.044727</v>
+        <v>0.045861</v>
       </c>
       <c r="C922" t="n">
         <v>0.5</v>
@@ -12413,7 +12413,7 @@
         </is>
       </c>
       <c r="B923" t="n">
-        <v>0.045685</v>
+        <v>0.045868</v>
       </c>
       <c r="C923" t="n">
         <v>0.497283</v>
@@ -12426,7 +12426,7 @@
         </is>
       </c>
       <c r="B924" t="n">
-        <v>0.04584</v>
+        <v>0.046342</v>
       </c>
       <c r="C924" t="n">
         <v>0.494565</v>
@@ -12439,7 +12439,7 @@
         </is>
       </c>
       <c r="B925" t="n">
-        <v>0.046152</v>
+        <v>0.046397</v>
       </c>
       <c r="C925" t="n">
         <v>0.491848</v>
@@ -12452,7 +12452,7 @@
         </is>
       </c>
       <c r="B926" t="n">
-        <v>0.046712</v>
+        <v>0.047155</v>
       </c>
       <c r="C926" t="n">
         <v>0.48913</v>
@@ -12465,7 +12465,7 @@
         </is>
       </c>
       <c r="B927" t="n">
-        <v>0.047102</v>
+        <v>0.048692</v>
       </c>
       <c r="C927" t="n">
         <v>0.486413</v>
@@ -12478,7 +12478,7 @@
         </is>
       </c>
       <c r="B928" t="n">
-        <v>0.048477</v>
+        <v>0.049129</v>
       </c>
       <c r="C928" t="n">
         <v>0.483696</v>
@@ -12491,7 +12491,7 @@
         </is>
       </c>
       <c r="B929" t="n">
-        <v>0.04898</v>
+        <v>0.049164</v>
       </c>
       <c r="C929" t="n">
         <v>0.480978</v>
@@ -12504,7 +12504,7 @@
         </is>
       </c>
       <c r="B930" t="n">
-        <v>0.049295</v>
+        <v>0.0494</v>
       </c>
       <c r="C930" t="n">
         <v>0.478261</v>
@@ -12517,7 +12517,7 @@
         </is>
       </c>
       <c r="B931" t="n">
-        <v>0.049467</v>
+        <v>0.04949</v>
       </c>
       <c r="C931" t="n">
         <v>0.475543</v>
@@ -12530,7 +12530,7 @@
         </is>
       </c>
       <c r="B932" t="n">
-        <v>0.049592</v>
+        <v>0.049589</v>
       </c>
       <c r="C932" t="n">
         <v>0.472826</v>
@@ -12543,7 +12543,7 @@
         </is>
       </c>
       <c r="B933" t="n">
-        <v>0.04966</v>
+        <v>0.049845</v>
       </c>
       <c r="C933" t="n">
         <v>0.470109</v>
@@ -12556,7 +12556,7 @@
         </is>
       </c>
       <c r="B934" t="n">
-        <v>0.049903</v>
+        <v>0.05038</v>
       </c>
       <c r="C934" t="n">
         <v>0.467391</v>
@@ -12569,7 +12569,7 @@
         </is>
       </c>
       <c r="B935" t="n">
-        <v>0.050217</v>
+        <v>0.050648</v>
       </c>
       <c r="C935" t="n">
         <v>0.464674</v>
@@ -12582,7 +12582,7 @@
         </is>
       </c>
       <c r="B936" t="n">
-        <v>0.050579</v>
+        <v>0.051132</v>
       </c>
       <c r="C936" t="n">
         <v>0.461957</v>
@@ -12595,7 +12595,7 @@
         </is>
       </c>
       <c r="B937" t="n">
-        <v>0.051156</v>
+        <v>0.051161</v>
       </c>
       <c r="C937" t="n">
         <v>0.459239</v>
@@ -12608,7 +12608,7 @@
         </is>
       </c>
       <c r="B938" t="n">
-        <v>0.051202</v>
+        <v>0.051176</v>
       </c>
       <c r="C938" t="n">
         <v>0.456522</v>
@@ -12621,7 +12621,7 @@
         </is>
       </c>
       <c r="B939" t="n">
-        <v>0.051233</v>
+        <v>0.051668</v>
       </c>
       <c r="C939" t="n">
         <v>0.453804</v>
@@ -12634,7 +12634,7 @@
         </is>
       </c>
       <c r="B940" t="n">
-        <v>0.051477</v>
+        <v>0.05188</v>
       </c>
       <c r="C940" t="n">
         <v>0.451087</v>
@@ -12647,7 +12647,7 @@
         </is>
       </c>
       <c r="B941" t="n">
-        <v>0.0518</v>
+        <v>0.052263</v>
       </c>
       <c r="C941" t="n">
         <v>0.44837</v>
@@ -12660,7 +12660,7 @@
         </is>
       </c>
       <c r="B942" t="n">
-        <v>0.051963</v>
+        <v>0.052303</v>
       </c>
       <c r="C942" t="n">
         <v>0.445652</v>
@@ -12673,7 +12673,7 @@
         </is>
       </c>
       <c r="B943" t="n">
-        <v>0.05279</v>
+        <v>0.052798</v>
       </c>
       <c r="C943" t="n">
         <v>0.442935</v>
@@ -12686,7 +12686,7 @@
         </is>
       </c>
       <c r="B944" t="n">
-        <v>0.053346</v>
+        <v>0.05344</v>
       </c>
       <c r="C944" t="n">
         <v>0.440217</v>
@@ -12699,7 +12699,7 @@
         </is>
       </c>
       <c r="B945" t="n">
-        <v>0.05364</v>
+        <v>0.053471</v>
       </c>
       <c r="C945" t="n">
         <v>0.4375</v>
@@ -12712,7 +12712,7 @@
         </is>
       </c>
       <c r="B946" t="n">
-        <v>0.05381</v>
+        <v>0.053946</v>
       </c>
       <c r="C946" t="n">
         <v>0.434783</v>
@@ -12725,7 +12725,7 @@
         </is>
       </c>
       <c r="B947" t="n">
-        <v>0.054958</v>
+        <v>0.054825</v>
       </c>
       <c r="C947" t="n">
         <v>0.432065</v>
@@ -12738,7 +12738,7 @@
         </is>
       </c>
       <c r="B948" t="n">
-        <v>0.055461</v>
+        <v>0.055512</v>
       </c>
       <c r="C948" t="n">
         <v>0.429348</v>
@@ -12751,7 +12751,7 @@
         </is>
       </c>
       <c r="B949" t="n">
-        <v>0.055467</v>
+        <v>0.055516</v>
       </c>
       <c r="C949" t="n">
         <v>0.42663</v>
@@ -12764,7 +12764,7 @@
         </is>
       </c>
       <c r="B950" t="n">
-        <v>0.055778</v>
+        <v>0.055814</v>
       </c>
       <c r="C950" t="n">
         <v>0.423913</v>
@@ -12777,7 +12777,7 @@
         </is>
       </c>
       <c r="B951" t="n">
-        <v>0.056298</v>
+        <v>0.05636</v>
       </c>
       <c r="C951" t="n">
         <v>0.421196</v>
@@ -12790,7 +12790,7 @@
         </is>
       </c>
       <c r="B952" t="n">
-        <v>0.056819</v>
+        <v>0.056841</v>
       </c>
       <c r="C952" t="n">
         <v>0.418478</v>
@@ -12803,7 +12803,7 @@
         </is>
       </c>
       <c r="B953" t="n">
-        <v>0.056897</v>
+        <v>0.056942</v>
       </c>
       <c r="C953" t="n">
         <v>0.415761</v>
@@ -12816,7 +12816,7 @@
         </is>
       </c>
       <c r="B954" t="n">
-        <v>0.057361</v>
+        <v>0.057717</v>
       </c>
       <c r="C954" t="n">
         <v>0.413043</v>
@@ -12829,7 +12829,7 @@
         </is>
       </c>
       <c r="B955" t="n">
-        <v>0.057835</v>
+        <v>0.057849</v>
       </c>
       <c r="C955" t="n">
         <v>0.410326</v>
@@ -12842,7 +12842,7 @@
         </is>
       </c>
       <c r="B956" t="n">
-        <v>0.058602</v>
+        <v>0.059949</v>
       </c>
       <c r="C956" t="n">
         <v>0.407609</v>
@@ -12855,7 +12855,7 @@
         </is>
       </c>
       <c r="B957" t="n">
-        <v>0.059654</v>
+        <v>0.060281</v>
       </c>
       <c r="C957" t="n">
         <v>0.404891</v>
@@ -12868,7 +12868,7 @@
         </is>
       </c>
       <c r="B958" t="n">
-        <v>0.060484</v>
+        <v>0.061262</v>
       </c>
       <c r="C958" t="n">
         <v>0.402174</v>
@@ -12881,7 +12881,7 @@
         </is>
       </c>
       <c r="B959" t="n">
-        <v>0.06125</v>
+        <v>0.061791</v>
       </c>
       <c r="C959" t="n">
         <v>0.399457</v>
@@ -12894,7 +12894,7 @@
         </is>
       </c>
       <c r="B960" t="n">
-        <v>0.061788</v>
+        <v>0.061919</v>
       </c>
       <c r="C960" t="n">
         <v>0.396739</v>
@@ -12907,7 +12907,7 @@
         </is>
       </c>
       <c r="B961" t="n">
-        <v>0.062044</v>
+        <v>0.062139</v>
       </c>
       <c r="C961" t="n">
         <v>0.394022</v>
@@ -12920,7 +12920,7 @@
         </is>
       </c>
       <c r="B962" t="n">
-        <v>0.062182</v>
+        <v>0.062355</v>
       </c>
       <c r="C962" t="n">
         <v>0.391304</v>
@@ -12933,7 +12933,7 @@
         </is>
       </c>
       <c r="B963" t="n">
-        <v>0.062197</v>
+        <v>0.062405</v>
       </c>
       <c r="C963" t="n">
         <v>0.388587</v>
@@ -12946,7 +12946,7 @@
         </is>
       </c>
       <c r="B964" t="n">
-        <v>0.062787</v>
+        <v>0.062956</v>
       </c>
       <c r="C964" t="n">
         <v>0.38587</v>
@@ -12959,7 +12959,7 @@
         </is>
       </c>
       <c r="B965" t="n">
-        <v>0.062804</v>
+        <v>0.063054</v>
       </c>
       <c r="C965" t="n">
         <v>0.383152</v>
@@ -12972,7 +12972,7 @@
         </is>
       </c>
       <c r="B966" t="n">
-        <v>0.063084</v>
+        <v>0.063306</v>
       </c>
       <c r="C966" t="n">
         <v>0.380435</v>
@@ -12985,7 +12985,7 @@
         </is>
       </c>
       <c r="B967" t="n">
-        <v>0.063085</v>
+        <v>0.06335</v>
       </c>
       <c r="C967" t="n">
         <v>0.377717</v>
@@ -12998,7 +12998,7 @@
         </is>
       </c>
       <c r="B968" t="n">
-        <v>0.063426</v>
+        <v>0.06351</v>
       </c>
       <c r="C968" t="n">
         <v>0.375</v>
@@ -13011,7 +13011,7 @@
         </is>
       </c>
       <c r="B969" t="n">
-        <v>0.063483</v>
+        <v>0.06354600000000001</v>
       </c>
       <c r="C969" t="n">
         <v>0.372283</v>
@@ -13024,7 +13024,7 @@
         </is>
       </c>
       <c r="B970" t="n">
-        <v>0.06375400000000001</v>
+        <v>0.064094</v>
       </c>
       <c r="C970" t="n">
         <v>0.369565</v>
@@ -13037,7 +13037,7 @@
         </is>
       </c>
       <c r="B971" t="n">
-        <v>0.06399199999999999</v>
+        <v>0.06419</v>
       </c>
       <c r="C971" t="n">
         <v>0.366848</v>
@@ -13050,7 +13050,7 @@
         </is>
       </c>
       <c r="B972" t="n">
-        <v>0.06422</v>
+        <v>0.064537</v>
       </c>
       <c r="C972" t="n">
         <v>0.36413</v>
@@ -13063,7 +13063,7 @@
         </is>
       </c>
       <c r="B973" t="n">
-        <v>0.064355</v>
+        <v>0.066438</v>
       </c>
       <c r="C973" t="n">
         <v>0.361413</v>
@@ -13076,7 +13076,7 @@
         </is>
       </c>
       <c r="B974" t="n">
-        <v>0.06615799999999999</v>
+        <v>0.06736200000000001</v>
       </c>
       <c r="C974" t="n">
         <v>0.358696</v>
@@ -13089,7 +13089,7 @@
         </is>
       </c>
       <c r="B975" t="n">
-        <v>0.066967</v>
+        <v>0.06745900000000001</v>
       </c>
       <c r="C975" t="n">
         <v>0.355978</v>
@@ -13102,7 +13102,7 @@
         </is>
       </c>
       <c r="B976" t="n">
-        <v>0.06705999999999999</v>
+        <v>0.06748</v>
       </c>
       <c r="C976" t="n">
         <v>0.353261</v>
@@ -13115,7 +13115,7 @@
         </is>
       </c>
       <c r="B977" t="n">
-        <v>0.067403</v>
+        <v>0.06757299999999999</v>
       </c>
       <c r="C977" t="n">
         <v>0.350543</v>
@@ -13128,7 +13128,7 @@
         </is>
       </c>
       <c r="B978" t="n">
-        <v>0.0678</v>
+        <v>0.068485</v>
       </c>
       <c r="C978" t="n">
         <v>0.347826</v>
@@ -13141,7 +13141,7 @@
         </is>
       </c>
       <c r="B979" t="n">
-        <v>0.068324</v>
+        <v>0.06851400000000001</v>
       </c>
       <c r="C979" t="n">
         <v>0.345109</v>
@@ -13154,7 +13154,7 @@
         </is>
       </c>
       <c r="B980" t="n">
-        <v>0.06862600000000001</v>
+        <v>0.06869699999999999</v>
       </c>
       <c r="C980" t="n">
         <v>0.342391</v>
@@ -13167,7 +13167,7 @@
         </is>
       </c>
       <c r="B981" t="n">
-        <v>0.068646</v>
+        <v>0.068795</v>
       </c>
       <c r="C981" t="n">
         <v>0.339674</v>
@@ -13180,7 +13180,7 @@
         </is>
       </c>
       <c r="B982" t="n">
-        <v>0.06890400000000001</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="C982" t="n">
         <v>0.336957</v>
@@ -13193,7 +13193,7 @@
         </is>
       </c>
       <c r="B983" t="n">
-        <v>0.069075</v>
+        <v>0.070063</v>
       </c>
       <c r="C983" t="n">
         <v>0.334239</v>
@@ -13206,7 +13206,7 @@
         </is>
       </c>
       <c r="B984" t="n">
-        <v>0.069629</v>
+        <v>0.070142</v>
       </c>
       <c r="C984" t="n">
         <v>0.331522</v>
@@ -13219,7 +13219,7 @@
         </is>
       </c>
       <c r="B985" t="n">
-        <v>0.070089</v>
+        <v>0.07026200000000001</v>
       </c>
       <c r="C985" t="n">
         <v>0.328804</v>
@@ -13232,7 +13232,7 @@
         </is>
       </c>
       <c r="B986" t="n">
-        <v>0.070618</v>
+        <v>0.071215</v>
       </c>
       <c r="C986" t="n">
         <v>0.326087</v>
@@ -13245,7 +13245,7 @@
         </is>
       </c>
       <c r="B987" t="n">
-        <v>0.07091600000000001</v>
+        <v>0.071296</v>
       </c>
       <c r="C987" t="n">
         <v>0.32337</v>
@@ -13258,7 +13258,7 @@
         </is>
       </c>
       <c r="B988" t="n">
-        <v>0.07127500000000001</v>
+        <v>0.07198499999999999</v>
       </c>
       <c r="C988" t="n">
         <v>0.320652</v>
@@ -13271,7 +13271,7 @@
         </is>
       </c>
       <c r="B989" t="n">
-        <v>0.072062</v>
+        <v>0.072002</v>
       </c>
       <c r="C989" t="n">
         <v>0.317935</v>
@@ -13284,7 +13284,7 @@
         </is>
       </c>
       <c r="B990" t="n">
-        <v>0.072131</v>
+        <v>0.07228800000000001</v>
       </c>
       <c r="C990" t="n">
         <v>0.315217</v>
@@ -13297,7 +13297,7 @@
         </is>
       </c>
       <c r="B991" t="n">
-        <v>0.072189</v>
+        <v>0.07270699999999999</v>
       </c>
       <c r="C991" t="n">
         <v>0.3125</v>
@@ -13310,7 +13310,7 @@
         </is>
       </c>
       <c r="B992" t="n">
-        <v>0.07244299999999999</v>
+        <v>0.073005</v>
       </c>
       <c r="C992" t="n">
         <v>0.309783</v>
@@ -13323,7 +13323,7 @@
         </is>
       </c>
       <c r="B993" t="n">
-        <v>0.07292700000000001</v>
+        <v>0.073439</v>
       </c>
       <c r="C993" t="n">
         <v>0.307065</v>
@@ -13336,7 +13336,7 @@
         </is>
       </c>
       <c r="B994" t="n">
-        <v>0.073102</v>
+        <v>0.07348300000000001</v>
       </c>
       <c r="C994" t="n">
         <v>0.304348</v>
@@ -13349,7 +13349,7 @@
         </is>
       </c>
       <c r="B995" t="n">
-        <v>0.07328800000000001</v>
+        <v>0.07359599999999999</v>
       </c>
       <c r="C995" t="n">
         <v>0.30163</v>
@@ -13362,7 +13362,7 @@
         </is>
       </c>
       <c r="B996" t="n">
-        <v>0.073348</v>
+        <v>0.074363</v>
       </c>
       <c r="C996" t="n">
         <v>0.298913</v>
@@ -13375,7 +13375,7 @@
         </is>
       </c>
       <c r="B997" t="n">
-        <v>0.074334</v>
+        <v>0.07765</v>
       </c>
       <c r="C997" t="n">
         <v>0.296196</v>
@@ -13388,7 +13388,7 @@
         </is>
       </c>
       <c r="B998" t="n">
-        <v>0.077588</v>
+        <v>0.078322</v>
       </c>
       <c r="C998" t="n">
         <v>0.293478</v>
@@ -13401,7 +13401,7 @@
         </is>
       </c>
       <c r="B999" t="n">
-        <v>0.077843</v>
+        <v>0.078587</v>
       </c>
       <c r="C999" t="n">
         <v>0.290761</v>
@@ -13414,7 +13414,7 @@
         </is>
       </c>
       <c r="B1000" t="n">
-        <v>0.078652</v>
+        <v>0.078761</v>
       </c>
       <c r="C1000" t="n">
         <v>0.288043</v>
@@ -13427,7 +13427,7 @@
         </is>
       </c>
       <c r="B1001" t="n">
-        <v>0.078693</v>
+        <v>0.079017</v>
       </c>
       <c r="C1001" t="n">
         <v>0.285326</v>
@@ -13440,7 +13440,7 @@
         </is>
       </c>
       <c r="B1002" t="n">
-        <v>0.079291</v>
+        <v>0.079815</v>
       </c>
       <c r="C1002" t="n">
         <v>0.282609</v>
@@ -13453,7 +13453,7 @@
         </is>
       </c>
       <c r="B1003" t="n">
-        <v>0.079693</v>
+        <v>0.080619</v>
       </c>
       <c r="C1003" t="n">
         <v>0.279891</v>
@@ -13466,7 +13466,7 @@
         </is>
       </c>
       <c r="B1004" t="n">
-        <v>0.080499</v>
+        <v>0.080905</v>
       </c>
       <c r="C1004" t="n">
         <v>0.277174</v>
@@ -13479,7 +13479,7 @@
         </is>
       </c>
       <c r="B1005" t="n">
-        <v>0.080651</v>
+        <v>0.080944</v>
       </c>
       <c r="C1005" t="n">
         <v>0.274457</v>
@@ -13492,7 +13492,7 @@
         </is>
       </c>
       <c r="B1006" t="n">
-        <v>0.081456</v>
+        <v>0.08166900000000001</v>
       </c>
       <c r="C1006" t="n">
         <v>0.271739</v>
@@ -13505,7 +13505,7 @@
         </is>
       </c>
       <c r="B1007" t="n">
-        <v>0.08153199999999999</v>
+        <v>0.08179599999999999</v>
       </c>
       <c r="C1007" t="n">
         <v>0.269022</v>
@@ -13518,7 +13518,7 @@
         </is>
       </c>
       <c r="B1008" t="n">
-        <v>0.08158700000000001</v>
+        <v>0.082319</v>
       </c>
       <c r="C1008" t="n">
         <v>0.266304</v>
@@ -13531,7 +13531,7 @@
         </is>
       </c>
       <c r="B1009" t="n">
-        <v>0.082234</v>
+        <v>0.08247400000000001</v>
       </c>
       <c r="C1009" t="n">
         <v>0.263587</v>
@@ -13544,7 +13544,7 @@
         </is>
       </c>
       <c r="B1010" t="n">
-        <v>0.08291</v>
+        <v>0.08297599999999999</v>
       </c>
       <c r="C1010" t="n">
         <v>0.26087</v>
@@ -13557,7 +13557,7 @@
         </is>
       </c>
       <c r="B1011" t="n">
-        <v>0.082964</v>
+        <v>0.083089</v>
       </c>
       <c r="C1011" t="n">
         <v>0.258152</v>
@@ -13570,7 +13570,7 @@
         </is>
       </c>
       <c r="B1012" t="n">
-        <v>0.083407</v>
+        <v>0.083706</v>
       </c>
       <c r="C1012" t="n">
         <v>0.255435</v>
@@ -13583,7 +13583,7 @@
         </is>
       </c>
       <c r="B1013" t="n">
-        <v>0.083637</v>
+        <v>0.085636</v>
       </c>
       <c r="C1013" t="n">
         <v>0.252717</v>
@@ -13596,7 +13596,7 @@
         </is>
       </c>
       <c r="B1014" t="n">
-        <v>0.085118</v>
+        <v>0.08580500000000001</v>
       </c>
       <c r="C1014" t="n">
         <v>0.25</v>
@@ -13609,7 +13609,7 @@
         </is>
       </c>
       <c r="B1015" t="n">
-        <v>0.08572</v>
+        <v>0.086079</v>
       </c>
       <c r="C1015" t="n">
         <v>0.247283</v>
@@ -13622,7 +13622,7 @@
         </is>
       </c>
       <c r="B1016" t="n">
-        <v>0.085741</v>
+        <v>0.08624800000000001</v>
       </c>
       <c r="C1016" t="n">
         <v>0.244565</v>
@@ -13635,7 +13635,7 @@
         </is>
       </c>
       <c r="B1017" t="n">
-        <v>0.085928</v>
+        <v>0.08684699999999999</v>
       </c>
       <c r="C1017" t="n">
         <v>0.241848</v>
@@ -13648,7 +13648,7 @@
         </is>
       </c>
       <c r="B1018" t="n">
-        <v>0.08698599999999999</v>
+        <v>0.08740100000000001</v>
       </c>
       <c r="C1018" t="n">
         <v>0.23913</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="B1019" t="n">
-        <v>0.08726</v>
+        <v>0.087564</v>
       </c>
       <c r="C1019" t="n">
         <v>0.236413</v>
@@ -13674,7 +13674,7 @@
         </is>
       </c>
       <c r="B1020" t="n">
-        <v>0.091005</v>
+        <v>0.090474</v>
       </c>
       <c r="C1020" t="n">
         <v>0.233696</v>
@@ -13687,7 +13687,7 @@
         </is>
       </c>
       <c r="B1021" t="n">
-        <v>0.09116200000000001</v>
+        <v>0.09106499999999999</v>
       </c>
       <c r="C1021" t="n">
         <v>0.230978</v>
@@ -13700,7 +13700,7 @@
         </is>
       </c>
       <c r="B1022" t="n">
-        <v>0.09124400000000001</v>
+        <v>0.091463</v>
       </c>
       <c r="C1022" t="n">
         <v>0.228261</v>
@@ -13713,7 +13713,7 @@
         </is>
       </c>
       <c r="B1023" t="n">
-        <v>0.09129900000000001</v>
+        <v>0.091599</v>
       </c>
       <c r="C1023" t="n">
         <v>0.225543</v>
@@ -13726,7 +13726,7 @@
         </is>
       </c>
       <c r="B1024" t="n">
-        <v>0.09195299999999999</v>
+        <v>0.091881</v>
       </c>
       <c r="C1024" t="n">
         <v>0.222826</v>
@@ -13739,7 +13739,7 @@
         </is>
       </c>
       <c r="B1025" t="n">
-        <v>0.09278400000000001</v>
+        <v>0.09291000000000001</v>
       </c>
       <c r="C1025" t="n">
         <v>0.220109</v>
@@ -13752,7 +13752,7 @@
         </is>
       </c>
       <c r="B1026" t="n">
-        <v>0.093303</v>
+        <v>0.092969</v>
       </c>
       <c r="C1026" t="n">
         <v>0.217391</v>
@@ -13765,7 +13765,7 @@
         </is>
       </c>
       <c r="B1027" t="n">
-        <v>0.093531</v>
+        <v>0.09375799999999999</v>
       </c>
       <c r="C1027" t="n">
         <v>0.214674</v>
@@ -13778,7 +13778,7 @@
         </is>
       </c>
       <c r="B1028" t="n">
-        <v>0.093704</v>
+        <v>0.093874</v>
       </c>
       <c r="C1028" t="n">
         <v>0.211957</v>
@@ -13791,7 +13791,7 @@
         </is>
       </c>
       <c r="B1029" t="n">
-        <v>0.093732</v>
+        <v>0.094115</v>
       </c>
       <c r="C1029" t="n">
         <v>0.209239</v>
@@ -13804,7 +13804,7 @@
         </is>
       </c>
       <c r="B1030" t="n">
-        <v>0.094004</v>
+        <v>0.094292</v>
       </c>
       <c r="C1030" t="n">
         <v>0.206522</v>
@@ -13817,7 +13817,7 @@
         </is>
       </c>
       <c r="B1031" t="n">
-        <v>0.094154</v>
+        <v>0.09492</v>
       </c>
       <c r="C1031" t="n">
         <v>0.203804</v>
@@ -13830,7 +13830,7 @@
         </is>
       </c>
       <c r="B1032" t="n">
-        <v>0.094662</v>
+        <v>0.09599299999999999</v>
       </c>
       <c r="C1032" t="n">
         <v>0.201087</v>
@@ -13843,7 +13843,7 @@
         </is>
       </c>
       <c r="B1033" t="n">
-        <v>0.096039</v>
+        <v>0.09671100000000001</v>
       </c>
       <c r="C1033" t="n">
         <v>0.19837</v>
@@ -13856,7 +13856,7 @@
         </is>
       </c>
       <c r="B1034" t="n">
-        <v>0.096987</v>
+        <v>0.097872</v>
       </c>
       <c r="C1034" t="n">
         <v>0.195652</v>
@@ -13869,7 +13869,7 @@
         </is>
       </c>
       <c r="B1035" t="n">
-        <v>0.097403</v>
+        <v>0.09987699999999999</v>
       </c>
       <c r="C1035" t="n">
         <v>0.192935</v>
@@ -13882,7 +13882,7 @@
         </is>
       </c>
       <c r="B1036" t="n">
-        <v>0.09958699999999999</v>
+        <v>0.10092</v>
       </c>
       <c r="C1036" t="n">
         <v>0.190217</v>
@@ -13895,7 +13895,7 @@
         </is>
       </c>
       <c r="B1037" t="n">
-        <v>0.100735</v>
+        <v>0.101844</v>
       </c>
       <c r="C1037" t="n">
         <v>0.1875</v>
@@ -13908,7 +13908,7 @@
         </is>
       </c>
       <c r="B1038" t="n">
-        <v>0.101811</v>
+        <v>0.102167</v>
       </c>
       <c r="C1038" t="n">
         <v>0.184783</v>
@@ -13921,7 +13921,7 @@
         </is>
       </c>
       <c r="B1039" t="n">
-        <v>0.102142</v>
+        <v>0.103233</v>
       </c>
       <c r="C1039" t="n">
         <v>0.182065</v>
@@ -13934,7 +13934,7 @@
         </is>
       </c>
       <c r="B1040" t="n">
-        <v>0.103043</v>
+        <v>0.103955</v>
       </c>
       <c r="C1040" t="n">
         <v>0.179348</v>
@@ -13947,7 +13947,7 @@
         </is>
       </c>
       <c r="B1041" t="n">
-        <v>0.103657</v>
+        <v>0.10396</v>
       </c>
       <c r="C1041" t="n">
         <v>0.17663</v>
@@ -13960,7 +13960,7 @@
         </is>
       </c>
       <c r="B1042" t="n">
-        <v>0.104053</v>
+        <v>0.107575</v>
       </c>
       <c r="C1042" t="n">
         <v>0.173913</v>
@@ -13973,7 +13973,7 @@
         </is>
       </c>
       <c r="B1043" t="n">
-        <v>0.106958</v>
+        <v>0.109615</v>
       </c>
       <c r="C1043" t="n">
         <v>0.171196</v>
@@ -13986,7 +13986,7 @@
         </is>
       </c>
       <c r="B1044" t="n">
-        <v>0.109789</v>
+        <v>0.111468</v>
       </c>
       <c r="C1044" t="n">
         <v>0.168478</v>
@@ -13999,7 +13999,7 @@
         </is>
       </c>
       <c r="B1045" t="n">
-        <v>0.111214</v>
+        <v>0.111473</v>
       </c>
       <c r="C1045" t="n">
         <v>0.165761</v>
@@ -14012,7 +14012,7 @@
         </is>
       </c>
       <c r="B1046" t="n">
-        <v>0.111429</v>
+        <v>0.11296</v>
       </c>
       <c r="C1046" t="n">
         <v>0.163043</v>
@@ -14025,7 +14025,7 @@
         </is>
       </c>
       <c r="B1047" t="n">
-        <v>0.112707</v>
+        <v>0.113539</v>
       </c>
       <c r="C1047" t="n">
         <v>0.160326</v>
@@ -14038,7 +14038,7 @@
         </is>
       </c>
       <c r="B1048" t="n">
-        <v>0.113811</v>
+        <v>0.115025</v>
       </c>
       <c r="C1048" t="n">
         <v>0.157609</v>
@@ -14051,7 +14051,7 @@
         </is>
       </c>
       <c r="B1049" t="n">
-        <v>0.115324</v>
+        <v>0.116004</v>
       </c>
       <c r="C1049" t="n">
         <v>0.154891</v>
@@ -14064,7 +14064,7 @@
         </is>
       </c>
       <c r="B1050" t="n">
-        <v>0.116084</v>
+        <v>0.116209</v>
       </c>
       <c r="C1050" t="n">
         <v>0.152174</v>
@@ -14077,7 +14077,7 @@
         </is>
       </c>
       <c r="B1051" t="n">
-        <v>0.117447</v>
+        <v>0.117286</v>
       </c>
       <c r="C1051" t="n">
         <v>0.149457</v>
@@ -14090,7 +14090,7 @@
         </is>
       </c>
       <c r="B1052" t="n">
-        <v>0.118357</v>
+        <v>0.118296</v>
       </c>
       <c r="C1052" t="n">
         <v>0.146739</v>
@@ -14103,7 +14103,7 @@
         </is>
       </c>
       <c r="B1053" t="n">
-        <v>0.120138</v>
+        <v>0.120351</v>
       </c>
       <c r="C1053" t="n">
         <v>0.144022</v>
@@ -14116,7 +14116,7 @@
         </is>
       </c>
       <c r="B1054" t="n">
-        <v>0.120965</v>
+        <v>0.121165</v>
       </c>
       <c r="C1054" t="n">
         <v>0.141304</v>
@@ -14129,7 +14129,7 @@
         </is>
       </c>
       <c r="B1055" t="n">
-        <v>0.121211</v>
+        <v>0.121696</v>
       </c>
       <c r="C1055" t="n">
         <v>0.138587</v>
@@ -14142,7 +14142,7 @@
         </is>
       </c>
       <c r="B1056" t="n">
-        <v>0.121753</v>
+        <v>0.12228</v>
       </c>
       <c r="C1056" t="n">
         <v>0.13587</v>
@@ -14155,7 +14155,7 @@
         </is>
       </c>
       <c r="B1057" t="n">
-        <v>0.122888</v>
+        <v>0.122857</v>
       </c>
       <c r="C1057" t="n">
         <v>0.133152</v>
@@ -14168,7 +14168,7 @@
         </is>
       </c>
       <c r="B1058" t="n">
-        <v>0.122907</v>
+        <v>0.123304</v>
       </c>
       <c r="C1058" t="n">
         <v>0.130435</v>
@@ -14181,7 +14181,7 @@
         </is>
       </c>
       <c r="B1059" t="n">
-        <v>0.123192</v>
+        <v>0.123801</v>
       </c>
       <c r="C1059" t="n">
         <v>0.127717</v>
@@ -14194,7 +14194,7 @@
         </is>
       </c>
       <c r="B1060" t="n">
-        <v>0.124727</v>
+        <v>0.123882</v>
       </c>
       <c r="C1060" t="n">
         <v>0.125</v>
@@ -14207,7 +14207,7 @@
         </is>
       </c>
       <c r="B1061" t="n">
-        <v>0.124946</v>
+        <v>0.123925</v>
       </c>
       <c r="C1061" t="n">
         <v>0.122283</v>
@@ -14220,7 +14220,7 @@
         </is>
       </c>
       <c r="B1062" t="n">
-        <v>0.126033</v>
+        <v>0.126186</v>
       </c>
       <c r="C1062" t="n">
         <v>0.119565</v>
@@ -14233,7 +14233,7 @@
         </is>
       </c>
       <c r="B1063" t="n">
-        <v>0.127874</v>
+        <v>0.127876</v>
       </c>
       <c r="C1063" t="n">
         <v>0.116848</v>
@@ -14246,7 +14246,7 @@
         </is>
       </c>
       <c r="B1064" t="n">
-        <v>0.129215</v>
+        <v>0.129805</v>
       </c>
       <c r="C1064" t="n">
         <v>0.11413</v>
@@ -14259,7 +14259,7 @@
         </is>
       </c>
       <c r="B1065" t="n">
-        <v>0.129638</v>
+        <v>0.130395</v>
       </c>
       <c r="C1065" t="n">
         <v>0.111413</v>
@@ -14272,7 +14272,7 @@
         </is>
       </c>
       <c r="B1066" t="n">
-        <v>0.130967</v>
+        <v>0.131006</v>
       </c>
       <c r="C1066" t="n">
         <v>0.108696</v>
@@ -14285,7 +14285,7 @@
         </is>
       </c>
       <c r="B1067" t="n">
-        <v>0.131204</v>
+        <v>0.131081</v>
       </c>
       <c r="C1067" t="n">
         <v>0.105978</v>
@@ -14298,7 +14298,7 @@
         </is>
       </c>
       <c r="B1068" t="n">
-        <v>0.131358</v>
+        <v>0.13152</v>
       </c>
       <c r="C1068" t="n">
         <v>0.103261</v>
@@ -14311,7 +14311,7 @@
         </is>
       </c>
       <c r="B1069" t="n">
-        <v>0.132054</v>
+        <v>0.132213</v>
       </c>
       <c r="C1069" t="n">
         <v>0.100543</v>
@@ -14324,7 +14324,7 @@
         </is>
       </c>
       <c r="B1070" t="n">
-        <v>0.133063</v>
+        <v>0.132365</v>
       </c>
       <c r="C1070" t="n">
         <v>0.097826</v>
@@ -14337,7 +14337,7 @@
         </is>
       </c>
       <c r="B1071" t="n">
-        <v>0.133636</v>
+        <v>0.133567</v>
       </c>
       <c r="C1071" t="n">
         <v>0.095109</v>
@@ -14350,7 +14350,7 @@
         </is>
       </c>
       <c r="B1072" t="n">
-        <v>0.142179</v>
+        <v>0.142351</v>
       </c>
       <c r="C1072" t="n">
         <v>0.092391</v>
@@ -14363,7 +14363,7 @@
         </is>
       </c>
       <c r="B1073" t="n">
-        <v>0.143172</v>
+        <v>0.143204</v>
       </c>
       <c r="C1073" t="n">
         <v>0.089674</v>
@@ -14376,7 +14376,7 @@
         </is>
       </c>
       <c r="B1074" t="n">
-        <v>0.144373</v>
+        <v>0.144914</v>
       </c>
       <c r="C1074" t="n">
         <v>0.08695700000000001</v>
@@ -14389,7 +14389,7 @@
         </is>
       </c>
       <c r="B1075" t="n">
-        <v>0.146771</v>
+        <v>0.146673</v>
       </c>
       <c r="C1075" t="n">
         <v>0.08423899999999999</v>
@@ -14402,7 +14402,7 @@
         </is>
       </c>
       <c r="B1076" t="n">
-        <v>0.150042</v>
+        <v>0.150116</v>
       </c>
       <c r="C1076" t="n">
         <v>0.081522</v>
@@ -14415,7 +14415,7 @@
         </is>
       </c>
       <c r="B1077" t="n">
-        <v>0.15208</v>
+        <v>0.151951</v>
       </c>
       <c r="C1077" t="n">
         <v>0.078804</v>
@@ -14428,7 +14428,7 @@
         </is>
       </c>
       <c r="B1078" t="n">
-        <v>0.152329</v>
+        <v>0.153028</v>
       </c>
       <c r="C1078" t="n">
         <v>0.076087</v>
@@ -14441,7 +14441,7 @@
         </is>
       </c>
       <c r="B1079" t="n">
-        <v>0.156939</v>
+        <v>0.157227</v>
       </c>
       <c r="C1079" t="n">
         <v>0.07337</v>
@@ -14454,7 +14454,7 @@
         </is>
       </c>
       <c r="B1080" t="n">
-        <v>0.158515</v>
+        <v>0.159085</v>
       </c>
       <c r="C1080" t="n">
         <v>0.07065200000000001</v>
@@ -14467,7 +14467,7 @@
         </is>
       </c>
       <c r="B1081" t="n">
-        <v>0.16548</v>
+        <v>0.165923</v>
       </c>
       <c r="C1081" t="n">
         <v>0.067935</v>
@@ -14480,7 +14480,7 @@
         </is>
       </c>
       <c r="B1082" t="n">
-        <v>0.166298</v>
+        <v>0.166927</v>
       </c>
       <c r="C1082" t="n">
         <v>0.065217</v>
@@ -14493,7 +14493,7 @@
         </is>
       </c>
       <c r="B1083" t="n">
-        <v>0.166483</v>
+        <v>0.167034</v>
       </c>
       <c r="C1083" t="n">
         <v>0.0625</v>
@@ -14506,7 +14506,7 @@
         </is>
       </c>
       <c r="B1084" t="n">
-        <v>0.169156</v>
+        <v>0.170066</v>
       </c>
       <c r="C1084" t="n">
         <v>0.059783</v>
@@ -14519,7 +14519,7 @@
         </is>
       </c>
       <c r="B1085" t="n">
-        <v>0.170889</v>
+        <v>0.170643</v>
       </c>
       <c r="C1085" t="n">
         <v>0.057065</v>
@@ -14532,7 +14532,7 @@
         </is>
       </c>
       <c r="B1086" t="n">
-        <v>0.171827</v>
+        <v>0.172721</v>
       </c>
       <c r="C1086" t="n">
         <v>0.054348</v>
@@ -14545,7 +14545,7 @@
         </is>
       </c>
       <c r="B1087" t="n">
-        <v>0.173807</v>
+        <v>0.174711</v>
       </c>
       <c r="C1087" t="n">
         <v>0.05163</v>
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="B1088" t="n">
-        <v>0.180126</v>
+        <v>0.179604</v>
       </c>
       <c r="C1088" t="n">
         <v>0.048913</v>
@@ -14571,7 +14571,7 @@
         </is>
       </c>
       <c r="B1089" t="n">
-        <v>0.182651</v>
+        <v>0.182144</v>
       </c>
       <c r="C1089" t="n">
         <v>0.046196</v>
@@ -14584,7 +14584,7 @@
         </is>
       </c>
       <c r="B1090" t="n">
-        <v>0.182911</v>
+        <v>0.183671</v>
       </c>
       <c r="C1090" t="n">
         <v>0.043478</v>
@@ -14597,7 +14597,7 @@
         </is>
       </c>
       <c r="B1091" t="n">
-        <v>0.193335</v>
+        <v>0.19345</v>
       </c>
       <c r="C1091" t="n">
         <v>0.040761</v>
@@ -14610,7 +14610,7 @@
         </is>
       </c>
       <c r="B1092" t="n">
-        <v>0.195238</v>
+        <v>0.194107</v>
       </c>
       <c r="C1092" t="n">
         <v>0.038043</v>
@@ -14623,7 +14623,7 @@
         </is>
       </c>
       <c r="B1093" t="n">
-        <v>0.195286</v>
+        <v>0.196231</v>
       </c>
       <c r="C1093" t="n">
         <v>0.035326</v>
@@ -14636,7 +14636,7 @@
         </is>
       </c>
       <c r="B1094" t="n">
-        <v>0.212126</v>
+        <v>0.212601</v>
       </c>
       <c r="C1094" t="n">
         <v>0.032609</v>
@@ -14649,7 +14649,7 @@
         </is>
       </c>
       <c r="B1095" t="n">
-        <v>0.217414</v>
+        <v>0.218454</v>
       </c>
       <c r="C1095" t="n">
         <v>0.029891</v>
@@ -14662,7 +14662,7 @@
         </is>
       </c>
       <c r="B1096" t="n">
-        <v>0.22569</v>
+        <v>0.227002</v>
       </c>
       <c r="C1096" t="n">
         <v>0.027174</v>
@@ -14675,7 +14675,7 @@
         </is>
       </c>
       <c r="B1097" t="n">
-        <v>0.22603</v>
+        <v>0.22743</v>
       </c>
       <c r="C1097" t="n">
         <v>0.024457</v>
@@ -14688,7 +14688,7 @@
         </is>
       </c>
       <c r="B1098" t="n">
-        <v>0.228438</v>
+        <v>0.229768</v>
       </c>
       <c r="C1098" t="n">
         <v>0.021739</v>
@@ -14701,7 +14701,7 @@
         </is>
       </c>
       <c r="B1099" t="n">
-        <v>0.238965</v>
+        <v>0.238082</v>
       </c>
       <c r="C1099" t="n">
         <v>0.019022</v>
@@ -14714,7 +14714,7 @@
         </is>
       </c>
       <c r="B1100" t="n">
-        <v>0.245219</v>
+        <v>0.246269</v>
       </c>
       <c r="C1100" t="n">
         <v>0.016304</v>
@@ -14727,7 +14727,7 @@
         </is>
       </c>
       <c r="B1101" t="n">
-        <v>0.252624</v>
+        <v>0.253529</v>
       </c>
       <c r="C1101" t="n">
         <v>0.013587</v>
@@ -14740,7 +14740,7 @@
         </is>
       </c>
       <c r="B1102" t="n">
-        <v>0.273454</v>
+        <v>0.273627</v>
       </c>
       <c r="C1102" t="n">
         <v>0.01087</v>
@@ -14753,7 +14753,7 @@
         </is>
       </c>
       <c r="B1103" t="n">
-        <v>0.288865</v>
+        <v>0.290455</v>
       </c>
       <c r="C1103" t="n">
         <v>0.008152</v>
@@ -14766,7 +14766,7 @@
         </is>
       </c>
       <c r="B1104" t="n">
-        <v>0.316073</v>
+        <v>0.317016</v>
       </c>
       <c r="C1104" t="n">
         <v>0.005435</v>
@@ -14779,7 +14779,7 @@
         </is>
       </c>
       <c r="B1105" t="n">
-        <v>0.451438</v>
+        <v>0.453289</v>
       </c>
       <c r="C1105" t="n">
         <v>0.002717</v>

--- a/vignettes/vignette-2/tail_exceedance_plot_data.xlsx
+++ b/vignettes/vignette-2/tail_exceedance_plot_data.xlsx
@@ -5627,7 +5627,7 @@
         </is>
       </c>
       <c r="B401" t="n">
-        <v>0.000311</v>
+        <v>0.00031</v>
       </c>
       <c r="C401" t="n">
         <v>0.997487</v>
@@ -5653,7 +5653,7 @@
         </is>
       </c>
       <c r="B403" t="n">
-        <v>0.000918</v>
+        <v>0.000917</v>
       </c>
       <c r="C403" t="n">
         <v>0.992462</v>
@@ -5679,7 +5679,7 @@
         </is>
       </c>
       <c r="B405" t="n">
-        <v>0.00164</v>
+        <v>0.001639</v>
       </c>
       <c r="C405" t="n">
         <v>0.987437</v>
@@ -5705,7 +5705,7 @@
         </is>
       </c>
       <c r="B407" t="n">
-        <v>0.00198</v>
+        <v>0.001978</v>
       </c>
       <c r="C407" t="n">
         <v>0.982412</v>
@@ -5744,7 +5744,7 @@
         </is>
       </c>
       <c r="B410" t="n">
-        <v>0.00231</v>
+        <v>0.002308</v>
       </c>
       <c r="C410" t="n">
         <v>0.974874</v>
@@ -5757,7 +5757,7 @@
         </is>
       </c>
       <c r="B411" t="n">
-        <v>0.00244</v>
+        <v>0.002442</v>
       </c>
       <c r="C411" t="n">
         <v>0.9723619999999999</v>
@@ -5770,7 +5770,7 @@
         </is>
       </c>
       <c r="B412" t="n">
-        <v>0.002567</v>
+        <v>0.00257</v>
       </c>
       <c r="C412" t="n">
         <v>0.969849</v>
@@ -5783,7 +5783,7 @@
         </is>
       </c>
       <c r="B413" t="n">
-        <v>0.002855</v>
+        <v>0.002853</v>
       </c>
       <c r="C413" t="n">
         <v>0.967337</v>
@@ -5796,7 +5796,7 @@
         </is>
       </c>
       <c r="B414" t="n">
-        <v>0.002973</v>
+        <v>0.002972</v>
       </c>
       <c r="C414" t="n">
         <v>0.964824</v>
@@ -5809,7 +5809,7 @@
         </is>
       </c>
       <c r="B415" t="n">
-        <v>0.003082</v>
+        <v>0.00308</v>
       </c>
       <c r="C415" t="n">
         <v>0.9623119999999999</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="B417" t="n">
-        <v>0.004026</v>
+        <v>0.004024</v>
       </c>
       <c r="C417" t="n">
         <v>0.957286</v>
@@ -5848,7 +5848,7 @@
         </is>
       </c>
       <c r="B418" t="n">
-        <v>0.004095</v>
+        <v>0.004092</v>
       </c>
       <c r="C418" t="n">
         <v>0.954774</v>
@@ -5861,7 +5861,7 @@
         </is>
       </c>
       <c r="B419" t="n">
-        <v>0.00429</v>
+        <v>0.004289</v>
       </c>
       <c r="C419" t="n">
         <v>0.952261</v>
@@ -5874,7 +5874,7 @@
         </is>
       </c>
       <c r="B420" t="n">
-        <v>0.004443</v>
+        <v>0.004452</v>
       </c>
       <c r="C420" t="n">
         <v>0.949749</v>
@@ -5887,7 +5887,7 @@
         </is>
       </c>
       <c r="B421" t="n">
-        <v>0.004533</v>
+        <v>0.004531</v>
       </c>
       <c r="C421" t="n">
         <v>0.947236</v>
@@ -5900,7 +5900,7 @@
         </is>
       </c>
       <c r="B422" t="n">
-        <v>0.004546</v>
+        <v>0.00455</v>
       </c>
       <c r="C422" t="n">
         <v>0.944724</v>
@@ -5913,7 +5913,7 @@
         </is>
       </c>
       <c r="B423" t="n">
-        <v>0.004652</v>
+        <v>0.004649</v>
       </c>
       <c r="C423" t="n">
         <v>0.942211</v>
@@ -5926,7 +5926,7 @@
         </is>
       </c>
       <c r="B424" t="n">
-        <v>0.004925</v>
+        <v>0.004926</v>
       </c>
       <c r="C424" t="n">
         <v>0.939698</v>
@@ -5939,7 +5939,7 @@
         </is>
       </c>
       <c r="B425" t="n">
-        <v>0.004956</v>
+        <v>0.004962</v>
       </c>
       <c r="C425" t="n">
         <v>0.937186</v>
@@ -5952,7 +5952,7 @@
         </is>
       </c>
       <c r="B426" t="n">
-        <v>0.005007</v>
+        <v>0.005005</v>
       </c>
       <c r="C426" t="n">
         <v>0.934673</v>
@@ -5965,7 +5965,7 @@
         </is>
       </c>
       <c r="B427" t="n">
-        <v>0.00516</v>
+        <v>0.005157</v>
       </c>
       <c r="C427" t="n">
         <v>0.932161</v>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="B428" t="n">
-        <v>0.005312</v>
+        <v>0.005313</v>
       </c>
       <c r="C428" t="n">
         <v>0.929648</v>
@@ -5991,7 +5991,7 @@
         </is>
       </c>
       <c r="B429" t="n">
-        <v>0.005317</v>
+        <v>0.00532</v>
       </c>
       <c r="C429" t="n">
         <v>0.927136</v>
@@ -6004,7 +6004,7 @@
         </is>
       </c>
       <c r="B430" t="n">
-        <v>0.005835</v>
+        <v>0.005831</v>
       </c>
       <c r="C430" t="n">
         <v>0.924623</v>
@@ -6017,7 +6017,7 @@
         </is>
       </c>
       <c r="B431" t="n">
-        <v>0.006101</v>
+        <v>0.006097</v>
       </c>
       <c r="C431" t="n">
         <v>0.922111</v>
@@ -6030,7 +6030,7 @@
         </is>
       </c>
       <c r="B432" t="n">
-        <v>0.006599</v>
+        <v>0.006595</v>
       </c>
       <c r="C432" t="n">
         <v>0.919598</v>
@@ -6043,7 +6043,7 @@
         </is>
       </c>
       <c r="B433" t="n">
-        <v>0.007415</v>
+        <v>0.00741</v>
       </c>
       <c r="C433" t="n">
         <v>0.917085</v>
@@ -6056,7 +6056,7 @@
         </is>
       </c>
       <c r="B434" t="n">
-        <v>0.007627</v>
+        <v>0.007636</v>
       </c>
       <c r="C434" t="n">
         <v>0.914573</v>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="B435" t="n">
-        <v>0.00779</v>
+        <v>0.007791</v>
       </c>
       <c r="C435" t="n">
         <v>0.91206</v>
@@ -6082,7 +6082,7 @@
         </is>
       </c>
       <c r="B436" t="n">
-        <v>0.007927999999999999</v>
+        <v>0.007941</v>
       </c>
       <c r="C436" t="n">
         <v>0.909548</v>
@@ -6095,7 +6095,7 @@
         </is>
       </c>
       <c r="B437" t="n">
-        <v>0.007948999999999999</v>
+        <v>0.007943</v>
       </c>
       <c r="C437" t="n">
         <v>0.907035</v>
@@ -6121,7 +6121,7 @@
         </is>
       </c>
       <c r="B439" t="n">
-        <v>0.008147</v>
+        <v>0.008142</v>
       </c>
       <c r="C439" t="n">
         <v>0.90201</v>
@@ -6134,7 +6134,7 @@
         </is>
       </c>
       <c r="B440" t="n">
-        <v>0.008182999999999999</v>
+        <v>0.008189999999999999</v>
       </c>
       <c r="C440" t="n">
         <v>0.899497</v>
@@ -6147,7 +6147,7 @@
         </is>
       </c>
       <c r="B441" t="n">
-        <v>0.008423999999999999</v>
+        <v>0.008418999999999999</v>
       </c>
       <c r="C441" t="n">
         <v>0.896985</v>
@@ -6160,7 +6160,7 @@
         </is>
       </c>
       <c r="B442" t="n">
-        <v>0.008541</v>
+        <v>0.008541999999999999</v>
       </c>
       <c r="C442" t="n">
         <v>0.894472</v>
@@ -6173,7 +6173,7 @@
         </is>
       </c>
       <c r="B443" t="n">
-        <v>0.008702</v>
+        <v>0.008699</v>
       </c>
       <c r="C443" t="n">
         <v>0.89196</v>
@@ -6186,7 +6186,7 @@
         </is>
       </c>
       <c r="B444" t="n">
-        <v>0.008874999999999999</v>
+        <v>0.008883</v>
       </c>
       <c r="C444" t="n">
         <v>0.889447</v>
@@ -6199,7 +6199,7 @@
         </is>
       </c>
       <c r="B445" t="n">
-        <v>0.009540999999999999</v>
+        <v>0.009558000000000001</v>
       </c>
       <c r="C445" t="n">
         <v>0.886935</v>
@@ -6212,7 +6212,7 @@
         </is>
       </c>
       <c r="B446" t="n">
-        <v>0.009646</v>
+        <v>0.009643000000000001</v>
       </c>
       <c r="C446" t="n">
         <v>0.884422</v>
@@ -6225,7 +6225,7 @@
         </is>
       </c>
       <c r="B447" t="n">
-        <v>0.009684999999999999</v>
+        <v>0.009678000000000001</v>
       </c>
       <c r="C447" t="n">
         <v>0.88191</v>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="B449" t="n">
-        <v>0.009972</v>
+        <v>0.009967999999999999</v>
       </c>
       <c r="C449" t="n">
         <v>0.876884</v>
@@ -6264,7 +6264,7 @@
         </is>
       </c>
       <c r="B450" t="n">
-        <v>0.009998999999999999</v>
+        <v>0.009991999999999999</v>
       </c>
       <c r="C450" t="n">
         <v>0.874372</v>
@@ -6277,7 +6277,7 @@
         </is>
       </c>
       <c r="B451" t="n">
-        <v>0.010079</v>
+        <v>0.010085</v>
       </c>
       <c r="C451" t="n">
         <v>0.8718590000000001</v>
@@ -6290,7 +6290,7 @@
         </is>
       </c>
       <c r="B452" t="n">
-        <v>0.010255</v>
+        <v>0.010249</v>
       </c>
       <c r="C452" t="n">
         <v>0.869347</v>
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="B453" t="n">
-        <v>0.010383</v>
+        <v>0.010389</v>
       </c>
       <c r="C453" t="n">
         <v>0.866834</v>
@@ -6316,7 +6316,7 @@
         </is>
       </c>
       <c r="B454" t="n">
-        <v>0.010694</v>
+        <v>0.01069</v>
       </c>
       <c r="C454" t="n">
         <v>0.864322</v>
@@ -6329,7 +6329,7 @@
         </is>
       </c>
       <c r="B455" t="n">
-        <v>0.01096</v>
+        <v>0.010953</v>
       </c>
       <c r="C455" t="n">
         <v>0.861809</v>
@@ -6342,7 +6342,7 @@
         </is>
       </c>
       <c r="B456" t="n">
-        <v>0.011018</v>
+        <v>0.011016</v>
       </c>
       <c r="C456" t="n">
         <v>0.8592959999999999</v>
@@ -6355,7 +6355,7 @@
         </is>
       </c>
       <c r="B457" t="n">
-        <v>0.011158</v>
+        <v>0.011152</v>
       </c>
       <c r="C457" t="n">
         <v>0.856784</v>
@@ -6368,7 +6368,7 @@
         </is>
       </c>
       <c r="B458" t="n">
-        <v>0.011236</v>
+        <v>0.011231</v>
       </c>
       <c r="C458" t="n">
         <v>0.854271</v>
@@ -6381,7 +6381,7 @@
         </is>
       </c>
       <c r="B459" t="n">
-        <v>0.011613</v>
+        <v>0.011606</v>
       </c>
       <c r="C459" t="n">
         <v>0.851759</v>
@@ -6394,7 +6394,7 @@
         </is>
       </c>
       <c r="B460" t="n">
-        <v>0.011672</v>
+        <v>0.011676</v>
       </c>
       <c r="C460" t="n">
         <v>0.8492459999999999</v>
@@ -6407,7 +6407,7 @@
         </is>
       </c>
       <c r="B461" t="n">
-        <v>0.011677</v>
+        <v>0.011697</v>
       </c>
       <c r="C461" t="n">
         <v>0.846734</v>
@@ -6420,7 +6420,7 @@
         </is>
       </c>
       <c r="B462" t="n">
-        <v>0.012061</v>
+        <v>0.012053</v>
       </c>
       <c r="C462" t="n">
         <v>0.844221</v>
@@ -6433,7 +6433,7 @@
         </is>
       </c>
       <c r="B463" t="n">
-        <v>0.012198</v>
+        <v>0.012189</v>
       </c>
       <c r="C463" t="n">
         <v>0.841709</v>
@@ -6446,7 +6446,7 @@
         </is>
       </c>
       <c r="B464" t="n">
-        <v>0.01259</v>
+        <v>0.012583</v>
       </c>
       <c r="C464" t="n">
         <v>0.8391960000000001</v>
@@ -6459,7 +6459,7 @@
         </is>
       </c>
       <c r="B465" t="n">
-        <v>0.012726</v>
+        <v>0.012717</v>
       </c>
       <c r="C465" t="n">
         <v>0.836683</v>
@@ -6472,7 +6472,7 @@
         </is>
       </c>
       <c r="B466" t="n">
-        <v>0.012769</v>
+        <v>0.012781</v>
       </c>
       <c r="C466" t="n">
         <v>0.834171</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="B467" t="n">
-        <v>0.01279</v>
+        <v>0.012787</v>
       </c>
       <c r="C467" t="n">
         <v>0.831658</v>
@@ -6498,7 +6498,7 @@
         </is>
       </c>
       <c r="B468" t="n">
-        <v>0.012808</v>
+        <v>0.012819</v>
       </c>
       <c r="C468" t="n">
         <v>0.829146</v>
@@ -6511,7 +6511,7 @@
         </is>
       </c>
       <c r="B469" t="n">
-        <v>0.012945</v>
+        <v>0.012938</v>
       </c>
       <c r="C469" t="n">
         <v>0.826633</v>
@@ -6524,7 +6524,7 @@
         </is>
       </c>
       <c r="B470" t="n">
-        <v>0.013249</v>
+        <v>0.013268</v>
       </c>
       <c r="C470" t="n">
         <v>0.824121</v>
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="B471" t="n">
-        <v>0.013355</v>
+        <v>0.01335</v>
       </c>
       <c r="C471" t="n">
         <v>0.821608</v>
@@ -6550,7 +6550,7 @@
         </is>
       </c>
       <c r="B472" t="n">
-        <v>0.013437</v>
+        <v>0.013434</v>
       </c>
       <c r="C472" t="n">
         <v>0.819095</v>
@@ -6563,7 +6563,7 @@
         </is>
       </c>
       <c r="B473" t="n">
-        <v>0.01348</v>
+        <v>0.013492</v>
       </c>
       <c r="C473" t="n">
         <v>0.8165829999999999</v>
@@ -6576,7 +6576,7 @@
         </is>
       </c>
       <c r="B474" t="n">
-        <v>0.013844</v>
+        <v>0.013839</v>
       </c>
       <c r="C474" t="n">
         <v>0.81407</v>
@@ -6602,7 +6602,7 @@
         </is>
       </c>
       <c r="B476" t="n">
-        <v>0.01463</v>
+        <v>0.014624</v>
       </c>
       <c r="C476" t="n">
         <v>0.809045</v>
@@ -6615,7 +6615,7 @@
         </is>
       </c>
       <c r="B477" t="n">
-        <v>0.014788</v>
+        <v>0.014779</v>
       </c>
       <c r="C477" t="n">
         <v>0.8065330000000001</v>
@@ -6628,7 +6628,7 @@
         </is>
       </c>
       <c r="B478" t="n">
-        <v>0.014811</v>
+        <v>0.014824</v>
       </c>
       <c r="C478" t="n">
         <v>0.80402</v>
@@ -6641,7 +6641,7 @@
         </is>
       </c>
       <c r="B479" t="n">
-        <v>0.014916</v>
+        <v>0.014917</v>
       </c>
       <c r="C479" t="n">
         <v>0.801508</v>
@@ -6654,7 +6654,7 @@
         </is>
       </c>
       <c r="B480" t="n">
-        <v>0.015101</v>
+        <v>0.015096</v>
       </c>
       <c r="C480" t="n">
         <v>0.798995</v>
@@ -6667,7 +6667,7 @@
         </is>
       </c>
       <c r="B481" t="n">
-        <v>0.015165</v>
+        <v>0.015169</v>
       </c>
       <c r="C481" t="n">
         <v>0.796482</v>
@@ -6680,7 +6680,7 @@
         </is>
       </c>
       <c r="B482" t="n">
-        <v>0.015418</v>
+        <v>0.015427</v>
       </c>
       <c r="C482" t="n">
         <v>0.79397</v>
@@ -6693,7 +6693,7 @@
         </is>
       </c>
       <c r="B483" t="n">
-        <v>0.015712</v>
+        <v>0.015703</v>
       </c>
       <c r="C483" t="n">
         <v>0.791457</v>
@@ -6706,7 +6706,7 @@
         </is>
       </c>
       <c r="B484" t="n">
-        <v>0.015763</v>
+        <v>0.015754</v>
       </c>
       <c r="C484" t="n">
         <v>0.788945</v>
@@ -6719,7 +6719,7 @@
         </is>
       </c>
       <c r="B485" t="n">
-        <v>0.015964</v>
+        <v>0.015984</v>
       </c>
       <c r="C485" t="n">
         <v>0.786432</v>
@@ -6732,7 +6732,7 @@
         </is>
       </c>
       <c r="B486" t="n">
-        <v>0.015993</v>
+        <v>0.015996</v>
       </c>
       <c r="C486" t="n">
         <v>0.78392</v>
@@ -6745,7 +6745,7 @@
         </is>
       </c>
       <c r="B487" t="n">
-        <v>0.016585</v>
+        <v>0.016594</v>
       </c>
       <c r="C487" t="n">
         <v>0.781407</v>
@@ -6758,7 +6758,7 @@
         </is>
       </c>
       <c r="B488" t="n">
-        <v>0.016673</v>
+        <v>0.016661</v>
       </c>
       <c r="C488" t="n">
         <v>0.778894</v>
@@ -6771,7 +6771,7 @@
         </is>
       </c>
       <c r="B489" t="n">
-        <v>0.016876</v>
+        <v>0.016864</v>
       </c>
       <c r="C489" t="n">
         <v>0.776382</v>
@@ -6784,7 +6784,7 @@
         </is>
       </c>
       <c r="B490" t="n">
-        <v>0.017119</v>
+        <v>0.017108</v>
       </c>
       <c r="C490" t="n">
         <v>0.773869</v>
@@ -6797,7 +6797,7 @@
         </is>
       </c>
       <c r="B491" t="n">
-        <v>0.017225</v>
+        <v>0.017214</v>
       </c>
       <c r="C491" t="n">
         <v>0.771357</v>
@@ -6810,7 +6810,7 @@
         </is>
       </c>
       <c r="B492" t="n">
-        <v>0.017242</v>
+        <v>0.017231</v>
       </c>
       <c r="C492" t="n">
         <v>0.768844</v>
@@ -6823,7 +6823,7 @@
         </is>
       </c>
       <c r="B493" t="n">
-        <v>0.017388</v>
+        <v>0.017379</v>
       </c>
       <c r="C493" t="n">
         <v>0.766332</v>
@@ -6836,7 +6836,7 @@
         </is>
       </c>
       <c r="B494" t="n">
-        <v>0.017459</v>
+        <v>0.017447</v>
       </c>
       <c r="C494" t="n">
         <v>0.763819</v>
@@ -6849,7 +6849,7 @@
         </is>
       </c>
       <c r="B495" t="n">
-        <v>0.017591</v>
+        <v>0.0176</v>
       </c>
       <c r="C495" t="n">
         <v>0.761307</v>
@@ -6875,7 +6875,7 @@
         </is>
       </c>
       <c r="B497" t="n">
-        <v>0.017967</v>
+        <v>0.017955</v>
       </c>
       <c r="C497" t="n">
         <v>0.756281</v>
@@ -6888,7 +6888,7 @@
         </is>
       </c>
       <c r="B498" t="n">
-        <v>0.018633</v>
+        <v>0.018622</v>
       </c>
       <c r="C498" t="n">
         <v>0.753769</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="B499" t="n">
-        <v>0.018773</v>
+        <v>0.018772</v>
       </c>
       <c r="C499" t="n">
         <v>0.751256</v>
@@ -6914,7 +6914,7 @@
         </is>
       </c>
       <c r="B500" t="n">
-        <v>0.019036</v>
+        <v>0.019024</v>
       </c>
       <c r="C500" t="n">
         <v>0.748744</v>
@@ -6927,7 +6927,7 @@
         </is>
       </c>
       <c r="B501" t="n">
-        <v>0.019253</v>
+        <v>0.019274</v>
       </c>
       <c r="C501" t="n">
         <v>0.746231</v>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="B503" t="n">
-        <v>0.019627</v>
+        <v>0.019635</v>
       </c>
       <c r="C503" t="n">
         <v>0.741206</v>
@@ -6966,7 +6966,7 @@
         </is>
       </c>
       <c r="B504" t="n">
-        <v>0.020175</v>
+        <v>0.020161</v>
       </c>
       <c r="C504" t="n">
         <v>0.738693</v>
@@ -6979,7 +6979,7 @@
         </is>
       </c>
       <c r="B505" t="n">
-        <v>0.020269</v>
+        <v>0.02032</v>
       </c>
       <c r="C505" t="n">
         <v>0.736181</v>
@@ -6992,7 +6992,7 @@
         </is>
       </c>
       <c r="B506" t="n">
-        <v>0.020349</v>
+        <v>0.020339</v>
       </c>
       <c r="C506" t="n">
         <v>0.733668</v>
@@ -7005,7 +7005,7 @@
         </is>
       </c>
       <c r="B507" t="n">
-        <v>0.020659</v>
+        <v>0.020662</v>
       </c>
       <c r="C507" t="n">
         <v>0.731156</v>
@@ -7018,7 +7018,7 @@
         </is>
       </c>
       <c r="B508" t="n">
-        <v>0.021061</v>
+        <v>0.021046</v>
       </c>
       <c r="C508" t="n">
         <v>0.728643</v>
@@ -7031,7 +7031,7 @@
         </is>
       </c>
       <c r="B509" t="n">
-        <v>0.021072</v>
+        <v>0.021099</v>
       </c>
       <c r="C509" t="n">
         <v>0.726131</v>
@@ -7044,7 +7044,7 @@
         </is>
       </c>
       <c r="B510" t="n">
-        <v>0.021313</v>
+        <v>0.021312</v>
       </c>
       <c r="C510" t="n">
         <v>0.723618</v>
@@ -7057,7 +7057,7 @@
         </is>
       </c>
       <c r="B511" t="n">
-        <v>0.021449</v>
+        <v>0.021486</v>
       </c>
       <c r="C511" t="n">
         <v>0.721106</v>
@@ -7070,7 +7070,7 @@
         </is>
       </c>
       <c r="B512" t="n">
-        <v>0.02161</v>
+        <v>0.021595</v>
       </c>
       <c r="C512" t="n">
         <v>0.718593</v>
@@ -7083,7 +7083,7 @@
         </is>
       </c>
       <c r="B513" t="n">
-        <v>0.02174</v>
+        <v>0.021759</v>
       </c>
       <c r="C513" t="n">
         <v>0.71608</v>
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="B514" t="n">
-        <v>0.021955</v>
+        <v>0.021953</v>
       </c>
       <c r="C514" t="n">
         <v>0.713568</v>
@@ -7109,7 +7109,7 @@
         </is>
       </c>
       <c r="B515" t="n">
-        <v>0.022125</v>
+        <v>0.02212</v>
       </c>
       <c r="C515" t="n">
         <v>0.711055</v>
@@ -7122,7 +7122,7 @@
         </is>
       </c>
       <c r="B516" t="n">
-        <v>0.022165</v>
+        <v>0.02221</v>
       </c>
       <c r="C516" t="n">
         <v>0.708543</v>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="B517" t="n">
-        <v>0.022496</v>
+        <v>0.022499</v>
       </c>
       <c r="C517" t="n">
         <v>0.70603</v>
@@ -7148,7 +7148,7 @@
         </is>
       </c>
       <c r="B518" t="n">
-        <v>0.022509</v>
+        <v>0.022534</v>
       </c>
       <c r="C518" t="n">
         <v>0.703518</v>
@@ -7161,7 +7161,7 @@
         </is>
       </c>
       <c r="B519" t="n">
-        <v>0.022917</v>
+        <v>0.022901</v>
       </c>
       <c r="C519" t="n">
         <v>0.701005</v>
@@ -7174,7 +7174,7 @@
         </is>
       </c>
       <c r="B520" t="n">
-        <v>0.022966</v>
+        <v>0.022955</v>
       </c>
       <c r="C520" t="n">
         <v>0.698492</v>
@@ -7187,7 +7187,7 @@
         </is>
       </c>
       <c r="B521" t="n">
-        <v>0.02308</v>
+        <v>0.023064</v>
       </c>
       <c r="C521" t="n">
         <v>0.69598</v>
@@ -7200,7 +7200,7 @@
         </is>
       </c>
       <c r="B522" t="n">
-        <v>0.023125</v>
+        <v>0.023113</v>
       </c>
       <c r="C522" t="n">
         <v>0.6934669999999999</v>
@@ -7213,7 +7213,7 @@
         </is>
       </c>
       <c r="B523" t="n">
-        <v>0.023458</v>
+        <v>0.023453</v>
       </c>
       <c r="C523" t="n">
         <v>0.690955</v>
@@ -7226,7 +7226,7 @@
         </is>
       </c>
       <c r="B524" t="n">
-        <v>0.023545</v>
+        <v>0.023533</v>
       </c>
       <c r="C524" t="n">
         <v>0.688442</v>
@@ -7239,7 +7239,7 @@
         </is>
       </c>
       <c r="B525" t="n">
-        <v>0.02362</v>
+        <v>0.02363</v>
       </c>
       <c r="C525" t="n">
         <v>0.68593</v>
@@ -7252,7 +7252,7 @@
         </is>
       </c>
       <c r="B526" t="n">
-        <v>0.023763</v>
+        <v>0.023767</v>
       </c>
       <c r="C526" t="n">
         <v>0.6834170000000001</v>
@@ -7265,7 +7265,7 @@
         </is>
       </c>
       <c r="B527" t="n">
-        <v>0.023828</v>
+        <v>0.023818</v>
       </c>
       <c r="C527" t="n">
         <v>0.680905</v>
@@ -7278,7 +7278,7 @@
         </is>
       </c>
       <c r="B528" t="n">
-        <v>0.023965</v>
+        <v>0.023977</v>
       </c>
       <c r="C528" t="n">
         <v>0.678392</v>
@@ -7291,7 +7291,7 @@
         </is>
       </c>
       <c r="B529" t="n">
-        <v>0.025381</v>
+        <v>0.025363</v>
       </c>
       <c r="C529" t="n">
         <v>0.675879</v>
@@ -7304,7 +7304,7 @@
         </is>
       </c>
       <c r="B530" t="n">
-        <v>0.025403</v>
+        <v>0.025387</v>
       </c>
       <c r="C530" t="n">
         <v>0.673367</v>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="B531" t="n">
-        <v>0.025514</v>
+        <v>0.025502</v>
       </c>
       <c r="C531" t="n">
         <v>0.670854</v>
@@ -7330,7 +7330,7 @@
         </is>
       </c>
       <c r="B532" t="n">
-        <v>0.025824</v>
+        <v>0.025806</v>
       </c>
       <c r="C532" t="n">
         <v>0.668342</v>
@@ -7343,7 +7343,7 @@
         </is>
       </c>
       <c r="B533" t="n">
-        <v>0.025873</v>
+        <v>0.025858</v>
       </c>
       <c r="C533" t="n">
         <v>0.665829</v>
@@ -7356,7 +7356,7 @@
         </is>
       </c>
       <c r="B534" t="n">
-        <v>0.025967</v>
+        <v>0.025974</v>
       </c>
       <c r="C534" t="n">
         <v>0.663317</v>
@@ -7369,7 +7369,7 @@
         </is>
       </c>
       <c r="B535" t="n">
-        <v>0.025968</v>
+        <v>0.025976</v>
       </c>
       <c r="C535" t="n">
         <v>0.6608039999999999</v>
@@ -7382,7 +7382,7 @@
         </is>
       </c>
       <c r="B536" t="n">
-        <v>0.026379</v>
+        <v>0.026372</v>
       </c>
       <c r="C536" t="n">
         <v>0.658291</v>
@@ -7395,7 +7395,7 @@
         </is>
       </c>
       <c r="B537" t="n">
-        <v>0.02641</v>
+        <v>0.026392</v>
       </c>
       <c r="C537" t="n">
         <v>0.655779</v>
@@ -7408,7 +7408,7 @@
         </is>
       </c>
       <c r="B538" t="n">
-        <v>0.026745</v>
+        <v>0.026733</v>
       </c>
       <c r="C538" t="n">
         <v>0.653266</v>
@@ -7421,7 +7421,7 @@
         </is>
       </c>
       <c r="B539" t="n">
-        <v>0.026867</v>
+        <v>0.026902</v>
       </c>
       <c r="C539" t="n">
         <v>0.6507540000000001</v>
@@ -7434,7 +7434,7 @@
         </is>
       </c>
       <c r="B540" t="n">
-        <v>0.027078</v>
+        <v>0.027059</v>
       </c>
       <c r="C540" t="n">
         <v>0.648241</v>
@@ -7447,7 +7447,7 @@
         </is>
       </c>
       <c r="B541" t="n">
-        <v>0.027172</v>
+        <v>0.027153</v>
       </c>
       <c r="C541" t="n">
         <v>0.645729</v>
@@ -7460,7 +7460,7 @@
         </is>
       </c>
       <c r="B542" t="n">
-        <v>0.027636</v>
+        <v>0.027629</v>
       </c>
       <c r="C542" t="n">
         <v>0.643216</v>
@@ -7473,7 +7473,7 @@
         </is>
       </c>
       <c r="B543" t="n">
-        <v>0.027978</v>
+        <v>0.028032</v>
       </c>
       <c r="C543" t="n">
         <v>0.6407040000000001</v>
@@ -7486,7 +7486,7 @@
         </is>
       </c>
       <c r="B544" t="n">
-        <v>0.028072</v>
+        <v>0.028055</v>
       </c>
       <c r="C544" t="n">
         <v>0.638191</v>
@@ -7499,7 +7499,7 @@
         </is>
       </c>
       <c r="B545" t="n">
-        <v>0.028114</v>
+        <v>0.028158</v>
       </c>
       <c r="C545" t="n">
         <v>0.635678</v>
@@ -7512,7 +7512,7 @@
         </is>
       </c>
       <c r="B546" t="n">
-        <v>0.028123</v>
+        <v>0.028169</v>
       </c>
       <c r="C546" t="n">
         <v>0.633166</v>
@@ -7525,7 +7525,7 @@
         </is>
       </c>
       <c r="B547" t="n">
-        <v>0.028367</v>
+        <v>0.02835</v>
       </c>
       <c r="C547" t="n">
         <v>0.630653</v>
@@ -7538,7 +7538,7 @@
         </is>
       </c>
       <c r="B548" t="n">
-        <v>0.028622</v>
+        <v>0.028601</v>
       </c>
       <c r="C548" t="n">
         <v>0.6281409999999999</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="B549" t="n">
-        <v>0.028891</v>
+        <v>0.028882</v>
       </c>
       <c r="C549" t="n">
         <v>0.625628</v>
@@ -7564,7 +7564,7 @@
         </is>
       </c>
       <c r="B550" t="n">
-        <v>0.029031</v>
+        <v>0.029038</v>
       </c>
       <c r="C550" t="n">
         <v>0.623116</v>
@@ -7577,7 +7577,7 @@
         </is>
       </c>
       <c r="B551" t="n">
-        <v>0.029054</v>
+        <v>0.029053</v>
       </c>
       <c r="C551" t="n">
         <v>0.620603</v>
@@ -7590,7 +7590,7 @@
         </is>
       </c>
       <c r="B552" t="n">
-        <v>0.029205</v>
+        <v>0.029238</v>
       </c>
       <c r="C552" t="n">
         <v>0.61809</v>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="B553" t="n">
-        <v>0.029415</v>
+        <v>0.029394</v>
       </c>
       <c r="C553" t="n">
         <v>0.615578</v>
@@ -7616,7 +7616,7 @@
         </is>
       </c>
       <c r="B554" t="n">
-        <v>0.029621</v>
+        <v>0.029618</v>
       </c>
       <c r="C554" t="n">
         <v>0.613065</v>
@@ -7629,7 +7629,7 @@
         </is>
       </c>
       <c r="B555" t="n">
-        <v>0.029803</v>
+        <v>0.029785</v>
       </c>
       <c r="C555" t="n">
         <v>0.610553</v>
@@ -7642,7 +7642,7 @@
         </is>
       </c>
       <c r="B556" t="n">
-        <v>0.029822</v>
+        <v>0.02981</v>
       </c>
       <c r="C556" t="n">
         <v>0.60804</v>
@@ -7655,7 +7655,7 @@
         </is>
       </c>
       <c r="B557" t="n">
-        <v>0.029986</v>
+        <v>0.03</v>
       </c>
       <c r="C557" t="n">
         <v>0.605528</v>
@@ -7668,7 +7668,7 @@
         </is>
       </c>
       <c r="B558" t="n">
-        <v>0.030124</v>
+        <v>0.030112</v>
       </c>
       <c r="C558" t="n">
         <v>0.603015</v>
@@ -7681,7 +7681,7 @@
         </is>
       </c>
       <c r="B559" t="n">
-        <v>0.030239</v>
+        <v>0.030257</v>
       </c>
       <c r="C559" t="n">
         <v>0.600503</v>
@@ -7694,7 +7694,7 @@
         </is>
       </c>
       <c r="B560" t="n">
-        <v>0.030351</v>
+        <v>0.030352</v>
       </c>
       <c r="C560" t="n">
         <v>0.59799</v>
@@ -7707,7 +7707,7 @@
         </is>
       </c>
       <c r="B561" t="n">
-        <v>0.030449</v>
+        <v>0.030427</v>
       </c>
       <c r="C561" t="n">
         <v>0.595477</v>
@@ -7720,7 +7720,7 @@
         </is>
       </c>
       <c r="B562" t="n">
-        <v>0.031192</v>
+        <v>0.031173</v>
       </c>
       <c r="C562" t="n">
         <v>0.592965</v>
@@ -7733,7 +7733,7 @@
         </is>
       </c>
       <c r="B563" t="n">
-        <v>0.03133</v>
+        <v>0.031338</v>
       </c>
       <c r="C563" t="n">
         <v>0.590452</v>
@@ -7746,7 +7746,7 @@
         </is>
       </c>
       <c r="B564" t="n">
-        <v>0.031513</v>
+        <v>0.031491</v>
       </c>
       <c r="C564" t="n">
         <v>0.58794</v>
@@ -7759,7 +7759,7 @@
         </is>
       </c>
       <c r="B565" t="n">
-        <v>0.031573</v>
+        <v>0.03156</v>
       </c>
       <c r="C565" t="n">
         <v>0.585427</v>
@@ -7772,7 +7772,7 @@
         </is>
       </c>
       <c r="B566" t="n">
-        <v>0.031835</v>
+        <v>0.031824</v>
       </c>
       <c r="C566" t="n">
         <v>0.582915</v>
@@ -7785,7 +7785,7 @@
         </is>
       </c>
       <c r="B567" t="n">
-        <v>0.031987</v>
+        <v>0.031966</v>
       </c>
       <c r="C567" t="n">
         <v>0.580402</v>
@@ -7798,7 +7798,7 @@
         </is>
       </c>
       <c r="B568" t="n">
-        <v>0.031991</v>
+        <v>0.031977</v>
       </c>
       <c r="C568" t="n">
         <v>0.577889</v>
@@ -7811,7 +7811,7 @@
         </is>
       </c>
       <c r="B569" t="n">
-        <v>0.032055</v>
+        <v>0.032052</v>
       </c>
       <c r="C569" t="n">
         <v>0.575377</v>
@@ -7824,7 +7824,7 @@
         </is>
       </c>
       <c r="B570" t="n">
-        <v>0.032643</v>
+        <v>0.032622</v>
       </c>
       <c r="C570" t="n">
         <v>0.572864</v>
@@ -7850,7 +7850,7 @@
         </is>
       </c>
       <c r="B572" t="n">
-        <v>0.032686</v>
+        <v>0.032674</v>
       </c>
       <c r="C572" t="n">
         <v>0.567839</v>
@@ -7863,7 +7863,7 @@
         </is>
       </c>
       <c r="B573" t="n">
-        <v>0.033222</v>
+        <v>0.033232</v>
       </c>
       <c r="C573" t="n">
         <v>0.565327</v>
@@ -7876,7 +7876,7 @@
         </is>
       </c>
       <c r="B574" t="n">
-        <v>0.033534</v>
+        <v>0.033604</v>
       </c>
       <c r="C574" t="n">
         <v>0.562814</v>
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="B575" t="n">
-        <v>0.033997</v>
+        <v>0.033998</v>
       </c>
       <c r="C575" t="n">
         <v>0.560302</v>
@@ -7902,7 +7902,7 @@
         </is>
       </c>
       <c r="B576" t="n">
-        <v>0.034279</v>
+        <v>0.034255</v>
       </c>
       <c r="C576" t="n">
         <v>0.557789</v>
@@ -7915,7 +7915,7 @@
         </is>
       </c>
       <c r="B577" t="n">
-        <v>0.034349</v>
+        <v>0.034332</v>
       </c>
       <c r="C577" t="n">
         <v>0.555276</v>
@@ -7928,7 +7928,7 @@
         </is>
       </c>
       <c r="B578" t="n">
-        <v>0.034919</v>
+        <v>0.034975</v>
       </c>
       <c r="C578" t="n">
         <v>0.552764</v>
@@ -7941,7 +7941,7 @@
         </is>
       </c>
       <c r="B579" t="n">
-        <v>0.035175</v>
+        <v>0.035167</v>
       </c>
       <c r="C579" t="n">
         <v>0.550251</v>
@@ -7954,7 +7954,7 @@
         </is>
       </c>
       <c r="B580" t="n">
-        <v>0.035291</v>
+        <v>0.035272</v>
       </c>
       <c r="C580" t="n">
         <v>0.547739</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="B581" t="n">
-        <v>0.035357</v>
+        <v>0.035342</v>
       </c>
       <c r="C581" t="n">
         <v>0.545226</v>
@@ -7980,7 +7980,7 @@
         </is>
       </c>
       <c r="B582" t="n">
-        <v>0.035589</v>
+        <v>0.035577</v>
       </c>
       <c r="C582" t="n">
         <v>0.542714</v>
@@ -7993,7 +7993,7 @@
         </is>
       </c>
       <c r="B583" t="n">
-        <v>0.035589</v>
+        <v>0.035584</v>
       </c>
       <c r="C583" t="n">
         <v>0.540201</v>
@@ -8006,7 +8006,7 @@
         </is>
       </c>
       <c r="B584" t="n">
-        <v>0.035609</v>
+        <v>0.035616</v>
       </c>
       <c r="C584" t="n">
         <v>0.5376880000000001</v>
@@ -8019,7 +8019,7 @@
         </is>
       </c>
       <c r="B585" t="n">
-        <v>0.036372</v>
+        <v>0.036347</v>
       </c>
       <c r="C585" t="n">
         <v>0.535176</v>
@@ -8032,7 +8032,7 @@
         </is>
       </c>
       <c r="B586" t="n">
-        <v>0.036374</v>
+        <v>0.036358</v>
       </c>
       <c r="C586" t="n">
         <v>0.532663</v>
@@ -8045,7 +8045,7 @@
         </is>
       </c>
       <c r="B587" t="n">
-        <v>0.036407</v>
+        <v>0.036382</v>
       </c>
       <c r="C587" t="n">
         <v>0.530151</v>
@@ -8058,7 +8058,7 @@
         </is>
       </c>
       <c r="B588" t="n">
-        <v>0.036422</v>
+        <v>0.03643</v>
       </c>
       <c r="C588" t="n">
         <v>0.5276380000000001</v>
@@ -8071,7 +8071,7 @@
         </is>
       </c>
       <c r="B589" t="n">
-        <v>0.036456</v>
+        <v>0.036444</v>
       </c>
       <c r="C589" t="n">
         <v>0.525126</v>
@@ -8084,7 +8084,7 @@
         </is>
       </c>
       <c r="B590" t="n">
-        <v>0.03786</v>
+        <v>0.037839</v>
       </c>
       <c r="C590" t="n">
         <v>0.522613</v>
@@ -8097,7 +8097,7 @@
         </is>
       </c>
       <c r="B591" t="n">
-        <v>0.038088</v>
+        <v>0.038077</v>
       </c>
       <c r="C591" t="n">
         <v>0.520101</v>
@@ -8110,7 +8110,7 @@
         </is>
       </c>
       <c r="B592" t="n">
-        <v>0.038341</v>
+        <v>0.038321</v>
       </c>
       <c r="C592" t="n">
         <v>0.517588</v>
@@ -8123,7 +8123,7 @@
         </is>
       </c>
       <c r="B593" t="n">
-        <v>0.038666</v>
+        <v>0.038688</v>
       </c>
       <c r="C593" t="n">
         <v>0.5150749999999999</v>
@@ -8136,7 +8136,7 @@
         </is>
       </c>
       <c r="B594" t="n">
-        <v>0.038837</v>
+        <v>0.038821</v>
       </c>
       <c r="C594" t="n">
         <v>0.512563</v>
@@ -8149,7 +8149,7 @@
         </is>
       </c>
       <c r="B595" t="n">
-        <v>0.038938</v>
+        <v>0.038915</v>
       </c>
       <c r="C595" t="n">
         <v>0.51005</v>
@@ -8162,7 +8162,7 @@
         </is>
       </c>
       <c r="B596" t="n">
-        <v>0.03905</v>
+        <v>0.039028</v>
       </c>
       <c r="C596" t="n">
         <v>0.507538</v>
@@ -8175,7 +8175,7 @@
         </is>
       </c>
       <c r="B597" t="n">
-        <v>0.039132</v>
+        <v>0.039195</v>
       </c>
       <c r="C597" t="n">
         <v>0.5050249999999999</v>
@@ -8188,7 +8188,7 @@
         </is>
       </c>
       <c r="B598" t="n">
-        <v>0.039603</v>
+        <v>0.03958</v>
       </c>
       <c r="C598" t="n">
         <v>0.502513</v>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="B599" t="n">
-        <v>0.039682</v>
+        <v>0.039666</v>
       </c>
       <c r="C599" t="n">
         <v>0.5</v>
@@ -8214,7 +8214,7 @@
         </is>
       </c>
       <c r="B600" t="n">
-        <v>0.039728</v>
+        <v>0.039699</v>
       </c>
       <c r="C600" t="n">
         <v>0.497487</v>
@@ -8227,7 +8227,7 @@
         </is>
       </c>
       <c r="B601" t="n">
-        <v>0.039906</v>
+        <v>0.039932</v>
       </c>
       <c r="C601" t="n">
         <v>0.494975</v>
@@ -8240,7 +8240,7 @@
         </is>
       </c>
       <c r="B602" t="n">
-        <v>0.039957</v>
+        <v>0.039933</v>
       </c>
       <c r="C602" t="n">
         <v>0.492462</v>
@@ -8253,7 +8253,7 @@
         </is>
       </c>
       <c r="B603" t="n">
-        <v>0.040076</v>
+        <v>0.040054</v>
       </c>
       <c r="C603" t="n">
         <v>0.48995</v>
@@ -8266,7 +8266,7 @@
         </is>
       </c>
       <c r="B604" t="n">
-        <v>0.040171</v>
+        <v>0.040159</v>
       </c>
       <c r="C604" t="n">
         <v>0.487437</v>
@@ -8279,7 +8279,7 @@
         </is>
       </c>
       <c r="B605" t="n">
-        <v>0.040234</v>
+        <v>0.040297</v>
       </c>
       <c r="C605" t="n">
         <v>0.484925</v>
@@ -8292,7 +8292,7 @@
         </is>
       </c>
       <c r="B606" t="n">
-        <v>0.040324</v>
+        <v>0.040336</v>
       </c>
       <c r="C606" t="n">
         <v>0.482412</v>
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="B607" t="n">
-        <v>0.040509</v>
+        <v>0.040481</v>
       </c>
       <c r="C607" t="n">
         <v>0.479899</v>
@@ -8318,7 +8318,7 @@
         </is>
       </c>
       <c r="B608" t="n">
-        <v>0.041057</v>
+        <v>0.04103</v>
       </c>
       <c r="C608" t="n">
         <v>0.477387</v>
@@ -8331,7 +8331,7 @@
         </is>
       </c>
       <c r="B609" t="n">
-        <v>0.041096</v>
+        <v>0.041067</v>
       </c>
       <c r="C609" t="n">
         <v>0.474874</v>
@@ -8344,7 +8344,7 @@
         </is>
       </c>
       <c r="B610" t="n">
-        <v>0.041301</v>
+        <v>0.041309</v>
       </c>
       <c r="C610" t="n">
         <v>0.472362</v>
@@ -8357,7 +8357,7 @@
         </is>
       </c>
       <c r="B611" t="n">
-        <v>0.041681</v>
+        <v>0.041679</v>
       </c>
       <c r="C611" t="n">
         <v>0.469849</v>
@@ -8370,7 +8370,7 @@
         </is>
       </c>
       <c r="B612" t="n">
-        <v>0.04182</v>
+        <v>0.04179</v>
       </c>
       <c r="C612" t="n">
         <v>0.467337</v>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="B613" t="n">
-        <v>0.042156</v>
+        <v>0.042256</v>
       </c>
       <c r="C613" t="n">
         <v>0.464824</v>
@@ -8396,7 +8396,7 @@
         </is>
       </c>
       <c r="B614" t="n">
-        <v>0.042289</v>
+        <v>0.042259</v>
       </c>
       <c r="C614" t="n">
         <v>0.462312</v>
@@ -8409,7 +8409,7 @@
         </is>
       </c>
       <c r="B615" t="n">
-        <v>0.042372</v>
+        <v>0.042355</v>
       </c>
       <c r="C615" t="n">
         <v>0.459799</v>
@@ -8422,7 +8422,7 @@
         </is>
       </c>
       <c r="B616" t="n">
-        <v>0.043259</v>
+        <v>0.043233</v>
       </c>
       <c r="C616" t="n">
         <v>0.457286</v>
@@ -8435,7 +8435,7 @@
         </is>
       </c>
       <c r="B617" t="n">
-        <v>0.043766</v>
+        <v>0.043752</v>
       </c>
       <c r="C617" t="n">
         <v>0.454774</v>
@@ -8448,7 +8448,7 @@
         </is>
       </c>
       <c r="B618" t="n">
-        <v>0.044583</v>
+        <v>0.044561</v>
       </c>
       <c r="C618" t="n">
         <v>0.452261</v>
@@ -8461,7 +8461,7 @@
         </is>
       </c>
       <c r="B619" t="n">
-        <v>0.044913</v>
+        <v>0.045001</v>
       </c>
       <c r="C619" t="n">
         <v>0.449749</v>
@@ -8474,7 +8474,7 @@
         </is>
       </c>
       <c r="B620" t="n">
-        <v>0.044954</v>
+        <v>0.045067</v>
       </c>
       <c r="C620" t="n">
         <v>0.447236</v>
@@ -8487,7 +8487,7 @@
         </is>
       </c>
       <c r="B621" t="n">
-        <v>0.0451</v>
+        <v>0.045173</v>
       </c>
       <c r="C621" t="n">
         <v>0.444724</v>
@@ -8500,7 +8500,7 @@
         </is>
       </c>
       <c r="B622" t="n">
-        <v>0.045235</v>
+        <v>0.045214</v>
       </c>
       <c r="C622" t="n">
         <v>0.442211</v>
@@ -8513,7 +8513,7 @@
         </is>
       </c>
       <c r="B623" t="n">
-        <v>0.045246</v>
+        <v>0.045214</v>
       </c>
       <c r="C623" t="n">
         <v>0.439698</v>
@@ -8526,7 +8526,7 @@
         </is>
       </c>
       <c r="B624" t="n">
-        <v>0.046139</v>
+        <v>0.04622</v>
       </c>
       <c r="C624" t="n">
         <v>0.437186</v>
@@ -8539,7 +8539,7 @@
         </is>
       </c>
       <c r="B625" t="n">
-        <v>0.046703</v>
+        <v>0.046692</v>
       </c>
       <c r="C625" t="n">
         <v>0.434673</v>
@@ -8552,7 +8552,7 @@
         </is>
       </c>
       <c r="B626" t="n">
-        <v>0.047042</v>
+        <v>0.047058</v>
       </c>
       <c r="C626" t="n">
         <v>0.432161</v>
@@ -8565,7 +8565,7 @@
         </is>
       </c>
       <c r="B627" t="n">
-        <v>0.047142</v>
+        <v>0.047133</v>
       </c>
       <c r="C627" t="n">
         <v>0.429648</v>
@@ -8578,7 +8578,7 @@
         </is>
       </c>
       <c r="B628" t="n">
-        <v>0.047236</v>
+        <v>0.047275</v>
       </c>
       <c r="C628" t="n">
         <v>0.427136</v>
@@ -8591,7 +8591,7 @@
         </is>
       </c>
       <c r="B629" t="n">
-        <v>0.047768</v>
+        <v>0.047767</v>
       </c>
       <c r="C629" t="n">
         <v>0.424623</v>
@@ -8604,7 +8604,7 @@
         </is>
       </c>
       <c r="B630" t="n">
-        <v>0.047797</v>
+        <v>0.047866</v>
       </c>
       <c r="C630" t="n">
         <v>0.422111</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="B631" t="n">
-        <v>0.0482</v>
+        <v>0.048207</v>
       </c>
       <c r="C631" t="n">
         <v>0.419598</v>
@@ -8630,7 +8630,7 @@
         </is>
       </c>
       <c r="B632" t="n">
-        <v>0.048304</v>
+        <v>0.048274</v>
       </c>
       <c r="C632" t="n">
         <v>0.417085</v>
@@ -8643,7 +8643,7 @@
         </is>
       </c>
       <c r="B633" t="n">
-        <v>0.048359</v>
+        <v>0.048325</v>
       </c>
       <c r="C633" t="n">
         <v>0.414573</v>
@@ -8656,7 +8656,7 @@
         </is>
       </c>
       <c r="B634" t="n">
-        <v>0.048471</v>
+        <v>0.048466</v>
       </c>
       <c r="C634" t="n">
         <v>0.41206</v>
@@ -8669,7 +8669,7 @@
         </is>
       </c>
       <c r="B635" t="n">
-        <v>0.048505</v>
+        <v>0.0485</v>
       </c>
       <c r="C635" t="n">
         <v>0.409548</v>
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="B636" t="n">
-        <v>0.048563</v>
+        <v>0.048546</v>
       </c>
       <c r="C636" t="n">
         <v>0.407035</v>
@@ -8695,7 +8695,7 @@
         </is>
       </c>
       <c r="B637" t="n">
-        <v>0.048568</v>
+        <v>0.048657</v>
       </c>
       <c r="C637" t="n">
         <v>0.404523</v>
@@ -8708,7 +8708,7 @@
         </is>
       </c>
       <c r="B638" t="n">
-        <v>0.048681</v>
+        <v>0.048666</v>
       </c>
       <c r="C638" t="n">
         <v>0.40201</v>
@@ -8721,7 +8721,7 @@
         </is>
       </c>
       <c r="B639" t="n">
-        <v>0.049008</v>
+        <v>0.048973</v>
       </c>
       <c r="C639" t="n">
         <v>0.399497</v>
@@ -8734,7 +8734,7 @@
         </is>
       </c>
       <c r="B640" t="n">
-        <v>0.049268</v>
+        <v>0.049233</v>
       </c>
       <c r="C640" t="n">
         <v>0.396985</v>
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="B641" t="n">
-        <v>0.049838</v>
+        <v>0.049872</v>
       </c>
       <c r="C641" t="n">
         <v>0.394472</v>
@@ -8760,7 +8760,7 @@
         </is>
       </c>
       <c r="B642" t="n">
-        <v>0.049939</v>
+        <v>0.049912</v>
       </c>
       <c r="C642" t="n">
         <v>0.39196</v>
@@ -8773,7 +8773,7 @@
         </is>
       </c>
       <c r="B643" t="n">
-        <v>0.050266</v>
+        <v>0.050254</v>
       </c>
       <c r="C643" t="n">
         <v>0.389447</v>
@@ -8786,7 +8786,7 @@
         </is>
       </c>
       <c r="B644" t="n">
-        <v>0.050435</v>
+        <v>0.050402</v>
       </c>
       <c r="C644" t="n">
         <v>0.386935</v>
@@ -8799,7 +8799,7 @@
         </is>
       </c>
       <c r="B645" t="n">
-        <v>0.050795</v>
+        <v>0.050759</v>
       </c>
       <c r="C645" t="n">
         <v>0.384422</v>
@@ -8812,7 +8812,7 @@
         </is>
       </c>
       <c r="B646" t="n">
-        <v>0.051314</v>
+        <v>0.051337</v>
       </c>
       <c r="C646" t="n">
         <v>0.38191</v>
@@ -8825,7 +8825,7 @@
         </is>
       </c>
       <c r="B647" t="n">
-        <v>0.051485</v>
+        <v>0.051502</v>
       </c>
       <c r="C647" t="n">
         <v>0.379397</v>
@@ -8838,7 +8838,7 @@
         </is>
       </c>
       <c r="B648" t="n">
-        <v>0.051531</v>
+        <v>0.05153</v>
       </c>
       <c r="C648" t="n">
         <v>0.376884</v>
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="B649" t="n">
-        <v>0.052387</v>
+        <v>0.052352</v>
       </c>
       <c r="C649" t="n">
         <v>0.374372</v>
@@ -8864,7 +8864,7 @@
         </is>
       </c>
       <c r="B650" t="n">
-        <v>0.053154</v>
+        <v>0.053132</v>
       </c>
       <c r="C650" t="n">
         <v>0.371859</v>
@@ -8877,7 +8877,7 @@
         </is>
       </c>
       <c r="B651" t="n">
-        <v>0.053169</v>
+        <v>0.053146</v>
       </c>
       <c r="C651" t="n">
         <v>0.369347</v>
@@ -8890,7 +8890,7 @@
         </is>
       </c>
       <c r="B652" t="n">
-        <v>0.053211</v>
+        <v>0.053224</v>
       </c>
       <c r="C652" t="n">
         <v>0.366834</v>
@@ -8903,7 +8903,7 @@
         </is>
       </c>
       <c r="B653" t="n">
-        <v>0.053339</v>
+        <v>0.053319</v>
       </c>
       <c r="C653" t="n">
         <v>0.364322</v>
@@ -8916,7 +8916,7 @@
         </is>
       </c>
       <c r="B654" t="n">
-        <v>0.05369</v>
+        <v>0.053692</v>
       </c>
       <c r="C654" t="n">
         <v>0.361809</v>
@@ -8929,7 +8929,7 @@
         </is>
       </c>
       <c r="B655" t="n">
-        <v>0.053875</v>
+        <v>0.053837</v>
       </c>
       <c r="C655" t="n">
         <v>0.359296</v>
@@ -8942,7 +8942,7 @@
         </is>
       </c>
       <c r="B656" t="n">
-        <v>0.054061</v>
+        <v>0.054036</v>
       </c>
       <c r="C656" t="n">
         <v>0.356784</v>
@@ -8955,7 +8955,7 @@
         </is>
       </c>
       <c r="B657" t="n">
-        <v>0.055109</v>
+        <v>0.055074</v>
       </c>
       <c r="C657" t="n">
         <v>0.354271</v>
@@ -8968,7 +8968,7 @@
         </is>
       </c>
       <c r="B658" t="n">
-        <v>0.055115</v>
+        <v>0.055101</v>
       </c>
       <c r="C658" t="n">
         <v>0.351759</v>
@@ -8981,7 +8981,7 @@
         </is>
       </c>
       <c r="B659" t="n">
-        <v>0.056118</v>
+        <v>0.056159</v>
       </c>
       <c r="C659" t="n">
         <v>0.349246</v>
@@ -8994,7 +8994,7 @@
         </is>
       </c>
       <c r="B660" t="n">
-        <v>0.056995</v>
+        <v>0.057108</v>
       </c>
       <c r="C660" t="n">
         <v>0.346734</v>
@@ -9007,7 +9007,7 @@
         </is>
       </c>
       <c r="B661" t="n">
-        <v>0.057141</v>
+        <v>0.057281</v>
       </c>
       <c r="C661" t="n">
         <v>0.344221</v>
@@ -9020,7 +9020,7 @@
         </is>
       </c>
       <c r="B662" t="n">
-        <v>0.057282</v>
+        <v>0.057346</v>
       </c>
       <c r="C662" t="n">
         <v>0.341709</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="B663" t="n">
-        <v>0.057916</v>
+        <v>0.058009</v>
       </c>
       <c r="C663" t="n">
         <v>0.339196</v>
@@ -9046,7 +9046,7 @@
         </is>
       </c>
       <c r="B664" t="n">
-        <v>0.058188</v>
+        <v>0.058238</v>
       </c>
       <c r="C664" t="n">
         <v>0.336683</v>
@@ -9059,7 +9059,7 @@
         </is>
       </c>
       <c r="B665" t="n">
-        <v>0.058351</v>
+        <v>0.058335</v>
       </c>
       <c r="C665" t="n">
         <v>0.334171</v>
@@ -9072,7 +9072,7 @@
         </is>
       </c>
       <c r="B666" t="n">
-        <v>0.058787</v>
+        <v>0.058774</v>
       </c>
       <c r="C666" t="n">
         <v>0.331658</v>
@@ -9085,7 +9085,7 @@
         </is>
       </c>
       <c r="B667" t="n">
-        <v>0.058967</v>
+        <v>0.05902</v>
       </c>
       <c r="C667" t="n">
         <v>0.329146</v>
@@ -9098,7 +9098,7 @@
         </is>
       </c>
       <c r="B668" t="n">
-        <v>0.059802</v>
+        <v>0.059771</v>
       </c>
       <c r="C668" t="n">
         <v>0.326633</v>
@@ -9111,7 +9111,7 @@
         </is>
       </c>
       <c r="B669" t="n">
-        <v>0.059936</v>
+        <v>0.059908</v>
       </c>
       <c r="C669" t="n">
         <v>0.324121</v>
@@ -9124,7 +9124,7 @@
         </is>
       </c>
       <c r="B670" t="n">
-        <v>0.06085</v>
+        <v>0.060844</v>
       </c>
       <c r="C670" t="n">
         <v>0.321608</v>
@@ -9137,7 +9137,7 @@
         </is>
       </c>
       <c r="B671" t="n">
-        <v>0.060898</v>
+        <v>0.060871</v>
       </c>
       <c r="C671" t="n">
         <v>0.319095</v>
@@ -9150,7 +9150,7 @@
         </is>
       </c>
       <c r="B672" t="n">
-        <v>0.06107</v>
+        <v>0.06103</v>
       </c>
       <c r="C672" t="n">
         <v>0.316583</v>
@@ -9163,7 +9163,7 @@
         </is>
       </c>
       <c r="B673" t="n">
-        <v>0.061261</v>
+        <v>0.061217</v>
       </c>
       <c r="C673" t="n">
         <v>0.31407</v>
@@ -9176,7 +9176,7 @@
         </is>
       </c>
       <c r="B674" t="n">
-        <v>0.061725</v>
+        <v>0.061692</v>
       </c>
       <c r="C674" t="n">
         <v>0.311558</v>
@@ -9189,7 +9189,7 @@
         </is>
       </c>
       <c r="B675" t="n">
-        <v>0.062102</v>
+        <v>0.062057</v>
       </c>
       <c r="C675" t="n">
         <v>0.309045</v>
@@ -9202,7 +9202,7 @@
         </is>
       </c>
       <c r="B676" t="n">
-        <v>0.062234</v>
+        <v>0.062362</v>
       </c>
       <c r="C676" t="n">
         <v>0.306533</v>
@@ -9215,7 +9215,7 @@
         </is>
       </c>
       <c r="B677" t="n">
-        <v>0.062651</v>
+        <v>0.06261</v>
       </c>
       <c r="C677" t="n">
         <v>0.30402</v>
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="B678" t="n">
-        <v>0.062905</v>
+        <v>0.06295099999999999</v>
       </c>
       <c r="C678" t="n">
         <v>0.301508</v>
@@ -9241,7 +9241,7 @@
         </is>
       </c>
       <c r="B679" t="n">
-        <v>0.063473</v>
+        <v>0.063531</v>
       </c>
       <c r="C679" t="n">
         <v>0.298995</v>
@@ -9254,7 +9254,7 @@
         </is>
       </c>
       <c r="B680" t="n">
-        <v>0.063792</v>
+        <v>0.06385399999999999</v>
       </c>
       <c r="C680" t="n">
         <v>0.296482</v>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="B681" t="n">
-        <v>0.06444800000000001</v>
+        <v>0.06446200000000001</v>
       </c>
       <c r="C681" t="n">
         <v>0.29397</v>
@@ -9280,7 +9280,7 @@
         </is>
       </c>
       <c r="B682" t="n">
-        <v>0.064637</v>
+        <v>0.0646</v>
       </c>
       <c r="C682" t="n">
         <v>0.291457</v>
@@ -9293,7 +9293,7 @@
         </is>
       </c>
       <c r="B683" t="n">
-        <v>0.064747</v>
+        <v>0.064717</v>
       </c>
       <c r="C683" t="n">
         <v>0.288945</v>
@@ -9306,7 +9306,7 @@
         </is>
       </c>
       <c r="B684" t="n">
-        <v>0.064808</v>
+        <v>0.06489300000000001</v>
       </c>
       <c r="C684" t="n">
         <v>0.286432</v>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="B685" t="n">
-        <v>0.065707</v>
+        <v>0.065682</v>
       </c>
       <c r="C685" t="n">
         <v>0.28392</v>
@@ -9332,7 +9332,7 @@
         </is>
       </c>
       <c r="B686" t="n">
-        <v>0.06573</v>
+        <v>0.06568599999999999</v>
       </c>
       <c r="C686" t="n">
         <v>0.281407</v>
@@ -9345,7 +9345,7 @@
         </is>
       </c>
       <c r="B687" t="n">
-        <v>0.06633600000000001</v>
+        <v>0.066302</v>
       </c>
       <c r="C687" t="n">
         <v>0.278894</v>
@@ -9358,7 +9358,7 @@
         </is>
       </c>
       <c r="B688" t="n">
-        <v>0.066402</v>
+        <v>0.066358</v>
       </c>
       <c r="C688" t="n">
         <v>0.276382</v>
@@ -9371,7 +9371,7 @@
         </is>
       </c>
       <c r="B689" t="n">
-        <v>0.067092</v>
+        <v>0.067066</v>
       </c>
       <c r="C689" t="n">
         <v>0.273869</v>
@@ -9384,7 +9384,7 @@
         </is>
       </c>
       <c r="B690" t="n">
-        <v>0.06721299999999999</v>
+        <v>0.06725200000000001</v>
       </c>
       <c r="C690" t="n">
         <v>0.271357</v>
@@ -9397,7 +9397,7 @@
         </is>
       </c>
       <c r="B691" t="n">
-        <v>0.067341</v>
+        <v>0.06734</v>
       </c>
       <c r="C691" t="n">
         <v>0.268844</v>
@@ -9423,7 +9423,7 @@
         </is>
       </c>
       <c r="B693" t="n">
-        <v>0.068838</v>
+        <v>0.068868</v>
       </c>
       <c r="C693" t="n">
         <v>0.263819</v>
@@ -9436,7 +9436,7 @@
         </is>
       </c>
       <c r="B694" t="n">
-        <v>0.06997200000000001</v>
+        <v>0.069928</v>
       </c>
       <c r="C694" t="n">
         <v>0.261307</v>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="B695" t="n">
-        <v>0.069995</v>
+        <v>0.069964</v>
       </c>
       <c r="C695" t="n">
         <v>0.258794</v>
@@ -9462,7 +9462,7 @@
         </is>
       </c>
       <c r="B696" t="n">
-        <v>0.07051399999999999</v>
+        <v>0.07048</v>
       </c>
       <c r="C696" t="n">
         <v>0.256281</v>
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="B697" t="n">
-        <v>0.070934</v>
+        <v>0.070912</v>
       </c>
       <c r="C697" t="n">
         <v>0.253769</v>
@@ -9488,7 +9488,7 @@
         </is>
       </c>
       <c r="B698" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.071379</v>
       </c>
       <c r="C698" t="n">
         <v>0.251256</v>
@@ -9501,7 +9501,7 @@
         </is>
       </c>
       <c r="B699" t="n">
-        <v>0.071825</v>
+        <v>0.07181</v>
       </c>
       <c r="C699" t="n">
         <v>0.248744</v>
@@ -9514,7 +9514,7 @@
         </is>
       </c>
       <c r="B700" t="n">
-        <v>0.07206</v>
+        <v>0.072197</v>
       </c>
       <c r="C700" t="n">
         <v>0.246231</v>
@@ -9527,7 +9527,7 @@
         </is>
       </c>
       <c r="B701" t="n">
-        <v>0.07278999999999999</v>
+        <v>0.072741</v>
       </c>
       <c r="C701" t="n">
         <v>0.243719</v>
@@ -9540,7 +9540,7 @@
         </is>
       </c>
       <c r="B702" t="n">
-        <v>0.073671</v>
+        <v>0.073785</v>
       </c>
       <c r="C702" t="n">
         <v>0.241206</v>
@@ -9553,7 +9553,7 @@
         </is>
       </c>
       <c r="B703" t="n">
-        <v>0.073674</v>
+        <v>0.073842</v>
       </c>
       <c r="C703" t="n">
         <v>0.238693</v>
@@ -9566,7 +9566,7 @@
         </is>
       </c>
       <c r="B704" t="n">
-        <v>0.073809</v>
+        <v>0.073849</v>
       </c>
       <c r="C704" t="n">
         <v>0.236181</v>
@@ -9579,7 +9579,7 @@
         </is>
       </c>
       <c r="B705" t="n">
-        <v>0.074298</v>
+        <v>0.074269</v>
       </c>
       <c r="C705" t="n">
         <v>0.233668</v>
@@ -9592,7 +9592,7 @@
         </is>
       </c>
       <c r="B706" t="n">
-        <v>0.07431500000000001</v>
+        <v>0.07431400000000001</v>
       </c>
       <c r="C706" t="n">
         <v>0.231156</v>
@@ -9605,7 +9605,7 @@
         </is>
       </c>
       <c r="B707" t="n">
-        <v>0.075988</v>
+        <v>0.07609299999999999</v>
       </c>
       <c r="C707" t="n">
         <v>0.228643</v>
@@ -9618,7 +9618,7 @@
         </is>
       </c>
       <c r="B708" t="n">
-        <v>0.076069</v>
+        <v>0.07621</v>
       </c>
       <c r="C708" t="n">
         <v>0.226131</v>
@@ -9631,7 +9631,7 @@
         </is>
       </c>
       <c r="B709" t="n">
-        <v>0.076461</v>
+        <v>0.07645200000000001</v>
       </c>
       <c r="C709" t="n">
         <v>0.223618</v>
@@ -9644,7 +9644,7 @@
         </is>
       </c>
       <c r="B710" t="n">
-        <v>0.07682700000000001</v>
+        <v>0.07678599999999999</v>
       </c>
       <c r="C710" t="n">
         <v>0.221106</v>
@@ -9657,7 +9657,7 @@
         </is>
       </c>
       <c r="B711" t="n">
-        <v>0.078051</v>
+        <v>0.077999</v>
       </c>
       <c r="C711" t="n">
         <v>0.218593</v>
@@ -9670,7 +9670,7 @@
         </is>
       </c>
       <c r="B712" t="n">
-        <v>0.078268</v>
+        <v>0.078234</v>
       </c>
       <c r="C712" t="n">
         <v>0.21608</v>
@@ -9683,7 +9683,7 @@
         </is>
       </c>
       <c r="B713" t="n">
-        <v>0.078914</v>
+        <v>0.078879</v>
       </c>
       <c r="C713" t="n">
         <v>0.213568</v>
@@ -9696,7 +9696,7 @@
         </is>
       </c>
       <c r="B714" t="n">
-        <v>0.079004</v>
+        <v>0.078984</v>
       </c>
       <c r="C714" t="n">
         <v>0.211055</v>
@@ -9709,7 +9709,7 @@
         </is>
       </c>
       <c r="B715" t="n">
-        <v>0.08087800000000001</v>
+        <v>0.08082399999999999</v>
       </c>
       <c r="C715" t="n">
         <v>0.208543</v>
@@ -9722,7 +9722,7 @@
         </is>
       </c>
       <c r="B716" t="n">
-        <v>0.081858</v>
+        <v>0.08185199999999999</v>
       </c>
       <c r="C716" t="n">
         <v>0.20603</v>
@@ -9735,7 +9735,7 @@
         </is>
       </c>
       <c r="B717" t="n">
-        <v>0.081996</v>
+        <v>0.082001</v>
       </c>
       <c r="C717" t="n">
         <v>0.203518</v>
@@ -9748,7 +9748,7 @@
         </is>
       </c>
       <c r="B718" t="n">
-        <v>0.08217000000000001</v>
+        <v>0.082111</v>
       </c>
       <c r="C718" t="n">
         <v>0.201005</v>
@@ -9761,7 +9761,7 @@
         </is>
       </c>
       <c r="B719" t="n">
-        <v>0.08311399999999999</v>
+        <v>0.083247</v>
       </c>
       <c r="C719" t="n">
         <v>0.198492</v>
@@ -9774,7 +9774,7 @@
         </is>
       </c>
       <c r="B720" t="n">
-        <v>0.083882</v>
+        <v>0.084217</v>
       </c>
       <c r="C720" t="n">
         <v>0.19598</v>
@@ -9787,7 +9787,7 @@
         </is>
       </c>
       <c r="B721" t="n">
-        <v>0.084801</v>
+        <v>0.084741</v>
       </c>
       <c r="C721" t="n">
         <v>0.193467</v>
@@ -9800,7 +9800,7 @@
         </is>
       </c>
       <c r="B722" t="n">
-        <v>0.085115</v>
+        <v>0.085059</v>
       </c>
       <c r="C722" t="n">
         <v>0.190955</v>
@@ -9813,7 +9813,7 @@
         </is>
       </c>
       <c r="B723" t="n">
-        <v>0.08516600000000001</v>
+        <v>0.08520899999999999</v>
       </c>
       <c r="C723" t="n">
         <v>0.188442</v>
@@ -9826,7 +9826,7 @@
         </is>
       </c>
       <c r="B724" t="n">
-        <v>0.085853</v>
+        <v>0.08579100000000001</v>
       </c>
       <c r="C724" t="n">
         <v>0.18593</v>
@@ -9839,7 +9839,7 @@
         </is>
       </c>
       <c r="B725" t="n">
-        <v>0.08643099999999999</v>
+        <v>0.086502</v>
       </c>
       <c r="C725" t="n">
         <v>0.183417</v>
@@ -9852,7 +9852,7 @@
         </is>
       </c>
       <c r="B726" t="n">
-        <v>0.086908</v>
+        <v>0.086907</v>
       </c>
       <c r="C726" t="n">
         <v>0.180905</v>
@@ -9865,7 +9865,7 @@
         </is>
       </c>
       <c r="B727" t="n">
-        <v>0.08713600000000001</v>
+        <v>0.08709</v>
       </c>
       <c r="C727" t="n">
         <v>0.178392</v>
@@ -9878,7 +9878,7 @@
         </is>
       </c>
       <c r="B728" t="n">
-        <v>0.088282</v>
+        <v>0.088367</v>
       </c>
       <c r="C728" t="n">
         <v>0.175879</v>
@@ -9891,7 +9891,7 @@
         </is>
       </c>
       <c r="B729" t="n">
-        <v>0.08870500000000001</v>
+        <v>0.088647</v>
       </c>
       <c r="C729" t="n">
         <v>0.173367</v>
@@ -9904,7 +9904,7 @@
         </is>
       </c>
       <c r="B730" t="n">
-        <v>0.08924700000000001</v>
+        <v>0.089237</v>
       </c>
       <c r="C730" t="n">
         <v>0.170854</v>
@@ -9917,7 +9917,7 @@
         </is>
       </c>
       <c r="B731" t="n">
-        <v>0.089296</v>
+        <v>0.089251</v>
       </c>
       <c r="C731" t="n">
         <v>0.168342</v>
@@ -9930,7 +9930,7 @@
         </is>
       </c>
       <c r="B732" t="n">
-        <v>0.090296</v>
+        <v>0.090348</v>
       </c>
       <c r="C732" t="n">
         <v>0.165829</v>
@@ -9943,7 +9943,7 @@
         </is>
       </c>
       <c r="B733" t="n">
-        <v>0.09095</v>
+        <v>0.09089</v>
       </c>
       <c r="C733" t="n">
         <v>0.163317</v>
@@ -9956,7 +9956,7 @@
         </is>
       </c>
       <c r="B734" t="n">
-        <v>0.090991</v>
+        <v>0.09098199999999999</v>
       </c>
       <c r="C734" t="n">
         <v>0.160804</v>
@@ -9969,7 +9969,7 @@
         </is>
       </c>
       <c r="B735" t="n">
-        <v>0.092347</v>
+        <v>0.092283</v>
       </c>
       <c r="C735" t="n">
         <v>0.158291</v>
@@ -9982,7 +9982,7 @@
         </is>
       </c>
       <c r="B736" t="n">
-        <v>0.097096</v>
+        <v>0.097068</v>
       </c>
       <c r="C736" t="n">
         <v>0.155779</v>
@@ -9995,7 +9995,7 @@
         </is>
       </c>
       <c r="B737" t="n">
-        <v>0.097342</v>
+        <v>0.097278</v>
       </c>
       <c r="C737" t="n">
         <v>0.153266</v>
@@ -10008,7 +10008,7 @@
         </is>
       </c>
       <c r="B738" t="n">
-        <v>0.097346</v>
+        <v>0.097316</v>
       </c>
       <c r="C738" t="n">
         <v>0.150754</v>
@@ -10021,7 +10021,7 @@
         </is>
       </c>
       <c r="B739" t="n">
-        <v>0.097387</v>
+        <v>0.09733</v>
       </c>
       <c r="C739" t="n">
         <v>0.148241</v>
@@ -10034,7 +10034,7 @@
         </is>
       </c>
       <c r="B740" t="n">
-        <v>0.09764399999999999</v>
+        <v>0.097594</v>
       </c>
       <c r="C740" t="n">
         <v>0.145729</v>
@@ -10047,7 +10047,7 @@
         </is>
       </c>
       <c r="B741" t="n">
-        <v>0.098259</v>
+        <v>0.09826</v>
       </c>
       <c r="C741" t="n">
         <v>0.143216</v>
@@ -10060,7 +10060,7 @@
         </is>
       </c>
       <c r="B742" t="n">
-        <v>0.099631</v>
+        <v>0.09957299999999999</v>
       </c>
       <c r="C742" t="n">
         <v>0.140704</v>
@@ -10073,7 +10073,7 @@
         </is>
       </c>
       <c r="B743" t="n">
-        <v>0.101286</v>
+        <v>0.101215</v>
       </c>
       <c r="C743" t="n">
         <v>0.138191</v>
@@ -10086,7 +10086,7 @@
         </is>
       </c>
       <c r="B744" t="n">
-        <v>0.103135</v>
+        <v>0.103156</v>
       </c>
       <c r="C744" t="n">
         <v>0.135678</v>
@@ -10099,7 +10099,7 @@
         </is>
       </c>
       <c r="B745" t="n">
-        <v>0.105824</v>
+        <v>0.106066</v>
       </c>
       <c r="C745" t="n">
         <v>0.133166</v>
@@ -10112,7 +10112,7 @@
         </is>
       </c>
       <c r="B746" t="n">
-        <v>0.106297</v>
+        <v>0.106295</v>
       </c>
       <c r="C746" t="n">
         <v>0.130653</v>
@@ -10125,7 +10125,7 @@
         </is>
       </c>
       <c r="B747" t="n">
-        <v>0.106327</v>
+        <v>0.106344</v>
       </c>
       <c r="C747" t="n">
         <v>0.128141</v>
@@ -10138,7 +10138,7 @@
         </is>
       </c>
       <c r="B748" t="n">
-        <v>0.107555</v>
+        <v>0.107609</v>
       </c>
       <c r="C748" t="n">
         <v>0.125628</v>
@@ -10151,7 +10151,7 @@
         </is>
       </c>
       <c r="B749" t="n">
-        <v>0.107993</v>
+        <v>0.107923</v>
       </c>
       <c r="C749" t="n">
         <v>0.123116</v>
@@ -10164,7 +10164,7 @@
         </is>
       </c>
       <c r="B750" t="n">
-        <v>0.109497</v>
+        <v>0.109521</v>
       </c>
       <c r="C750" t="n">
         <v>0.120603</v>
@@ -10177,7 +10177,7 @@
         </is>
       </c>
       <c r="B751" t="n">
-        <v>0.109796</v>
+        <v>0.109792</v>
       </c>
       <c r="C751" t="n">
         <v>0.11809</v>
@@ -10190,7 +10190,7 @@
         </is>
       </c>
       <c r="B752" t="n">
-        <v>0.1121</v>
+        <v>0.112091</v>
       </c>
       <c r="C752" t="n">
         <v>0.115578</v>
@@ -10203,7 +10203,7 @@
         </is>
       </c>
       <c r="B753" t="n">
-        <v>0.112614</v>
+        <v>0.112893</v>
       </c>
       <c r="C753" t="n">
         <v>0.113065</v>
@@ -10216,7 +10216,7 @@
         </is>
       </c>
       <c r="B754" t="n">
-        <v>0.113291</v>
+        <v>0.113511</v>
       </c>
       <c r="C754" t="n">
         <v>0.110553</v>
@@ -10229,7 +10229,7 @@
         </is>
       </c>
       <c r="B755" t="n">
-        <v>0.116076</v>
+        <v>0.116009</v>
       </c>
       <c r="C755" t="n">
         <v>0.10804</v>
@@ -10242,7 +10242,7 @@
         </is>
       </c>
       <c r="B756" t="n">
-        <v>0.116513</v>
+        <v>0.1165</v>
       </c>
       <c r="C756" t="n">
         <v>0.105528</v>
@@ -10255,7 +10255,7 @@
         </is>
       </c>
       <c r="B757" t="n">
-        <v>0.11674</v>
+        <v>0.116675</v>
       </c>
       <c r="C757" t="n">
         <v>0.103015</v>
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="B758" t="n">
-        <v>0.118234</v>
+        <v>0.118186</v>
       </c>
       <c r="C758" t="n">
         <v>0.100503</v>
@@ -10281,7 +10281,7 @@
         </is>
       </c>
       <c r="B759" t="n">
-        <v>0.121137</v>
+        <v>0.121061</v>
       </c>
       <c r="C759" t="n">
         <v>0.09798999999999999</v>
@@ -10294,7 +10294,7 @@
         </is>
       </c>
       <c r="B760" t="n">
-        <v>0.121139</v>
+        <v>0.12108</v>
       </c>
       <c r="C760" t="n">
         <v>0.09547700000000001</v>
@@ -10307,7 +10307,7 @@
         </is>
       </c>
       <c r="B761" t="n">
-        <v>0.121639</v>
+        <v>0.121612</v>
       </c>
       <c r="C761" t="n">
         <v>0.09296500000000001</v>
@@ -10320,7 +10320,7 @@
         </is>
       </c>
       <c r="B762" t="n">
-        <v>0.121962</v>
+        <v>0.122131</v>
       </c>
       <c r="C762" t="n">
         <v>0.090452</v>
@@ -10333,7 +10333,7 @@
         </is>
       </c>
       <c r="B763" t="n">
-        <v>0.123785</v>
+        <v>0.123729</v>
       </c>
       <c r="C763" t="n">
         <v>0.08794</v>
@@ -10346,7 +10346,7 @@
         </is>
       </c>
       <c r="B764" t="n">
-        <v>0.125491</v>
+        <v>0.12544</v>
       </c>
       <c r="C764" t="n">
         <v>0.085427</v>
@@ -10359,7 +10359,7 @@
         </is>
       </c>
       <c r="B765" t="n">
-        <v>0.126578</v>
+        <v>0.126567</v>
       </c>
       <c r="C765" t="n">
         <v>0.082915</v>
@@ -10372,7 +10372,7 @@
         </is>
       </c>
       <c r="B766" t="n">
-        <v>0.126915</v>
+        <v>0.126855</v>
       </c>
       <c r="C766" t="n">
         <v>0.080402</v>
@@ -10385,7 +10385,7 @@
         </is>
       </c>
       <c r="B767" t="n">
-        <v>0.127563</v>
+        <v>0.127479</v>
       </c>
       <c r="C767" t="n">
         <v>0.077889</v>
@@ -10398,7 +10398,7 @@
         </is>
       </c>
       <c r="B768" t="n">
-        <v>0.129015</v>
+        <v>0.128939</v>
       </c>
       <c r="C768" t="n">
         <v>0.075377</v>
@@ -10411,7 +10411,7 @@
         </is>
       </c>
       <c r="B769" t="n">
-        <v>0.136429</v>
+        <v>0.136392</v>
       </c>
       <c r="C769" t="n">
         <v>0.072864</v>
@@ -10424,7 +10424,7 @@
         </is>
       </c>
       <c r="B770" t="n">
-        <v>0.13885</v>
+        <v>0.138843</v>
       </c>
       <c r="C770" t="n">
         <v>0.070352</v>
@@ -10437,7 +10437,7 @@
         </is>
       </c>
       <c r="B771" t="n">
-        <v>0.142176</v>
+        <v>0.142243</v>
       </c>
       <c r="C771" t="n">
         <v>0.067839</v>
@@ -10450,7 +10450,7 @@
         </is>
       </c>
       <c r="B772" t="n">
-        <v>0.142521</v>
+        <v>0.14242</v>
       </c>
       <c r="C772" t="n">
         <v>0.065327</v>
@@ -10463,7 +10463,7 @@
         </is>
       </c>
       <c r="B773" t="n">
-        <v>0.143305</v>
+        <v>0.143258</v>
       </c>
       <c r="C773" t="n">
         <v>0.06281399999999999</v>
@@ -10476,7 +10476,7 @@
         </is>
       </c>
       <c r="B774" t="n">
-        <v>0.151722</v>
+        <v>0.151633</v>
       </c>
       <c r="C774" t="n">
         <v>0.060302</v>
@@ -10489,7 +10489,7 @@
         </is>
       </c>
       <c r="B775" t="n">
-        <v>0.156192</v>
+        <v>0.15608</v>
       </c>
       <c r="C775" t="n">
         <v>0.057789</v>
@@ -10502,7 +10502,7 @@
         </is>
       </c>
       <c r="B776" t="n">
-        <v>0.160519</v>
+        <v>0.160739</v>
       </c>
       <c r="C776" t="n">
         <v>0.055276</v>
@@ -10515,7 +10515,7 @@
         </is>
       </c>
       <c r="B777" t="n">
-        <v>0.160712</v>
+        <v>0.160877</v>
       </c>
       <c r="C777" t="n">
         <v>0.052764</v>
@@ -10528,7 +10528,7 @@
         </is>
       </c>
       <c r="B778" t="n">
-        <v>0.161339</v>
+        <v>0.161229</v>
       </c>
       <c r="C778" t="n">
         <v>0.050251</v>
@@ -10541,7 +10541,7 @@
         </is>
       </c>
       <c r="B779" t="n">
-        <v>0.1623</v>
+        <v>0.162188</v>
       </c>
       <c r="C779" t="n">
         <v>0.047739</v>
@@ -10554,7 +10554,7 @@
         </is>
       </c>
       <c r="B780" t="n">
-        <v>0.165681</v>
+        <v>0.165578</v>
       </c>
       <c r="C780" t="n">
         <v>0.045226</v>
@@ -10567,7 +10567,7 @@
         </is>
       </c>
       <c r="B781" t="n">
-        <v>0.166211</v>
+        <v>0.166187</v>
       </c>
       <c r="C781" t="n">
         <v>0.042714</v>
@@ -10580,7 +10580,7 @@
         </is>
       </c>
       <c r="B782" t="n">
-        <v>0.167636</v>
+        <v>0.167736</v>
       </c>
       <c r="C782" t="n">
         <v>0.040201</v>
@@ -10593,7 +10593,7 @@
         </is>
       </c>
       <c r="B783" t="n">
-        <v>0.168762</v>
+        <v>0.168935</v>
       </c>
       <c r="C783" t="n">
         <v>0.037688</v>
@@ -10606,7 +10606,7 @@
         </is>
       </c>
       <c r="B784" t="n">
-        <v>0.175469</v>
+        <v>0.175412</v>
       </c>
       <c r="C784" t="n">
         <v>0.035176</v>
@@ -10619,7 +10619,7 @@
         </is>
       </c>
       <c r="B785" t="n">
-        <v>0.17814</v>
+        <v>0.178438</v>
       </c>
       <c r="C785" t="n">
         <v>0.032663</v>
@@ -10632,7 +10632,7 @@
         </is>
       </c>
       <c r="B786" t="n">
-        <v>0.184804</v>
+        <v>0.184739</v>
       </c>
       <c r="C786" t="n">
         <v>0.030151</v>
@@ -10645,7 +10645,7 @@
         </is>
       </c>
       <c r="B787" t="n">
-        <v>0.196669</v>
+        <v>0.196592</v>
       </c>
       <c r="C787" t="n">
         <v>0.027638</v>
@@ -10658,7 +10658,7 @@
         </is>
       </c>
       <c r="B788" t="n">
-        <v>0.217834</v>
+        <v>0.21772</v>
       </c>
       <c r="C788" t="n">
         <v>0.025126</v>
@@ -10671,7 +10671,7 @@
         </is>
       </c>
       <c r="B789" t="n">
-        <v>0.221201</v>
+        <v>0.22139</v>
       </c>
       <c r="C789" t="n">
         <v>0.022613</v>
@@ -10684,7 +10684,7 @@
         </is>
       </c>
       <c r="B790" t="n">
-        <v>0.231328</v>
+        <v>0.231395</v>
       </c>
       <c r="C790" t="n">
         <v>0.020101</v>
@@ -10697,7 +10697,7 @@
         </is>
       </c>
       <c r="B791" t="n">
-        <v>0.234258</v>
+        <v>0.234331</v>
       </c>
       <c r="C791" t="n">
         <v>0.017588</v>
@@ -10710,7 +10710,7 @@
         </is>
       </c>
       <c r="B792" t="n">
-        <v>0.236687</v>
+        <v>0.237071</v>
       </c>
       <c r="C792" t="n">
         <v>0.015075</v>
@@ -10723,7 +10723,7 @@
         </is>
       </c>
       <c r="B793" t="n">
-        <v>0.24381</v>
+        <v>0.243651</v>
       </c>
       <c r="C793" t="n">
         <v>0.012563</v>
@@ -10736,7 +10736,7 @@
         </is>
       </c>
       <c r="B794" t="n">
-        <v>0.293574</v>
+        <v>0.293547</v>
       </c>
       <c r="C794" t="n">
         <v>0.01005</v>
@@ -10749,7 +10749,7 @@
         </is>
       </c>
       <c r="B795" t="n">
-        <v>0.30921</v>
+        <v>0.308992</v>
       </c>
       <c r="C795" t="n">
         <v>0.007538</v>
@@ -10762,7 +10762,7 @@
         </is>
       </c>
       <c r="B796" t="n">
-        <v>0.3194</v>
+        <v>0.319252</v>
       </c>
       <c r="C796" t="n">
         <v>0.005025</v>
@@ -10775,7 +10775,7 @@
         </is>
       </c>
       <c r="B797" t="n">
-        <v>0.447711</v>
+        <v>0.447407</v>
       </c>
       <c r="C797" t="n">
         <v>0.002513</v>
@@ -10801,7 +10801,7 @@
         </is>
       </c>
       <c r="B799" t="n">
-        <v>0.000327</v>
+        <v>0.000326</v>
       </c>
       <c r="C799" t="n">
         <v>0.997487</v>
@@ -10866,7 +10866,7 @@
         </is>
       </c>
       <c r="B804" t="n">
-        <v>0.001886</v>
+        <v>0.001887</v>
       </c>
       <c r="C804" t="n">
         <v>0.9849250000000001</v>
@@ -10879,7 +10879,7 @@
         </is>
       </c>
       <c r="B805" t="n">
-        <v>0.002081</v>
+        <v>0.00208</v>
       </c>
       <c r="C805" t="n">
         <v>0.982412</v>
@@ -10918,7 +10918,7 @@
         </is>
       </c>
       <c r="B808" t="n">
-        <v>0.002428</v>
+        <v>0.002427</v>
       </c>
       <c r="C808" t="n">
         <v>0.974874</v>
@@ -10931,7 +10931,7 @@
         </is>
       </c>
       <c r="B809" t="n">
-        <v>0.002565</v>
+        <v>0.002568</v>
       </c>
       <c r="C809" t="n">
         <v>0.9723619999999999</v>
@@ -10944,7 +10944,7 @@
         </is>
       </c>
       <c r="B810" t="n">
-        <v>0.002699</v>
+        <v>0.002703</v>
       </c>
       <c r="C810" t="n">
         <v>0.969849</v>
@@ -10957,7 +10957,7 @@
         </is>
       </c>
       <c r="B811" t="n">
-        <v>0.003001</v>
+        <v>0.003</v>
       </c>
       <c r="C811" t="n">
         <v>0.967337</v>
@@ -10983,7 +10983,7 @@
         </is>
       </c>
       <c r="B813" t="n">
-        <v>0.00324</v>
+        <v>0.003239</v>
       </c>
       <c r="C813" t="n">
         <v>0.9623119999999999</v>
@@ -10996,7 +10996,7 @@
         </is>
       </c>
       <c r="B814" t="n">
-        <v>0.003633</v>
+        <v>0.003634</v>
       </c>
       <c r="C814" t="n">
         <v>0.959799</v>
@@ -11009,7 +11009,7 @@
         </is>
       </c>
       <c r="B815" t="n">
-        <v>0.004233</v>
+        <v>0.004232</v>
       </c>
       <c r="C815" t="n">
         <v>0.957286</v>
@@ -11022,7 +11022,7 @@
         </is>
       </c>
       <c r="B816" t="n">
-        <v>0.004305</v>
+        <v>0.004304</v>
       </c>
       <c r="C816" t="n">
         <v>0.954774</v>
@@ -11035,7 +11035,7 @@
         </is>
       </c>
       <c r="B817" t="n">
-        <v>0.004511</v>
+        <v>0.00451</v>
       </c>
       <c r="C817" t="n">
         <v>0.952261</v>
@@ -11048,7 +11048,7 @@
         </is>
       </c>
       <c r="B818" t="n">
-        <v>0.004671</v>
+        <v>0.004682</v>
       </c>
       <c r="C818" t="n">
         <v>0.949749</v>
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="B819" t="n">
-        <v>0.004766</v>
+        <v>0.004765</v>
       </c>
       <c r="C819" t="n">
         <v>0.947236</v>
@@ -11074,7 +11074,7 @@
         </is>
       </c>
       <c r="B820" t="n">
-        <v>0.00478</v>
+        <v>0.004785</v>
       </c>
       <c r="C820" t="n">
         <v>0.944724</v>
@@ -11087,7 +11087,7 @@
         </is>
       </c>
       <c r="B821" t="n">
-        <v>0.004891</v>
+        <v>0.004889</v>
       </c>
       <c r="C821" t="n">
         <v>0.942211</v>
@@ -11100,7 +11100,7 @@
         </is>
       </c>
       <c r="B822" t="n">
-        <v>0.005178</v>
+        <v>0.00518</v>
       </c>
       <c r="C822" t="n">
         <v>0.939698</v>
@@ -11113,7 +11113,7 @@
         </is>
       </c>
       <c r="B823" t="n">
-        <v>0.005211</v>
+        <v>0.005219</v>
       </c>
       <c r="C823" t="n">
         <v>0.937186</v>
@@ -11126,7 +11126,7 @@
         </is>
       </c>
       <c r="B824" t="n">
-        <v>0.005264</v>
+        <v>0.005263</v>
       </c>
       <c r="C824" t="n">
         <v>0.934673</v>
@@ -11139,7 +11139,7 @@
         </is>
       </c>
       <c r="B825" t="n">
-        <v>0.005426</v>
+        <v>0.005423</v>
       </c>
       <c r="C825" t="n">
         <v>0.932161</v>
@@ -11152,7 +11152,7 @@
         </is>
       </c>
       <c r="B826" t="n">
-        <v>0.005585</v>
+        <v>0.005588</v>
       </c>
       <c r="C826" t="n">
         <v>0.929648</v>
@@ -11165,7 +11165,7 @@
         </is>
       </c>
       <c r="B827" t="n">
-        <v>0.00559</v>
+        <v>0.005594</v>
       </c>
       <c r="C827" t="n">
         <v>0.927136</v>
@@ -11178,7 +11178,7 @@
         </is>
       </c>
       <c r="B828" t="n">
-        <v>0.006135</v>
+        <v>0.006132</v>
       </c>
       <c r="C828" t="n">
         <v>0.924623</v>
@@ -11191,7 +11191,7 @@
         </is>
       </c>
       <c r="B829" t="n">
-        <v>0.006415</v>
+        <v>0.006411</v>
       </c>
       <c r="C829" t="n">
         <v>0.922111</v>
@@ -11204,7 +11204,7 @@
         </is>
       </c>
       <c r="B830" t="n">
-        <v>0.006939</v>
+        <v>0.006936</v>
       </c>
       <c r="C830" t="n">
         <v>0.919598</v>
@@ -11217,7 +11217,7 @@
         </is>
       </c>
       <c r="B831" t="n">
-        <v>0.007796</v>
+        <v>0.007792</v>
       </c>
       <c r="C831" t="n">
         <v>0.917085</v>
@@ -11230,7 +11230,7 @@
         </is>
       </c>
       <c r="B832" t="n">
-        <v>0.008019</v>
+        <v>0.008030000000000001</v>
       </c>
       <c r="C832" t="n">
         <v>0.914573</v>
@@ -11243,7 +11243,7 @@
         </is>
       </c>
       <c r="B833" t="n">
-        <v>0.008189999999999999</v>
+        <v>0.008193000000000001</v>
       </c>
       <c r="C833" t="n">
         <v>0.91206</v>
@@ -11256,7 +11256,7 @@
         </is>
       </c>
       <c r="B834" t="n">
-        <v>0.008335</v>
+        <v>0.008351000000000001</v>
       </c>
       <c r="C834" t="n">
         <v>0.909548</v>
@@ -11269,7 +11269,7 @@
         </is>
       </c>
       <c r="B835" t="n">
-        <v>0.008357</v>
+        <v>0.008352999999999999</v>
       </c>
       <c r="C835" t="n">
         <v>0.907035</v>
@@ -11282,7 +11282,7 @@
         </is>
       </c>
       <c r="B836" t="n">
-        <v>0.008517</v>
+        <v>0.008519000000000001</v>
       </c>
       <c r="C836" t="n">
         <v>0.904523</v>
@@ -11295,7 +11295,7 @@
         </is>
       </c>
       <c r="B837" t="n">
-        <v>0.008566000000000001</v>
+        <v>0.008562</v>
       </c>
       <c r="C837" t="n">
         <v>0.90201</v>
@@ -11308,7 +11308,7 @@
         </is>
       </c>
       <c r="B838" t="n">
-        <v>0.008604000000000001</v>
+        <v>0.008612</v>
       </c>
       <c r="C838" t="n">
         <v>0.899497</v>
@@ -11321,7 +11321,7 @@
         </is>
       </c>
       <c r="B839" t="n">
-        <v>0.008857</v>
+        <v>0.008854000000000001</v>
       </c>
       <c r="C839" t="n">
         <v>0.896985</v>
@@ -11334,7 +11334,7 @@
         </is>
       </c>
       <c r="B840" t="n">
-        <v>0.00898</v>
+        <v>0.008983</v>
       </c>
       <c r="C840" t="n">
         <v>0.894472</v>
@@ -11347,7 +11347,7 @@
         </is>
       </c>
       <c r="B841" t="n">
-        <v>0.009148999999999999</v>
+        <v>0.009148</v>
       </c>
       <c r="C841" t="n">
         <v>0.89196</v>
@@ -11360,7 +11360,7 @@
         </is>
       </c>
       <c r="B842" t="n">
-        <v>0.009332</v>
+        <v>0.009341</v>
       </c>
       <c r="C842" t="n">
         <v>0.889447</v>
@@ -11373,7 +11373,7 @@
         </is>
       </c>
       <c r="B843" t="n">
-        <v>0.010031</v>
+        <v>0.010051</v>
       </c>
       <c r="C843" t="n">
         <v>0.886935</v>
@@ -11386,7 +11386,7 @@
         </is>
       </c>
       <c r="B844" t="n">
-        <v>0.010142</v>
+        <v>0.010141</v>
       </c>
       <c r="C844" t="n">
         <v>0.884422</v>
@@ -11399,7 +11399,7 @@
         </is>
       </c>
       <c r="B845" t="n">
-        <v>0.010182</v>
+        <v>0.010178</v>
       </c>
       <c r="C845" t="n">
         <v>0.88191</v>
@@ -11412,7 +11412,7 @@
         </is>
       </c>
       <c r="B846" t="n">
-        <v>0.010361</v>
+        <v>0.010364</v>
       </c>
       <c r="C846" t="n">
         <v>0.879397</v>
@@ -11425,7 +11425,7 @@
         </is>
       </c>
       <c r="B847" t="n">
-        <v>0.010485</v>
+        <v>0.010482</v>
       </c>
       <c r="C847" t="n">
         <v>0.876884</v>
@@ -11438,7 +11438,7 @@
         </is>
       </c>
       <c r="B848" t="n">
-        <v>0.010513</v>
+        <v>0.010508</v>
       </c>
       <c r="C848" t="n">
         <v>0.874372</v>
@@ -11451,7 +11451,7 @@
         </is>
       </c>
       <c r="B849" t="n">
-        <v>0.010597</v>
+        <v>0.010606</v>
       </c>
       <c r="C849" t="n">
         <v>0.8718590000000001</v>
@@ -11464,7 +11464,7 @@
         </is>
       </c>
       <c r="B850" t="n">
-        <v>0.010783</v>
+        <v>0.010779</v>
       </c>
       <c r="C850" t="n">
         <v>0.869347</v>
@@ -11477,7 +11477,7 @@
         </is>
       </c>
       <c r="B851" t="n">
-        <v>0.010917</v>
+        <v>0.010925</v>
       </c>
       <c r="C851" t="n">
         <v>0.866834</v>
@@ -11490,7 +11490,7 @@
         </is>
       </c>
       <c r="B852" t="n">
-        <v>0.011243</v>
+        <v>0.011241</v>
       </c>
       <c r="C852" t="n">
         <v>0.864322</v>
@@ -11503,7 +11503,7 @@
         </is>
       </c>
       <c r="B853" t="n">
-        <v>0.011523</v>
+        <v>0.011518</v>
       </c>
       <c r="C853" t="n">
         <v>0.861809</v>
@@ -11516,7 +11516,7 @@
         </is>
       </c>
       <c r="B854" t="n">
-        <v>0.011584</v>
+        <v>0.011585</v>
       </c>
       <c r="C854" t="n">
         <v>0.8592959999999999</v>
@@ -11529,7 +11529,7 @@
         </is>
       </c>
       <c r="B855" t="n">
-        <v>0.011731</v>
+        <v>0.011727</v>
       </c>
       <c r="C855" t="n">
         <v>0.856784</v>
@@ -11542,7 +11542,7 @@
         </is>
       </c>
       <c r="B856" t="n">
-        <v>0.011814</v>
+        <v>0.011811</v>
       </c>
       <c r="C856" t="n">
         <v>0.854271</v>
@@ -11555,7 +11555,7 @@
         </is>
       </c>
       <c r="B857" t="n">
-        <v>0.01221</v>
+        <v>0.012205</v>
       </c>
       <c r="C857" t="n">
         <v>0.851759</v>
@@ -11568,7 +11568,7 @@
         </is>
       </c>
       <c r="B858" t="n">
-        <v>0.012272</v>
+        <v>0.012278</v>
       </c>
       <c r="C858" t="n">
         <v>0.8492459999999999</v>
@@ -11581,7 +11581,7 @@
         </is>
       </c>
       <c r="B859" t="n">
-        <v>0.012277</v>
+        <v>0.012301</v>
       </c>
       <c r="C859" t="n">
         <v>0.846734</v>
@@ -11594,7 +11594,7 @@
         </is>
       </c>
       <c r="B860" t="n">
-        <v>0.012681</v>
+        <v>0.012676</v>
       </c>
       <c r="C860" t="n">
         <v>0.844221</v>
@@ -11607,7 +11607,7 @@
         </is>
       </c>
       <c r="B861" t="n">
-        <v>0.012825</v>
+        <v>0.012819</v>
       </c>
       <c r="C861" t="n">
         <v>0.841709</v>
@@ -11620,7 +11620,7 @@
         </is>
       </c>
       <c r="B862" t="n">
-        <v>0.013237</v>
+        <v>0.013232</v>
       </c>
       <c r="C862" t="n">
         <v>0.8391960000000001</v>
@@ -11633,7 +11633,7 @@
         </is>
       </c>
       <c r="B863" t="n">
-        <v>0.01338</v>
+        <v>0.013374</v>
       </c>
       <c r="C863" t="n">
         <v>0.836683</v>
@@ -11646,7 +11646,7 @@
         </is>
       </c>
       <c r="B864" t="n">
-        <v>0.013426</v>
+        <v>0.013441</v>
       </c>
       <c r="C864" t="n">
         <v>0.834171</v>
@@ -11672,7 +11672,7 @@
         </is>
       </c>
       <c r="B866" t="n">
-        <v>0.013467</v>
+        <v>0.013481</v>
       </c>
       <c r="C866" t="n">
         <v>0.829146</v>
@@ -11685,7 +11685,7 @@
         </is>
       </c>
       <c r="B867" t="n">
-        <v>0.01361</v>
+        <v>0.013606</v>
       </c>
       <c r="C867" t="n">
         <v>0.826633</v>
@@ -11698,7 +11698,7 @@
         </is>
       </c>
       <c r="B868" t="n">
-        <v>0.01393</v>
+        <v>0.013953</v>
       </c>
       <c r="C868" t="n">
         <v>0.824121</v>
@@ -11711,7 +11711,7 @@
         </is>
       </c>
       <c r="B869" t="n">
-        <v>0.014041</v>
+        <v>0.014039</v>
       </c>
       <c r="C869" t="n">
         <v>0.821608</v>
@@ -11737,7 +11737,7 @@
         </is>
       </c>
       <c r="B871" t="n">
-        <v>0.014172</v>
+        <v>0.014188</v>
       </c>
       <c r="C871" t="n">
         <v>0.8165829999999999</v>
@@ -11750,7 +11750,7 @@
         </is>
       </c>
       <c r="B872" t="n">
-        <v>0.014555</v>
+        <v>0.014554</v>
       </c>
       <c r="C872" t="n">
         <v>0.81407</v>
@@ -11763,7 +11763,7 @@
         </is>
       </c>
       <c r="B873" t="n">
-        <v>0.014694</v>
+        <v>0.014697</v>
       </c>
       <c r="C873" t="n">
         <v>0.811558</v>
@@ -11776,7 +11776,7 @@
         </is>
       </c>
       <c r="B874" t="n">
-        <v>0.015382</v>
+        <v>0.015379</v>
       </c>
       <c r="C874" t="n">
         <v>0.809045</v>
@@ -11789,7 +11789,7 @@
         </is>
       </c>
       <c r="B875" t="n">
-        <v>0.015549</v>
+        <v>0.015542</v>
       </c>
       <c r="C875" t="n">
         <v>0.8065330000000001</v>
@@ -11802,7 +11802,7 @@
         </is>
       </c>
       <c r="B876" t="n">
-        <v>0.015573</v>
+        <v>0.01559</v>
       </c>
       <c r="C876" t="n">
         <v>0.80402</v>
@@ -11815,7 +11815,7 @@
         </is>
       </c>
       <c r="B877" t="n">
-        <v>0.015683</v>
+        <v>0.015687</v>
       </c>
       <c r="C877" t="n">
         <v>0.801508</v>
@@ -11828,7 +11828,7 @@
         </is>
       </c>
       <c r="B878" t="n">
-        <v>0.015877</v>
+        <v>0.015875</v>
       </c>
       <c r="C878" t="n">
         <v>0.798995</v>
@@ -11841,7 +11841,7 @@
         </is>
       </c>
       <c r="B879" t="n">
-        <v>0.015944</v>
+        <v>0.015952</v>
       </c>
       <c r="C879" t="n">
         <v>0.796482</v>
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="B880" t="n">
-        <v>0.01621</v>
+        <v>0.016223</v>
       </c>
       <c r="C880" t="n">
         <v>0.79397</v>
@@ -11867,7 +11867,7 @@
         </is>
       </c>
       <c r="B881" t="n">
-        <v>0.01652</v>
+        <v>0.016514</v>
       </c>
       <c r="C881" t="n">
         <v>0.791457</v>
@@ -11880,7 +11880,7 @@
         </is>
       </c>
       <c r="B882" t="n">
-        <v>0.016573</v>
+        <v>0.016567</v>
       </c>
       <c r="C882" t="n">
         <v>0.788945</v>
@@ -11893,7 +11893,7 @@
         </is>
       </c>
       <c r="B883" t="n">
-        <v>0.016785</v>
+        <v>0.016809</v>
       </c>
       <c r="C883" t="n">
         <v>0.786432</v>
@@ -11906,7 +11906,7 @@
         </is>
       </c>
       <c r="B884" t="n">
-        <v>0.016814</v>
+        <v>0.016822</v>
       </c>
       <c r="C884" t="n">
         <v>0.78392</v>
@@ -11919,7 +11919,7 @@
         </is>
       </c>
       <c r="B885" t="n">
-        <v>0.017437</v>
+        <v>0.017451</v>
       </c>
       <c r="C885" t="n">
         <v>0.781407</v>
@@ -11932,7 +11932,7 @@
         </is>
       </c>
       <c r="B886" t="n">
-        <v>0.01753</v>
+        <v>0.017521</v>
       </c>
       <c r="C886" t="n">
         <v>0.778894</v>
@@ -11945,7 +11945,7 @@
         </is>
       </c>
       <c r="B887" t="n">
-        <v>0.017743</v>
+        <v>0.017734</v>
       </c>
       <c r="C887" t="n">
         <v>0.776382</v>
@@ -11958,7 +11958,7 @@
         </is>
       </c>
       <c r="B888" t="n">
-        <v>0.017999</v>
+        <v>0.017991</v>
       </c>
       <c r="C888" t="n">
         <v>0.773869</v>
@@ -11971,7 +11971,7 @@
         </is>
       </c>
       <c r="B889" t="n">
-        <v>0.018111</v>
+        <v>0.018103</v>
       </c>
       <c r="C889" t="n">
         <v>0.771357</v>
@@ -11984,7 +11984,7 @@
         </is>
       </c>
       <c r="B890" t="n">
-        <v>0.018128</v>
+        <v>0.01812</v>
       </c>
       <c r="C890" t="n">
         <v>0.768844</v>
@@ -11997,7 +11997,7 @@
         </is>
       </c>
       <c r="B891" t="n">
-        <v>0.018281</v>
+        <v>0.018276</v>
       </c>
       <c r="C891" t="n">
         <v>0.766332</v>
@@ -12010,7 +12010,7 @@
         </is>
       </c>
       <c r="B892" t="n">
-        <v>0.018356</v>
+        <v>0.018348</v>
       </c>
       <c r="C892" t="n">
         <v>0.763819</v>
@@ -12023,7 +12023,7 @@
         </is>
       </c>
       <c r="B893" t="n">
-        <v>0.018495</v>
+        <v>0.018509</v>
       </c>
       <c r="C893" t="n">
         <v>0.761307</v>
@@ -12036,7 +12036,7 @@
         </is>
       </c>
       <c r="B894" t="n">
-        <v>0.018681</v>
+        <v>0.018685</v>
       </c>
       <c r="C894" t="n">
         <v>0.758794</v>
@@ -12049,7 +12049,7 @@
         </is>
       </c>
       <c r="B895" t="n">
-        <v>0.01889</v>
+        <v>0.018882</v>
       </c>
       <c r="C895" t="n">
         <v>0.756281</v>
@@ -12062,7 +12062,7 @@
         </is>
       </c>
       <c r="B896" t="n">
-        <v>0.019591</v>
+        <v>0.019584</v>
       </c>
       <c r="C896" t="n">
         <v>0.753769</v>
@@ -12075,7 +12075,7 @@
         </is>
       </c>
       <c r="B897" t="n">
-        <v>0.019737</v>
+        <v>0.019741</v>
       </c>
       <c r="C897" t="n">
         <v>0.751256</v>
@@ -12088,7 +12088,7 @@
         </is>
       </c>
       <c r="B898" t="n">
-        <v>0.020015</v>
+        <v>0.020006</v>
       </c>
       <c r="C898" t="n">
         <v>0.748744</v>
@@ -12101,7 +12101,7 @@
         </is>
       </c>
       <c r="B899" t="n">
-        <v>0.020243</v>
+        <v>0.020269</v>
       </c>
       <c r="C899" t="n">
         <v>0.746231</v>
@@ -12114,7 +12114,7 @@
         </is>
       </c>
       <c r="B900" t="n">
-        <v>0.020473</v>
+        <v>0.020478</v>
       </c>
       <c r="C900" t="n">
         <v>0.743719</v>
@@ -12127,7 +12127,7 @@
         </is>
       </c>
       <c r="B901" t="n">
-        <v>0.020636</v>
+        <v>0.020649</v>
       </c>
       <c r="C901" t="n">
         <v>0.741206</v>
@@ -12140,7 +12140,7 @@
         </is>
       </c>
       <c r="B902" t="n">
-        <v>0.021212</v>
+        <v>0.021201</v>
       </c>
       <c r="C902" t="n">
         <v>0.738693</v>
@@ -12153,7 +12153,7 @@
         </is>
       </c>
       <c r="B903" t="n">
-        <v>0.021311</v>
+        <v>0.021368</v>
       </c>
       <c r="C903" t="n">
         <v>0.736181</v>
@@ -12166,7 +12166,7 @@
         </is>
       </c>
       <c r="B904" t="n">
-        <v>0.021395</v>
+        <v>0.021389</v>
       </c>
       <c r="C904" t="n">
         <v>0.733668</v>
@@ -12179,7 +12179,7 @@
         </is>
       </c>
       <c r="B905" t="n">
-        <v>0.021721</v>
+        <v>0.021729</v>
       </c>
       <c r="C905" t="n">
         <v>0.731156</v>
@@ -12192,7 +12192,7 @@
         </is>
       </c>
       <c r="B906" t="n">
-        <v>0.022143</v>
+        <v>0.022132</v>
       </c>
       <c r="C906" t="n">
         <v>0.728643</v>
@@ -12205,7 +12205,7 @@
         </is>
       </c>
       <c r="B907" t="n">
-        <v>0.022155</v>
+        <v>0.022188</v>
       </c>
       <c r="C907" t="n">
         <v>0.726131</v>
@@ -12218,7 +12218,7 @@
         </is>
       </c>
       <c r="B908" t="n">
-        <v>0.022408</v>
+        <v>0.022412</v>
       </c>
       <c r="C908" t="n">
         <v>0.723618</v>
@@ -12231,7 +12231,7 @@
         </is>
       </c>
       <c r="B909" t="n">
-        <v>0.022552</v>
+        <v>0.022595</v>
       </c>
       <c r="C909" t="n">
         <v>0.721106</v>
@@ -12244,7 +12244,7 @@
         </is>
       </c>
       <c r="B910" t="n">
-        <v>0.022721</v>
+        <v>0.02271</v>
       </c>
       <c r="C910" t="n">
         <v>0.718593</v>
@@ -12257,7 +12257,7 @@
         </is>
       </c>
       <c r="B911" t="n">
-        <v>0.022858</v>
+        <v>0.022883</v>
       </c>
       <c r="C911" t="n">
         <v>0.71608</v>
@@ -12270,7 +12270,7 @@
         </is>
       </c>
       <c r="B912" t="n">
-        <v>0.023083</v>
+        <v>0.023086</v>
       </c>
       <c r="C912" t="n">
         <v>0.713568</v>
@@ -12283,7 +12283,7 @@
         </is>
       </c>
       <c r="B913" t="n">
-        <v>0.023262</v>
+        <v>0.023261</v>
       </c>
       <c r="C913" t="n">
         <v>0.711055</v>
@@ -12296,7 +12296,7 @@
         </is>
       </c>
       <c r="B914" t="n">
-        <v>0.023304</v>
+        <v>0.023356</v>
       </c>
       <c r="C914" t="n">
         <v>0.708543</v>
@@ -12309,7 +12309,7 @@
         </is>
       </c>
       <c r="B915" t="n">
-        <v>0.023652</v>
+        <v>0.023661</v>
       </c>
       <c r="C915" t="n">
         <v>0.70603</v>
@@ -12322,7 +12322,7 @@
         </is>
       </c>
       <c r="B916" t="n">
-        <v>0.023666</v>
+        <v>0.023698</v>
       </c>
       <c r="C916" t="n">
         <v>0.703518</v>
@@ -12335,7 +12335,7 @@
         </is>
       </c>
       <c r="B917" t="n">
-        <v>0.024095</v>
+        <v>0.024083</v>
       </c>
       <c r="C917" t="n">
         <v>0.701005</v>
@@ -12348,7 +12348,7 @@
         </is>
       </c>
       <c r="B918" t="n">
-        <v>0.024147</v>
+        <v>0.02414</v>
       </c>
       <c r="C918" t="n">
         <v>0.698492</v>
@@ -12361,7 +12361,7 @@
         </is>
       </c>
       <c r="B919" t="n">
-        <v>0.024266</v>
+        <v>0.024255</v>
       </c>
       <c r="C919" t="n">
         <v>0.69598</v>
@@ -12374,7 +12374,7 @@
         </is>
       </c>
       <c r="B920" t="n">
-        <v>0.024314</v>
+        <v>0.024306</v>
       </c>
       <c r="C920" t="n">
         <v>0.6934669999999999</v>
@@ -12387,7 +12387,7 @@
         </is>
       </c>
       <c r="B921" t="n">
-        <v>0.024664</v>
+        <v>0.024663</v>
       </c>
       <c r="C921" t="n">
         <v>0.690955</v>
@@ -12400,7 +12400,7 @@
         </is>
       </c>
       <c r="B922" t="n">
-        <v>0.024755</v>
+        <v>0.024748</v>
       </c>
       <c r="C922" t="n">
         <v>0.688442</v>
@@ -12413,7 +12413,7 @@
         </is>
       </c>
       <c r="B923" t="n">
-        <v>0.024834</v>
+        <v>0.02485</v>
       </c>
       <c r="C923" t="n">
         <v>0.68593</v>
@@ -12426,7 +12426,7 @@
         </is>
       </c>
       <c r="B924" t="n">
-        <v>0.024985</v>
+        <v>0.024994</v>
       </c>
       <c r="C924" t="n">
         <v>0.6834170000000001</v>
@@ -12439,7 +12439,7 @@
         </is>
       </c>
       <c r="B925" t="n">
-        <v>0.025053</v>
+        <v>0.025047</v>
       </c>
       <c r="C925" t="n">
         <v>0.680905</v>
@@ -12452,7 +12452,7 @@
         </is>
       </c>
       <c r="B926" t="n">
-        <v>0.025197</v>
+        <v>0.025215</v>
       </c>
       <c r="C926" t="n">
         <v>0.678392</v>
@@ -12465,7 +12465,7 @@
         </is>
       </c>
       <c r="B927" t="n">
-        <v>0.026686</v>
+        <v>0.026672</v>
       </c>
       <c r="C927" t="n">
         <v>0.675879</v>
@@ -12478,7 +12478,7 @@
         </is>
       </c>
       <c r="B928" t="n">
-        <v>0.026708</v>
+        <v>0.026698</v>
       </c>
       <c r="C928" t="n">
         <v>0.673367</v>
@@ -12491,7 +12491,7 @@
         </is>
       </c>
       <c r="B929" t="n">
-        <v>0.026825</v>
+        <v>0.026818</v>
       </c>
       <c r="C929" t="n">
         <v>0.670854</v>
@@ -12504,7 +12504,7 @@
         </is>
       </c>
       <c r="B930" t="n">
-        <v>0.027151</v>
+        <v>0.027138</v>
       </c>
       <c r="C930" t="n">
         <v>0.668342</v>
@@ -12517,7 +12517,7 @@
         </is>
       </c>
       <c r="B931" t="n">
-        <v>0.027202</v>
+        <v>0.027193</v>
       </c>
       <c r="C931" t="n">
         <v>0.665829</v>
@@ -12530,7 +12530,7 @@
         </is>
       </c>
       <c r="B932" t="n">
-        <v>0.027301</v>
+        <v>0.027315</v>
       </c>
       <c r="C932" t="n">
         <v>0.663317</v>
@@ -12543,7 +12543,7 @@
         </is>
       </c>
       <c r="B933" t="n">
-        <v>0.027303</v>
+        <v>0.027316</v>
       </c>
       <c r="C933" t="n">
         <v>0.6608039999999999</v>
@@ -12556,7 +12556,7 @@
         </is>
       </c>
       <c r="B934" t="n">
-        <v>0.027735</v>
+        <v>0.027734</v>
       </c>
       <c r="C934" t="n">
         <v>0.658291</v>
@@ -12569,7 +12569,7 @@
         </is>
       </c>
       <c r="B935" t="n">
-        <v>0.027768</v>
+        <v>0.027755</v>
       </c>
       <c r="C935" t="n">
         <v>0.655779</v>
@@ -12582,7 +12582,7 @@
         </is>
       </c>
       <c r="B936" t="n">
-        <v>0.02812</v>
+        <v>0.028113</v>
       </c>
       <c r="C936" t="n">
         <v>0.653266</v>
@@ -12595,7 +12595,7 @@
         </is>
       </c>
       <c r="B937" t="n">
-        <v>0.028247</v>
+        <v>0.02829</v>
       </c>
       <c r="C937" t="n">
         <v>0.6507540000000001</v>
@@ -12608,7 +12608,7 @@
         </is>
       </c>
       <c r="B938" t="n">
-        <v>0.02847</v>
+        <v>0.028456</v>
       </c>
       <c r="C938" t="n">
         <v>0.648241</v>
@@ -12621,7 +12621,7 @@
         </is>
       </c>
       <c r="B939" t="n">
-        <v>0.028569</v>
+        <v>0.028554</v>
       </c>
       <c r="C939" t="n">
         <v>0.645729</v>
@@ -12634,7 +12634,7 @@
         </is>
       </c>
       <c r="B940" t="n">
-        <v>0.029057</v>
+        <v>0.029055</v>
       </c>
       <c r="C940" t="n">
         <v>0.643216</v>
@@ -12647,7 +12647,7 @@
         </is>
       </c>
       <c r="B941" t="n">
-        <v>0.029416</v>
+        <v>0.029479</v>
       </c>
       <c r="C941" t="n">
         <v>0.6407040000000001</v>
@@ -12660,7 +12660,7 @@
         </is>
       </c>
       <c r="B942" t="n">
-        <v>0.029515</v>
+        <v>0.029503</v>
       </c>
       <c r="C942" t="n">
         <v>0.638191</v>
@@ -12673,7 +12673,7 @@
         </is>
       </c>
       <c r="B943" t="n">
-        <v>0.029559</v>
+        <v>0.029612</v>
       </c>
       <c r="C943" t="n">
         <v>0.635678</v>
@@ -12686,7 +12686,7 @@
         </is>
       </c>
       <c r="B944" t="n">
-        <v>0.029568</v>
+        <v>0.029623</v>
       </c>
       <c r="C944" t="n">
         <v>0.633166</v>
@@ -12699,7 +12699,7 @@
         </is>
       </c>
       <c r="B945" t="n">
-        <v>0.029825</v>
+        <v>0.029813</v>
       </c>
       <c r="C945" t="n">
         <v>0.630653</v>
@@ -12712,7 +12712,7 @@
         </is>
       </c>
       <c r="B946" t="n">
-        <v>0.030093</v>
+        <v>0.030077</v>
       </c>
       <c r="C946" t="n">
         <v>0.6281409999999999</v>
@@ -12725,7 +12725,7 @@
         </is>
       </c>
       <c r="B947" t="n">
-        <v>0.030376</v>
+        <v>0.030373</v>
       </c>
       <c r="C947" t="n">
         <v>0.625628</v>
@@ -12738,7 +12738,7 @@
         </is>
       </c>
       <c r="B948" t="n">
-        <v>0.030523</v>
+        <v>0.030537</v>
       </c>
       <c r="C948" t="n">
         <v>0.623116</v>
@@ -12751,7 +12751,7 @@
         </is>
       </c>
       <c r="B949" t="n">
-        <v>0.030548</v>
+        <v>0.030552</v>
       </c>
       <c r="C949" t="n">
         <v>0.620603</v>
@@ -12764,7 +12764,7 @@
         </is>
       </c>
       <c r="B950" t="n">
-        <v>0.030706</v>
+        <v>0.030747</v>
       </c>
       <c r="C950" t="n">
         <v>0.61809</v>
@@ -12777,7 +12777,7 @@
         </is>
       </c>
       <c r="B951" t="n">
-        <v>0.030927</v>
+        <v>0.030912</v>
       </c>
       <c r="C951" t="n">
         <v>0.615578</v>
@@ -12790,7 +12790,7 @@
         </is>
       </c>
       <c r="B952" t="n">
-        <v>0.031144</v>
+        <v>0.031147</v>
       </c>
       <c r="C952" t="n">
         <v>0.613065</v>
@@ -12803,7 +12803,7 @@
         </is>
       </c>
       <c r="B953" t="n">
-        <v>0.031335</v>
+        <v>0.031323</v>
       </c>
       <c r="C953" t="n">
         <v>0.610553</v>
@@ -12816,7 +12816,7 @@
         </is>
       </c>
       <c r="B954" t="n">
-        <v>0.031355</v>
+        <v>0.031348</v>
       </c>
       <c r="C954" t="n">
         <v>0.60804</v>
@@ -12829,7 +12829,7 @@
         </is>
       </c>
       <c r="B955" t="n">
-        <v>0.031527</v>
+        <v>0.031549</v>
       </c>
       <c r="C955" t="n">
         <v>0.605528</v>
@@ -12842,7 +12842,7 @@
         </is>
       </c>
       <c r="B956" t="n">
-        <v>0.031672</v>
+        <v>0.031666</v>
       </c>
       <c r="C956" t="n">
         <v>0.603015</v>
@@ -12855,7 +12855,7 @@
         </is>
       </c>
       <c r="B957" t="n">
-        <v>0.031793</v>
+        <v>0.031819</v>
       </c>
       <c r="C957" t="n">
         <v>0.600503</v>
@@ -12868,7 +12868,7 @@
         </is>
       </c>
       <c r="B958" t="n">
-        <v>0.031911</v>
+        <v>0.031919</v>
       </c>
       <c r="C958" t="n">
         <v>0.59799</v>
@@ -12881,7 +12881,7 @@
         </is>
       </c>
       <c r="B959" t="n">
-        <v>0.032014</v>
+        <v>0.031998</v>
       </c>
       <c r="C959" t="n">
         <v>0.595477</v>
@@ -12894,7 +12894,7 @@
         </is>
       </c>
       <c r="B960" t="n">
-        <v>0.032795</v>
+        <v>0.032782</v>
       </c>
       <c r="C960" t="n">
         <v>0.592965</v>
@@ -12907,7 +12907,7 @@
         </is>
       </c>
       <c r="B961" t="n">
-        <v>0.03294</v>
+        <v>0.032956</v>
       </c>
       <c r="C961" t="n">
         <v>0.590452</v>
@@ -12920,7 +12920,7 @@
         </is>
       </c>
       <c r="B962" t="n">
-        <v>0.033133</v>
+        <v>0.033116</v>
       </c>
       <c r="C962" t="n">
         <v>0.58794</v>
@@ -12933,7 +12933,7 @@
         </is>
       </c>
       <c r="B963" t="n">
-        <v>0.033196</v>
+        <v>0.033189</v>
       </c>
       <c r="C963" t="n">
         <v>0.585427</v>
@@ -12946,7 +12946,7 @@
         </is>
       </c>
       <c r="B964" t="n">
-        <v>0.033471</v>
+        <v>0.033467</v>
       </c>
       <c r="C964" t="n">
         <v>0.582915</v>
@@ -12959,7 +12959,7 @@
         </is>
       </c>
       <c r="B965" t="n">
-        <v>0.033631</v>
+        <v>0.033616</v>
       </c>
       <c r="C965" t="n">
         <v>0.580402</v>
@@ -12972,7 +12972,7 @@
         </is>
       </c>
       <c r="B966" t="n">
-        <v>0.033635</v>
+        <v>0.033627</v>
       </c>
       <c r="C966" t="n">
         <v>0.577889</v>
@@ -12985,7 +12985,7 @@
         </is>
       </c>
       <c r="B967" t="n">
-        <v>0.033702</v>
+        <v>0.033706</v>
       </c>
       <c r="C967" t="n">
         <v>0.575377</v>
@@ -12998,7 +12998,7 @@
         </is>
       </c>
       <c r="B968" t="n">
-        <v>0.03432</v>
+        <v>0.034307</v>
       </c>
       <c r="C968" t="n">
         <v>0.572864</v>
@@ -13011,7 +13011,7 @@
         </is>
       </c>
       <c r="B969" t="n">
-        <v>0.034342</v>
+        <v>0.03435</v>
       </c>
       <c r="C969" t="n">
         <v>0.570352</v>
@@ -13024,7 +13024,7 @@
         </is>
       </c>
       <c r="B970" t="n">
-        <v>0.034366</v>
+        <v>0.034361</v>
       </c>
       <c r="C970" t="n">
         <v>0.567839</v>
@@ -13037,7 +13037,7 @@
         </is>
       </c>
       <c r="B971" t="n">
-        <v>0.034929</v>
+        <v>0.034948</v>
       </c>
       <c r="C971" t="n">
         <v>0.565327</v>
@@ -13050,7 +13050,7 @@
         </is>
       </c>
       <c r="B972" t="n">
-        <v>0.035258</v>
+        <v>0.035338</v>
       </c>
       <c r="C972" t="n">
         <v>0.562814</v>
@@ -13063,7 +13063,7 @@
         </is>
       </c>
       <c r="B973" t="n">
-        <v>0.035745</v>
+        <v>0.035753</v>
       </c>
       <c r="C973" t="n">
         <v>0.560302</v>
@@ -13076,7 +13076,7 @@
         </is>
       </c>
       <c r="B974" t="n">
-        <v>0.036041</v>
+        <v>0.036023</v>
       </c>
       <c r="C974" t="n">
         <v>0.557789</v>
@@ -13089,7 +13089,7 @@
         </is>
       </c>
       <c r="B975" t="n">
-        <v>0.036114</v>
+        <v>0.036104</v>
       </c>
       <c r="C975" t="n">
         <v>0.555276</v>
@@ -13102,7 +13102,7 @@
         </is>
       </c>
       <c r="B976" t="n">
-        <v>0.036713</v>
+        <v>0.03678</v>
       </c>
       <c r="C976" t="n">
         <v>0.552764</v>
@@ -13128,7 +13128,7 @@
         </is>
       </c>
       <c r="B978" t="n">
-        <v>0.037105</v>
+        <v>0.037093</v>
       </c>
       <c r="C978" t="n">
         <v>0.547739</v>
@@ -13141,7 +13141,7 @@
         </is>
       </c>
       <c r="B979" t="n">
-        <v>0.037174</v>
+        <v>0.037166</v>
       </c>
       <c r="C979" t="n">
         <v>0.545226</v>
@@ -13154,7 +13154,7 @@
         </is>
       </c>
       <c r="B980" t="n">
-        <v>0.037418</v>
+        <v>0.037413</v>
       </c>
       <c r="C980" t="n">
         <v>0.542714</v>
@@ -13167,7 +13167,7 @@
         </is>
       </c>
       <c r="B981" t="n">
-        <v>0.037418</v>
+        <v>0.037421</v>
       </c>
       <c r="C981" t="n">
         <v>0.540201</v>
@@ -13180,7 +13180,7 @@
         </is>
       </c>
       <c r="B982" t="n">
-        <v>0.037439</v>
+        <v>0.037454</v>
       </c>
       <c r="C982" t="n">
         <v>0.5376880000000001</v>
@@ -13193,7 +13193,7 @@
         </is>
       </c>
       <c r="B983" t="n">
-        <v>0.038241</v>
+        <v>0.038223</v>
       </c>
       <c r="C983" t="n">
         <v>0.535176</v>
@@ -13206,7 +13206,7 @@
         </is>
       </c>
       <c r="B984" t="n">
-        <v>0.038243</v>
+        <v>0.038235</v>
       </c>
       <c r="C984" t="n">
         <v>0.532663</v>
@@ -13219,7 +13219,7 @@
         </is>
       </c>
       <c r="B985" t="n">
-        <v>0.038278</v>
+        <v>0.03826</v>
       </c>
       <c r="C985" t="n">
         <v>0.530151</v>
@@ -13232,7 +13232,7 @@
         </is>
       </c>
       <c r="B986" t="n">
-        <v>0.038294</v>
+        <v>0.03831</v>
       </c>
       <c r="C986" t="n">
         <v>0.5276380000000001</v>
@@ -13245,7 +13245,7 @@
         </is>
       </c>
       <c r="B987" t="n">
-        <v>0.03833</v>
+        <v>0.038326</v>
       </c>
       <c r="C987" t="n">
         <v>0.525126</v>
@@ -13258,7 +13258,7 @@
         </is>
       </c>
       <c r="B988" t="n">
-        <v>0.039806</v>
+        <v>0.039792</v>
       </c>
       <c r="C988" t="n">
         <v>0.522613</v>
@@ -13271,7 +13271,7 @@
         </is>
       </c>
       <c r="B989" t="n">
-        <v>0.040046</v>
+        <v>0.040043</v>
       </c>
       <c r="C989" t="n">
         <v>0.520101</v>
@@ -13284,7 +13284,7 @@
         </is>
       </c>
       <c r="B990" t="n">
-        <v>0.040311</v>
+        <v>0.0403</v>
       </c>
       <c r="C990" t="n">
         <v>0.517588</v>
@@ -13297,7 +13297,7 @@
         </is>
       </c>
       <c r="B991" t="n">
-        <v>0.040653</v>
+        <v>0.040685</v>
       </c>
       <c r="C991" t="n">
         <v>0.5150749999999999</v>
@@ -13310,7 +13310,7 @@
         </is>
       </c>
       <c r="B992" t="n">
-        <v>0.040833</v>
+        <v>0.040825</v>
       </c>
       <c r="C992" t="n">
         <v>0.512563</v>
@@ -13323,7 +13323,7 @@
         </is>
       </c>
       <c r="B993" t="n">
-        <v>0.040939</v>
+        <v>0.040924</v>
       </c>
       <c r="C993" t="n">
         <v>0.51005</v>
@@ -13336,7 +13336,7 @@
         </is>
       </c>
       <c r="B994" t="n">
-        <v>0.041057</v>
+        <v>0.041042</v>
       </c>
       <c r="C994" t="n">
         <v>0.507538</v>
@@ -13349,7 +13349,7 @@
         </is>
       </c>
       <c r="B995" t="n">
-        <v>0.041143</v>
+        <v>0.041218</v>
       </c>
       <c r="C995" t="n">
         <v>0.5050249999999999</v>
@@ -13362,7 +13362,7 @@
         </is>
       </c>
       <c r="B996" t="n">
-        <v>0.041639</v>
+        <v>0.041624</v>
       </c>
       <c r="C996" t="n">
         <v>0.502513</v>
@@ -13375,7 +13375,7 @@
         </is>
       </c>
       <c r="B997" t="n">
-        <v>0.041721</v>
+        <v>0.041714</v>
       </c>
       <c r="C997" t="n">
         <v>0.5</v>
@@ -13388,7 +13388,7 @@
         </is>
       </c>
       <c r="B998" t="n">
-        <v>0.04177</v>
+        <v>0.041749</v>
       </c>
       <c r="C998" t="n">
         <v>0.497487</v>
@@ -13401,7 +13401,7 @@
         </is>
       </c>
       <c r="B999" t="n">
-        <v>0.041957</v>
+        <v>0.041994</v>
       </c>
       <c r="C999" t="n">
         <v>0.494975</v>
@@ -13414,7 +13414,7 @@
         </is>
       </c>
       <c r="B1000" t="n">
-        <v>0.042011</v>
+        <v>0.041995</v>
       </c>
       <c r="C1000" t="n">
         <v>0.492462</v>
@@ -13427,7 +13427,7 @@
         </is>
       </c>
       <c r="B1001" t="n">
-        <v>0.042135</v>
+        <v>0.042121</v>
       </c>
       <c r="C1001" t="n">
         <v>0.48995</v>
@@ -13440,7 +13440,7 @@
         </is>
       </c>
       <c r="B1002" t="n">
-        <v>0.042236</v>
+        <v>0.042232</v>
       </c>
       <c r="C1002" t="n">
         <v>0.487437</v>
@@ -13453,7 +13453,7 @@
         </is>
       </c>
       <c r="B1003" t="n">
-        <v>0.042302</v>
+        <v>0.042377</v>
       </c>
       <c r="C1003" t="n">
         <v>0.484925</v>
@@ -13466,7 +13466,7 @@
         </is>
       </c>
       <c r="B1004" t="n">
-        <v>0.042396</v>
+        <v>0.042418</v>
       </c>
       <c r="C1004" t="n">
         <v>0.482412</v>
@@ -13479,7 +13479,7 @@
         </is>
       </c>
       <c r="B1005" t="n">
-        <v>0.042591</v>
+        <v>0.042571</v>
       </c>
       <c r="C1005" t="n">
         <v>0.479899</v>
@@ -13492,7 +13492,7 @@
         </is>
       </c>
       <c r="B1006" t="n">
-        <v>0.043167</v>
+        <v>0.043148</v>
       </c>
       <c r="C1006" t="n">
         <v>0.477387</v>
@@ -13505,7 +13505,7 @@
         </is>
       </c>
       <c r="B1007" t="n">
-        <v>0.043208</v>
+        <v>0.043187</v>
       </c>
       <c r="C1007" t="n">
         <v>0.474874</v>
@@ -13518,7 +13518,7 @@
         </is>
       </c>
       <c r="B1008" t="n">
-        <v>0.043424</v>
+        <v>0.043442</v>
       </c>
       <c r="C1008" t="n">
         <v>0.472362</v>
@@ -13531,7 +13531,7 @@
         </is>
       </c>
       <c r="B1009" t="n">
-        <v>0.043823</v>
+        <v>0.04383</v>
       </c>
       <c r="C1009" t="n">
         <v>0.469849</v>
@@ -13544,7 +13544,7 @@
         </is>
       </c>
       <c r="B1010" t="n">
-        <v>0.04397</v>
+        <v>0.043948</v>
       </c>
       <c r="C1010" t="n">
         <v>0.467337</v>
@@ -13557,7 +13557,7 @@
         </is>
       </c>
       <c r="B1011" t="n">
-        <v>0.044323</v>
+        <v>0.044438</v>
       </c>
       <c r="C1011" t="n">
         <v>0.464824</v>
@@ -13570,7 +13570,7 @@
         </is>
       </c>
       <c r="B1012" t="n">
-        <v>0.044463</v>
+        <v>0.04444</v>
       </c>
       <c r="C1012" t="n">
         <v>0.462312</v>
@@ -13583,7 +13583,7 @@
         </is>
       </c>
       <c r="B1013" t="n">
-        <v>0.04455</v>
+        <v>0.044541</v>
       </c>
       <c r="C1013" t="n">
         <v>0.459799</v>
@@ -13596,7 +13596,7 @@
         </is>
       </c>
       <c r="B1014" t="n">
-        <v>0.045482</v>
+        <v>0.045465</v>
       </c>
       <c r="C1014" t="n">
         <v>0.457286</v>
@@ -13609,7 +13609,7 @@
         </is>
       </c>
       <c r="B1015" t="n">
-        <v>0.046016</v>
+        <v>0.046011</v>
       </c>
       <c r="C1015" t="n">
         <v>0.454774</v>
@@ -13622,7 +13622,7 @@
         </is>
       </c>
       <c r="B1016" t="n">
-        <v>0.046875</v>
+        <v>0.046861</v>
       </c>
       <c r="C1016" t="n">
         <v>0.452261</v>
@@ -13635,7 +13635,7 @@
         </is>
       </c>
       <c r="B1017" t="n">
-        <v>0.047221</v>
+        <v>0.047324</v>
       </c>
       <c r="C1017" t="n">
         <v>0.449749</v>
@@ -13648,7 +13648,7 @@
         </is>
       </c>
       <c r="B1018" t="n">
-        <v>0.047264</v>
+        <v>0.047393</v>
       </c>
       <c r="C1018" t="n">
         <v>0.447236</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="B1019" t="n">
-        <v>0.047418</v>
+        <v>0.047505</v>
       </c>
       <c r="C1019" t="n">
         <v>0.444724</v>
@@ -13674,7 +13674,7 @@
         </is>
       </c>
       <c r="B1020" t="n">
-        <v>0.04756</v>
+        <v>0.047548</v>
       </c>
       <c r="C1020" t="n">
         <v>0.442211</v>
@@ -13687,7 +13687,7 @@
         </is>
       </c>
       <c r="B1021" t="n">
-        <v>0.047571</v>
+        <v>0.047548</v>
       </c>
       <c r="C1021" t="n">
         <v>0.439698</v>
@@ -13700,7 +13700,7 @@
         </is>
       </c>
       <c r="B1022" t="n">
-        <v>0.048511</v>
+        <v>0.048606</v>
       </c>
       <c r="C1022" t="n">
         <v>0.437186</v>
@@ -13713,7 +13713,7 @@
         </is>
       </c>
       <c r="B1023" t="n">
-        <v>0.049104</v>
+        <v>0.049102</v>
       </c>
       <c r="C1023" t="n">
         <v>0.434673</v>
@@ -13726,7 +13726,7 @@
         </is>
       </c>
       <c r="B1024" t="n">
-        <v>0.04946</v>
+        <v>0.049487</v>
       </c>
       <c r="C1024" t="n">
         <v>0.432161</v>
@@ -13739,7 +13739,7 @@
         </is>
       </c>
       <c r="B1025" t="n">
-        <v>0.049565</v>
+        <v>0.049566</v>
       </c>
       <c r="C1025" t="n">
         <v>0.429648</v>
@@ -13752,7 +13752,7 @@
         </is>
       </c>
       <c r="B1026" t="n">
-        <v>0.049664</v>
+        <v>0.049715</v>
       </c>
       <c r="C1026" t="n">
         <v>0.427136</v>
@@ -13765,7 +13765,7 @@
         </is>
       </c>
       <c r="B1027" t="n">
-        <v>0.050223</v>
+        <v>0.050233</v>
       </c>
       <c r="C1027" t="n">
         <v>0.424623</v>
@@ -13778,7 +13778,7 @@
         </is>
       </c>
       <c r="B1028" t="n">
-        <v>0.050253</v>
+        <v>0.050337</v>
       </c>
       <c r="C1028" t="n">
         <v>0.422111</v>
@@ -13791,7 +13791,7 @@
         </is>
       </c>
       <c r="B1029" t="n">
-        <v>0.050677</v>
+        <v>0.050695</v>
       </c>
       <c r="C1029" t="n">
         <v>0.419598</v>
@@ -13804,7 +13804,7 @@
         </is>
       </c>
       <c r="B1030" t="n">
-        <v>0.050787</v>
+        <v>0.050766</v>
       </c>
       <c r="C1030" t="n">
         <v>0.417085</v>
@@ -13817,7 +13817,7 @@
         </is>
       </c>
       <c r="B1031" t="n">
-        <v>0.050845</v>
+        <v>0.05082</v>
       </c>
       <c r="C1031" t="n">
         <v>0.414573</v>
@@ -13830,7 +13830,7 @@
         </is>
       </c>
       <c r="B1032" t="n">
-        <v>0.050962</v>
+        <v>0.050968</v>
       </c>
       <c r="C1032" t="n">
         <v>0.41206</v>
@@ -13843,7 +13843,7 @@
         </is>
       </c>
       <c r="B1033" t="n">
-        <v>0.050998</v>
+        <v>0.051004</v>
       </c>
       <c r="C1033" t="n">
         <v>0.409548</v>
@@ -13856,7 +13856,7 @@
         </is>
       </c>
       <c r="B1034" t="n">
-        <v>0.051059</v>
+        <v>0.051052</v>
       </c>
       <c r="C1034" t="n">
         <v>0.407035</v>
@@ -13869,7 +13869,7 @@
         </is>
       </c>
       <c r="B1035" t="n">
-        <v>0.051064</v>
+        <v>0.051168</v>
       </c>
       <c r="C1035" t="n">
         <v>0.404523</v>
@@ -13882,7 +13882,7 @@
         </is>
       </c>
       <c r="B1036" t="n">
-        <v>0.051183</v>
+        <v>0.051178</v>
       </c>
       <c r="C1036" t="n">
         <v>0.40201</v>
@@ -13895,7 +13895,7 @@
         </is>
       </c>
       <c r="B1037" t="n">
-        <v>0.051527</v>
+        <v>0.051501</v>
       </c>
       <c r="C1037" t="n">
         <v>0.399497</v>
@@ -13908,7 +13908,7 @@
         </is>
       </c>
       <c r="B1038" t="n">
-        <v>0.051801</v>
+        <v>0.051775</v>
       </c>
       <c r="C1038" t="n">
         <v>0.396985</v>
@@ -13921,7 +13921,7 @@
         </is>
       </c>
       <c r="B1039" t="n">
-        <v>0.0524</v>
+        <v>0.052447</v>
       </c>
       <c r="C1039" t="n">
         <v>0.394472</v>
@@ -13934,7 +13934,7 @@
         </is>
       </c>
       <c r="B1040" t="n">
-        <v>0.052506</v>
+        <v>0.052489</v>
       </c>
       <c r="C1040" t="n">
         <v>0.39196</v>
@@ -13947,7 +13947,7 @@
         </is>
       </c>
       <c r="B1041" t="n">
-        <v>0.05285</v>
+        <v>0.052848</v>
       </c>
       <c r="C1041" t="n">
         <v>0.389447</v>
@@ -13960,7 +13960,7 @@
         </is>
       </c>
       <c r="B1042" t="n">
-        <v>0.053027</v>
+        <v>0.053004</v>
       </c>
       <c r="C1042" t="n">
         <v>0.386935</v>
@@ -13973,7 +13973,7 @@
         </is>
       </c>
       <c r="B1043" t="n">
-        <v>0.053406</v>
+        <v>0.053379</v>
       </c>
       <c r="C1043" t="n">
         <v>0.384422</v>
@@ -13986,7 +13986,7 @@
         </is>
       </c>
       <c r="B1044" t="n">
-        <v>0.053951</v>
+        <v>0.053987</v>
       </c>
       <c r="C1044" t="n">
         <v>0.38191</v>
@@ -13999,7 +13999,7 @@
         </is>
       </c>
       <c r="B1045" t="n">
-        <v>0.054131</v>
+        <v>0.054161</v>
       </c>
       <c r="C1045" t="n">
         <v>0.379397</v>
@@ -14012,7 +14012,7 @@
         </is>
       </c>
       <c r="B1046" t="n">
-        <v>0.05418</v>
+        <v>0.05419</v>
       </c>
       <c r="C1046" t="n">
         <v>0.376884</v>
@@ -14025,7 +14025,7 @@
         </is>
       </c>
       <c r="B1047" t="n">
-        <v>0.05508</v>
+        <v>0.055055</v>
       </c>
       <c r="C1047" t="n">
         <v>0.374372</v>
@@ -14038,7 +14038,7 @@
         </is>
       </c>
       <c r="B1048" t="n">
-        <v>0.055886</v>
+        <v>0.055875</v>
       </c>
       <c r="C1048" t="n">
         <v>0.371859</v>
@@ -14051,7 +14051,7 @@
         </is>
       </c>
       <c r="B1049" t="n">
-        <v>0.055901</v>
+        <v>0.05589</v>
       </c>
       <c r="C1049" t="n">
         <v>0.369347</v>
@@ -14064,7 +14064,7 @@
         </is>
       </c>
       <c r="B1050" t="n">
-        <v>0.055946</v>
+        <v>0.055972</v>
       </c>
       <c r="C1050" t="n">
         <v>0.366834</v>
@@ -14077,7 +14077,7 @@
         </is>
       </c>
       <c r="B1051" t="n">
-        <v>0.05608</v>
+        <v>0.056072</v>
       </c>
       <c r="C1051" t="n">
         <v>0.364322</v>
@@ -14090,7 +14090,7 @@
         </is>
       </c>
       <c r="B1052" t="n">
-        <v>0.056449</v>
+        <v>0.056464</v>
       </c>
       <c r="C1052" t="n">
         <v>0.361809</v>
@@ -14103,7 +14103,7 @@
         </is>
       </c>
       <c r="B1053" t="n">
-        <v>0.056644</v>
+        <v>0.056617</v>
       </c>
       <c r="C1053" t="n">
         <v>0.359296</v>
@@ -14116,7 +14116,7 @@
         </is>
       </c>
       <c r="B1054" t="n">
-        <v>0.056839</v>
+        <v>0.056825</v>
       </c>
       <c r="C1054" t="n">
         <v>0.356784</v>
@@ -14129,7 +14129,7 @@
         </is>
       </c>
       <c r="B1055" t="n">
-        <v>0.057941</v>
+        <v>0.057917</v>
       </c>
       <c r="C1055" t="n">
         <v>0.354271</v>
@@ -14142,7 +14142,7 @@
         </is>
       </c>
       <c r="B1056" t="n">
-        <v>0.057948</v>
+        <v>0.057945</v>
       </c>
       <c r="C1056" t="n">
         <v>0.351759</v>
@@ -14155,7 +14155,7 @@
         </is>
       </c>
       <c r="B1057" t="n">
-        <v>0.059002</v>
+        <v>0.059059</v>
       </c>
       <c r="C1057" t="n">
         <v>0.349246</v>
@@ -14168,7 +14168,7 @@
         </is>
       </c>
       <c r="B1058" t="n">
-        <v>0.059924</v>
+        <v>0.060056</v>
       </c>
       <c r="C1058" t="n">
         <v>0.346734</v>
@@ -14181,7 +14181,7 @@
         </is>
       </c>
       <c r="B1059" t="n">
-        <v>0.060078</v>
+        <v>0.060237</v>
       </c>
       <c r="C1059" t="n">
         <v>0.344221</v>
@@ -14194,7 +14194,7 @@
         </is>
       </c>
       <c r="B1060" t="n">
-        <v>0.060226</v>
+        <v>0.060306</v>
       </c>
       <c r="C1060" t="n">
         <v>0.341709</v>
@@ -14207,7 +14207,7 @@
         </is>
       </c>
       <c r="B1061" t="n">
-        <v>0.060892</v>
+        <v>0.061003</v>
       </c>
       <c r="C1061" t="n">
         <v>0.339196</v>
@@ -14220,7 +14220,7 @@
         </is>
       </c>
       <c r="B1062" t="n">
-        <v>0.061178</v>
+        <v>0.061244</v>
       </c>
       <c r="C1062" t="n">
         <v>0.336683</v>
@@ -14233,7 +14233,7 @@
         </is>
       </c>
       <c r="B1063" t="n">
-        <v>0.06135</v>
+        <v>0.061347</v>
       </c>
       <c r="C1063" t="n">
         <v>0.334171</v>
@@ -14246,7 +14246,7 @@
         </is>
       </c>
       <c r="B1064" t="n">
-        <v>0.061809</v>
+        <v>0.061808</v>
       </c>
       <c r="C1064" t="n">
         <v>0.331658</v>
@@ -14259,7 +14259,7 @@
         </is>
       </c>
       <c r="B1065" t="n">
-        <v>0.061997</v>
+        <v>0.062066</v>
       </c>
       <c r="C1065" t="n">
         <v>0.329146</v>
@@ -14272,7 +14272,7 @@
         </is>
       </c>
       <c r="B1066" t="n">
-        <v>0.062876</v>
+        <v>0.062856</v>
       </c>
       <c r="C1066" t="n">
         <v>0.326633</v>
@@ -14285,7 +14285,7 @@
         </is>
       </c>
       <c r="B1067" t="n">
-        <v>0.063016</v>
+        <v>0.063001</v>
       </c>
       <c r="C1067" t="n">
         <v>0.324121</v>
@@ -14298,7 +14298,7 @@
         </is>
       </c>
       <c r="B1068" t="n">
-        <v>0.06397700000000001</v>
+        <v>0.063985</v>
       </c>
       <c r="C1068" t="n">
         <v>0.321608</v>
@@ -14311,7 +14311,7 @@
         </is>
       </c>
       <c r="B1069" t="n">
-        <v>0.064028</v>
+        <v>0.064013</v>
       </c>
       <c r="C1069" t="n">
         <v>0.319095</v>
@@ -14324,7 +14324,7 @@
         </is>
       </c>
       <c r="B1070" t="n">
-        <v>0.064209</v>
+        <v>0.06418</v>
       </c>
       <c r="C1070" t="n">
         <v>0.316583</v>
@@ -14337,7 +14337,7 @@
         </is>
       </c>
       <c r="B1071" t="n">
-        <v>0.06440899999999999</v>
+        <v>0.064377</v>
       </c>
       <c r="C1071" t="n">
         <v>0.31407</v>
@@ -14350,7 +14350,7 @@
         </is>
       </c>
       <c r="B1072" t="n">
-        <v>0.064898</v>
+        <v>0.064876</v>
       </c>
       <c r="C1072" t="n">
         <v>0.311558</v>
@@ -14363,7 +14363,7 @@
         </is>
       </c>
       <c r="B1073" t="n">
-        <v>0.065294</v>
+        <v>0.065261</v>
       </c>
       <c r="C1073" t="n">
         <v>0.309045</v>
@@ -14376,7 +14376,7 @@
         </is>
       </c>
       <c r="B1074" t="n">
-        <v>0.065432</v>
+        <v>0.065581</v>
       </c>
       <c r="C1074" t="n">
         <v>0.306533</v>
@@ -14389,7 +14389,7 @@
         </is>
       </c>
       <c r="B1075" t="n">
-        <v>0.065871</v>
+        <v>0.065842</v>
       </c>
       <c r="C1075" t="n">
         <v>0.30402</v>
@@ -14402,7 +14402,7 @@
         </is>
       </c>
       <c r="B1076" t="n">
-        <v>0.066138</v>
+        <v>0.066201</v>
       </c>
       <c r="C1076" t="n">
         <v>0.301508</v>
@@ -14415,7 +14415,7 @@
         </is>
       </c>
       <c r="B1077" t="n">
-        <v>0.066735</v>
+        <v>0.066811</v>
       </c>
       <c r="C1077" t="n">
         <v>0.298995</v>
@@ -14428,7 +14428,7 @@
         </is>
       </c>
       <c r="B1078" t="n">
-        <v>0.06707100000000001</v>
+        <v>0.067151</v>
       </c>
       <c r="C1078" t="n">
         <v>0.296482</v>
@@ -14441,7 +14441,7 @@
         </is>
       </c>
       <c r="B1079" t="n">
-        <v>0.067761</v>
+        <v>0.06779</v>
       </c>
       <c r="C1079" t="n">
         <v>0.29397</v>
@@ -14454,7 +14454,7 @@
         </is>
       </c>
       <c r="B1080" t="n">
-        <v>0.06795900000000001</v>
+        <v>0.067935</v>
       </c>
       <c r="C1080" t="n">
         <v>0.291457</v>
@@ -14467,7 +14467,7 @@
         </is>
       </c>
       <c r="B1081" t="n">
-        <v>0.068075</v>
+        <v>0.06805799999999999</v>
       </c>
       <c r="C1081" t="n">
         <v>0.288945</v>
@@ -14480,7 +14480,7 @@
         </is>
       </c>
       <c r="B1082" t="n">
-        <v>0.06813900000000001</v>
+        <v>0.068243</v>
       </c>
       <c r="C1082" t="n">
         <v>0.286432</v>
@@ -14493,7 +14493,7 @@
         </is>
       </c>
       <c r="B1083" t="n">
-        <v>0.06908400000000001</v>
+        <v>0.06907199999999999</v>
       </c>
       <c r="C1083" t="n">
         <v>0.28392</v>
@@ -14506,7 +14506,7 @@
         </is>
       </c>
       <c r="B1084" t="n">
-        <v>0.069108</v>
+        <v>0.069077</v>
       </c>
       <c r="C1084" t="n">
         <v>0.281407</v>
@@ -14519,7 +14519,7 @@
         </is>
       </c>
       <c r="B1085" t="n">
-        <v>0.069746</v>
+        <v>0.069725</v>
       </c>
       <c r="C1085" t="n">
         <v>0.278894</v>
@@ -14532,7 +14532,7 @@
         </is>
       </c>
       <c r="B1086" t="n">
-        <v>0.069815</v>
+        <v>0.069784</v>
       </c>
       <c r="C1086" t="n">
         <v>0.276382</v>
@@ -14545,7 +14545,7 @@
         </is>
       </c>
       <c r="B1087" t="n">
-        <v>0.07054000000000001</v>
+        <v>0.07052799999999999</v>
       </c>
       <c r="C1087" t="n">
         <v>0.273869</v>
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="B1088" t="n">
-        <v>0.07066799999999999</v>
+        <v>0.070724</v>
       </c>
       <c r="C1088" t="n">
         <v>0.271357</v>
@@ -14571,7 +14571,7 @@
         </is>
       </c>
       <c r="B1089" t="n">
-        <v>0.070802</v>
+        <v>0.070817</v>
       </c>
       <c r="C1089" t="n">
         <v>0.268844</v>
@@ -14584,7 +14584,7 @@
         </is>
       </c>
       <c r="B1090" t="n">
-        <v>0.07158399999999999</v>
+        <v>0.071599</v>
       </c>
       <c r="C1090" t="n">
         <v>0.266332</v>
@@ -14597,7 +14597,7 @@
         </is>
       </c>
       <c r="B1091" t="n">
-        <v>0.072376</v>
+        <v>0.072423</v>
       </c>
       <c r="C1091" t="n">
         <v>0.263819</v>
@@ -14610,7 +14610,7 @@
         </is>
       </c>
       <c r="B1092" t="n">
-        <v>0.073569</v>
+        <v>0.07353800000000001</v>
       </c>
       <c r="C1092" t="n">
         <v>0.261307</v>
@@ -14623,7 +14623,7 @@
         </is>
       </c>
       <c r="B1093" t="n">
-        <v>0.07359300000000001</v>
+        <v>0.073576</v>
       </c>
       <c r="C1093" t="n">
         <v>0.258794</v>
@@ -14636,7 +14636,7 @@
         </is>
       </c>
       <c r="B1094" t="n">
-        <v>0.074138</v>
+        <v>0.074118</v>
       </c>
       <c r="C1094" t="n">
         <v>0.256281</v>
@@ -14649,7 +14649,7 @@
         </is>
       </c>
       <c r="B1095" t="n">
-        <v>0.07457999999999999</v>
+        <v>0.074573</v>
       </c>
       <c r="C1095" t="n">
         <v>0.253769</v>
@@ -14662,7 +14662,7 @@
         </is>
       </c>
       <c r="B1096" t="n">
-        <v>0.075101</v>
+        <v>0.07506400000000001</v>
       </c>
       <c r="C1096" t="n">
         <v>0.251256</v>
@@ -14688,7 +14688,7 @@
         </is>
       </c>
       <c r="B1098" t="n">
-        <v>0.075763</v>
+        <v>0.07592400000000001</v>
       </c>
       <c r="C1098" t="n">
         <v>0.246231</v>
@@ -14701,7 +14701,7 @@
         </is>
       </c>
       <c r="B1099" t="n">
-        <v>0.076531</v>
+        <v>0.07649599999999999</v>
       </c>
       <c r="C1099" t="n">
         <v>0.243719</v>
@@ -14714,7 +14714,7 @@
         </is>
       </c>
       <c r="B1100" t="n">
-        <v>0.077457</v>
+        <v>0.077594</v>
       </c>
       <c r="C1100" t="n">
         <v>0.241206</v>
@@ -14727,7 +14727,7 @@
         </is>
       </c>
       <c r="B1101" t="n">
-        <v>0.07746</v>
+        <v>0.077654</v>
       </c>
       <c r="C1101" t="n">
         <v>0.238693</v>
@@ -14740,7 +14740,7 @@
         </is>
       </c>
       <c r="B1102" t="n">
-        <v>0.07760300000000001</v>
+        <v>0.07766199999999999</v>
       </c>
       <c r="C1102" t="n">
         <v>0.236181</v>
@@ -14753,7 +14753,7 @@
         </is>
       </c>
       <c r="B1103" t="n">
-        <v>0.07811700000000001</v>
+        <v>0.07810300000000001</v>
       </c>
       <c r="C1103" t="n">
         <v>0.233668</v>
@@ -14766,7 +14766,7 @@
         </is>
       </c>
       <c r="B1104" t="n">
-        <v>0.078134</v>
+        <v>0.078151</v>
       </c>
       <c r="C1104" t="n">
         <v>0.231156</v>
@@ -14779,7 +14779,7 @@
         </is>
       </c>
       <c r="B1105" t="n">
-        <v>0.07989300000000001</v>
+        <v>0.08002099999999999</v>
       </c>
       <c r="C1105" t="n">
         <v>0.228643</v>
@@ -14792,7 +14792,7 @@
         </is>
       </c>
       <c r="B1106" t="n">
-        <v>0.07997899999999999</v>
+        <v>0.08014400000000001</v>
       </c>
       <c r="C1106" t="n">
         <v>0.226131</v>
@@ -14805,7 +14805,7 @@
         </is>
       </c>
       <c r="B1107" t="n">
-        <v>0.08039</v>
+        <v>0.080398</v>
       </c>
       <c r="C1107" t="n">
         <v>0.223618</v>
@@ -14818,7 +14818,7 @@
         </is>
       </c>
       <c r="B1108" t="n">
-        <v>0.080775</v>
+        <v>0.080749</v>
       </c>
       <c r="C1108" t="n">
         <v>0.221106</v>
@@ -14831,7 +14831,7 @@
         </is>
       </c>
       <c r="B1109" t="n">
-        <v>0.082063</v>
+        <v>0.082025</v>
       </c>
       <c r="C1109" t="n">
         <v>0.218593</v>
@@ -14844,7 +14844,7 @@
         </is>
       </c>
       <c r="B1110" t="n">
-        <v>0.082291</v>
+        <v>0.082273</v>
       </c>
       <c r="C1110" t="n">
         <v>0.21608</v>
@@ -14857,7 +14857,7 @@
         </is>
       </c>
       <c r="B1111" t="n">
-        <v>0.08297</v>
+        <v>0.082951</v>
       </c>
       <c r="C1111" t="n">
         <v>0.213568</v>
@@ -14870,7 +14870,7 @@
         </is>
       </c>
       <c r="B1112" t="n">
-        <v>0.083064</v>
+        <v>0.083061</v>
       </c>
       <c r="C1112" t="n">
         <v>0.211055</v>
@@ -14883,7 +14883,7 @@
         </is>
       </c>
       <c r="B1113" t="n">
-        <v>0.085035</v>
+        <v>0.084996</v>
       </c>
       <c r="C1113" t="n">
         <v>0.208543</v>
@@ -14896,7 +14896,7 @@
         </is>
       </c>
       <c r="B1114" t="n">
-        <v>0.086065</v>
+        <v>0.086077</v>
       </c>
       <c r="C1114" t="n">
         <v>0.20603</v>
@@ -14909,7 +14909,7 @@
         </is>
       </c>
       <c r="B1115" t="n">
-        <v>0.086211</v>
+        <v>0.08623400000000001</v>
       </c>
       <c r="C1115" t="n">
         <v>0.203518</v>
@@ -14922,7 +14922,7 @@
         </is>
       </c>
       <c r="B1116" t="n">
-        <v>0.086393</v>
+        <v>0.086349</v>
       </c>
       <c r="C1116" t="n">
         <v>0.201005</v>
@@ -14935,7 +14935,7 @@
         </is>
       </c>
       <c r="B1117" t="n">
-        <v>0.08738600000000001</v>
+        <v>0.087544</v>
       </c>
       <c r="C1117" t="n">
         <v>0.198492</v>
@@ -14948,7 +14948,7 @@
         </is>
       </c>
       <c r="B1118" t="n">
-        <v>0.08819299999999999</v>
+        <v>0.088565</v>
       </c>
       <c r="C1118" t="n">
         <v>0.19598</v>
@@ -14961,7 +14961,7 @@
         </is>
       </c>
       <c r="B1119" t="n">
-        <v>0.08916</v>
+        <v>0.089116</v>
       </c>
       <c r="C1119" t="n">
         <v>0.193467</v>
@@ -14974,7 +14974,7 @@
         </is>
       </c>
       <c r="B1120" t="n">
-        <v>0.08949</v>
+        <v>0.089449</v>
       </c>
       <c r="C1120" t="n">
         <v>0.190955</v>
@@ -14987,7 +14987,7 @@
         </is>
       </c>
       <c r="B1121" t="n">
-        <v>0.089544</v>
+        <v>0.08960700000000001</v>
       </c>
       <c r="C1121" t="n">
         <v>0.188442</v>
@@ -15000,7 +15000,7 @@
         </is>
       </c>
       <c r="B1122" t="n">
-        <v>0.090266</v>
+        <v>0.09021999999999999</v>
       </c>
       <c r="C1122" t="n">
         <v>0.18593</v>
@@ -15013,7 +15013,7 @@
         </is>
       </c>
       <c r="B1123" t="n">
-        <v>0.090874</v>
+        <v>0.09096799999999999</v>
       </c>
       <c r="C1123" t="n">
         <v>0.183417</v>
@@ -15026,7 +15026,7 @@
         </is>
       </c>
       <c r="B1124" t="n">
-        <v>0.091375</v>
+        <v>0.091393</v>
       </c>
       <c r="C1124" t="n">
         <v>0.180905</v>
@@ -15039,7 +15039,7 @@
         </is>
       </c>
       <c r="B1125" t="n">
-        <v>0.091615</v>
+        <v>0.091586</v>
       </c>
       <c r="C1125" t="n">
         <v>0.178392</v>
@@ -15052,7 +15052,7 @@
         </is>
       </c>
       <c r="B1126" t="n">
-        <v>0.09282</v>
+        <v>0.092929</v>
       </c>
       <c r="C1126" t="n">
         <v>0.175879</v>
@@ -15065,7 +15065,7 @@
         </is>
       </c>
       <c r="B1127" t="n">
-        <v>0.093264</v>
+        <v>0.093223</v>
       </c>
       <c r="C1127" t="n">
         <v>0.173367</v>
@@ -15078,7 +15078,7 @@
         </is>
       </c>
       <c r="B1128" t="n">
-        <v>0.093834</v>
+        <v>0.093844</v>
       </c>
       <c r="C1128" t="n">
         <v>0.170854</v>
@@ -15091,7 +15091,7 @@
         </is>
       </c>
       <c r="B1129" t="n">
-        <v>0.093885</v>
+        <v>0.093858</v>
       </c>
       <c r="C1129" t="n">
         <v>0.168342</v>
@@ -15104,7 +15104,7 @@
         </is>
       </c>
       <c r="B1130" t="n">
-        <v>0.09493699999999999</v>
+        <v>0.095012</v>
       </c>
       <c r="C1130" t="n">
         <v>0.165829</v>
@@ -15117,7 +15117,7 @@
         </is>
       </c>
       <c r="B1131" t="n">
-        <v>0.095624</v>
+        <v>0.095581</v>
       </c>
       <c r="C1131" t="n">
         <v>0.163317</v>
@@ -15130,7 +15130,7 @@
         </is>
       </c>
       <c r="B1132" t="n">
-        <v>0.095667</v>
+        <v>0.095679</v>
       </c>
       <c r="C1132" t="n">
         <v>0.160804</v>
@@ -15143,7 +15143,7 @@
         </is>
       </c>
       <c r="B1133" t="n">
-        <v>0.097093</v>
+        <v>0.09704699999999999</v>
       </c>
       <c r="C1133" t="n">
         <v>0.158291</v>
@@ -15156,7 +15156,7 @@
         </is>
       </c>
       <c r="B1134" t="n">
-        <v>0.102086</v>
+        <v>0.102079</v>
       </c>
       <c r="C1134" t="n">
         <v>0.155779</v>
@@ -15169,7 +15169,7 @@
         </is>
       </c>
       <c r="B1135" t="n">
-        <v>0.102345</v>
+        <v>0.1023</v>
       </c>
       <c r="C1135" t="n">
         <v>0.153266</v>
@@ -15182,7 +15182,7 @@
         </is>
       </c>
       <c r="B1136" t="n">
-        <v>0.10235</v>
+        <v>0.102339</v>
       </c>
       <c r="C1136" t="n">
         <v>0.150754</v>
@@ -15195,7 +15195,7 @@
         </is>
       </c>
       <c r="B1137" t="n">
-        <v>0.102393</v>
+        <v>0.102355</v>
       </c>
       <c r="C1137" t="n">
         <v>0.148241</v>
@@ -15208,7 +15208,7 @@
         </is>
       </c>
       <c r="B1138" t="n">
-        <v>0.102663</v>
+        <v>0.102632</v>
       </c>
       <c r="C1138" t="n">
         <v>0.145729</v>
@@ -15221,7 +15221,7 @@
         </is>
       </c>
       <c r="B1139" t="n">
-        <v>0.103309</v>
+        <v>0.103333</v>
       </c>
       <c r="C1139" t="n">
         <v>0.143216</v>
@@ -15234,7 +15234,7 @@
         </is>
       </c>
       <c r="B1140" t="n">
-        <v>0.104752</v>
+        <v>0.104713</v>
       </c>
       <c r="C1140" t="n">
         <v>0.140704</v>
@@ -15247,7 +15247,7 @@
         </is>
       </c>
       <c r="B1141" t="n">
-        <v>0.106492</v>
+        <v>0.10644</v>
       </c>
       <c r="C1141" t="n">
         <v>0.138191</v>
@@ -15260,7 +15260,7 @@
         </is>
       </c>
       <c r="B1142" t="n">
-        <v>0.108436</v>
+        <v>0.108481</v>
       </c>
       <c r="C1142" t="n">
         <v>0.135678</v>
@@ -15273,7 +15273,7 @@
         </is>
       </c>
       <c r="B1143" t="n">
-        <v>0.111263</v>
+        <v>0.111542</v>
       </c>
       <c r="C1143" t="n">
         <v>0.133166</v>
@@ -15286,7 +15286,7 @@
         </is>
       </c>
       <c r="B1144" t="n">
-        <v>0.11176</v>
+        <v>0.111782</v>
       </c>
       <c r="C1144" t="n">
         <v>0.130653</v>
@@ -15299,7 +15299,7 @@
         </is>
       </c>
       <c r="B1145" t="n">
-        <v>0.111792</v>
+        <v>0.111834</v>
       </c>
       <c r="C1145" t="n">
         <v>0.128141</v>
@@ -15312,7 +15312,7 @@
         </is>
       </c>
       <c r="B1146" t="n">
-        <v>0.113083</v>
+        <v>0.113164</v>
       </c>
       <c r="C1146" t="n">
         <v>0.125628</v>
@@ -15325,7 +15325,7 @@
         </is>
       </c>
       <c r="B1147" t="n">
-        <v>0.113543</v>
+        <v>0.113494</v>
       </c>
       <c r="C1147" t="n">
         <v>0.123116</v>
@@ -15338,7 +15338,7 @@
         </is>
       </c>
       <c r="B1148" t="n">
-        <v>0.115124</v>
+        <v>0.115175</v>
       </c>
       <c r="C1148" t="n">
         <v>0.120603</v>
@@ -15351,7 +15351,7 @@
         </is>
       </c>
       <c r="B1149" t="n">
-        <v>0.11544</v>
+        <v>0.11546</v>
       </c>
       <c r="C1149" t="n">
         <v>0.11809</v>
@@ -15364,7 +15364,7 @@
         </is>
       </c>
       <c r="B1150" t="n">
-        <v>0.117862</v>
+        <v>0.117877</v>
       </c>
       <c r="C1150" t="n">
         <v>0.115578</v>
@@ -15377,7 +15377,7 @@
         </is>
       </c>
       <c r="B1151" t="n">
-        <v>0.118402</v>
+        <v>0.11872</v>
       </c>
       <c r="C1151" t="n">
         <v>0.113065</v>
@@ -15390,7 +15390,7 @@
         </is>
       </c>
       <c r="B1152" t="n">
-        <v>0.119114</v>
+        <v>0.11937</v>
       </c>
       <c r="C1152" t="n">
         <v>0.110553</v>
@@ -15403,7 +15403,7 @@
         </is>
       </c>
       <c r="B1153" t="n">
-        <v>0.122042</v>
+        <v>0.121998</v>
       </c>
       <c r="C1153" t="n">
         <v>0.10804</v>
@@ -15416,7 +15416,7 @@
         </is>
       </c>
       <c r="B1154" t="n">
-        <v>0.122502</v>
+        <v>0.122514</v>
       </c>
       <c r="C1154" t="n">
         <v>0.105528</v>
@@ -15429,7 +15429,7 @@
         </is>
       </c>
       <c r="B1155" t="n">
-        <v>0.12274</v>
+        <v>0.122698</v>
       </c>
       <c r="C1155" t="n">
         <v>0.103015</v>
@@ -15442,7 +15442,7 @@
         </is>
       </c>
       <c r="B1156" t="n">
-        <v>0.124311</v>
+        <v>0.124287</v>
       </c>
       <c r="C1156" t="n">
         <v>0.100503</v>
@@ -15455,7 +15455,7 @@
         </is>
       </c>
       <c r="B1157" t="n">
-        <v>0.127363</v>
+        <v>0.127311</v>
       </c>
       <c r="C1157" t="n">
         <v>0.09798999999999999</v>
@@ -15468,7 +15468,7 @@
         </is>
       </c>
       <c r="B1158" t="n">
-        <v>0.127365</v>
+        <v>0.12733</v>
       </c>
       <c r="C1158" t="n">
         <v>0.09547700000000001</v>
@@ -15481,7 +15481,7 @@
         </is>
       </c>
       <c r="B1159" t="n">
-        <v>0.127891</v>
+        <v>0.12789</v>
       </c>
       <c r="C1159" t="n">
         <v>0.09296500000000001</v>
@@ -15494,7 +15494,7 @@
         </is>
       </c>
       <c r="B1160" t="n">
-        <v>0.128231</v>
+        <v>0.128436</v>
       </c>
       <c r="C1160" t="n">
         <v>0.090452</v>
@@ -15507,7 +15507,7 @@
         </is>
       </c>
       <c r="B1161" t="n">
-        <v>0.130147</v>
+        <v>0.130116</v>
       </c>
       <c r="C1161" t="n">
         <v>0.08794</v>
@@ -15520,7 +15520,7 @@
         </is>
       </c>
       <c r="B1162" t="n">
-        <v>0.131941</v>
+        <v>0.131915</v>
       </c>
       <c r="C1162" t="n">
         <v>0.085427</v>
@@ -15533,7 +15533,7 @@
         </is>
       </c>
       <c r="B1163" t="n">
-        <v>0.133084</v>
+        <v>0.133101</v>
       </c>
       <c r="C1163" t="n">
         <v>0.082915</v>
@@ -15546,7 +15546,7 @@
         </is>
       </c>
       <c r="B1164" t="n">
-        <v>0.133438</v>
+        <v>0.133403</v>
       </c>
       <c r="C1164" t="n">
         <v>0.080402</v>
@@ -15559,7 +15559,7 @@
         </is>
       </c>
       <c r="B1165" t="n">
-        <v>0.134119</v>
+        <v>0.13406</v>
       </c>
       <c r="C1165" t="n">
         <v>0.077889</v>
@@ -15572,7 +15572,7 @@
         </is>
       </c>
       <c r="B1166" t="n">
-        <v>0.135646</v>
+        <v>0.135595</v>
       </c>
       <c r="C1166" t="n">
         <v>0.075377</v>
@@ -15585,7 +15585,7 @@
         </is>
       </c>
       <c r="B1167" t="n">
-        <v>0.143441</v>
+        <v>0.143433</v>
       </c>
       <c r="C1167" t="n">
         <v>0.072864</v>
@@ -15598,7 +15598,7 @@
         </is>
       </c>
       <c r="B1168" t="n">
-        <v>0.145986</v>
+        <v>0.146011</v>
       </c>
       <c r="C1168" t="n">
         <v>0.070352</v>
@@ -15611,7 +15611,7 @@
         </is>
       </c>
       <c r="B1169" t="n">
-        <v>0.149483</v>
+        <v>0.149586</v>
       </c>
       <c r="C1169" t="n">
         <v>0.067839</v>
@@ -15624,7 +15624,7 @@
         </is>
       </c>
       <c r="B1170" t="n">
-        <v>0.149846</v>
+        <v>0.149772</v>
       </c>
       <c r="C1170" t="n">
         <v>0.065327</v>
@@ -15637,7 +15637,7 @@
         </is>
       </c>
       <c r="B1171" t="n">
-        <v>0.15067</v>
+        <v>0.150653</v>
       </c>
       <c r="C1171" t="n">
         <v>0.06281399999999999</v>
@@ -15650,7 +15650,7 @@
         </is>
       </c>
       <c r="B1172" t="n">
-        <v>0.15952</v>
+        <v>0.159461</v>
       </c>
       <c r="C1172" t="n">
         <v>0.060302</v>
@@ -15663,7 +15663,7 @@
         </is>
       </c>
       <c r="B1173" t="n">
-        <v>0.16422</v>
+        <v>0.164137</v>
       </c>
       <c r="C1173" t="n">
         <v>0.057789</v>
@@ -15676,7 +15676,7 @@
         </is>
       </c>
       <c r="B1174" t="n">
-        <v>0.168769</v>
+        <v>0.169036</v>
       </c>
       <c r="C1174" t="n">
         <v>0.055276</v>
@@ -15689,7 +15689,7 @@
         </is>
       </c>
       <c r="B1175" t="n">
-        <v>0.168972</v>
+        <v>0.169182</v>
       </c>
       <c r="C1175" t="n">
         <v>0.052764</v>
@@ -15702,7 +15702,7 @@
         </is>
       </c>
       <c r="B1176" t="n">
-        <v>0.169632</v>
+        <v>0.169552</v>
       </c>
       <c r="C1176" t="n">
         <v>0.050251</v>
@@ -15715,7 +15715,7 @@
         </is>
       </c>
       <c r="B1177" t="n">
-        <v>0.170641</v>
+        <v>0.170561</v>
       </c>
       <c r="C1177" t="n">
         <v>0.047739</v>
@@ -15728,7 +15728,7 @@
         </is>
       </c>
       <c r="B1178" t="n">
-        <v>0.174196</v>
+        <v>0.174125</v>
       </c>
       <c r="C1178" t="n">
         <v>0.045226</v>
@@ -15741,7 +15741,7 @@
         </is>
       </c>
       <c r="B1179" t="n">
-        <v>0.174754</v>
+        <v>0.174766</v>
       </c>
       <c r="C1179" t="n">
         <v>0.042714</v>
@@ -15754,7 +15754,7 @@
         </is>
       </c>
       <c r="B1180" t="n">
-        <v>0.176252</v>
+        <v>0.176395</v>
       </c>
       <c r="C1180" t="n">
         <v>0.040201</v>
@@ -15767,7 +15767,7 @@
         </is>
       </c>
       <c r="B1181" t="n">
-        <v>0.177436</v>
+        <v>0.177655</v>
       </c>
       <c r="C1181" t="n">
         <v>0.037688</v>
@@ -15780,7 +15780,7 @@
         </is>
       </c>
       <c r="B1182" t="n">
-        <v>0.184487</v>
+        <v>0.184467</v>
       </c>
       <c r="C1182" t="n">
         <v>0.035176</v>
@@ -15793,7 +15793,7 @@
         </is>
       </c>
       <c r="B1183" t="n">
-        <v>0.187296</v>
+        <v>0.187649</v>
       </c>
       <c r="C1183" t="n">
         <v>0.032663</v>
@@ -15806,7 +15806,7 @@
         </is>
       </c>
       <c r="B1184" t="n">
-        <v>0.194302</v>
+        <v>0.194276</v>
       </c>
       <c r="C1184" t="n">
         <v>0.030151</v>
@@ -15819,7 +15819,7 @@
         </is>
       </c>
       <c r="B1185" t="n">
-        <v>0.206777</v>
+        <v>0.20674</v>
       </c>
       <c r="C1185" t="n">
         <v>0.027638</v>
@@ -15832,7 +15832,7 @@
         </is>
       </c>
       <c r="B1186" t="n">
-        <v>0.22903</v>
+        <v>0.22896</v>
       </c>
       <c r="C1186" t="n">
         <v>0.025126</v>
@@ -15845,7 +15845,7 @@
         </is>
       </c>
       <c r="B1187" t="n">
-        <v>0.23257</v>
+        <v>0.232819</v>
       </c>
       <c r="C1187" t="n">
         <v>0.022613</v>
@@ -15858,7 +15858,7 @@
         </is>
       </c>
       <c r="B1188" t="n">
-        <v>0.243218</v>
+        <v>0.24334</v>
       </c>
       <c r="C1188" t="n">
         <v>0.020101</v>
@@ -15871,7 +15871,7 @@
         </is>
       </c>
       <c r="B1189" t="n">
-        <v>0.246299</v>
+        <v>0.246428</v>
       </c>
       <c r="C1189" t="n">
         <v>0.017588</v>
@@ -15884,7 +15884,7 @@
         </is>
       </c>
       <c r="B1190" t="n">
-        <v>0.248852</v>
+        <v>0.249309</v>
       </c>
       <c r="C1190" t="n">
         <v>0.015075</v>
@@ -15897,7 +15897,7 @@
         </is>
       </c>
       <c r="B1191" t="n">
-        <v>0.256341</v>
+        <v>0.256229</v>
       </c>
       <c r="C1191" t="n">
         <v>0.012563</v>
@@ -15910,7 +15910,7 @@
         </is>
       </c>
       <c r="B1192" t="n">
-        <v>0.308663</v>
+        <v>0.3087</v>
       </c>
       <c r="C1192" t="n">
         <v>0.01005</v>
@@ -15923,7 +15923,7 @@
         </is>
       </c>
       <c r="B1193" t="n">
-        <v>0.325103</v>
+        <v>0.324942</v>
       </c>
       <c r="C1193" t="n">
         <v>0.007538</v>
@@ -15936,7 +15936,7 @@
         </is>
       </c>
       <c r="B1194" t="n">
-        <v>0.335817</v>
+        <v>0.335732</v>
       </c>
       <c r="C1194" t="n">
         <v>0.005025</v>
@@ -15949,7 +15949,7 @@
         </is>
       </c>
       <c r="B1195" t="n">
-        <v>0.470722</v>
+        <v>0.470503</v>
       </c>
       <c r="C1195" t="n">
         <v>0.002513</v>

--- a/vignettes/vignette-2/tail_exceedance_plot_data.xlsx
+++ b/vignettes/vignette-2/tail_exceedance_plot_data.xlsx
@@ -3404,7 +3404,7 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>0.056487</v>
+        <v>0.056702</v>
       </c>
       <c r="C230" t="n">
         <v>0.42132</v>
@@ -3417,7 +3417,7 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>0.056702</v>
+        <v>0.056785</v>
       </c>
       <c r="C231" t="n">
         <v>0.418782</v>
@@ -3430,7 +3430,7 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>0.056785</v>
+        <v>0.057942</v>
       </c>
       <c r="C232" t="n">
         <v>0.416244</v>
@@ -3443,7 +3443,7 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>0.057942</v>
+        <v>0.05854</v>
       </c>
       <c r="C233" t="n">
         <v>0.413706</v>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>0.05854</v>
+        <v>0.058745</v>
       </c>
       <c r="C234" t="n">
         <v>0.411168</v>
@@ -3469,7 +3469,7 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>0.058745</v>
+        <v>0.058836</v>
       </c>
       <c r="C235" t="n">
         <v>0.408629</v>
@@ -3482,7 +3482,7 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>0.058836</v>
+        <v>0.059279</v>
       </c>
       <c r="C236" t="n">
         <v>0.406091</v>
@@ -3495,7 +3495,7 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>0.059279</v>
+        <v>0.059367</v>
       </c>
       <c r="C237" t="n">
         <v>0.403553</v>
@@ -3508,7 +3508,7 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>0.059367</v>
+        <v>0.059553</v>
       </c>
       <c r="C238" t="n">
         <v>0.401015</v>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>0.059553</v>
+        <v>0.059579</v>
       </c>
       <c r="C239" t="n">
         <v>0.398477</v>
@@ -3534,7 +3534,7 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>0.059579</v>
+        <v>0.060111</v>
       </c>
       <c r="C240" t="n">
         <v>0.395939</v>
@@ -3547,7 +3547,7 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>0.060111</v>
+        <v>0.060827</v>
       </c>
       <c r="C241" t="n">
         <v>0.393401</v>
@@ -3560,7 +3560,7 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>0.060827</v>
+        <v>0.060882</v>
       </c>
       <c r="C242" t="n">
         <v>0.390863</v>
@@ -3573,7 +3573,7 @@
         </is>
       </c>
       <c r="B243" t="n">
-        <v>0.060882</v>
+        <v>0.061437</v>
       </c>
       <c r="C243" t="n">
         <v>0.388325</v>
@@ -3586,7 +3586,7 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>0.061437</v>
+        <v>0.061712</v>
       </c>
       <c r="C244" t="n">
         <v>0.385787</v>
@@ -3599,7 +3599,7 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>0.061712</v>
+        <v>0.061784</v>
       </c>
       <c r="C245" t="n">
         <v>0.383249</v>
@@ -3612,7 +3612,7 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>0.061784</v>
+        <v>0.06179</v>
       </c>
       <c r="C246" t="n">
         <v>0.380711</v>
@@ -3625,7 +3625,7 @@
         </is>
       </c>
       <c r="B247" t="n">
-        <v>0.06179</v>
+        <v>0.061969</v>
       </c>
       <c r="C247" t="n">
         <v>0.378173</v>
@@ -3638,7 +3638,7 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>0.061969</v>
+        <v>0.062129</v>
       </c>
       <c r="C248" t="n">
         <v>0.375635</v>
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="B249" t="n">
-        <v>0.062129</v>
+        <v>0.062168</v>
       </c>
       <c r="C249" t="n">
         <v>0.373096</v>
@@ -3664,7 +3664,7 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>0.062168</v>
+        <v>0.06263299999999999</v>
       </c>
       <c r="C250" t="n">
         <v>0.370558</v>
@@ -3677,7 +3677,7 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>0.06263299999999999</v>
+        <v>0.062844</v>
       </c>
       <c r="C251" t="n">
         <v>0.36802</v>
@@ -3690,7 +3690,7 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>0.062844</v>
+        <v>0.063808</v>
       </c>
       <c r="C252" t="n">
         <v>0.365482</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>0.063808</v>
+        <v>0.064842</v>
       </c>
       <c r="C253" t="n">
         <v>0.362944</v>
@@ -3716,7 +3716,7 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>0.064842</v>
+        <v>0.06555900000000001</v>
       </c>
       <c r="C254" t="n">
         <v>0.360406</v>
@@ -3729,7 +3729,7 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>0.06555900000000001</v>
+        <v>0.067176</v>
       </c>
       <c r="C255" t="n">
         <v>0.357868</v>
@@ -3742,7 +3742,7 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>0.067176</v>
+        <v>0.06736399999999999</v>
       </c>
       <c r="C256" t="n">
         <v>0.35533</v>
@@ -3755,7 +3755,7 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>0.06736399999999999</v>
+        <v>0.067375</v>
       </c>
       <c r="C257" t="n">
         <v>0.352792</v>
@@ -3768,7 +3768,7 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>0.067375</v>
+        <v>0.067555</v>
       </c>
       <c r="C258" t="n">
         <v>0.350254</v>
@@ -3781,7 +3781,7 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>0.067555</v>
+        <v>0.067604</v>
       </c>
       <c r="C259" t="n">
         <v>0.347716</v>
@@ -3794,7 +3794,7 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>0.067604</v>
+        <v>0.067644</v>
       </c>
       <c r="C260" t="n">
         <v>0.345178</v>
@@ -3807,7 +3807,7 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>0.067644</v>
+        <v>0.068111</v>
       </c>
       <c r="C261" t="n">
         <v>0.34264</v>
@@ -3820,7 +3820,7 @@
         </is>
       </c>
       <c r="B262" t="n">
-        <v>0.068111</v>
+        <v>0.068538</v>
       </c>
       <c r="C262" t="n">
         <v>0.340102</v>
@@ -3833,7 +3833,7 @@
         </is>
       </c>
       <c r="B263" t="n">
-        <v>0.068538</v>
+        <v>0.068601</v>
       </c>
       <c r="C263" t="n">
         <v>0.337563</v>
@@ -3846,7 +3846,7 @@
         </is>
       </c>
       <c r="B264" t="n">
-        <v>0.068601</v>
+        <v>0.068845</v>
       </c>
       <c r="C264" t="n">
         <v>0.335025</v>
@@ -3859,7 +3859,7 @@
         </is>
       </c>
       <c r="B265" t="n">
-        <v>0.068845</v>
+        <v>0.068939</v>
       </c>
       <c r="C265" t="n">
         <v>0.332487</v>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="B266" t="n">
-        <v>0.068939</v>
+        <v>0.06909</v>
       </c>
       <c r="C266" t="n">
         <v>0.329949</v>
@@ -3885,7 +3885,7 @@
         </is>
       </c>
       <c r="B267" t="n">
-        <v>0.06909</v>
+        <v>0.069253</v>
       </c>
       <c r="C267" t="n">
         <v>0.327411</v>
@@ -3898,7 +3898,7 @@
         </is>
       </c>
       <c r="B268" t="n">
-        <v>0.069253</v>
+        <v>0.070214</v>
       </c>
       <c r="C268" t="n">
         <v>0.324873</v>
@@ -3911,7 +3911,7 @@
         </is>
       </c>
       <c r="B269" t="n">
-        <v>0.070214</v>
+        <v>0.070659</v>
       </c>
       <c r="C269" t="n">
         <v>0.322335</v>
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="B270" t="n">
-        <v>0.070659</v>
+        <v>0.071449</v>
       </c>
       <c r="C270" t="n">
         <v>0.319797</v>
@@ -5627,7 +5627,7 @@
         </is>
       </c>
       <c r="B401" t="n">
-        <v>0.001658</v>
+        <v>0.001659</v>
       </c>
       <c r="C401" t="n">
         <v>0.98731</v>
@@ -5653,7 +5653,7 @@
         </is>
       </c>
       <c r="B403" t="n">
-        <v>0.001997</v>
+        <v>0.001998</v>
       </c>
       <c r="C403" t="n">
         <v>0.9822340000000001</v>
@@ -5679,7 +5679,7 @@
         </is>
       </c>
       <c r="B405" t="n">
-        <v>0.00227</v>
+        <v>0.002273</v>
       </c>
       <c r="C405" t="n">
         <v>0.9771570000000001</v>
@@ -5692,7 +5692,7 @@
         </is>
       </c>
       <c r="B406" t="n">
-        <v>0.002335</v>
+        <v>0.002336</v>
       </c>
       <c r="C406" t="n">
         <v>0.974619</v>
@@ -5744,7 +5744,7 @@
         </is>
       </c>
       <c r="B410" t="n">
-        <v>0.003011</v>
+        <v>0.003013</v>
       </c>
       <c r="C410" t="n">
         <v>0.964467</v>
@@ -5770,7 +5770,7 @@
         </is>
       </c>
       <c r="B412" t="n">
-        <v>0.003504</v>
+        <v>0.003508</v>
       </c>
       <c r="C412" t="n">
         <v>0.959391</v>
@@ -5822,7 +5822,7 @@
         </is>
       </c>
       <c r="B416" t="n">
-        <v>0.004407</v>
+        <v>0.004408</v>
       </c>
       <c r="C416" t="n">
         <v>0.9492390000000001</v>
@@ -5848,7 +5848,7 @@
         </is>
       </c>
       <c r="B418" t="n">
-        <v>0.004553</v>
+        <v>0.004554</v>
       </c>
       <c r="C418" t="n">
         <v>0.9441619999999999</v>
@@ -5861,7 +5861,7 @@
         </is>
       </c>
       <c r="B419" t="n">
-        <v>0.004678</v>
+        <v>0.004679</v>
       </c>
       <c r="C419" t="n">
         <v>0.941624</v>
@@ -5887,7 +5887,7 @@
         </is>
       </c>
       <c r="B421" t="n">
-        <v>0.005048</v>
+        <v>0.005056</v>
       </c>
       <c r="C421" t="n">
         <v>0.936548</v>
@@ -5900,7 +5900,7 @@
         </is>
       </c>
       <c r="B422" t="n">
-        <v>0.005068</v>
+        <v>0.005072</v>
       </c>
       <c r="C422" t="n">
         <v>0.93401</v>
@@ -5913,7 +5913,7 @@
         </is>
       </c>
       <c r="B423" t="n">
-        <v>0.005201</v>
+        <v>0.005202</v>
       </c>
       <c r="C423" t="n">
         <v>0.931472</v>
@@ -5926,7 +5926,7 @@
         </is>
       </c>
       <c r="B424" t="n">
-        <v>0.005368</v>
+        <v>0.005371</v>
       </c>
       <c r="C424" t="n">
         <v>0.928934</v>
@@ -5939,7 +5939,7 @@
         </is>
       </c>
       <c r="B425" t="n">
-        <v>0.005413</v>
+        <v>0.005422</v>
       </c>
       <c r="C425" t="n">
         <v>0.926396</v>
@@ -5952,7 +5952,7 @@
         </is>
       </c>
       <c r="B426" t="n">
-        <v>0.005889</v>
+        <v>0.005891</v>
       </c>
       <c r="C426" t="n">
         <v>0.923858</v>
@@ -5965,7 +5965,7 @@
         </is>
       </c>
       <c r="B427" t="n">
-        <v>0.006147</v>
+        <v>0.006149</v>
       </c>
       <c r="C427" t="n">
         <v>0.92132</v>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="B428" t="n">
-        <v>0.006633</v>
+        <v>0.006634</v>
       </c>
       <c r="C428" t="n">
         <v>0.918782</v>
@@ -5991,7 +5991,7 @@
         </is>
       </c>
       <c r="B429" t="n">
-        <v>0.007458</v>
+        <v>0.00746</v>
       </c>
       <c r="C429" t="n">
         <v>0.9162439999999999</v>
@@ -6030,7 +6030,7 @@
         </is>
       </c>
       <c r="B432" t="n">
-        <v>0.007906</v>
+        <v>0.007913999999999999</v>
       </c>
       <c r="C432" t="n">
         <v>0.908629</v>
@@ -6043,7 +6043,7 @@
         </is>
       </c>
       <c r="B433" t="n">
-        <v>0.008007999999999999</v>
+        <v>0.00801</v>
       </c>
       <c r="C433" t="n">
         <v>0.906091</v>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="B435" t="n">
-        <v>0.008201</v>
+        <v>0.008203</v>
       </c>
       <c r="C435" t="n">
         <v>0.901015</v>
@@ -6082,7 +6082,7 @@
         </is>
       </c>
       <c r="B436" t="n">
-        <v>0.008324</v>
+        <v>0.008336</v>
       </c>
       <c r="C436" t="n">
         <v>0.898477</v>
@@ -6095,7 +6095,7 @@
         </is>
       </c>
       <c r="B437" t="n">
-        <v>0.008463</v>
+        <v>0.008465</v>
       </c>
       <c r="C437" t="n">
         <v>0.895939</v>
@@ -6121,7 +6121,7 @@
         </is>
       </c>
       <c r="B439" t="n">
-        <v>0.008812</v>
+        <v>0.008817999999999999</v>
       </c>
       <c r="C439" t="n">
         <v>0.890863</v>
@@ -6134,7 +6134,7 @@
         </is>
       </c>
       <c r="B440" t="n">
-        <v>0.009029000000000001</v>
+        <v>0.009042</v>
       </c>
       <c r="C440" t="n">
         <v>0.888325</v>
@@ -6147,7 +6147,7 @@
         </is>
       </c>
       <c r="B441" t="n">
-        <v>0.009472</v>
+        <v>0.009473000000000001</v>
       </c>
       <c r="C441" t="n">
         <v>0.885787</v>
@@ -6160,7 +6160,7 @@
         </is>
       </c>
       <c r="B442" t="n">
-        <v>0.009769999999999999</v>
+        <v>0.009776999999999999</v>
       </c>
       <c r="C442" t="n">
         <v>0.883249</v>
@@ -6173,7 +6173,7 @@
         </is>
       </c>
       <c r="B443" t="n">
-        <v>0.009778</v>
+        <v>0.009782000000000001</v>
       </c>
       <c r="C443" t="n">
         <v>0.880711</v>
@@ -6199,7 +6199,7 @@
         </is>
       </c>
       <c r="B445" t="n">
-        <v>0.010004</v>
+        <v>0.010005</v>
       </c>
       <c r="C445" t="n">
         <v>0.8756350000000001</v>
@@ -6212,7 +6212,7 @@
         </is>
       </c>
       <c r="B446" t="n">
-        <v>0.01007</v>
+        <v>0.010072</v>
       </c>
       <c r="C446" t="n">
         <v>0.873096</v>
@@ -6225,7 +6225,7 @@
         </is>
       </c>
       <c r="B447" t="n">
-        <v>0.010247</v>
+        <v>0.010261</v>
       </c>
       <c r="C447" t="n">
         <v>0.8705580000000001</v>
@@ -6238,7 +6238,7 @@
         </is>
       </c>
       <c r="B448" t="n">
-        <v>0.010301</v>
+        <v>0.010302</v>
       </c>
       <c r="C448" t="n">
         <v>0.86802</v>
@@ -6277,7 +6277,7 @@
         </is>
       </c>
       <c r="B451" t="n">
-        <v>0.011022</v>
+        <v>0.011024</v>
       </c>
       <c r="C451" t="n">
         <v>0.860406</v>
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="B453" t="n">
-        <v>0.011203</v>
+        <v>0.011205</v>
       </c>
       <c r="C453" t="n">
         <v>0.85533</v>
@@ -6316,7 +6316,7 @@
         </is>
       </c>
       <c r="B454" t="n">
-        <v>0.011271</v>
+        <v>0.011272</v>
       </c>
       <c r="C454" t="n">
         <v>0.852792</v>
@@ -6329,7 +6329,7 @@
         </is>
       </c>
       <c r="B455" t="n">
-        <v>0.011576</v>
+        <v>0.011577</v>
       </c>
       <c r="C455" t="n">
         <v>0.850254</v>
@@ -6342,7 +6342,7 @@
         </is>
       </c>
       <c r="B456" t="n">
-        <v>0.011673</v>
+        <v>0.011675</v>
       </c>
       <c r="C456" t="n">
         <v>0.847716</v>
@@ -6368,7 +6368,7 @@
         </is>
       </c>
       <c r="B458" t="n">
-        <v>0.012186</v>
+        <v>0.012192</v>
       </c>
       <c r="C458" t="n">
         <v>0.8426399999999999</v>
@@ -6381,7 +6381,7 @@
         </is>
       </c>
       <c r="B459" t="n">
-        <v>0.012305</v>
+        <v>0.012309</v>
       </c>
       <c r="C459" t="n">
         <v>0.840102</v>
@@ -6394,7 +6394,7 @@
         </is>
       </c>
       <c r="B460" t="n">
-        <v>0.012645</v>
+        <v>0.012647</v>
       </c>
       <c r="C460" t="n">
         <v>0.8375629999999999</v>
@@ -6420,7 +6420,7 @@
         </is>
       </c>
       <c r="B462" t="n">
-        <v>0.012757</v>
+        <v>0.012756</v>
       </c>
       <c r="C462" t="n">
         <v>0.832487</v>
@@ -6433,7 +6433,7 @@
         </is>
       </c>
       <c r="B463" t="n">
-        <v>0.012835</v>
+        <v>0.012839</v>
       </c>
       <c r="C463" t="n">
         <v>0.829949</v>
@@ -6446,7 +6446,7 @@
         </is>
       </c>
       <c r="B464" t="n">
-        <v>0.012912</v>
+        <v>0.012918</v>
       </c>
       <c r="C464" t="n">
         <v>0.827411</v>
@@ -6459,7 +6459,7 @@
         </is>
       </c>
       <c r="B465" t="n">
-        <v>0.013093</v>
+        <v>0.013101</v>
       </c>
       <c r="C465" t="n">
         <v>0.824873</v>
@@ -6511,7 +6511,7 @@
         </is>
       </c>
       <c r="B469" t="n">
-        <v>0.0135</v>
+        <v>0.013523</v>
       </c>
       <c r="C469" t="n">
         <v>0.814721</v>
@@ -6524,7 +6524,7 @@
         </is>
       </c>
       <c r="B470" t="n">
-        <v>0.013873</v>
+        <v>0.013874</v>
       </c>
       <c r="C470" t="n">
         <v>0.812183</v>
@@ -6550,7 +6550,7 @@
         </is>
       </c>
       <c r="B472" t="n">
-        <v>0.014671</v>
+        <v>0.014672</v>
       </c>
       <c r="C472" t="n">
         <v>0.807107</v>
@@ -6589,7 +6589,7 @@
         </is>
       </c>
       <c r="B475" t="n">
-        <v>0.014934</v>
+        <v>0.014941</v>
       </c>
       <c r="C475" t="n">
         <v>0.799492</v>
@@ -6602,7 +6602,7 @@
         </is>
       </c>
       <c r="B476" t="n">
-        <v>0.015136</v>
+        <v>0.015137</v>
       </c>
       <c r="C476" t="n">
         <v>0.7969540000000001</v>
@@ -6628,7 +6628,7 @@
         </is>
       </c>
       <c r="B478" t="n">
-        <v>0.015402</v>
+        <v>0.01542</v>
       </c>
       <c r="C478" t="n">
         <v>0.791878</v>
@@ -6641,7 +6641,7 @@
         </is>
       </c>
       <c r="B479" t="n">
-        <v>0.01578</v>
+        <v>0.015781</v>
       </c>
       <c r="C479" t="n">
         <v>0.78934</v>
@@ -6654,7 +6654,7 @@
         </is>
       </c>
       <c r="B480" t="n">
-        <v>0.015839</v>
+        <v>0.01584</v>
       </c>
       <c r="C480" t="n">
         <v>0.786802</v>
@@ -6667,7 +6667,7 @@
         </is>
       </c>
       <c r="B481" t="n">
-        <v>0.015937</v>
+        <v>0.015946</v>
       </c>
       <c r="C481" t="n">
         <v>0.784264</v>
@@ -6680,7 +6680,7 @@
         </is>
       </c>
       <c r="B482" t="n">
-        <v>0.016174</v>
+        <v>0.016184</v>
       </c>
       <c r="C482" t="n">
         <v>0.781726</v>
@@ -6693,7 +6693,7 @@
         </is>
       </c>
       <c r="B483" t="n">
-        <v>0.016541</v>
+        <v>0.01654</v>
       </c>
       <c r="C483" t="n">
         <v>0.779188</v>
@@ -6706,7 +6706,7 @@
         </is>
       </c>
       <c r="B484" t="n">
-        <v>0.016803</v>
+        <v>0.016809</v>
       </c>
       <c r="C484" t="n">
         <v>0.77665</v>
@@ -6719,7 +6719,7 @@
         </is>
       </c>
       <c r="B485" t="n">
-        <v>0.017025</v>
+        <v>0.017031</v>
       </c>
       <c r="C485" t="n">
         <v>0.774112</v>
@@ -6732,7 +6732,7 @@
         </is>
       </c>
       <c r="B486" t="n">
-        <v>0.017292</v>
+        <v>0.0173</v>
       </c>
       <c r="C486" t="n">
         <v>0.771574</v>
@@ -6745,7 +6745,7 @@
         </is>
       </c>
       <c r="B487" t="n">
-        <v>0.017323</v>
+        <v>0.017326</v>
       </c>
       <c r="C487" t="n">
         <v>0.7690360000000001</v>
@@ -6758,7 +6758,7 @@
         </is>
       </c>
       <c r="B488" t="n">
-        <v>0.017333</v>
+        <v>0.017335</v>
       </c>
       <c r="C488" t="n">
         <v>0.766497</v>
@@ -6771,7 +6771,7 @@
         </is>
       </c>
       <c r="B489" t="n">
-        <v>0.017451</v>
+        <v>0.017453</v>
       </c>
       <c r="C489" t="n">
         <v>0.7639590000000001</v>
@@ -6797,7 +6797,7 @@
         </is>
       </c>
       <c r="B491" t="n">
-        <v>0.017567</v>
+        <v>0.017571</v>
       </c>
       <c r="C491" t="n">
         <v>0.758883</v>
@@ -6810,7 +6810,7 @@
         </is>
       </c>
       <c r="B492" t="n">
-        <v>0.018023</v>
+        <v>0.01804</v>
       </c>
       <c r="C492" t="n">
         <v>0.756345</v>
@@ -6823,7 +6823,7 @@
         </is>
       </c>
       <c r="B493" t="n">
-        <v>0.018147</v>
+        <v>0.018155</v>
       </c>
       <c r="C493" t="n">
         <v>0.753807</v>
@@ -6836,7 +6836,7 @@
         </is>
       </c>
       <c r="B494" t="n">
-        <v>0.018718</v>
+        <v>0.018721</v>
       </c>
       <c r="C494" t="n">
         <v>0.751269</v>
@@ -6862,7 +6862,7 @@
         </is>
       </c>
       <c r="B496" t="n">
-        <v>0.019139</v>
+        <v>0.019142</v>
       </c>
       <c r="C496" t="n">
         <v>0.746193</v>
@@ -6875,7 +6875,7 @@
         </is>
       </c>
       <c r="B497" t="n">
-        <v>0.019158</v>
+        <v>0.019159</v>
       </c>
       <c r="C497" t="n">
         <v>0.743655</v>
@@ -6914,7 +6914,7 @@
         </is>
       </c>
       <c r="B500" t="n">
-        <v>0.02031</v>
+        <v>0.020315</v>
       </c>
       <c r="C500" t="n">
         <v>0.7360409999999999</v>
@@ -6927,7 +6927,7 @@
         </is>
       </c>
       <c r="B501" t="n">
-        <v>0.020586</v>
+        <v>0.020599</v>
       </c>
       <c r="C501" t="n">
         <v>0.733503</v>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="B503" t="n">
-        <v>0.020698</v>
+        <v>0.020743</v>
       </c>
       <c r="C503" t="n">
         <v>0.728426</v>
@@ -6979,7 +6979,7 @@
         </is>
       </c>
       <c r="B505" t="n">
-        <v>0.021202</v>
+        <v>0.021207</v>
       </c>
       <c r="C505" t="n">
         <v>0.72335</v>
@@ -6992,7 +6992,7 @@
         </is>
       </c>
       <c r="B506" t="n">
-        <v>0.021299</v>
+        <v>0.0213</v>
       </c>
       <c r="C506" t="n">
         <v>0.720812</v>
@@ -7031,7 +7031,7 @@
         </is>
       </c>
       <c r="B509" t="n">
-        <v>0.021812</v>
+        <v>0.021821</v>
       </c>
       <c r="C509" t="n">
         <v>0.713198</v>
@@ -7057,7 +7057,7 @@
         </is>
       </c>
       <c r="B511" t="n">
-        <v>0.02199</v>
+        <v>0.021992</v>
       </c>
       <c r="C511" t="n">
         <v>0.708122</v>
@@ -7070,7 +7070,7 @@
         </is>
       </c>
       <c r="B512" t="n">
-        <v>0.022159</v>
+        <v>0.02216</v>
       </c>
       <c r="C512" t="n">
         <v>0.705584</v>
@@ -7083,7 +7083,7 @@
         </is>
       </c>
       <c r="B513" t="n">
-        <v>0.022338</v>
+        <v>0.022339</v>
       </c>
       <c r="C513" t="n">
         <v>0.7030459999999999</v>
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="B514" t="n">
-        <v>0.022578</v>
+        <v>0.022579</v>
       </c>
       <c r="C514" t="n">
         <v>0.700508</v>
@@ -7109,7 +7109,7 @@
         </is>
       </c>
       <c r="B515" t="n">
-        <v>0.02305</v>
+        <v>0.023052</v>
       </c>
       <c r="C515" t="n">
         <v>0.69797</v>
@@ -7122,7 +7122,7 @@
         </is>
       </c>
       <c r="B516" t="n">
-        <v>0.02312</v>
+        <v>0.023129</v>
       </c>
       <c r="C516" t="n">
         <v>0.695431</v>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="B517" t="n">
-        <v>0.023219</v>
+        <v>0.023222</v>
       </c>
       <c r="C517" t="n">
         <v>0.692893</v>
@@ -7148,7 +7148,7 @@
         </is>
       </c>
       <c r="B518" t="n">
-        <v>0.023296</v>
+        <v>0.023306</v>
       </c>
       <c r="C518" t="n">
         <v>0.6903550000000001</v>
@@ -7161,7 +7161,7 @@
         </is>
       </c>
       <c r="B519" t="n">
-        <v>0.023493</v>
+        <v>0.023494</v>
       </c>
       <c r="C519" t="n">
         <v>0.687817</v>
@@ -7187,7 +7187,7 @@
         </is>
       </c>
       <c r="B521" t="n">
-        <v>0.023633</v>
+        <v>0.023635</v>
       </c>
       <c r="C521" t="n">
         <v>0.682741</v>
@@ -7213,7 +7213,7 @@
         </is>
       </c>
       <c r="B523" t="n">
-        <v>0.023904</v>
+        <v>0.023903</v>
       </c>
       <c r="C523" t="n">
         <v>0.677665</v>
@@ -7226,7 +7226,7 @@
         </is>
       </c>
       <c r="B524" t="n">
-        <v>0.024117</v>
+        <v>0.024133</v>
       </c>
       <c r="C524" t="n">
         <v>0.675127</v>
@@ -7239,7 +7239,7 @@
         </is>
       </c>
       <c r="B525" t="n">
-        <v>0.025525</v>
+        <v>0.025529</v>
       </c>
       <c r="C525" t="n">
         <v>0.672589</v>
@@ -7252,7 +7252,7 @@
         </is>
       </c>
       <c r="B526" t="n">
-        <v>0.02559</v>
+        <v>0.025599</v>
       </c>
       <c r="C526" t="n">
         <v>0.670051</v>
@@ -7265,7 +7265,7 @@
         </is>
       </c>
       <c r="B527" t="n">
-        <v>0.025815</v>
+        <v>0.025831</v>
       </c>
       <c r="C527" t="n">
         <v>0.667513</v>
@@ -7278,7 +7278,7 @@
         </is>
       </c>
       <c r="B528" t="n">
-        <v>0.025922</v>
+        <v>0.025921</v>
       </c>
       <c r="C528" t="n">
         <v>0.664975</v>
@@ -7304,7 +7304,7 @@
         </is>
       </c>
       <c r="B530" t="n">
-        <v>0.025984</v>
+        <v>0.025987</v>
       </c>
       <c r="C530" t="n">
         <v>0.659898</v>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="B531" t="n">
-        <v>0.026068</v>
+        <v>0.026079</v>
       </c>
       <c r="C531" t="n">
         <v>0.6573600000000001</v>
@@ -7343,7 +7343,7 @@
         </is>
       </c>
       <c r="B533" t="n">
-        <v>0.026652</v>
+        <v>0.026663</v>
       </c>
       <c r="C533" t="n">
         <v>0.652284</v>
@@ -7356,7 +7356,7 @@
         </is>
       </c>
       <c r="B534" t="n">
-        <v>0.026715</v>
+        <v>0.026716</v>
       </c>
       <c r="C534" t="n">
         <v>0.649746</v>
@@ -7369,7 +7369,7 @@
         </is>
       </c>
       <c r="B535" t="n">
-        <v>0.027067</v>
+        <v>0.027085</v>
       </c>
       <c r="C535" t="n">
         <v>0.647208</v>
@@ -7382,7 +7382,7 @@
         </is>
       </c>
       <c r="B536" t="n">
-        <v>0.027243</v>
+        <v>0.027249</v>
       </c>
       <c r="C536" t="n">
         <v>0.64467</v>
@@ -7395,7 +7395,7 @@
         </is>
       </c>
       <c r="B537" t="n">
-        <v>0.027411</v>
+        <v>0.027421</v>
       </c>
       <c r="C537" t="n">
         <v>0.642132</v>
@@ -7408,7 +7408,7 @@
         </is>
       </c>
       <c r="B538" t="n">
-        <v>0.027684</v>
+        <v>0.027685</v>
       </c>
       <c r="C538" t="n">
         <v>0.639594</v>
@@ -7421,7 +7421,7 @@
         </is>
       </c>
       <c r="B539" t="n">
-        <v>0.027765</v>
+        <v>0.027766</v>
       </c>
       <c r="C539" t="n">
         <v>0.637056</v>
@@ -7434,7 +7434,7 @@
         </is>
       </c>
       <c r="B540" t="n">
-        <v>0.027897</v>
+        <v>0.027899</v>
       </c>
       <c r="C540" t="n">
         <v>0.634518</v>
@@ -7447,7 +7447,7 @@
         </is>
       </c>
       <c r="B541" t="n">
-        <v>0.028206</v>
+        <v>0.028209</v>
       </c>
       <c r="C541" t="n">
         <v>0.63198</v>
@@ -7460,7 +7460,7 @@
         </is>
       </c>
       <c r="B542" t="n">
-        <v>0.028502</v>
+        <v>0.028506</v>
       </c>
       <c r="C542" t="n">
         <v>0.6294419999999999</v>
@@ -7473,7 +7473,7 @@
         </is>
       </c>
       <c r="B543" t="n">
-        <v>0.028641</v>
+        <v>0.028688</v>
       </c>
       <c r="C543" t="n">
         <v>0.626904</v>
@@ -7486,7 +7486,7 @@
         </is>
       </c>
       <c r="B544" t="n">
-        <v>0.028947</v>
+        <v>0.028948</v>
       </c>
       <c r="C544" t="n">
         <v>0.6243649999999999</v>
@@ -7525,7 +7525,7 @@
         </is>
       </c>
       <c r="B547" t="n">
-        <v>0.029467</v>
+        <v>0.029495</v>
       </c>
       <c r="C547" t="n">
         <v>0.616751</v>
@@ -7538,7 +7538,7 @@
         </is>
       </c>
       <c r="B548" t="n">
-        <v>0.029638</v>
+        <v>0.029639</v>
       </c>
       <c r="C548" t="n">
         <v>0.614213</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="B549" t="n">
-        <v>0.029643</v>
+        <v>0.029651</v>
       </c>
       <c r="C549" t="n">
         <v>0.611675</v>
@@ -7577,7 +7577,7 @@
         </is>
       </c>
       <c r="B551" t="n">
-        <v>0.030121</v>
+        <v>0.030137</v>
       </c>
       <c r="C551" t="n">
         <v>0.606599</v>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="B553" t="n">
-        <v>0.030186</v>
+        <v>0.030206</v>
       </c>
       <c r="C553" t="n">
         <v>0.601523</v>
@@ -7616,7 +7616,7 @@
         </is>
       </c>
       <c r="B554" t="n">
-        <v>0.030204</v>
+        <v>0.030207</v>
       </c>
       <c r="C554" t="n">
         <v>0.598985</v>
@@ -7629,7 +7629,7 @@
         </is>
       </c>
       <c r="B555" t="n">
-        <v>0.030346</v>
+        <v>0.030345</v>
       </c>
       <c r="C555" t="n">
         <v>0.5964469999999999</v>
@@ -7642,7 +7642,7 @@
         </is>
       </c>
       <c r="B556" t="n">
-        <v>0.030714</v>
+        <v>0.030726</v>
       </c>
       <c r="C556" t="n">
         <v>0.593909</v>
@@ -7668,7 +7668,7 @@
         </is>
       </c>
       <c r="B558" t="n">
-        <v>0.031344</v>
+        <v>0.031349</v>
       </c>
       <c r="C558" t="n">
         <v>0.588832</v>
@@ -7681,7 +7681,7 @@
         </is>
       </c>
       <c r="B559" t="n">
-        <v>0.031728</v>
+        <v>0.031735</v>
       </c>
       <c r="C559" t="n">
         <v>0.586294</v>
@@ -7694,7 +7694,7 @@
         </is>
       </c>
       <c r="B560" t="n">
-        <v>0.031961</v>
+        <v>0.031983</v>
       </c>
       <c r="C560" t="n">
         <v>0.5837560000000001</v>
@@ -7707,7 +7707,7 @@
         </is>
       </c>
       <c r="B561" t="n">
-        <v>0.032085</v>
+        <v>0.032087</v>
       </c>
       <c r="C561" t="n">
         <v>0.581218</v>
@@ -7720,7 +7720,7 @@
         </is>
       </c>
       <c r="B562" t="n">
-        <v>0.03217</v>
+        <v>0.032175</v>
       </c>
       <c r="C562" t="n">
         <v>0.57868</v>
@@ -7733,7 +7733,7 @@
         </is>
       </c>
       <c r="B563" t="n">
-        <v>0.032242</v>
+        <v>0.032266</v>
       </c>
       <c r="C563" t="n">
         <v>0.576142</v>
@@ -7746,7 +7746,7 @@
         </is>
       </c>
       <c r="B564" t="n">
-        <v>0.032506</v>
+        <v>0.032536</v>
       </c>
       <c r="C564" t="n">
         <v>0.573604</v>
@@ -7772,7 +7772,7 @@
         </is>
       </c>
       <c r="B566" t="n">
-        <v>0.032984</v>
+        <v>0.033001</v>
       </c>
       <c r="C566" t="n">
         <v>0.568528</v>
@@ -7785,7 +7785,7 @@
         </is>
       </c>
       <c r="B567" t="n">
-        <v>0.033098</v>
+        <v>0.033122</v>
       </c>
       <c r="C567" t="n">
         <v>0.56599</v>
@@ -7811,7 +7811,7 @@
         </is>
       </c>
       <c r="B569" t="n">
-        <v>0.033265</v>
+        <v>0.033268</v>
       </c>
       <c r="C569" t="n">
         <v>0.560914</v>
@@ -7837,7 +7837,7 @@
         </is>
       </c>
       <c r="B571" t="n">
-        <v>0.034469</v>
+        <v>0.034472</v>
       </c>
       <c r="C571" t="n">
         <v>0.5558380000000001</v>
@@ -7850,7 +7850,7 @@
         </is>
       </c>
       <c r="B572" t="n">
-        <v>0.034513</v>
+        <v>0.034521</v>
       </c>
       <c r="C572" t="n">
         <v>0.553299</v>
@@ -7863,7 +7863,7 @@
         </is>
       </c>
       <c r="B573" t="n">
-        <v>0.034687</v>
+        <v>0.034688</v>
       </c>
       <c r="C573" t="n">
         <v>0.5507609999999999</v>
@@ -7876,7 +7876,7 @@
         </is>
       </c>
       <c r="B574" t="n">
-        <v>0.035224</v>
+        <v>0.035225</v>
       </c>
       <c r="C574" t="n">
         <v>0.548223</v>
@@ -7902,7 +7902,7 @@
         </is>
       </c>
       <c r="B576" t="n">
-        <v>0.035462</v>
+        <v>0.035465</v>
       </c>
       <c r="C576" t="n">
         <v>0.543147</v>
@@ -7915,7 +7915,7 @@
         </is>
       </c>
       <c r="B577" t="n">
-        <v>0.035667</v>
+        <v>0.035668</v>
       </c>
       <c r="C577" t="n">
         <v>0.540609</v>
@@ -7928,7 +7928,7 @@
         </is>
       </c>
       <c r="B578" t="n">
-        <v>0.03569</v>
+        <v>0.035711</v>
       </c>
       <c r="C578" t="n">
         <v>0.538071</v>
@@ -7941,7 +7941,7 @@
         </is>
       </c>
       <c r="B579" t="n">
-        <v>0.035936</v>
+        <v>0.035951</v>
       </c>
       <c r="C579" t="n">
         <v>0.535533</v>
@@ -7954,7 +7954,7 @@
         </is>
       </c>
       <c r="B580" t="n">
-        <v>0.036313</v>
+        <v>0.036312</v>
       </c>
       <c r="C580" t="n">
         <v>0.532995</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="B581" t="n">
-        <v>0.036482</v>
+        <v>0.036485</v>
       </c>
       <c r="C581" t="n">
         <v>0.530457</v>
@@ -7980,7 +7980,7 @@
         </is>
       </c>
       <c r="B582" t="n">
-        <v>0.036651</v>
+        <v>0.03666</v>
       </c>
       <c r="C582" t="n">
         <v>0.527919</v>
@@ -7993,7 +7993,7 @@
         </is>
       </c>
       <c r="B583" t="n">
-        <v>0.036706</v>
+        <v>0.036721</v>
       </c>
       <c r="C583" t="n">
         <v>0.525381</v>
@@ -8006,7 +8006,7 @@
         </is>
       </c>
       <c r="B584" t="n">
-        <v>0.036765</v>
+        <v>0.036777</v>
       </c>
       <c r="C584" t="n">
         <v>0.5228429999999999</v>
@@ -8019,7 +8019,7 @@
         </is>
       </c>
       <c r="B585" t="n">
-        <v>0.038157</v>
+        <v>0.038159</v>
       </c>
       <c r="C585" t="n">
         <v>0.520305</v>
@@ -8032,7 +8032,7 @@
         </is>
       </c>
       <c r="B586" t="n">
-        <v>0.038282</v>
+        <v>0.038304</v>
       </c>
       <c r="C586" t="n">
         <v>0.5177659999999999</v>
@@ -8045,7 +8045,7 @@
         </is>
       </c>
       <c r="B587" t="n">
-        <v>0.038479</v>
+        <v>0.038482</v>
       </c>
       <c r="C587" t="n">
         <v>0.515228</v>
@@ -8071,7 +8071,7 @@
         </is>
       </c>
       <c r="B589" t="n">
-        <v>0.038871</v>
+        <v>0.038872</v>
       </c>
       <c r="C589" t="n">
         <v>0.510152</v>
@@ -8084,7 +8084,7 @@
         </is>
       </c>
       <c r="B590" t="n">
-        <v>0.038947</v>
+        <v>0.038949</v>
       </c>
       <c r="C590" t="n">
         <v>0.507614</v>
@@ -8097,7 +8097,7 @@
         </is>
       </c>
       <c r="B591" t="n">
-        <v>0.039113</v>
+        <v>0.039117</v>
       </c>
       <c r="C591" t="n">
         <v>0.505076</v>
@@ -8110,7 +8110,7 @@
         </is>
       </c>
       <c r="B592" t="n">
-        <v>0.039481</v>
+        <v>0.039503</v>
       </c>
       <c r="C592" t="n">
         <v>0.502538</v>
@@ -8123,7 +8123,7 @@
         </is>
       </c>
       <c r="B593" t="n">
-        <v>0.039499</v>
+        <v>0.039504</v>
       </c>
       <c r="C593" t="n">
         <v>0.5</v>
@@ -8149,7 +8149,7 @@
         </is>
       </c>
       <c r="B595" t="n">
-        <v>0.03986</v>
+        <v>0.039866</v>
       </c>
       <c r="C595" t="n">
         <v>0.494924</v>
@@ -8162,7 +8162,7 @@
         </is>
       </c>
       <c r="B596" t="n">
-        <v>0.040032</v>
+        <v>0.040054</v>
       </c>
       <c r="C596" t="n">
         <v>0.492386</v>
@@ -8175,7 +8175,7 @@
         </is>
       </c>
       <c r="B597" t="n">
-        <v>0.040032</v>
+        <v>0.0402</v>
       </c>
       <c r="C597" t="n">
         <v>0.489848</v>
@@ -8188,7 +8188,7 @@
         </is>
       </c>
       <c r="B598" t="n">
-        <v>0.040171</v>
+        <v>0.040391</v>
       </c>
       <c r="C598" t="n">
         <v>0.48731</v>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="B599" t="n">
-        <v>0.04037</v>
+        <v>0.040546</v>
       </c>
       <c r="C599" t="n">
         <v>0.484772</v>
@@ -8214,7 +8214,7 @@
         </is>
       </c>
       <c r="B600" t="n">
-        <v>0.040523</v>
+        <v>0.040574</v>
       </c>
       <c r="C600" t="n">
         <v>0.482234</v>
@@ -8227,7 +8227,7 @@
         </is>
       </c>
       <c r="B601" t="n">
-        <v>0.040566</v>
+        <v>0.040724</v>
       </c>
       <c r="C601" t="n">
         <v>0.479695</v>
@@ -8240,7 +8240,7 @@
         </is>
       </c>
       <c r="B602" t="n">
-        <v>0.040692</v>
+        <v>0.040813</v>
       </c>
       <c r="C602" t="n">
         <v>0.477157</v>
@@ -8253,7 +8253,7 @@
         </is>
       </c>
       <c r="B603" t="n">
-        <v>0.040808</v>
+        <v>0.040894</v>
       </c>
       <c r="C603" t="n">
         <v>0.474619</v>
@@ -8266,7 +8266,7 @@
         </is>
       </c>
       <c r="B604" t="n">
-        <v>0.040878</v>
+        <v>0.041301</v>
       </c>
       <c r="C604" t="n">
         <v>0.472081</v>
@@ -8279,7 +8279,7 @@
         </is>
       </c>
       <c r="B605" t="n">
-        <v>0.041294</v>
+        <v>0.041786</v>
       </c>
       <c r="C605" t="n">
         <v>0.469543</v>
@@ -8292,7 +8292,7 @@
         </is>
       </c>
       <c r="B606" t="n">
-        <v>0.041781</v>
+        <v>0.041976</v>
       </c>
       <c r="C606" t="n">
         <v>0.467005</v>
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="B607" t="n">
-        <v>0.041931</v>
+        <v>0.04217</v>
       </c>
       <c r="C607" t="n">
         <v>0.464467</v>
@@ -8318,7 +8318,7 @@
         </is>
       </c>
       <c r="B608" t="n">
-        <v>0.042157</v>
+        <v>0.042316</v>
       </c>
       <c r="C608" t="n">
         <v>0.461929</v>
@@ -8331,7 +8331,7 @@
         </is>
       </c>
       <c r="B609" t="n">
-        <v>0.042276</v>
+        <v>0.042488</v>
       </c>
       <c r="C609" t="n">
         <v>0.459391</v>
@@ -8344,7 +8344,7 @@
         </is>
       </c>
       <c r="B610" t="n">
-        <v>0.042486</v>
+        <v>0.042618</v>
       </c>
       <c r="C610" t="n">
         <v>0.456853</v>
@@ -8357,7 +8357,7 @@
         </is>
       </c>
       <c r="B611" t="n">
-        <v>0.042606</v>
+        <v>0.043463</v>
       </c>
       <c r="C611" t="n">
         <v>0.454315</v>
@@ -8370,7 +8370,7 @@
         </is>
       </c>
       <c r="B612" t="n">
-        <v>0.043457</v>
+        <v>0.043838</v>
       </c>
       <c r="C612" t="n">
         <v>0.451777</v>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="B613" t="n">
-        <v>0.043819</v>
+        <v>0.043858</v>
       </c>
       <c r="C613" t="n">
         <v>0.449239</v>
@@ -8396,7 +8396,7 @@
         </is>
       </c>
       <c r="B614" t="n">
-        <v>0.043856</v>
+        <v>0.044544</v>
       </c>
       <c r="C614" t="n">
         <v>0.446701</v>
@@ -8409,7 +8409,7 @@
         </is>
       </c>
       <c r="B615" t="n">
-        <v>0.044538</v>
+        <v>0.044569</v>
       </c>
       <c r="C615" t="n">
         <v>0.444162</v>
@@ -8422,7 +8422,7 @@
         </is>
       </c>
       <c r="B616" t="n">
-        <v>0.044566</v>
+        <v>0.044799</v>
       </c>
       <c r="C616" t="n">
         <v>0.441624</v>
@@ -8435,7 +8435,7 @@
         </is>
       </c>
       <c r="B617" t="n">
-        <v>0.044797</v>
+        <v>0.045129</v>
       </c>
       <c r="C617" t="n">
         <v>0.439086</v>
@@ -8448,7 +8448,7 @@
         </is>
       </c>
       <c r="B618" t="n">
-        <v>0.045101</v>
+        <v>0.045383</v>
       </c>
       <c r="C618" t="n">
         <v>0.436548</v>
@@ -8461,7 +8461,7 @@
         </is>
       </c>
       <c r="B619" t="n">
-        <v>0.04538</v>
+        <v>0.04568</v>
       </c>
       <c r="C619" t="n">
         <v>0.43401</v>
@@ -8474,7 +8474,7 @@
         </is>
       </c>
       <c r="B620" t="n">
-        <v>0.045662</v>
+        <v>0.045815</v>
       </c>
       <c r="C620" t="n">
         <v>0.431472</v>
@@ -8487,7 +8487,7 @@
         </is>
       </c>
       <c r="B621" t="n">
-        <v>0.045813</v>
+        <v>0.046961</v>
       </c>
       <c r="C621" t="n">
         <v>0.428934</v>
@@ -8500,7 +8500,7 @@
         </is>
       </c>
       <c r="B622" t="n">
-        <v>0.046962</v>
+        <v>0.047055</v>
       </c>
       <c r="C622" t="n">
         <v>0.426396</v>
@@ -8513,7 +8513,7 @@
         </is>
       </c>
       <c r="B623" t="n">
-        <v>0.047055</v>
+        <v>0.0472</v>
       </c>
       <c r="C623" t="n">
         <v>0.423858</v>
@@ -8526,7 +8526,7 @@
         </is>
       </c>
       <c r="B624" t="n">
-        <v>0.047199</v>
+        <v>0.047362</v>
       </c>
       <c r="C624" t="n">
         <v>0.42132</v>
@@ -8539,7 +8539,7 @@
         </is>
       </c>
       <c r="B625" t="n">
-        <v>0.047324</v>
+        <v>0.047392</v>
       </c>
       <c r="C625" t="n">
         <v>0.418782</v>
@@ -8552,7 +8552,7 @@
         </is>
       </c>
       <c r="B626" t="n">
-        <v>0.047388</v>
+        <v>0.048047</v>
       </c>
       <c r="C626" t="n">
         <v>0.416244</v>
@@ -8565,7 +8565,7 @@
         </is>
       </c>
       <c r="B627" t="n">
-        <v>0.04804</v>
+        <v>0.04816</v>
       </c>
       <c r="C627" t="n">
         <v>0.413706</v>
@@ -8578,7 +8578,7 @@
         </is>
       </c>
       <c r="B628" t="n">
-        <v>0.04816</v>
+        <v>0.048188</v>
       </c>
       <c r="C628" t="n">
         <v>0.411168</v>
@@ -8591,7 +8591,7 @@
         </is>
       </c>
       <c r="B629" t="n">
-        <v>0.048185</v>
+        <v>0.048499</v>
       </c>
       <c r="C629" t="n">
         <v>0.408629</v>
@@ -8604,7 +8604,7 @@
         </is>
       </c>
       <c r="B630" t="n">
-        <v>0.048498</v>
+        <v>0.048531</v>
       </c>
       <c r="C630" t="n">
         <v>0.406091</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="B631" t="n">
-        <v>0.04853</v>
+        <v>0.048677</v>
       </c>
       <c r="C631" t="n">
         <v>0.403553</v>
@@ -8630,7 +8630,7 @@
         </is>
       </c>
       <c r="B632" t="n">
-        <v>0.048675</v>
+        <v>0.048793</v>
       </c>
       <c r="C632" t="n">
         <v>0.401015</v>
@@ -8643,7 +8643,7 @@
         </is>
       </c>
       <c r="B633" t="n">
-        <v>0.048776</v>
+        <v>0.048829</v>
       </c>
       <c r="C633" t="n">
         <v>0.398477</v>
@@ -8656,7 +8656,7 @@
         </is>
       </c>
       <c r="B634" t="n">
-        <v>0.048805</v>
+        <v>0.048863</v>
       </c>
       <c r="C634" t="n">
         <v>0.395939</v>
@@ -8669,7 +8669,7 @@
         </is>
       </c>
       <c r="B635" t="n">
-        <v>0.048858</v>
+        <v>0.049443</v>
       </c>
       <c r="C635" t="n">
         <v>0.393401</v>
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="B636" t="n">
-        <v>0.049425</v>
+        <v>0.049646</v>
       </c>
       <c r="C636" t="n">
         <v>0.390863</v>
@@ -8695,7 +8695,7 @@
         </is>
       </c>
       <c r="B637" t="n">
-        <v>0.049632</v>
+        <v>0.049676</v>
       </c>
       <c r="C637" t="n">
         <v>0.388325</v>
@@ -8708,7 +8708,7 @@
         </is>
       </c>
       <c r="B638" t="n">
-        <v>0.049676</v>
+        <v>0.050142</v>
       </c>
       <c r="C638" t="n">
         <v>0.385787</v>
@@ -8721,7 +8721,7 @@
         </is>
       </c>
       <c r="B639" t="n">
-        <v>0.050137</v>
+        <v>0.050345</v>
       </c>
       <c r="C639" t="n">
         <v>0.383249</v>
@@ -8734,7 +8734,7 @@
         </is>
       </c>
       <c r="B640" t="n">
-        <v>0.050343</v>
+        <v>0.050962</v>
       </c>
       <c r="C640" t="n">
         <v>0.380711</v>
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="B641" t="n">
-        <v>0.050938</v>
+        <v>0.051195</v>
       </c>
       <c r="C641" t="n">
         <v>0.378173</v>
@@ -8760,7 +8760,7 @@
         </is>
       </c>
       <c r="B642" t="n">
-        <v>0.051196</v>
+        <v>0.051244</v>
       </c>
       <c r="C642" t="n">
         <v>0.375635</v>
@@ -8773,7 +8773,7 @@
         </is>
       </c>
       <c r="B643" t="n">
-        <v>0.051226</v>
+        <v>0.051278</v>
       </c>
       <c r="C643" t="n">
         <v>0.373096</v>
@@ -8786,7 +8786,7 @@
         </is>
       </c>
       <c r="B644" t="n">
-        <v>0.051279</v>
+        <v>0.051762</v>
       </c>
       <c r="C644" t="n">
         <v>0.370558</v>
@@ -8799,7 +8799,7 @@
         </is>
       </c>
       <c r="B645" t="n">
-        <v>0.051756</v>
+        <v>0.052705</v>
       </c>
       <c r="C645" t="n">
         <v>0.36802</v>
@@ -8812,7 +8812,7 @@
         </is>
       </c>
       <c r="B646" t="n">
-        <v>0.052695</v>
+        <v>0.053305</v>
       </c>
       <c r="C646" t="n">
         <v>0.365482</v>
@@ -8825,7 +8825,7 @@
         </is>
       </c>
       <c r="B647" t="n">
-        <v>0.053302</v>
+        <v>0.053324</v>
       </c>
       <c r="C647" t="n">
         <v>0.362944</v>
@@ -8838,7 +8838,7 @@
         </is>
       </c>
       <c r="B648" t="n">
-        <v>0.053321</v>
+        <v>0.053468</v>
       </c>
       <c r="C648" t="n">
         <v>0.360406</v>
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="B649" t="n">
-        <v>0.053465</v>
+        <v>0.053677</v>
       </c>
       <c r="C649" t="n">
         <v>0.357868</v>
@@ -8864,7 +8864,7 @@
         </is>
       </c>
       <c r="B650" t="n">
-        <v>0.053677</v>
+        <v>0.054093</v>
       </c>
       <c r="C650" t="n">
         <v>0.35533</v>
@@ -8877,7 +8877,7 @@
         </is>
       </c>
       <c r="B651" t="n">
-        <v>0.054033</v>
+        <v>0.054231</v>
       </c>
       <c r="C651" t="n">
         <v>0.352792</v>
@@ -8890,7 +8890,7 @@
         </is>
       </c>
       <c r="B652" t="n">
-        <v>0.054233</v>
+        <v>0.054237</v>
       </c>
       <c r="C652" t="n">
         <v>0.350254</v>
@@ -8903,7 +8903,7 @@
         </is>
       </c>
       <c r="B653" t="n">
-        <v>0.055209</v>
+        <v>0.05521</v>
       </c>
       <c r="C653" t="n">
         <v>0.347716</v>
@@ -8916,7 +8916,7 @@
         </is>
       </c>
       <c r="B654" t="n">
-        <v>0.055392</v>
+        <v>0.055401</v>
       </c>
       <c r="C654" t="n">
         <v>0.345178</v>
@@ -8929,7 +8929,7 @@
         </is>
       </c>
       <c r="B655" t="n">
-        <v>0.05592</v>
+        <v>0.055919</v>
       </c>
       <c r="C655" t="n">
         <v>0.34264</v>
@@ -8942,7 +8942,7 @@
         </is>
       </c>
       <c r="B656" t="n">
-        <v>0.056552</v>
+        <v>0.056557</v>
       </c>
       <c r="C656" t="n">
         <v>0.340102</v>
@@ -8955,7 +8955,7 @@
         </is>
       </c>
       <c r="B657" t="n">
-        <v>0.056623</v>
+        <v>0.05663</v>
       </c>
       <c r="C657" t="n">
         <v>0.337563</v>
@@ -8981,7 +8981,7 @@
         </is>
       </c>
       <c r="B659" t="n">
-        <v>0.057532</v>
+        <v>0.057534</v>
       </c>
       <c r="C659" t="n">
         <v>0.332487</v>
@@ -9007,7 +9007,7 @@
         </is>
       </c>
       <c r="B661" t="n">
-        <v>0.058446</v>
+        <v>0.058447</v>
       </c>
       <c r="C661" t="n">
         <v>0.327411</v>
@@ -9020,7 +9020,7 @@
         </is>
       </c>
       <c r="B662" t="n">
-        <v>0.058723</v>
+        <v>0.058722</v>
       </c>
       <c r="C662" t="n">
         <v>0.324873</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="B663" t="n">
-        <v>0.058868</v>
+        <v>0.05887</v>
       </c>
       <c r="C663" t="n">
         <v>0.322335</v>
@@ -9046,7 +9046,7 @@
         </is>
       </c>
       <c r="B664" t="n">
-        <v>0.060037</v>
+        <v>0.060043</v>
       </c>
       <c r="C664" t="n">
         <v>0.319797</v>
@@ -9059,7 +9059,7 @@
         </is>
       </c>
       <c r="B665" t="n">
-        <v>0.060651</v>
+        <v>0.060691</v>
       </c>
       <c r="C665" t="n">
         <v>0.317259</v>
@@ -9085,7 +9085,7 @@
         </is>
       </c>
       <c r="B667" t="n">
-        <v>0.061079</v>
+        <v>0.061083</v>
       </c>
       <c r="C667" t="n">
         <v>0.312183</v>
@@ -9098,7 +9098,7 @@
         </is>
       </c>
       <c r="B668" t="n">
-        <v>0.061414</v>
+        <v>0.061425</v>
       </c>
       <c r="C668" t="n">
         <v>0.309645</v>
@@ -9111,7 +9111,7 @@
         </is>
       </c>
       <c r="B669" t="n">
-        <v>0.061734</v>
+        <v>0.061739</v>
       </c>
       <c r="C669" t="n">
         <v>0.307107</v>
@@ -9124,7 +9124,7 @@
         </is>
       </c>
       <c r="B670" t="n">
-        <v>0.061762</v>
+        <v>0.061782</v>
       </c>
       <c r="C670" t="n">
         <v>0.304569</v>
@@ -9137,7 +9137,7 @@
         </is>
       </c>
       <c r="B671" t="n">
-        <v>0.061976</v>
+        <v>0.061983</v>
       </c>
       <c r="C671" t="n">
         <v>0.30203</v>
@@ -9150,7 +9150,7 @@
         </is>
       </c>
       <c r="B672" t="n">
-        <v>0.062601</v>
+        <v>0.062621</v>
       </c>
       <c r="C672" t="n">
         <v>0.299492</v>
@@ -9176,7 +9176,7 @@
         </is>
       </c>
       <c r="B674" t="n">
-        <v>0.063205</v>
+        <v>0.063204</v>
       </c>
       <c r="C674" t="n">
         <v>0.294416</v>
@@ -9189,7 +9189,7 @@
         </is>
       </c>
       <c r="B675" t="n">
-        <v>0.063261</v>
+        <v>0.063289</v>
       </c>
       <c r="C675" t="n">
         <v>0.291878</v>
@@ -9202,7 +9202,7 @@
         </is>
       </c>
       <c r="B676" t="n">
-        <v>0.06351</v>
+        <v>0.063509</v>
       </c>
       <c r="C676" t="n">
         <v>0.28934</v>
@@ -9215,7 +9215,7 @@
         </is>
       </c>
       <c r="B677" t="n">
-        <v>0.064373</v>
+        <v>0.064372</v>
       </c>
       <c r="C677" t="n">
         <v>0.286802</v>
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="B678" t="n">
-        <v>0.064441</v>
+        <v>0.064442</v>
       </c>
       <c r="C678" t="n">
         <v>0.284264</v>
@@ -9241,7 +9241,7 @@
         </is>
       </c>
       <c r="B679" t="n">
-        <v>0.064918</v>
+        <v>0.064926</v>
       </c>
       <c r="C679" t="n">
         <v>0.281726</v>
@@ -9254,7 +9254,7 @@
         </is>
       </c>
       <c r="B680" t="n">
-        <v>0.064958</v>
+        <v>0.06496300000000001</v>
       </c>
       <c r="C680" t="n">
         <v>0.279188</v>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="B681" t="n">
-        <v>0.065875</v>
+        <v>0.06587800000000001</v>
       </c>
       <c r="C681" t="n">
         <v>0.27665</v>
@@ -9280,7 +9280,7 @@
         </is>
       </c>
       <c r="B682" t="n">
-        <v>0.066374</v>
+        <v>0.066404</v>
       </c>
       <c r="C682" t="n">
         <v>0.274112</v>
@@ -9293,7 +9293,7 @@
         </is>
       </c>
       <c r="B683" t="n">
-        <v>0.066581</v>
+        <v>0.06658699999999999</v>
       </c>
       <c r="C683" t="n">
         <v>0.271574</v>
@@ -9306,7 +9306,7 @@
         </is>
       </c>
       <c r="B684" t="n">
-        <v>0.066769</v>
+        <v>0.06678099999999999</v>
       </c>
       <c r="C684" t="n">
         <v>0.269036</v>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="B685" t="n">
-        <v>0.067022</v>
+        <v>0.067021</v>
       </c>
       <c r="C685" t="n">
         <v>0.266497</v>
@@ -9332,7 +9332,7 @@
         </is>
       </c>
       <c r="B686" t="n">
-        <v>0.067264</v>
+        <v>0.06726799999999999</v>
       </c>
       <c r="C686" t="n">
         <v>0.263959</v>
@@ -9371,7 +9371,7 @@
         </is>
       </c>
       <c r="B689" t="n">
-        <v>0.069947</v>
+        <v>0.070033</v>
       </c>
       <c r="C689" t="n">
         <v>0.256345</v>
@@ -9384,7 +9384,7 @@
         </is>
       </c>
       <c r="B690" t="n">
-        <v>0.070212</v>
+        <v>0.070217</v>
       </c>
       <c r="C690" t="n">
         <v>0.253807</v>
@@ -9397,7 +9397,7 @@
         </is>
       </c>
       <c r="B691" t="n">
-        <v>0.07033499999999999</v>
+        <v>0.070345</v>
       </c>
       <c r="C691" t="n">
         <v>0.251269</v>
@@ -9410,7 +9410,7 @@
         </is>
       </c>
       <c r="B692" t="n">
-        <v>0.070754</v>
+        <v>0.07076</v>
       </c>
       <c r="C692" t="n">
         <v>0.248731</v>
@@ -9423,7 +9423,7 @@
         </is>
       </c>
       <c r="B693" t="n">
-        <v>0.071073</v>
+        <v>0.071076</v>
       </c>
       <c r="C693" t="n">
         <v>0.246193</v>
@@ -9436,7 +9436,7 @@
         </is>
       </c>
       <c r="B694" t="n">
-        <v>0.071516</v>
+        <v>0.071521</v>
       </c>
       <c r="C694" t="n">
         <v>0.243655</v>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="B695" t="n">
-        <v>0.07202600000000001</v>
+        <v>0.072051</v>
       </c>
       <c r="C695" t="n">
         <v>0.241117</v>
@@ -9462,7 +9462,7 @@
         </is>
       </c>
       <c r="B696" t="n">
-        <v>0.07278999999999999</v>
+        <v>0.072851</v>
       </c>
       <c r="C696" t="n">
         <v>0.238579</v>
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="B697" t="n">
-        <v>0.073036</v>
+        <v>0.073044</v>
       </c>
       <c r="C697" t="n">
         <v>0.236041</v>
@@ -9488,7 +9488,7 @@
         </is>
       </c>
       <c r="B698" t="n">
-        <v>0.07349899999999999</v>
+        <v>0.073532</v>
       </c>
       <c r="C698" t="n">
         <v>0.233503</v>
@@ -9514,7 +9514,7 @@
         </is>
       </c>
       <c r="B700" t="n">
-        <v>0.074494</v>
+        <v>0.074499</v>
       </c>
       <c r="C700" t="n">
         <v>0.228426</v>
@@ -9527,7 +9527,7 @@
         </is>
       </c>
       <c r="B701" t="n">
-        <v>0.07475800000000001</v>
+        <v>0.07481500000000001</v>
       </c>
       <c r="C701" t="n">
         <v>0.225888</v>
@@ -9540,7 +9540,7 @@
         </is>
       </c>
       <c r="B702" t="n">
-        <v>0.07522</v>
+        <v>0.07538400000000001</v>
       </c>
       <c r="C702" t="n">
         <v>0.22335</v>
@@ -9553,7 +9553,7 @@
         </is>
       </c>
       <c r="B703" t="n">
-        <v>0.075507</v>
+        <v>0.075512</v>
       </c>
       <c r="C703" t="n">
         <v>0.220812</v>
@@ -9566,7 +9566,7 @@
         </is>
       </c>
       <c r="B704" t="n">
-        <v>0.07553799999999999</v>
+        <v>0.07554</v>
       </c>
       <c r="C704" t="n">
         <v>0.218274</v>
@@ -9592,7 +9592,7 @@
         </is>
       </c>
       <c r="B706" t="n">
-        <v>0.07713</v>
+        <v>0.077138</v>
       </c>
       <c r="C706" t="n">
         <v>0.213198</v>
@@ -9605,7 +9605,7 @@
         </is>
       </c>
       <c r="B707" t="n">
-        <v>0.078503</v>
+        <v>0.07850799999999999</v>
       </c>
       <c r="C707" t="n">
         <v>0.21066</v>
@@ -9618,7 +9618,7 @@
         </is>
       </c>
       <c r="B708" t="n">
-        <v>0.078792</v>
+        <v>0.07882500000000001</v>
       </c>
       <c r="C708" t="n">
         <v>0.208122</v>
@@ -9631,7 +9631,7 @@
         </is>
       </c>
       <c r="B709" t="n">
-        <v>0.079126</v>
+        <v>0.079128</v>
       </c>
       <c r="C709" t="n">
         <v>0.205584</v>
@@ -9644,7 +9644,7 @@
         </is>
       </c>
       <c r="B710" t="n">
-        <v>0.079155</v>
+        <v>0.079161</v>
       </c>
       <c r="C710" t="n">
         <v>0.203046</v>
@@ -9657,7 +9657,7 @@
         </is>
       </c>
       <c r="B711" t="n">
-        <v>0.081662</v>
+        <v>0.08169800000000001</v>
       </c>
       <c r="C711" t="n">
         <v>0.200508</v>
@@ -9670,7 +9670,7 @@
         </is>
       </c>
       <c r="B712" t="n">
-        <v>0.081969</v>
+        <v>0.081968</v>
       </c>
       <c r="C712" t="n">
         <v>0.19797</v>
@@ -9683,7 +9683,7 @@
         </is>
       </c>
       <c r="B713" t="n">
-        <v>0.082567</v>
+        <v>0.08257</v>
       </c>
       <c r="C713" t="n">
         <v>0.195431</v>
@@ -9696,7 +9696,7 @@
         </is>
       </c>
       <c r="B714" t="n">
-        <v>0.082842</v>
+        <v>0.082869</v>
       </c>
       <c r="C714" t="n">
         <v>0.192893</v>
@@ -9709,7 +9709,7 @@
         </is>
       </c>
       <c r="B715" t="n">
-        <v>0.08301799999999999</v>
+        <v>0.083095</v>
       </c>
       <c r="C715" t="n">
         <v>0.190355</v>
@@ -9722,7 +9722,7 @@
         </is>
       </c>
       <c r="B716" t="n">
-        <v>0.084955</v>
+        <v>0.084954</v>
       </c>
       <c r="C716" t="n">
         <v>0.187817</v>
@@ -9735,7 +9735,7 @@
         </is>
       </c>
       <c r="B717" t="n">
-        <v>0.085524</v>
+        <v>0.08555400000000001</v>
       </c>
       <c r="C717" t="n">
         <v>0.185279</v>
@@ -9748,7 +9748,7 @@
         </is>
       </c>
       <c r="B718" t="n">
-        <v>0.085893</v>
+        <v>0.085979</v>
       </c>
       <c r="C718" t="n">
         <v>0.182741</v>
@@ -9761,7 +9761,7 @@
         </is>
       </c>
       <c r="B719" t="n">
-        <v>0.085941</v>
+        <v>0.08609899999999999</v>
       </c>
       <c r="C719" t="n">
         <v>0.180203</v>
@@ -9774,7 +9774,7 @@
         </is>
       </c>
       <c r="B720" t="n">
-        <v>0.0861</v>
+        <v>0.08613899999999999</v>
       </c>
       <c r="C720" t="n">
         <v>0.177665</v>
@@ -9787,7 +9787,7 @@
         </is>
       </c>
       <c r="B721" t="n">
-        <v>0.086534</v>
+        <v>0.08656</v>
       </c>
       <c r="C721" t="n">
         <v>0.175127</v>
@@ -9813,7 +9813,7 @@
         </is>
       </c>
       <c r="B723" t="n">
-        <v>0.088127</v>
+        <v>0.08817999999999999</v>
       </c>
       <c r="C723" t="n">
         <v>0.170051</v>
@@ -9826,7 +9826,7 @@
         </is>
       </c>
       <c r="B724" t="n">
-        <v>0.089202</v>
+        <v>0.089217</v>
       </c>
       <c r="C724" t="n">
         <v>0.167513</v>
@@ -9839,7 +9839,7 @@
         </is>
       </c>
       <c r="B725" t="n">
-        <v>0.08930399999999999</v>
+        <v>0.089305</v>
       </c>
       <c r="C725" t="n">
         <v>0.164975</v>
@@ -9852,7 +9852,7 @@
         </is>
       </c>
       <c r="B726" t="n">
-        <v>0.089619</v>
+        <v>0.089627</v>
       </c>
       <c r="C726" t="n">
         <v>0.162437</v>
@@ -9865,7 +9865,7 @@
         </is>
       </c>
       <c r="B727" t="n">
-        <v>0.08984399999999999</v>
+        <v>0.089978</v>
       </c>
       <c r="C727" t="n">
         <v>0.159898</v>
@@ -9878,7 +9878,7 @@
         </is>
       </c>
       <c r="B728" t="n">
-        <v>0.09003700000000001</v>
+        <v>0.090036</v>
       </c>
       <c r="C728" t="n">
         <v>0.15736</v>
@@ -9891,7 +9891,7 @@
         </is>
       </c>
       <c r="B729" t="n">
-        <v>0.091041</v>
+        <v>0.091042</v>
       </c>
       <c r="C729" t="n">
         <v>0.154822</v>
@@ -9904,7 +9904,7 @@
         </is>
       </c>
       <c r="B730" t="n">
-        <v>0.091463</v>
+        <v>0.091479</v>
       </c>
       <c r="C730" t="n">
         <v>0.152284</v>
@@ -9917,7 +9917,7 @@
         </is>
       </c>
       <c r="B731" t="n">
-        <v>0.09292599999999999</v>
+        <v>0.092945</v>
       </c>
       <c r="C731" t="n">
         <v>0.149746</v>
@@ -9930,7 +9930,7 @@
         </is>
       </c>
       <c r="B732" t="n">
-        <v>0.097275</v>
+        <v>0.097278</v>
       </c>
       <c r="C732" t="n">
         <v>0.147208</v>
@@ -9943,7 +9943,7 @@
         </is>
       </c>
       <c r="B733" t="n">
-        <v>0.097507</v>
+        <v>0.09751</v>
       </c>
       <c r="C733" t="n">
         <v>0.14467</v>
@@ -9956,7 +9956,7 @@
         </is>
       </c>
       <c r="B734" t="n">
-        <v>0.097826</v>
+        <v>0.09783799999999999</v>
       </c>
       <c r="C734" t="n">
         <v>0.142132</v>
@@ -9969,7 +9969,7 @@
         </is>
       </c>
       <c r="B735" t="n">
-        <v>0.097995</v>
+        <v>0.09801799999999999</v>
       </c>
       <c r="C735" t="n">
         <v>0.139594</v>
@@ -9995,7 +9995,7 @@
         </is>
       </c>
       <c r="B737" t="n">
-        <v>0.09876799999999999</v>
+        <v>0.098829</v>
       </c>
       <c r="C737" t="n">
         <v>0.134518</v>
@@ -10008,7 +10008,7 @@
         </is>
       </c>
       <c r="B738" t="n">
-        <v>0.101953</v>
+        <v>0.101976</v>
       </c>
       <c r="C738" t="n">
         <v>0.13198</v>
@@ -10021,7 +10021,7 @@
         </is>
       </c>
       <c r="B739" t="n">
-        <v>0.10302</v>
+        <v>0.103019</v>
       </c>
       <c r="C739" t="n">
         <v>0.129442</v>
@@ -10034,7 +10034,7 @@
         </is>
       </c>
       <c r="B740" t="n">
-        <v>0.104909</v>
+        <v>0.10492</v>
       </c>
       <c r="C740" t="n">
         <v>0.126904</v>
@@ -10047,7 +10047,7 @@
         </is>
       </c>
       <c r="B741" t="n">
-        <v>0.106534</v>
+        <v>0.106538</v>
       </c>
       <c r="C741" t="n">
         <v>0.124365</v>
@@ -10060,7 +10060,7 @@
         </is>
       </c>
       <c r="B742" t="n">
-        <v>0.107283</v>
+        <v>0.107282</v>
       </c>
       <c r="C742" t="n">
         <v>0.121827</v>
@@ -10073,7 +10073,7 @@
         </is>
       </c>
       <c r="B743" t="n">
-        <v>0.108572</v>
+        <v>0.10859</v>
       </c>
       <c r="C743" t="n">
         <v>0.119289</v>
@@ -10099,7 +10099,7 @@
         </is>
       </c>
       <c r="B745" t="n">
-        <v>0.111182</v>
+        <v>0.111305</v>
       </c>
       <c r="C745" t="n">
         <v>0.114213</v>
@@ -10112,7 +10112,7 @@
         </is>
       </c>
       <c r="B746" t="n">
-        <v>0.111584</v>
+        <v>0.111598</v>
       </c>
       <c r="C746" t="n">
         <v>0.111675</v>
@@ -10125,7 +10125,7 @@
         </is>
       </c>
       <c r="B747" t="n">
-        <v>0.112155</v>
+        <v>0.112156</v>
       </c>
       <c r="C747" t="n">
         <v>0.109137</v>
@@ -10138,7 +10138,7 @@
         </is>
       </c>
       <c r="B748" t="n">
-        <v>0.112425</v>
+        <v>0.112433</v>
       </c>
       <c r="C748" t="n">
         <v>0.106599</v>
@@ -10151,7 +10151,7 @@
         </is>
       </c>
       <c r="B749" t="n">
-        <v>0.116591</v>
+        <v>0.116592</v>
       </c>
       <c r="C749" t="n">
         <v>0.104061</v>
@@ -10164,7 +10164,7 @@
         </is>
       </c>
       <c r="B750" t="n">
-        <v>0.117226</v>
+        <v>0.117238</v>
       </c>
       <c r="C750" t="n">
         <v>0.101523</v>
@@ -10177,7 +10177,7 @@
         </is>
       </c>
       <c r="B751" t="n">
-        <v>0.118562</v>
+        <v>0.118569</v>
       </c>
       <c r="C751" t="n">
         <v>0.098985</v>
@@ -10190,7 +10190,7 @@
         </is>
       </c>
       <c r="B752" t="n">
-        <v>0.121243</v>
+        <v>0.121246</v>
       </c>
       <c r="C752" t="n">
         <v>0.096447</v>
@@ -10203,7 +10203,7 @@
         </is>
       </c>
       <c r="B753" t="n">
-        <v>0.121545</v>
+        <v>0.121555</v>
       </c>
       <c r="C753" t="n">
         <v>0.09390900000000001</v>
@@ -10216,7 +10216,7 @@
         </is>
       </c>
       <c r="B754" t="n">
-        <v>0.121801</v>
+        <v>0.121804</v>
       </c>
       <c r="C754" t="n">
         <v>0.09137099999999999</v>
@@ -10229,7 +10229,7 @@
         </is>
       </c>
       <c r="B755" t="n">
-        <v>0.122361</v>
+        <v>0.122419</v>
       </c>
       <c r="C755" t="n">
         <v>0.08883199999999999</v>
@@ -10242,7 +10242,7 @@
         </is>
       </c>
       <c r="B756" t="n">
-        <v>0.125265</v>
+        <v>0.125348</v>
       </c>
       <c r="C756" t="n">
         <v>0.086294</v>
@@ -10255,7 +10255,7 @@
         </is>
       </c>
       <c r="B757" t="n">
-        <v>0.125837</v>
+        <v>0.125845</v>
       </c>
       <c r="C757" t="n">
         <v>0.083756</v>
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="B758" t="n">
-        <v>0.126641</v>
+        <v>0.126642</v>
       </c>
       <c r="C758" t="n">
         <v>0.081218</v>
@@ -10281,7 +10281,7 @@
         </is>
       </c>
       <c r="B759" t="n">
-        <v>0.127341</v>
+        <v>0.127351</v>
       </c>
       <c r="C759" t="n">
         <v>0.07868</v>
@@ -10294,7 +10294,7 @@
         </is>
       </c>
       <c r="B760" t="n">
-        <v>0.128279</v>
+        <v>0.128301</v>
       </c>
       <c r="C760" t="n">
         <v>0.076142</v>
@@ -10307,7 +10307,7 @@
         </is>
       </c>
       <c r="B761" t="n">
-        <v>0.130403</v>
+        <v>0.130473</v>
       </c>
       <c r="C761" t="n">
         <v>0.073604</v>
@@ -10320,7 +10320,7 @@
         </is>
       </c>
       <c r="B762" t="n">
-        <v>0.136657</v>
+        <v>0.136662</v>
       </c>
       <c r="C762" t="n">
         <v>0.071066</v>
@@ -10333,7 +10333,7 @@
         </is>
       </c>
       <c r="B763" t="n">
-        <v>0.138886</v>
+        <v>0.138887</v>
       </c>
       <c r="C763" t="n">
         <v>0.06852800000000001</v>
@@ -10346,7 +10346,7 @@
         </is>
       </c>
       <c r="B764" t="n">
-        <v>0.141838</v>
+        <v>0.141836</v>
       </c>
       <c r="C764" t="n">
         <v>0.06598999999999999</v>
@@ -10359,7 +10359,7 @@
         </is>
       </c>
       <c r="B765" t="n">
-        <v>0.14361</v>
+        <v>0.143616</v>
       </c>
       <c r="C765" t="n">
         <v>0.06345199999999999</v>
@@ -10372,7 +10372,7 @@
         </is>
       </c>
       <c r="B766" t="n">
-        <v>0.143743</v>
+        <v>0.143794</v>
       </c>
       <c r="C766" t="n">
         <v>0.060914</v>
@@ -10385,7 +10385,7 @@
         </is>
       </c>
       <c r="B767" t="n">
-        <v>0.152406</v>
+        <v>0.152424</v>
       </c>
       <c r="C767" t="n">
         <v>0.058376</v>
@@ -10398,7 +10398,7 @@
         </is>
       </c>
       <c r="B768" t="n">
-        <v>0.157475</v>
+        <v>0.157527</v>
       </c>
       <c r="C768" t="n">
         <v>0.055838</v>
@@ -10411,7 +10411,7 @@
         </is>
       </c>
       <c r="B769" t="n">
-        <v>0.160569</v>
+        <v>0.160567</v>
       </c>
       <c r="C769" t="n">
         <v>0.053299</v>
@@ -10424,7 +10424,7 @@
         </is>
       </c>
       <c r="B770" t="n">
-        <v>0.162333</v>
+        <v>0.162366</v>
       </c>
       <c r="C770" t="n">
         <v>0.050761</v>
@@ -10437,7 +10437,7 @@
         </is>
       </c>
       <c r="B771" t="n">
-        <v>0.163296</v>
+        <v>0.163329</v>
       </c>
       <c r="C771" t="n">
         <v>0.048223</v>
@@ -10450,7 +10450,7 @@
         </is>
       </c>
       <c r="B772" t="n">
-        <v>0.163831</v>
+        <v>0.164173</v>
       </c>
       <c r="C772" t="n">
         <v>0.045685</v>
@@ -10463,7 +10463,7 @@
         </is>
       </c>
       <c r="B773" t="n">
-        <v>0.167144</v>
+        <v>0.167141</v>
       </c>
       <c r="C773" t="n">
         <v>0.043147</v>
@@ -10476,7 +10476,7 @@
         </is>
       </c>
       <c r="B774" t="n">
-        <v>0.167394</v>
+        <v>0.167478</v>
       </c>
       <c r="C774" t="n">
         <v>0.040609</v>
@@ -10502,7 +10502,7 @@
         </is>
       </c>
       <c r="B776" t="n">
-        <v>0.168508</v>
+        <v>0.168657</v>
       </c>
       <c r="C776" t="n">
         <v>0.035533</v>
@@ -10515,7 +10515,7 @@
         </is>
       </c>
       <c r="B777" t="n">
-        <v>0.176925</v>
+        <v>0.176933</v>
       </c>
       <c r="C777" t="n">
         <v>0.032995</v>
@@ -10528,7 +10528,7 @@
         </is>
       </c>
       <c r="B778" t="n">
-        <v>0.177722</v>
+        <v>0.177857</v>
       </c>
       <c r="C778" t="n">
         <v>0.030457</v>
@@ -10541,7 +10541,7 @@
         </is>
       </c>
       <c r="B779" t="n">
-        <v>0.185227</v>
+        <v>0.185235</v>
       </c>
       <c r="C779" t="n">
         <v>0.027919</v>
@@ -10554,7 +10554,7 @@
         </is>
       </c>
       <c r="B780" t="n">
-        <v>0.22032</v>
+        <v>0.220319</v>
       </c>
       <c r="C780" t="n">
         <v>0.025381</v>
@@ -10567,7 +10567,7 @@
         </is>
       </c>
       <c r="B781" t="n">
-        <v>0.220321</v>
+        <v>0.220454</v>
       </c>
       <c r="C781" t="n">
         <v>0.022843</v>
@@ -10580,7 +10580,7 @@
         </is>
       </c>
       <c r="B782" t="n">
-        <v>0.234939</v>
+        <v>0.235207</v>
       </c>
       <c r="C782" t="n">
         <v>0.020305</v>
@@ -10593,7 +10593,7 @@
         </is>
       </c>
       <c r="B783" t="n">
-        <v>0.237935</v>
+        <v>0.23821</v>
       </c>
       <c r="C783" t="n">
         <v>0.017766</v>
@@ -10606,7 +10606,7 @@
         </is>
       </c>
       <c r="B784" t="n">
-        <v>0.241259</v>
+        <v>0.241696</v>
       </c>
       <c r="C784" t="n">
         <v>0.015228</v>
@@ -10619,7 +10619,7 @@
         </is>
       </c>
       <c r="B785" t="n">
-        <v>0.246236</v>
+        <v>0.246351</v>
       </c>
       <c r="C785" t="n">
         <v>0.01269</v>
@@ -10632,7 +10632,7 @@
         </is>
       </c>
       <c r="B786" t="n">
-        <v>0.297704</v>
+        <v>0.297977</v>
       </c>
       <c r="C786" t="n">
         <v>0.010152</v>
@@ -10645,7 +10645,7 @@
         </is>
       </c>
       <c r="B787" t="n">
-        <v>0.311319</v>
+        <v>0.311394</v>
       </c>
       <c r="C787" t="n">
         <v>0.007614</v>
@@ -10658,7 +10658,7 @@
         </is>
       </c>
       <c r="B788" t="n">
-        <v>0.323199</v>
+        <v>0.32341</v>
       </c>
       <c r="C788" t="n">
         <v>0.005076</v>
@@ -10671,7 +10671,7 @@
         </is>
       </c>
       <c r="B789" t="n">
-        <v>0.451949</v>
+        <v>0.452141</v>
       </c>
       <c r="C789" t="n">
         <v>0.002538</v>
@@ -10749,7 +10749,7 @@
         </is>
       </c>
       <c r="B795" t="n">
-        <v>0.001741</v>
+        <v>0.001742</v>
       </c>
       <c r="C795" t="n">
         <v>0.98731</v>
@@ -10801,7 +10801,7 @@
         </is>
       </c>
       <c r="B799" t="n">
-        <v>0.002384</v>
+        <v>0.002386</v>
       </c>
       <c r="C799" t="n">
         <v>0.9771570000000001</v>
@@ -10814,7 +10814,7 @@
         </is>
       </c>
       <c r="B800" t="n">
-        <v>0.002451</v>
+        <v>0.002453</v>
       </c>
       <c r="C800" t="n">
         <v>0.974619</v>
@@ -10840,7 +10840,7 @@
         </is>
       </c>
       <c r="B802" t="n">
-        <v>0.002682</v>
+        <v>0.002681</v>
       </c>
       <c r="C802" t="n">
         <v>0.969543</v>
@@ -10853,7 +10853,7 @@
         </is>
       </c>
       <c r="B803" t="n">
-        <v>0.003016</v>
+        <v>0.003017</v>
       </c>
       <c r="C803" t="n">
         <v>0.967005</v>
@@ -10866,7 +10866,7 @@
         </is>
       </c>
       <c r="B804" t="n">
-        <v>0.003162</v>
+        <v>0.003164</v>
       </c>
       <c r="C804" t="n">
         <v>0.964467</v>
@@ -10892,7 +10892,7 @@
         </is>
       </c>
       <c r="B806" t="n">
-        <v>0.00368</v>
+        <v>0.003683</v>
       </c>
       <c r="C806" t="n">
         <v>0.959391</v>
@@ -10918,7 +10918,7 @@
         </is>
       </c>
       <c r="B808" t="n">
-        <v>0.004318</v>
+        <v>0.004319</v>
       </c>
       <c r="C808" t="n">
         <v>0.954315</v>
@@ -10957,7 +10957,7 @@
         </is>
       </c>
       <c r="B811" t="n">
-        <v>0.004754</v>
+        <v>0.004753</v>
       </c>
       <c r="C811" t="n">
         <v>0.946701</v>
@@ -10983,7 +10983,7 @@
         </is>
       </c>
       <c r="B813" t="n">
-        <v>0.004912</v>
+        <v>0.004913</v>
       </c>
       <c r="C813" t="n">
         <v>0.941624</v>
@@ -11009,7 +11009,7 @@
         </is>
       </c>
       <c r="B815" t="n">
-        <v>0.0053</v>
+        <v>0.005309</v>
       </c>
       <c r="C815" t="n">
         <v>0.936548</v>
@@ -11022,7 +11022,7 @@
         </is>
       </c>
       <c r="B816" t="n">
-        <v>0.005322</v>
+        <v>0.005325</v>
       </c>
       <c r="C816" t="n">
         <v>0.93401</v>
@@ -11035,7 +11035,7 @@
         </is>
       </c>
       <c r="B817" t="n">
-        <v>0.005461</v>
+        <v>0.005463</v>
       </c>
       <c r="C817" t="n">
         <v>0.931472</v>
@@ -11048,7 +11048,7 @@
         </is>
       </c>
       <c r="B818" t="n">
-        <v>0.005637</v>
+        <v>0.005639</v>
       </c>
       <c r="C818" t="n">
         <v>0.928934</v>
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="B819" t="n">
-        <v>0.005683</v>
+        <v>0.005693</v>
       </c>
       <c r="C819" t="n">
         <v>0.926396</v>
@@ -11074,7 +11074,7 @@
         </is>
       </c>
       <c r="B820" t="n">
-        <v>0.006184</v>
+        <v>0.006186</v>
       </c>
       <c r="C820" t="n">
         <v>0.923858</v>
@@ -11087,7 +11087,7 @@
         </is>
       </c>
       <c r="B821" t="n">
-        <v>0.006454</v>
+        <v>0.006456</v>
       </c>
       <c r="C821" t="n">
         <v>0.92132</v>
@@ -11113,7 +11113,7 @@
         </is>
       </c>
       <c r="B823" t="n">
-        <v>0.007830999999999999</v>
+        <v>0.007833</v>
       </c>
       <c r="C823" t="n">
         <v>0.9162439999999999</v>
@@ -11152,7 +11152,7 @@
         </is>
       </c>
       <c r="B826" t="n">
-        <v>0.008300999999999999</v>
+        <v>0.00831</v>
       </c>
       <c r="C826" t="n">
         <v>0.908629</v>
@@ -11165,7 +11165,7 @@
         </is>
       </c>
       <c r="B827" t="n">
-        <v>0.008408000000000001</v>
+        <v>0.008410000000000001</v>
       </c>
       <c r="C827" t="n">
         <v>0.906091</v>
@@ -11191,7 +11191,7 @@
         </is>
       </c>
       <c r="B829" t="n">
-        <v>0.008612</v>
+        <v>0.008613000000000001</v>
       </c>
       <c r="C829" t="n">
         <v>0.901015</v>
@@ -11204,7 +11204,7 @@
         </is>
       </c>
       <c r="B830" t="n">
-        <v>0.008741000000000001</v>
+        <v>0.008753</v>
       </c>
       <c r="C830" t="n">
         <v>0.898477</v>
@@ -11217,7 +11217,7 @@
         </is>
       </c>
       <c r="B831" t="n">
-        <v>0.008887000000000001</v>
+        <v>0.008888</v>
       </c>
       <c r="C831" t="n">
         <v>0.895939</v>
@@ -11243,7 +11243,7 @@
         </is>
       </c>
       <c r="B833" t="n">
-        <v>0.009252</v>
+        <v>0.009259</v>
       </c>
       <c r="C833" t="n">
         <v>0.890863</v>
@@ -11256,7 +11256,7 @@
         </is>
       </c>
       <c r="B834" t="n">
-        <v>0.009481</v>
+        <v>0.009494000000000001</v>
       </c>
       <c r="C834" t="n">
         <v>0.888325</v>
@@ -11282,7 +11282,7 @@
         </is>
       </c>
       <c r="B836" t="n">
-        <v>0.010258</v>
+        <v>0.010266</v>
       </c>
       <c r="C836" t="n">
         <v>0.883249</v>
@@ -11295,7 +11295,7 @@
         </is>
       </c>
       <c r="B837" t="n">
-        <v>0.010267</v>
+        <v>0.010271</v>
       </c>
       <c r="C837" t="n">
         <v>0.880711</v>
@@ -11321,7 +11321,7 @@
         </is>
       </c>
       <c r="B839" t="n">
-        <v>0.010504</v>
+        <v>0.010505</v>
       </c>
       <c r="C839" t="n">
         <v>0.8756350000000001</v>
@@ -11334,7 +11334,7 @@
         </is>
       </c>
       <c r="B840" t="n">
-        <v>0.010573</v>
+        <v>0.010576</v>
       </c>
       <c r="C840" t="n">
         <v>0.873096</v>
@@ -11347,7 +11347,7 @@
         </is>
       </c>
       <c r="B841" t="n">
-        <v>0.01076</v>
+        <v>0.010774</v>
       </c>
       <c r="C841" t="n">
         <v>0.8705580000000001</v>
@@ -11360,7 +11360,7 @@
         </is>
       </c>
       <c r="B842" t="n">
-        <v>0.010816</v>
+        <v>0.010817</v>
       </c>
       <c r="C842" t="n">
         <v>0.86802</v>
@@ -11399,7 +11399,7 @@
         </is>
       </c>
       <c r="B845" t="n">
-        <v>0.011573</v>
+        <v>0.011575</v>
       </c>
       <c r="C845" t="n">
         <v>0.860406</v>
@@ -11425,7 +11425,7 @@
         </is>
       </c>
       <c r="B847" t="n">
-        <v>0.011764</v>
+        <v>0.011765</v>
       </c>
       <c r="C847" t="n">
         <v>0.85533</v>
@@ -11438,7 +11438,7 @@
         </is>
       </c>
       <c r="B848" t="n">
-        <v>0.011835</v>
+        <v>0.011836</v>
       </c>
       <c r="C848" t="n">
         <v>0.852792</v>
@@ -11451,7 +11451,7 @@
         </is>
       </c>
       <c r="B849" t="n">
-        <v>0.012155</v>
+        <v>0.012156</v>
       </c>
       <c r="C849" t="n">
         <v>0.850254</v>
@@ -11464,7 +11464,7 @@
         </is>
       </c>
       <c r="B850" t="n">
-        <v>0.012257</v>
+        <v>0.012259</v>
       </c>
       <c r="C850" t="n">
         <v>0.847716</v>
@@ -11490,7 +11490,7 @@
         </is>
       </c>
       <c r="B852" t="n">
-        <v>0.012796</v>
+        <v>0.012802</v>
       </c>
       <c r="C852" t="n">
         <v>0.8426399999999999</v>
@@ -11503,7 +11503,7 @@
         </is>
       </c>
       <c r="B853" t="n">
-        <v>0.01292</v>
+        <v>0.012924</v>
       </c>
       <c r="C853" t="n">
         <v>0.840102</v>
@@ -11516,7 +11516,7 @@
         </is>
       </c>
       <c r="B854" t="n">
-        <v>0.013278</v>
+        <v>0.013279</v>
       </c>
       <c r="C854" t="n">
         <v>0.8375629999999999</v>
@@ -11542,7 +11542,7 @@
         </is>
       </c>
       <c r="B856" t="n">
-        <v>0.013395</v>
+        <v>0.013394</v>
       </c>
       <c r="C856" t="n">
         <v>0.832487</v>
@@ -11555,7 +11555,7 @@
         </is>
       </c>
       <c r="B857" t="n">
-        <v>0.013477</v>
+        <v>0.013481</v>
       </c>
       <c r="C857" t="n">
         <v>0.829949</v>
@@ -11568,7 +11568,7 @@
         </is>
       </c>
       <c r="B858" t="n">
-        <v>0.013558</v>
+        <v>0.013564</v>
       </c>
       <c r="C858" t="n">
         <v>0.827411</v>
@@ -11581,7 +11581,7 @@
         </is>
       </c>
       <c r="B859" t="n">
-        <v>0.013748</v>
+        <v>0.013756</v>
       </c>
       <c r="C859" t="n">
         <v>0.824873</v>
@@ -11594,7 +11594,7 @@
         </is>
       </c>
       <c r="B860" t="n">
-        <v>0.01406</v>
+        <v>0.014061</v>
       </c>
       <c r="C860" t="n">
         <v>0.822335</v>
@@ -11633,7 +11633,7 @@
         </is>
       </c>
       <c r="B863" t="n">
-        <v>0.014175</v>
+        <v>0.014199</v>
       </c>
       <c r="C863" t="n">
         <v>0.814721</v>
@@ -11672,7 +11672,7 @@
         </is>
       </c>
       <c r="B866" t="n">
-        <v>0.015405</v>
+        <v>0.015406</v>
       </c>
       <c r="C866" t="n">
         <v>0.807107</v>
@@ -11685,7 +11685,7 @@
         </is>
       </c>
       <c r="B867" t="n">
-        <v>0.01549</v>
+        <v>0.015489</v>
       </c>
       <c r="C867" t="n">
         <v>0.804569</v>
@@ -11711,7 +11711,7 @@
         </is>
       </c>
       <c r="B869" t="n">
-        <v>0.015681</v>
+        <v>0.015688</v>
       </c>
       <c r="C869" t="n">
         <v>0.799492</v>
@@ -11724,7 +11724,7 @@
         </is>
       </c>
       <c r="B870" t="n">
-        <v>0.015893</v>
+        <v>0.015894</v>
       </c>
       <c r="C870" t="n">
         <v>0.7969540000000001</v>
@@ -11750,7 +11750,7 @@
         </is>
       </c>
       <c r="B872" t="n">
-        <v>0.016173</v>
+        <v>0.016191</v>
       </c>
       <c r="C872" t="n">
         <v>0.791878</v>
@@ -11763,7 +11763,7 @@
         </is>
       </c>
       <c r="B873" t="n">
-        <v>0.016569</v>
+        <v>0.01657</v>
       </c>
       <c r="C873" t="n">
         <v>0.78934</v>
@@ -11776,7 +11776,7 @@
         </is>
       </c>
       <c r="B874" t="n">
-        <v>0.016631</v>
+        <v>0.016632</v>
       </c>
       <c r="C874" t="n">
         <v>0.786802</v>
@@ -11789,7 +11789,7 @@
         </is>
       </c>
       <c r="B875" t="n">
-        <v>0.016734</v>
+        <v>0.016743</v>
       </c>
       <c r="C875" t="n">
         <v>0.784264</v>
@@ -11802,7 +11802,7 @@
         </is>
       </c>
       <c r="B876" t="n">
-        <v>0.016983</v>
+        <v>0.016993</v>
       </c>
       <c r="C876" t="n">
         <v>0.781726</v>
@@ -11815,7 +11815,7 @@
         </is>
       </c>
       <c r="B877" t="n">
-        <v>0.017368</v>
+        <v>0.017367</v>
       </c>
       <c r="C877" t="n">
         <v>0.779188</v>
@@ -11828,7 +11828,7 @@
         </is>
       </c>
       <c r="B878" t="n">
-        <v>0.017644</v>
+        <v>0.017649</v>
       </c>
       <c r="C878" t="n">
         <v>0.77665</v>
@@ -11841,7 +11841,7 @@
         </is>
       </c>
       <c r="B879" t="n">
-        <v>0.017876</v>
+        <v>0.017883</v>
       </c>
       <c r="C879" t="n">
         <v>0.774112</v>
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="B880" t="n">
-        <v>0.018157</v>
+        <v>0.018165</v>
       </c>
       <c r="C880" t="n">
         <v>0.771574</v>
@@ -11867,7 +11867,7 @@
         </is>
       </c>
       <c r="B881" t="n">
-        <v>0.01819</v>
+        <v>0.018193</v>
       </c>
       <c r="C881" t="n">
         <v>0.7690360000000001</v>
@@ -11880,7 +11880,7 @@
         </is>
       </c>
       <c r="B882" t="n">
-        <v>0.0182</v>
+        <v>0.018202</v>
       </c>
       <c r="C882" t="n">
         <v>0.766497</v>
@@ -11893,7 +11893,7 @@
         </is>
       </c>
       <c r="B883" t="n">
-        <v>0.018324</v>
+        <v>0.018326</v>
       </c>
       <c r="C883" t="n">
         <v>0.7639590000000001</v>
@@ -11906,7 +11906,7 @@
         </is>
       </c>
       <c r="B884" t="n">
-        <v>0.018422</v>
+        <v>0.018421</v>
       </c>
       <c r="C884" t="n">
         <v>0.761421</v>
@@ -11919,7 +11919,7 @@
         </is>
       </c>
       <c r="B885" t="n">
-        <v>0.018446</v>
+        <v>0.018449</v>
       </c>
       <c r="C885" t="n">
         <v>0.758883</v>
@@ -11932,7 +11932,7 @@
         </is>
       </c>
       <c r="B886" t="n">
-        <v>0.018924</v>
+        <v>0.018942</v>
       </c>
       <c r="C886" t="n">
         <v>0.756345</v>
@@ -11945,7 +11945,7 @@
         </is>
       </c>
       <c r="B887" t="n">
-        <v>0.019054</v>
+        <v>0.019063</v>
       </c>
       <c r="C887" t="n">
         <v>0.753807</v>
@@ -11958,7 +11958,7 @@
         </is>
       </c>
       <c r="B888" t="n">
-        <v>0.019655</v>
+        <v>0.019657</v>
       </c>
       <c r="C888" t="n">
         <v>0.751269</v>
@@ -11984,7 +11984,7 @@
         </is>
       </c>
       <c r="B890" t="n">
-        <v>0.020096</v>
+        <v>0.020099</v>
       </c>
       <c r="C890" t="n">
         <v>0.746193</v>
@@ -11997,7 +11997,7 @@
         </is>
       </c>
       <c r="B891" t="n">
-        <v>0.020117</v>
+        <v>0.020116</v>
       </c>
       <c r="C891" t="n">
         <v>0.743655</v>
@@ -12023,7 +12023,7 @@
         </is>
       </c>
       <c r="B893" t="n">
-        <v>0.020566</v>
+        <v>0.020565</v>
       </c>
       <c r="C893" t="n">
         <v>0.738579</v>
@@ -12036,7 +12036,7 @@
         </is>
       </c>
       <c r="B894" t="n">
-        <v>0.021326</v>
+        <v>0.021331</v>
       </c>
       <c r="C894" t="n">
         <v>0.7360409999999999</v>
@@ -12049,7 +12049,7 @@
         </is>
       </c>
       <c r="B895" t="n">
-        <v>0.021616</v>
+        <v>0.021629</v>
       </c>
       <c r="C895" t="n">
         <v>0.733503</v>
@@ -12075,7 +12075,7 @@
         </is>
       </c>
       <c r="B897" t="n">
-        <v>0.021733</v>
+        <v>0.021781</v>
       </c>
       <c r="C897" t="n">
         <v>0.728426</v>
@@ -12101,7 +12101,7 @@
         </is>
       </c>
       <c r="B899" t="n">
-        <v>0.022263</v>
+        <v>0.022267</v>
       </c>
       <c r="C899" t="n">
         <v>0.72335</v>
@@ -12114,7 +12114,7 @@
         </is>
       </c>
       <c r="B900" t="n">
-        <v>0.022364</v>
+        <v>0.022365</v>
       </c>
       <c r="C900" t="n">
         <v>0.720812</v>
@@ -12153,7 +12153,7 @@
         </is>
       </c>
       <c r="B903" t="n">
-        <v>0.022903</v>
+        <v>0.022912</v>
       </c>
       <c r="C903" t="n">
         <v>0.713198</v>
@@ -12166,7 +12166,7 @@
         </is>
       </c>
       <c r="B904" t="n">
-        <v>0.023063</v>
+        <v>0.023062</v>
       </c>
       <c r="C904" t="n">
         <v>0.71066</v>
@@ -12179,7 +12179,7 @@
         </is>
       </c>
       <c r="B905" t="n">
-        <v>0.02309</v>
+        <v>0.023091</v>
       </c>
       <c r="C905" t="n">
         <v>0.708122</v>
@@ -12218,7 +12218,7 @@
         </is>
       </c>
       <c r="B908" t="n">
-        <v>0.023707</v>
+        <v>0.023708</v>
       </c>
       <c r="C908" t="n">
         <v>0.700508</v>
@@ -12231,7 +12231,7 @@
         </is>
       </c>
       <c r="B909" t="n">
-        <v>0.024203</v>
+        <v>0.024205</v>
       </c>
       <c r="C909" t="n">
         <v>0.69797</v>
@@ -12244,7 +12244,7 @@
         </is>
       </c>
       <c r="B910" t="n">
-        <v>0.024276</v>
+        <v>0.024285</v>
       </c>
       <c r="C910" t="n">
         <v>0.695431</v>
@@ -12257,7 +12257,7 @@
         </is>
       </c>
       <c r="B911" t="n">
-        <v>0.024381</v>
+        <v>0.024383</v>
       </c>
       <c r="C911" t="n">
         <v>0.692893</v>
@@ -12270,7 +12270,7 @@
         </is>
       </c>
       <c r="B912" t="n">
-        <v>0.024461</v>
+        <v>0.024471</v>
       </c>
       <c r="C912" t="n">
         <v>0.6903550000000001</v>
@@ -12296,7 +12296,7 @@
         </is>
       </c>
       <c r="B914" t="n">
-        <v>0.024749</v>
+        <v>0.024748</v>
       </c>
       <c r="C914" t="n">
         <v>0.685279</v>
@@ -12309,7 +12309,7 @@
         </is>
       </c>
       <c r="B915" t="n">
-        <v>0.024815</v>
+        <v>0.024817</v>
       </c>
       <c r="C915" t="n">
         <v>0.682741</v>
@@ -12335,7 +12335,7 @@
         </is>
       </c>
       <c r="B917" t="n">
-        <v>0.025099</v>
+        <v>0.025098</v>
       </c>
       <c r="C917" t="n">
         <v>0.677665</v>
@@ -12348,7 +12348,7 @@
         </is>
       </c>
       <c r="B918" t="n">
-        <v>0.025323</v>
+        <v>0.02534</v>
       </c>
       <c r="C918" t="n">
         <v>0.675127</v>
@@ -12361,7 +12361,7 @@
         </is>
       </c>
       <c r="B919" t="n">
-        <v>0.026802</v>
+        <v>0.026805</v>
       </c>
       <c r="C919" t="n">
         <v>0.672589</v>
@@ -12374,7 +12374,7 @@
         </is>
       </c>
       <c r="B920" t="n">
-        <v>0.02687</v>
+        <v>0.026878</v>
       </c>
       <c r="C920" t="n">
         <v>0.670051</v>
@@ -12387,7 +12387,7 @@
         </is>
       </c>
       <c r="B921" t="n">
-        <v>0.027106</v>
+        <v>0.027123</v>
       </c>
       <c r="C921" t="n">
         <v>0.667513</v>
@@ -12400,7 +12400,7 @@
         </is>
       </c>
       <c r="B922" t="n">
-        <v>0.027218</v>
+        <v>0.027217</v>
       </c>
       <c r="C922" t="n">
         <v>0.664975</v>
@@ -12413,7 +12413,7 @@
         </is>
       </c>
       <c r="B923" t="n">
-        <v>0.027235</v>
+        <v>0.027234</v>
       </c>
       <c r="C923" t="n">
         <v>0.6624370000000001</v>
@@ -12426,7 +12426,7 @@
         </is>
       </c>
       <c r="B924" t="n">
-        <v>0.027283</v>
+        <v>0.027286</v>
       </c>
       <c r="C924" t="n">
         <v>0.659898</v>
@@ -12439,7 +12439,7 @@
         </is>
       </c>
       <c r="B925" t="n">
-        <v>0.027372</v>
+        <v>0.027383</v>
       </c>
       <c r="C925" t="n">
         <v>0.6573600000000001</v>
@@ -12465,7 +12465,7 @@
         </is>
       </c>
       <c r="B927" t="n">
-        <v>0.027985</v>
+        <v>0.027996</v>
       </c>
       <c r="C927" t="n">
         <v>0.652284</v>
@@ -12478,7 +12478,7 @@
         </is>
       </c>
       <c r="B928" t="n">
-        <v>0.028052</v>
+        <v>0.028051</v>
       </c>
       <c r="C928" t="n">
         <v>0.649746</v>
@@ -12491,7 +12491,7 @@
         </is>
       </c>
       <c r="B929" t="n">
-        <v>0.02842</v>
+        <v>0.028439</v>
       </c>
       <c r="C929" t="n">
         <v>0.647208</v>
@@ -12504,7 +12504,7 @@
         </is>
       </c>
       <c r="B930" t="n">
-        <v>0.028606</v>
+        <v>0.028611</v>
       </c>
       <c r="C930" t="n">
         <v>0.64467</v>
@@ -12517,7 +12517,7 @@
         </is>
       </c>
       <c r="B931" t="n">
-        <v>0.028782</v>
+        <v>0.028792</v>
       </c>
       <c r="C931" t="n">
         <v>0.642132</v>
@@ -12543,7 +12543,7 @@
         </is>
       </c>
       <c r="B933" t="n">
-        <v>0.029153</v>
+        <v>0.029155</v>
       </c>
       <c r="C933" t="n">
         <v>0.637056</v>
@@ -12556,7 +12556,7 @@
         </is>
       </c>
       <c r="B934" t="n">
-        <v>0.029292</v>
+        <v>0.029294</v>
       </c>
       <c r="C934" t="n">
         <v>0.634518</v>
@@ -12569,7 +12569,7 @@
         </is>
       </c>
       <c r="B935" t="n">
-        <v>0.029617</v>
+        <v>0.02962</v>
       </c>
       <c r="C935" t="n">
         <v>0.63198</v>
@@ -12582,7 +12582,7 @@
         </is>
       </c>
       <c r="B936" t="n">
-        <v>0.029928</v>
+        <v>0.029931</v>
       </c>
       <c r="C936" t="n">
         <v>0.6294419999999999</v>
@@ -12595,7 +12595,7 @@
         </is>
       </c>
       <c r="B937" t="n">
-        <v>0.030074</v>
+        <v>0.030122</v>
       </c>
       <c r="C937" t="n">
         <v>0.626904</v>
@@ -12608,7 +12608,7 @@
         </is>
       </c>
       <c r="B938" t="n">
-        <v>0.030394</v>
+        <v>0.030395</v>
       </c>
       <c r="C938" t="n">
         <v>0.6243649999999999</v>
@@ -12621,7 +12621,7 @@
         </is>
       </c>
       <c r="B939" t="n">
-        <v>0.030443</v>
+        <v>0.030442</v>
       </c>
       <c r="C939" t="n">
         <v>0.621827</v>
@@ -12647,7 +12647,7 @@
         </is>
       </c>
       <c r="B941" t="n">
-        <v>0.030941</v>
+        <v>0.03097</v>
       </c>
       <c r="C941" t="n">
         <v>0.616751</v>
@@ -12660,7 +12660,7 @@
         </is>
       </c>
       <c r="B942" t="n">
-        <v>0.031121</v>
+        <v>0.03112</v>
       </c>
       <c r="C942" t="n">
         <v>0.614213</v>
@@ -12673,7 +12673,7 @@
         </is>
       </c>
       <c r="B943" t="n">
-        <v>0.031125</v>
+        <v>0.031134</v>
       </c>
       <c r="C943" t="n">
         <v>0.611675</v>
@@ -12686,7 +12686,7 @@
         </is>
       </c>
       <c r="B944" t="n">
-        <v>0.031409</v>
+        <v>0.031408</v>
       </c>
       <c r="C944" t="n">
         <v>0.609137</v>
@@ -12699,7 +12699,7 @@
         </is>
       </c>
       <c r="B945" t="n">
-        <v>0.031628</v>
+        <v>0.031644</v>
       </c>
       <c r="C945" t="n">
         <v>0.606599</v>
@@ -12712,7 +12712,7 @@
         </is>
       </c>
       <c r="B946" t="n">
-        <v>0.03166</v>
+        <v>0.031658</v>
       </c>
       <c r="C946" t="n">
         <v>0.604061</v>
@@ -12725,7 +12725,7 @@
         </is>
       </c>
       <c r="B947" t="n">
-        <v>0.031696</v>
+        <v>0.031716</v>
       </c>
       <c r="C947" t="n">
         <v>0.601523</v>
@@ -12738,7 +12738,7 @@
         </is>
       </c>
       <c r="B948" t="n">
-        <v>0.031715</v>
+        <v>0.031717</v>
       </c>
       <c r="C948" t="n">
         <v>0.598985</v>
@@ -12764,7 +12764,7 @@
         </is>
       </c>
       <c r="B950" t="n">
-        <v>0.032251</v>
+        <v>0.032262</v>
       </c>
       <c r="C950" t="n">
         <v>0.593909</v>
@@ -12777,7 +12777,7 @@
         </is>
       </c>
       <c r="B951" t="n">
-        <v>0.032853</v>
+        <v>0.032852</v>
       </c>
       <c r="C951" t="n">
         <v>0.591371</v>
@@ -12790,7 +12790,7 @@
         </is>
       </c>
       <c r="B952" t="n">
-        <v>0.032912</v>
+        <v>0.032916</v>
       </c>
       <c r="C952" t="n">
         <v>0.588832</v>
@@ -12803,7 +12803,7 @@
         </is>
       </c>
       <c r="B953" t="n">
-        <v>0.033315</v>
+        <v>0.033322</v>
       </c>
       <c r="C953" t="n">
         <v>0.586294</v>
@@ -12816,7 +12816,7 @@
         </is>
       </c>
       <c r="B954" t="n">
-        <v>0.03356</v>
+        <v>0.033582</v>
       </c>
       <c r="C954" t="n">
         <v>0.5837560000000001</v>
@@ -12829,7 +12829,7 @@
         </is>
       </c>
       <c r="B955" t="n">
-        <v>0.03369</v>
+        <v>0.033692</v>
       </c>
       <c r="C955" t="n">
         <v>0.581218</v>
@@ -12842,7 +12842,7 @@
         </is>
       </c>
       <c r="B956" t="n">
-        <v>0.033779</v>
+        <v>0.033784</v>
       </c>
       <c r="C956" t="n">
         <v>0.57868</v>
@@ -12855,7 +12855,7 @@
         </is>
       </c>
       <c r="B957" t="n">
-        <v>0.033855</v>
+        <v>0.033879</v>
       </c>
       <c r="C957" t="n">
         <v>0.576142</v>
@@ -12868,7 +12868,7 @@
         </is>
       </c>
       <c r="B958" t="n">
-        <v>0.034132</v>
+        <v>0.034162</v>
       </c>
       <c r="C958" t="n">
         <v>0.573604</v>
@@ -12881,7 +12881,7 @@
         </is>
       </c>
       <c r="B959" t="n">
-        <v>0.034293</v>
+        <v>0.034292</v>
       </c>
       <c r="C959" t="n">
         <v>0.571066</v>
@@ -12894,7 +12894,7 @@
         </is>
       </c>
       <c r="B960" t="n">
-        <v>0.034634</v>
+        <v>0.034651</v>
       </c>
       <c r="C960" t="n">
         <v>0.568528</v>
@@ -12907,7 +12907,7 @@
         </is>
       </c>
       <c r="B961" t="n">
-        <v>0.034753</v>
+        <v>0.034778</v>
       </c>
       <c r="C961" t="n">
         <v>0.56599</v>
@@ -12920,7 +12920,7 @@
         </is>
       </c>
       <c r="B962" t="n">
-        <v>0.034826</v>
+        <v>0.034825</v>
       </c>
       <c r="C962" t="n">
         <v>0.563452</v>
@@ -12933,7 +12933,7 @@
         </is>
       </c>
       <c r="B963" t="n">
-        <v>0.034929</v>
+        <v>0.034931</v>
       </c>
       <c r="C963" t="n">
         <v>0.560914</v>
@@ -12946,7 +12946,7 @@
         </is>
       </c>
       <c r="B964" t="n">
-        <v>0.035695</v>
+        <v>0.035694</v>
       </c>
       <c r="C964" t="n">
         <v>0.558376</v>
@@ -12959,7 +12959,7 @@
         </is>
       </c>
       <c r="B965" t="n">
-        <v>0.036193</v>
+        <v>0.036196</v>
       </c>
       <c r="C965" t="n">
         <v>0.5558380000000001</v>
@@ -12972,7 +12972,7 @@
         </is>
       </c>
       <c r="B966" t="n">
-        <v>0.036239</v>
+        <v>0.036247</v>
       </c>
       <c r="C966" t="n">
         <v>0.553299</v>
@@ -12985,7 +12985,7 @@
         </is>
       </c>
       <c r="B967" t="n">
-        <v>0.036422</v>
+        <v>0.036423</v>
       </c>
       <c r="C967" t="n">
         <v>0.5507609999999999</v>
@@ -13011,7 +13011,7 @@
         </is>
       </c>
       <c r="B969" t="n">
-        <v>0.037236</v>
+        <v>0.037235</v>
       </c>
       <c r="C969" t="n">
         <v>0.545685</v>
@@ -13024,7 +13024,7 @@
         </is>
       </c>
       <c r="B970" t="n">
-        <v>0.037236</v>
+        <v>0.037238</v>
       </c>
       <c r="C970" t="n">
         <v>0.543147</v>
@@ -13050,7 +13050,7 @@
         </is>
       </c>
       <c r="B972" t="n">
-        <v>0.037475</v>
+        <v>0.037496</v>
       </c>
       <c r="C972" t="n">
         <v>0.538071</v>
@@ -13063,7 +13063,7 @@
         </is>
       </c>
       <c r="B973" t="n">
-        <v>0.037734</v>
+        <v>0.037748</v>
       </c>
       <c r="C973" t="n">
         <v>0.535533</v>
@@ -13076,7 +13076,7 @@
         </is>
       </c>
       <c r="B974" t="n">
-        <v>0.038129</v>
+        <v>0.038127</v>
       </c>
       <c r="C974" t="n">
         <v>0.532995</v>
@@ -13089,7 +13089,7 @@
         </is>
       </c>
       <c r="B975" t="n">
-        <v>0.038307</v>
+        <v>0.038309</v>
       </c>
       <c r="C975" t="n">
         <v>0.530457</v>
@@ -13102,7 +13102,7 @@
         </is>
       </c>
       <c r="B976" t="n">
-        <v>0.038484</v>
+        <v>0.038492</v>
       </c>
       <c r="C976" t="n">
         <v>0.527919</v>
@@ -13115,7 +13115,7 @@
         </is>
       </c>
       <c r="B977" t="n">
-        <v>0.038542</v>
+        <v>0.038557</v>
       </c>
       <c r="C977" t="n">
         <v>0.525381</v>
@@ -13128,7 +13128,7 @@
         </is>
       </c>
       <c r="B978" t="n">
-        <v>0.038604</v>
+        <v>0.038616</v>
       </c>
       <c r="C978" t="n">
         <v>0.5228429999999999</v>
@@ -13154,7 +13154,7 @@
         </is>
       </c>
       <c r="B980" t="n">
-        <v>0.040196</v>
+        <v>0.040219</v>
       </c>
       <c r="C980" t="n">
         <v>0.5177659999999999</v>
@@ -13167,7 +13167,7 @@
         </is>
       </c>
       <c r="B981" t="n">
-        <v>0.040404</v>
+        <v>0.040406</v>
       </c>
       <c r="C981" t="n">
         <v>0.515228</v>
@@ -13180,7 +13180,7 @@
         </is>
       </c>
       <c r="B982" t="n">
-        <v>0.040488</v>
+        <v>0.040486</v>
       </c>
       <c r="C982" t="n">
         <v>0.51269</v>
@@ -13193,7 +13193,7 @@
         </is>
       </c>
       <c r="B983" t="n">
-        <v>0.040815</v>
+        <v>0.040816</v>
       </c>
       <c r="C983" t="n">
         <v>0.510152</v>
@@ -13206,7 +13206,7 @@
         </is>
       </c>
       <c r="B984" t="n">
-        <v>0.040895</v>
+        <v>0.040897</v>
       </c>
       <c r="C984" t="n">
         <v>0.507614</v>
@@ -13219,7 +13219,7 @@
         </is>
       </c>
       <c r="B985" t="n">
-        <v>0.041069</v>
+        <v>0.041073</v>
       </c>
       <c r="C985" t="n">
         <v>0.505076</v>
@@ -13232,7 +13232,7 @@
         </is>
       </c>
       <c r="B986" t="n">
-        <v>0.041456</v>
+        <v>0.041478</v>
       </c>
       <c r="C986" t="n">
         <v>0.502538</v>
@@ -13245,7 +13245,7 @@
         </is>
       </c>
       <c r="B987" t="n">
-        <v>0.041475</v>
+        <v>0.041479</v>
       </c>
       <c r="C987" t="n">
         <v>0.5</v>
@@ -13258,7 +13258,7 @@
         </is>
       </c>
       <c r="B988" t="n">
-        <v>0.041765</v>
+        <v>0.041764</v>
       </c>
       <c r="C988" t="n">
         <v>0.497462</v>
@@ -13271,7 +13271,7 @@
         </is>
       </c>
       <c r="B989" t="n">
-        <v>0.041854</v>
+        <v>0.041859</v>
       </c>
       <c r="C989" t="n">
         <v>0.494924</v>
@@ -13284,7 +13284,7 @@
         </is>
       </c>
       <c r="B990" t="n">
-        <v>0.042034</v>
+        <v>0.042056</v>
       </c>
       <c r="C990" t="n">
         <v>0.492386</v>
@@ -13297,7 +13297,7 @@
         </is>
       </c>
       <c r="B991" t="n">
-        <v>0.042035</v>
+        <v>0.04221</v>
       </c>
       <c r="C991" t="n">
         <v>0.489848</v>
@@ -13310,7 +13310,7 @@
         </is>
       </c>
       <c r="B992" t="n">
-        <v>0.042181</v>
+        <v>0.04241</v>
       </c>
       <c r="C992" t="n">
         <v>0.48731</v>
@@ -13323,7 +13323,7 @@
         </is>
       </c>
       <c r="B993" t="n">
-        <v>0.04239</v>
+        <v>0.042573</v>
       </c>
       <c r="C993" t="n">
         <v>0.484772</v>
@@ -13336,7 +13336,7 @@
         </is>
       </c>
       <c r="B994" t="n">
-        <v>0.04255</v>
+        <v>0.042602</v>
       </c>
       <c r="C994" t="n">
         <v>0.482234</v>
@@ -13349,7 +13349,7 @@
         </is>
       </c>
       <c r="B995" t="n">
-        <v>0.042595</v>
+        <v>0.04276</v>
       </c>
       <c r="C995" t="n">
         <v>0.479695</v>
@@ -13362,7 +13362,7 @@
         </is>
       </c>
       <c r="B996" t="n">
-        <v>0.042728</v>
+        <v>0.042853</v>
       </c>
       <c r="C996" t="n">
         <v>0.477157</v>
@@ -13375,7 +13375,7 @@
         </is>
       </c>
       <c r="B997" t="n">
-        <v>0.042849</v>
+        <v>0.042939</v>
       </c>
       <c r="C997" t="n">
         <v>0.474619</v>
@@ -13388,7 +13388,7 @@
         </is>
       </c>
       <c r="B998" t="n">
-        <v>0.042923</v>
+        <v>0.043366</v>
       </c>
       <c r="C998" t="n">
         <v>0.472081</v>
@@ -13401,7 +13401,7 @@
         </is>
       </c>
       <c r="B999" t="n">
-        <v>0.043359</v>
+        <v>0.043875</v>
       </c>
       <c r="C999" t="n">
         <v>0.469543</v>
@@ -13414,7 +13414,7 @@
         </is>
       </c>
       <c r="B1000" t="n">
-        <v>0.043871</v>
+        <v>0.044075</v>
       </c>
       <c r="C1000" t="n">
         <v>0.467005</v>
@@ -13427,7 +13427,7 @@
         </is>
       </c>
       <c r="B1001" t="n">
-        <v>0.044028</v>
+        <v>0.044279</v>
       </c>
       <c r="C1001" t="n">
         <v>0.464467</v>
@@ -13440,7 +13440,7 @@
         </is>
       </c>
       <c r="B1002" t="n">
-        <v>0.044266</v>
+        <v>0.044431</v>
       </c>
       <c r="C1002" t="n">
         <v>0.461929</v>
@@ -13453,7 +13453,7 @@
         </is>
       </c>
       <c r="B1003" t="n">
-        <v>0.04439</v>
+        <v>0.044613</v>
       </c>
       <c r="C1003" t="n">
         <v>0.459391</v>
@@ -13466,7 +13466,7 @@
         </is>
       </c>
       <c r="B1004" t="n">
-        <v>0.044611</v>
+        <v>0.044749</v>
       </c>
       <c r="C1004" t="n">
         <v>0.456853</v>
@@ -13479,7 +13479,7 @@
         </is>
       </c>
       <c r="B1005" t="n">
-        <v>0.044737</v>
+        <v>0.045636</v>
       </c>
       <c r="C1005" t="n">
         <v>0.454315</v>
@@ -13492,7 +13492,7 @@
         </is>
       </c>
       <c r="B1006" t="n">
-        <v>0.045631</v>
+        <v>0.046029</v>
       </c>
       <c r="C1006" t="n">
         <v>0.451777</v>
@@ -13505,7 +13505,7 @@
         </is>
       </c>
       <c r="B1007" t="n">
-        <v>0.046011</v>
+        <v>0.046051</v>
       </c>
       <c r="C1007" t="n">
         <v>0.449239</v>
@@ -13518,7 +13518,7 @@
         </is>
       </c>
       <c r="B1008" t="n">
-        <v>0.04605</v>
+        <v>0.046771</v>
       </c>
       <c r="C1008" t="n">
         <v>0.446701</v>
@@ -13531,7 +13531,7 @@
         </is>
       </c>
       <c r="B1009" t="n">
-        <v>0.046766</v>
+        <v>0.046797</v>
       </c>
       <c r="C1009" t="n">
         <v>0.444162</v>
@@ -13544,7 +13544,7 @@
         </is>
       </c>
       <c r="B1010" t="n">
-        <v>0.046795</v>
+        <v>0.047039</v>
       </c>
       <c r="C1010" t="n">
         <v>0.441624</v>
@@ -13557,7 +13557,7 @@
         </is>
       </c>
       <c r="B1011" t="n">
-        <v>0.047038</v>
+        <v>0.047385</v>
       </c>
       <c r="C1011" t="n">
         <v>0.439086</v>
@@ -13570,7 +13570,7 @@
         </is>
       </c>
       <c r="B1012" t="n">
-        <v>0.047357</v>
+        <v>0.047652</v>
       </c>
       <c r="C1012" t="n">
         <v>0.436548</v>
@@ -13583,7 +13583,7 @@
         </is>
       </c>
       <c r="B1013" t="n">
-        <v>0.04765</v>
+        <v>0.047964</v>
       </c>
       <c r="C1013" t="n">
         <v>0.43401</v>
@@ -13596,7 +13596,7 @@
         </is>
       </c>
       <c r="B1014" t="n">
-        <v>0.047946</v>
+        <v>0.048106</v>
       </c>
       <c r="C1014" t="n">
         <v>0.431472</v>
@@ -13609,7 +13609,7 @@
         </is>
       </c>
       <c r="B1015" t="n">
-        <v>0.048104</v>
+        <v>0.049309</v>
       </c>
       <c r="C1015" t="n">
         <v>0.428934</v>
@@ -13622,7 +13622,7 @@
         </is>
       </c>
       <c r="B1016" t="n">
-        <v>0.049311</v>
+        <v>0.049407</v>
       </c>
       <c r="C1016" t="n">
         <v>0.426396</v>
@@ -13635,7 +13635,7 @@
         </is>
       </c>
       <c r="B1017" t="n">
-        <v>0.049409</v>
+        <v>0.04956</v>
       </c>
       <c r="C1017" t="n">
         <v>0.423858</v>
@@ -13648,7 +13648,7 @@
         </is>
       </c>
       <c r="B1018" t="n">
-        <v>0.04956</v>
+        <v>0.04973</v>
       </c>
       <c r="C1018" t="n">
         <v>0.42132</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="B1019" t="n">
-        <v>0.049691</v>
+        <v>0.049761</v>
       </c>
       <c r="C1019" t="n">
         <v>0.418782</v>
@@ -13674,7 +13674,7 @@
         </is>
       </c>
       <c r="B1020" t="n">
-        <v>0.049758</v>
+        <v>0.050449</v>
       </c>
       <c r="C1020" t="n">
         <v>0.416244</v>
@@ -13687,7 +13687,7 @@
         </is>
       </c>
       <c r="B1021" t="n">
-        <v>0.050443</v>
+        <v>0.050568</v>
       </c>
       <c r="C1021" t="n">
         <v>0.413706</v>
@@ -13700,7 +13700,7 @@
         </is>
       </c>
       <c r="B1022" t="n">
-        <v>0.050569</v>
+        <v>0.050598</v>
       </c>
       <c r="C1022" t="n">
         <v>0.411168</v>
@@ -13713,7 +13713,7 @@
         </is>
       </c>
       <c r="B1023" t="n">
-        <v>0.050595</v>
+        <v>0.050924</v>
       </c>
       <c r="C1023" t="n">
         <v>0.408629</v>
@@ -13726,7 +13726,7 @@
         </is>
       </c>
       <c r="B1024" t="n">
-        <v>0.050924</v>
+        <v>0.050957</v>
       </c>
       <c r="C1024" t="n">
         <v>0.406091</v>
@@ -13739,7 +13739,7 @@
         </is>
       </c>
       <c r="B1025" t="n">
-        <v>0.050958</v>
+        <v>0.051111</v>
       </c>
       <c r="C1025" t="n">
         <v>0.403553</v>
@@ -13752,7 +13752,7 @@
         </is>
       </c>
       <c r="B1026" t="n">
-        <v>0.05111</v>
+        <v>0.051233</v>
       </c>
       <c r="C1026" t="n">
         <v>0.401015</v>
@@ -13765,7 +13765,7 @@
         </is>
       </c>
       <c r="B1027" t="n">
-        <v>0.051215</v>
+        <v>0.05127</v>
       </c>
       <c r="C1027" t="n">
         <v>0.398477</v>
@@ -13778,7 +13778,7 @@
         </is>
       </c>
       <c r="B1028" t="n">
-        <v>0.051246</v>
+        <v>0.051306</v>
       </c>
       <c r="C1028" t="n">
         <v>0.395939</v>
@@ -13791,7 +13791,7 @@
         </is>
       </c>
       <c r="B1029" t="n">
-        <v>0.051302</v>
+        <v>0.051915</v>
       </c>
       <c r="C1029" t="n">
         <v>0.393401</v>
@@ -13804,7 +13804,7 @@
         </is>
       </c>
       <c r="B1030" t="n">
-        <v>0.051898</v>
+        <v>0.052128</v>
       </c>
       <c r="C1030" t="n">
         <v>0.390863</v>
@@ -13817,7 +13817,7 @@
         </is>
       </c>
       <c r="B1031" t="n">
-        <v>0.052115</v>
+        <v>0.052159</v>
       </c>
       <c r="C1031" t="n">
         <v>0.388325</v>
@@ -13830,7 +13830,7 @@
         </is>
       </c>
       <c r="B1032" t="n">
-        <v>0.052161</v>
+        <v>0.052649</v>
       </c>
       <c r="C1032" t="n">
         <v>0.385787</v>
@@ -13843,7 +13843,7 @@
         </is>
       </c>
       <c r="B1033" t="n">
-        <v>0.052645</v>
+        <v>0.052862</v>
       </c>
       <c r="C1033" t="n">
         <v>0.383249</v>
@@ -13856,7 +13856,7 @@
         </is>
       </c>
       <c r="B1034" t="n">
-        <v>0.052862</v>
+        <v>0.05351</v>
       </c>
       <c r="C1034" t="n">
         <v>0.380711</v>
@@ -13869,7 +13869,7 @@
         </is>
       </c>
       <c r="B1035" t="n">
-        <v>0.053486</v>
+        <v>0.053755</v>
       </c>
       <c r="C1035" t="n">
         <v>0.378173</v>
@@ -13882,7 +13882,7 @@
         </is>
       </c>
       <c r="B1036" t="n">
-        <v>0.053757</v>
+        <v>0.053806</v>
       </c>
       <c r="C1036" t="n">
         <v>0.375635</v>
@@ -13895,7 +13895,7 @@
         </is>
       </c>
       <c r="B1037" t="n">
-        <v>0.053789</v>
+        <v>0.053842</v>
       </c>
       <c r="C1037" t="n">
         <v>0.373096</v>
@@ -13908,7 +13908,7 @@
         </is>
       </c>
       <c r="B1038" t="n">
-        <v>0.053844</v>
+        <v>0.054349</v>
       </c>
       <c r="C1038" t="n">
         <v>0.370558</v>
@@ -13921,7 +13921,7 @@
         </is>
       </c>
       <c r="B1039" t="n">
-        <v>0.054344</v>
+        <v>0.05534</v>
       </c>
       <c r="C1039" t="n">
         <v>0.36802</v>
@@ -13934,7 +13934,7 @@
         </is>
       </c>
       <c r="B1040" t="n">
-        <v>0.055331</v>
+        <v>0.05597</v>
       </c>
       <c r="C1040" t="n">
         <v>0.365482</v>
@@ -13947,7 +13947,7 @@
         </is>
       </c>
       <c r="B1041" t="n">
-        <v>0.055968</v>
+        <v>0.05599</v>
       </c>
       <c r="C1041" t="n">
         <v>0.362944</v>
@@ -13960,7 +13960,7 @@
         </is>
       </c>
       <c r="B1042" t="n">
-        <v>0.055988</v>
+        <v>0.056141</v>
       </c>
       <c r="C1042" t="n">
         <v>0.360406</v>
@@ -13973,7 +13973,7 @@
         </is>
       </c>
       <c r="B1043" t="n">
-        <v>0.056139</v>
+        <v>0.056361</v>
       </c>
       <c r="C1043" t="n">
         <v>0.357868</v>
@@ -13986,7 +13986,7 @@
         </is>
       </c>
       <c r="B1044" t="n">
-        <v>0.056362</v>
+        <v>0.056798</v>
       </c>
       <c r="C1044" t="n">
         <v>0.35533</v>
@@ -13999,7 +13999,7 @@
         </is>
       </c>
       <c r="B1045" t="n">
-        <v>0.056736</v>
+        <v>0.056943</v>
       </c>
       <c r="C1045" t="n">
         <v>0.352792</v>
@@ -14012,7 +14012,7 @@
         </is>
       </c>
       <c r="B1046" t="n">
-        <v>0.056946</v>
+        <v>0.056949</v>
       </c>
       <c r="C1046" t="n">
         <v>0.350254</v>
@@ -14025,7 +14025,7 @@
         </is>
       </c>
       <c r="B1047" t="n">
-        <v>0.05797</v>
+        <v>0.057971</v>
       </c>
       <c r="C1047" t="n">
         <v>0.347716</v>
@@ -14038,7 +14038,7 @@
         </is>
       </c>
       <c r="B1048" t="n">
-        <v>0.058163</v>
+        <v>0.05817</v>
       </c>
       <c r="C1048" t="n">
         <v>0.345178</v>
@@ -14051,7 +14051,7 @@
         </is>
       </c>
       <c r="B1049" t="n">
-        <v>0.058717</v>
+        <v>0.058715</v>
       </c>
       <c r="C1049" t="n">
         <v>0.34264</v>
@@ -14064,7 +14064,7 @@
         </is>
       </c>
       <c r="B1050" t="n">
-        <v>0.059381</v>
+        <v>0.059384</v>
       </c>
       <c r="C1050" t="n">
         <v>0.340102</v>
@@ -14077,7 +14077,7 @@
         </is>
       </c>
       <c r="B1051" t="n">
-        <v>0.059455</v>
+        <v>0.059461</v>
       </c>
       <c r="C1051" t="n">
         <v>0.337563</v>
@@ -14090,7 +14090,7 @@
         </is>
       </c>
       <c r="B1052" t="n">
-        <v>0.059848</v>
+        <v>0.059847</v>
       </c>
       <c r="C1052" t="n">
         <v>0.335025</v>
@@ -14103,7 +14103,7 @@
         </is>
       </c>
       <c r="B1053" t="n">
-        <v>0.06041</v>
+        <v>0.060411</v>
       </c>
       <c r="C1053" t="n">
         <v>0.332487</v>
@@ -14116,7 +14116,7 @@
         </is>
       </c>
       <c r="B1054" t="n">
-        <v>0.060854</v>
+        <v>0.060852</v>
       </c>
       <c r="C1054" t="n">
         <v>0.329949</v>
@@ -14142,7 +14142,7 @@
         </is>
       </c>
       <c r="B1056" t="n">
-        <v>0.06166</v>
+        <v>0.061658</v>
       </c>
       <c r="C1056" t="n">
         <v>0.324873</v>
@@ -14168,7 +14168,7 @@
         </is>
       </c>
       <c r="B1058" t="n">
-        <v>0.06304</v>
+        <v>0.063045</v>
       </c>
       <c r="C1058" t="n">
         <v>0.319797</v>
@@ -14181,7 +14181,7 @@
         </is>
       </c>
       <c r="B1059" t="n">
-        <v>0.06368500000000001</v>
+        <v>0.063726</v>
       </c>
       <c r="C1059" t="n">
         <v>0.317259</v>
@@ -14194,7 +14194,7 @@
         </is>
       </c>
       <c r="B1060" t="n">
-        <v>0.06393</v>
+        <v>0.063929</v>
       </c>
       <c r="C1060" t="n">
         <v>0.314721</v>
@@ -14207,7 +14207,7 @@
         </is>
       </c>
       <c r="B1061" t="n">
-        <v>0.064134</v>
+        <v>0.064137</v>
       </c>
       <c r="C1061" t="n">
         <v>0.312183</v>
@@ -14220,7 +14220,7 @@
         </is>
       </c>
       <c r="B1062" t="n">
-        <v>0.064486</v>
+        <v>0.064496</v>
       </c>
       <c r="C1062" t="n">
         <v>0.309645</v>
@@ -14233,7 +14233,7 @@
         </is>
       </c>
       <c r="B1063" t="n">
-        <v>0.064822</v>
+        <v>0.06482599999999999</v>
       </c>
       <c r="C1063" t="n">
         <v>0.307107</v>
@@ -14246,7 +14246,7 @@
         </is>
       </c>
       <c r="B1064" t="n">
-        <v>0.06485200000000001</v>
+        <v>0.064871</v>
       </c>
       <c r="C1064" t="n">
         <v>0.304569</v>
@@ -14259,7 +14259,7 @@
         </is>
       </c>
       <c r="B1065" t="n">
-        <v>0.06507599999999999</v>
+        <v>0.065082</v>
       </c>
       <c r="C1065" t="n">
         <v>0.30203</v>
@@ -14272,7 +14272,7 @@
         </is>
       </c>
       <c r="B1066" t="n">
-        <v>0.065733</v>
+        <v>0.065752</v>
       </c>
       <c r="C1066" t="n">
         <v>0.299492</v>
@@ -14285,7 +14285,7 @@
         </is>
       </c>
       <c r="B1067" t="n">
-        <v>0.065818</v>
+        <v>0.065815</v>
       </c>
       <c r="C1067" t="n">
         <v>0.296954</v>
@@ -14298,7 +14298,7 @@
         </is>
       </c>
       <c r="B1068" t="n">
-        <v>0.06636599999999999</v>
+        <v>0.06636400000000001</v>
       </c>
       <c r="C1068" t="n">
         <v>0.294416</v>
@@ -14311,7 +14311,7 @@
         </is>
       </c>
       <c r="B1069" t="n">
-        <v>0.066425</v>
+        <v>0.066454</v>
       </c>
       <c r="C1069" t="n">
         <v>0.291878</v>
@@ -14324,7 +14324,7 @@
         </is>
       </c>
       <c r="B1070" t="n">
-        <v>0.066686</v>
+        <v>0.06668499999999999</v>
       </c>
       <c r="C1070" t="n">
         <v>0.28934</v>
@@ -14337,7 +14337,7 @@
         </is>
       </c>
       <c r="B1071" t="n">
-        <v>0.067593</v>
+        <v>0.06759</v>
       </c>
       <c r="C1071" t="n">
         <v>0.286802</v>
@@ -14350,7 +14350,7 @@
         </is>
       </c>
       <c r="B1072" t="n">
-        <v>0.067665</v>
+        <v>0.067664</v>
       </c>
       <c r="C1072" t="n">
         <v>0.284264</v>
@@ -14363,7 +14363,7 @@
         </is>
       </c>
       <c r="B1073" t="n">
-        <v>0.068166</v>
+        <v>0.068172</v>
       </c>
       <c r="C1073" t="n">
         <v>0.281726</v>
@@ -14376,7 +14376,7 @@
         </is>
       </c>
       <c r="B1074" t="n">
-        <v>0.068207</v>
+        <v>0.06821099999999999</v>
       </c>
       <c r="C1074" t="n">
         <v>0.279188</v>
@@ -14389,7 +14389,7 @@
         </is>
       </c>
       <c r="B1075" t="n">
-        <v>0.06917</v>
+        <v>0.069172</v>
       </c>
       <c r="C1075" t="n">
         <v>0.27665</v>
@@ -14402,7 +14402,7 @@
         </is>
       </c>
       <c r="B1076" t="n">
-        <v>0.06969400000000001</v>
+        <v>0.06972399999999999</v>
       </c>
       <c r="C1076" t="n">
         <v>0.274112</v>
@@ -14415,7 +14415,7 @@
         </is>
       </c>
       <c r="B1077" t="n">
-        <v>0.069911</v>
+        <v>0.06991600000000001</v>
       </c>
       <c r="C1077" t="n">
         <v>0.271574</v>
@@ -14428,7 +14428,7 @@
         </is>
       </c>
       <c r="B1078" t="n">
-        <v>0.070109</v>
+        <v>0.07012</v>
       </c>
       <c r="C1078" t="n">
         <v>0.269036</v>
@@ -14441,7 +14441,7 @@
         </is>
       </c>
       <c r="B1079" t="n">
-        <v>0.07037400000000001</v>
+        <v>0.070372</v>
       </c>
       <c r="C1079" t="n">
         <v>0.266497</v>
@@ -14454,7 +14454,7 @@
         </is>
       </c>
       <c r="B1080" t="n">
-        <v>0.070629</v>
+        <v>0.070631</v>
       </c>
       <c r="C1080" t="n">
         <v>0.263959</v>
@@ -14467,7 +14467,7 @@
         </is>
       </c>
       <c r="B1081" t="n">
-        <v>0.07071</v>
+        <v>0.07070799999999999</v>
       </c>
       <c r="C1081" t="n">
         <v>0.261421</v>
@@ -14480,7 +14480,7 @@
         </is>
       </c>
       <c r="B1082" t="n">
-        <v>0.071491</v>
+        <v>0.07149</v>
       </c>
       <c r="C1082" t="n">
         <v>0.258883</v>
@@ -14493,7 +14493,7 @@
         </is>
       </c>
       <c r="B1083" t="n">
-        <v>0.073446</v>
+        <v>0.073534</v>
       </c>
       <c r="C1083" t="n">
         <v>0.256345</v>
@@ -14506,7 +14506,7 @@
         </is>
       </c>
       <c r="B1084" t="n">
-        <v>0.073724</v>
+        <v>0.073727</v>
       </c>
       <c r="C1084" t="n">
         <v>0.253807</v>
@@ -14519,7 +14519,7 @@
         </is>
       </c>
       <c r="B1085" t="n">
-        <v>0.073853</v>
+        <v>0.073862</v>
       </c>
       <c r="C1085" t="n">
         <v>0.251269</v>
@@ -14532,7 +14532,7 @@
         </is>
       </c>
       <c r="B1086" t="n">
-        <v>0.074293</v>
+        <v>0.074298</v>
       </c>
       <c r="C1086" t="n">
         <v>0.248731</v>
@@ -14545,7 +14545,7 @@
         </is>
       </c>
       <c r="B1087" t="n">
-        <v>0.074628</v>
+        <v>0.074629</v>
       </c>
       <c r="C1087" t="n">
         <v>0.246193</v>
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="B1088" t="n">
-        <v>0.07509299999999999</v>
+        <v>0.075097</v>
       </c>
       <c r="C1088" t="n">
         <v>0.243655</v>
@@ -14571,7 +14571,7 @@
         </is>
       </c>
       <c r="B1089" t="n">
-        <v>0.075629</v>
+        <v>0.075653</v>
       </c>
       <c r="C1089" t="n">
         <v>0.241117</v>
@@ -14584,7 +14584,7 @@
         </is>
       </c>
       <c r="B1090" t="n">
-        <v>0.076431</v>
+        <v>0.07649400000000001</v>
       </c>
       <c r="C1090" t="n">
         <v>0.238579</v>
@@ -14597,7 +14597,7 @@
         </is>
       </c>
       <c r="B1091" t="n">
-        <v>0.07668899999999999</v>
+        <v>0.076696</v>
       </c>
       <c r="C1091" t="n">
         <v>0.236041</v>
@@ -14610,7 +14610,7 @@
         </is>
       </c>
       <c r="B1092" t="n">
-        <v>0.07717599999999999</v>
+        <v>0.077209</v>
       </c>
       <c r="C1092" t="n">
         <v>0.233503</v>
@@ -14623,7 +14623,7 @@
         </is>
       </c>
       <c r="B1093" t="n">
-        <v>0.07803400000000001</v>
+        <v>0.078032</v>
       </c>
       <c r="C1093" t="n">
         <v>0.230964</v>
@@ -14636,7 +14636,7 @@
         </is>
       </c>
       <c r="B1094" t="n">
-        <v>0.078221</v>
+        <v>0.078223</v>
       </c>
       <c r="C1094" t="n">
         <v>0.228426</v>
@@ -14649,7 +14649,7 @@
         </is>
       </c>
       <c r="B1095" t="n">
-        <v>0.078498</v>
+        <v>0.078556</v>
       </c>
       <c r="C1095" t="n">
         <v>0.225888</v>
@@ -14662,7 +14662,7 @@
         </is>
       </c>
       <c r="B1096" t="n">
-        <v>0.078983</v>
+        <v>0.079153</v>
       </c>
       <c r="C1096" t="n">
         <v>0.22335</v>
@@ -14675,7 +14675,7 @@
         </is>
       </c>
       <c r="B1097" t="n">
-        <v>0.07928399999999999</v>
+        <v>0.079287</v>
       </c>
       <c r="C1097" t="n">
         <v>0.220812</v>
@@ -14701,7 +14701,7 @@
         </is>
       </c>
       <c r="B1099" t="n">
-        <v>0.08033999999999999</v>
+        <v>0.08033899999999999</v>
       </c>
       <c r="C1099" t="n">
         <v>0.215736</v>
@@ -14714,7 +14714,7 @@
         </is>
       </c>
       <c r="B1100" t="n">
-        <v>0.08098900000000001</v>
+        <v>0.080995</v>
       </c>
       <c r="C1100" t="n">
         <v>0.213198</v>
@@ -14727,7 +14727,7 @@
         </is>
       </c>
       <c r="B1101" t="n">
-        <v>0.082429</v>
+        <v>0.08243300000000001</v>
       </c>
       <c r="C1101" t="n">
         <v>0.21066</v>
@@ -14740,7 +14740,7 @@
         </is>
       </c>
       <c r="B1102" t="n">
-        <v>0.082733</v>
+        <v>0.08276600000000001</v>
       </c>
       <c r="C1102" t="n">
         <v>0.208122</v>
@@ -14766,7 +14766,7 @@
         </is>
       </c>
       <c r="B1104" t="n">
-        <v>0.08311499999999999</v>
+        <v>0.083119</v>
       </c>
       <c r="C1104" t="n">
         <v>0.203046</v>
@@ -14779,7 +14779,7 @@
         </is>
       </c>
       <c r="B1105" t="n">
-        <v>0.085747</v>
+        <v>0.085783</v>
       </c>
       <c r="C1105" t="n">
         <v>0.200508</v>
@@ -14792,7 +14792,7 @@
         </is>
       </c>
       <c r="B1106" t="n">
-        <v>0.08606900000000001</v>
+        <v>0.086067</v>
       </c>
       <c r="C1106" t="n">
         <v>0.19797</v>
@@ -14805,7 +14805,7 @@
         </is>
       </c>
       <c r="B1107" t="n">
-        <v>0.086697</v>
+        <v>0.086698</v>
       </c>
       <c r="C1107" t="n">
         <v>0.195431</v>
@@ -14818,7 +14818,7 @@
         </is>
       </c>
       <c r="B1108" t="n">
-        <v>0.08698599999999999</v>
+        <v>0.08701200000000001</v>
       </c>
       <c r="C1108" t="n">
         <v>0.192893</v>
@@ -14831,7 +14831,7 @@
         </is>
       </c>
       <c r="B1109" t="n">
-        <v>0.08717</v>
+        <v>0.08724999999999999</v>
       </c>
       <c r="C1109" t="n">
         <v>0.190355</v>
@@ -14844,7 +14844,7 @@
         </is>
       </c>
       <c r="B1110" t="n">
-        <v>0.08920500000000001</v>
+        <v>0.089201</v>
       </c>
       <c r="C1110" t="n">
         <v>0.187817</v>
@@ -14857,7 +14857,7 @@
         </is>
       </c>
       <c r="B1111" t="n">
-        <v>0.08980200000000001</v>
+        <v>0.08983099999999999</v>
       </c>
       <c r="C1111" t="n">
         <v>0.185279</v>
@@ -14870,7 +14870,7 @@
         </is>
       </c>
       <c r="B1112" t="n">
-        <v>0.09018900000000001</v>
+        <v>0.090277</v>
       </c>
       <c r="C1112" t="n">
         <v>0.182741</v>
@@ -14883,7 +14883,7 @@
         </is>
       </c>
       <c r="B1113" t="n">
-        <v>0.090239</v>
+        <v>0.090404</v>
       </c>
       <c r="C1113" t="n">
         <v>0.180203</v>
@@ -14896,7 +14896,7 @@
         </is>
       </c>
       <c r="B1114" t="n">
-        <v>0.090407</v>
+        <v>0.090446</v>
       </c>
       <c r="C1114" t="n">
         <v>0.177665</v>
@@ -14909,7 +14909,7 @@
         </is>
       </c>
       <c r="B1115" t="n">
-        <v>0.090862</v>
+        <v>0.090888</v>
       </c>
       <c r="C1115" t="n">
         <v>0.175127</v>
@@ -14922,7 +14922,7 @@
         </is>
       </c>
       <c r="B1116" t="n">
-        <v>0.091262</v>
+        <v>0.09125999999999999</v>
       </c>
       <c r="C1116" t="n">
         <v>0.172589</v>
@@ -14935,7 +14935,7 @@
         </is>
       </c>
       <c r="B1117" t="n">
-        <v>0.09253500000000001</v>
+        <v>0.092589</v>
       </c>
       <c r="C1117" t="n">
         <v>0.170051</v>
@@ -14948,7 +14948,7 @@
         </is>
       </c>
       <c r="B1118" t="n">
-        <v>0.093664</v>
+        <v>0.093678</v>
       </c>
       <c r="C1118" t="n">
         <v>0.167513</v>
@@ -14961,7 +14961,7 @@
         </is>
       </c>
       <c r="B1119" t="n">
-        <v>0.09377099999999999</v>
+        <v>0.09377000000000001</v>
       </c>
       <c r="C1119" t="n">
         <v>0.164975</v>
@@ -14974,7 +14974,7 @@
         </is>
       </c>
       <c r="B1120" t="n">
-        <v>0.09410200000000001</v>
+        <v>0.094108</v>
       </c>
       <c r="C1120" t="n">
         <v>0.162437</v>
@@ -14987,7 +14987,7 @@
         </is>
       </c>
       <c r="B1121" t="n">
-        <v>0.09433800000000001</v>
+        <v>0.094476</v>
       </c>
       <c r="C1121" t="n">
         <v>0.159898</v>
@@ -15000,7 +15000,7 @@
         </is>
       </c>
       <c r="B1122" t="n">
-        <v>0.094541</v>
+        <v>0.094538</v>
       </c>
       <c r="C1122" t="n">
         <v>0.15736</v>
@@ -15013,7 +15013,7 @@
         </is>
       </c>
       <c r="B1123" t="n">
-        <v>0.095595</v>
+        <v>0.095594</v>
       </c>
       <c r="C1123" t="n">
         <v>0.154822</v>
@@ -15026,7 +15026,7 @@
         </is>
       </c>
       <c r="B1124" t="n">
-        <v>0.096038</v>
+        <v>0.096052</v>
       </c>
       <c r="C1124" t="n">
         <v>0.152284</v>
@@ -15039,7 +15039,7 @@
         </is>
       </c>
       <c r="B1125" t="n">
-        <v>0.09757399999999999</v>
+        <v>0.097592</v>
       </c>
       <c r="C1125" t="n">
         <v>0.149746</v>
@@ -15052,7 +15052,7 @@
         </is>
       </c>
       <c r="B1126" t="n">
-        <v>0.10214</v>
+        <v>0.102142</v>
       </c>
       <c r="C1126" t="n">
         <v>0.147208</v>
@@ -15078,7 +15078,7 @@
         </is>
       </c>
       <c r="B1128" t="n">
-        <v>0.102719</v>
+        <v>0.10273</v>
       </c>
       <c r="C1128" t="n">
         <v>0.142132</v>
@@ -15091,7 +15091,7 @@
         </is>
       </c>
       <c r="B1129" t="n">
-        <v>0.102897</v>
+        <v>0.102918</v>
       </c>
       <c r="C1129" t="n">
         <v>0.139594</v>
@@ -15104,7 +15104,7 @@
         </is>
       </c>
       <c r="B1130" t="n">
-        <v>0.103164</v>
+        <v>0.103162</v>
       </c>
       <c r="C1130" t="n">
         <v>0.137056</v>
@@ -15117,7 +15117,7 @@
         </is>
       </c>
       <c r="B1131" t="n">
-        <v>0.103709</v>
+        <v>0.10377</v>
       </c>
       <c r="C1131" t="n">
         <v>0.134518</v>
@@ -15130,7 +15130,7 @@
         </is>
       </c>
       <c r="B1132" t="n">
-        <v>0.107053</v>
+        <v>0.107074</v>
       </c>
       <c r="C1132" t="n">
         <v>0.13198</v>
@@ -15143,7 +15143,7 @@
         </is>
       </c>
       <c r="B1133" t="n">
-        <v>0.108173</v>
+        <v>0.108169</v>
       </c>
       <c r="C1133" t="n">
         <v>0.129442</v>
@@ -15156,7 +15156,7 @@
         </is>
       </c>
       <c r="B1134" t="n">
-        <v>0.110156</v>
+        <v>0.110166</v>
       </c>
       <c r="C1134" t="n">
         <v>0.126904</v>
@@ -15169,7 +15169,7 @@
         </is>
       </c>
       <c r="B1135" t="n">
-        <v>0.111863</v>
+        <v>0.111864</v>
       </c>
       <c r="C1135" t="n">
         <v>0.124365</v>
@@ -15182,7 +15182,7 @@
         </is>
       </c>
       <c r="B1136" t="n">
-        <v>0.11265</v>
+        <v>0.112646</v>
       </c>
       <c r="C1136" t="n">
         <v>0.121827</v>
@@ -15195,7 +15195,7 @@
         </is>
       </c>
       <c r="B1137" t="n">
-        <v>0.114003</v>
+        <v>0.114019</v>
       </c>
       <c r="C1137" t="n">
         <v>0.119289</v>
@@ -15208,7 +15208,7 @@
         </is>
       </c>
       <c r="B1138" t="n">
-        <v>0.115314</v>
+        <v>0.115312</v>
       </c>
       <c r="C1138" t="n">
         <v>0.116751</v>
@@ -15221,7 +15221,7 @@
         </is>
       </c>
       <c r="B1139" t="n">
-        <v>0.116743</v>
+        <v>0.11687</v>
       </c>
       <c r="C1139" t="n">
         <v>0.114213</v>
@@ -15234,7 +15234,7 @@
         </is>
       </c>
       <c r="B1140" t="n">
-        <v>0.117165</v>
+        <v>0.117177</v>
       </c>
       <c r="C1140" t="n">
         <v>0.111675</v>
@@ -15247,7 +15247,7 @@
         </is>
       </c>
       <c r="B1141" t="n">
-        <v>0.117765</v>
+        <v>0.117763</v>
       </c>
       <c r="C1141" t="n">
         <v>0.109137</v>
@@ -15260,7 +15260,7 @@
         </is>
       </c>
       <c r="B1142" t="n">
-        <v>0.118048</v>
+        <v>0.118054</v>
       </c>
       <c r="C1142" t="n">
         <v>0.106599</v>
@@ -15273,7 +15273,7 @@
         </is>
       </c>
       <c r="B1143" t="n">
-        <v>0.122422</v>
+        <v>0.122421</v>
       </c>
       <c r="C1143" t="n">
         <v>0.104061</v>
@@ -15286,7 +15286,7 @@
         </is>
       </c>
       <c r="B1144" t="n">
-        <v>0.123089</v>
+        <v>0.1231</v>
       </c>
       <c r="C1144" t="n">
         <v>0.101523</v>
@@ -15299,7 +15299,7 @@
         </is>
       </c>
       <c r="B1145" t="n">
-        <v>0.124492</v>
+        <v>0.124497</v>
       </c>
       <c r="C1145" t="n">
         <v>0.098985</v>
@@ -15325,7 +15325,7 @@
         </is>
       </c>
       <c r="B1147" t="n">
-        <v>0.127625</v>
+        <v>0.127632</v>
       </c>
       <c r="C1147" t="n">
         <v>0.09390900000000001</v>
@@ -15351,7 +15351,7 @@
         </is>
       </c>
       <c r="B1149" t="n">
-        <v>0.128481</v>
+        <v>0.12854</v>
       </c>
       <c r="C1149" t="n">
         <v>0.08883199999999999</v>
@@ -15364,7 +15364,7 @@
         </is>
       </c>
       <c r="B1150" t="n">
-        <v>0.131531</v>
+        <v>0.131615</v>
       </c>
       <c r="C1150" t="n">
         <v>0.086294</v>
@@ -15377,7 +15377,7 @@
         </is>
       </c>
       <c r="B1151" t="n">
-        <v>0.132132</v>
+        <v>0.132137</v>
       </c>
       <c r="C1151" t="n">
         <v>0.083756</v>
@@ -15390,7 +15390,7 @@
         </is>
       </c>
       <c r="B1152" t="n">
-        <v>0.132976</v>
+        <v>0.132974</v>
       </c>
       <c r="C1152" t="n">
         <v>0.081218</v>
@@ -15403,7 +15403,7 @@
         </is>
       </c>
       <c r="B1153" t="n">
-        <v>0.13371</v>
+        <v>0.133718</v>
       </c>
       <c r="C1153" t="n">
         <v>0.07868</v>
@@ -15416,7 +15416,7 @@
         </is>
       </c>
       <c r="B1154" t="n">
-        <v>0.134695</v>
+        <v>0.134716</v>
       </c>
       <c r="C1154" t="n">
         <v>0.076142</v>
@@ -15429,7 +15429,7 @@
         </is>
       </c>
       <c r="B1155" t="n">
-        <v>0.136925</v>
+        <v>0.136996</v>
       </c>
       <c r="C1155" t="n">
         <v>0.073604</v>
@@ -15442,7 +15442,7 @@
         </is>
       </c>
       <c r="B1156" t="n">
-        <v>0.143493</v>
+        <v>0.143494</v>
       </c>
       <c r="C1156" t="n">
         <v>0.071066</v>
@@ -15455,7 +15455,7 @@
         </is>
       </c>
       <c r="B1157" t="n">
-        <v>0.145833</v>
+        <v>0.14583</v>
       </c>
       <c r="C1157" t="n">
         <v>0.06852800000000001</v>
@@ -15468,7 +15468,7 @@
         </is>
       </c>
       <c r="B1158" t="n">
-        <v>0.148933</v>
+        <v>0.148928</v>
       </c>
       <c r="C1158" t="n">
         <v>0.06598999999999999</v>
@@ -15481,7 +15481,7 @@
         </is>
       </c>
       <c r="B1159" t="n">
-        <v>0.150793</v>
+        <v>0.150796</v>
       </c>
       <c r="C1159" t="n">
         <v>0.06345199999999999</v>
@@ -15494,7 +15494,7 @@
         </is>
       </c>
       <c r="B1160" t="n">
-        <v>0.150933</v>
+        <v>0.150984</v>
       </c>
       <c r="C1160" t="n">
         <v>0.060914</v>
@@ -15507,7 +15507,7 @@
         </is>
       </c>
       <c r="B1161" t="n">
-        <v>0.160029</v>
+        <v>0.160045</v>
       </c>
       <c r="C1161" t="n">
         <v>0.058376</v>
@@ -15520,7 +15520,7 @@
         </is>
       </c>
       <c r="B1162" t="n">
-        <v>0.165352</v>
+        <v>0.165403</v>
       </c>
       <c r="C1162" t="n">
         <v>0.055838</v>
@@ -15533,7 +15533,7 @@
         </is>
       </c>
       <c r="B1163" t="n">
-        <v>0.1686</v>
+        <v>0.168595</v>
       </c>
       <c r="C1163" t="n">
         <v>0.053299</v>
@@ -15546,7 +15546,7 @@
         </is>
       </c>
       <c r="B1164" t="n">
-        <v>0.170453</v>
+        <v>0.170484</v>
       </c>
       <c r="C1164" t="n">
         <v>0.050761</v>
@@ -15559,7 +15559,7 @@
         </is>
       </c>
       <c r="B1165" t="n">
-        <v>0.171464</v>
+        <v>0.171494</v>
       </c>
       <c r="C1165" t="n">
         <v>0.048223</v>
@@ -15572,7 +15572,7 @@
         </is>
       </c>
       <c r="B1166" t="n">
-        <v>0.172026</v>
+        <v>0.172381</v>
       </c>
       <c r="C1166" t="n">
         <v>0.045685</v>
@@ -15585,7 +15585,7 @@
         </is>
       </c>
       <c r="B1167" t="n">
-        <v>0.175504</v>
+        <v>0.175498</v>
       </c>
       <c r="C1167" t="n">
         <v>0.043147</v>
@@ -15598,7 +15598,7 @@
         </is>
       </c>
       <c r="B1168" t="n">
-        <v>0.175767</v>
+        <v>0.175851</v>
       </c>
       <c r="C1168" t="n">
         <v>0.040609</v>
@@ -15611,7 +15611,7 @@
         </is>
       </c>
       <c r="B1169" t="n">
-        <v>0.176386</v>
+        <v>0.176382</v>
       </c>
       <c r="C1169" t="n">
         <v>0.038071</v>
@@ -15624,7 +15624,7 @@
         </is>
       </c>
       <c r="B1170" t="n">
-        <v>0.176937</v>
+        <v>0.177089</v>
       </c>
       <c r="C1170" t="n">
         <v>0.035533</v>
@@ -15637,7 +15637,7 @@
         </is>
       </c>
       <c r="B1171" t="n">
-        <v>0.185775</v>
+        <v>0.185779</v>
       </c>
       <c r="C1171" t="n">
         <v>0.032995</v>
@@ -15650,7 +15650,7 @@
         </is>
       </c>
       <c r="B1172" t="n">
-        <v>0.186611</v>
+        <v>0.186749</v>
       </c>
       <c r="C1172" t="n">
         <v>0.030457</v>
@@ -15663,7 +15663,7 @@
         </is>
       </c>
       <c r="B1173" t="n">
-        <v>0.194492</v>
+        <v>0.194497</v>
       </c>
       <c r="C1173" t="n">
         <v>0.027919</v>
@@ -15676,7 +15676,7 @@
         </is>
       </c>
       <c r="B1174" t="n">
-        <v>0.231341</v>
+        <v>0.231334</v>
       </c>
       <c r="C1174" t="n">
         <v>0.025381</v>
@@ -15689,7 +15689,7 @@
         </is>
       </c>
       <c r="B1175" t="n">
-        <v>0.231341</v>
+        <v>0.231476</v>
       </c>
       <c r="C1175" t="n">
         <v>0.022843</v>
@@ -15702,7 +15702,7 @@
         </is>
       </c>
       <c r="B1176" t="n">
-        <v>0.246691</v>
+        <v>0.246966</v>
       </c>
       <c r="C1176" t="n">
         <v>0.020305</v>
@@ -15715,7 +15715,7 @@
         </is>
       </c>
       <c r="B1177" t="n">
-        <v>0.249837</v>
+        <v>0.250119</v>
       </c>
       <c r="C1177" t="n">
         <v>0.017766</v>
@@ -15728,7 +15728,7 @@
         </is>
       </c>
       <c r="B1178" t="n">
-        <v>0.253327</v>
+        <v>0.25378</v>
       </c>
       <c r="C1178" t="n">
         <v>0.015228</v>
@@ -15741,7 +15741,7 @@
         </is>
       </c>
       <c r="B1179" t="n">
-        <v>0.258553</v>
+        <v>0.258667</v>
       </c>
       <c r="C1179" t="n">
         <v>0.01269</v>
@@ -15754,7 +15754,7 @@
         </is>
       </c>
       <c r="B1180" t="n">
-        <v>0.312595</v>
+        <v>0.312875</v>
       </c>
       <c r="C1180" t="n">
         <v>0.010152</v>
@@ -15767,7 +15767,7 @@
         </is>
       </c>
       <c r="B1181" t="n">
-        <v>0.326891</v>
+        <v>0.326962</v>
       </c>
       <c r="C1181" t="n">
         <v>0.007614</v>
@@ -15780,7 +15780,7 @@
         </is>
       </c>
       <c r="B1182" t="n">
-        <v>0.339365</v>
+        <v>0.33958</v>
       </c>
       <c r="C1182" t="n">
         <v>0.005076</v>
@@ -15793,7 +15793,7 @@
         </is>
       </c>
       <c r="B1183" t="n">
-        <v>0.474555</v>
+        <v>0.474746</v>
       </c>
       <c r="C1183" t="n">
         <v>0.002538</v>
